--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U881" headerRowCount="1">
-  <autoFilter ref="A1:U881"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U879" headerRowCount="1">
+  <autoFilter ref="A1:U879"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U881"/>
+  <dimension ref="A1:U879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="L137" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M137" s="1" t="inlineStr">
@@ -11977,12 +11977,23 @@
       </c>
       <c r="N137" s="1" t="n"/>
       <c r="O137" s="1" t="n"/>
-      <c r="P137" s="1" t="n"/>
-      <c r="Q137" s="1" t="inlineStr"/>
-      <c r="R137" s="1" t="inlineStr"/>
+      <c r="P137" s="2" t="n">
+        <v>46280.51998788195</v>
+      </c>
+      <c r="Q137" s="1" t="inlineStr">
+        <is>
+          <t>Thaiza Oliveira</t>
+        </is>
+      </c>
+      <c r="R137" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde,
+Para regularizar, precisamos retificar os períodos, entretanto, o cliente não paga taxa eletrônica. Por favor, verificar com o cliente sobre o pagamento da taxa.</t>
+        </is>
+      </c>
       <c r="S137" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T137" s="1" t="n"/>
@@ -15765,7 +15776,7 @@
       </c>
       <c r="N182" s="1" t="n"/>
       <c r="O182" s="2" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="P182" s="1" t="n"/>
       <c r="Q182" s="1" t="inlineStr"/>
@@ -52055,69 +52066,59 @@
     </row>
     <row r="680">
       <c r="A680" s="1" t="n">
-        <v>81296</v>
+        <v>84022</v>
       </c>
       <c r="B680" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C680" s="1" t="inlineStr">
         <is>
-          <t>Outras Cláusulas</t>
+          <t xml:space="preserve">Novo </t>
         </is>
       </c>
       <c r="D680" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E680" s="1" t="inlineStr">
         <is>
-          <t>Providenciar a inclusão do CNAE descrito abaixo na empresa.8630-5/03 - ATIVIDADE MÉDICA AMBULATORIAL RESTRITA A CONSULTAS.Ela irá prestar serviços médicos como Pessoa Jurídica, para Hospitais, UBS, Clínicas e Eventos, conforme encaminhamento da resposta dela, pelo WhatsApp.Valor será o mesmo da última alteração do grupo.</t>
+          <t>Estou tentando usar a ferramenta de fechamento e está com a mensagem: Falta informação de contato de endereço Comercial no cadastro do clienteEmpresa: 6977 - PROTECTION SHIELD LTDA</t>
         </is>
       </c>
       <c r="F680" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G680" s="1" t="n"/>
-      <c r="H680" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
+      <c r="H680" s="1" t="n"/>
       <c r="I680" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J680" s="2" t="n">
-        <v>46225.4866127662</v>
+        <v>46280.50560975695</v>
       </c>
       <c r="K680" s="2" t="n">
-        <v>46255</v>
+        <v>46281</v>
       </c>
       <c r="L680" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M680" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N680" s="2" t="n">
-        <v>46253.38738584491</v>
-      </c>
+          <t>Gisele Rodrigues</t>
+        </is>
+      </c>
+      <c r="N680" s="1" t="n"/>
       <c r="O680" s="1" t="n"/>
       <c r="P680" s="1" t="n"/>
       <c r="Q680" s="1" t="inlineStr"/>
-      <c r="R680" s="1" t="inlineStr">
-        <is>
-          <t>Raisa, para esse processo, será necessário o envio do IPTU e também que seja informado quem será o responsável tecnico perante o CREMESP, enviando-nos inclusive a carteira do CREMESP do responsável.</t>
-        </is>
-      </c>
+      <c r="R680" s="1" t="n"/>
       <c r="S680" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -52128,59 +52129,69 @@
     </row>
     <row r="681">
       <c r="A681" s="1" t="n">
-        <v>83981</v>
+        <v>81296</v>
       </c>
       <c r="B681" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C681" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Outras Cláusulas</t>
         </is>
       </c>
       <c r="D681" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E681" s="1" t="inlineStr">
         <is>
-          <t>3262 - JCV - GNRE de ALPEC - AlagoasConforme solicitação no e-mail anexo, é necessário providenciar o preenchimento do REDAR, emissão da taxa e protocolar do processo junto à SEFAZ/AL.</t>
+          <t>Providenciar a inclusão do CNAE descrito abaixo na empresa.8630-5/03 - ATIVIDADE MÉDICA AMBULATORIAL RESTRITA A CONSULTAS.Ela irá prestar serviços médicos como Pessoa Jurídica, para Hospitais, UBS, Clínicas e Eventos, conforme encaminhamento da resposta dela, pelo WhatsApp.Valor será o mesmo da última alteração do grupo.</t>
         </is>
       </c>
       <c r="F681" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G681" s="1" t="n"/>
-      <c r="H681" s="1" t="n"/>
+      <c r="H681" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
       <c r="I681" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J681" s="2" t="n">
-        <v>46280.38897322916</v>
+        <v>46225.4866127662</v>
       </c>
       <c r="K681" s="2" t="n">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L681" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M681" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
-      <c r="N681" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N681" s="2" t="n">
+        <v>46253.38738584491</v>
+      </c>
       <c r="O681" s="1" t="n"/>
       <c r="P681" s="1" t="n"/>
       <c r="Q681" s="1" t="inlineStr"/>
-      <c r="R681" s="1" t="n"/>
+      <c r="R681" s="1" t="inlineStr">
+        <is>
+          <t>Raisa, para esse processo, será necessário o envio do IPTU e também que seja informado quem será o responsável tecnico perante o CREMESP, enviando-nos inclusive a carteira do CREMESP do responsável.</t>
+        </is>
+      </c>
       <c r="S681" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -52191,16 +52202,16 @@
     </row>
     <row r="682">
       <c r="A682" s="1" t="n">
-        <v>83985</v>
+        <v>83981</v>
       </c>
       <c r="B682" s="1" t="inlineStr">
         <is>
-          <t>Procuração</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C682" s="1" t="inlineStr">
         <is>
-          <t>Fiscalização Federal</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D682" s="1" t="inlineStr">
@@ -52210,7 +52221,7 @@
       </c>
       <c r="E682" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, preciso que vincule a empresa 7041 - PROMOTORAS GYN ao certificado da SDD</t>
+          <t>3262 - JCV - GNRE de ALPEC - AlagoasConforme solicitação no e-mail anexo, é necessário providenciar o preenchimento do REDAR, emissão da taxa e protocolar do processo junto à SEFAZ/AL.</t>
         </is>
       </c>
       <c r="F682" s="1" t="n">
@@ -52224,7 +52235,7 @@
         </is>
       </c>
       <c r="J682" s="2" t="n">
-        <v>46280.41337118056</v>
+        <v>46280.38897322916</v>
       </c>
       <c r="K682" s="2" t="n">
         <v>46282</v>
@@ -52236,7 +52247,7 @@
       </c>
       <c r="M682" s="1" t="inlineStr">
         <is>
-          <t>Gisele Rodrigues</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="N682" s="1" t="n"/>
@@ -59833,7 +59844,7 @@
       </c>
       <c r="I782" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J782" s="2" t="n">
@@ -59844,7 +59855,7 @@
       </c>
       <c r="L782" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M782" s="1" t="inlineStr">
@@ -59852,9 +59863,7 @@
           <t>Ricardo Ferreira</t>
         </is>
       </c>
-      <c r="N782" s="2" t="n">
-        <v>46268.41803993056</v>
-      </c>
+      <c r="N782" s="1" t="n"/>
       <c r="O782" s="1" t="n"/>
       <c r="P782" s="1" t="n"/>
       <c r="Q782" s="1" t="inlineStr"/>
@@ -59868,7 +59877,11 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T782" s="1" t="n"/>
+      <c r="T782" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
       <c r="U782" s="1" t="inlineStr"/>
     </row>
     <row r="783">
@@ -63246,7 +63259,7 @@
       </c>
       <c r="L828" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M828" s="1" t="inlineStr">
@@ -63254,7 +63267,9 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N828" s="1" t="n"/>
+      <c r="N828" s="2" t="n">
+        <v>46267.54541188657</v>
+      </c>
       <c r="O828" s="2" t="n">
         <v>46283</v>
       </c>
@@ -64898,7 +64913,7 @@
       </c>
       <c r="L849" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M849" s="1" t="inlineStr">
@@ -64906,7 +64921,9 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N849" s="1" t="n"/>
+      <c r="N849" s="2" t="n">
+        <v>46255.4431121875</v>
+      </c>
       <c r="O849" s="2" t="n">
         <v>46283</v>
       </c>
@@ -65198,7 +65215,7 @@
       </c>
       <c r="L853" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M853" s="1" t="inlineStr">
@@ -65206,7 +65223,9 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N853" s="1" t="n"/>
+      <c r="N853" s="2" t="n">
+        <v>46255.48540517361</v>
+      </c>
       <c r="O853" s="1" t="n"/>
       <c r="P853" s="1" t="n"/>
       <c r="Q853" s="1" t="inlineStr"/>
@@ -65298,7 +65317,7 @@
     </row>
     <row r="855">
       <c r="A855" s="1" t="n">
-        <v>81052</v>
+        <v>81055</v>
       </c>
       <c r="B855" s="1" t="inlineStr">
         <is>
@@ -65317,7 +65336,7 @@
       </c>
       <c r="E855" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
         </is>
       </c>
       <c r="F855" s="1" t="n">
@@ -65335,7 +65354,7 @@
         </is>
       </c>
       <c r="J855" s="2" t="n">
-        <v>46218.38736744213</v>
+        <v>46218.40379614583</v>
       </c>
       <c r="K855" s="2" t="n">
         <v>46219</v>
@@ -65351,7 +65370,7 @@
         </is>
       </c>
       <c r="N855" s="2" t="n">
-        <v>46219.50471747686</v>
+        <v>46219.50607847222</v>
       </c>
       <c r="O855" s="2" t="n">
         <v>46283</v>
@@ -65360,7 +65379,7 @@
       <c r="Q855" s="1" t="inlineStr"/>
       <c r="R855" s="1" t="inlineStr">
         <is>
-          <t>cobramos os documentos do antigo contador.</t>
+          <t>Aguardando retorno dos dados do contador</t>
         </is>
       </c>
       <c r="S855" s="1" t="inlineStr">
@@ -65373,74 +65392,83 @@
     </row>
     <row r="856">
       <c r="A856" s="1" t="n">
-        <v>81055</v>
+        <v>82881</v>
       </c>
       <c r="B856" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Cadastro de Produtos</t>
         </is>
       </c>
       <c r="C856" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Cadastro de produtos</t>
         </is>
       </c>
       <c r="D856" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E856" s="1" t="inlineStr">
         <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+          <t xml:space="preserve">Prezados, bom dia.Estou formalizando, via chamado, a solicitação de revisão do cadastro de produtos da empresa.Em anexo, encaminho o e-mail com a tratativa referente ao assunto. </t>
         </is>
       </c>
       <c r="F856" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G856" s="1" t="n"/>
+        <v>6336</v>
+      </c>
+      <c r="G856" s="1" t="inlineStr">
+        <is>
+          <t>BEL LINE COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
       <c r="H856" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Fernanda Bertunes</t>
         </is>
       </c>
       <c r="I856" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>CADASTRO DE PRODUTOS</t>
         </is>
       </c>
       <c r="J856" s="2" t="n">
-        <v>46218.40379614583</v>
+        <v>46258.42822939815</v>
       </c>
       <c r="K856" s="2" t="n">
-        <v>46219</v>
+        <v>46288</v>
       </c>
       <c r="L856" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M856" s="1" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
-      <c r="N856" s="2" t="n">
-        <v>46219.50607847222</v>
-      </c>
+          <t>Lohany Martins</t>
+        </is>
+      </c>
+      <c r="N856" s="1" t="n"/>
       <c r="O856" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="P856" s="1" t="n"/>
-      <c r="Q856" s="1" t="inlineStr"/>
+        <v>46269</v>
+      </c>
+      <c r="P856" s="2" t="n">
+        <v>46265.43684837963</v>
+      </c>
+      <c r="Q856" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Bertunes</t>
+        </is>
+      </c>
       <c r="R856" s="1" t="inlineStr">
         <is>
-          <t>Aguardando retorno dos dados do contador</t>
+          <t>Bom dia 
+Cadastro analisado e enviado por email</t>
         </is>
       </c>
       <c r="S856" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T856" s="1" t="n"/>
@@ -65448,69 +65476,72 @@
     </row>
     <row r="857">
       <c r="A857" s="1" t="n">
-        <v>82430</v>
+        <v>81757</v>
       </c>
       <c r="B857" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Cadastro de Produtos</t>
         </is>
       </c>
       <c r="C857" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Cadastro de produtos</t>
         </is>
       </c>
       <c r="D857" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E857" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia!Segue checklist atualizado da empresa 7007 - SANTOS&amp;DIAN Itens dispensáveis, por gentileza, sinalizar. </t>
+          <t>6945 - BRASIL DISTRIBUIDORA DE PEÇAS - CADASTRO DE INTENS, PARA INCLUSÃO DE INFORMAÇÕES TRIBUTÁRIAS.Por favor dar início na inclusão das informações tributarias no cadastro de itens do clienteAtt.Vander</t>
         </is>
       </c>
       <c r="F857" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G857" s="1" t="n"/>
+        <v>6945</v>
+      </c>
+      <c r="G857" s="1" t="inlineStr">
+        <is>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+        </is>
+      </c>
       <c r="H857" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Fernanda Bertunes</t>
         </is>
       </c>
       <c r="I857" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>CADASTRO DE PRODUTOS</t>
         </is>
       </c>
       <c r="J857" s="2" t="n">
-        <v>46248.47311612269</v>
+        <v>46237.52224869213</v>
       </c>
       <c r="K857" s="2" t="n">
-        <v>46251</v>
+        <v>46267</v>
       </c>
       <c r="L857" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M857" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
-        </is>
-      </c>
-      <c r="N857" s="2" t="n">
-        <v>46253.38669748843</v>
-      </c>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="N857" s="1" t="n"/>
       <c r="O857" s="2" t="n">
-        <v>46283</v>
+        <v>46267</v>
       </c>
       <c r="P857" s="1" t="n"/>
       <c r="Q857" s="1" t="inlineStr"/>
       <c r="R857" s="1" t="inlineStr">
         <is>
-          <t>cobramos novamente o antigo contador</t>
+          <t xml:space="preserve">Por favor , enviar a planilha de cadastro no layout padrão para analise 
+Enviar a planilha no layout correto e abrir novo chamado anexando email </t>
         </is>
       </c>
       <c r="S857" s="1" t="inlineStr">
@@ -65523,7 +65554,7 @@
     </row>
     <row r="858">
       <c r="A858" s="1" t="n">
-        <v>82881</v>
+        <v>82777</v>
       </c>
       <c r="B858" s="1" t="inlineStr">
         <is>
@@ -65537,20 +65568,20 @@
       </c>
       <c r="D858" s="1" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="E858" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados, bom dia.Estou formalizando, via chamado, a solicitação de revisão do cadastro de produtos da empresa.Em anexo, encaminho o e-mail com a tratativa referente ao assunto. </t>
+          <t>Prezados, bom dia!Enviei um e-mail sobre a solicitação da Jéssica sobre o cliente JEM TRUCK.Por favor verificar e validar se chegam a mesma conclusão antes de envio ao cliente.</t>
         </is>
       </c>
       <c r="F858" s="1" t="n">
-        <v>6336</v>
+        <v>6979</v>
       </c>
       <c r="G858" s="1" t="inlineStr">
         <is>
-          <t>BEL LINE COMERCIO DE COSMETICOS LTDA</t>
+          <t xml:space="preserve">JEM TRUCK TRANSPORTE DE CARGAS E TERRAPLANAGEM LTDA </t>
         </is>
       </c>
       <c r="H858" s="1" t="inlineStr">
@@ -65564,10 +65595,10 @@
         </is>
       </c>
       <c r="J858" s="2" t="n">
-        <v>46258.42822939815</v>
+        <v>46255.4226837963</v>
       </c>
       <c r="K858" s="2" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="L858" s="1" t="inlineStr">
         <is>
@@ -65576,15 +65607,15 @@
       </c>
       <c r="M858" s="1" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Maicon Costa</t>
         </is>
       </c>
       <c r="N858" s="1" t="n"/>
       <c r="O858" s="2" t="n">
-        <v>46269</v>
+        <v>46267</v>
       </c>
       <c r="P858" s="2" t="n">
-        <v>46265.43684837963</v>
+        <v>46262.63475393518</v>
       </c>
       <c r="Q858" s="1" t="inlineStr">
         <is>
@@ -65592,174 +65623,181 @@
         </is>
       </c>
       <c r="R858" s="1" t="inlineStr">
-        <is>
-          <t>Bom dia 
-Cadastro analisado e enviado por email</t>
-        </is>
-      </c>
-      <c r="S858" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T858" s="1" t="n"/>
-      <c r="U858" s="1" t="inlineStr"/>
-    </row>
-    <row r="859">
-      <c r="A859" s="1" t="n">
-        <v>81757</v>
-      </c>
-      <c r="B859" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro de Produtos</t>
-        </is>
-      </c>
-      <c r="C859" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro de produtos</t>
-        </is>
-      </c>
-      <c r="D859" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E859" s="1" t="inlineStr">
-        <is>
-          <t>6945 - BRASIL DISTRIBUIDORA DE PEÇAS - CADASTRO DE INTENS, PARA INCLUSÃO DE INFORMAÇÕES TRIBUTÁRIAS.Por favor dar início na inclusão das informações tributarias no cadastro de itens do clienteAtt.Vander</t>
-        </is>
-      </c>
-      <c r="F859" s="1" t="n">
-        <v>6945</v>
-      </c>
-      <c r="G859" s="1" t="inlineStr">
-        <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
-        </is>
-      </c>
-      <c r="H859" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
-      <c r="I859" s="1" t="inlineStr">
-        <is>
-          <t>CADASTRO DE PRODUTOS</t>
-        </is>
-      </c>
-      <c r="J859" s="2" t="n">
-        <v>46237.52224869213</v>
-      </c>
-      <c r="K859" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="L859" s="1" t="inlineStr">
-        <is>
-          <t>Devolvido</t>
-        </is>
-      </c>
-      <c r="M859" s="1" t="inlineStr">
-        <is>
-          <t>Vander Silva</t>
-        </is>
-      </c>
-      <c r="N859" s="1" t="n"/>
-      <c r="O859" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="P859" s="1" t="n"/>
-      <c r="Q859" s="1" t="inlineStr"/>
-      <c r="R859" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por favor , enviar a planilha de cadastro no layout padrão para analise 
-Enviar a planilha no layout correto e abrir novo chamado anexando email </t>
-        </is>
-      </c>
-      <c r="S859" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T859" s="1" t="n"/>
-      <c r="U859" s="1" t="inlineStr"/>
-    </row>
-    <row r="860">
-      <c r="A860" s="1" t="n">
-        <v>82777</v>
-      </c>
-      <c r="B860" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro de Produtos</t>
-        </is>
-      </c>
-      <c r="C860" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro de produtos</t>
-        </is>
-      </c>
-      <c r="D860" s="1" t="inlineStr">
-        <is>
-          <t>RJ - GC</t>
-        </is>
-      </c>
-      <c r="E860" s="1" t="inlineStr">
-        <is>
-          <t>Prezados, bom dia!Enviei um e-mail sobre a solicitação da Jéssica sobre o cliente JEM TRUCK.Por favor verificar e validar se chegam a mesma conclusão antes de envio ao cliente.</t>
-        </is>
-      </c>
-      <c r="F860" s="1" t="n">
-        <v>6979</v>
-      </c>
-      <c r="G860" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JEM TRUCK TRANSPORTE DE CARGAS E TERRAPLANAGEM LTDA </t>
-        </is>
-      </c>
-      <c r="H860" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
-      <c r="I860" s="1" t="inlineStr">
-        <is>
-          <t>CADASTRO DE PRODUTOS</t>
-        </is>
-      </c>
-      <c r="J860" s="2" t="n">
-        <v>46255.4226837963</v>
-      </c>
-      <c r="K860" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="L860" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M860" s="1" t="inlineStr">
-        <is>
-          <t>Maicon Costa</t>
-        </is>
-      </c>
-      <c r="N860" s="1" t="n"/>
-      <c r="O860" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="P860" s="2" t="n">
-        <v>46262.63475393518</v>
-      </c>
-      <c r="Q860" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
-      <c r="R860" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Boa tarde 
 Informação já respondida por email
 Assuntos sobre duvidas tributarias, não deve ser aberto chamado </t>
         </is>
       </c>
+      <c r="S858" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T858" s="1" t="n"/>
+      <c r="U858" s="1" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="1" t="n">
+        <v>82815</v>
+      </c>
+      <c r="B859" s="1" t="inlineStr">
+        <is>
+          <t>Cadastro de Produtos</t>
+        </is>
+      </c>
+      <c r="C859" s="1" t="inlineStr">
+        <is>
+          <t>Cadastro de produtos</t>
+        </is>
+      </c>
+      <c r="D859" s="1" t="inlineStr">
+        <is>
+          <t>RJ - GC ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E859" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde, segue em anexo cadastro de produtos da empresa para validação do CBS/IBS.</t>
+        </is>
+      </c>
+      <c r="F859" s="1" t="n">
+        <v>5789</v>
+      </c>
+      <c r="G859" s="1" t="inlineStr">
+        <is>
+          <t>ACE FRUIT COMERCIO DE ALIMENTOS LTDA (Filial 2)</t>
+        </is>
+      </c>
+      <c r="H859" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Bertunes</t>
+        </is>
+      </c>
+      <c r="I859" s="1" t="inlineStr">
+        <is>
+          <t>CADASTRO DE PRODUTOS</t>
+        </is>
+      </c>
+      <c r="J859" s="2" t="n">
+        <v>46255.67638510417</v>
+      </c>
+      <c r="K859" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="L859" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M859" s="1" t="inlineStr">
+        <is>
+          <t>Lohany Martins</t>
+        </is>
+      </c>
+      <c r="N859" s="2" t="n">
+        <v>46262.65963637731</v>
+      </c>
+      <c r="O859" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="P859" s="2" t="n">
+        <v>46266.5932252662</v>
+      </c>
+      <c r="Q859" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Bertunes</t>
+        </is>
+      </c>
+      <c r="R859" s="1" t="inlineStr">
+        <is>
+          <t>Em fila para atendimento</t>
+        </is>
+      </c>
+      <c r="S859" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T859" s="1" t="n"/>
+      <c r="U859" s="1" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="1" t="n">
+        <v>82817</v>
+      </c>
+      <c r="B860" s="1" t="inlineStr">
+        <is>
+          <t>Cadastro de Produtos</t>
+        </is>
+      </c>
+      <c r="C860" s="1" t="inlineStr">
+        <is>
+          <t>Cadastro de produtos</t>
+        </is>
+      </c>
+      <c r="D860" s="1" t="inlineStr">
+        <is>
+          <t>RJ - GC ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E860" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde, segue em anexo cadastro de produtos da empresa para validação do CBS/IBS.</t>
+        </is>
+      </c>
+      <c r="F860" s="1" t="n">
+        <v>3808</v>
+      </c>
+      <c r="G860" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mercearia Doce Bom Ltda. </t>
+        </is>
+      </c>
+      <c r="H860" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Bertunes</t>
+        </is>
+      </c>
+      <c r="I860" s="1" t="inlineStr">
+        <is>
+          <t>CADASTRO DE PRODUTOS</t>
+        </is>
+      </c>
+      <c r="J860" s="2" t="n">
+        <v>46255.6791724537</v>
+      </c>
+      <c r="K860" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="L860" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M860" s="1" t="inlineStr">
+        <is>
+          <t>Lohany Martins</t>
+        </is>
+      </c>
+      <c r="N860" s="1" t="n"/>
+      <c r="O860" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="P860" s="2" t="n">
+        <v>46262.65880697917</v>
+      </c>
+      <c r="Q860" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Bertunes</t>
+        </is>
+      </c>
+      <c r="R860" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde
+Cadastro analisado e devolvido por email em 24/08</t>
+        </is>
+      </c>
       <c r="S860" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -65770,7 +65808,7 @@
     </row>
     <row r="861">
       <c r="A861" s="1" t="n">
-        <v>82815</v>
+        <v>82818</v>
       </c>
       <c r="B861" s="1" t="inlineStr">
         <is>
@@ -65793,11 +65831,11 @@
         </is>
       </c>
       <c r="F861" s="1" t="n">
-        <v>5789</v>
+        <v>4222</v>
       </c>
       <c r="G861" s="1" t="inlineStr">
         <is>
-          <t>ACE FRUIT COMERCIO DE ALIMENTOS LTDA (Filial 2)</t>
+          <t>STOCK FRANGO DISTRIBUIDORA DE GÊNEROS ALIMENTÍCIOS E TRANSPORTE LTDA</t>
         </is>
       </c>
       <c r="H861" s="1" t="inlineStr">
@@ -65811,7 +65849,7 @@
         </is>
       </c>
       <c r="J861" s="2" t="n">
-        <v>46255.67638510417</v>
+        <v>46255.67973850694</v>
       </c>
       <c r="K861" s="2" t="n">
         <v>46287</v>
@@ -65826,14 +65864,12 @@
           <t>Lohany Martins</t>
         </is>
       </c>
-      <c r="N861" s="2" t="n">
-        <v>46262.65963637731</v>
-      </c>
+      <c r="N861" s="1" t="n"/>
       <c r="O861" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="P861" s="2" t="n">
-        <v>46266.5932252662</v>
+        <v>46262.65957361111</v>
       </c>
       <c r="Q861" s="1" t="inlineStr">
         <is>
@@ -65842,7 +65878,8 @@
       </c>
       <c r="R861" s="1" t="inlineStr">
         <is>
-          <t>Em fila para atendimento</t>
+          <t>Boa tarde 
+Cadastro analisado e enviado por email em 24/08</t>
         </is>
       </c>
       <c r="S861" s="1" t="inlineStr">
@@ -65855,7 +65892,7 @@
     </row>
     <row r="862">
       <c r="A862" s="1" t="n">
-        <v>82817</v>
+        <v>82819</v>
       </c>
       <c r="B862" s="1" t="inlineStr">
         <is>
@@ -65878,11 +65915,11 @@
         </is>
       </c>
       <c r="F862" s="1" t="n">
-        <v>3808</v>
+        <v>6529</v>
       </c>
       <c r="G862" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercearia Doce Bom Ltda. </t>
+          <t>VALLEMAR MERCADO LTDA</t>
         </is>
       </c>
       <c r="H862" s="1" t="inlineStr">
@@ -65896,7 +65933,7 @@
         </is>
       </c>
       <c r="J862" s="2" t="n">
-        <v>46255.6791724537</v>
+        <v>46255.68034375</v>
       </c>
       <c r="K862" s="2" t="n">
         <v>46287</v>
@@ -65916,7 +65953,7 @@
         <v>46269</v>
       </c>
       <c r="P862" s="2" t="n">
-        <v>46262.65880697917</v>
+        <v>46262.66115917824</v>
       </c>
       <c r="Q862" s="1" t="inlineStr">
         <is>
@@ -65925,7 +65962,7 @@
       </c>
       <c r="R862" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde
+          <t>Boa tarde 
 Cadastro analisado e devolvido por email em 24/08</t>
         </is>
       </c>
@@ -65939,7 +65976,7 @@
     </row>
     <row r="863">
       <c r="A863" s="1" t="n">
-        <v>82818</v>
+        <v>82901</v>
       </c>
       <c r="B863" s="1" t="inlineStr">
         <is>
@@ -65962,11 +65999,11 @@
         </is>
       </c>
       <c r="F863" s="1" t="n">
-        <v>4222</v>
+        <v>4604</v>
       </c>
       <c r="G863" s="1" t="inlineStr">
         <is>
-          <t>STOCK FRANGO DISTRIBUIDORA DE GÊNEROS ALIMENTÍCIOS E TRANSPORTE LTDA</t>
+          <t>H P T COMERCIO E INDUSTRIA DE MÓVEIS LTDA</t>
         </is>
       </c>
       <c r="H863" s="1" t="inlineStr">
@@ -65980,10 +66017,10 @@
         </is>
       </c>
       <c r="J863" s="2" t="n">
-        <v>46255.67973850694</v>
+        <v>46258.64696304398</v>
       </c>
       <c r="K863" s="2" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="L863" s="1" t="inlineStr">
         <is>
@@ -65995,12 +66032,14 @@
           <t>Lohany Martins</t>
         </is>
       </c>
-      <c r="N863" s="1" t="n"/>
+      <c r="N863" s="2" t="n">
+        <v>46265.43650153935</v>
+      </c>
       <c r="O863" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="P863" s="2" t="n">
-        <v>46262.65957361111</v>
+        <v>46266.6452650463</v>
       </c>
       <c r="Q863" s="1" t="inlineStr">
         <is>
@@ -66009,8 +66048,7 @@
       </c>
       <c r="R863" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde 
-Cadastro analisado e enviado por email em 24/08</t>
+          <t>Na fila para atendimento</t>
         </is>
       </c>
       <c r="S863" s="1" t="inlineStr">
@@ -66023,7 +66061,7 @@
     </row>
     <row r="864">
       <c r="A864" s="1" t="n">
-        <v>82819</v>
+        <v>82924</v>
       </c>
       <c r="B864" s="1" t="inlineStr">
         <is>
@@ -66046,11 +66084,11 @@
         </is>
       </c>
       <c r="F864" s="1" t="n">
-        <v>6529</v>
+        <v>5739</v>
       </c>
       <c r="G864" s="1" t="inlineStr">
         <is>
-          <t>VALLEMAR MERCADO LTDA</t>
+          <t>GOLD REAL MOVEIS LTDA</t>
         </is>
       </c>
       <c r="H864" s="1" t="inlineStr">
@@ -66064,10 +66102,10 @@
         </is>
       </c>
       <c r="J864" s="2" t="n">
-        <v>46255.68034375</v>
+        <v>46258.73919143518</v>
       </c>
       <c r="K864" s="2" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="L864" s="1" t="inlineStr">
         <is>
@@ -66079,12 +66117,14 @@
           <t>Lohany Martins</t>
         </is>
       </c>
-      <c r="N864" s="1" t="n"/>
+      <c r="N864" s="2" t="n">
+        <v>46265.44787318287</v>
+      </c>
       <c r="O864" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="P864" s="2" t="n">
-        <v>46262.66115917824</v>
+        <v>46266.64227896991</v>
       </c>
       <c r="Q864" s="1" t="inlineStr">
         <is>
@@ -66093,8 +66133,7 @@
       </c>
       <c r="R864" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde 
-Cadastro analisado e devolvido por email em 24/08</t>
+          <t xml:space="preserve">Em fila de atendimento </t>
         </is>
       </c>
       <c r="S864" s="1" t="inlineStr">
@@ -66107,7 +66146,7 @@
     </row>
     <row r="865">
       <c r="A865" s="1" t="n">
-        <v>82901</v>
+        <v>82951</v>
       </c>
       <c r="B865" s="1" t="inlineStr">
         <is>
@@ -66126,15 +66165,15 @@
       </c>
       <c r="E865" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, segue em anexo cadastro de produtos da empresa para validação do CBS/IBS.</t>
+          <t>Bom dia, segue em anexo cadastro de produtos da empresa para validação do CBS/IBS.</t>
         </is>
       </c>
       <c r="F865" s="1" t="n">
-        <v>4604</v>
+        <v>3959</v>
       </c>
       <c r="G865" s="1" t="inlineStr">
         <is>
-          <t>H P T COMERCIO E INDUSTRIA DE MÓVEIS LTDA</t>
+          <t>ALDEBARAN DISTRIBUIDORA E COMÉRCIO DE MATERIAL MÉDICO E HOSPITALAR LTDA</t>
         </is>
       </c>
       <c r="H865" s="1" t="inlineStr">
@@ -66148,14 +66187,14 @@
         </is>
       </c>
       <c r="J865" s="2" t="n">
-        <v>46258.64696304398</v>
+        <v>46259.43735</v>
       </c>
       <c r="K865" s="2" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="L865" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M865" s="1" t="inlineStr">
@@ -66164,27 +66203,21 @@
         </is>
       </c>
       <c r="N865" s="2" t="n">
-        <v>46265.43650153935</v>
+        <v>46265.45876041667</v>
       </c>
       <c r="O865" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="P865" s="2" t="n">
-        <v>46266.6452650463</v>
-      </c>
-      <c r="Q865" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="P865" s="1" t="n"/>
+      <c r="Q865" s="1" t="inlineStr"/>
       <c r="R865" s="1" t="inlineStr">
         <is>
-          <t>Na fila para atendimento</t>
+          <t xml:space="preserve">Em fila de atendimento </t>
         </is>
       </c>
       <c r="S865" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T865" s="1" t="n"/>
@@ -66192,7 +66225,7 @@
     </row>
     <row r="866">
       <c r="A866" s="1" t="n">
-        <v>82924</v>
+        <v>83005</v>
       </c>
       <c r="B866" s="1" t="inlineStr">
         <is>
@@ -66215,11 +66248,11 @@
         </is>
       </c>
       <c r="F866" s="1" t="n">
-        <v>5739</v>
+        <v>6523</v>
       </c>
       <c r="G866" s="1" t="inlineStr">
         <is>
-          <t>GOLD REAL MOVEIS LTDA</t>
+          <t>PARADA DOS PAES LTDA</t>
         </is>
       </c>
       <c r="H866" s="1" t="inlineStr">
@@ -66233,10 +66266,10 @@
         </is>
       </c>
       <c r="J866" s="2" t="n">
-        <v>46258.73919143518</v>
+        <v>46259.70646643519</v>
       </c>
       <c r="K866" s="2" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="L866" s="1" t="inlineStr">
         <is>
@@ -66249,13 +66282,13 @@
         </is>
       </c>
       <c r="N866" s="2" t="n">
-        <v>46265.44787318287</v>
+        <v>46265.51365540509</v>
       </c>
       <c r="O866" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="P866" s="2" t="n">
-        <v>46266.64227896991</v>
+        <v>46268.69805833334</v>
       </c>
       <c r="Q866" s="1" t="inlineStr">
         <is>
@@ -66264,7 +66297,7 @@
       </c>
       <c r="R866" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Em fila de atendimento </t>
+          <t>Em fila de atendimento</t>
         </is>
       </c>
       <c r="S866" s="1" t="inlineStr">
@@ -66277,34 +66310,34 @@
     </row>
     <row r="867">
       <c r="A867" s="1" t="n">
-        <v>82951</v>
+        <v>82502</v>
       </c>
       <c r="B867" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Produtos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C867" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de produtos</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D867" s="1" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E867" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, segue em anexo cadastro de produtos da empresa para validação do CBS/IBS.</t>
+          <t>6070	MEGACAR	Cliente informou que já enviou o cadastro de produto, por favor verificar se já foi revisado e devolvido para o cliente. Como esta o andamento?</t>
         </is>
       </c>
       <c r="F867" s="1" t="n">
-        <v>3959</v>
+        <v>6070</v>
       </c>
       <c r="G867" s="1" t="inlineStr">
         <is>
-          <t>ALDEBARAN DISTRIBUIDORA E COMÉRCIO DE MATERIAL MÉDICO E HOSPITALAR LTDA</t>
+          <t xml:space="preserve">MEGACAR DISTRIBUIDORA AUTOMOTIVA LTDA </t>
         </is>
       </c>
       <c r="H867" s="1" t="inlineStr">
@@ -66318,37 +66351,40 @@
         </is>
       </c>
       <c r="J867" s="2" t="n">
-        <v>46259.43735</v>
+        <v>46251.42708194444</v>
       </c>
       <c r="K867" s="2" t="n">
-        <v>46290</v>
+        <v>46258</v>
       </c>
       <c r="L867" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M867" s="1" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
-        </is>
-      </c>
-      <c r="N867" s="2" t="n">
-        <v>46265.45876041667</v>
-      </c>
-      <c r="O867" s="2" t="n">
-        <v>46273</v>
-      </c>
-      <c r="P867" s="1" t="n"/>
-      <c r="Q867" s="1" t="inlineStr"/>
+          <t>Leticia Queiroz</t>
+        </is>
+      </c>
+      <c r="N867" s="1" t="n"/>
+      <c r="O867" s="1" t="n"/>
+      <c r="P867" s="2" t="n">
+        <v>46261.54547850695</v>
+      </c>
+      <c r="Q867" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Bertunes</t>
+        </is>
+      </c>
       <c r="R867" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Em fila de atendimento </t>
+          <t xml:space="preserve">Em 2026, não recebemos nenhuma solicitação referente a esse cliente 
+Por favor, solicitar o cadastro de produtos atualizado, enviar por email para @integracaocadastroechat e abrir novo chamado </t>
         </is>
       </c>
       <c r="S867" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T867" s="1" t="n"/>
@@ -66356,7 +66392,7 @@
     </row>
     <row r="868">
       <c r="A868" s="1" t="n">
-        <v>83005</v>
+        <v>83231</v>
       </c>
       <c r="B868" s="1" t="inlineStr">
         <is>
@@ -66370,20 +66406,20 @@
       </c>
       <c r="D868" s="1" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E868" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, segue em anexo cadastro de produtos da empresa para validação do CBS/IBS.</t>
+          <t>Por gentileza, realizar a analise do cadastro dos produtos anexo.</t>
         </is>
       </c>
       <c r="F868" s="1" t="n">
-        <v>6523</v>
+        <v>4469</v>
       </c>
       <c r="G868" s="1" t="inlineStr">
         <is>
-          <t>PARADA DOS PAES LTDA</t>
+          <t xml:space="preserve">REI DOS GRÃOS LTDA </t>
         </is>
       </c>
       <c r="H868" s="1" t="inlineStr">
@@ -66397,10 +66433,10 @@
         </is>
       </c>
       <c r="J868" s="2" t="n">
-        <v>46259.70646643519</v>
+        <v>46262.59248885416</v>
       </c>
       <c r="K868" s="2" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="L868" s="1" t="inlineStr">
         <is>
@@ -66409,17 +66445,15 @@
       </c>
       <c r="M868" s="1" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="N868" s="2" t="n">
-        <v>46265.51365540509</v>
-      </c>
-      <c r="O868" s="2" t="n">
-        <v>46273</v>
-      </c>
+        <v>46265.59963434028</v>
+      </c>
+      <c r="O868" s="1" t="n"/>
       <c r="P868" s="2" t="n">
-        <v>46268.69805833334</v>
+        <v>46269.6534278125</v>
       </c>
       <c r="Q868" s="1" t="inlineStr">
         <is>
@@ -66428,7 +66462,8 @@
       </c>
       <c r="R868" s="1" t="inlineStr">
         <is>
-          <t>Em fila de atendimento</t>
+          <t xml:space="preserve">Em fila de atendimento
+Por favor sempre anexar o email no chamado </t>
         </is>
       </c>
       <c r="S868" s="1" t="inlineStr">
@@ -66441,34 +66476,34 @@
     </row>
     <row r="869">
       <c r="A869" s="1" t="n">
-        <v>82502</v>
+        <v>83139</v>
       </c>
       <c r="B869" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Cadastro de Produtos</t>
         </is>
       </c>
       <c r="C869" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Cadastro de produtos</t>
         </is>
       </c>
       <c r="D869" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E869" s="1" t="inlineStr">
         <is>
-          <t>6070	MEGACAR	Cliente informou que já enviou o cadastro de produto, por favor verificar se já foi revisado e devolvido para o cliente. Como esta o andamento?</t>
+          <t>Prezados, boa tarde! Segue anexo e-mail enviado com a planilha de cadastro de produtos da empresa.</t>
         </is>
       </c>
       <c r="F869" s="1" t="n">
-        <v>6070</v>
+        <v>6049</v>
       </c>
       <c r="G869" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEGACAR DISTRIBUIDORA AUTOMOTIVA LTDA </t>
+          <t>ESTACAO DO PEIXE RESTAURANTE LTDA</t>
         </is>
       </c>
       <c r="H869" s="1" t="inlineStr">
@@ -66482,40 +66517,35 @@
         </is>
       </c>
       <c r="J869" s="2" t="n">
-        <v>46251.42708194444</v>
+        <v>46261.59434112268</v>
       </c>
       <c r="K869" s="2" t="n">
-        <v>46258</v>
+        <v>46294</v>
       </c>
       <c r="L869" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M869" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N869" s="1" t="n"/>
+          <t>Amanda Mesquita</t>
+        </is>
+      </c>
+      <c r="N869" s="2" t="n">
+        <v>46265.60815690972</v>
+      </c>
       <c r="O869" s="1" t="n"/>
-      <c r="P869" s="2" t="n">
-        <v>46261.54547850695</v>
-      </c>
-      <c r="Q869" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
+      <c r="P869" s="1" t="n"/>
+      <c r="Q869" s="1" t="inlineStr"/>
       <c r="R869" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Em 2026, não recebemos nenhuma solicitação referente a esse cliente 
-Por favor, solicitar o cadastro de produtos atualizado, enviar por email para @integracaocadastroechat e abrir novo chamado </t>
+          <t>Em fila de atendimento</t>
         </is>
       </c>
       <c r="S869" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T869" s="1" t="n"/>
@@ -66523,7 +66553,7 @@
     </row>
     <row r="870">
       <c r="A870" s="1" t="n">
-        <v>83231</v>
+        <v>83262</v>
       </c>
       <c r="B870" s="1" t="inlineStr">
         <is>
@@ -66537,20 +66567,20 @@
       </c>
       <c r="D870" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E870" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, realizar a analise do cadastro dos produtos anexo.</t>
+          <t xml:space="preserve">Prezados, bom dia! Segue e-mail enviado com a planilha de cadastro de produtos. </t>
         </is>
       </c>
       <c r="F870" s="1" t="n">
-        <v>4469</v>
+        <v>6540</v>
       </c>
       <c r="G870" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">REI DOS GRÃOS LTDA </t>
+          <t>MERCADINHO BAMBINA LTDA</t>
         </is>
       </c>
       <c r="H870" s="1" t="inlineStr">
@@ -66564,10 +66594,10 @@
         </is>
       </c>
       <c r="J870" s="2" t="n">
-        <v>46262.59248885416</v>
+        <v>46265.4616653125</v>
       </c>
       <c r="K870" s="2" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="L870" s="1" t="inlineStr">
         <is>
@@ -66576,15 +66606,15 @@
       </c>
       <c r="M870" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Amanda Mesquita</t>
         </is>
       </c>
       <c r="N870" s="2" t="n">
-        <v>46265.59963434028</v>
+        <v>46265.62414548611</v>
       </c>
       <c r="O870" s="1" t="n"/>
       <c r="P870" s="2" t="n">
-        <v>46269.6534278125</v>
+        <v>46276.71389502315</v>
       </c>
       <c r="Q870" s="1" t="inlineStr">
         <is>
@@ -66593,8 +66623,7 @@
       </c>
       <c r="R870" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Em fila de atendimento
-Por favor sempre anexar o email no chamado </t>
+          <t>Em fila de atendimento</t>
         </is>
       </c>
       <c r="S870" s="1" t="inlineStr">
@@ -66607,7 +66636,7 @@
     </row>
     <row r="871">
       <c r="A871" s="1" t="n">
-        <v>83139</v>
+        <v>83367</v>
       </c>
       <c r="B871" s="1" t="inlineStr">
         <is>
@@ -66626,15 +66655,15 @@
       </c>
       <c r="E871" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tarde! Segue anexo e-mail enviado com a planilha de cadastro de produtos da empresa.</t>
+          <t>Prezados, boa tarde!Segue em anexo cadastro de produtos da empresa 5789 – ACE FRUIT para validação do CBS/IBS.</t>
         </is>
       </c>
       <c r="F871" s="1" t="n">
-        <v>6049</v>
+        <v>5789</v>
       </c>
       <c r="G871" s="1" t="inlineStr">
         <is>
-          <t>ESTACAO DO PEIXE RESTAURANTE LTDA</t>
+          <t>ACE FRUIT COMERCIO DE ALIMENTOS LTDA (Filial 2)</t>
         </is>
       </c>
       <c r="H871" s="1" t="inlineStr">
@@ -66648,10 +66677,10 @@
         </is>
       </c>
       <c r="J871" s="2" t="n">
-        <v>46261.59434112268</v>
+        <v>46266.64626565972</v>
       </c>
       <c r="K871" s="2" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="L871" s="1" t="inlineStr">
         <is>
@@ -66660,18 +66689,18 @@
       </c>
       <c r="M871" s="1" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Lohany Martins</t>
         </is>
       </c>
       <c r="N871" s="2" t="n">
-        <v>46265.60815690972</v>
+        <v>46269.66462141203</v>
       </c>
       <c r="O871" s="1" t="n"/>
       <c r="P871" s="1" t="n"/>
       <c r="Q871" s="1" t="inlineStr"/>
       <c r="R871" s="1" t="inlineStr">
         <is>
-          <t>Em fila de atendimento</t>
+          <t>Em fila para atendimento</t>
         </is>
       </c>
       <c r="S871" s="1" t="inlineStr">
@@ -66684,7 +66713,7 @@
     </row>
     <row r="872">
       <c r="A872" s="1" t="n">
-        <v>83262</v>
+        <v>83429</v>
       </c>
       <c r="B872" s="1" t="inlineStr">
         <is>
@@ -66703,15 +66732,15 @@
       </c>
       <c r="E872" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados, bom dia! Segue e-mail enviado com a planilha de cadastro de produtos. </t>
+          <t xml:space="preserve">Prezados, boa tarde!Segue novamente planilha de IBS/CBS da empresa 3965 - TUTTI DELI, ela já foi enviada anteriormente o número do chamado antigo é 82784, porém ela foi retornada mesmo estando completa. Na planilha consta NCM, Descrição e EAN. </t>
         </is>
       </c>
       <c r="F872" s="1" t="n">
-        <v>6540</v>
+        <v>3965</v>
       </c>
       <c r="G872" s="1" t="inlineStr">
         <is>
-          <t>MERCADINHO BAMBINA LTDA</t>
+          <t>TUTTI QUITUTE PRODUTOS ALIMENTICIOS LTDA</t>
         </is>
       </c>
       <c r="H872" s="1" t="inlineStr">
@@ -66725,41 +66754,29 @@
         </is>
       </c>
       <c r="J872" s="2" t="n">
-        <v>46265.4616653125</v>
+        <v>46266.75154699074</v>
       </c>
       <c r="K872" s="2" t="n">
         <v>46296</v>
       </c>
       <c r="L872" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M872" s="1" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
-        </is>
-      </c>
-      <c r="N872" s="2" t="n">
-        <v>46265.62414548611</v>
-      </c>
+          <t>Lohany Martins</t>
+        </is>
+      </c>
+      <c r="N872" s="1" t="n"/>
       <c r="O872" s="1" t="n"/>
-      <c r="P872" s="2" t="n">
-        <v>46276.71389502315</v>
-      </c>
-      <c r="Q872" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
-      <c r="R872" s="1" t="inlineStr">
-        <is>
-          <t>Em fila de atendimento</t>
-        </is>
-      </c>
+      <c r="P872" s="1" t="n"/>
+      <c r="Q872" s="1" t="inlineStr"/>
+      <c r="R872" s="1" t="inlineStr"/>
       <c r="S872" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T872" s="1" t="n"/>
@@ -66767,7 +66784,7 @@
     </row>
     <row r="873">
       <c r="A873" s="1" t="n">
-        <v>83367</v>
+        <v>83313</v>
       </c>
       <c r="B873" s="1" t="inlineStr">
         <is>
@@ -66786,15 +66803,15 @@
       </c>
       <c r="E873" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tarde!Segue em anexo cadastro de produtos da empresa 5789 – ACE FRUIT para validação do CBS/IBS.</t>
+          <t xml:space="preserve">Prezados, bom dia.Segue e-mail enviado com a planilha de cadastro de produtos. Conforme falado com o gerente de contas Bruno, fica de acordo realizar a validação do cadastro de acordo com as informações enviadas ao cliente. Caso validação não seja realizada por completo iremos comunicar ao cliente. </t>
         </is>
       </c>
       <c r="F873" s="1" t="n">
-        <v>5789</v>
+        <v>6644</v>
       </c>
       <c r="G873" s="1" t="inlineStr">
         <is>
-          <t>ACE FRUIT COMERCIO DE ALIMENTOS LTDA (Filial 2)</t>
+          <t>MAPA DISTRIBUIDORA DE ALIMENTOS IMPORTACAO E EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="H873" s="1" t="inlineStr">
@@ -66808,32 +66825,26 @@
         </is>
       </c>
       <c r="J873" s="2" t="n">
-        <v>46266.64626565972</v>
+        <v>46266.41307797454</v>
       </c>
       <c r="K873" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="L873" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M873" s="1" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
-        </is>
-      </c>
-      <c r="N873" s="2" t="n">
-        <v>46269.66462141203</v>
-      </c>
+          <t>Amanda Mesquita</t>
+        </is>
+      </c>
+      <c r="N873" s="1" t="n"/>
       <c r="O873" s="1" t="n"/>
       <c r="P873" s="1" t="n"/>
       <c r="Q873" s="1" t="inlineStr"/>
-      <c r="R873" s="1" t="inlineStr">
-        <is>
-          <t>Em fila para atendimento</t>
-        </is>
-      </c>
+      <c r="R873" s="1" t="inlineStr"/>
       <c r="S873" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -66844,7 +66855,7 @@
     </row>
     <row r="874">
       <c r="A874" s="1" t="n">
-        <v>83429</v>
+        <v>83541</v>
       </c>
       <c r="B874" s="1" t="inlineStr">
         <is>
@@ -66863,15 +66874,15 @@
       </c>
       <c r="E874" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados, boa tarde!Segue novamente planilha de IBS/CBS da empresa 3965 - TUTTI DELI, ela já foi enviada anteriormente o número do chamado antigo é 82784, porém ela foi retornada mesmo estando completa. Na planilha consta NCM, Descrição e EAN. </t>
+          <t>Prezados, bom dia!Segue em anexo cadastro de produtos da empresa 4411 – JPS MATERIAIS para validação do CBS/IBS.</t>
         </is>
       </c>
       <c r="F874" s="1" t="n">
-        <v>3965</v>
+        <v>4411</v>
       </c>
       <c r="G874" s="1" t="inlineStr">
         <is>
-          <t>TUTTI QUITUTE PRODUTOS ALIMENTICIOS LTDA</t>
+          <t>JPS MATERIAIS DE CONSTRUÇÃO E DECORAÇÕES LTDA</t>
         </is>
       </c>
       <c r="H874" s="1" t="inlineStr">
@@ -66885,14 +66896,14 @@
         </is>
       </c>
       <c r="J874" s="2" t="n">
-        <v>46266.75154699074</v>
+        <v>46268.43361015046</v>
       </c>
       <c r="K874" s="2" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="L874" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M874" s="1" t="inlineStr">
@@ -66902,12 +66913,22 @@
       </c>
       <c r="N874" s="1" t="n"/>
       <c r="O874" s="1" t="n"/>
-      <c r="P874" s="1" t="n"/>
-      <c r="Q874" s="1" t="inlineStr"/>
-      <c r="R874" s="1" t="inlineStr"/>
+      <c r="P874" s="2" t="n">
+        <v>46273.43621866898</v>
+      </c>
+      <c r="Q874" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Bertunes</t>
+        </is>
+      </c>
+      <c r="R874" s="1" t="inlineStr">
+        <is>
+          <t>Cadastro analisado e enviado por email em 04/09</t>
+        </is>
+      </c>
       <c r="S874" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T874" s="1" t="n"/>
@@ -66915,7 +66936,7 @@
     </row>
     <row r="875">
       <c r="A875" s="1" t="n">
-        <v>83313</v>
+        <v>83542</v>
       </c>
       <c r="B875" s="1" t="inlineStr">
         <is>
@@ -66934,15 +66955,15 @@
       </c>
       <c r="E875" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados, bom dia.Segue e-mail enviado com a planilha de cadastro de produtos. Conforme falado com o gerente de contas Bruno, fica de acordo realizar a validação do cadastro de acordo com as informações enviadas ao cliente. Caso validação não seja realizada por completo iremos comunicar ao cliente. </t>
+          <t>Prezados, bom dia!Segue em anexo cadastro de produtos da empresa 4411 – JPS MATERIAIS para validação do CBS/IBS.</t>
         </is>
       </c>
       <c r="F875" s="1" t="n">
-        <v>6644</v>
+        <v>6412</v>
       </c>
       <c r="G875" s="1" t="inlineStr">
         <is>
-          <t>MAPA DISTRIBUIDORA DE ALIMENTOS IMPORTACAO E EXPORTACAO LTDA</t>
+          <t xml:space="preserve">SPJ MATERIAIS DE CONSTRUCAO LTDA </t>
         </is>
       </c>
       <c r="H875" s="1" t="inlineStr">
@@ -66956,29 +66977,39 @@
         </is>
       </c>
       <c r="J875" s="2" t="n">
-        <v>46266.41307797454</v>
+        <v>46268.43411693287</v>
       </c>
       <c r="K875" s="2" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="L875" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M875" s="1" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Lohany Martins</t>
         </is>
       </c>
       <c r="N875" s="1" t="n"/>
       <c r="O875" s="1" t="n"/>
-      <c r="P875" s="1" t="n"/>
-      <c r="Q875" s="1" t="inlineStr"/>
-      <c r="R875" s="1" t="inlineStr"/>
+      <c r="P875" s="2" t="n">
+        <v>46273.43373032408</v>
+      </c>
+      <c r="Q875" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Bertunes</t>
+        </is>
+      </c>
+      <c r="R875" s="1" t="inlineStr">
+        <is>
+          <t>Cadastro analisado e enviado por email em 04/03</t>
+        </is>
+      </c>
       <c r="S875" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T875" s="1" t="n"/>
@@ -66986,7 +67017,7 @@
     </row>
     <row r="876">
       <c r="A876" s="1" t="n">
-        <v>83541</v>
+        <v>83562</v>
       </c>
       <c r="B876" s="1" t="inlineStr">
         <is>
@@ -67000,20 +67031,20 @@
       </c>
       <c r="D876" s="1" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E876" s="1" t="inlineStr">
         <is>
-          <t>Prezados, bom dia!Segue em anexo cadastro de produtos da empresa 4411 – JPS MATERIAIS para validação do CBS/IBS.</t>
+          <t>6947 - F. MARQUES DE SA LTDA - PLANILHA DE INTENS Em anexo email enviado com a planilha.</t>
         </is>
       </c>
       <c r="F876" s="1" t="n">
-        <v>4411</v>
+        <v>6947</v>
       </c>
       <c r="G876" s="1" t="inlineStr">
         <is>
-          <t>JPS MATERIAIS DE CONSTRUÇÃO E DECORAÇÕES LTDA</t>
+          <t>F. MARQUES DE SA LTDA</t>
         </is>
       </c>
       <c r="H876" s="1" t="inlineStr">
@@ -67027,39 +67058,29 @@
         </is>
       </c>
       <c r="J876" s="2" t="n">
-        <v>46268.43361015046</v>
+        <v>46268.52269753473</v>
       </c>
       <c r="K876" s="2" t="n">
         <v>46300</v>
       </c>
       <c r="L876" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M876" s="1" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="N876" s="1" t="n"/>
       <c r="O876" s="1" t="n"/>
-      <c r="P876" s="2" t="n">
-        <v>46273.43621866898</v>
-      </c>
-      <c r="Q876" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
-      <c r="R876" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro analisado e enviado por email em 04/09</t>
-        </is>
-      </c>
+      <c r="P876" s="1" t="n"/>
+      <c r="Q876" s="1" t="inlineStr"/>
+      <c r="R876" s="1" t="inlineStr"/>
       <c r="S876" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T876" s="1" t="n"/>
@@ -67067,7 +67088,7 @@
     </row>
     <row r="877">
       <c r="A877" s="1" t="n">
-        <v>83542</v>
+        <v>83432</v>
       </c>
       <c r="B877" s="1" t="inlineStr">
         <is>
@@ -67081,20 +67102,20 @@
       </c>
       <c r="D877" s="1" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E877" s="1" t="inlineStr">
         <is>
-          <t>Prezados, bom dia!Segue em anexo cadastro de produtos da empresa 4411 – JPS MATERIAIS para validação do CBS/IBS.</t>
+          <t>Revisão de cadastro de produtos da Ki-Preco</t>
         </is>
       </c>
       <c r="F877" s="1" t="n">
-        <v>6412</v>
+        <v>6442</v>
       </c>
       <c r="G877" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPJ MATERIAIS DE CONSTRUCAO LTDA </t>
+          <t>KI PRECO SERVICOS ADMINISTRATIVOS LTDA</t>
         </is>
       </c>
       <c r="H877" s="1" t="inlineStr">
@@ -67108,39 +67129,29 @@
         </is>
       </c>
       <c r="J877" s="2" t="n">
-        <v>46268.43411693287</v>
+        <v>46266.81141119213</v>
       </c>
       <c r="K877" s="2" t="n">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="L877" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M877" s="1" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N877" s="1" t="n"/>
       <c r="O877" s="1" t="n"/>
-      <c r="P877" s="2" t="n">
-        <v>46273.43373032408</v>
-      </c>
-      <c r="Q877" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
-      <c r="R877" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro analisado e enviado por email em 04/03</t>
-        </is>
-      </c>
+      <c r="P877" s="1" t="n"/>
+      <c r="Q877" s="1" t="inlineStr"/>
+      <c r="R877" s="1" t="inlineStr"/>
       <c r="S877" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T877" s="1" t="n"/>
@@ -67148,7 +67159,7 @@
     </row>
     <row r="878">
       <c r="A878" s="1" t="n">
-        <v>83562</v>
+        <v>83644</v>
       </c>
       <c r="B878" s="1" t="inlineStr">
         <is>
@@ -67167,15 +67178,15 @@
       </c>
       <c r="E878" s="1" t="inlineStr">
         <is>
-          <t>6947 - F. MARQUES DE SA LTDA - PLANILHA DE INTENS Em anexo email enviado com a planilha.</t>
+          <t>Prezadas, conforme solicitado pelo Nilton, segue:Abrir um chamado para esta empresa fazer a análise do cadastro de produtos dividido em 3 partes:1º - primeira parte analisar os produtos que estão com a exclusão a partir de primeiro de outubro fusão do ICMS – ST (que acho que não deve ter nenhum)2º - segunda parte fazer a classificação da alíquota teste do IBS e CBS3º - Classificação total das alíquotas atuais de ICMS PIS e COFINScadastro enviado no e-mail.</t>
         </is>
       </c>
       <c r="F878" s="1" t="n">
-        <v>6947</v>
+        <v>1603</v>
       </c>
       <c r="G878" s="1" t="inlineStr">
         <is>
-          <t>F. MARQUES DE SA LTDA</t>
+          <t>MERCADINHO KI PREÇO BAIXO LTDA</t>
         </is>
       </c>
       <c r="H878" s="1" t="inlineStr">
@@ -67189,10 +67200,10 @@
         </is>
       </c>
       <c r="J878" s="2" t="n">
-        <v>46268.52269753473</v>
+        <v>46273.47367033565</v>
       </c>
       <c r="K878" s="2" t="n">
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="L878" s="1" t="inlineStr">
         <is>
@@ -67201,7 +67212,7 @@
       </c>
       <c r="M878" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N878" s="1" t="n"/>
@@ -67219,7 +67230,7 @@
     </row>
     <row r="879">
       <c r="A879" s="1" t="n">
-        <v>83432</v>
+        <v>83654</v>
       </c>
       <c r="B879" s="1" t="inlineStr">
         <is>
@@ -67233,20 +67244,20 @@
       </c>
       <c r="D879" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E879" s="1" t="inlineStr">
         <is>
-          <t>Revisão de cadastro de produtos da Ki-Preco</t>
+          <t>Prezados, segue em anexo e-mail com planilha de cadastro de produtos da empresa.</t>
         </is>
       </c>
       <c r="F879" s="1" t="n">
-        <v>6442</v>
+        <v>5714</v>
       </c>
       <c r="G879" s="1" t="inlineStr">
         <is>
-          <t>KI PRECO SERVICOS ADMINISTRATIVOS LTDA</t>
+          <t>DIBRAMASUL MADEIRAS LTDA</t>
         </is>
       </c>
       <c r="H879" s="1" t="inlineStr">
@@ -67260,185 +67271,43 @@
         </is>
       </c>
       <c r="J879" s="2" t="n">
-        <v>46266.81141119213</v>
+        <v>46273.54331446759</v>
       </c>
       <c r="K879" s="2" t="n">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="L879" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M879" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Amanda Mesquita</t>
         </is>
       </c>
       <c r="N879" s="1" t="n"/>
       <c r="O879" s="1" t="n"/>
-      <c r="P879" s="1" t="n"/>
-      <c r="Q879" s="1" t="inlineStr"/>
-      <c r="R879" s="1" t="inlineStr"/>
+      <c r="P879" s="2" t="n">
+        <v>46276.69486894676</v>
+      </c>
+      <c r="Q879" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Bertunes</t>
+        </is>
+      </c>
+      <c r="R879" s="1" t="inlineStr">
+        <is>
+          <t>Cadastro analisado e devolvido por email em 10/09</t>
+        </is>
+      </c>
       <c r="S879" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T879" s="1" t="n"/>
       <c r="U879" s="1" t="inlineStr"/>
-    </row>
-    <row r="880">
-      <c r="A880" s="1" t="n">
-        <v>83644</v>
-      </c>
-      <c r="B880" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro de Produtos</t>
-        </is>
-      </c>
-      <c r="C880" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro de produtos</t>
-        </is>
-      </c>
-      <c r="D880" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E880" s="1" t="inlineStr">
-        <is>
-          <t>Prezadas, conforme solicitado pelo Nilton, segue:Abrir um chamado para esta empresa fazer a análise do cadastro de produtos dividido em 3 partes:1º - primeira parte analisar os produtos que estão com a exclusão a partir de primeiro de outubro fusão do ICMS – ST (que acho que não deve ter nenhum)2º - segunda parte fazer a classificação da alíquota teste do IBS e CBS3º - Classificação total das alíquotas atuais de ICMS PIS e COFINScadastro enviado no e-mail.</t>
-        </is>
-      </c>
-      <c r="F880" s="1" t="n">
-        <v>1603</v>
-      </c>
-      <c r="G880" s="1" t="inlineStr">
-        <is>
-          <t>MERCADINHO KI PREÇO BAIXO LTDA</t>
-        </is>
-      </c>
-      <c r="H880" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
-      <c r="I880" s="1" t="inlineStr">
-        <is>
-          <t>CADASTRO DE PRODUTOS</t>
-        </is>
-      </c>
-      <c r="J880" s="2" t="n">
-        <v>46273.47367033565</v>
-      </c>
-      <c r="K880" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="L880" s="1" t="inlineStr">
-        <is>
-          <t>Esperando Atendimento</t>
-        </is>
-      </c>
-      <c r="M880" s="1" t="inlineStr">
-        <is>
-          <t>Ricardo Ferreira</t>
-        </is>
-      </c>
-      <c r="N880" s="1" t="n"/>
-      <c r="O880" s="1" t="n"/>
-      <c r="P880" s="1" t="n"/>
-      <c r="Q880" s="1" t="inlineStr"/>
-      <c r="R880" s="1" t="inlineStr"/>
-      <c r="S880" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T880" s="1" t="n"/>
-      <c r="U880" s="1" t="inlineStr"/>
-    </row>
-    <row r="881">
-      <c r="A881" s="1" t="n">
-        <v>83654</v>
-      </c>
-      <c r="B881" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro de Produtos</t>
-        </is>
-      </c>
-      <c r="C881" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro de produtos</t>
-        </is>
-      </c>
-      <c r="D881" s="1" t="inlineStr">
-        <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E881" s="1" t="inlineStr">
-        <is>
-          <t>Prezados, segue em anexo e-mail com planilha de cadastro de produtos da empresa.</t>
-        </is>
-      </c>
-      <c r="F881" s="1" t="n">
-        <v>5714</v>
-      </c>
-      <c r="G881" s="1" t="inlineStr">
-        <is>
-          <t>DIBRAMASUL MADEIRAS LTDA</t>
-        </is>
-      </c>
-      <c r="H881" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
-      <c r="I881" s="1" t="inlineStr">
-        <is>
-          <t>CADASTRO DE PRODUTOS</t>
-        </is>
-      </c>
-      <c r="J881" s="2" t="n">
-        <v>46273.54331446759</v>
-      </c>
-      <c r="K881" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="L881" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M881" s="1" t="inlineStr">
-        <is>
-          <t>Amanda Mesquita</t>
-        </is>
-      </c>
-      <c r="N881" s="1" t="n"/>
-      <c r="O881" s="1" t="n"/>
-      <c r="P881" s="2" t="n">
-        <v>46276.69486894676</v>
-      </c>
-      <c r="Q881" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Bertunes</t>
-        </is>
-      </c>
-      <c r="R881" s="1" t="inlineStr">
-        <is>
-          <t>Cadastro analisado e devolvido por email em 10/09</t>
-        </is>
-      </c>
-      <c r="S881" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T881" s="1" t="n"/>
-      <c r="U881" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U833" headerRowCount="1">
-  <autoFilter ref="A1:U833"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U831" headerRowCount="1">
+  <autoFilter ref="A1:U831"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U833"/>
+  <dimension ref="A1:U831"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="L52" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M52" s="1" t="inlineStr">
@@ -4709,11 +4709,17 @@
           <t>Sofia Souza</t>
         </is>
       </c>
-      <c r="N52" s="1" t="n"/>
+      <c r="N52" s="2" t="n">
+        <v>46281.55894710648</v>
+      </c>
       <c r="O52" s="1" t="n"/>
       <c r="P52" s="1" t="n"/>
       <c r="Q52" s="1" t="inlineStr"/>
-      <c r="R52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr">
+        <is>
+          <t>Estamos gerando os relatorios no sistema, a demora se da pela consolidação de muitas lojas</t>
+        </is>
+      </c>
       <c r="S52" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -12064,7 +12070,7 @@
       </c>
       <c r="L140" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M140" s="1" t="inlineStr">
@@ -12074,12 +12080,22 @@
       </c>
       <c r="N140" s="1" t="n"/>
       <c r="O140" s="1" t="n"/>
-      <c r="P140" s="1" t="n"/>
-      <c r="Q140" s="1" t="inlineStr"/>
-      <c r="R140" s="1" t="inlineStr"/>
+      <c r="P140" s="2" t="n">
+        <v>46281.56319537037</v>
+      </c>
+      <c r="Q140" s="1" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
+      <c r="R140" s="1" t="inlineStr">
+        <is>
+          <t>Gua recalculada e publicada em 10/09</t>
+        </is>
+      </c>
       <c r="S140" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T140" s="1" t="n"/>
@@ -48541,7 +48557,7 @@
     </row>
     <row r="634">
       <c r="A634" s="1" t="n">
-        <v>83479</v>
+        <v>83657</v>
       </c>
       <c r="B634" s="1" t="inlineStr">
         <is>
@@ -48550,17 +48566,17 @@
       </c>
       <c r="C634" s="1" t="inlineStr">
         <is>
-          <t>Chamados</t>
+          <t>Baixa automática - Arquivos</t>
         </is>
       </c>
       <c r="D634" s="1" t="inlineStr">
         <is>
-          <t>TI - DESENVOLVIMENTO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E634" s="1" t="inlineStr">
         <is>
-          <t>Teste - Troca de Status.</t>
+          <t>não estou conseguindo realizar a baixa da tarefa dec primeira quinzena com vencimento para hoje</t>
         </is>
       </c>
       <c r="F634" s="1" t="n">
@@ -48569,7 +48585,7 @@
       <c r="G634" s="1" t="n"/>
       <c r="H634" s="1" t="inlineStr">
         <is>
-          <t>Nicole Oliveira</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="I634" s="1" t="inlineStr">
@@ -48578,37 +48594,39 @@
         </is>
       </c>
       <c r="J634" s="2" t="n">
-        <v>46267.48583834491</v>
+        <v>46273.56905054398</v>
       </c>
       <c r="K634" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="L634" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M634" s="1" t="inlineStr">
         <is>
-          <t>Eduardo Lima</t>
-        </is>
-      </c>
-      <c r="N634" s="2" t="n">
-        <v>46267.48404930555</v>
-      </c>
-      <c r="O634" s="2" t="n">
-        <v>46273</v>
-      </c>
-      <c r="P634" s="1" t="n"/>
-      <c r="Q634" s="1" t="inlineStr"/>
+          <t>Daniela Silva</t>
+        </is>
+      </c>
+      <c r="N634" s="1" t="n"/>
+      <c r="O634" s="1" t="n"/>
+      <c r="P634" s="2" t="n">
+        <v>46273.66095663195</v>
+      </c>
+      <c r="Q634" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
       <c r="R634" s="1" t="inlineStr">
         <is>
-          <t>Teste - Trocando o status.</t>
+          <t>Tarefa da empresa 7046 baixada</t>
         </is>
       </c>
       <c r="S634" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T634" s="1" t="n"/>
@@ -48616,7 +48634,7 @@
     </row>
     <row r="635">
       <c r="A635" s="1" t="n">
-        <v>83657</v>
+        <v>83681</v>
       </c>
       <c r="B635" s="1" t="inlineStr">
         <is>
@@ -48635,7 +48653,7 @@
       </c>
       <c r="E635" s="1" t="inlineStr">
         <is>
-          <t>não estou conseguindo realizar a baixa da tarefa dec primeira quinzena com vencimento para hoje</t>
+          <t>Boa tarde!Por gentileza baixar as tarefas do DEC 1 quinzena das empresas abaixo, não possuem IE:4295, 5795 e 7016obrigada.</t>
         </is>
       </c>
       <c r="F635" s="1" t="n">
@@ -48653,7 +48671,7 @@
         </is>
       </c>
       <c r="J635" s="2" t="n">
-        <v>46273.56905054398</v>
+        <v>46273.70785818287</v>
       </c>
       <c r="K635" s="2" t="n">
         <v>46274</v>
@@ -48665,13 +48683,13 @@
       </c>
       <c r="M635" s="1" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="N635" s="1" t="n"/>
       <c r="O635" s="1" t="n"/>
       <c r="P635" s="2" t="n">
-        <v>46273.66095663195</v>
+        <v>46273.7466596875</v>
       </c>
       <c r="Q635" s="1" t="inlineStr">
         <is>
@@ -48680,7 +48698,7 @@
       </c>
       <c r="R635" s="1" t="inlineStr">
         <is>
-          <t>Tarefa da empresa 7046 baixada</t>
+          <t>Tarefas baixadas</t>
         </is>
       </c>
       <c r="S635" s="1" t="inlineStr">
@@ -48693,7 +48711,7 @@
     </row>
     <row r="636">
       <c r="A636" s="1" t="n">
-        <v>83681</v>
+        <v>83753</v>
       </c>
       <c r="B636" s="1" t="inlineStr">
         <is>
@@ -48702,17 +48720,17 @@
       </c>
       <c r="C636" s="1" t="inlineStr">
         <is>
-          <t>Baixa automática - Arquivos</t>
+          <t>Implementação de Melhoria</t>
         </is>
       </c>
       <c r="D636" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E636" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por gentileza baixar as tarefas do DEC 1 quinzena das empresas abaixo, não possuem IE:4295, 5795 e 7016obrigada.</t>
+          <t>Gostaria de solicitar uma melhoria em relação aos comentários das empresas com pendências e com previsão de fechamento no Sistema de Análise, integrando essas informações à tarefa “Movimento - Sistema de Análise” do MG Controle. Pois tivemos o vencimento dessa tarefa antecipado devido as prioridades determinadas pela diretoria.A ideia é aproveitar os comentários e previsões que atualizamos diariamente no Controle de Status para que diminua o retrabalho, da seguinte forma:Empresas com pendências Status A: na tarefa correspondente do MG Controle, reconhecer automaticamente o status e atribuir o comentário padrão “Empresa com pendência”, replicando também o comentário registrado no Sistema de Análise.Empresas sem pendências e com data de previsão Status E e F: atribuir o comentário padrão “Comentário Colaborador + Previsão de Conclusão” e adicionar a data de previsão do Sistema de Análise.</t>
         </is>
       </c>
       <c r="F636" s="1" t="n">
@@ -48721,7 +48739,7 @@
       <c r="G636" s="1" t="n"/>
       <c r="H636" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="I636" s="1" t="inlineStr">
@@ -48730,39 +48748,29 @@
         </is>
       </c>
       <c r="J636" s="2" t="n">
-        <v>46273.70785818287</v>
+        <v>46274.72510725694</v>
       </c>
       <c r="K636" s="2" t="n">
-        <v>46274</v>
+        <v>46286</v>
       </c>
       <c r="L636" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M636" s="1" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="N636" s="1" t="n"/>
       <c r="O636" s="1" t="n"/>
-      <c r="P636" s="2" t="n">
-        <v>46273.7466596875</v>
-      </c>
-      <c r="Q636" s="1" t="inlineStr">
-        <is>
-          <t>Gabriel Amaral</t>
-        </is>
-      </c>
-      <c r="R636" s="1" t="inlineStr">
-        <is>
-          <t>Tarefas baixadas</t>
-        </is>
-      </c>
+      <c r="P636" s="1" t="n"/>
+      <c r="Q636" s="1" t="inlineStr"/>
+      <c r="R636" s="1" t="inlineStr"/>
       <c r="S636" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T636" s="1" t="n"/>
@@ -48770,7 +48778,7 @@
     </row>
     <row r="637">
       <c r="A637" s="1" t="n">
-        <v>83753</v>
+        <v>83804</v>
       </c>
       <c r="B637" s="1" t="inlineStr">
         <is>
@@ -48779,17 +48787,17 @@
       </c>
       <c r="C637" s="1" t="inlineStr">
         <is>
-          <t>Implementação de Melhoria</t>
+          <t>Responsável Direto</t>
         </is>
       </c>
       <c r="D637" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="E637" s="1" t="inlineStr">
         <is>
-          <t>Gostaria de solicitar uma melhoria em relação aos comentários das empresas com pendências e com previsão de fechamento no Sistema de Análise, integrando essas informações à tarefa “Movimento - Sistema de Análise” do MG Controle. Pois tivemos o vencimento dessa tarefa antecipado devido as prioridades determinadas pela diretoria.A ideia é aproveitar os comentários e previsões que atualizamos diariamente no Controle de Status para que diminua o retrabalho, da seguinte forma:Empresas com pendências Status A: na tarefa correspondente do MG Controle, reconhecer automaticamente o status e atribuir o comentário padrão “Empresa com pendência”, replicando também o comentário registrado no Sistema de Análise.Empresas sem pendências e com data de previsão Status E e F: atribuir o comentário padrão “Comentário Colaborador + Previsão de Conclusão” e adicionar a data de previsão do Sistema de Análise.</t>
+          <t>Bom dia, tudo bom?Para as emrpesas, no relatório anexo, já troquei diversas vezes o GC de Cavalcante para Maicon. Tiro o relatório de pendências do MGC e ainda continua como GC Cavalcante. Por favor, poderiam verificar?</t>
         </is>
       </c>
       <c r="F637" s="1" t="n">
@@ -48798,7 +48806,7 @@
       <c r="G637" s="1" t="n"/>
       <c r="H637" s="1" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="I637" s="1" t="inlineStr">
@@ -48807,29 +48815,39 @@
         </is>
       </c>
       <c r="J637" s="2" t="n">
-        <v>46274.72510725694</v>
+        <v>46275.49970760417</v>
       </c>
       <c r="K637" s="2" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="L637" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M637" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Bruno Mota</t>
         </is>
       </c>
       <c r="N637" s="1" t="n"/>
       <c r="O637" s="1" t="n"/>
-      <c r="P637" s="1" t="n"/>
-      <c r="Q637" s="1" t="inlineStr"/>
-      <c r="R637" s="1" t="inlineStr"/>
+      <c r="P637" s="2" t="n">
+        <v>46275.61615810185</v>
+      </c>
+      <c r="Q637" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
+      <c r="R637" s="1" t="inlineStr">
+        <is>
+          <t>GC's ajustados</t>
+        </is>
+      </c>
       <c r="S637" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T637" s="1" t="n"/>
@@ -48837,7 +48855,7 @@
     </row>
     <row r="638">
       <c r="A638" s="1" t="n">
-        <v>83804</v>
+        <v>84075</v>
       </c>
       <c r="B638" s="1" t="inlineStr">
         <is>
@@ -48846,17 +48864,17 @@
       </c>
       <c r="C638" s="1" t="inlineStr">
         <is>
-          <t>Responsável Direto</t>
+          <t>Baixa automática - Arquivos</t>
         </is>
       </c>
       <c r="D638" s="1" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E638" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, tudo bom?Para as emrpesas, no relatório anexo, já troquei diversas vezes o GC de Cavalcante para Maicon. Tiro o relatório de pendências do MGC e ainda continua como GC Cavalcante. Por favor, poderiam verificar?</t>
+          <t>EMPRESA -  5292 ezekyCOMPETENCIA  - 08-2026TAREFA -ENVIO DE DCT WEBMOTIVO - EMPRESA SOLICITOU POR E-MAIL - JÁ ENVIEI EM 16/09</t>
         </is>
       </c>
       <c r="F638" s="1" t="n">
@@ -48865,7 +48883,7 @@
       <c r="G638" s="1" t="n"/>
       <c r="H638" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I638" s="1" t="inlineStr">
@@ -48874,39 +48892,29 @@
         </is>
       </c>
       <c r="J638" s="2" t="n">
-        <v>46275.49970760417</v>
+        <v>46281.50936770834</v>
       </c>
       <c r="K638" s="2" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="L638" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M638" s="1" t="inlineStr">
         <is>
-          <t>Bruno Mota</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="N638" s="1" t="n"/>
       <c r="O638" s="1" t="n"/>
-      <c r="P638" s="2" t="n">
-        <v>46275.61615810185</v>
-      </c>
-      <c r="Q638" s="1" t="inlineStr">
-        <is>
-          <t>Gabriel Amaral</t>
-        </is>
-      </c>
-      <c r="R638" s="1" t="inlineStr">
-        <is>
-          <t>GC's ajustados</t>
-        </is>
-      </c>
+      <c r="P638" s="1" t="n"/>
+      <c r="Q638" s="1" t="inlineStr"/>
+      <c r="R638" s="1" t="inlineStr"/>
       <c r="S638" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T638" s="1" t="n"/>
@@ -48914,7 +48922,7 @@
     </row>
     <row r="639">
       <c r="A639" s="1" t="n">
-        <v>84075</v>
+        <v>84077</v>
       </c>
       <c r="B639" s="1" t="inlineStr">
         <is>
@@ -48923,50 +48931,54 @@
       </c>
       <c r="C639" s="1" t="inlineStr">
         <is>
-          <t>Baixa automática - Arquivos</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D639" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="E639" s="1" t="inlineStr">
         <is>
-          <t>EMPRESA -  5292 ezekyCOMPETENCIA  - 08-2026TAREFA -ENVIO DE DCT WEBMOTIVO - EMPRESA SOLICITOU POR E-MAIL - JÁ ENVIEI EM 16/09</t>
+          <t>Empresa 3130 Translog está com divergências de honorários ( valores iguais ao do Portal Nacional) mês 07 e 08, sendo que mês tinha baixado normalmente no mês anterior. Segue anexo arquivo.</t>
         </is>
       </c>
       <c r="F639" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G639" s="1" t="n"/>
-      <c r="H639" s="1" t="n"/>
+      <c r="H639" s="1" t="inlineStr">
+        <is>
+          <t>Nicole Oliveira</t>
+        </is>
+      </c>
       <c r="I639" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J639" s="2" t="n">
-        <v>46281.50936770834</v>
+        <v>46281.55680065972</v>
       </c>
       <c r="K639" s="2" t="n">
         <v>46282</v>
       </c>
       <c r="L639" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M639" s="1" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Veronica Barbosa</t>
         </is>
       </c>
       <c r="N639" s="1" t="n"/>
       <c r="O639" s="1" t="n"/>
       <c r="P639" s="1" t="n"/>
       <c r="Q639" s="1" t="inlineStr"/>
-      <c r="R639" s="1" t="n"/>
+      <c r="R639" s="1" t="inlineStr"/>
       <c r="S639" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -48977,26 +48989,26 @@
     </row>
     <row r="640">
       <c r="A640" s="1" t="n">
-        <v>81777</v>
+        <v>84078</v>
       </c>
       <c r="B640" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C640" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D640" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="E640" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tarde, poderia fazer o processo administrativo da empresa 3616 - CCV do ISS mes 04/2026, a guia foi cancelada para realizar emissão de notas da MG Negócios , que tinha nota emitidas contra a CCV, pós o financeiro realizou o pagamento da guia de ISS de serviços prestados </t>
+          <t>Empresa 3595 P L F 4 está com divergências de honorários ( valores iguais ao do Portal Nacional) mês 07 e 08, sendo que mês tinha baixado normalmente no mês anterior. Segue anexo arquivo.</t>
         </is>
       </c>
       <c r="F640" s="1" t="n">
@@ -49005,41 +49017,35 @@
       <c r="G640" s="1" t="n"/>
       <c r="H640" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I640" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J640" s="2" t="n">
-        <v>46237.59220239583</v>
+        <v>46281.55733619213</v>
       </c>
       <c r="K640" s="2" t="n">
-        <v>46239</v>
+        <v>46282</v>
       </c>
       <c r="L640" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M640" s="1" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
-        </is>
-      </c>
-      <c r="N640" s="2" t="n">
-        <v>46241.63536697916</v>
-      </c>
+          <t>Veronica Barbosa</t>
+        </is>
+      </c>
+      <c r="N640" s="1" t="n"/>
       <c r="O640" s="1" t="n"/>
       <c r="P640" s="1" t="n"/>
       <c r="Q640" s="1" t="inlineStr"/>
-      <c r="R640" s="1" t="inlineStr">
-        <is>
-          <t>Solicitei orientações à Prefeitura em como proceder para regularização, aguardando retorno.</t>
-        </is>
-      </c>
+      <c r="R640" s="1" t="inlineStr"/>
       <c r="S640" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -49050,26 +49056,26 @@
     </row>
     <row r="641">
       <c r="A641" s="1" t="n">
-        <v>82094</v>
+        <v>81777</v>
       </c>
       <c r="B641" s="1" t="inlineStr">
         <is>
-          <t>Processo de VISA</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C641" s="1" t="inlineStr">
         <is>
-          <t>Renovação</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D641" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - GC</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E641" s="1" t="inlineStr">
         <is>
-          <t>Favor providenciar a renovação da vigilância sanitária das empresas do grupo Atalaia - código - 1685/2616/4881/6175 - com urgência. Muito Obrigada!</t>
+          <t xml:space="preserve">Boa tarde, poderia fazer o processo administrativo da empresa 3616 - CCV do ISS mes 04/2026, a guia foi cancelada para realizar emissão de notas da MG Negócios , que tinha nota emitidas contra a CCV, pós o financeiro realizou o pagamento da guia de ISS de serviços prestados </t>
         </is>
       </c>
       <c r="F641" s="1" t="n">
@@ -49078,43 +49084,116 @@
       <c r="G641" s="1" t="n"/>
       <c r="H641" s="1" t="inlineStr">
         <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I641" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J641" s="2" t="n">
+        <v>46237.59220239583</v>
+      </c>
+      <c r="K641" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="L641" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M641" s="1" t="inlineStr">
+        <is>
+          <t>Romario Silva</t>
+        </is>
+      </c>
+      <c r="N641" s="2" t="n">
+        <v>46241.63536697916</v>
+      </c>
+      <c r="O641" s="1" t="n"/>
+      <c r="P641" s="1" t="n"/>
+      <c r="Q641" s="1" t="inlineStr"/>
+      <c r="R641" s="1" t="inlineStr">
+        <is>
+          <t>Solicitei orientações à Prefeitura em como proceder para regularização, aguardando retorno.</t>
+        </is>
+      </c>
+      <c r="S641" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T641" s="1" t="n"/>
+      <c r="U641" s="1" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="n">
+        <v>82094</v>
+      </c>
+      <c r="B642" s="1" t="inlineStr">
+        <is>
+          <t>Processo de VISA</t>
+        </is>
+      </c>
+      <c r="C642" s="1" t="inlineStr">
+        <is>
+          <t>Renovação</t>
+        </is>
+      </c>
+      <c r="D642" s="1" t="inlineStr">
+        <is>
+          <t>SANTOS - GC</t>
+        </is>
+      </c>
+      <c r="E642" s="1" t="inlineStr">
+        <is>
+          <t>Favor providenciar a renovação da vigilância sanitária das empresas do grupo Atalaia - código - 1685/2616/4881/6175 - com urgência. Muito Obrigada!</t>
+        </is>
+      </c>
+      <c r="F642" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G642" s="1" t="n"/>
+      <c r="H642" s="1" t="inlineStr">
+        <is>
           <t>Talita Silva</t>
         </is>
       </c>
-      <c r="I641" s="1" t="inlineStr">
+      <c r="I642" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J641" s="2" t="n">
+      <c r="J642" s="2" t="n">
         <v>46241.66958043981</v>
       </c>
-      <c r="K641" s="2" t="n">
+      <c r="K642" s="2" t="n">
         <v>46244</v>
       </c>
-      <c r="L641" s="1" t="inlineStr">
+      <c r="L642" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M641" s="1" t="inlineStr">
+      <c r="M642" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N641" s="2" t="n">
+      <c r="N642" s="2" t="n">
         <v>46252.70058159722</v>
       </c>
-      <c r="O641" s="1" t="n"/>
-      <c r="P641" s="2" t="n">
+      <c r="O642" s="1" t="n"/>
+      <c r="P642" s="2" t="n">
         <v>46280.42831450231</v>
       </c>
-      <c r="Q641" s="1" t="inlineStr">
+      <c r="Q642" s="1" t="inlineStr">
         <is>
           <t>Talita Silva</t>
         </is>
       </c>
-      <c r="R641" s="1" t="inlineStr">
+      <c r="R642" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Olá, boa tarde!
 Enviei por e-mail o Anexo III das empresas para assinatura.
@@ -49122,85 +49201,6 @@
 </t>
         </is>
       </c>
-      <c r="S641" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T641" s="1" t="n"/>
-      <c r="U641" s="1" t="inlineStr"/>
-    </row>
-    <row r="642">
-      <c r="A642" s="1" t="n">
-        <v>82296</v>
-      </c>
-      <c r="B642" s="1" t="inlineStr">
-        <is>
-          <t>Parcelamento Estadual</t>
-        </is>
-      </c>
-      <c r="C642" s="1" t="inlineStr">
-        <is>
-          <t>Divida Ativa</t>
-        </is>
-      </c>
-      <c r="D642" s="1" t="inlineStr">
-        <is>
-          <t>SANTOS - ADM</t>
-        </is>
-      </c>
-      <c r="E642" s="1" t="inlineStr">
-        <is>
-          <t>Cliente 5219 e 5551 solicitou parcelamento do ICMS , pode fazer a simulação</t>
-        </is>
-      </c>
-      <c r="F642" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G642" s="1" t="n"/>
-      <c r="H642" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="I642" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J642" s="2" t="n">
-        <v>46246.6211778588</v>
-      </c>
-      <c r="K642" s="2" t="n">
-        <v>46248</v>
-      </c>
-      <c r="L642" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M642" s="1" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
-      <c r="N642" s="2" t="n">
-        <v>46268.68634155093</v>
-      </c>
-      <c r="O642" s="1" t="n"/>
-      <c r="P642" s="2" t="n">
-        <v>46276.37282434028</v>
-      </c>
-      <c r="Q642" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="R642" s="1" t="inlineStr">
-        <is>
-          <t>Deve ser aberto um chamado para cada solicitação/cliente.</t>
-        </is>
-      </c>
       <c r="S642" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -49211,16 +49211,16 @@
     </row>
     <row r="643">
       <c r="A643" s="1" t="n">
-        <v>81227</v>
+        <v>82296</v>
       </c>
       <c r="B643" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Parcelamento Estadual</t>
         </is>
       </c>
       <c r="C643" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Divida Ativa</t>
         </is>
       </c>
       <c r="D643" s="1" t="inlineStr">
@@ -49230,7 +49230,7 @@
       </c>
       <c r="E643" s="1" t="inlineStr">
         <is>
-          <t>Empresa 5988 - Maurício Toniati - Cliente que haviamos feito a apuração incorreta de pis e cofins - Foi feito parcelamento , mais depois da retificação dos impostos não teria imposto a apagar. Gerei um relatório da situação fiscal e não consta nenhuma informação referente à Malha Fiscal, apenas a indicação de Parcelamento Suspenso.Poderia verificar, por gentileza, se há algum procedimento adicional que precise ser realizado ou alguma outra consulta que devemos efetuar?</t>
+          <t>Cliente 5219 e 5551 solicitou parcelamento do ICMS , pode fazer a simulação</t>
         </is>
       </c>
       <c r="F643" s="1" t="n">
@@ -49248,14 +49248,14 @@
         </is>
       </c>
       <c r="J643" s="2" t="n">
-        <v>46223.69836307871</v>
+        <v>46246.6211778588</v>
       </c>
       <c r="K643" s="2" t="n">
-        <v>46224</v>
+        <v>46248</v>
       </c>
       <c r="L643" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M643" s="1" t="inlineStr">
@@ -49264,19 +49264,25 @@
         </is>
       </c>
       <c r="N643" s="2" t="n">
-        <v>46232.73233688658</v>
+        <v>46268.68634155093</v>
       </c>
       <c r="O643" s="1" t="n"/>
-      <c r="P643" s="1" t="n"/>
-      <c r="Q643" s="1" t="inlineStr"/>
+      <c r="P643" s="2" t="n">
+        <v>46276.37282434028</v>
+      </c>
+      <c r="Q643" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="R643" s="1" t="inlineStr">
         <is>
-          <t>Verificando via chat.</t>
+          <t>Deve ser aberto um chamado para cada solicitação/cliente.</t>
         </is>
       </c>
       <c r="S643" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T643" s="1" t="n"/>
@@ -49284,26 +49290,26 @@
     </row>
     <row r="644">
       <c r="A644" s="1" t="n">
-        <v>81267</v>
+        <v>81227</v>
       </c>
       <c r="B644" s="1" t="inlineStr">
         <is>
-          <t>Processo de Prefeitura</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C644" s="1" t="inlineStr">
         <is>
-          <t>Geral</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D644" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="E644" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, poderia cancelar a nota na prefeitura do cliente 4422 - ALL Service , numero da nota 841</t>
+          <t>Empresa 5988 - Maurício Toniati - Cliente que haviamos feito a apuração incorreta de pis e cofins - Foi feito parcelamento , mais depois da retificação dos impostos não teria imposto a apagar. Gerei um relatório da situação fiscal e não consta nenhuma informação referente à Malha Fiscal, apenas a indicação de Parcelamento Suspenso.Poderia verificar, por gentileza, se há algum procedimento adicional que precise ser realizado ou alguma outra consulta que devemos efetuar?</t>
         </is>
       </c>
       <c r="F644" s="1" t="n">
@@ -49321,10 +49327,10 @@
         </is>
       </c>
       <c r="J644" s="2" t="n">
-        <v>46224.66958634259</v>
+        <v>46223.69836307871</v>
       </c>
       <c r="K644" s="2" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="L644" s="1" t="inlineStr">
         <is>
@@ -49333,18 +49339,18 @@
       </c>
       <c r="M644" s="1" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Lidia Tavares</t>
         </is>
       </c>
       <c r="N644" s="2" t="n">
-        <v>46231.70811304398</v>
+        <v>46232.73233688658</v>
       </c>
       <c r="O644" s="1" t="n"/>
       <c r="P644" s="1" t="n"/>
       <c r="Q644" s="1" t="inlineStr"/>
       <c r="R644" s="1" t="inlineStr">
         <is>
-          <t>Enviada proposta ao cliente, aguardando aceite para providenciar a documentação.</t>
+          <t>Verificando via chat.</t>
         </is>
       </c>
       <c r="S644" s="1" t="inlineStr">
@@ -49357,26 +49363,26 @@
     </row>
     <row r="645">
       <c r="A645" s="1" t="n">
-        <v>83249</v>
+        <v>81267</v>
       </c>
       <c r="B645" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>Processo de Prefeitura</t>
         </is>
       </c>
       <c r="C645" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="D645" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - GC</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E645" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">6533 - OFICIALMED BOM JESUS PRODUTOS FARMACÊUTICOS E APOIO ADMINISTRATIVO LTDA - Renovação do Alvará </t>
+          <t>Boa tarde, poderia cancelar a nota na prefeitura do cliente 4422 - ALL Service , numero da nota 841</t>
         </is>
       </c>
       <c r="F645" s="1" t="n">
@@ -49385,7 +49391,7 @@
       <c r="G645" s="1" t="n"/>
       <c r="H645" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I645" s="1" t="inlineStr">
@@ -49394,10 +49400,10 @@
         </is>
       </c>
       <c r="J645" s="2" t="n">
-        <v>46265.38856802083</v>
+        <v>46224.66958634259</v>
       </c>
       <c r="K645" s="2" t="n">
-        <v>46267</v>
+        <v>46225</v>
       </c>
       <c r="L645" s="1" t="inlineStr">
         <is>
@@ -49406,95 +49412,168 @@
       </c>
       <c r="M645" s="1" t="inlineStr">
         <is>
-          <t>Rafaella Massuia</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="N645" s="2" t="n">
-        <v>46267.71143642361</v>
+        <v>46231.70811304398</v>
       </c>
       <c r="O645" s="1" t="n"/>
       <c r="P645" s="1" t="n"/>
       <c r="Q645" s="1" t="inlineStr"/>
       <c r="R645" s="1" t="inlineStr">
         <is>
+          <t>Enviada proposta ao cliente, aguardando aceite para providenciar a documentação.</t>
+        </is>
+      </c>
+      <c r="S645" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T645" s="1" t="n"/>
+      <c r="U645" s="1" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="n">
+        <v>83249</v>
+      </c>
+      <c r="B646" s="1" t="inlineStr">
+        <is>
+          <t>Regularização</t>
+        </is>
+      </c>
+      <c r="C646" s="1" t="inlineStr">
+        <is>
+          <t>Prefeitura</t>
+        </is>
+      </c>
+      <c r="D646" s="1" t="inlineStr">
+        <is>
+          <t>SANTOS - GC</t>
+        </is>
+      </c>
+      <c r="E646" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6533 - OFICIALMED BOM JESUS PRODUTOS FARMACÊUTICOS E APOIO ADMINISTRATIVO LTDA - Renovação do Alvará </t>
+        </is>
+      </c>
+      <c r="F646" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G646" s="1" t="n"/>
+      <c r="H646" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
+      <c r="I646" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J646" s="2" t="n">
+        <v>46265.38856802083</v>
+      </c>
+      <c r="K646" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="L646" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M646" s="1" t="inlineStr">
+        <is>
+          <t>Rafaella Massuia</t>
+        </is>
+      </c>
+      <c r="N646" s="2" t="n">
+        <v>46267.71143642361</v>
+      </c>
+      <c r="O646" s="1" t="n"/>
+      <c r="P646" s="1" t="n"/>
+      <c r="Q646" s="1" t="inlineStr"/>
+      <c r="R646" s="1" t="inlineStr">
+        <is>
           <t>Boa tarde.
 Qual alvará?
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S645" s="1" t="inlineStr">
+      <c r="S646" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T645" s="1" t="n"/>
-      <c r="U645" s="1" t="inlineStr"/>
-    </row>
-    <row r="646">
-      <c r="A646" s="1" t="n">
+      <c r="T646" s="1" t="n"/>
+      <c r="U646" s="1" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="n">
         <v>83452</v>
       </c>
-      <c r="B646" s="1" t="inlineStr">
+      <c r="B647" s="1" t="inlineStr">
         <is>
           <t>Encerramento de Empresa</t>
         </is>
       </c>
-      <c r="C646" s="1" t="inlineStr">
+      <c r="C647" s="1" t="inlineStr">
         <is>
           <t>Eireli - Comércio</t>
         </is>
       </c>
-      <c r="D646" s="1" t="inlineStr">
+      <c r="D647" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E646" s="1" t="inlineStr">
+      <c r="E647" s="1" t="inlineStr">
         <is>
           <t>Pós Ata de reunião - 2876 -  BAR E LANCHES JUVENTUDE DE PRAIA GRANDE- EIRELI  Juventude	Encerramento Empresa 	O cliente solicitou o encerramento da empresa Juventude, ficando registrada a pendência para avaliação e condução dos procedimentos fiscais, cadastrais e societários necessários. 31/08/2026</t>
         </is>
       </c>
-      <c r="F646" s="1" t="n">
+      <c r="F647" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G646" s="1" t="n"/>
-      <c r="H646" s="1" t="inlineStr">
+      <c r="G647" s="1" t="n"/>
+      <c r="H647" s="1" t="inlineStr">
         <is>
           <t>Ronaldo Dias</t>
         </is>
       </c>
-      <c r="I646" s="1" t="inlineStr">
+      <c r="I647" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J646" s="2" t="n">
+      <c r="J647" s="2" t="n">
         <v>46267.40487928241</v>
       </c>
-      <c r="K646" s="2" t="n">
+      <c r="K647" s="2" t="n">
         <v>46269</v>
       </c>
-      <c r="L646" s="1" t="inlineStr">
+      <c r="L647" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M646" s="1" t="inlineStr">
+      <c r="M647" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N646" s="1" t="n"/>
-      <c r="O646" s="1" t="n"/>
-      <c r="P646" s="2" t="n">
+      <c r="N647" s="1" t="n"/>
+      <c r="O647" s="1" t="n"/>
+      <c r="P647" s="2" t="n">
         <v>46268.72386732639</v>
       </c>
-      <c r="Q646" s="1" t="inlineStr">
+      <c r="Q647" s="1" t="inlineStr">
         <is>
           <t>Ronaldo Dias</t>
         </is>
       </c>
-      <c r="R646" s="1" t="inlineStr">
+      <c r="R647" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Anexo proposta e abaixo as condições para dar andamento.
 1.	Quadro de pessoal: não possuir funcionários ativos — todos os contratos de trabalho devem estar encerrados e as obrigações trabalhistas devidamente quitadas;
@@ -49505,161 +49584,88 @@
 </t>
         </is>
       </c>
-      <c r="S646" s="1" t="inlineStr">
+      <c r="S647" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T646" s="1" t="n"/>
-      <c r="U646" s="1" t="inlineStr"/>
-    </row>
-    <row r="647">
-      <c r="A647" s="1" t="n">
+      <c r="T647" s="1" t="n"/>
+      <c r="U647" s="1" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="n">
         <v>83530</v>
       </c>
-      <c r="B647" s="1" t="inlineStr">
+      <c r="B648" s="1" t="inlineStr">
         <is>
           <t>Parcelamento RFB</t>
         </is>
       </c>
-      <c r="C647" s="1" t="inlineStr">
+      <c r="C648" s="1" t="inlineStr">
         <is>
           <t>Simplificado</t>
         </is>
       </c>
-      <c r="D647" s="1" t="inlineStr">
+      <c r="D648" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E647" s="1" t="inlineStr">
+      <c r="E648" s="1" t="inlineStr">
         <is>
           <t>6296 - GRAND DIVINO COMERCIO DE ALIMENTOS LTDA - Por gentileza simular em 12 vezes os debitos em aberto na RFB. obrigada.</t>
         </is>
       </c>
-      <c r="F647" s="1" t="n">
+      <c r="F648" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G647" s="1" t="n"/>
-      <c r="H647" s="1" t="inlineStr">
+      <c r="G648" s="1" t="n"/>
+      <c r="H648" s="1" t="inlineStr">
         <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="I647" s="1" t="inlineStr">
+      <c r="I648" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J647" s="2" t="n">
+      <c r="J648" s="2" t="n">
         <v>46267.7888037037</v>
       </c>
-      <c r="K647" s="2" t="n">
+      <c r="K648" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="L647" s="1" t="inlineStr">
+      <c r="L648" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M647" s="1" t="inlineStr">
+      <c r="M648" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N647" s="1" t="n"/>
-      <c r="O647" s="1" t="n"/>
-      <c r="P647" s="2" t="n">
+      <c r="N648" s="1" t="n"/>
+      <c r="O648" s="1" t="n"/>
+      <c r="P648" s="2" t="n">
         <v>46280.77879980324</v>
       </c>
-      <c r="Q647" s="1" t="inlineStr">
+      <c r="Q648" s="1" t="inlineStr">
         <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="R647" s="1" t="inlineStr">
+      <c r="R648" s="1" t="inlineStr">
         <is>
           <t>Rafa, boa tarde!
 Segue simulado e proposta em anexo.
 Por gentileza, verificar a omissão de DCTFWEB 12/2025.</t>
         </is>
       </c>
-      <c r="S647" s="1" t="inlineStr">
+      <c r="S648" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
-        </is>
-      </c>
-      <c r="T647" s="1" t="n"/>
-      <c r="U647" s="1" t="inlineStr"/>
-    </row>
-    <row r="648">
-      <c r="A648" s="1" t="n">
-        <v>83544</v>
-      </c>
-      <c r="B648" s="1" t="inlineStr">
-        <is>
-          <t>Senha</t>
-        </is>
-      </c>
-      <c r="C648" s="1" t="inlineStr">
-        <is>
-          <t>Prefeitura</t>
-        </is>
-      </c>
-      <c r="D648" s="1" t="inlineStr">
-        <is>
-          <t>EF - INDUSTRIA</t>
-        </is>
-      </c>
-      <c r="E648" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EMPRESA - 6428 CONCEITO CAMPINASBom dia, Tudo bem? poderia gerar a senha da Prefeitura para acesso as Notas. Entrei em contato com a Prefeitura e a mesma me reporto que o site está sofrendo instabilidade quando o acesso é via certificado.Atte. </t>
-        </is>
-      </c>
-      <c r="F648" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G648" s="1" t="n"/>
-      <c r="H648" s="1" t="inlineStr">
-        <is>
-          <t>Sarah Amaro</t>
-        </is>
-      </c>
-      <c r="I648" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J648" s="2" t="n">
-        <v>46268.44168938657</v>
-      </c>
-      <c r="K648" s="2" t="n">
-        <v>46273</v>
-      </c>
-      <c r="L648" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M648" s="1" t="inlineStr">
-        <is>
-          <t>Caroline Nascimento</t>
-        </is>
-      </c>
-      <c r="N648" s="2" t="n">
-        <v>46274.44113792824</v>
-      </c>
-      <c r="O648" s="1" t="n"/>
-      <c r="P648" s="1" t="n"/>
-      <c r="Q648" s="1" t="inlineStr"/>
-      <c r="R648" s="1" t="inlineStr">
-        <is>
-          <t>Solicitado ao cliente o link de acesso para cadastro</t>
-        </is>
-      </c>
-      <c r="S648" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
         </is>
       </c>
       <c r="T648" s="1" t="n"/>
@@ -49667,26 +49673,26 @@
     </row>
     <row r="649">
       <c r="A649" s="1" t="n">
-        <v>83563</v>
+        <v>83544</v>
       </c>
       <c r="B649" s="1" t="inlineStr">
         <is>
-          <t>Processo de Prefeitura</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C649" s="1" t="inlineStr">
         <is>
-          <t>Geral</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D649" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - GC</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E649" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">3173 - Providenciar o Alvará/CLI por favor </t>
+          <t xml:space="preserve">EMPRESA - 6428 CONCEITO CAMPINASBom dia, Tudo bem? poderia gerar a senha da Prefeitura para acesso as Notas. Entrei em contato com a Prefeitura e a mesma me reporto que o site está sofrendo instabilidade quando o acesso é via certificado.Atte. </t>
         </is>
       </c>
       <c r="F649" s="1" t="n">
@@ -49695,7 +49701,7 @@
       <c r="G649" s="1" t="n"/>
       <c r="H649" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Sarah Amaro</t>
         </is>
       </c>
       <c r="I649" s="1" t="inlineStr">
@@ -49704,194 +49710,267 @@
         </is>
       </c>
       <c r="J649" s="2" t="n">
-        <v>46268.54673834491</v>
+        <v>46268.44168938657</v>
       </c>
       <c r="K649" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="L649" s="1" t="inlineStr">
         <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M649" s="1" t="inlineStr">
+        <is>
+          <t>Caroline Nascimento</t>
+        </is>
+      </c>
+      <c r="N649" s="2" t="n">
+        <v>46274.44113792824</v>
+      </c>
+      <c r="O649" s="1" t="n"/>
+      <c r="P649" s="1" t="n"/>
+      <c r="Q649" s="1" t="inlineStr"/>
+      <c r="R649" s="1" t="inlineStr">
+        <is>
+          <t>Solicitado ao cliente o link de acesso para cadastro</t>
+        </is>
+      </c>
+      <c r="S649" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T649" s="1" t="n"/>
+      <c r="U649" s="1" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="n">
+        <v>83563</v>
+      </c>
+      <c r="B650" s="1" t="inlineStr">
+        <is>
+          <t>Processo de Prefeitura</t>
+        </is>
+      </c>
+      <c r="C650" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="D650" s="1" t="inlineStr">
+        <is>
+          <t>SANTOS - GC</t>
+        </is>
+      </c>
+      <c r="E650" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3173 - Providenciar o Alvará/CLI por favor </t>
+        </is>
+      </c>
+      <c r="F650" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G650" s="1" t="n"/>
+      <c r="H650" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
+      <c r="I650" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J650" s="2" t="n">
+        <v>46268.54673834491</v>
+      </c>
+      <c r="K650" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="L650" s="1" t="inlineStr">
+        <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M649" s="1" t="inlineStr">
+      <c r="M650" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N649" s="2" t="n">
+      <c r="N650" s="2" t="n">
         <v>46268.67929375</v>
       </c>
-      <c r="O649" s="1" t="n"/>
-      <c r="P649" s="2" t="n">
+      <c r="O650" s="1" t="n"/>
+      <c r="P650" s="2" t="n">
         <v>46275.64996585648</v>
       </c>
-      <c r="Q649" s="1" t="inlineStr">
+      <c r="Q650" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R649" s="1" t="inlineStr">
+      <c r="R650" s="1" t="inlineStr">
         <is>
           <t>Boa tarde.
 Providenciando a Viabilidade.
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S649" s="1" t="inlineStr">
+      <c r="S650" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T649" s="1" t="n"/>
-      <c r="U649" s="1" t="inlineStr"/>
-    </row>
-    <row r="650">
-      <c r="A650" s="1" t="n">
+      <c r="T650" s="1" t="n"/>
+      <c r="U650" s="1" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="n">
         <v>83564</v>
       </c>
-      <c r="B650" s="1" t="inlineStr">
+      <c r="B651" s="1" t="inlineStr">
         <is>
           <t>Processo de Prefeitura</t>
         </is>
       </c>
-      <c r="C650" s="1" t="inlineStr">
+      <c r="C651" s="1" t="inlineStr">
         <is>
           <t>Geral</t>
         </is>
       </c>
-      <c r="D650" s="1" t="inlineStr">
+      <c r="D651" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E650" s="1" t="inlineStr">
+      <c r="E651" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">3176 - renovar o Alvará/CLi por favor </t>
         </is>
       </c>
-      <c r="F650" s="1" t="n">
+      <c r="F651" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G650" s="1" t="n"/>
-      <c r="H650" s="1" t="inlineStr">
+      <c r="G651" s="1" t="n"/>
+      <c r="H651" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="I650" s="1" t="inlineStr">
+      <c r="I651" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J650" s="2" t="n">
+      <c r="J651" s="2" t="n">
         <v>46268.54783070602</v>
       </c>
-      <c r="K650" s="2" t="n">
+      <c r="K651" s="2" t="n">
         <v>46273</v>
       </c>
-      <c r="L650" s="1" t="inlineStr">
+      <c r="L651" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M650" s="1" t="inlineStr">
+      <c r="M651" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N650" s="2" t="n">
+      <c r="N651" s="2" t="n">
         <v>46268.67942207176</v>
       </c>
-      <c r="O650" s="1" t="n"/>
-      <c r="P650" s="2" t="n">
+      <c r="O651" s="1" t="n"/>
+      <c r="P651" s="2" t="n">
         <v>46275.65324540509</v>
       </c>
-      <c r="Q650" s="1" t="inlineStr">
+      <c r="Q651" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R650" s="1" t="inlineStr">
+      <c r="R651" s="1" t="inlineStr">
         <is>
           <t>Boa tarde.
 Providenciando a Viabilidade.
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S650" s="1" t="inlineStr">
+      <c r="S651" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T650" s="1" t="n"/>
-      <c r="U650" s="1" t="inlineStr"/>
-    </row>
-    <row r="651">
-      <c r="A651" s="1" t="n">
+      <c r="T651" s="1" t="n"/>
+      <c r="U651" s="1" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="n">
         <v>83565</v>
       </c>
-      <c r="B651" s="1" t="inlineStr">
+      <c r="B652" s="1" t="inlineStr">
         <is>
           <t>Processo de Prefeitura</t>
         </is>
       </c>
-      <c r="C651" s="1" t="inlineStr">
+      <c r="C652" s="1" t="inlineStr">
         <is>
           <t>Geral</t>
         </is>
       </c>
-      <c r="D651" s="1" t="inlineStr">
+      <c r="D652" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E651" s="1" t="inlineStr">
+      <c r="E652" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">3177 - Renovação de Alvará/cli por favor </t>
         </is>
       </c>
-      <c r="F651" s="1" t="n">
+      <c r="F652" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G651" s="1" t="n"/>
-      <c r="H651" s="1" t="inlineStr">
+      <c r="G652" s="1" t="n"/>
+      <c r="H652" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="I651" s="1" t="inlineStr">
+      <c r="I652" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J651" s="2" t="n">
+      <c r="J652" s="2" t="n">
         <v>46268.54870725694</v>
       </c>
-      <c r="K651" s="2" t="n">
+      <c r="K652" s="2" t="n">
         <v>46273</v>
       </c>
-      <c r="L651" s="1" t="inlineStr">
+      <c r="L652" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M651" s="1" t="inlineStr">
+      <c r="M652" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N651" s="1" t="n"/>
-      <c r="O651" s="1" t="n"/>
-      <c r="P651" s="2" t="n">
+      <c r="N652" s="1" t="n"/>
+      <c r="O652" s="1" t="n"/>
+      <c r="P652" s="2" t="n">
         <v>46268.56602326389</v>
       </c>
-      <c r="Q651" s="1" t="inlineStr">
+      <c r="Q652" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R651" s="1" t="inlineStr">
+      <c r="R652" s="1" t="inlineStr">
         <is>
           <t>Boa tarde.
 O endereço do AVCB ( AVENIDA CABUÇU Nº: 377) e o endereço da empresa (RUA JOAO MARIANO, 193).
@@ -49899,82 +49978,9 @@
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S651" s="1" t="inlineStr">
+      <c r="S652" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
-        </is>
-      </c>
-      <c r="T651" s="1" t="n"/>
-      <c r="U651" s="1" t="inlineStr"/>
-    </row>
-    <row r="652">
-      <c r="A652" s="1" t="n">
-        <v>83580</v>
-      </c>
-      <c r="B652" s="1" t="inlineStr">
-        <is>
-          <t>Senha</t>
-        </is>
-      </c>
-      <c r="C652" s="1" t="inlineStr">
-        <is>
-          <t>Prefeitura</t>
-        </is>
-      </c>
-      <c r="D652" s="1" t="inlineStr">
-        <is>
-          <t>EF - INDUSTRIA</t>
-        </is>
-      </c>
-      <c r="E652" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde! Por gentileza, verificar e disponibilizar acesso a prefeitura de Santo André para o cliente 6352- Novais It.Acredito que seja pela nova versão giss online. Pois não estou conseguindo acessar pelos cadastrados no MGC (giss online antigo e Ginfes).</t>
-        </is>
-      </c>
-      <c r="F652" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G652" s="1" t="n"/>
-      <c r="H652" s="1" t="inlineStr">
-        <is>
-          <t>Sarah Amaro</t>
-        </is>
-      </c>
-      <c r="I652" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J652" s="2" t="n">
-        <v>46268.64901890046</v>
-      </c>
-      <c r="K652" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="L652" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M652" s="1" t="inlineStr">
-        <is>
-          <t>Thayna Melo</t>
-        </is>
-      </c>
-      <c r="N652" s="2" t="n">
-        <v>46274.37637820602</v>
-      </c>
-      <c r="O652" s="1" t="n"/>
-      <c r="P652" s="1" t="n"/>
-      <c r="Q652" s="1" t="inlineStr"/>
-      <c r="R652" s="1" t="inlineStr">
-        <is>
-          <t>Aguardando retorno de cliente</t>
-        </is>
-      </c>
-      <c r="S652" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
         </is>
       </c>
       <c r="T652" s="1" t="n"/>
@@ -49982,26 +49988,26 @@
     </row>
     <row r="653">
       <c r="A653" s="1" t="n">
-        <v>83583</v>
+        <v>83580</v>
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>Processo de Prefeitura</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C653" s="1" t="inlineStr">
         <is>
-          <t>Geral</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D653" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - GC</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E653" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">3174 - Ronovação do Alvará/Cli por favor </t>
+          <t>Boa tarde! Por gentileza, verificar e disponibilizar acesso a prefeitura de Santo André para o cliente 6352- Novais It.Acredito que seja pela nova versão giss online. Pois não estou conseguindo acessar pelos cadastrados no MGC (giss online antigo e Ginfes).</t>
         </is>
       </c>
       <c r="F653" s="1" t="n">
@@ -50010,7 +50016,7 @@
       <c r="G653" s="1" t="n"/>
       <c r="H653" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Sarah Amaro</t>
         </is>
       </c>
       <c r="I653" s="1" t="inlineStr">
@@ -50019,10 +50025,10 @@
         </is>
       </c>
       <c r="J653" s="2" t="n">
-        <v>46268.69685413194</v>
+        <v>46268.64901890046</v>
       </c>
       <c r="K653" s="2" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="L653" s="1" t="inlineStr">
         <is>
@@ -50031,102 +50037,98 @@
       </c>
       <c r="M653" s="1" t="inlineStr">
         <is>
-          <t>Rafaella Massuia</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="N653" s="2" t="n">
-        <v>46273.69585717592</v>
+        <v>46274.37637820602</v>
       </c>
       <c r="O653" s="1" t="n"/>
       <c r="P653" s="1" t="n"/>
       <c r="Q653" s="1" t="inlineStr"/>
       <c r="R653" s="1" t="inlineStr">
         <is>
+          <t>Aguardando retorno de cliente</t>
+        </is>
+      </c>
+      <c r="S653" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T653" s="1" t="n"/>
+      <c r="U653" s="1" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="n">
+        <v>83583</v>
+      </c>
+      <c r="B654" s="1" t="inlineStr">
+        <is>
+          <t>Processo de Prefeitura</t>
+        </is>
+      </c>
+      <c r="C654" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="D654" s="1" t="inlineStr">
+        <is>
+          <t>SANTOS - GC</t>
+        </is>
+      </c>
+      <c r="E654" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3174 - Ronovação do Alvará/Cli por favor </t>
+        </is>
+      </c>
+      <c r="F654" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G654" s="1" t="n"/>
+      <c r="H654" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
+      <c r="I654" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J654" s="2" t="n">
+        <v>46268.69685413194</v>
+      </c>
+      <c r="K654" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="L654" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M654" s="1" t="inlineStr">
+        <is>
+          <t>Rafaella Massuia</t>
+        </is>
+      </c>
+      <c r="N654" s="2" t="n">
+        <v>46273.69585717592</v>
+      </c>
+      <c r="O654" s="1" t="n"/>
+      <c r="P654" s="1" t="n"/>
+      <c r="Q654" s="1" t="inlineStr"/>
+      <c r="R654" s="1" t="inlineStr">
+        <is>
           <t>Boa tarde,
 Aguardando a aprovação da viabilidade.
 Atenciosamente</t>
         </is>
       </c>
-      <c r="S653" s="1" t="inlineStr">
+      <c r="S654" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T653" s="1" t="n"/>
-      <c r="U653" s="1" t="inlineStr"/>
-    </row>
-    <row r="654">
-      <c r="A654" s="1" t="n">
-        <v>83704</v>
-      </c>
-      <c r="B654" s="1" t="inlineStr">
-        <is>
-          <t>Levantamento de Débitos Mensal</t>
-        </is>
-      </c>
-      <c r="C654" s="1" t="inlineStr">
-        <is>
-          <t>PGFN</t>
-        </is>
-      </c>
-      <c r="D654" s="1" t="inlineStr">
-        <is>
-          <t>SANTOS - GC</t>
-        </is>
-      </c>
-      <c r="E654" s="1" t="inlineStr">
-        <is>
-          <t>4200 - Henrique Leone- Por gentileza simular o parcelamento dos débitos que são mencionados na carta em anexo por favor.</t>
-        </is>
-      </c>
-      <c r="F654" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G654" s="1" t="n"/>
-      <c r="H654" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="I654" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J654" s="2" t="n">
-        <v>46274.42889741898</v>
-      </c>
-      <c r="K654" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="L654" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M654" s="1" t="inlineStr">
-        <is>
-          <t>Rafaella Massuia</t>
-        </is>
-      </c>
-      <c r="N654" s="1" t="n"/>
-      <c r="O654" s="1" t="n"/>
-      <c r="P654" s="2" t="n">
-        <v>46275.83228032407</v>
-      </c>
-      <c r="Q654" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="R654" s="1" t="inlineStr">
-        <is>
-          <t>Segue proposta e simulado para parcelamento das inscrições 80 6 26 082503-45, 80 2 26 064060-04 e 80 2 26 064396-03, referente a notificação recebida.</t>
-        </is>
-      </c>
-      <c r="S654" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
         </is>
       </c>
       <c r="T654" s="1" t="n"/>
@@ -50134,36 +50136,32 @@
     </row>
     <row r="655">
       <c r="A655" s="1" t="n">
-        <v>83960</v>
+        <v>83704</v>
       </c>
       <c r="B655" s="1" t="inlineStr">
         <is>
-          <t>Restituição</t>
+          <t>Levantamento de Débitos Mensal</t>
         </is>
       </c>
       <c r="C655" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>PGFN</t>
         </is>
       </c>
       <c r="D655" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>SANTOS - GC</t>
         </is>
       </c>
       <c r="E655" s="1" t="inlineStr">
         <is>
-          <t>Prezados, Houve um erro na informação de quotas do IRPJ e CSLL 3º trimestre de 2025.anexo comprovantes de pagamento do protesto.</t>
+          <t>4200 - Henrique Leone- Por gentileza simular o parcelamento dos débitos que são mencionados na carta em anexo por favor.</t>
         </is>
       </c>
       <c r="F655" s="1" t="n">
-        <v>2575</v>
-      </c>
-      <c r="G655" s="1" t="inlineStr">
-        <is>
-          <t>VITTA SALAD - PRODUTOS NATURAIS COMÉRCIO DE HORTI FRUTI LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G655" s="1" t="n"/>
       <c r="H655" s="1" t="inlineStr">
         <is>
           <t>Ellen Leite</t>
@@ -50175,29 +50173,39 @@
         </is>
       </c>
       <c r="J655" s="2" t="n">
-        <v>46279.67358012732</v>
+        <v>46274.42889741898</v>
       </c>
       <c r="K655" s="2" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="L655" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M655" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Rafaella Massuia</t>
         </is>
       </c>
       <c r="N655" s="1" t="n"/>
       <c r="O655" s="1" t="n"/>
-      <c r="P655" s="1" t="n"/>
-      <c r="Q655" s="1" t="inlineStr"/>
-      <c r="R655" s="1" t="inlineStr"/>
+      <c r="P655" s="2" t="n">
+        <v>46275.83228032407</v>
+      </c>
+      <c r="Q655" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R655" s="1" t="inlineStr">
+        <is>
+          <t>Segue proposta e simulado para parcelamento das inscrições 80 6 26 082503-45, 80 2 26 064060-04 e 80 2 26 064396-03, referente a notificação recebida.</t>
+        </is>
+      </c>
       <c r="S655" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T655" s="1" t="n"/>
@@ -50205,16 +50213,16 @@
     </row>
     <row r="656">
       <c r="A656" s="1" t="n">
-        <v>83708</v>
+        <v>83960</v>
       </c>
       <c r="B656" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Restituição</t>
         </is>
       </c>
       <c r="C656" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D656" s="1" t="inlineStr">
@@ -50224,20 +50232,20 @@
       </c>
       <c r="E656" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, providenciar a CND Municipal e enviar para Sr. Aurelio </t>
+          <t>Prezados, Houve um erro na informação de quotas do IRPJ e CSLL 3º trimestre de 2025.anexo comprovantes de pagamento do protesto.</t>
         </is>
       </c>
       <c r="F656" s="1" t="n">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="G656" s="1" t="inlineStr">
         <is>
-          <t>P.E Latina Maquinas para Rotulagem Ltda.</t>
+          <t>VITTA SALAD - PRODUTOS NATURAIS COMÉRCIO DE HORTI FRUTI LTDA</t>
         </is>
       </c>
       <c r="H656" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I656" s="1" t="inlineStr">
@@ -50246,117 +50254,111 @@
         </is>
       </c>
       <c r="J656" s="2" t="n">
-        <v>46274.43152577546</v>
+        <v>46279.67358012732</v>
       </c>
       <c r="K656" s="2" t="n">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="L656" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M656" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N656" s="1" t="n"/>
       <c r="O656" s="1" t="n"/>
-      <c r="P656" s="2" t="n">
+      <c r="P656" s="1" t="n"/>
+      <c r="Q656" s="1" t="inlineStr"/>
+      <c r="R656" s="1" t="inlineStr"/>
+      <c r="S656" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T656" s="1" t="n"/>
+      <c r="U656" s="1" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="n">
+        <v>83708</v>
+      </c>
+      <c r="B657" s="1" t="inlineStr">
+        <is>
+          <t>Certidão</t>
+        </is>
+      </c>
+      <c r="C657" s="1" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="D657" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E657" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por gentileza, providenciar a CND Municipal e enviar para Sr. Aurelio </t>
+        </is>
+      </c>
+      <c r="F657" s="1" t="n">
+        <v>2576</v>
+      </c>
+      <c r="G657" s="1" t="inlineStr">
+        <is>
+          <t>P.E Latina Maquinas para Rotulagem Ltda.</t>
+        </is>
+      </c>
+      <c r="H657" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="I657" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J657" s="2" t="n">
+        <v>46274.43152577546</v>
+      </c>
+      <c r="K657" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="L657" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M657" s="1" t="inlineStr">
+        <is>
+          <t>Simone Marques</t>
+        </is>
+      </c>
+      <c r="N657" s="1" t="n"/>
+      <c r="O657" s="1" t="n"/>
+      <c r="P657" s="2" t="n">
         <v>46280.78062473379</v>
       </c>
-      <c r="Q656" s="1" t="inlineStr">
+      <c r="Q657" s="1" t="inlineStr">
         <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="R656" s="1" t="inlineStr">
+      <c r="R657" s="1" t="inlineStr">
         <is>
           <t>Boa noite!
 Não foi possivel emitir, há débitos em aberto.</t>
         </is>
       </c>
-      <c r="S656" s="1" t="inlineStr">
+      <c r="S657" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
-        </is>
-      </c>
-      <c r="T656" s="1" t="n"/>
-      <c r="U656" s="1" t="inlineStr"/>
-    </row>
-    <row r="657">
-      <c r="A657" s="1" t="n">
-        <v>82566</v>
-      </c>
-      <c r="B657" s="1" t="inlineStr">
-        <is>
-          <t>Alteração Contratual</t>
-        </is>
-      </c>
-      <c r="C657" s="1" t="inlineStr">
-        <is>
-          <t>Objeto Social</t>
-        </is>
-      </c>
-      <c r="D657" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E657" s="1" t="inlineStr">
-        <is>
-          <t>Alteração contratual do objeto social da empresa: 2618-G.M. Omine - Quitandão Ltda Grupo: Quitandão do GuarujáTributação: Lucro RealProposta já negociada no valor de R$2.500,00 em 3xInserir CNAE´s de Panificação (O cliente está produzindo e assando pães)</t>
-        </is>
-      </c>
-      <c r="F657" s="1" t="n">
-        <v>2618</v>
-      </c>
-      <c r="G657" s="1" t="inlineStr">
-        <is>
-          <t>G. M. OMINE - QUITANDAO LTDA</t>
-        </is>
-      </c>
-      <c r="H657" s="1" t="inlineStr">
-        <is>
-          <t>Thifany Leite</t>
-        </is>
-      </c>
-      <c r="I657" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J657" s="2" t="n">
-        <v>46252.5234783912</v>
-      </c>
-      <c r="K657" s="2" t="n">
-        <v>46280</v>
-      </c>
-      <c r="L657" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M657" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N657" s="2" t="n">
-        <v>46260.66696751158</v>
-      </c>
-      <c r="O657" s="1" t="n"/>
-      <c r="P657" s="1" t="n"/>
-      <c r="Q657" s="1" t="inlineStr"/>
-      <c r="R657" s="1" t="inlineStr">
-        <is>
-          <t>Processo em elaboração</t>
-        </is>
-      </c>
-      <c r="S657" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
         </is>
       </c>
       <c r="T657" s="1" t="n"/>
@@ -50364,16 +50366,16 @@
     </row>
     <row r="658">
       <c r="A658" s="1" t="n">
-        <v>83030</v>
+        <v>82566</v>
       </c>
       <c r="B658" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C658" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Objeto Social</t>
         </is>
       </c>
       <c r="D658" s="1" t="inlineStr">
@@ -50383,15 +50385,15 @@
       </c>
       <c r="E658" s="1" t="inlineStr">
         <is>
-          <t>Abertura de holding da empresa 2681- Mercadinho Alves e Farias.Grupo: Paraná GuarulhosTributação: Lucro PresumidoFinalidade: Holding/EstratégiaForma Juridica: LTDAProposta já negociada no valor de: R$9.800,00 em 5x</t>
+          <t>Alteração contratual do objeto social da empresa: 2618-G.M. Omine - Quitandão Ltda Grupo: Quitandão do GuarujáTributação: Lucro RealProposta já negociada no valor de R$2.500,00 em 3xInserir CNAE´s de Panificação (O cliente está produzindo e assando pães)</t>
         </is>
       </c>
       <c r="F658" s="1" t="n">
-        <v>2681</v>
+        <v>2618</v>
       </c>
       <c r="G658" s="1" t="inlineStr">
         <is>
-          <t>COMÉRCIO DE ALIMENTOS ALVES E FARIAS LTDA</t>
+          <t>G. M. OMINE - QUITANDAO LTDA</t>
         </is>
       </c>
       <c r="H658" s="1" t="inlineStr">
@@ -50405,10 +50407,10 @@
         </is>
       </c>
       <c r="J658" s="2" t="n">
-        <v>46260.44763082176</v>
+        <v>46252.5234783912</v>
       </c>
       <c r="K658" s="2" t="n">
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="L658" s="1" t="inlineStr">
         <is>
@@ -50421,7 +50423,7 @@
         </is>
       </c>
       <c r="N658" s="2" t="n">
-        <v>46267.34800902778</v>
+        <v>46260.66696751158</v>
       </c>
       <c r="O658" s="1" t="n"/>
       <c r="P658" s="1" t="n"/>
@@ -50441,16 +50443,16 @@
     </row>
     <row r="659">
       <c r="A659" s="1" t="n">
-        <v>83004</v>
+        <v>83030</v>
       </c>
       <c r="B659" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C659" s="1" t="inlineStr">
         <is>
-          <t>Sócios</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D659" s="1" t="inlineStr">
@@ -50460,20 +50462,20 @@
       </c>
       <c r="E659" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual na empresa 2710-HORTIFRUTI BOM DO CAMPOGrupo: AlvoradaRETIRAR A LETICIA TORQUATO SILVEIRA DO QUADRO SOCIETÁRIO</t>
+          <t>Abertura de holding da empresa 2681- Mercadinho Alves e Farias.Grupo: Paraná GuarulhosTributação: Lucro PresumidoFinalidade: Holding/EstratégiaForma Juridica: LTDAProposta já negociada no valor de: R$9.800,00 em 5x</t>
         </is>
       </c>
       <c r="F659" s="1" t="n">
-        <v>2710</v>
+        <v>2681</v>
       </c>
       <c r="G659" s="1" t="inlineStr">
         <is>
-          <t>HORTIFRUTI BOM DO CAMPO LTDA</t>
+          <t>COMÉRCIO DE ALIMENTOS ALVES E FARIAS LTDA</t>
         </is>
       </c>
       <c r="H659" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I659" s="1" t="inlineStr">
@@ -50482,7 +50484,7 @@
         </is>
       </c>
       <c r="J659" s="2" t="n">
-        <v>46259.70523434028</v>
+        <v>46260.44763082176</v>
       </c>
       <c r="K659" s="2" t="n">
         <v>46287</v>
@@ -50498,16 +50500,14 @@
         </is>
       </c>
       <c r="N659" s="2" t="n">
-        <v>46266.72352233796</v>
+        <v>46267.34800902778</v>
       </c>
       <c r="O659" s="1" t="n"/>
       <c r="P659" s="1" t="n"/>
       <c r="Q659" s="1" t="inlineStr"/>
       <c r="R659" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.
-Preparando a minuta.
-Atenciosamente,</t>
+          <t>Processo em elaboração</t>
         </is>
       </c>
       <c r="S659" s="1" t="inlineStr">
@@ -50520,39 +50520,39 @@
     </row>
     <row r="660">
       <c r="A660" s="1" t="n">
-        <v>83570</v>
+        <v>83004</v>
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>Inuitilização de Nota Fiscais</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C660" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D660" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E660" s="1" t="inlineStr">
         <is>
-          <t>Bom dia. Nosso cliente 2789 está com um valor de ISS em aberto. Este valor é referente a uma NF que foi emitida incorretamente pela MG e não foi cancelada.Precisamos fazer um processo de cancelamento desta nota e cancelamento do valor que está sendo cobrado de ISS.NF Anexa</t>
+          <t>Alteração contratual na empresa 2710-HORTIFRUTI BOM DO CAMPOGrupo: AlvoradaRETIRAR A LETICIA TORQUATO SILVEIRA DO QUADRO SOCIETÁRIO</t>
         </is>
       </c>
       <c r="F660" s="1" t="n">
-        <v>2789</v>
+        <v>2710</v>
       </c>
       <c r="G660" s="1" t="inlineStr">
         <is>
-          <t>MARINGÁ MANUTENÇÃO DE EQUIPAMENTOS LTDA</t>
+          <t>HORTIFRUTI BOM DO CAMPO LTDA</t>
         </is>
       </c>
       <c r="H660" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I660" s="1" t="inlineStr">
@@ -50561,10 +50561,10 @@
         </is>
       </c>
       <c r="J660" s="2" t="n">
-        <v>46268.57512141204</v>
+        <v>46259.70523434028</v>
       </c>
       <c r="K660" s="2" t="n">
-        <v>46272</v>
+        <v>46287</v>
       </c>
       <c r="L660" s="1" t="inlineStr">
         <is>
@@ -50573,20 +50573,20 @@
       </c>
       <c r="M660" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N660" s="2" t="n">
-        <v>46273.66325274306</v>
+        <v>46266.72352233796</v>
       </c>
       <c r="O660" s="1" t="n"/>
       <c r="P660" s="1" t="n"/>
       <c r="Q660" s="1" t="inlineStr"/>
       <c r="R660" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tarde!
-A Prefeitura solicita que seja informado o motivo do cancelamento. Qual o motivo?
-Iremos precisar enviar ao cliente a carta de anuência e procuração para assinatura. </t>
+          <t>Boa tarde.
+Preparando a minuta.
+Atenciosamente,</t>
         </is>
       </c>
       <c r="S660" s="1" t="inlineStr">
@@ -50599,39 +50599,39 @@
     </row>
     <row r="661">
       <c r="A661" s="1" t="n">
-        <v>82573</v>
+        <v>83570</v>
       </c>
       <c r="B661" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Inuitilização de Nota Fiscais</t>
         </is>
       </c>
       <c r="C661" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D661" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E661" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual de endereço da empresa 2823-G.T. Oshiro Distribuidora de Hortifruttigranjeiros LtdaGrupo: Quitandão do GuarujáTributação: Lucro PresumidoProposta já negociada no valor de R$2.500,00 em 3xOBS.: Alteração de Endereço para "RUA IRACEMA, 378"</t>
+          <t>Bom dia. Nosso cliente 2789 está com um valor de ISS em aberto. Este valor é referente a uma NF que foi emitida incorretamente pela MG e não foi cancelada.Precisamos fazer um processo de cancelamento desta nota e cancelamento do valor que está sendo cobrado de ISS.NF Anexa</t>
         </is>
       </c>
       <c r="F661" s="1" t="n">
-        <v>2823</v>
+        <v>2789</v>
       </c>
       <c r="G661" s="1" t="inlineStr">
         <is>
-          <t>GT Oshiro Distribuidora de Hortifrutigranjeiros Ltda</t>
+          <t>MARINGÁ MANUTENÇÃO DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H661" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I661" s="1" t="inlineStr">
@@ -50640,10 +50640,10 @@
         </is>
       </c>
       <c r="J661" s="2" t="n">
-        <v>46252.54034239583</v>
+        <v>46268.57512141204</v>
       </c>
       <c r="K661" s="2" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="L661" s="1" t="inlineStr">
         <is>
@@ -50652,18 +50652,20 @@
       </c>
       <c r="M661" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N661" s="2" t="n">
-        <v>46260.66719386574</v>
+        <v>46273.66325274306</v>
       </c>
       <c r="O661" s="1" t="n"/>
       <c r="P661" s="1" t="n"/>
       <c r="Q661" s="1" t="inlineStr"/>
       <c r="R661" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo em elaboração </t>
+          <t xml:space="preserve">Boa tarde!
+A Prefeitura solicita que seja informado o motivo do cancelamento. Qual o motivo?
+Iremos precisar enviar ao cliente a carta de anuência e procuração para assinatura. </t>
         </is>
       </c>
       <c r="S661" s="1" t="inlineStr">
@@ -50676,26 +50678,26 @@
     </row>
     <row r="662">
       <c r="A662" s="1" t="n">
-        <v>83990</v>
+        <v>82573</v>
       </c>
       <c r="B662" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C662" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D662" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E662" s="1" t="inlineStr">
         <is>
-          <t>A empresa 2823 está sem Inscrição Municipal disponível, impossibilitando o levantamento de débitos.Foi localizado um e-mail de 08/05/2025 informando que a inscrição estava em processo de abertura.Podem verificar a situação atual e nos auxiliar com o levantamento?</t>
+          <t>Alteração contratual de endereço da empresa 2823-G.T. Oshiro Distribuidora de Hortifruttigranjeiros LtdaGrupo: Quitandão do GuarujáTributação: Lucro PresumidoProposta já negociada no valor de R$2.500,00 em 3xOBS.: Alteração de Endereço para "RUA IRACEMA, 378"</t>
         </is>
       </c>
       <c r="F662" s="1" t="n">
@@ -50708,7 +50710,7 @@
       </c>
       <c r="H662" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I662" s="1" t="inlineStr">
@@ -50717,26 +50719,32 @@
         </is>
       </c>
       <c r="J662" s="2" t="n">
-        <v>46280.43936226852</v>
+        <v>46252.54034239583</v>
       </c>
       <c r="K662" s="2" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="L662" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M662" s="1" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
-        </is>
-      </c>
-      <c r="N662" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N662" s="2" t="n">
+        <v>46260.66719386574</v>
+      </c>
       <c r="O662" s="1" t="n"/>
       <c r="P662" s="1" t="n"/>
       <c r="Q662" s="1" t="inlineStr"/>
-      <c r="R662" s="1" t="inlineStr"/>
+      <c r="R662" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Processo em elaboração </t>
+        </is>
+      </c>
       <c r="S662" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -50747,63 +50755,67 @@
     </row>
     <row r="663">
       <c r="A663" s="1" t="n">
-        <v>83967</v>
+        <v>83990</v>
       </c>
       <c r="B663" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C663" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D663" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="E663" s="1" t="inlineStr">
         <is>
-          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A3</t>
+          <t>A empresa 2823 está sem Inscrição Municipal disponível, impossibilitando o levantamento de débitos.Foi localizado um e-mail de 08/05/2025 informando que a inscrição estava em processo de abertura.Podem verificar a situação atual e nos auxiliar com o levantamento?</t>
         </is>
       </c>
       <c r="F663" s="1" t="n">
-        <v>2853</v>
+        <v>2823</v>
       </c>
       <c r="G663" s="1" t="inlineStr">
         <is>
-          <t>BERTON SUPERMERCADOS COMERCIO DE ALIMENTOS LTDA</t>
-        </is>
-      </c>
-      <c r="H663" s="1" t="n"/>
+          <t>GT Oshiro Distribuidora de Hortifrutigranjeiros Ltda</t>
+        </is>
+      </c>
+      <c r="H663" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
       <c r="I663" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J663" s="2" t="n">
-        <v>46279.73161238426</v>
+        <v>46280.43936226852</v>
       </c>
       <c r="K663" s="2" t="n">
-        <v>46307</v>
+        <v>46281</v>
       </c>
       <c r="L663" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M663" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Kauany Pereira</t>
         </is>
       </c>
       <c r="N663" s="1" t="n"/>
       <c r="O663" s="1" t="n"/>
       <c r="P663" s="1" t="n"/>
       <c r="Q663" s="1" t="inlineStr"/>
-      <c r="R663" s="1" t="n"/>
+      <c r="R663" s="1" t="inlineStr"/>
       <c r="S663" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -50814,7 +50826,7 @@
     </row>
     <row r="664">
       <c r="A664" s="1" t="n">
-        <v>83969</v>
+        <v>83967</v>
       </c>
       <c r="B664" s="1" t="inlineStr">
         <is>
@@ -50833,7 +50845,7 @@
       </c>
       <c r="E664" s="1" t="inlineStr">
         <is>
-          <t>Abertura de nova empresa vinculada ao grupo: Berton Tributação: Simples NacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A2</t>
+          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A3</t>
         </is>
       </c>
       <c r="F664" s="1" t="n">
@@ -50851,7 +50863,7 @@
         </is>
       </c>
       <c r="J664" s="2" t="n">
-        <v>46279.73473055555</v>
+        <v>46279.73161238426</v>
       </c>
       <c r="K664" s="2" t="n">
         <v>46307</v>
@@ -50881,7 +50893,7 @@
     </row>
     <row r="665">
       <c r="A665" s="1" t="n">
-        <v>83970</v>
+        <v>83969</v>
       </c>
       <c r="B665" s="1" t="inlineStr">
         <is>
@@ -50900,7 +50912,7 @@
       </c>
       <c r="E665" s="1" t="inlineStr">
         <is>
-          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A1</t>
+          <t>Abertura de nova empresa vinculada ao grupo: Berton Tributação: Simples NacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A2</t>
         </is>
       </c>
       <c r="F665" s="1" t="n">
@@ -50918,7 +50930,7 @@
         </is>
       </c>
       <c r="J665" s="2" t="n">
-        <v>46279.73921559028</v>
+        <v>46279.73473055555</v>
       </c>
       <c r="K665" s="2" t="n">
         <v>46307</v>
@@ -50948,7 +50960,7 @@
     </row>
     <row r="666">
       <c r="A666" s="1" t="n">
-        <v>83972</v>
+        <v>83970</v>
       </c>
       <c r="B666" s="1" t="inlineStr">
         <is>
@@ -50967,7 +50979,7 @@
       </c>
       <c r="E666" s="1" t="inlineStr">
         <is>
-          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples NacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala B-1</t>
+          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A1</t>
         </is>
       </c>
       <c r="F666" s="1" t="n">
@@ -50985,7 +50997,7 @@
         </is>
       </c>
       <c r="J666" s="2" t="n">
-        <v>46279.74341068287</v>
+        <v>46279.73921559028</v>
       </c>
       <c r="K666" s="2" t="n">
         <v>46307</v>
@@ -51015,7 +51027,7 @@
     </row>
     <row r="667">
       <c r="A667" s="1" t="n">
-        <v>83974</v>
+        <v>83972</v>
       </c>
       <c r="B667" s="1" t="inlineStr">
         <is>
@@ -51034,7 +51046,7 @@
       </c>
       <c r="E667" s="1" t="inlineStr">
         <is>
-          <t>Abertura de empresa vinculada ao grupo: Berton Tributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala B-2</t>
+          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples NacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala B-1</t>
         </is>
       </c>
       <c r="F667" s="1" t="n">
@@ -51052,7 +51064,7 @@
         </is>
       </c>
       <c r="J667" s="2" t="n">
-        <v>46279.74682947917</v>
+        <v>46279.74341068287</v>
       </c>
       <c r="K667" s="2" t="n">
         <v>46307</v>
@@ -51082,73 +51094,63 @@
     </row>
     <row r="668">
       <c r="A668" s="1" t="n">
-        <v>83689</v>
+        <v>83974</v>
       </c>
       <c r="B668" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C668" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D668" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E668" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">anteriormente Havia aberto um chamado no qual foi concluído Realmente havia posto a senha e login da prefeitura de holambra porém ao efetuar o fechamento neste mês aparenta que o login e senha é invalido. solicito a Verificação.  </t>
+          <t>Abertura de empresa vinculada ao grupo: Berton Tributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala B-2</t>
         </is>
       </c>
       <c r="F668" s="1" t="n">
-        <v>2878</v>
+        <v>2853</v>
       </c>
       <c r="G668" s="1" t="inlineStr">
         <is>
-          <t>CEOS EMPREENDIMENTOS S.A.</t>
-        </is>
-      </c>
-      <c r="H668" s="1" t="inlineStr">
-        <is>
-          <t>Sarah Amaro</t>
-        </is>
-      </c>
+          <t>BERTON SUPERMERCADOS COMERCIO DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="H668" s="1" t="n"/>
       <c r="I668" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J668" s="2" t="n">
-        <v>46273.78789517361</v>
+        <v>46279.74682947917</v>
       </c>
       <c r="K668" s="2" t="n">
-        <v>46282</v>
+        <v>46307</v>
       </c>
       <c r="L668" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M668" s="1" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
-        </is>
-      </c>
-      <c r="N668" s="2" t="n">
-        <v>46275.64629545139</v>
-      </c>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N668" s="1" t="n"/>
       <c r="O668" s="1" t="n"/>
       <c r="P668" s="1" t="n"/>
       <c r="Q668" s="1" t="inlineStr"/>
-      <c r="R668" s="1" t="inlineStr">
-        <is>
-          <t>Prefeitura com instabilidade.</t>
-        </is>
-      </c>
+      <c r="R668" s="1" t="n"/>
       <c r="S668" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -51159,51 +51161,51 @@
     </row>
     <row r="669">
       <c r="A669" s="1" t="n">
-        <v>83702</v>
+        <v>83689</v>
       </c>
       <c r="B669" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C669" s="1" t="inlineStr">
         <is>
-          <t>Razão Social</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D669" s="1" t="inlineStr">
         <is>
+          <t>EF - INDUSTRIA</t>
+        </is>
+      </c>
+      <c r="E669" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anteriormente Havia aberto um chamado no qual foi concluído Realmente havia posto a senha e login da prefeitura de holambra porém ao efetuar o fechamento neste mês aparenta que o login e senha é invalido. solicito a Verificação.  </t>
+        </is>
+      </c>
+      <c r="F669" s="1" t="n">
+        <v>2878</v>
+      </c>
+      <c r="G669" s="1" t="inlineStr">
+        <is>
+          <t>CEOS EMPREENDIMENTOS S.A.</t>
+        </is>
+      </c>
+      <c r="H669" s="1" t="inlineStr">
+        <is>
+          <t>Sarah Amaro</t>
+        </is>
+      </c>
+      <c r="I669" s="1" t="inlineStr">
+        <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="E669" s="1" t="inlineStr">
-        <is>
-          <t>AGGYO ADMINISTRAÇÃO DE BENS E PATICIPAÇÕES S.ACNPJ: 21.940.311/0001-00 Alteração: JSVE RENTAL ADMINISTRAÇÃO DE BENS E PATICIPAÇÕES S.A</t>
-        </is>
-      </c>
-      <c r="F669" s="1" t="n">
-        <v>2956</v>
-      </c>
-      <c r="G669" s="1" t="inlineStr">
-        <is>
-          <t>AGGYO ADMINISTRAÇÃO DE BENS E PARTICIPAÇÕES S.A.</t>
-        </is>
-      </c>
-      <c r="H669" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
-      <c r="I669" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
       <c r="J669" s="2" t="n">
-        <v>46274.42399050926</v>
+        <v>46273.78789517361</v>
       </c>
       <c r="K669" s="2" t="n">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="L669" s="1" t="inlineStr">
         <is>
@@ -51212,107 +51214,102 @@
       </c>
       <c r="M669" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="N669" s="2" t="n">
-        <v>46274.79115416667</v>
+        <v>46275.64629545139</v>
       </c>
       <c r="O669" s="1" t="n"/>
       <c r="P669" s="1" t="n"/>
       <c r="Q669" s="1" t="inlineStr"/>
       <c r="R669" s="1" t="inlineStr">
         <is>
+          <t>Prefeitura com instabilidade.</t>
+        </is>
+      </c>
+      <c r="S669" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T669" s="1" t="n"/>
+      <c r="U669" s="1" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>83702</v>
+      </c>
+      <c r="B670" s="1" t="inlineStr">
+        <is>
+          <t>Alteração Contratual</t>
+        </is>
+      </c>
+      <c r="C670" s="1" t="inlineStr">
+        <is>
+          <t>Razão Social</t>
+        </is>
+      </c>
+      <c r="D670" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="E670" s="1" t="inlineStr">
+        <is>
+          <t>AGGYO ADMINISTRAÇÃO DE BENS E PATICIPAÇÕES S.ACNPJ: 21.940.311/0001-00 Alteração: JSVE RENTAL ADMINISTRAÇÃO DE BENS E PATICIPAÇÕES S.A</t>
+        </is>
+      </c>
+      <c r="F670" s="1" t="n">
+        <v>2956</v>
+      </c>
+      <c r="G670" s="1" t="inlineStr">
+        <is>
+          <t>AGGYO ADMINISTRAÇÃO DE BENS E PARTICIPAÇÕES S.A.</t>
+        </is>
+      </c>
+      <c r="H670" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Ribeiro</t>
+        </is>
+      </c>
+      <c r="I670" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J670" s="2" t="n">
+        <v>46274.42399050926</v>
+      </c>
+      <c r="K670" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="L670" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M670" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
+      <c r="N670" s="2" t="n">
+        <v>46274.79115416667</v>
+      </c>
+      <c r="O670" s="1" t="n"/>
+      <c r="P670" s="1" t="n"/>
+      <c r="Q670" s="1" t="inlineStr"/>
+      <c r="R670" s="1" t="inlineStr">
+        <is>
           <t>Prezados(as), boa tarde!
 Alteração contratual em andamento, conforme solicitado.
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S669" s="1" t="inlineStr">
+      <c r="S670" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T669" s="1" t="n"/>
-      <c r="U669" s="1" t="inlineStr"/>
-    </row>
-    <row r="670">
-      <c r="A670" s="1" t="n">
-        <v>82934</v>
-      </c>
-      <c r="B670" s="1" t="inlineStr">
-        <is>
-          <t>Parcelamento Estadual</t>
-        </is>
-      </c>
-      <c r="C670" s="1" t="inlineStr">
-        <is>
-          <t>Divida Ativa</t>
-        </is>
-      </c>
-      <c r="D670" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E670" s="1" t="inlineStr">
-        <is>
-          <t>Por favor efetuar o parcelamento que consta em aberto no CADIN.</t>
-        </is>
-      </c>
-      <c r="F670" s="1" t="n">
-        <v>3033</v>
-      </c>
-      <c r="G670" s="1" t="inlineStr">
-        <is>
-          <t>WORLD FOOD GESTÃO LTDA</t>
-        </is>
-      </c>
-      <c r="H670" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="I670" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J670" s="2" t="n">
-        <v>46258.77766778935</v>
-      </c>
-      <c r="K670" s="2" t="n">
-        <v>46261</v>
-      </c>
-      <c r="L670" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M670" s="1" t="inlineStr">
-        <is>
-          <t>Rodrigo Rego</t>
-        </is>
-      </c>
-      <c r="N670" s="1" t="n"/>
-      <c r="O670" s="1" t="n"/>
-      <c r="P670" s="2" t="n">
-        <v>46276.37249575232</v>
-      </c>
-      <c r="Q670" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="R670" s="1" t="inlineStr">
-        <is>
-          <t>Rodrigo, segue simulado para parcelamento dos débitos federais em aberto da 3033 - WORLD FOOD.
-Apenas dois dos débitos em aberto não estão em CADIN, sendo assim, inclui tudo que há em aberto no simulado.</t>
-        </is>
-      </c>
-      <c r="S670" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
         </is>
       </c>
       <c r="T670" s="1" t="n"/>
@@ -51320,7 +51317,7 @@
     </row>
     <row r="671">
       <c r="A671" s="1" t="n">
-        <v>83075</v>
+        <v>82934</v>
       </c>
       <c r="B671" s="1" t="inlineStr">
         <is>
@@ -51339,20 +51336,20 @@
       </c>
       <c r="E671" s="1" t="inlineStr">
         <is>
-          <t>Prezados, o cliente está solicitando a simulação de parcelamento dos débitos, que estão no CADIN.</t>
+          <t>Por favor efetuar o parcelamento que consta em aberto no CADIN.</t>
         </is>
       </c>
       <c r="F671" s="1" t="n">
-        <v>3153</v>
+        <v>3033</v>
       </c>
       <c r="G671" s="1" t="inlineStr">
         <is>
-          <t>Zibetto Pizzaria Eireli</t>
+          <t>WORLD FOOD GESTÃO LTDA</t>
         </is>
       </c>
       <c r="H671" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I671" s="1" t="inlineStr">
@@ -51361,10 +51358,10 @@
         </is>
       </c>
       <c r="J671" s="2" t="n">
-        <v>46260.70641142361</v>
+        <v>46258.77766778935</v>
       </c>
       <c r="K671" s="2" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="L671" s="1" t="inlineStr">
         <is>
@@ -51379,17 +51376,17 @@
       <c r="N671" s="1" t="n"/>
       <c r="O671" s="1" t="n"/>
       <c r="P671" s="2" t="n">
-        <v>46262.43234614583</v>
+        <v>46276.37249575232</v>
       </c>
       <c r="Q671" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="R671" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia!
-Segue simulados e proposta. </t>
+          <t>Rodrigo, segue simulado para parcelamento dos débitos federais em aberto da 3033 - WORLD FOOD.
+Apenas dois dos débitos em aberto não estão em CADIN, sendo assim, inclui tudo que há em aberto no simulado.</t>
         </is>
       </c>
       <c r="S671" s="1" t="inlineStr">
@@ -51402,39 +51399,39 @@
     </row>
     <row r="672">
       <c r="A672" s="1" t="n">
-        <v>83859</v>
+        <v>83075</v>
       </c>
       <c r="B672" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Parcelamento Estadual</t>
         </is>
       </c>
       <c r="C672" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Divida Ativa</t>
         </is>
       </c>
       <c r="D672" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E672" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por gentileza solicito  CND estadual e municipal da empresa 3253 - COMERCIO DE ALIMENTOS ALVES E FARIA Desde já agradeço.</t>
+          <t>Prezados, o cliente está solicitando a simulação de parcelamento dos débitos, que estão no CADIN.</t>
         </is>
       </c>
       <c r="F672" s="1" t="n">
-        <v>3253</v>
+        <v>3153</v>
       </c>
       <c r="G672" s="1" t="inlineStr">
         <is>
-          <t>COMÉRCIO DE ALIMENTOS ALVES E FARIAS LTDA (FILIAL 02)</t>
+          <t>Zibetto Pizzaria Eireli</t>
         </is>
       </c>
       <c r="H672" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I672" s="1" t="inlineStr">
@@ -51443,10 +51440,10 @@
         </is>
       </c>
       <c r="J672" s="2" t="n">
-        <v>46276.59444927084</v>
+        <v>46260.70641142361</v>
       </c>
       <c r="K672" s="2" t="n">
-        <v>46279</v>
+        <v>46262</v>
       </c>
       <c r="L672" s="1" t="inlineStr">
         <is>
@@ -51455,22 +51452,23 @@
       </c>
       <c r="M672" s="1" t="inlineStr">
         <is>
-          <t>Clara Maria</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="N672" s="1" t="n"/>
       <c r="O672" s="1" t="n"/>
       <c r="P672" s="2" t="n">
-        <v>46276.61261813658</v>
+        <v>46262.43234614583</v>
       </c>
       <c r="Q672" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="R672" s="1" t="inlineStr">
         <is>
-          <t>Segue levantamento referente a 3253 - filial 02, verificar com o cliente se estes débitos apontados na Prefeitura de Itapevi foram pagos na data de ontem 10/09 (constam no relatório que venceram ontem).</t>
+          <t xml:space="preserve">Bom dia!
+Segue simulados e proposta. </t>
         </is>
       </c>
       <c r="S672" s="1" t="inlineStr">
@@ -51483,16 +51481,16 @@
     </row>
     <row r="673">
       <c r="A673" s="1" t="n">
-        <v>84015</v>
+        <v>83859</v>
       </c>
       <c r="B673" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C673" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D673" s="1" t="inlineStr">
@@ -51502,15 +51500,15 @@
       </c>
       <c r="E673" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Boa tarde.Por gentileza solicito  CND estadual e municipal da empresa 3253 - COMERCIO DE ALIMENTOS ALVES E FARIA Desde já agradeço.</t>
         </is>
       </c>
       <c r="F673" s="1" t="n">
-        <v>3482</v>
+        <v>3253</v>
       </c>
       <c r="G673" s="1" t="inlineStr">
         <is>
-          <t>L. A. TAHA - ESTACIONAMENTO</t>
+          <t>COMÉRCIO DE ALIMENTOS ALVES E FARIAS LTDA (FILIAL 02)</t>
         </is>
       </c>
       <c r="H673" s="1" t="inlineStr">
@@ -51524,29 +51522,39 @@
         </is>
       </c>
       <c r="J673" s="2" t="n">
-        <v>46280.47807916666</v>
+        <v>46276.59444927084</v>
       </c>
       <c r="K673" s="2" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="L673" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M673" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Clara Maria</t>
         </is>
       </c>
       <c r="N673" s="1" t="n"/>
       <c r="O673" s="1" t="n"/>
-      <c r="P673" s="1" t="n"/>
-      <c r="Q673" s="1" t="inlineStr"/>
-      <c r="R673" s="1" t="inlineStr"/>
+      <c r="P673" s="2" t="n">
+        <v>46276.61261813658</v>
+      </c>
+      <c r="Q673" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R673" s="1" t="inlineStr">
+        <is>
+          <t>Segue levantamento referente a 3253 - filial 02, verificar com o cliente se estes débitos apontados na Prefeitura de Itapevi foram pagos na data de ontem 10/09 (constam no relatório que venceram ontem).</t>
+        </is>
+      </c>
       <c r="S673" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T673" s="1" t="n"/>
@@ -51554,39 +51562,39 @@
     </row>
     <row r="674">
       <c r="A674" s="1" t="n">
-        <v>82810</v>
+        <v>84015</v>
       </c>
       <c r="B674" s="1" t="inlineStr">
         <is>
-          <t>Processo de VISA</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C674" s="1" t="inlineStr">
         <is>
-          <t>Renovação</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D674" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E674" s="1" t="inlineStr">
         <is>
-          <t>Cliente solicita renovação de alvará de funcionamento.</t>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
         </is>
       </c>
       <c r="F674" s="1" t="n">
-        <v>3759</v>
+        <v>3482</v>
       </c>
       <c r="G674" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDIC NET LTDA </t>
+          <t>L. A. TAHA - ESTACIONAMENTO</t>
         </is>
       </c>
       <c r="H674" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I674" s="1" t="inlineStr">
@@ -51595,34 +51603,26 @@
         </is>
       </c>
       <c r="J674" s="2" t="n">
-        <v>46255.63596686342</v>
+        <v>46280.47807916666</v>
       </c>
       <c r="K674" s="2" t="n">
-        <v>46258</v>
+        <v>46281</v>
       </c>
       <c r="L674" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M674" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N674" s="2" t="n">
-        <v>46273.36963711806</v>
-      </c>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N674" s="1" t="n"/>
       <c r="O674" s="1" t="n"/>
       <c r="P674" s="1" t="n"/>
       <c r="Q674" s="1" t="inlineStr"/>
-      <c r="R674" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prezados(as), bom dia!
-Solicitação em andamento. 
-Atenciosamente, </t>
-        </is>
-      </c>
+      <c r="R674" s="1" t="inlineStr"/>
       <c r="S674" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -51633,7 +51633,7 @@
     </row>
     <row r="675">
       <c r="A675" s="1" t="n">
-        <v>82809</v>
+        <v>82810</v>
       </c>
       <c r="B675" s="1" t="inlineStr">
         <is>
@@ -51656,11 +51656,11 @@
         </is>
       </c>
       <c r="F675" s="1" t="n">
-        <v>3760</v>
+        <v>3759</v>
       </c>
       <c r="G675" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED ALPHA DISTRIBUIDORA DE PRODUTOS MÉDICOS E HOSPITALARES EM GERAL LTDA </t>
+          <t xml:space="preserve">MEDIC NET LTDA </t>
         </is>
       </c>
       <c r="H675" s="1" t="inlineStr">
@@ -51674,7 +51674,7 @@
         </is>
       </c>
       <c r="J675" s="2" t="n">
-        <v>46255.63541871528</v>
+        <v>46255.63596686342</v>
       </c>
       <c r="K675" s="2" t="n">
         <v>46258</v>
@@ -51690,7 +51690,7 @@
         </is>
       </c>
       <c r="N675" s="2" t="n">
-        <v>46273.36949383102</v>
+        <v>46273.36963711806</v>
       </c>
       <c r="O675" s="1" t="n"/>
       <c r="P675" s="1" t="n"/>
@@ -51712,63 +51712,75 @@
     </row>
     <row r="676">
       <c r="A676" s="1" t="n">
-        <v>84048</v>
+        <v>82809</v>
       </c>
       <c r="B676" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Processo de VISA</t>
         </is>
       </c>
       <c r="C676" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Renovação</t>
         </is>
       </c>
       <c r="D676" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E676" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por gentileza providenciar a CND da Prefeitura.Obrigada.</t>
+          <t>Cliente solicita renovação de alvará de funcionamento.</t>
         </is>
       </c>
       <c r="F676" s="1" t="n">
-        <v>3859</v>
+        <v>3760</v>
       </c>
       <c r="G676" s="1" t="inlineStr">
         <is>
-          <t>Montezanno Administração de Bens S.A.</t>
-        </is>
-      </c>
-      <c r="H676" s="1" t="n"/>
+          <t xml:space="preserve">MED ALPHA DISTRIBUIDORA DE PRODUTOS MÉDICOS E HOSPITALARES EM GERAL LTDA </t>
+        </is>
+      </c>
+      <c r="H676" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Ribeiro</t>
+        </is>
+      </c>
       <c r="I676" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J676" s="2" t="n">
-        <v>46280.75768283565</v>
+        <v>46255.63541871528</v>
       </c>
       <c r="K676" s="2" t="n">
-        <v>46281</v>
+        <v>46258</v>
       </c>
       <c r="L676" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M676" s="1" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
-        </is>
-      </c>
-      <c r="N676" s="1" t="n"/>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N676" s="2" t="n">
+        <v>46273.36949383102</v>
+      </c>
       <c r="O676" s="1" t="n"/>
       <c r="P676" s="1" t="n"/>
       <c r="Q676" s="1" t="inlineStr"/>
-      <c r="R676" s="1" t="n"/>
+      <c r="R676" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prezados(as), bom dia!
+Solicitação em andamento. 
+Atenciosamente, </t>
+        </is>
+      </c>
       <c r="S676" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -51779,16 +51791,16 @@
     </row>
     <row r="677">
       <c r="A677" s="1" t="n">
-        <v>84006</v>
+        <v>84048</v>
       </c>
       <c r="B677" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C677" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D677" s="1" t="inlineStr">
@@ -51798,61 +51810,47 @@
       </c>
       <c r="E677" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Boa tarde!Por gentileza providenciar a CND da Prefeitura.Obrigada.</t>
         </is>
       </c>
       <c r="F677" s="1" t="n">
-        <v>3917</v>
+        <v>3859</v>
       </c>
       <c r="G677" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO CASTELO DA SERRA (FILIAL 02)</t>
-        </is>
-      </c>
-      <c r="H677" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+          <t>Montezanno Administração de Bens S.A.</t>
+        </is>
+      </c>
+      <c r="H677" s="1" t="n"/>
       <c r="I677" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J677" s="2" t="n">
-        <v>46280.47271759259</v>
+        <v>46280.75768283565</v>
       </c>
       <c r="K677" s="2" t="n">
         <v>46281</v>
       </c>
       <c r="L677" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M677" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="N677" s="1" t="n"/>
       <c r="O677" s="1" t="n"/>
-      <c r="P677" s="2" t="n">
-        <v>46281.41418700232</v>
-      </c>
-      <c r="Q677" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="R677" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yasmin, segue levantamento de débitos referente a filial 02 3917, anexei a taxa referente 2025 recalculada, vence no dia da emissão, sendo assim, vencimento hoje 16/09. </t>
-        </is>
-      </c>
+      <c r="P677" s="1" t="n"/>
+      <c r="Q677" s="1" t="inlineStr"/>
+      <c r="R677" s="1" t="n"/>
       <c r="S677" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T677" s="1" t="n"/>
@@ -51860,7 +51858,7 @@
     </row>
     <row r="678">
       <c r="A678" s="1" t="n">
-        <v>84016</v>
+        <v>84006</v>
       </c>
       <c r="B678" s="1" t="inlineStr">
         <is>
@@ -51883,11 +51881,11 @@
         </is>
       </c>
       <c r="F678" s="1" t="n">
-        <v>3979</v>
+        <v>3917</v>
       </c>
       <c r="G678" s="1" t="inlineStr">
         <is>
-          <t>OLANA ADMINISTRAÇÃO E PARTICIPAÇÕES S.A.</t>
+          <t>SUPERMERCADO CASTELO DA SERRA (FILIAL 02)</t>
         </is>
       </c>
       <c r="H678" s="1" t="inlineStr">
@@ -51901,14 +51899,14 @@
         </is>
       </c>
       <c r="J678" s="2" t="n">
-        <v>46280.48075957176</v>
+        <v>46280.47271759259</v>
       </c>
       <c r="K678" s="2" t="n">
         <v>46281</v>
       </c>
       <c r="L678" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M678" s="1" t="inlineStr">
@@ -51918,12 +51916,22 @@
       </c>
       <c r="N678" s="1" t="n"/>
       <c r="O678" s="1" t="n"/>
-      <c r="P678" s="1" t="n"/>
-      <c r="Q678" s="1" t="inlineStr"/>
-      <c r="R678" s="1" t="inlineStr"/>
+      <c r="P678" s="2" t="n">
+        <v>46281.41418700232</v>
+      </c>
+      <c r="Q678" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R678" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yasmin, segue levantamento de débitos referente a filial 02 3917, anexei a taxa referente 2025 recalculada, vence no dia da emissão, sendo assim, vencimento hoje 16/09. </t>
+        </is>
+      </c>
       <c r="S678" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T678" s="1" t="n"/>
@@ -51931,16 +51939,16 @@
     </row>
     <row r="679">
       <c r="A679" s="1" t="n">
-        <v>81560</v>
+        <v>84016</v>
       </c>
       <c r="B679" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C679" s="1" t="inlineStr">
         <is>
-          <t>Divida Ativa ICMS</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D679" s="1" t="inlineStr">
@@ -51950,20 +51958,20 @@
       </c>
       <c r="E679" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Certidão de Débitos Estaduais (ICMS) </t>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
         </is>
       </c>
       <c r="F679" s="1" t="n">
-        <v>4091</v>
+        <v>3979</v>
       </c>
       <c r="G679" s="1" t="inlineStr">
         <is>
-          <t>NOBRES DOCES DISTRIBUIDORA LTDA</t>
+          <t>OLANA ADMINISTRAÇÃO E PARTICIPAÇÕES S.A.</t>
         </is>
       </c>
       <c r="H679" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I679" s="1" t="inlineStr">
@@ -51972,39 +51980,29 @@
         </is>
       </c>
       <c r="J679" s="2" t="n">
-        <v>46232.47750069445</v>
+        <v>46280.48075957176</v>
       </c>
       <c r="K679" s="2" t="n">
-        <v>46234</v>
+        <v>46281</v>
       </c>
       <c r="L679" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M679" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N679" s="1" t="n"/>
       <c r="O679" s="1" t="n"/>
-      <c r="P679" s="2" t="n">
-        <v>46233.73991982639</v>
-      </c>
-      <c r="Q679" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
-      <c r="R679" s="1" t="inlineStr">
-        <is>
-          <t>Conforme e-mail do GM Fernando Sensulini, solicitação deve ser desconsiderada.</t>
-        </is>
-      </c>
+      <c r="P679" s="1" t="n"/>
+      <c r="Q679" s="1" t="inlineStr"/>
+      <c r="R679" s="1" t="inlineStr"/>
       <c r="S679" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T679" s="1" t="n"/>
@@ -52012,7 +52010,7 @@
     </row>
     <row r="680">
       <c r="A680" s="1" t="n">
-        <v>81561</v>
+        <v>81560</v>
       </c>
       <c r="B680" s="1" t="inlineStr">
         <is>
@@ -52021,7 +52019,7 @@
       </c>
       <c r="C680" s="1" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Divida Ativa ICMS</t>
         </is>
       </c>
       <c r="D680" s="1" t="inlineStr">
@@ -52031,7 +52029,7 @@
       </c>
       <c r="E680" s="1" t="inlineStr">
         <is>
-          <t>Certidão de Débitos Municipais (ISS)</t>
+          <t xml:space="preserve">Certidão de Débitos Estaduais (ICMS) </t>
         </is>
       </c>
       <c r="F680" s="1" t="n">
@@ -52053,7 +52051,7 @@
         </is>
       </c>
       <c r="J680" s="2" t="n">
-        <v>46232.47807924769</v>
+        <v>46232.47750069445</v>
       </c>
       <c r="K680" s="2" t="n">
         <v>46234</v>
@@ -52071,7 +52069,7 @@
       <c r="N680" s="1" t="n"/>
       <c r="O680" s="1" t="n"/>
       <c r="P680" s="2" t="n">
-        <v>46233.74022094908</v>
+        <v>46233.73991982639</v>
       </c>
       <c r="Q680" s="1" t="inlineStr">
         <is>
@@ -52093,7 +52091,7 @@
     </row>
     <row r="681">
       <c r="A681" s="1" t="n">
-        <v>81562</v>
+        <v>81561</v>
       </c>
       <c r="B681" s="1" t="inlineStr">
         <is>
@@ -52112,7 +52110,7 @@
       </c>
       <c r="E681" s="1" t="inlineStr">
         <is>
-          <t>Certidão Negativa de Débitos Federais (CND), abrangendo a Receita Federal e a Dívida Ativa da União.</t>
+          <t>Certidão de Débitos Municipais (ISS)</t>
         </is>
       </c>
       <c r="F681" s="1" t="n">
@@ -52134,7 +52132,7 @@
         </is>
       </c>
       <c r="J681" s="2" t="n">
-        <v>46232.47872149305</v>
+        <v>46232.47807924769</v>
       </c>
       <c r="K681" s="2" t="n">
         <v>46234</v>
@@ -52152,7 +52150,7 @@
       <c r="N681" s="1" t="n"/>
       <c r="O681" s="1" t="n"/>
       <c r="P681" s="2" t="n">
-        <v>46233.74015570602</v>
+        <v>46233.74022094908</v>
       </c>
       <c r="Q681" s="1" t="inlineStr">
         <is>
@@ -52174,16 +52172,16 @@
     </row>
     <row r="682">
       <c r="A682" s="1" t="n">
-        <v>84014</v>
+        <v>81562</v>
       </c>
       <c r="B682" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C682" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="D682" s="1" t="inlineStr">
@@ -52193,20 +52191,20 @@
       </c>
       <c r="E682" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Certidão Negativa de Débitos Federais (CND), abrangendo a Receita Federal e a Dívida Ativa da União.</t>
         </is>
       </c>
       <c r="F682" s="1" t="n">
-        <v>4178</v>
+        <v>4091</v>
       </c>
       <c r="G682" s="1" t="inlineStr">
         <is>
-          <t>SERFARMA DROGARIA LTDA</t>
+          <t>NOBRES DOCES DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="H682" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I682" s="1" t="inlineStr">
@@ -52215,10 +52213,10 @@
         </is>
       </c>
       <c r="J682" s="2" t="n">
-        <v>46280.47752337963</v>
+        <v>46232.47872149305</v>
       </c>
       <c r="K682" s="2" t="n">
-        <v>46281</v>
+        <v>46234</v>
       </c>
       <c r="L682" s="1" t="inlineStr">
         <is>
@@ -52227,22 +52225,22 @@
       </c>
       <c r="M682" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N682" s="1" t="n"/>
       <c r="O682" s="1" t="n"/>
       <c r="P682" s="2" t="n">
-        <v>46281.42727723379</v>
+        <v>46233.74015570602</v>
       </c>
       <c r="Q682" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="R682" s="1" t="inlineStr">
         <is>
-          <t>Yasmin, segue levantamento de débitos na Prefeitura de Itapecerica da Serfarma, consta um ISS de 2023, segue guia atualizada com vencimento para hoje, 16/09/2026.</t>
+          <t>Conforme e-mail do GM Fernando Sensulini, solicitação deve ser desconsiderada.</t>
         </is>
       </c>
       <c r="S682" s="1" t="inlineStr">
@@ -52255,39 +52253,39 @@
     </row>
     <row r="683">
       <c r="A683" s="1" t="n">
-        <v>81601</v>
+        <v>84014</v>
       </c>
       <c r="B683" s="1" t="inlineStr">
         <is>
-          <t>Processo de VISA</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C683" s="1" t="inlineStr">
         <is>
-          <t>Renovação</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D683" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E683" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa BEST SALAD conforme solicitação do cliente.Grato,Bruno.</t>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
         </is>
       </c>
       <c r="F683" s="1" t="n">
-        <v>4194</v>
+        <v>4178</v>
       </c>
       <c r="G683" s="1" t="inlineStr">
         <is>
-          <t>BEST SALAD HORTI FRUTI LTDA</t>
+          <t>SERFARMA DROGARIA LTDA</t>
         </is>
       </c>
       <c r="H683" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I683" s="1" t="inlineStr">
@@ -52296,10 +52294,10 @@
         </is>
       </c>
       <c r="J683" s="2" t="n">
-        <v>46233.40595859953</v>
+        <v>46280.47752337963</v>
       </c>
       <c r="K683" s="2" t="n">
-        <v>46237</v>
+        <v>46281</v>
       </c>
       <c r="L683" s="1" t="inlineStr">
         <is>
@@ -52308,264 +52306,278 @@
       </c>
       <c r="M683" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N683" s="2" t="n">
-        <v>46234.48805347223</v>
-      </c>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N683" s="1" t="n"/>
       <c r="O683" s="1" t="n"/>
       <c r="P683" s="2" t="n">
+        <v>46281.42727723379</v>
+      </c>
+      <c r="Q683" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R683" s="1" t="inlineStr">
+        <is>
+          <t>Yasmin, segue levantamento de débitos na Prefeitura de Itapecerica da Serfarma, consta um ISS de 2023, segue guia atualizada com vencimento para hoje, 16/09/2026.</t>
+        </is>
+      </c>
+      <c r="S683" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T683" s="1" t="n"/>
+      <c r="U683" s="1" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>81601</v>
+      </c>
+      <c r="B684" s="1" t="inlineStr">
+        <is>
+          <t>Processo de VISA</t>
+        </is>
+      </c>
+      <c r="C684" s="1" t="inlineStr">
+        <is>
+          <t>Renovação</t>
+        </is>
+      </c>
+      <c r="D684" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E684" s="1" t="inlineStr">
+        <is>
+          <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa BEST SALAD conforme solicitação do cliente.Grato,Bruno.</t>
+        </is>
+      </c>
+      <c r="F684" s="1" t="n">
+        <v>4194</v>
+      </c>
+      <c r="G684" s="1" t="inlineStr">
+        <is>
+          <t>BEST SALAD HORTI FRUTI LTDA</t>
+        </is>
+      </c>
+      <c r="H684" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
+      <c r="I684" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J684" s="2" t="n">
+        <v>46233.40595859953</v>
+      </c>
+      <c r="K684" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="L684" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M684" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N684" s="2" t="n">
+        <v>46234.48805347223</v>
+      </c>
+      <c r="O684" s="1" t="n"/>
+      <c r="P684" s="2" t="n">
         <v>46237.37169996528</v>
       </c>
-      <c r="Q683" s="1" t="inlineStr">
+      <c r="Q684" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R683" s="1" t="inlineStr">
+      <c r="R684" s="1" t="inlineStr">
         <is>
           <t>O sistema do VRE está com problemas, assim que disponível, concluímos o CLI.
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S683" s="1" t="inlineStr">
+      <c r="S684" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T683" s="1" t="n"/>
-      <c r="U683" s="1" t="inlineStr"/>
-    </row>
-    <row r="684">
-      <c r="A684" s="1" t="n">
+      <c r="T684" s="1" t="n"/>
+      <c r="U684" s="1" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
         <v>81603</v>
       </c>
-      <c r="B684" s="1" t="inlineStr">
+      <c r="B685" s="1" t="inlineStr">
         <is>
           <t>Processo de VISA</t>
         </is>
       </c>
-      <c r="C684" s="1" t="inlineStr">
+      <c r="C685" s="1" t="inlineStr">
         <is>
           <t>Renovação</t>
         </is>
       </c>
-      <c r="D684" s="1" t="inlineStr">
+      <c r="D685" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
-      <c r="E684" s="1" t="inlineStr">
+      <c r="E685" s="1" t="inlineStr">
         <is>
           <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa Terra Brasil conforme solicitação do cliente.Grato,Bruno.</t>
         </is>
       </c>
-      <c r="F684" s="1" t="n">
+      <c r="F685" s="1" t="n">
         <v>4195</v>
       </c>
-      <c r="G684" s="1" t="inlineStr">
+      <c r="G685" s="1" t="inlineStr">
         <is>
           <t>TERRA BRASIL HORTI FRUTI LTDA</t>
         </is>
       </c>
-      <c r="H684" s="1" t="inlineStr">
+      <c r="H685" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="I684" s="1" t="inlineStr">
+      <c r="I685" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J684" s="2" t="n">
+      <c r="J685" s="2" t="n">
         <v>46233.40691574074</v>
       </c>
-      <c r="K684" s="2" t="n">
+      <c r="K685" s="2" t="n">
         <v>46237</v>
       </c>
-      <c r="L684" s="1" t="inlineStr">
+      <c r="L685" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M684" s="1" t="inlineStr">
+      <c r="M685" s="1" t="inlineStr">
         <is>
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N684" s="2" t="n">
+      <c r="N685" s="2" t="n">
         <v>46234.48788619213</v>
       </c>
-      <c r="O684" s="1" t="n"/>
-      <c r="P684" s="2" t="n">
+      <c r="O685" s="1" t="n"/>
+      <c r="P685" s="2" t="n">
         <v>46240.39679517361</v>
       </c>
-      <c r="Q684" s="1" t="inlineStr">
+      <c r="Q685" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R684" s="1" t="inlineStr">
+      <c r="R685" s="1" t="inlineStr">
         <is>
           <t>O sistema do VRE está com problemas, assim que disponível, concluímos o CLI.
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S684" s="1" t="inlineStr">
+      <c r="S685" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T684" s="1" t="n"/>
-      <c r="U684" s="1" t="inlineStr"/>
-    </row>
-    <row r="685">
-      <c r="A685" s="1" t="n">
+      <c r="T685" s="1" t="n"/>
+      <c r="U685" s="1" t="inlineStr"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n">
         <v>83684</v>
       </c>
-      <c r="B685" s="1" t="inlineStr">
+      <c r="B686" s="1" t="inlineStr">
         <is>
           <t>Processo de VISA</t>
         </is>
       </c>
-      <c r="C685" s="1" t="inlineStr">
+      <c r="C686" s="1" t="inlineStr">
         <is>
           <t>Renovação</t>
         </is>
       </c>
-      <c r="D685" s="1" t="inlineStr">
+      <c r="D686" s="1" t="inlineStr">
         <is>
           <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="E685" s="1" t="inlineStr">
+      <c r="E686" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Por gentileza, providenciar renovação de alvará de funcionamento. </t>
         </is>
       </c>
-      <c r="F685" s="1" t="n">
+      <c r="F686" s="1" t="n">
         <v>4195</v>
       </c>
-      <c r="G685" s="1" t="inlineStr">
+      <c r="G686" s="1" t="inlineStr">
         <is>
           <t>TERRA BRASIL HORTI FRUTI LTDA</t>
         </is>
       </c>
-      <c r="H685" s="1" t="inlineStr">
+      <c r="H686" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="I685" s="1" t="inlineStr">
+      <c r="I686" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J685" s="2" t="n">
+      <c r="J686" s="2" t="n">
         <v>46273.73010833334</v>
       </c>
-      <c r="K685" s="2" t="n">
+      <c r="K686" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="L685" s="1" t="inlineStr">
+      <c r="L686" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M685" s="1" t="inlineStr">
+      <c r="M686" s="1" t="inlineStr">
         <is>
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N685" s="1" t="n"/>
-      <c r="O685" s="1" t="n"/>
-      <c r="P685" s="2" t="n">
+      <c r="N686" s="1" t="n"/>
+      <c r="O686" s="1" t="n"/>
+      <c r="P686" s="2" t="n">
         <v>46274.48608564815</v>
       </c>
-      <c r="Q685" s="1" t="inlineStr">
+      <c r="Q686" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R685" s="1" t="inlineStr">
+      <c r="R686" s="1" t="inlineStr">
         <is>
           <t>Bom dia.
 Email respondido hoje para a Patricia com Gerente Bruno em cópia.
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S685" s="1" t="inlineStr">
+      <c r="S686" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
-        </is>
-      </c>
-      <c r="T685" s="1" t="n"/>
-      <c r="U685" s="1" t="inlineStr"/>
-    </row>
-    <row r="686">
-      <c r="A686" s="1" t="n">
-        <v>83924</v>
-      </c>
-      <c r="B686" s="1" t="inlineStr">
-        <is>
-          <t>Regularização</t>
-        </is>
-      </c>
-      <c r="C686" s="1" t="inlineStr">
-        <is>
-          <t>Prefeitura</t>
-        </is>
-      </c>
-      <c r="D686" s="1" t="inlineStr">
-        <is>
-          <t>SANTOS - GC</t>
-        </is>
-      </c>
-      <c r="E686" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3828 - Supermercado Popular - Renovação do Cli </t>
-        </is>
-      </c>
-      <c r="F686" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G686" s="1" t="n"/>
-      <c r="H686" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
-      <c r="I686" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J686" s="2" t="n">
-        <v>46279.40335633101</v>
-      </c>
-      <c r="K686" s="2" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L686" s="1" t="inlineStr">
-        <is>
-          <t>Esperando Atendimento</t>
-        </is>
-      </c>
-      <c r="M686" s="1" t="inlineStr">
-        <is>
-          <t>Rafaella Massuia</t>
-        </is>
-      </c>
-      <c r="N686" s="1" t="n"/>
-      <c r="O686" s="1" t="n"/>
-      <c r="P686" s="1" t="n"/>
-      <c r="Q686" s="1" t="inlineStr"/>
-      <c r="R686" s="1" t="inlineStr"/>
-      <c r="S686" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
         </is>
       </c>
       <c r="T686" s="1" t="n"/>
@@ -52573,59 +52585,71 @@
     </row>
     <row r="687">
       <c r="A687" s="1" t="n">
-        <v>84061</v>
+        <v>83924</v>
       </c>
       <c r="B687" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C687" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D687" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>SANTOS - GC</t>
         </is>
       </c>
       <c r="E687" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, encaminhar o levamento de débitos e CND's (inclusive trabalhista) de todas as empresas do grupo Medical Discovery.</t>
+          <t xml:space="preserve">3828 - Supermercado Popular - Renovação do Cli </t>
         </is>
       </c>
       <c r="F687" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G687" s="1" t="n"/>
-      <c r="H687" s="1" t="n"/>
+      <c r="H687" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
       <c r="I687" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J687" s="2" t="n">
-        <v>46281.41060396991</v>
+        <v>46279.40335633101</v>
       </c>
       <c r="K687" s="2" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="L687" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M687" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
-      <c r="N687" s="1" t="n"/>
+          <t>Rafaella Massuia</t>
+        </is>
+      </c>
+      <c r="N687" s="2" t="n">
+        <v>46281.55550413195</v>
+      </c>
       <c r="O687" s="1" t="n"/>
       <c r="P687" s="1" t="n"/>
       <c r="Q687" s="1" t="inlineStr"/>
-      <c r="R687" s="1" t="n"/>
+      <c r="R687" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde.
+Aguardando o deferimento.
+Atenciosamente,</t>
+        </is>
+      </c>
       <c r="S687" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -52636,69 +52660,59 @@
     </row>
     <row r="688">
       <c r="A688" s="1" t="n">
-        <v>81296</v>
+        <v>84061</v>
       </c>
       <c r="B688" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C688" s="1" t="inlineStr">
         <is>
-          <t>Outras Cláusulas</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D688" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E688" s="1" t="inlineStr">
         <is>
-          <t>Providenciar a inclusão do CNAE descrito abaixo na empresa.8630-5/03 - ATIVIDADE MÉDICA AMBULATORIAL RESTRITA A CONSULTAS.Ela irá prestar serviços médicos como Pessoa Jurídica, para Hospitais, UBS, Clínicas e Eventos, conforme encaminhamento da resposta dela, pelo WhatsApp.Valor será o mesmo da última alteração do grupo.</t>
+          <t>Bom dia! Por gentileza, encaminhar o levamento de débitos e CND's (inclusive trabalhista) de todas as empresas do grupo Medical Discovery.</t>
         </is>
       </c>
       <c r="F688" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G688" s="1" t="n"/>
-      <c r="H688" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
+      <c r="H688" s="1" t="n"/>
       <c r="I688" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J688" s="2" t="n">
-        <v>46225.4866127662</v>
+        <v>46281.41060396991</v>
       </c>
       <c r="K688" s="2" t="n">
-        <v>46255</v>
+        <v>46282</v>
       </c>
       <c r="L688" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M688" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N688" s="2" t="n">
-        <v>46253.38738584491</v>
-      </c>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N688" s="1" t="n"/>
       <c r="O688" s="1" t="n"/>
       <c r="P688" s="1" t="n"/>
       <c r="Q688" s="1" t="inlineStr"/>
-      <c r="R688" s="1" t="inlineStr">
-        <is>
-          <t>Raisa, para esse processo, será necessário o envio do IPTU e também que seja informado quem será o responsável tecnico perante o CREMESP, enviando-nos inclusive a carteira do CREMESP do responsável.</t>
-        </is>
-      </c>
+      <c r="R688" s="1" t="n"/>
       <c r="S688" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -52709,59 +52723,69 @@
     </row>
     <row r="689">
       <c r="A689" s="1" t="n">
-        <v>83981</v>
+        <v>81296</v>
       </c>
       <c r="B689" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C689" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Outras Cláusulas</t>
         </is>
       </c>
       <c r="D689" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E689" s="1" t="inlineStr">
         <is>
-          <t>3262 - JCV - GNRE de ALPEC - AlagoasConforme solicitação no e-mail anexo, é necessário providenciar o preenchimento do REDAR, emissão da taxa e protocolar do processo junto à SEFAZ/AL.</t>
+          <t>Providenciar a inclusão do CNAE descrito abaixo na empresa.8630-5/03 - ATIVIDADE MÉDICA AMBULATORIAL RESTRITA A CONSULTAS.Ela irá prestar serviços médicos como Pessoa Jurídica, para Hospitais, UBS, Clínicas e Eventos, conforme encaminhamento da resposta dela, pelo WhatsApp.Valor será o mesmo da última alteração do grupo.</t>
         </is>
       </c>
       <c r="F689" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G689" s="1" t="n"/>
-      <c r="H689" s="1" t="n"/>
+      <c r="H689" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
       <c r="I689" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J689" s="2" t="n">
-        <v>46280.38897322916</v>
+        <v>46225.4866127662</v>
       </c>
       <c r="K689" s="2" t="n">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L689" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M689" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
-      <c r="N689" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N689" s="2" t="n">
+        <v>46253.38738584491</v>
+      </c>
       <c r="O689" s="1" t="n"/>
       <c r="P689" s="1" t="n"/>
       <c r="Q689" s="1" t="inlineStr"/>
-      <c r="R689" s="1" t="n"/>
+      <c r="R689" s="1" t="inlineStr">
+        <is>
+          <t>Raisa, para esse processo, será necessário o envio do IPTU e também que seja informado quem será o responsável tecnico perante o CREMESP, enviando-nos inclusive a carteira do CREMESP do responsável.</t>
+        </is>
+      </c>
       <c r="S689" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -52772,7 +52796,7 @@
     </row>
     <row r="690">
       <c r="A690" s="1" t="n">
-        <v>84060</v>
+        <v>83981</v>
       </c>
       <c r="B690" s="1" t="inlineStr">
         <is>
@@ -52791,7 +52815,7 @@
       </c>
       <c r="E690" s="1" t="inlineStr">
         <is>
-          <t>5132 - CABEXPRESS - Notificação GNRE UF MT.Nosso cliente recebeu uma notificação da SEFAZ de MT sobre o não pagamento da GNRE de uma venda referente à NF-e 45.008 que já havia sido recolhido em 04/09/2026, 10 dias antes da emissão do TAD em 14/09/2026.O valor principal cobrado no TAD é exatamente o mesmo valor que consta na GNRE paga R$ 1.204,18. Porém, o TAD indica que a fiscalização não reconheceu/localizou esse recolhimento no momento da abordagem, e por isso constituiu o débito e acrescentou multa.O documento informa a possibilidade de provar a regularidade, mas não apresenta de forma clara, um canal eletrônico específico, e-mail ou botão/link para enviar os comprovantes.Segue anexo o e-mail do cliente com a GNRE e o comprovante bancário para que vejam a possibilidade de solicitar a baixa/cancelamento da exigência TAD.</t>
+          <t>3262 - JCV - GNRE de ALPEC - AlagoasConforme solicitação no e-mail anexo, é necessário providenciar o preenchimento do REDAR, emissão da taxa e protocolar do processo junto à SEFAZ/AL.</t>
         </is>
       </c>
       <c r="F690" s="1" t="n">
@@ -52805,10 +52829,10 @@
         </is>
       </c>
       <c r="J690" s="2" t="n">
-        <v>46281.40508255787</v>
+        <v>46280.38897322916</v>
       </c>
       <c r="K690" s="2" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="L690" s="1" t="inlineStr">
         <is>
@@ -52835,73 +52859,59 @@
     </row>
     <row r="691">
       <c r="A691" s="1" t="n">
-        <v>84003</v>
+        <v>84060</v>
       </c>
       <c r="B691" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C691" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D691" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E691" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>5132 - CABEXPRESS - Notificação GNRE UF MT.Nosso cliente recebeu uma notificação da SEFAZ de MT sobre o não pagamento da GNRE de uma venda referente à NF-e 45.008 que já havia sido recolhido em 04/09/2026, 10 dias antes da emissão do TAD em 14/09/2026.O valor principal cobrado no TAD é exatamente o mesmo valor que consta na GNRE paga R$ 1.204,18. Porém, o TAD indica que a fiscalização não reconheceu/localizou esse recolhimento no momento da abordagem, e por isso constituiu o débito e acrescentou multa.O documento informa a possibilidade de provar a regularidade, mas não apresenta de forma clara, um canal eletrônico específico, e-mail ou botão/link para enviar os comprovantes.Segue anexo o e-mail do cliente com a GNRE e o comprovante bancário para que vejam a possibilidade de solicitar a baixa/cancelamento da exigência TAD.</t>
         </is>
       </c>
       <c r="F691" s="1" t="n">
-        <v>861</v>
-      </c>
-      <c r="G691" s="1" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO CASTELO DA SERRA LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H691" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G691" s="1" t="n"/>
+      <c r="H691" s="1" t="n"/>
       <c r="I691" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J691" s="2" t="n">
-        <v>46280.47044158565</v>
+        <v>46281.40508255787</v>
       </c>
       <c r="K691" s="2" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="L691" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M691" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N691" s="2" t="n">
-        <v>46280.72077896991</v>
-      </c>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
+      <c r="N691" s="1" t="n"/>
       <c r="O691" s="1" t="n"/>
       <c r="P691" s="1" t="n"/>
       <c r="Q691" s="1" t="inlineStr"/>
-      <c r="R691" s="1" t="inlineStr">
-        <is>
-          <t>Certidão emitida somente presencialmente, estou verificando.</t>
-        </is>
-      </c>
+      <c r="R691" s="1" t="n"/>
       <c r="S691" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -52912,16 +52922,16 @@
     </row>
     <row r="692">
       <c r="A692" s="1" t="n">
-        <v>83516</v>
+        <v>84003</v>
       </c>
       <c r="B692" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C692" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D692" s="1" t="inlineStr">
@@ -52931,20 +52941,20 @@
       </c>
       <c r="E692" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, solicito a alteração do endereço cadastrado para o novo endereço informado. </t>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
         </is>
       </c>
       <c r="F692" s="1" t="n">
-        <v>1147</v>
+        <v>861</v>
       </c>
       <c r="G692" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO CATROQUE LTDA</t>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H692" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I692" s="1" t="inlineStr">
@@ -52953,28 +52963,30 @@
         </is>
       </c>
       <c r="J692" s="2" t="n">
-        <v>46267.68259945602</v>
+        <v>46280.47044158565</v>
       </c>
       <c r="K692" s="2" t="n">
-        <v>46268</v>
+        <v>46281</v>
       </c>
       <c r="L692" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M692" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
-        </is>
-      </c>
-      <c r="N692" s="1" t="n"/>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N692" s="2" t="n">
+        <v>46280.72077896991</v>
+      </c>
       <c r="O692" s="1" t="n"/>
       <c r="P692" s="1" t="n"/>
       <c r="Q692" s="1" t="inlineStr"/>
       <c r="R692" s="1" t="inlineStr">
         <is>
-          <t>Endereço é o memo que consta em todos os cadastros da empresa, o que é para alterar de fato?</t>
+          <t>Certidão emitida somente presencialmente, estou verificando.</t>
         </is>
       </c>
       <c r="S692" s="1" t="inlineStr">
@@ -52987,7 +52999,7 @@
     </row>
     <row r="693">
       <c r="A693" s="1" t="n">
-        <v>82960</v>
+        <v>83516</v>
       </c>
       <c r="B693" s="1" t="inlineStr">
         <is>
@@ -52996,7 +53008,7 @@
       </c>
       <c r="C693" s="1" t="inlineStr">
         <is>
-          <t>Objeto Social</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D693" s="1" t="inlineStr">
@@ -53006,15 +53018,15 @@
       </c>
       <c r="E693" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia! Por gentileza, encaminhar uma proposta para inclusão do código em anexo. </t>
+          <t xml:space="preserve">Por gentileza, solicito a alteração do endereço cadastrado para o novo endereço informado. </t>
         </is>
       </c>
       <c r="F693" s="1" t="n">
-        <v>1286</v>
+        <v>1147</v>
       </c>
       <c r="G693" s="1" t="inlineStr">
         <is>
-          <t>BY ENGENHARIA IMPORTAÇÃO E EXPORTAÇÃO LTDA (MATRIZ)</t>
+          <t>SUPERMERCADO CATROQUE LTDA</t>
         </is>
       </c>
       <c r="H693" s="1" t="inlineStr">
@@ -53028,39 +53040,33 @@
         </is>
       </c>
       <c r="J693" s="2" t="n">
-        <v>46259.47975929398</v>
+        <v>46267.68259945602</v>
       </c>
       <c r="K693" s="2" t="n">
-        <v>46260</v>
+        <v>46268</v>
       </c>
       <c r="L693" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M693" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="N693" s="1" t="n"/>
       <c r="O693" s="1" t="n"/>
-      <c r="P693" s="2" t="n">
-        <v>46268.73202989584</v>
-      </c>
-      <c r="Q693" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="P693" s="1" t="n"/>
+      <c r="Q693" s="1" t="inlineStr"/>
       <c r="R693" s="1" t="inlineStr">
         <is>
-          <t>Anexo a proposta.</t>
+          <t>Endereço é o memo que consta em todos os cadastros da empresa, o que é para alterar de fato?</t>
         </is>
       </c>
       <c r="S693" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T693" s="1" t="n"/>
@@ -53068,39 +53074,39 @@
     </row>
     <row r="694">
       <c r="A694" s="1" t="n">
-        <v>82182</v>
+        <v>82960</v>
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C694" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Comércio</t>
+          <t>Objeto Social</t>
         </is>
       </c>
       <c r="D694" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E694" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE FILIAL DA EMPRESA 1603-MERCADINHO KI PREÇO BAIXO LTDAGRUPO: KI-PREÇO BAIXOPROPOSTA JÁ NEGOCIADA NO VALOR DE R$1.800,00FILIAL SERÁ ESPELHO DA EMPRESA 1603-MERCADINHO KI PREÇO BAIXO LTDA</t>
+          <t xml:space="preserve">Bom dia! Por gentileza, encaminhar uma proposta para inclusão do código em anexo. </t>
         </is>
       </c>
       <c r="F694" s="1" t="n">
-        <v>1603</v>
+        <v>1286</v>
       </c>
       <c r="G694" s="1" t="inlineStr">
         <is>
-          <t>MERCADINHO KI PREÇO BAIXO LTDA</t>
+          <t>BY ENGENHARIA IMPORTAÇÃO E EXPORTAÇÃO LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H694" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I694" s="1" t="inlineStr">
@@ -53109,35 +53115,39 @@
         </is>
       </c>
       <c r="J694" s="2" t="n">
-        <v>46244.71370034722</v>
+        <v>46259.47975929398</v>
       </c>
       <c r="K694" s="2" t="n">
-        <v>46272</v>
+        <v>46260</v>
       </c>
       <c r="L694" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M694" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N694" s="2" t="n">
-        <v>46251.42906362269</v>
-      </c>
+          <t>Simone Marques</t>
+        </is>
+      </c>
+      <c r="N694" s="1" t="n"/>
       <c r="O694" s="1" t="n"/>
-      <c r="P694" s="1" t="n"/>
-      <c r="Q694" s="1" t="inlineStr"/>
+      <c r="P694" s="2" t="n">
+        <v>46268.73202989584</v>
+      </c>
+      <c r="Q694" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="R694" s="1" t="inlineStr">
         <is>
-          <t>Minuta em análise com cliente (Charles).</t>
+          <t>Anexo a proposta.</t>
         </is>
       </c>
       <c r="S694" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T694" s="1" t="n"/>
@@ -53145,39 +53155,39 @@
     </row>
     <row r="695">
       <c r="A695" s="1" t="n">
-        <v>83485</v>
+        <v>82182</v>
       </c>
       <c r="B695" s="1" t="inlineStr">
         <is>
-          <t>Parcelamento RFB</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C695" s="1" t="inlineStr">
         <is>
-          <t>Simplificado</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D695" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E695" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tarde, por gentileza verificar mensagem recebida pelo cliente referente a débitos em aberto e nos encaminhar a simulação de parcelamento. </t>
+          <t>ABERTURA DE FILIAL DA EMPRESA 1603-MERCADINHO KI PREÇO BAIXO LTDAGRUPO: KI-PREÇO BAIXOPROPOSTA JÁ NEGOCIADA NO VALOR DE R$1.800,00FILIAL SERÁ ESPELHO DA EMPRESA 1603-MERCADINHO KI PREÇO BAIXO LTDA</t>
         </is>
       </c>
       <c r="F695" s="1" t="n">
-        <v>1653</v>
+        <v>1603</v>
       </c>
       <c r="G695" s="1" t="inlineStr">
         <is>
-          <t>SANTANA COMÉRCIO DE PEÇAS LTDA</t>
+          <t>MERCADINHO KI PREÇO BAIXO LTDA</t>
         </is>
       </c>
       <c r="H695" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I695" s="1" t="inlineStr">
@@ -53186,39 +53196,35 @@
         </is>
       </c>
       <c r="J695" s="2" t="n">
-        <v>46267.58544814815</v>
+        <v>46244.71370034722</v>
       </c>
       <c r="K695" s="2" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="L695" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M695" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
-      <c r="N695" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N695" s="2" t="n">
+        <v>46251.42906362269</v>
+      </c>
       <c r="O695" s="1" t="n"/>
-      <c r="P695" s="2" t="n">
-        <v>46268.70828846065</v>
-      </c>
-      <c r="Q695" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="P695" s="1" t="n"/>
+      <c r="Q695" s="1" t="inlineStr"/>
       <c r="R695" s="1" t="inlineStr">
         <is>
-          <t>Atendimento feito diretamente ao cliente Sr. Carlos Santana, que entrou em contato direto com o nosso departamento.</t>
+          <t>Minuta em análise com cliente (Charles).</t>
         </is>
       </c>
       <c r="S695" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T695" s="1" t="n"/>
@@ -53226,16 +53232,16 @@
     </row>
     <row r="696">
       <c r="A696" s="1" t="n">
-        <v>81794</v>
+        <v>83485</v>
       </c>
       <c r="B696" s="1" t="inlineStr">
         <is>
-          <t>Processo de VISA</t>
+          <t>Parcelamento RFB</t>
         </is>
       </c>
       <c r="C696" s="1" t="inlineStr">
         <is>
-          <t>Renovação</t>
+          <t>Simplificado</t>
         </is>
       </c>
       <c r="D696" s="1" t="inlineStr">
@@ -53245,20 +53251,20 @@
       </c>
       <c r="E696" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Bom dia!Conforme solicitação do cliente, por gentileza, providenciar renovação CLI de todas as empresas do grupo Carvalho (exceto empresa 3195, já regularizada).Grato,Bruno.</t>
+          <t xml:space="preserve">Boa tarde, por gentileza verificar mensagem recebida pelo cliente referente a débitos em aberto e nos encaminhar a simulação de parcelamento. </t>
         </is>
       </c>
       <c r="F696" s="1" t="n">
-        <v>1688</v>
+        <v>1653</v>
       </c>
       <c r="G696" s="1" t="inlineStr">
         <is>
-          <t>MERCADO ROQUE TADEU CARVALHO LTDA</t>
+          <t>SANTANA COMÉRCIO DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="H696" s="1" t="inlineStr">
         <is>
-          <t>Talita Silva</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I696" s="1" t="inlineStr">
@@ -53267,10 +53273,10 @@
         </is>
       </c>
       <c r="J696" s="2" t="n">
-        <v>46237.71846929398</v>
+        <v>46267.58544814815</v>
       </c>
       <c r="K696" s="2" t="n">
-        <v>46248</v>
+        <v>46269</v>
       </c>
       <c r="L696" s="1" t="inlineStr">
         <is>
@@ -53279,22 +53285,103 @@
       </c>
       <c r="M696" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N696" s="2" t="n">
-        <v>46240.68919447916</v>
-      </c>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N696" s="1" t="n"/>
       <c r="O696" s="1" t="n"/>
       <c r="P696" s="2" t="n">
+        <v>46268.70828846065</v>
+      </c>
+      <c r="Q696" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
+      <c r="R696" s="1" t="inlineStr">
+        <is>
+          <t>Atendimento feito diretamente ao cliente Sr. Carlos Santana, que entrou em contato direto com o nosso departamento.</t>
+        </is>
+      </c>
+      <c r="S696" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T696" s="1" t="n"/>
+      <c r="U696" s="1" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="n">
+        <v>81794</v>
+      </c>
+      <c r="B697" s="1" t="inlineStr">
+        <is>
+          <t>Processo de VISA</t>
+        </is>
+      </c>
+      <c r="C697" s="1" t="inlineStr">
+        <is>
+          <t>Renovação</t>
+        </is>
+      </c>
+      <c r="D697" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E697" s="1" t="inlineStr">
+        <is>
+          <t>Prezados,Bom dia!Conforme solicitação do cliente, por gentileza, providenciar renovação CLI de todas as empresas do grupo Carvalho (exceto empresa 3195, já regularizada).Grato,Bruno.</t>
+        </is>
+      </c>
+      <c r="F697" s="1" t="n">
+        <v>1688</v>
+      </c>
+      <c r="G697" s="1" t="inlineStr">
+        <is>
+          <t>MERCADO ROQUE TADEU CARVALHO LTDA</t>
+        </is>
+      </c>
+      <c r="H697" s="1" t="inlineStr">
+        <is>
+          <t>Talita Silva</t>
+        </is>
+      </c>
+      <c r="I697" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J697" s="2" t="n">
+        <v>46237.71846929398</v>
+      </c>
+      <c r="K697" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="L697" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M697" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N697" s="2" t="n">
+        <v>46240.68919447916</v>
+      </c>
+      <c r="O697" s="1" t="n"/>
+      <c r="P697" s="2" t="n">
         <v>46244.6818821412</v>
       </c>
-      <c r="Q696" s="1" t="inlineStr">
+      <c r="Q697" s="1" t="inlineStr">
         <is>
           <t>Talita Silva</t>
         </is>
       </c>
-      <c r="R696" s="1" t="inlineStr">
+      <c r="R697" s="1" t="inlineStr">
         <is>
           <t>Boa tarde!
 Segue em anexo o CLI Parcial.
@@ -53302,165 +53389,94 @@
 Qualquer duvida estamos a disposição</t>
         </is>
       </c>
-      <c r="S696" s="1" t="inlineStr">
+      <c r="S697" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T696" s="1" t="n"/>
-      <c r="U696" s="1" t="inlineStr"/>
-    </row>
-    <row r="697">
-      <c r="A697" s="1" t="n">
+      <c r="T697" s="1" t="n"/>
+      <c r="U697" s="1" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="n">
         <v>81795</v>
       </c>
-      <c r="B697" s="1" t="inlineStr">
+      <c r="B698" s="1" t="inlineStr">
         <is>
           <t>Processo de VISA</t>
         </is>
       </c>
-      <c r="C697" s="1" t="inlineStr">
+      <c r="C698" s="1" t="inlineStr">
         <is>
           <t>Renovação</t>
         </is>
       </c>
-      <c r="D697" s="1" t="inlineStr">
+      <c r="D698" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
-      <c r="E697" s="1" t="inlineStr">
+      <c r="E698" s="1" t="inlineStr">
         <is>
           <t>Prezados,Bom dia!Conforme solicitação do cliente, por gentileza, providenciar renovação CLI de todas as empresas do grupo Carvalho (exceto empresa 3195, já regularizada).Grato,Bruno.</t>
         </is>
       </c>
-      <c r="F697" s="1" t="n">
+      <c r="F698" s="1" t="n">
         <v>1689</v>
       </c>
-      <c r="G697" s="1" t="inlineStr">
+      <c r="G698" s="1" t="inlineStr">
         <is>
           <t>MERCADO EXPEDITA ISIDORO LTDA</t>
         </is>
       </c>
-      <c r="H697" s="1" t="inlineStr">
+      <c r="H698" s="1" t="inlineStr">
         <is>
           <t>Talita Silva</t>
         </is>
       </c>
-      <c r="I697" s="1" t="inlineStr">
+      <c r="I698" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J697" s="2" t="n">
+      <c r="J698" s="2" t="n">
         <v>46237.71903387731</v>
       </c>
-      <c r="K697" s="2" t="n">
+      <c r="K698" s="2" t="n">
         <v>46248</v>
       </c>
-      <c r="L697" s="1" t="inlineStr">
+      <c r="L698" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M697" s="1" t="inlineStr">
+      <c r="M698" s="1" t="inlineStr">
         <is>
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N697" s="2" t="n">
+      <c r="N698" s="2" t="n">
         <v>46241.5472042824</v>
       </c>
-      <c r="O697" s="1" t="n"/>
-      <c r="P697" s="2" t="n">
+      <c r="O698" s="1" t="n"/>
+      <c r="P698" s="2" t="n">
         <v>46244.6815815625</v>
       </c>
-      <c r="Q697" s="1" t="inlineStr">
+      <c r="Q698" s="1" t="inlineStr">
         <is>
           <t>Talita Silva</t>
         </is>
       </c>
-      <c r="R697" s="1" t="inlineStr">
+      <c r="R698" s="1" t="inlineStr">
         <is>
           <t>Bom dia!
 Preciso do AVCB/CLCB para dar andamento no CLI
 Aguardo retorno.</t>
         </is>
       </c>
-      <c r="S697" s="1" t="inlineStr">
+      <c r="S698" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
-        </is>
-      </c>
-      <c r="T697" s="1" t="n"/>
-      <c r="U697" s="1" t="inlineStr"/>
-    </row>
-    <row r="698">
-      <c r="A698" s="1" t="n">
-        <v>83929</v>
-      </c>
-      <c r="B698" s="1" t="inlineStr">
-        <is>
-          <t>Abertura de Empresa</t>
-        </is>
-      </c>
-      <c r="C698" s="1" t="inlineStr">
-        <is>
-          <t>Sociedade - Comércio</t>
-        </is>
-      </c>
-      <c r="D698" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E698" s="1" t="inlineStr">
-        <is>
-          <t>Abertura de nova empresa do grupo: 1776-FERROSTributação: Lucro RealTipo de atividade: ComércioFinalidade: Operacional Forma jurídica: LTDAProposta já negociada no valor de R$2.000,00</t>
-        </is>
-      </c>
-      <c r="F698" s="1" t="n">
-        <v>1776</v>
-      </c>
-      <c r="G698" s="1" t="inlineStr">
-        <is>
-          <t>FERROS COMÉRCIO DE DOCES E DERIVADOS LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H698" s="1" t="inlineStr">
-        <is>
-          <t>Thifany Leite</t>
-        </is>
-      </c>
-      <c r="I698" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J698" s="2" t="n">
-        <v>46279.41321524305</v>
-      </c>
-      <c r="K698" s="2" t="n">
-        <v>46307</v>
-      </c>
-      <c r="L698" s="1" t="inlineStr">
-        <is>
-          <t>Esperando Atendimento</t>
-        </is>
-      </c>
-      <c r="M698" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N698" s="1" t="n"/>
-      <c r="O698" s="1" t="n"/>
-      <c r="P698" s="1" t="n"/>
-      <c r="Q698" s="1" t="inlineStr"/>
-      <c r="R698" s="1" t="inlineStr"/>
-      <c r="S698" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
         </is>
       </c>
       <c r="T698" s="1" t="n"/>
@@ -60449,39 +60465,39 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>83902</v>
+        <v>81933</v>
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C789" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D789" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E789" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Por gentileza, providenciar:6990 - RC MATERIAIS ELETRICOS E HIDRAULICOS (MATRIZ) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL6991 - RC MATERIAIS ELETRICOS E HIDRAULICOS (FILIAL 1) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL</t>
         </is>
       </c>
       <c r="F789" s="1" t="n">
-        <v>6989</v>
+        <v>6990</v>
       </c>
       <c r="G789" s="1" t="inlineStr">
         <is>
-          <t>ATRIA CENOGRAFIA LTDA</t>
+          <t>AMANCIO S ELETRICA, HIDRAULICA E CONSTRUCAO EM GERAL LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H789" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I789" s="1" t="inlineStr">
@@ -60490,37 +60506,39 @@
         </is>
       </c>
       <c r="J789" s="2" t="n">
-        <v>46279.39199953704</v>
+        <v>46239.72520292824</v>
       </c>
       <c r="K789" s="2" t="n">
-        <v>46281</v>
+        <v>46241</v>
       </c>
       <c r="L789" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M789" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N789" s="2" t="n">
-        <v>46281.50711435185</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N789" s="1" t="n"/>
       <c r="O789" s="1" t="n"/>
-      <c r="P789" s="1" t="n"/>
-      <c r="Q789" s="1" t="inlineStr"/>
+      <c r="P789" s="2" t="n">
+        <v>46241.65195802083</v>
+      </c>
+      <c r="Q789" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="R789" s="1" t="inlineStr">
         <is>
-          <t>Prezados, bom dia.
-Aguardamos o retorno das informações do cliente.
-Atenciosamente,</t>
+          <t>Abrir um chamado por empresa, por gentileza.</t>
         </is>
       </c>
       <c r="S789" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T789" s="1" t="n"/>
@@ -60528,39 +60546,39 @@
     </row>
     <row r="790">
       <c r="A790" s="1" t="n">
-        <v>81933</v>
+        <v>81780</v>
       </c>
       <c r="B790" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C790" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Objeto Social</t>
         </is>
       </c>
       <c r="D790" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E790" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar:6990 - RC MATERIAIS ELETRICOS E HIDRAULICOS (MATRIZ) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL6991 - RC MATERIAIS ELETRICOS E HIDRAULICOS (FILIAL 1) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL</t>
+          <t>ALTERAÇÃO CONTRATUAL DA EMPRESA: 6993-GOMES SERVIÇOS - LTDAGRUPO: CRISTO REIALTERAÇÃO DE QSA E OBJETO SOCIALPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.500,00MESMA ATIVIDADE E SÓCIOS DO SUP. AVENIDA, APÓS ALTERAÇÃO MIGRAR FUNCIONÁRIOS PARA NOVA EMPRESA ALTERAR QSA E OBJETO SOCIAL.</t>
         </is>
       </c>
       <c r="F790" s="1" t="n">
-        <v>6990</v>
+        <v>6993</v>
       </c>
       <c r="G790" s="1" t="inlineStr">
         <is>
-          <t>AMANCIO S ELETRICA, HIDRAULICA E CONSTRUCAO EM GERAL LTDA (MATRIZ)</t>
+          <t>GOMES SERVIÇOS - LTDA</t>
         </is>
       </c>
       <c r="H790" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I790" s="1" t="inlineStr">
@@ -60569,39 +60587,37 @@
         </is>
       </c>
       <c r="J790" s="2" t="n">
-        <v>46239.72520292824</v>
+        <v>46237.62372283565</v>
       </c>
       <c r="K790" s="2" t="n">
-        <v>46241</v>
+        <v>46265</v>
       </c>
       <c r="L790" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M790" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N790" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N790" s="2" t="n">
+        <v>46246.66900671296</v>
+      </c>
       <c r="O790" s="1" t="n"/>
-      <c r="P790" s="2" t="n">
-        <v>46241.65195802083</v>
-      </c>
-      <c r="Q790" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P790" s="1" t="n"/>
+      <c r="Q790" s="1" t="inlineStr"/>
       <c r="R790" s="1" t="inlineStr">
         <is>
-          <t>Abrir um chamado por empresa, por gentileza.</t>
+          <t xml:space="preserve">Prezados(as), boa tarde!
+Alteração contratual em andamento. 
+Atenciosamente, </t>
         </is>
       </c>
       <c r="S790" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T790" s="1" t="n"/>
@@ -60609,34 +60625,34 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>81780</v>
+        <v>83921</v>
       </c>
       <c r="B791" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C791" s="1" t="inlineStr">
         <is>
-          <t>Objeto Social</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D791" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E791" s="1" t="inlineStr">
         <is>
-          <t>ALTERAÇÃO CONTRATUAL DA EMPRESA: 6993-GOMES SERVIÇOS - LTDAGRUPO: CRISTO REIALTERAÇÃO DE QSA E OBJETO SOCIALPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.500,00MESMA ATIVIDADE E SÓCIOS DO SUP. AVENIDA, APÓS ALTERAÇÃO MIGRAR FUNCIONÁRIOS PARA NOVA EMPRESA ALTERAR QSA E OBJETO SOCIAL.</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F791" s="1" t="n">
-        <v>6993</v>
+        <v>6999</v>
       </c>
       <c r="G791" s="1" t="inlineStr">
         <is>
-          <t>GOMES SERVIÇOS - LTDA</t>
+          <t>VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="H791" s="1" t="inlineStr">
@@ -60650,34 +60666,26 @@
         </is>
       </c>
       <c r="J791" s="2" t="n">
-        <v>46237.62372283565</v>
+        <v>46279.39769957176</v>
       </c>
       <c r="K791" s="2" t="n">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="L791" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M791" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N791" s="2" t="n">
-        <v>46246.66900671296</v>
-      </c>
+          <t>Ney Barbosa</t>
+        </is>
+      </c>
+      <c r="N791" s="1" t="n"/>
       <c r="O791" s="1" t="n"/>
       <c r="P791" s="1" t="n"/>
       <c r="Q791" s="1" t="inlineStr"/>
-      <c r="R791" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prezados(as), boa tarde!
-Alteração contratual em andamento. 
-Atenciosamente, </t>
-        </is>
-      </c>
+      <c r="R791" s="1" t="inlineStr"/>
       <c r="S791" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -60688,7 +60696,7 @@
     </row>
     <row r="792">
       <c r="A792" s="1" t="n">
-        <v>83921</v>
+        <v>83904</v>
       </c>
       <c r="B792" s="1" t="inlineStr">
         <is>
@@ -60711,16 +60719,16 @@
         </is>
       </c>
       <c r="F792" s="1" t="n">
-        <v>6999</v>
+        <v>7005</v>
       </c>
       <c r="G792" s="1" t="inlineStr">
         <is>
-          <t>VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
+          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H792" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I792" s="1" t="inlineStr">
@@ -60729,7 +60737,7 @@
         </is>
       </c>
       <c r="J792" s="2" t="n">
-        <v>46279.39769957176</v>
+        <v>46279.39261207176</v>
       </c>
       <c r="K792" s="2" t="n">
         <v>46281</v>
@@ -60759,7 +60767,7 @@
     </row>
     <row r="793">
       <c r="A793" s="1" t="n">
-        <v>83904</v>
+        <v>83905</v>
       </c>
       <c r="B793" s="1" t="inlineStr">
         <is>
@@ -60782,11 +60790,11 @@
         </is>
       </c>
       <c r="F793" s="1" t="n">
-        <v>7005</v>
+        <v>7006</v>
       </c>
       <c r="G793" s="1" t="inlineStr">
         <is>
-          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H793" s="1" t="inlineStr">
@@ -60800,7 +60808,7 @@
         </is>
       </c>
       <c r="J793" s="2" t="n">
-        <v>46279.39261207176</v>
+        <v>46279.39292399306</v>
       </c>
       <c r="K793" s="2" t="n">
         <v>46281</v>
@@ -60830,39 +60838,39 @@
     </row>
     <row r="794">
       <c r="A794" s="1" t="n">
-        <v>83905</v>
+        <v>83447</v>
       </c>
       <c r="B794" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C794" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D794" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E794" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Por favor, abrir o chamado na empresa Nova Boston Grill (7039) para pedir que corrija o endereço de cobrança para Rua: Clodomiro Amazonas, 816 (escritório central do grupo Boston), Corrigir  para todo o grupo Boston.</t>
         </is>
       </c>
       <c r="F794" s="1" t="n">
-        <v>7006</v>
+        <v>7039</v>
       </c>
       <c r="G794" s="1" t="inlineStr">
         <is>
-          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>NOVA BOSTON GRILL RESTAURANTE LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H794" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I794" s="1" t="inlineStr">
@@ -60871,26 +60879,30 @@
         </is>
       </c>
       <c r="J794" s="2" t="n">
-        <v>46279.39292399306</v>
+        <v>46267.38457577546</v>
       </c>
       <c r="K794" s="2" t="n">
-        <v>46281</v>
+        <v>46268</v>
       </c>
       <c r="L794" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M794" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="N794" s="1" t="n"/>
       <c r="O794" s="1" t="n"/>
       <c r="P794" s="1" t="n"/>
       <c r="Q794" s="1" t="inlineStr"/>
-      <c r="R794" s="1" t="inlineStr"/>
+      <c r="R794" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O endereço da empresa está de acordo com o CNPJ. O que deve ser alterado? Onde deve ser alterado? </t>
+        </is>
+      </c>
       <c r="S794" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -60901,39 +60913,39 @@
     </row>
     <row r="795">
       <c r="A795" s="1" t="n">
-        <v>83447</v>
+        <v>83907</v>
       </c>
       <c r="B795" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C795" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D795" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E795" s="1" t="inlineStr">
         <is>
-          <t>Por favor, abrir o chamado na empresa Nova Boston Grill (7039) para pedir que corrija o endereço de cobrança para Rua: Clodomiro Amazonas, 816 (escritório central do grupo Boston), Corrigir  para todo o grupo Boston.</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F795" s="1" t="n">
-        <v>7039</v>
+        <v>7041</v>
       </c>
       <c r="G795" s="1" t="inlineStr">
         <is>
-          <t>NOVA BOSTON GRILL RESTAURANTE LTDA (FILIAL 1)</t>
+          <t>PROMOTORAS GYN SERVICOS PROMOCIONAIS LTDA</t>
         </is>
       </c>
       <c r="H795" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I795" s="1" t="inlineStr">
@@ -60942,30 +60954,26 @@
         </is>
       </c>
       <c r="J795" s="2" t="n">
-        <v>46267.38457577546</v>
+        <v>46279.39348993055</v>
       </c>
       <c r="K795" s="2" t="n">
-        <v>46268</v>
+        <v>46281</v>
       </c>
       <c r="L795" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M795" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Ney Barbosa</t>
         </is>
       </c>
       <c r="N795" s="1" t="n"/>
       <c r="O795" s="1" t="n"/>
       <c r="P795" s="1" t="n"/>
       <c r="Q795" s="1" t="inlineStr"/>
-      <c r="R795" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O endereço da empresa está de acordo com o CNPJ. O que deve ser alterado? Onde deve ser alterado? </t>
-        </is>
-      </c>
+      <c r="R795" s="1" t="inlineStr"/>
       <c r="S795" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -60976,39 +60984,39 @@
     </row>
     <row r="796">
       <c r="A796" s="1" t="n">
-        <v>83907</v>
+        <v>83261</v>
       </c>
       <c r="B796" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C796" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D796" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E796" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Alteração contratual do QSA da empresa: 7046-RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDAGrupo: RamiroProposta já negociada no valor de R$1.800,00Retirar os dois sócios (João e Lucas) e deixar 100% do QSA com o Ramiro. Colocar atividade no Simples impeditiva, para que no mês de outubro essa empresa entre no Lucro Real</t>
         </is>
       </c>
       <c r="F796" s="1" t="n">
-        <v>7041</v>
+        <v>7046</v>
       </c>
       <c r="G796" s="1" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN SERVICOS PROMOCIONAIS LTDA</t>
+          <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
         </is>
       </c>
       <c r="H796" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I796" s="1" t="inlineStr">
@@ -61017,26 +61025,34 @@
         </is>
       </c>
       <c r="J796" s="2" t="n">
-        <v>46279.39348993055</v>
+        <v>46265.45567503473</v>
       </c>
       <c r="K796" s="2" t="n">
-        <v>46281</v>
+        <v>46293</v>
       </c>
       <c r="L796" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M796" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N796" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N796" s="2" t="n">
+        <v>46266.72388877315</v>
+      </c>
       <c r="O796" s="1" t="n"/>
       <c r="P796" s="1" t="n"/>
       <c r="Q796" s="1" t="inlineStr"/>
-      <c r="R796" s="1" t="inlineStr"/>
+      <c r="R796" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde.
+Preparando a minuta.
+Atenciosamente,</t>
+        </is>
+      </c>
       <c r="S796" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -61047,39 +61063,39 @@
     </row>
     <row r="797">
       <c r="A797" s="1" t="n">
-        <v>83261</v>
+        <v>83908</v>
       </c>
       <c r="B797" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C797" s="1" t="inlineStr">
         <is>
-          <t>Sócios</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D797" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E797" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual do QSA da empresa: 7046-RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDAGrupo: RamiroProposta já negociada no valor de R$1.800,00Retirar os dois sócios (João e Lucas) e deixar 100% do QSA com o Ramiro. Colocar atividade no Simples impeditiva, para que no mês de outubro essa empresa entre no Lucro Real</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F797" s="1" t="n">
-        <v>7046</v>
+        <v>7052</v>
       </c>
       <c r="G797" s="1" t="inlineStr">
         <is>
-          <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
+          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
         </is>
       </c>
       <c r="H797" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I797" s="1" t="inlineStr">
@@ -61088,34 +61104,26 @@
         </is>
       </c>
       <c r="J797" s="2" t="n">
-        <v>46265.45567503473</v>
+        <v>46279.3937971875</v>
       </c>
       <c r="K797" s="2" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="L797" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M797" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N797" s="2" t="n">
-        <v>46266.72388877315</v>
-      </c>
+          <t>Ney Barbosa</t>
+        </is>
+      </c>
+      <c r="N797" s="1" t="n"/>
       <c r="O797" s="1" t="n"/>
       <c r="P797" s="1" t="n"/>
       <c r="Q797" s="1" t="inlineStr"/>
-      <c r="R797" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde.
-Preparando a minuta.
-Atenciosamente,</t>
-        </is>
-      </c>
+      <c r="R797" s="1" t="inlineStr"/>
       <c r="S797" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -61126,7 +61134,7 @@
     </row>
     <row r="798">
       <c r="A798" s="1" t="n">
-        <v>83908</v>
+        <v>83909</v>
       </c>
       <c r="B798" s="1" t="inlineStr">
         <is>
@@ -61149,11 +61157,11 @@
         </is>
       </c>
       <c r="F798" s="1" t="n">
-        <v>7052</v>
+        <v>7053</v>
       </c>
       <c r="G798" s="1" t="inlineStr">
         <is>
-          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
+          <t>BIANCA EMBREAGENS LTDA</t>
         </is>
       </c>
       <c r="H798" s="1" t="inlineStr">
@@ -61167,7 +61175,7 @@
         </is>
       </c>
       <c r="J798" s="2" t="n">
-        <v>46279.3937971875</v>
+        <v>46279.39412114584</v>
       </c>
       <c r="K798" s="2" t="n">
         <v>46281</v>
@@ -61197,7 +61205,7 @@
     </row>
     <row r="799">
       <c r="A799" s="1" t="n">
-        <v>83909</v>
+        <v>83910</v>
       </c>
       <c r="B799" s="1" t="inlineStr">
         <is>
@@ -61220,11 +61228,11 @@
         </is>
       </c>
       <c r="F799" s="1" t="n">
-        <v>7053</v>
+        <v>7054</v>
       </c>
       <c r="G799" s="1" t="inlineStr">
         <is>
-          <t>BIANCA EMBREAGENS LTDA</t>
+          <t>KADOSH DISTRIBUIDOR COMERCIO E SERVICO DIGITAL LTDA</t>
         </is>
       </c>
       <c r="H799" s="1" t="inlineStr">
@@ -61238,7 +61246,7 @@
         </is>
       </c>
       <c r="J799" s="2" t="n">
-        <v>46279.39412114584</v>
+        <v>46279.39450123843</v>
       </c>
       <c r="K799" s="2" t="n">
         <v>46281</v>
@@ -61268,7 +61276,7 @@
     </row>
     <row r="800">
       <c r="A800" s="1" t="n">
-        <v>83910</v>
+        <v>83911</v>
       </c>
       <c r="B800" s="1" t="inlineStr">
         <is>
@@ -61291,11 +61299,11 @@
         </is>
       </c>
       <c r="F800" s="1" t="n">
-        <v>7054</v>
+        <v>7055</v>
       </c>
       <c r="G800" s="1" t="inlineStr">
         <is>
-          <t>KADOSH DISTRIBUIDOR COMERCIO E SERVICO DIGITAL LTDA</t>
+          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
         </is>
       </c>
       <c r="H800" s="1" t="inlineStr">
@@ -61309,7 +61317,7 @@
         </is>
       </c>
       <c r="J800" s="2" t="n">
-        <v>46279.39450123843</v>
+        <v>46279.39479143519</v>
       </c>
       <c r="K800" s="2" t="n">
         <v>46281</v>
@@ -61339,7 +61347,7 @@
     </row>
     <row r="801">
       <c r="A801" s="1" t="n">
-        <v>83911</v>
+        <v>83912</v>
       </c>
       <c r="B801" s="1" t="inlineStr">
         <is>
@@ -61362,11 +61370,11 @@
         </is>
       </c>
       <c r="F801" s="1" t="n">
-        <v>7055</v>
+        <v>7056</v>
       </c>
       <c r="G801" s="1" t="inlineStr">
         <is>
-          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
+          <t>AUTO CENTER EMBRASIL LTDA</t>
         </is>
       </c>
       <c r="H801" s="1" t="inlineStr">
@@ -61380,7 +61388,7 @@
         </is>
       </c>
       <c r="J801" s="2" t="n">
-        <v>46279.39479143519</v>
+        <v>46279.39518283565</v>
       </c>
       <c r="K801" s="2" t="n">
         <v>46281</v>
@@ -61410,7 +61418,7 @@
     </row>
     <row r="802">
       <c r="A802" s="1" t="n">
-        <v>83912</v>
+        <v>83913</v>
       </c>
       <c r="B802" s="1" t="inlineStr">
         <is>
@@ -61433,11 +61441,11 @@
         </is>
       </c>
       <c r="F802" s="1" t="n">
-        <v>7056</v>
+        <v>7057</v>
       </c>
       <c r="G802" s="1" t="inlineStr">
         <is>
-          <t>AUTO CENTER EMBRASIL LTDA</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H802" s="1" t="inlineStr">
@@ -61451,7 +61459,7 @@
         </is>
       </c>
       <c r="J802" s="2" t="n">
-        <v>46279.39518283565</v>
+        <v>46279.39551385416</v>
       </c>
       <c r="K802" s="2" t="n">
         <v>46281</v>
@@ -61481,7 +61489,7 @@
     </row>
     <row r="803">
       <c r="A803" s="1" t="n">
-        <v>83913</v>
+        <v>83916</v>
       </c>
       <c r="B803" s="1" t="inlineStr">
         <is>
@@ -61504,11 +61512,11 @@
         </is>
       </c>
       <c r="F803" s="1" t="n">
-        <v>7057</v>
+        <v>7060</v>
       </c>
       <c r="G803" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
+          <t>GAPEMA LOCACAO DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H803" s="1" t="inlineStr">
@@ -61522,7 +61530,7 @@
         </is>
       </c>
       <c r="J803" s="2" t="n">
-        <v>46279.39551385416</v>
+        <v>46279.39634756945</v>
       </c>
       <c r="K803" s="2" t="n">
         <v>46281</v>
@@ -61552,7 +61560,7 @@
     </row>
     <row r="804">
       <c r="A804" s="1" t="n">
-        <v>83916</v>
+        <v>83917</v>
       </c>
       <c r="B804" s="1" t="inlineStr">
         <is>
@@ -61575,11 +61583,11 @@
         </is>
       </c>
       <c r="F804" s="1" t="n">
-        <v>7060</v>
+        <v>7061</v>
       </c>
       <c r="G804" s="1" t="inlineStr">
         <is>
-          <t>GAPEMA LOCACAO DE EQUIPAMENTOS LTDA</t>
+          <t>BF CORTES E FUROS TECNICOS E LOCACAO LTDA</t>
         </is>
       </c>
       <c r="H804" s="1" t="inlineStr">
@@ -61593,7 +61601,7 @@
         </is>
       </c>
       <c r="J804" s="2" t="n">
-        <v>46279.39634756945</v>
+        <v>46279.39663144676</v>
       </c>
       <c r="K804" s="2" t="n">
         <v>46281</v>
@@ -61623,7 +61631,7 @@
     </row>
     <row r="805">
       <c r="A805" s="1" t="n">
-        <v>83917</v>
+        <v>83918</v>
       </c>
       <c r="B805" s="1" t="inlineStr">
         <is>
@@ -61646,11 +61654,11 @@
         </is>
       </c>
       <c r="F805" s="1" t="n">
-        <v>7061</v>
+        <v>7062</v>
       </c>
       <c r="G805" s="1" t="inlineStr">
         <is>
-          <t>BF CORTES E FUROS TECNICOS E LOCACAO LTDA</t>
+          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="H805" s="1" t="inlineStr">
@@ -61664,7 +61672,7 @@
         </is>
       </c>
       <c r="J805" s="2" t="n">
-        <v>46279.39663144676</v>
+        <v>46279.39692175926</v>
       </c>
       <c r="K805" s="2" t="n">
         <v>46281</v>
@@ -61694,7 +61702,7 @@
     </row>
     <row r="806">
       <c r="A806" s="1" t="n">
-        <v>83918</v>
+        <v>83919</v>
       </c>
       <c r="B806" s="1" t="inlineStr">
         <is>
@@ -61717,11 +61725,11 @@
         </is>
       </c>
       <c r="F806" s="1" t="n">
-        <v>7062</v>
+        <v>7063</v>
       </c>
       <c r="G806" s="1" t="inlineStr">
         <is>
-          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
+          <t>CR LOCACAO E VENDAS DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H806" s="1" t="inlineStr">
@@ -61735,7 +61743,7 @@
         </is>
       </c>
       <c r="J806" s="2" t="n">
-        <v>46279.39692175926</v>
+        <v>46279.39713047454</v>
       </c>
       <c r="K806" s="2" t="n">
         <v>46281</v>
@@ -61765,67 +61773,63 @@
     </row>
     <row r="807">
       <c r="A807" s="1" t="n">
-        <v>83919</v>
+        <v>83982</v>
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C807" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D807" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E807" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Abertura de nova empresa do grupo: 7064-BC SUPERMERCADOTributação: Simples NacionalTipo de Atividade: ComércioFinalidade: OperacionalForma Juridica: LtdaProposta: já negociada no valor de R$1.800,00</t>
         </is>
       </c>
       <c r="F807" s="1" t="n">
-        <v>7063</v>
+        <v>7064</v>
       </c>
       <c r="G807" s="1" t="inlineStr">
         <is>
-          <t>CR LOCACAO E VENDAS DE EQUIPAMENTOS LTDA</t>
-        </is>
-      </c>
-      <c r="H807" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+          <t>BISPO E CARVALHO SUPERMERCADO LTDA</t>
+        </is>
+      </c>
+      <c r="H807" s="1" t="n"/>
       <c r="I807" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J807" s="2" t="n">
-        <v>46279.39713047454</v>
+        <v>46280.39557824074</v>
       </c>
       <c r="K807" s="2" t="n">
-        <v>46281</v>
+        <v>46308</v>
       </c>
       <c r="L807" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M807" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N807" s="1" t="n"/>
       <c r="O807" s="1" t="n"/>
       <c r="P807" s="1" t="n"/>
       <c r="Q807" s="1" t="inlineStr"/>
-      <c r="R807" s="1" t="inlineStr"/>
+      <c r="R807" s="1" t="n"/>
       <c r="S807" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -61836,63 +61840,67 @@
     </row>
     <row r="808">
       <c r="A808" s="1" t="n">
-        <v>83982</v>
+        <v>83922</v>
       </c>
       <c r="B808" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C808" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Comércio</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D808" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E808" s="1" t="inlineStr">
         <is>
-          <t>Abertura de nova empresa do grupo: 7064-BC SUPERMERCADOTributação: Simples NacionalTipo de Atividade: ComércioFinalidade: OperacionalForma Juridica: LtdaProposta: já negociada no valor de R$1.800,00</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F808" s="1" t="n">
-        <v>7064</v>
+        <v>7065</v>
       </c>
       <c r="G808" s="1" t="inlineStr">
         <is>
-          <t>BISPO E CARVALHO SUPERMERCADO LTDA</t>
-        </is>
-      </c>
-      <c r="H808" s="1" t="n"/>
+          <t>GRANUA AGROINDUSTRIA E COMERCIO DE ALIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="H808" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Ribeiro</t>
+        </is>
+      </c>
       <c r="I808" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J808" s="2" t="n">
-        <v>46280.39557824074</v>
+        <v>46279.39797662037</v>
       </c>
       <c r="K808" s="2" t="n">
-        <v>46308</v>
+        <v>46281</v>
       </c>
       <c r="L808" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M808" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Ney Barbosa</t>
         </is>
       </c>
       <c r="N808" s="1" t="n"/>
       <c r="O808" s="1" t="n"/>
       <c r="P808" s="1" t="n"/>
       <c r="Q808" s="1" t="inlineStr"/>
-      <c r="R808" s="1" t="n"/>
+      <c r="R808" s="1" t="inlineStr"/>
       <c r="S808" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -61903,67 +61911,75 @@
     </row>
     <row r="809">
       <c r="A809" s="1" t="n">
-        <v>83922</v>
+        <v>83218</v>
       </c>
       <c r="B809" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C809" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D809" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E809" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F809" s="1" t="n">
-        <v>7065</v>
+        <v>7063</v>
       </c>
       <c r="G809" s="1" t="inlineStr">
         <is>
-          <t>GRANUA AGROINDUSTRIA E COMERCIO DE ALIMENTOS LTDA</t>
+          <t>CR LOCACAO E VENDAS DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H809" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I809" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J809" s="2" t="n">
-        <v>46279.39797662037</v>
+        <v>46262.49630575231</v>
       </c>
       <c r="K809" s="2" t="n">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="L809" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M809" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N809" s="1" t="n"/>
-      <c r="O809" s="1" t="n"/>
+          <t>Santos Karina</t>
+        </is>
+      </c>
+      <c r="N809" s="2" t="n">
+        <v>46267.54627245371</v>
+      </c>
+      <c r="O809" s="2" t="n">
+        <v>46283</v>
+      </c>
       <c r="P809" s="1" t="n"/>
       <c r="Q809" s="1" t="inlineStr"/>
-      <c r="R809" s="1" t="inlineStr"/>
+      <c r="R809" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando o SAC liberar para cobrar os documentos .</t>
+        </is>
+      </c>
       <c r="S809" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -61974,7 +61990,7 @@
     </row>
     <row r="810">
       <c r="A810" s="1" t="n">
-        <v>83218</v>
+        <v>83205</v>
       </c>
       <c r="B810" s="1" t="inlineStr">
         <is>
@@ -61993,15 +62009,15 @@
       </c>
       <c r="E810" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
+          <t>Bom dia, por gentileza, providenciar documentos para implantação da empresa.</t>
         </is>
       </c>
       <c r="F810" s="1" t="n">
-        <v>7063</v>
+        <v>7064</v>
       </c>
       <c r="G810" s="1" t="inlineStr">
         <is>
-          <t>CR LOCACAO E VENDAS DE EQUIPAMENTOS LTDA</t>
+          <t>BISPO E CARVALHO SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="H810" s="1" t="inlineStr">
@@ -62015,7 +62031,7 @@
         </is>
       </c>
       <c r="J810" s="2" t="n">
-        <v>46262.49630575231</v>
+        <v>46262.47796832176</v>
       </c>
       <c r="K810" s="2" t="n">
         <v>46265</v>
@@ -62031,7 +62047,7 @@
         </is>
       </c>
       <c r="N810" s="2" t="n">
-        <v>46267.54627245371</v>
+        <v>46267.54541188657</v>
       </c>
       <c r="O810" s="2" t="n">
         <v>46283</v>
@@ -62053,7 +62069,7 @@
     </row>
     <row r="811">
       <c r="A811" s="1" t="n">
-        <v>83205</v>
+        <v>83216</v>
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
@@ -62072,15 +62088,15 @@
       </c>
       <c r="E811" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar documentos para implantação da empresa.</t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F811" s="1" t="n">
-        <v>7064</v>
+        <v>7061</v>
       </c>
       <c r="G811" s="1" t="inlineStr">
         <is>
-          <t>BISPO E CARVALHO SUPERMERCADO LTDA</t>
+          <t>BF CORTES E FUROS TECNICOS E LOCACAO LTDA</t>
         </is>
       </c>
       <c r="H811" s="1" t="inlineStr">
@@ -62094,7 +62110,7 @@
         </is>
       </c>
       <c r="J811" s="2" t="n">
-        <v>46262.47796832176</v>
+        <v>46262.49574116898</v>
       </c>
       <c r="K811" s="2" t="n">
         <v>46265</v>
@@ -62110,7 +62126,7 @@
         </is>
       </c>
       <c r="N811" s="2" t="n">
-        <v>46267.54541188657</v>
+        <v>46267.54612248843</v>
       </c>
       <c r="O811" s="2" t="n">
         <v>46283</v>
@@ -62132,7 +62148,7 @@
     </row>
     <row r="812">
       <c r="A812" s="1" t="n">
-        <v>83216</v>
+        <v>83217</v>
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
@@ -62155,11 +62171,11 @@
         </is>
       </c>
       <c r="F812" s="1" t="n">
-        <v>7061</v>
+        <v>7062</v>
       </c>
       <c r="G812" s="1" t="inlineStr">
         <is>
-          <t>BF CORTES E FUROS TECNICOS E LOCACAO LTDA</t>
+          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="H812" s="1" t="inlineStr">
@@ -62173,7 +62189,7 @@
         </is>
       </c>
       <c r="J812" s="2" t="n">
-        <v>46262.49574116898</v>
+        <v>46262.49604351852</v>
       </c>
       <c r="K812" s="2" t="n">
         <v>46265</v>
@@ -62189,7 +62205,7 @@
         </is>
       </c>
       <c r="N812" s="2" t="n">
-        <v>46267.54612248843</v>
+        <v>46267.54619818287</v>
       </c>
       <c r="O812" s="2" t="n">
         <v>46283</v>
@@ -62211,7 +62227,7 @@
     </row>
     <row r="813">
       <c r="A813" s="1" t="n">
-        <v>83217</v>
+        <v>83212</v>
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
@@ -62234,11 +62250,11 @@
         </is>
       </c>
       <c r="F813" s="1" t="n">
-        <v>7062</v>
+        <v>7057</v>
       </c>
       <c r="G813" s="1" t="inlineStr">
         <is>
-          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H813" s="1" t="inlineStr">
@@ -62252,7 +62268,7 @@
         </is>
       </c>
       <c r="J813" s="2" t="n">
-        <v>46262.49604351852</v>
+        <v>46262.49474181713</v>
       </c>
       <c r="K813" s="2" t="n">
         <v>46265</v>
@@ -62268,7 +62284,7 @@
         </is>
       </c>
       <c r="N813" s="2" t="n">
-        <v>46267.54619818287</v>
+        <v>46267.54564378472</v>
       </c>
       <c r="O813" s="2" t="n">
         <v>46283</v>
@@ -62290,7 +62306,7 @@
     </row>
     <row r="814">
       <c r="A814" s="1" t="n">
-        <v>83212</v>
+        <v>83213</v>
       </c>
       <c r="B814" s="1" t="inlineStr">
         <is>
@@ -62313,11 +62329,11 @@
         </is>
       </c>
       <c r="F814" s="1" t="n">
-        <v>7057</v>
+        <v>7058</v>
       </c>
       <c r="G814" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H814" s="1" t="inlineStr">
@@ -62331,7 +62347,7 @@
         </is>
       </c>
       <c r="J814" s="2" t="n">
-        <v>46262.49474181713</v>
+        <v>46262.49500332176</v>
       </c>
       <c r="K814" s="2" t="n">
         <v>46265</v>
@@ -62347,7 +62363,7 @@
         </is>
       </c>
       <c r="N814" s="2" t="n">
-        <v>46267.54564378472</v>
+        <v>46267.5457496875</v>
       </c>
       <c r="O814" s="2" t="n">
         <v>46283</v>
@@ -62369,7 +62385,7 @@
     </row>
     <row r="815">
       <c r="A815" s="1" t="n">
-        <v>83213</v>
+        <v>83214</v>
       </c>
       <c r="B815" s="1" t="inlineStr">
         <is>
@@ -62392,11 +62408,11 @@
         </is>
       </c>
       <c r="F815" s="1" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="G815" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 1)</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 2)</t>
         </is>
       </c>
       <c r="H815" s="1" t="inlineStr">
@@ -62410,7 +62426,7 @@
         </is>
       </c>
       <c r="J815" s="2" t="n">
-        <v>46262.49500332176</v>
+        <v>46262.49526809028</v>
       </c>
       <c r="K815" s="2" t="n">
         <v>46265</v>
@@ -62426,7 +62442,7 @@
         </is>
       </c>
       <c r="N815" s="2" t="n">
-        <v>46267.5457496875</v>
+        <v>46267.54582943287</v>
       </c>
       <c r="O815" s="2" t="n">
         <v>46283</v>
@@ -62448,7 +62464,7 @@
     </row>
     <row r="816">
       <c r="A816" s="1" t="n">
-        <v>83214</v>
+        <v>83215</v>
       </c>
       <c r="B816" s="1" t="inlineStr">
         <is>
@@ -62471,11 +62487,11 @@
         </is>
       </c>
       <c r="F816" s="1" t="n">
-        <v>7059</v>
+        <v>7060</v>
       </c>
       <c r="G816" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 2)</t>
+          <t>GAPEMA LOCACAO DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H816" s="1" t="inlineStr">
@@ -62489,7 +62505,7 @@
         </is>
       </c>
       <c r="J816" s="2" t="n">
-        <v>46262.49526809028</v>
+        <v>46262.49551331018</v>
       </c>
       <c r="K816" s="2" t="n">
         <v>46265</v>
@@ -62505,7 +62521,7 @@
         </is>
       </c>
       <c r="N816" s="2" t="n">
-        <v>46267.54582943287</v>
+        <v>46267.54604818287</v>
       </c>
       <c r="O816" s="2" t="n">
         <v>46283</v>
@@ -62527,7 +62543,7 @@
     </row>
     <row r="817">
       <c r="A817" s="1" t="n">
-        <v>83215</v>
+        <v>83116</v>
       </c>
       <c r="B817" s="1" t="inlineStr">
         <is>
@@ -62546,15 +62562,15 @@
       </c>
       <c r="E817" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
         </is>
       </c>
       <c r="F817" s="1" t="n">
-        <v>7060</v>
+        <v>7055</v>
       </c>
       <c r="G817" s="1" t="inlineStr">
         <is>
-          <t>GAPEMA LOCACAO DE EQUIPAMENTOS LTDA</t>
+          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
         </is>
       </c>
       <c r="H817" s="1" t="inlineStr">
@@ -62568,10 +62584,10 @@
         </is>
       </c>
       <c r="J817" s="2" t="n">
-        <v>46262.49551331018</v>
+        <v>46261.47479783565</v>
       </c>
       <c r="K817" s="2" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="L817" s="1" t="inlineStr">
         <is>
@@ -62584,7 +62600,7 @@
         </is>
       </c>
       <c r="N817" s="2" t="n">
-        <v>46267.54604818287</v>
+        <v>46261.69765454861</v>
       </c>
       <c r="O817" s="2" t="n">
         <v>46283</v>
@@ -62593,7 +62609,7 @@
       <c r="Q817" s="1" t="inlineStr"/>
       <c r="R817" s="1" t="inlineStr">
         <is>
-          <t>Aguardando o SAC liberar para cobrar os documentos .</t>
+          <t>Cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S817" s="1" t="inlineStr">
@@ -62606,7 +62622,7 @@
     </row>
     <row r="818">
       <c r="A818" s="1" t="n">
-        <v>83116</v>
+        <v>83117</v>
       </c>
       <c r="B818" s="1" t="inlineStr">
         <is>
@@ -62629,11 +62645,11 @@
         </is>
       </c>
       <c r="F818" s="1" t="n">
-        <v>7055</v>
+        <v>7056</v>
       </c>
       <c r="G818" s="1" t="inlineStr">
         <is>
-          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
+          <t>AUTO CENTER EMBRASIL LTDA</t>
         </is>
       </c>
       <c r="H818" s="1" t="inlineStr">
@@ -62647,7 +62663,7 @@
         </is>
       </c>
       <c r="J818" s="2" t="n">
-        <v>46261.47479783565</v>
+        <v>46261.47502040509</v>
       </c>
       <c r="K818" s="2" t="n">
         <v>46262</v>
@@ -62663,7 +62679,7 @@
         </is>
       </c>
       <c r="N818" s="2" t="n">
-        <v>46261.69765454861</v>
+        <v>46261.69782774305</v>
       </c>
       <c r="O818" s="2" t="n">
         <v>46283</v>
@@ -62685,7 +62701,7 @@
     </row>
     <row r="819">
       <c r="A819" s="1" t="n">
-        <v>83117</v>
+        <v>83115</v>
       </c>
       <c r="B819" s="1" t="inlineStr">
         <is>
@@ -62708,11 +62724,11 @@
         </is>
       </c>
       <c r="F819" s="1" t="n">
-        <v>7056</v>
+        <v>7054</v>
       </c>
       <c r="G819" s="1" t="inlineStr">
         <is>
-          <t>AUTO CENTER EMBRASIL LTDA</t>
+          <t>KADOSH DISTRIBUIDOR COMERCIO E SERVICO DIGITAL LTDA</t>
         </is>
       </c>
       <c r="H819" s="1" t="inlineStr">
@@ -62726,7 +62742,7 @@
         </is>
       </c>
       <c r="J819" s="2" t="n">
-        <v>46261.47502040509</v>
+        <v>46261.47454267361</v>
       </c>
       <c r="K819" s="2" t="n">
         <v>46262</v>
@@ -62742,7 +62758,7 @@
         </is>
       </c>
       <c r="N819" s="2" t="n">
-        <v>46261.69782774305</v>
+        <v>46261.6975778125</v>
       </c>
       <c r="O819" s="2" t="n">
         <v>46283</v>
@@ -62764,7 +62780,7 @@
     </row>
     <row r="820">
       <c r="A820" s="1" t="n">
-        <v>83115</v>
+        <v>82905</v>
       </c>
       <c r="B820" s="1" t="inlineStr">
         <is>
@@ -62783,15 +62799,15 @@
       </c>
       <c r="E820" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
+          <t xml:space="preserve">Boa tarde, por gentileza, solicitar os documentos para a implantação da empresa. </t>
         </is>
       </c>
       <c r="F820" s="1" t="n">
-        <v>7054</v>
+        <v>7046</v>
       </c>
       <c r="G820" s="1" t="inlineStr">
         <is>
-          <t>KADOSH DISTRIBUIDOR COMERCIO E SERVICO DIGITAL LTDA</t>
+          <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
         </is>
       </c>
       <c r="H820" s="1" t="inlineStr">
@@ -62805,10 +62821,10 @@
         </is>
       </c>
       <c r="J820" s="2" t="n">
-        <v>46261.47454267361</v>
+        <v>46258.65608700232</v>
       </c>
       <c r="K820" s="2" t="n">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="L820" s="1" t="inlineStr">
         <is>
@@ -62821,7 +62837,7 @@
         </is>
       </c>
       <c r="N820" s="2" t="n">
-        <v>46261.6975778125</v>
+        <v>46259.7507258449</v>
       </c>
       <c r="O820" s="2" t="n">
         <v>46283</v>
@@ -62830,7 +62846,7 @@
       <c r="Q820" s="1" t="inlineStr"/>
       <c r="R820" s="1" t="inlineStr">
         <is>
-          <t>Cobramos os documentos do antigo contador.</t>
+          <t xml:space="preserve">Cobramos os documentos </t>
         </is>
       </c>
       <c r="S820" s="1" t="inlineStr">
@@ -62843,7 +62859,7 @@
     </row>
     <row r="821">
       <c r="A821" s="1" t="n">
-        <v>82905</v>
+        <v>83112</v>
       </c>
       <c r="B821" s="1" t="inlineStr">
         <is>
@@ -62862,15 +62878,15 @@
       </c>
       <c r="E821" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tarde, por gentileza, solicitar os documentos para a implantação da empresa. </t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
         </is>
       </c>
       <c r="F821" s="1" t="n">
-        <v>7046</v>
+        <v>7052</v>
       </c>
       <c r="G821" s="1" t="inlineStr">
         <is>
-          <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
+          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
         </is>
       </c>
       <c r="H821" s="1" t="inlineStr">
@@ -62884,10 +62900,10 @@
         </is>
       </c>
       <c r="J821" s="2" t="n">
-        <v>46258.65608700232</v>
+        <v>46261.47219082176</v>
       </c>
       <c r="K821" s="2" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="L821" s="1" t="inlineStr">
         <is>
@@ -62900,7 +62916,7 @@
         </is>
       </c>
       <c r="N821" s="2" t="n">
-        <v>46259.7507258449</v>
+        <v>46261.69723422454</v>
       </c>
       <c r="O821" s="2" t="n">
         <v>46283</v>
@@ -62909,7 +62925,7 @@
       <c r="Q821" s="1" t="inlineStr"/>
       <c r="R821" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cobramos os documentos </t>
+          <t>Cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S821" s="1" t="inlineStr">
@@ -62922,7 +62938,7 @@
     </row>
     <row r="822">
       <c r="A822" s="1" t="n">
-        <v>83112</v>
+        <v>82755</v>
       </c>
       <c r="B822" s="1" t="inlineStr">
         <is>
@@ -62941,15 +62957,15 @@
       </c>
       <c r="E822" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
+          <t>Boa tarde, por gentileza, providenciar documentos para implantação.</t>
         </is>
       </c>
       <c r="F822" s="1" t="n">
-        <v>7052</v>
+        <v>7005</v>
       </c>
       <c r="G822" s="1" t="inlineStr">
         <is>
-          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
+          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H822" s="1" t="inlineStr">
@@ -62963,10 +62979,10 @@
         </is>
       </c>
       <c r="J822" s="2" t="n">
-        <v>46261.47219082176</v>
+        <v>46254.65957604167</v>
       </c>
       <c r="K822" s="2" t="n">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="L822" s="1" t="inlineStr">
         <is>
@@ -62979,7 +62995,7 @@
         </is>
       </c>
       <c r="N822" s="2" t="n">
-        <v>46261.69723422454</v>
+        <v>46255.48691519676</v>
       </c>
       <c r="O822" s="2" t="n">
         <v>46283</v>
@@ -62988,7 +63004,7 @@
       <c r="Q822" s="1" t="inlineStr"/>
       <c r="R822" s="1" t="inlineStr">
         <is>
-          <t>Cobramos os documentos do antigo contador.</t>
+          <t>cobramos novamente o retorno dos documentos</t>
         </is>
       </c>
       <c r="S822" s="1" t="inlineStr">
@@ -63001,7 +63017,7 @@
     </row>
     <row r="823">
       <c r="A823" s="1" t="n">
-        <v>82755</v>
+        <v>82756</v>
       </c>
       <c r="B823" s="1" t="inlineStr">
         <is>
@@ -63024,11 +63040,11 @@
         </is>
       </c>
       <c r="F823" s="1" t="n">
-        <v>7005</v>
+        <v>7006</v>
       </c>
       <c r="G823" s="1" t="inlineStr">
         <is>
-          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H823" s="1" t="inlineStr">
@@ -63042,7 +63058,7 @@
         </is>
       </c>
       <c r="J823" s="2" t="n">
-        <v>46254.65957604167</v>
+        <v>46254.65986380787</v>
       </c>
       <c r="K823" s="2" t="n">
         <v>46255</v>
@@ -63058,7 +63074,7 @@
         </is>
       </c>
       <c r="N823" s="2" t="n">
-        <v>46255.48691519676</v>
+        <v>46255.48792758102</v>
       </c>
       <c r="O823" s="2" t="n">
         <v>46283</v>
@@ -63067,7 +63083,7 @@
       <c r="Q823" s="1" t="inlineStr"/>
       <c r="R823" s="1" t="inlineStr">
         <is>
-          <t>cobramos novamente o retorno dos documentos</t>
+          <t>cobramos novamente os documentos</t>
         </is>
       </c>
       <c r="S823" s="1" t="inlineStr">
@@ -63080,7 +63096,7 @@
     </row>
     <row r="824">
       <c r="A824" s="1" t="n">
-        <v>82756</v>
+        <v>82753</v>
       </c>
       <c r="B824" s="1" t="inlineStr">
         <is>
@@ -63103,11 +63119,11 @@
         </is>
       </c>
       <c r="F824" s="1" t="n">
-        <v>7006</v>
+        <v>6993</v>
       </c>
       <c r="G824" s="1" t="inlineStr">
         <is>
-          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>GOMES SERVIÇOS - LTDA</t>
         </is>
       </c>
       <c r="H824" s="1" t="inlineStr">
@@ -63117,18 +63133,18 @@
       </c>
       <c r="I824" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J824" s="2" t="n">
-        <v>46254.65986380787</v>
+        <v>46254.65888769676</v>
       </c>
       <c r="K824" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="L824" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M824" s="1" t="inlineStr">
@@ -63136,9 +63152,7 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N824" s="2" t="n">
-        <v>46255.48792758102</v>
-      </c>
+      <c r="N824" s="1" t="n"/>
       <c r="O824" s="2" t="n">
         <v>46283</v>
       </c>
@@ -63146,7 +63160,7 @@
       <c r="Q824" s="1" t="inlineStr"/>
       <c r="R824" s="1" t="inlineStr">
         <is>
-          <t>cobramos novamente os documentos</t>
+          <t xml:space="preserve">GRUPO SUPERMERCADO CRISTE REI </t>
         </is>
       </c>
       <c r="S824" s="1" t="inlineStr">
@@ -63154,12 +63168,16 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T824" s="1" t="n"/>
+      <c r="T824" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
       <c r="U824" s="1" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" s="1" t="n">
-        <v>82753</v>
+        <v>79867</v>
       </c>
       <c r="B825" s="1" t="inlineStr">
         <is>
@@ -63168,62 +63186,63 @@
       </c>
       <c r="C825" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D825" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E825" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza, providenciar documentos para implantação.</t>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
         </is>
       </c>
       <c r="F825" s="1" t="n">
-        <v>6993</v>
+        <v>6704</v>
       </c>
       <c r="G825" s="1" t="inlineStr">
         <is>
-          <t>GOMES SERVIÇOS - LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="H825" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I825" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J825" s="2" t="n">
-        <v>46254.65888769676</v>
+        <v>46183.62582114583</v>
       </c>
       <c r="K825" s="2" t="n">
-        <v>46255</v>
+        <v>46185</v>
       </c>
       <c r="L825" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M825" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
-        </is>
-      </c>
-      <c r="N825" s="1" t="n"/>
-      <c r="O825" s="2" t="n">
-        <v>46283</v>
-      </c>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
+      <c r="N825" s="2" t="n">
+        <v>46237.4174340625</v>
+      </c>
+      <c r="O825" s="1" t="n"/>
       <c r="P825" s="1" t="n"/>
       <c r="Q825" s="1" t="inlineStr"/>
       <c r="R825" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRUPO SUPERMERCADO CRISTE REI </t>
+          <t>Bom dia!
+Cobramos a antiga contabilidade.</t>
         </is>
       </c>
       <c r="S825" s="1" t="inlineStr">
@@ -63231,16 +63250,12 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T825" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
+      <c r="T825" s="1" t="n"/>
       <c r="U825" s="1" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" s="1" t="n">
-        <v>79867</v>
+        <v>82310</v>
       </c>
       <c r="B826" s="1" t="inlineStr">
         <is>
@@ -63259,20 +63274,20 @@
       </c>
       <c r="E826" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t>Bom dia!Por favor, solicitar ao antigo contador o balanço de abertura.</t>
         </is>
       </c>
       <c r="F826" s="1" t="n">
-        <v>6704</v>
+        <v>6974</v>
       </c>
       <c r="G826" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>FRANCINALDO FERREIRA DE ANDRADE LTDA</t>
         </is>
       </c>
       <c r="H826" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I826" s="1" t="inlineStr">
@@ -63281,10 +63296,10 @@
         </is>
       </c>
       <c r="J826" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46247.3783179051</v>
       </c>
       <c r="K826" s="2" t="n">
-        <v>46185</v>
+        <v>46248</v>
       </c>
       <c r="L826" s="1" t="inlineStr">
         <is>
@@ -63297,15 +63312,14 @@
         </is>
       </c>
       <c r="N826" s="2" t="n">
-        <v>46237.4174340625</v>
+        <v>46253.39089305556</v>
       </c>
       <c r="O826" s="1" t="n"/>
       <c r="P826" s="1" t="n"/>
       <c r="Q826" s="1" t="inlineStr"/>
       <c r="R826" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!
-Cobramos a antiga contabilidade.</t>
+          <t>cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S826" s="1" t="inlineStr">
@@ -63318,16 +63332,16 @@
     </row>
     <row r="827">
       <c r="A827" s="1" t="n">
-        <v>82310</v>
+        <v>79865</v>
       </c>
       <c r="B827" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C827" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D827" s="1" t="inlineStr">
@@ -63337,15 +63351,15 @@
       </c>
       <c r="E827" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Por favor, solicitar ao antigo contador o balanço de abertura.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F827" s="1" t="n">
-        <v>6974</v>
+        <v>6278</v>
       </c>
       <c r="G827" s="1" t="inlineStr">
         <is>
-          <t>FRANCINALDO FERREIRA DE ANDRADE LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="H827" s="1" t="inlineStr">
@@ -63359,10 +63373,10 @@
         </is>
       </c>
       <c r="J827" s="2" t="n">
-        <v>46247.3783179051</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K827" s="2" t="n">
-        <v>46248</v>
+        <v>46185</v>
       </c>
       <c r="L827" s="1" t="inlineStr">
         <is>
@@ -63375,14 +63389,15 @@
         </is>
       </c>
       <c r="N827" s="2" t="n">
-        <v>46253.39089305556</v>
+        <v>46246.6616841088</v>
       </c>
       <c r="O827" s="1" t="n"/>
       <c r="P827" s="1" t="n"/>
       <c r="Q827" s="1" t="inlineStr"/>
       <c r="R827" s="1" t="inlineStr">
         <is>
-          <t>cobramos os documentos do antigo contador.</t>
+          <t>Bom dia!
+Já foi atendido?</t>
         </is>
       </c>
       <c r="S827" s="1" t="inlineStr">
@@ -63395,36 +63410,32 @@
     </row>
     <row r="828">
       <c r="A828" s="1" t="n">
-        <v>79865</v>
+        <v>82701</v>
       </c>
       <c r="B828" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C828" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D828" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E828" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde, por gentileza, providencias documentos de implantação da empresa: 7037 - EXPANDItens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F828" s="1" t="n">
-        <v>6278</v>
-      </c>
-      <c r="G828" s="1" t="inlineStr">
-        <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G828" s="1" t="n"/>
       <c r="H828" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -63436,10 +63447,10 @@
         </is>
       </c>
       <c r="J828" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46253.71124814815</v>
       </c>
       <c r="K828" s="2" t="n">
-        <v>46185</v>
+        <v>46255</v>
       </c>
       <c r="L828" s="1" t="inlineStr">
         <is>
@@ -63448,19 +63459,20 @@
       </c>
       <c r="M828" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="N828" s="2" t="n">
-        <v>46246.6616841088</v>
-      </c>
-      <c r="O828" s="1" t="n"/>
+        <v>46255.46909065972</v>
+      </c>
+      <c r="O828" s="2" t="n">
+        <v>46283</v>
+      </c>
       <c r="P828" s="1" t="n"/>
       <c r="Q828" s="1" t="inlineStr"/>
       <c r="R828" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!
-Já foi atendido?</t>
+          <t xml:space="preserve">CObramos os documentos </t>
         </is>
       </c>
       <c r="S828" s="1" t="inlineStr">
@@ -63473,36 +63485,32 @@
     </row>
     <row r="829">
       <c r="A829" s="1" t="n">
-        <v>79863</v>
+        <v>82706</v>
       </c>
       <c r="B829" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C829" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D829" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E829" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde, por gentileza, providenciar documentos de implantação da empresa: 6978 - HEPA FILTROS.Itens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F829" s="1" t="n">
-        <v>6404</v>
-      </c>
-      <c r="G829" s="1" t="inlineStr">
-        <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G829" s="1" t="n"/>
       <c r="H829" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -63514,10 +63522,10 @@
         </is>
       </c>
       <c r="J829" s="2" t="n">
-        <v>46183.6188202199</v>
+        <v>46253.72086076389</v>
       </c>
       <c r="K829" s="2" t="n">
-        <v>46185</v>
+        <v>46255</v>
       </c>
       <c r="L829" s="1" t="inlineStr">
         <is>
@@ -63526,19 +63534,18 @@
       </c>
       <c r="M829" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="N829" s="2" t="n">
-        <v>46246.66157939815</v>
+        <v>46255.48540517361</v>
       </c>
       <c r="O829" s="1" t="n"/>
       <c r="P829" s="1" t="n"/>
       <c r="Q829" s="1" t="inlineStr"/>
       <c r="R829" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!
-Já foi atendido?</t>
+          <t>cobramos os documentos.</t>
         </is>
       </c>
       <c r="S829" s="1" t="inlineStr">
@@ -63551,7 +63558,7 @@
     </row>
     <row r="830">
       <c r="A830" s="1" t="n">
-        <v>82701</v>
+        <v>81244</v>
       </c>
       <c r="B830" s="1" t="inlineStr">
         <is>
@@ -63570,7 +63577,7 @@
       </c>
       <c r="E830" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza, providencias documentos de implantação da empresa: 7037 - EXPANDItens dispensáveis, por gentileza, sinalizar.</t>
+          <t>6966 - HELBRAZ COMERCIO DE PAPELARIA LTDA6967 - JL DISTRIBUIDORA DE PAPELARIA LTDAPor gentileza, providenciar as documentações de implantação das empresas, anexo o checklist.</t>
         </is>
       </c>
       <c r="F830" s="1" t="n">
@@ -63579,7 +63586,7 @@
       <c r="G830" s="1" t="n"/>
       <c r="H830" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I830" s="1" t="inlineStr">
@@ -63588,10 +63595,10 @@
         </is>
       </c>
       <c r="J830" s="2" t="n">
-        <v>46253.71124814815</v>
+        <v>46224.42615887732</v>
       </c>
       <c r="K830" s="2" t="n">
-        <v>46255</v>
+        <v>46226</v>
       </c>
       <c r="L830" s="1" t="inlineStr">
         <is>
@@ -63600,11 +63607,11 @@
       </c>
       <c r="M830" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="N830" s="2" t="n">
-        <v>46255.46909065972</v>
+        <v>46225.4986497338</v>
       </c>
       <c r="O830" s="2" t="n">
         <v>46283</v>
@@ -63613,7 +63620,7 @@
       <c r="Q830" s="1" t="inlineStr"/>
       <c r="R830" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CObramos os documentos </t>
+          <t xml:space="preserve">Aguardando contato do contador. </t>
         </is>
       </c>
       <c r="S830" s="1" t="inlineStr">
@@ -63626,7 +63633,7 @@
     </row>
     <row r="831">
       <c r="A831" s="1" t="n">
-        <v>82706</v>
+        <v>81055</v>
       </c>
       <c r="B831" s="1" t="inlineStr">
         <is>
@@ -63645,7 +63652,7 @@
       </c>
       <c r="E831" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza, providenciar documentos de implantação da empresa: 6978 - HEPA FILTROS.Itens dispensáveis, por gentileza, sinalizar.</t>
+          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
         </is>
       </c>
       <c r="F831" s="1" t="n">
@@ -63663,10 +63670,10 @@
         </is>
       </c>
       <c r="J831" s="2" t="n">
-        <v>46253.72086076389</v>
+        <v>46218.40379614583</v>
       </c>
       <c r="K831" s="2" t="n">
-        <v>46255</v>
+        <v>46219</v>
       </c>
       <c r="L831" s="1" t="inlineStr">
         <is>
@@ -63675,18 +63682,20 @@
       </c>
       <c r="M831" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="N831" s="2" t="n">
-        <v>46255.48540517361</v>
-      </c>
-      <c r="O831" s="1" t="n"/>
+        <v>46219.50607847222</v>
+      </c>
+      <c r="O831" s="2" t="n">
+        <v>46283</v>
+      </c>
       <c r="P831" s="1" t="n"/>
       <c r="Q831" s="1" t="inlineStr"/>
       <c r="R831" s="1" t="inlineStr">
         <is>
-          <t>cobramos os documentos.</t>
+          <t>Aguardando retorno dos dados do contador</t>
         </is>
       </c>
       <c r="S831" s="1" t="inlineStr">
@@ -63696,156 +63705,6 @@
       </c>
       <c r="T831" s="1" t="n"/>
       <c r="U831" s="1" t="inlineStr"/>
-    </row>
-    <row r="832">
-      <c r="A832" s="1" t="n">
-        <v>81244</v>
-      </c>
-      <c r="B832" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C832" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D832" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E832" s="1" t="inlineStr">
-        <is>
-          <t>6966 - HELBRAZ COMERCIO DE PAPELARIA LTDA6967 - JL DISTRIBUIDORA DE PAPELARIA LTDAPor gentileza, providenciar as documentações de implantação das empresas, anexo o checklist.</t>
-        </is>
-      </c>
-      <c r="F832" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G832" s="1" t="n"/>
-      <c r="H832" s="1" t="inlineStr">
-        <is>
-          <t>Karina Dantas</t>
-        </is>
-      </c>
-      <c r="I832" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="J832" s="2" t="n">
-        <v>46224.42615887732</v>
-      </c>
-      <c r="K832" s="2" t="n">
-        <v>46226</v>
-      </c>
-      <c r="L832" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M832" s="1" t="inlineStr">
-        <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
-      <c r="N832" s="2" t="n">
-        <v>46225.4986497338</v>
-      </c>
-      <c r="O832" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="P832" s="1" t="n"/>
-      <c r="Q832" s="1" t="inlineStr"/>
-      <c r="R832" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aguardando contato do contador. </t>
-        </is>
-      </c>
-      <c r="S832" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T832" s="1" t="n"/>
-      <c r="U832" s="1" t="inlineStr"/>
-    </row>
-    <row r="833">
-      <c r="A833" s="1" t="n">
-        <v>81055</v>
-      </c>
-      <c r="B833" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C833" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D833" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E833" s="1" t="inlineStr">
-        <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
-        </is>
-      </c>
-      <c r="F833" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G833" s="1" t="n"/>
-      <c r="H833" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="I833" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="J833" s="2" t="n">
-        <v>46218.40379614583</v>
-      </c>
-      <c r="K833" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="L833" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M833" s="1" t="inlineStr">
-        <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
-      <c r="N833" s="2" t="n">
-        <v>46219.50607847222</v>
-      </c>
-      <c r="O833" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="P833" s="1" t="n"/>
-      <c r="Q833" s="1" t="inlineStr"/>
-      <c r="R833" s="1" t="inlineStr">
-        <is>
-          <t>Aguardando retorno dos dados do contador</t>
-        </is>
-      </c>
-      <c r="S833" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T833" s="1" t="n"/>
-      <c r="U833" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -51865,7 +51865,7 @@
       </c>
       <c r="L678" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M678" s="1" t="inlineStr">
@@ -51873,11 +51873,17 @@
           <t>Yasmin Peixoto</t>
         </is>
       </c>
-      <c r="N678" s="1" t="n"/>
+      <c r="N678" s="2" t="n">
+        <v>46281.75651021991</v>
+      </c>
       <c r="O678" s="1" t="n"/>
       <c r="P678" s="1" t="n"/>
       <c r="Q678" s="1" t="inlineStr"/>
-      <c r="R678" s="1" t="inlineStr"/>
+      <c r="R678" s="1" t="inlineStr">
+        <is>
+          <t>Certidão/Levantamento solicitado, aguardando retorno.</t>
+        </is>
+      </c>
       <c r="S678" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -52242,7 +52248,7 @@
       </c>
       <c r="L683" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M683" s="1" t="inlineStr">
@@ -52252,12 +52258,22 @@
       </c>
       <c r="N683" s="1" t="n"/>
       <c r="O683" s="1" t="n"/>
-      <c r="P683" s="1" t="n"/>
-      <c r="Q683" s="1" t="inlineStr"/>
-      <c r="R683" s="1" t="inlineStr"/>
+      <c r="P683" s="2" t="n">
+        <v>46281.76203364583</v>
+      </c>
+      <c r="Q683" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R683" s="1" t="inlineStr">
+        <is>
+          <t>Empresa não possui inscrição municipal.</t>
+        </is>
+      </c>
       <c r="S683" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T683" s="1" t="n"/>
@@ -59473,7 +59489,7 @@
       </c>
       <c r="L776" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M776" s="1" t="inlineStr">
@@ -59483,12 +59499,27 @@
       </c>
       <c r="N776" s="1" t="n"/>
       <c r="O776" s="1" t="n"/>
-      <c r="P776" s="1" t="n"/>
-      <c r="Q776" s="1" t="inlineStr"/>
-      <c r="R776" s="1" t="inlineStr"/>
+      <c r="P776" s="2" t="n">
+        <v>46281.75655381945</v>
+      </c>
+      <c r="Q776" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R776" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ricardo, boa tarde!
+Realizei as simulações considerando as opções atualmente disponíveis para adesão. Como a PGFN estabeleceu limites para os valores que podem ser incluídos em cada modalidade de transação, foi necessário realizar as simulações separadamente, de acordo com cada opção disponível.
+Encaminho as simulações em anexo para sua análise, contemplando os cenários com o número mínimo e máximo de parcelas permitido em cada modalidade.
+É importante destacar que o cliente já possui algumas transações em andamento. Entre elas, há uma transação referente aos débitos do Simples Nacional, atualmente parcelada em 145 parcelas. Essa condição, porém, não está mais disponível para novas adesões neste momento, uma vez que o limite atual para essa modalidade é de 60 parcelas.
+Dessa forma, as simulações anexas demonstram as condições que podem ser obtidas atualmente, permitindo uma comparação com as transações que o cliente já possui e a avaliação do cenário mais adequado.
+</t>
+        </is>
+      </c>
       <c r="S776" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T776" s="1" t="n"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U845" headerRowCount="1">
-  <autoFilter ref="A1:U845"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U842" headerRowCount="1">
+  <autoFilter ref="A1:U842"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U845"/>
+  <dimension ref="A1:U842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -60278,7 +60278,7 @@
       </c>
       <c r="L782" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M782" s="1" t="inlineStr">
@@ -60288,12 +60288,23 @@
       </c>
       <c r="N782" s="1" t="n"/>
       <c r="O782" s="1" t="n"/>
-      <c r="P782" s="1" t="n"/>
-      <c r="Q782" s="1" t="inlineStr"/>
-      <c r="R782" s="1" t="inlineStr"/>
+      <c r="P782" s="2" t="n">
+        <v>46287.39302276621</v>
+      </c>
+      <c r="Q782" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R782" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bom dia!
+Segue simulado e proposta. </t>
+        </is>
+      </c>
       <c r="S782" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T782" s="1" t="n"/>
@@ -61071,39 +61082,39 @@
     </row>
     <row r="793">
       <c r="A793" s="1" t="n">
-        <v>83897</v>
+        <v>83642</v>
       </c>
       <c r="B793" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Notificação</t>
         </is>
       </c>
       <c r="C793" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D793" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E793" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Cliente recebeu notificação CRC, prazo de 15 dias de retorno.</t>
         </is>
       </c>
       <c r="F793" s="1" t="n">
-        <v>6973</v>
+        <v>6588</v>
       </c>
       <c r="G793" s="1" t="inlineStr">
         <is>
-          <t>SINDIFY TECNOLOGIA LTDA</t>
+          <t>ALM GESTAO TECH RETAIL LTDA</t>
         </is>
       </c>
       <c r="H793" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I793" s="1" t="inlineStr">
@@ -61112,10 +61123,10 @@
         </is>
       </c>
       <c r="J793" s="2" t="n">
-        <v>46279.39057037037</v>
+        <v>46273.44699390046</v>
       </c>
       <c r="K793" s="2" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="L793" s="1" t="inlineStr">
         <is>
@@ -61124,7 +61135,7 @@
       </c>
       <c r="M793" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
+          <t>Romero Borges</t>
         </is>
       </c>
       <c r="N793" s="1" t="n"/>
@@ -61142,39 +61153,39 @@
     </row>
     <row r="794">
       <c r="A794" s="1" t="n">
-        <v>83642</v>
+        <v>84129</v>
       </c>
       <c r="B794" s="1" t="inlineStr">
         <is>
-          <t>Notificação</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C794" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D794" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E794" s="1" t="inlineStr">
         <is>
-          <t>Cliente recebeu notificação CRC, prazo de 15 dias de retorno.</t>
+          <t>Por gentileza poderia me informar o login e a senha da prefeitura.</t>
         </is>
       </c>
       <c r="F794" s="1" t="n">
-        <v>6588</v>
+        <v>6608</v>
       </c>
       <c r="G794" s="1" t="inlineStr">
         <is>
-          <t>ALM GESTAO TECH RETAIL LTDA</t>
+          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 4)</t>
         </is>
       </c>
       <c r="H794" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Talita Silva</t>
         </is>
       </c>
       <c r="I794" s="1" t="inlineStr">
@@ -61183,10 +61194,10 @@
         </is>
       </c>
       <c r="J794" s="2" t="n">
-        <v>46273.44699390046</v>
+        <v>46282.74585570602</v>
       </c>
       <c r="K794" s="2" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="L794" s="1" t="inlineStr">
         <is>
@@ -61195,7 +61206,7 @@
       </c>
       <c r="M794" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
+          <t>Rafaella Macedo</t>
         </is>
       </c>
       <c r="N794" s="1" t="n"/>
@@ -61213,11 +61224,11 @@
     </row>
     <row r="795">
       <c r="A795" s="1" t="n">
-        <v>84129</v>
+        <v>82264</v>
       </c>
       <c r="B795" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C795" s="1" t="inlineStr">
@@ -61227,25 +61238,25 @@
       </c>
       <c r="D795" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E795" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza poderia me informar o login e a senha da prefeitura.</t>
+          <t>Por gentileza enviar a guia atualizada da TFEdas duas empresas do grupo BOMBEIROS 6621 E 6622</t>
         </is>
       </c>
       <c r="F795" s="1" t="n">
-        <v>6608</v>
+        <v>6621</v>
       </c>
       <c r="G795" s="1" t="inlineStr">
         <is>
-          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 4)</t>
+          <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
         </is>
       </c>
       <c r="H795" s="1" t="inlineStr">
         <is>
-          <t>Talita Silva</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I795" s="1" t="inlineStr">
@@ -61254,29 +61265,40 @@
         </is>
       </c>
       <c r="J795" s="2" t="n">
-        <v>46282.74585570602</v>
+        <v>46246.3872690162</v>
       </c>
       <c r="K795" s="2" t="n">
-        <v>46286</v>
+        <v>46248</v>
       </c>
       <c r="L795" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M795" s="1" t="inlineStr">
         <is>
-          <t>Rafaella Macedo</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N795" s="1" t="n"/>
       <c r="O795" s="1" t="n"/>
-      <c r="P795" s="1" t="n"/>
-      <c r="Q795" s="1" t="inlineStr"/>
-      <c r="R795" s="1" t="inlineStr"/>
+      <c r="P795" s="2" t="n">
+        <v>46246.66841165509</v>
+      </c>
+      <c r="Q795" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R795" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boa tarde!
+Não há débitos em aberto, seguem certidões. </t>
+        </is>
+      </c>
       <c r="S795" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T795" s="1" t="n"/>
@@ -61284,39 +61306,39 @@
     </row>
     <row r="796">
       <c r="A796" s="1" t="n">
-        <v>82264</v>
+        <v>82915</v>
       </c>
       <c r="B796" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C796" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D796" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E796" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza enviar a guia atualizada da TFEdas duas empresas do grupo BOMBEIROS 6621 E 6622</t>
+          <t>Alteração contratual do CAPITAL SOCIAL, QSA, ADMINISTRADOR e ATIVIDADE/CNAE da empresa 6628-TSN TECHNICAL SERVICE NETWORK LTDAGrupo: GTG1- Alteração de Sócio:Saida da Sra. MARIA BARBOSA DOS SANTOS CLEMENTE, que sede e tranfere o total das cotas para o Sr. ALISSON BARBOSA DE SOUSA 2- Aumento do capital:será aumentado de 150.000, para 300.000, sendo a integralização de 50.000, através do registro de um carro, e o restante (100.000), a integralizar em 12 parcelas.3- Alteração de CNAEs, seram removidos  4 e temos e incluir 6, conforme abaixo:CNAEs RETIRAR: (OK)•	23.41-9-00 - Fabricação de produtos cerâmicos refratários •	61.10-8-01 - Serviços de telefonia fixa comutada - STFC •	61.10-8-03 - Serviços de comunicação multimídia - SCM•	62.02-3-00 - Desenvolvimento e licenciamento de programas de computador customizáveisINCLUIR: (OK)•	4686-9/02 — Comércio atacadista de embalagens;•	4789-0/99 — Comércio varejista de outros produtos não especificados anteriormente;•	4744-0/03 — Comércio varejista de materiais hidráulicos;•	4679-6/04 — Comércio atacadista especializado de materiais de construção não especificados anteriormente;•	4673-7/00 — Comércio atacadista de material elétrico.•	86.60-7-00 - Atividades de apoio à gestão de saúde</t>
         </is>
       </c>
       <c r="F796" s="1" t="n">
-        <v>6621</v>
+        <v>6628</v>
       </c>
       <c r="G796" s="1" t="inlineStr">
         <is>
-          <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="H796" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I796" s="1" t="inlineStr">
@@ -61325,119 +61347,120 @@
         </is>
       </c>
       <c r="J796" s="2" t="n">
-        <v>46246.3872690162</v>
+        <v>46258.70282021991</v>
       </c>
       <c r="K796" s="2" t="n">
-        <v>46248</v>
+        <v>46286</v>
       </c>
       <c r="L796" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M796" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N796" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N796" s="2" t="n">
+        <v>46261.63173943287</v>
+      </c>
       <c r="O796" s="1" t="n"/>
-      <c r="P796" s="2" t="n">
-        <v>46246.66841165509</v>
-      </c>
-      <c r="Q796" s="1" t="inlineStr">
-        <is>
-          <t>Karina Dantas</t>
-        </is>
-      </c>
+      <c r="P796" s="1" t="n"/>
+      <c r="Q796" s="1" t="inlineStr"/>
       <c r="R796" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Boa tarde!
-Não há débitos em aberto, seguem certidões. </t>
-        </is>
-      </c>
-      <c r="S796" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T796" s="1" t="n"/>
-      <c r="U796" s="1" t="inlineStr"/>
-    </row>
-    <row r="797">
-      <c r="A797" s="1" t="n">
-        <v>82915</v>
-      </c>
-      <c r="B797" s="1" t="inlineStr">
-        <is>
-          <t>Alteração Contratual</t>
-        </is>
-      </c>
-      <c r="C797" s="1" t="inlineStr">
-        <is>
-          <t>Sócios</t>
-        </is>
-      </c>
-      <c r="D797" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E797" s="1" t="inlineStr">
-        <is>
-          <t>Alteração contratual do CAPITAL SOCIAL, QSA, ADMINISTRADOR e ATIVIDADE/CNAE da empresa 6628-TSN TECHNICAL SERVICE NETWORK LTDAGrupo: GTG1- Alteração de Sócio:Saida da Sra. MARIA BARBOSA DOS SANTOS CLEMENTE, que sede e tranfere o total das cotas para o Sr. ALISSON BARBOSA DE SOUSA 2- Aumento do capital:será aumentado de 150.000, para 300.000, sendo a integralização de 50.000, através do registro de um carro, e o restante (100.000), a integralizar em 12 parcelas.3- Alteração de CNAEs, seram removidos  4 e temos e incluir 6, conforme abaixo:CNAEs RETIRAR: (OK)•	23.41-9-00 - Fabricação de produtos cerâmicos refratários •	61.10-8-01 - Serviços de telefonia fixa comutada - STFC •	61.10-8-03 - Serviços de comunicação multimídia - SCM•	62.02-3-00 - Desenvolvimento e licenciamento de programas de computador customizáveisINCLUIR: (OK)•	4686-9/02 — Comércio atacadista de embalagens;•	4789-0/99 — Comércio varejista de outros produtos não especificados anteriormente;•	4744-0/03 — Comércio varejista de materiais hidráulicos;•	4679-6/04 — Comércio atacadista especializado de materiais de construção não especificados anteriormente;•	4673-7/00 — Comércio atacadista de material elétrico.•	86.60-7-00 - Atividades de apoio à gestão de saúde</t>
-        </is>
-      </c>
-      <c r="F797" s="1" t="n">
-        <v>6628</v>
-      </c>
-      <c r="G797" s="1" t="inlineStr">
-        <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
-        </is>
-      </c>
-      <c r="H797" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
-      <c r="I797" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J797" s="2" t="n">
-        <v>46258.70282021991</v>
-      </c>
-      <c r="K797" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="L797" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M797" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N797" s="2" t="n">
-        <v>46261.63173943287</v>
-      </c>
-      <c r="O797" s="1" t="n"/>
-      <c r="P797" s="1" t="n"/>
-      <c r="Q797" s="1" t="inlineStr"/>
-      <c r="R797" s="1" t="inlineStr">
         <is>
           <t>Prezados(as), boa tarde!
 Conforme solicitado, alteração contratual em andamento. 
 Atenciosamente,</t>
         </is>
       </c>
+      <c r="S796" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T796" s="1" t="n"/>
+      <c r="U796" s="1" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>84101</v>
+      </c>
+      <c r="B797" s="1" t="inlineStr">
+        <is>
+          <t>Parcelamento PGFN</t>
+        </is>
+      </c>
+      <c r="C797" s="1" t="inlineStr">
+        <is>
+          <t>Simples Nacional</t>
+        </is>
+      </c>
+      <c r="D797" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E797" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia! Por gentileza, poderiam emitir uma guia atualizada</t>
+        </is>
+      </c>
+      <c r="F797" s="1" t="n">
+        <v>6650</v>
+      </c>
+      <c r="G797" s="1" t="inlineStr">
+        <is>
+          <t>ACJ COMERCIO DE EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="H797" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="I797" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J797" s="2" t="n">
+        <v>46282.47985864583</v>
+      </c>
+      <c r="K797" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="L797" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M797" s="1" t="inlineStr">
+        <is>
+          <t>Sofia Souza</t>
+        </is>
+      </c>
+      <c r="N797" s="1" t="n"/>
+      <c r="O797" s="1" t="n"/>
+      <c r="P797" s="2" t="n">
+        <v>46283.70308052083</v>
+      </c>
+      <c r="Q797" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R797" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde!
+Qual parcela que voce deseja que seja emitida?
+Simples Nacional ou PGFN Simples Nacional?</t>
+        </is>
+      </c>
       <c r="S797" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T797" s="1" t="n"/>
@@ -61445,16 +61468,16 @@
     </row>
     <row r="798">
       <c r="A798" s="1" t="n">
-        <v>84101</v>
+        <v>81317</v>
       </c>
       <c r="B798" s="1" t="inlineStr">
         <is>
-          <t>Parcelamento PGFN</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C798" s="1" t="inlineStr">
         <is>
-          <t>Simples Nacional</t>
+          <t xml:space="preserve">Inclusão de Ata </t>
         </is>
       </c>
       <c r="D798" s="1" t="inlineStr">
@@ -61464,20 +61487,20 @@
       </c>
       <c r="E798" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, poderiam emitir uma guia atualizada</t>
+          <t>6673 – CHER SOLUÇÕESAlteração contratual na empresa CHER tirando a Juliana“Necessário realizar a alteração contratual tirando a JULIANA do quadro societário e a sócia remanescente ficará com 100% das cotas da empresa. Enviar a relação de documentos necessários.”</t>
         </is>
       </c>
       <c r="F798" s="1" t="n">
-        <v>6650</v>
+        <v>6673</v>
       </c>
       <c r="G798" s="1" t="inlineStr">
         <is>
-          <t>ACJ COMERCIO DE EMBALAGENS LTDA</t>
+          <t>CHER SOLUÇÕES COMERCIAIS LTDA</t>
         </is>
       </c>
       <c r="H798" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I798" s="1" t="inlineStr">
@@ -61486,10 +61509,10 @@
         </is>
       </c>
       <c r="J798" s="2" t="n">
-        <v>46282.47985864583</v>
+        <v>46225.61752997685</v>
       </c>
       <c r="K798" s="2" t="n">
-        <v>46286</v>
+        <v>46231</v>
       </c>
       <c r="L798" s="1" t="inlineStr">
         <is>
@@ -61498,24 +61521,22 @@
       </c>
       <c r="M798" s="1" t="inlineStr">
         <is>
-          <t>Sofia Souza</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="N798" s="1" t="n"/>
       <c r="O798" s="1" t="n"/>
       <c r="P798" s="2" t="n">
-        <v>46283.70308052083</v>
+        <v>46230.66237318287</v>
       </c>
       <c r="Q798" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="R798" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!
-Qual parcela que voce deseja que seja emitida?
-Simples Nacional ou PGFN Simples Nacional?</t>
+          <t>Enviar a planilha devidamente preechida (com todas as informações).</t>
         </is>
       </c>
       <c r="S798" s="1" t="inlineStr">
@@ -61528,7 +61549,7 @@
     </row>
     <row r="799">
       <c r="A799" s="1" t="n">
-        <v>81317</v>
+        <v>81316</v>
       </c>
       <c r="B799" s="1" t="inlineStr">
         <is>
@@ -61547,15 +61568,15 @@
       </c>
       <c r="E799" s="1" t="inlineStr">
         <is>
-          <t>6673 – CHER SOLUÇÕESAlteração contratual na empresa CHER tirando a Juliana“Necessário realizar a alteração contratual tirando a JULIANA do quadro societário e a sócia remanescente ficará com 100% das cotas da empresa. Enviar a relação de documentos necessários.”</t>
+          <t>6674 – HORTIFRUTI CENTRALAlteração contratual incluindo o CPF dos sócios da Nippo com o Fernando“No Hortifruti vai receber os sócios da Nippo. Fazer essa alteração contratual. Vamos aguardar o cliente definir as participações societárias na empresa. Enviar relação de documentos.”</t>
         </is>
       </c>
       <c r="F799" s="1" t="n">
-        <v>6673</v>
+        <v>6674</v>
       </c>
       <c r="G799" s="1" t="inlineStr">
         <is>
-          <t>CHER SOLUÇÕES COMERCIAIS LTDA</t>
+          <t>HORTIFRUTI CENTRAL DO COIMBRA LTDA</t>
         </is>
       </c>
       <c r="H799" s="1" t="inlineStr">
@@ -61569,7 +61590,7 @@
         </is>
       </c>
       <c r="J799" s="2" t="n">
-        <v>46225.61752997685</v>
+        <v>46225.61705821759</v>
       </c>
       <c r="K799" s="2" t="n">
         <v>46231</v>
@@ -61587,7 +61608,7 @@
       <c r="N799" s="1" t="n"/>
       <c r="O799" s="1" t="n"/>
       <c r="P799" s="2" t="n">
-        <v>46230.66237318287</v>
+        <v>46230.66303518519</v>
       </c>
       <c r="Q799" s="1" t="inlineStr">
         <is>
@@ -61596,7 +61617,7 @@
       </c>
       <c r="R799" s="1" t="inlineStr">
         <is>
-          <t>Enviar a planilha devidamente preechida (com todas as informações).</t>
+          <t>Enviar a planilha devidamente preenchida e completa.</t>
         </is>
       </c>
       <c r="S799" s="1" t="inlineStr">
@@ -61609,39 +61630,39 @@
     </row>
     <row r="800">
       <c r="A800" s="1" t="n">
-        <v>81316</v>
+        <v>81987</v>
       </c>
       <c r="B800" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C800" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inclusão de Ata </t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="D800" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E800" s="1" t="inlineStr">
         <is>
-          <t>6674 – HORTIFRUTI CENTRALAlteração contratual incluindo o CPF dos sócios da Nippo com o Fernando“No Hortifruti vai receber os sócios da Nippo. Fazer essa alteração contratual. Vamos aguardar o cliente definir as participações societárias na empresa. Enviar relação de documentos.”</t>
+          <t>6977 - PROTECTION SHIELD - MUDANÇAS NO CONTRATO SOCIALO Cliente precisa mudar o CNAI e incluir um sócio, poderia nos informar qual o honorário e quais documento você precisa?Desejo do cliente é fazer a transferência dos funcionário que estão hoje na 6976, para 6977, para isto é necessário haver a equiparação de atividades para não ter problemas Sindicais, então será necessita mudanças no CNAE, e para haver formação de grupo econômico a sócia deseja ter 1% de participação na 6977, hoje ela  da sociedade apenas como tutora do socio de menor, e como administradora.  Mais informações com o REYNALDO.Att.Vander</t>
         </is>
       </c>
       <c r="F800" s="1" t="n">
-        <v>6674</v>
+        <v>6977</v>
       </c>
       <c r="G800" s="1" t="inlineStr">
         <is>
-          <t>HORTIFRUTI CENTRAL DO COIMBRA LTDA</t>
+          <t>PROTECTION SHIELD LTDA</t>
         </is>
       </c>
       <c r="H800" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I800" s="1" t="inlineStr">
@@ -61650,39 +61671,35 @@
         </is>
       </c>
       <c r="J800" s="2" t="n">
-        <v>46225.61705821759</v>
+        <v>46240.55237392361</v>
       </c>
       <c r="K800" s="2" t="n">
-        <v>46231</v>
+        <v>46241</v>
       </c>
       <c r="L800" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M800" s="1" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
-        </is>
-      </c>
-      <c r="N800" s="1" t="n"/>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="N800" s="2" t="n">
+        <v>46268.68733116899</v>
+      </c>
       <c r="O800" s="1" t="n"/>
-      <c r="P800" s="2" t="n">
-        <v>46230.66303518519</v>
-      </c>
-      <c r="Q800" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="P800" s="1" t="n"/>
+      <c r="Q800" s="1" t="inlineStr"/>
       <c r="R800" s="1" t="inlineStr">
         <is>
-          <t>Enviar a planilha devidamente preenchida e completa.</t>
+          <t>Favor, informar o que vai ser alterado de fato.</t>
         </is>
       </c>
       <c r="S800" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T800" s="1" t="n"/>
@@ -61690,7 +61707,7 @@
     </row>
     <row r="801">
       <c r="A801" s="1" t="n">
-        <v>81987</v>
+        <v>82091</v>
       </c>
       <c r="B801" s="1" t="inlineStr">
         <is>
@@ -61699,17 +61716,17 @@
       </c>
       <c r="C801" s="1" t="inlineStr">
         <is>
-          <t>Geral</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D801" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E801" s="1" t="inlineStr">
         <is>
-          <t>6977 - PROTECTION SHIELD - MUDANÇAS NO CONTRATO SOCIALO Cliente precisa mudar o CNAI e incluir um sócio, poderia nos informar qual o honorário e quais documento você precisa?Desejo do cliente é fazer a transferência dos funcionário que estão hoje na 6976, para 6977, para isto é necessário haver a equiparação de atividades para não ter problemas Sindicais, então será necessita mudanças no CNAE, e para haver formação de grupo econômico a sócia deseja ter 1% de participação na 6977, hoje ela  da sociedade apenas como tutora do socio de menor, e como administradora.  Mais informações com o REYNALDO.Att.Vander</t>
+          <t>ALTERAÇÃO CONTRATUAL NA EMPRESA 6977-PROTECTION SHIELD LTDAGRUPO: FILM FACILALTERAÇÃO DE ATIVIDADE E QSAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$1.500,00EMPRESA DE ESTRATEGIA PARA FUNCIONARIOS, APÓS A TRANSFERRENCIA DOS FUNCIONÁRIOS, VOLTAR QUADRO SOCIETARIO ANTIGO</t>
         </is>
       </c>
       <c r="F801" s="1" t="n">
@@ -61731,10 +61748,10 @@
         </is>
       </c>
       <c r="J801" s="2" t="n">
-        <v>46240.55237392361</v>
+        <v>46241.64981377315</v>
       </c>
       <c r="K801" s="2" t="n">
-        <v>46241</v>
+        <v>46269</v>
       </c>
       <c r="L801" s="1" t="inlineStr">
         <is>
@@ -61743,18 +61760,18 @@
       </c>
       <c r="M801" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N801" s="2" t="n">
-        <v>46268.68733116899</v>
+        <v>46268.68579398148</v>
       </c>
       <c r="O801" s="1" t="n"/>
       <c r="P801" s="1" t="n"/>
       <c r="Q801" s="1" t="inlineStr"/>
       <c r="R801" s="1" t="inlineStr">
         <is>
-          <t>Favor, informar o que vai ser alterado de fato.</t>
+          <t>Raisa, a empresa  6977 já possui o quadro de sócios exatamente como consta na planilha, não tem o que ser alterado.</t>
         </is>
       </c>
       <c r="S801" s="1" t="inlineStr">
@@ -61767,26 +61784,26 @@
     </row>
     <row r="802">
       <c r="A802" s="1" t="n">
-        <v>82091</v>
+        <v>83899</v>
       </c>
       <c r="B802" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C802" s="1" t="inlineStr">
         <is>
-          <t>Sócios</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D802" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E802" s="1" t="inlineStr">
         <is>
-          <t>ALTERAÇÃO CONTRATUAL NA EMPRESA 6977-PROTECTION SHIELD LTDAGRUPO: FILM FACILALTERAÇÃO DE ATIVIDADE E QSAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$1.500,00EMPRESA DE ESTRATEGIA PARA FUNCIONARIOS, APÓS A TRANSFERRENCIA DOS FUNCIONÁRIOS, VOLTAR QUADRO SOCIETARIO ANTIGO</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F802" s="1" t="n">
@@ -61799,7 +61816,7 @@
       </c>
       <c r="H802" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I802" s="1" t="inlineStr">
@@ -61808,32 +61825,26 @@
         </is>
       </c>
       <c r="J802" s="2" t="n">
-        <v>46241.64981377315</v>
+        <v>46279.39114621528</v>
       </c>
       <c r="K802" s="2" t="n">
-        <v>46269</v>
+        <v>46281</v>
       </c>
       <c r="L802" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M802" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N802" s="2" t="n">
-        <v>46268.68579398148</v>
-      </c>
+          <t>Ney Barbosa</t>
+        </is>
+      </c>
+      <c r="N802" s="1" t="n"/>
       <c r="O802" s="1" t="n"/>
       <c r="P802" s="1" t="n"/>
       <c r="Q802" s="1" t="inlineStr"/>
-      <c r="R802" s="1" t="inlineStr">
-        <is>
-          <t>Raisa, a empresa  6977 já possui o quadro de sócios exatamente como consta na planilha, não tem o que ser alterado.</t>
-        </is>
-      </c>
+      <c r="R802" s="1" t="inlineStr"/>
       <c r="S802" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -61844,39 +61855,39 @@
     </row>
     <row r="803">
       <c r="A803" s="1" t="n">
-        <v>83899</v>
+        <v>81753</v>
       </c>
       <c r="B803" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C803" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D803" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E803" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>ABERTURA DE EMPRESA - 6981-LUIZ GOMES DA SILVA - O GOIANOGRUPO: SUPERMERCADO AVENIDATRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIO FINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.500,00EMPRESA DE ESTRATÉGIA, APÓS CONSTITUIDA MIGRAR OS FUNCIONARIOS. APÓS TERMINO DA MIGRAÇÃO ALTERAR ATIVIDADE E QUADRO SOCIETÁRIO.</t>
         </is>
       </c>
       <c r="F803" s="1" t="n">
-        <v>6977</v>
+        <v>6981</v>
       </c>
       <c r="G803" s="1" t="inlineStr">
         <is>
-          <t>PROTECTION SHIELD LTDA</t>
+          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
         </is>
       </c>
       <c r="H803" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I803" s="1" t="inlineStr">
@@ -61885,26 +61896,34 @@
         </is>
       </c>
       <c r="J803" s="2" t="n">
-        <v>46279.39114621528</v>
+        <v>46237.51070853009</v>
       </c>
       <c r="K803" s="2" t="n">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="L803" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M803" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N803" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N803" s="2" t="n">
+        <v>46246.66714818287</v>
+      </c>
       <c r="O803" s="1" t="n"/>
       <c r="P803" s="1" t="n"/>
       <c r="Q803" s="1" t="inlineStr"/>
-      <c r="R803" s="1" t="inlineStr"/>
+      <c r="R803" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prezados(as), boa tarde!
+Processo de abertura em andamento. 
+Atenciosamente, </t>
+        </is>
+      </c>
       <c r="S803" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -61915,39 +61934,39 @@
     </row>
     <row r="804">
       <c r="A804" s="1" t="n">
-        <v>81753</v>
+        <v>83634</v>
       </c>
       <c r="B804" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C804" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Comércio</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D804" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E804" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA - 6981-LUIZ GOMES DA SILVA - O GOIANOGRUPO: SUPERMERCADO AVENIDATRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIO FINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.500,00EMPRESA DE ESTRATÉGIA, APÓS CONSTITUIDA MIGRAR OS FUNCIONARIOS. APÓS TERMINO DA MIGRAÇÃO ALTERAR ATIVIDADE E QUADRO SOCIETÁRIO.</t>
+          <t>6984 – SUPERMERCADOS BANDEIRA LTDA - senha DA PREFEITURA DE ITAPECERICA DA SERRA - PARA DECLARAR ISS NA PREFEITURA</t>
         </is>
       </c>
       <c r="F804" s="1" t="n">
-        <v>6981</v>
+        <v>6984</v>
       </c>
       <c r="G804" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
+          <t xml:space="preserve"> SUPERMERCADOS BANDEIRA LTDA.</t>
         </is>
       </c>
       <c r="H804" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I804" s="1" t="inlineStr">
@@ -61956,10 +61975,10 @@
         </is>
       </c>
       <c r="J804" s="2" t="n">
-        <v>46237.51070853009</v>
+        <v>46273.39513472222</v>
       </c>
       <c r="K804" s="2" t="n">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="L804" s="1" t="inlineStr">
         <is>
@@ -61968,20 +61987,18 @@
       </c>
       <c r="M804" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="N804" s="2" t="n">
-        <v>46246.66714818287</v>
+        <v>46274.49502619213</v>
       </c>
       <c r="O804" s="1" t="n"/>
       <c r="P804" s="1" t="n"/>
       <c r="Q804" s="1" t="inlineStr"/>
       <c r="R804" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados(as), boa tarde!
-Processo de abertura em andamento. 
-Atenciosamente, </t>
+          <t>Cobramos novamente o antigo contador</t>
         </is>
       </c>
       <c r="S804" s="1" t="inlineStr">
@@ -61994,39 +62011,39 @@
     </row>
     <row r="805">
       <c r="A805" s="1" t="n">
-        <v>83634</v>
+        <v>81933</v>
       </c>
       <c r="B805" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C805" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D805" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E805" s="1" t="inlineStr">
         <is>
-          <t>6984 – SUPERMERCADOS BANDEIRA LTDA - senha DA PREFEITURA DE ITAPECERICA DA SERRA - PARA DECLARAR ISS NA PREFEITURA</t>
+          <t>Por gentileza, providenciar:6990 - RC MATERIAIS ELETRICOS E HIDRAULICOS (MATRIZ) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL6991 - RC MATERIAIS ELETRICOS E HIDRAULICOS (FILIAL 1) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL</t>
         </is>
       </c>
       <c r="F805" s="1" t="n">
-        <v>6984</v>
+        <v>6990</v>
       </c>
       <c r="G805" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SUPERMERCADOS BANDEIRA LTDA.</t>
+          <t>AMANCIO S ELETRICA, HIDRAULICA E CONSTRUCAO EM GERAL LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H805" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I805" s="1" t="inlineStr">
@@ -62035,35 +62052,39 @@
         </is>
       </c>
       <c r="J805" s="2" t="n">
-        <v>46273.39513472222</v>
+        <v>46239.72520292824</v>
       </c>
       <c r="K805" s="2" t="n">
-        <v>46275</v>
+        <v>46241</v>
       </c>
       <c r="L805" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M805" s="1" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
-        </is>
-      </c>
-      <c r="N805" s="2" t="n">
-        <v>46274.49502619213</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N805" s="1" t="n"/>
       <c r="O805" s="1" t="n"/>
-      <c r="P805" s="1" t="n"/>
-      <c r="Q805" s="1" t="inlineStr"/>
+      <c r="P805" s="2" t="n">
+        <v>46241.65195802083</v>
+      </c>
+      <c r="Q805" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="R805" s="1" t="inlineStr">
         <is>
-          <t>Cobramos novamente o antigo contador</t>
+          <t>Abrir um chamado por empresa, por gentileza.</t>
         </is>
       </c>
       <c r="S805" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T805" s="1" t="n"/>
@@ -62071,39 +62092,39 @@
     </row>
     <row r="806">
       <c r="A806" s="1" t="n">
-        <v>81933</v>
+        <v>81780</v>
       </c>
       <c r="B806" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C806" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Objeto Social</t>
         </is>
       </c>
       <c r="D806" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E806" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar:6990 - RC MATERIAIS ELETRICOS E HIDRAULICOS (MATRIZ) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL6991 - RC MATERIAIS ELETRICOS E HIDRAULICOS (FILIAL 1) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL</t>
+          <t>ALTERAÇÃO CONTRATUAL DA EMPRESA: 6993-GOMES SERVIÇOS - LTDAGRUPO: CRISTO REIALTERAÇÃO DE QSA E OBJETO SOCIALPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.500,00MESMA ATIVIDADE E SÓCIOS DO SUP. AVENIDA, APÓS ALTERAÇÃO MIGRAR FUNCIONÁRIOS PARA NOVA EMPRESA ALTERAR QSA E OBJETO SOCIAL.</t>
         </is>
       </c>
       <c r="F806" s="1" t="n">
-        <v>6990</v>
+        <v>6993</v>
       </c>
       <c r="G806" s="1" t="inlineStr">
         <is>
-          <t>AMANCIO S ELETRICA, HIDRAULICA E CONSTRUCAO EM GERAL LTDA (MATRIZ)</t>
+          <t>GOMES SERVIÇOS - LTDA</t>
         </is>
       </c>
       <c r="H806" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I806" s="1" t="inlineStr">
@@ -62112,39 +62133,37 @@
         </is>
       </c>
       <c r="J806" s="2" t="n">
-        <v>46239.72520292824</v>
+        <v>46237.62372283565</v>
       </c>
       <c r="K806" s="2" t="n">
-        <v>46241</v>
+        <v>46265</v>
       </c>
       <c r="L806" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M806" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N806" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N806" s="2" t="n">
+        <v>46246.66900671296</v>
+      </c>
       <c r="O806" s="1" t="n"/>
-      <c r="P806" s="2" t="n">
-        <v>46241.65195802083</v>
-      </c>
-      <c r="Q806" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P806" s="1" t="n"/>
+      <c r="Q806" s="1" t="inlineStr"/>
       <c r="R806" s="1" t="inlineStr">
         <is>
-          <t>Abrir um chamado por empresa, por gentileza.</t>
+          <t xml:space="preserve">Prezados(as), boa tarde!
+Alteração contratual em andamento. 
+Atenciosamente, </t>
         </is>
       </c>
       <c r="S806" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T806" s="1" t="n"/>
@@ -62152,34 +62171,34 @@
     </row>
     <row r="807">
       <c r="A807" s="1" t="n">
-        <v>81780</v>
+        <v>83921</v>
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C807" s="1" t="inlineStr">
         <is>
-          <t>Objeto Social</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D807" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E807" s="1" t="inlineStr">
         <is>
-          <t>ALTERAÇÃO CONTRATUAL DA EMPRESA: 6993-GOMES SERVIÇOS - LTDAGRUPO: CRISTO REIALTERAÇÃO DE QSA E OBJETO SOCIALPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.500,00MESMA ATIVIDADE E SÓCIOS DO SUP. AVENIDA, APÓS ALTERAÇÃO MIGRAR FUNCIONÁRIOS PARA NOVA EMPRESA ALTERAR QSA E OBJETO SOCIAL.</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F807" s="1" t="n">
-        <v>6993</v>
+        <v>6999</v>
       </c>
       <c r="G807" s="1" t="inlineStr">
         <is>
-          <t>GOMES SERVIÇOS - LTDA</t>
+          <t>VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="H807" s="1" t="inlineStr">
@@ -62193,34 +62212,26 @@
         </is>
       </c>
       <c r="J807" s="2" t="n">
-        <v>46237.62372283565</v>
+        <v>46279.39769957176</v>
       </c>
       <c r="K807" s="2" t="n">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="L807" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M807" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N807" s="2" t="n">
-        <v>46246.66900671296</v>
-      </c>
+          <t>Ney Barbosa</t>
+        </is>
+      </c>
+      <c r="N807" s="1" t="n"/>
       <c r="O807" s="1" t="n"/>
       <c r="P807" s="1" t="n"/>
       <c r="Q807" s="1" t="inlineStr"/>
-      <c r="R807" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prezados(as), boa tarde!
-Alteração contratual em andamento. 
-Atenciosamente, </t>
-        </is>
-      </c>
+      <c r="R807" s="1" t="inlineStr"/>
       <c r="S807" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -62231,7 +62242,7 @@
     </row>
     <row r="808">
       <c r="A808" s="1" t="n">
-        <v>83921</v>
+        <v>83904</v>
       </c>
       <c r="B808" s="1" t="inlineStr">
         <is>
@@ -62254,16 +62265,16 @@
         </is>
       </c>
       <c r="F808" s="1" t="n">
-        <v>6999</v>
+        <v>7005</v>
       </c>
       <c r="G808" s="1" t="inlineStr">
         <is>
-          <t>VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
+          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H808" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I808" s="1" t="inlineStr">
@@ -62272,7 +62283,7 @@
         </is>
       </c>
       <c r="J808" s="2" t="n">
-        <v>46279.39769957176</v>
+        <v>46279.39261207176</v>
       </c>
       <c r="K808" s="2" t="n">
         <v>46281</v>
@@ -62302,7 +62313,7 @@
     </row>
     <row r="809">
       <c r="A809" s="1" t="n">
-        <v>83904</v>
+        <v>83905</v>
       </c>
       <c r="B809" s="1" t="inlineStr">
         <is>
@@ -62325,11 +62336,11 @@
         </is>
       </c>
       <c r="F809" s="1" t="n">
-        <v>7005</v>
+        <v>7006</v>
       </c>
       <c r="G809" s="1" t="inlineStr">
         <is>
-          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H809" s="1" t="inlineStr">
@@ -62343,7 +62354,7 @@
         </is>
       </c>
       <c r="J809" s="2" t="n">
-        <v>46279.39261207176</v>
+        <v>46279.39292399306</v>
       </c>
       <c r="K809" s="2" t="n">
         <v>46281</v>
@@ -62373,39 +62384,39 @@
     </row>
     <row r="810">
       <c r="A810" s="1" t="n">
-        <v>83905</v>
+        <v>83261</v>
       </c>
       <c r="B810" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C810" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D810" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E810" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Alteração contratual do QSA da empresa: 7046-RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDAGrupo: RamiroProposta já negociada no valor de R$1.800,00Retirar os dois sócios (João e Lucas) e deixar 100% do QSA com o Ramiro. Colocar atividade no Simples impeditiva, para que no mês de outubro essa empresa entre no Lucro Real</t>
         </is>
       </c>
       <c r="F810" s="1" t="n">
-        <v>7006</v>
+        <v>7046</v>
       </c>
       <c r="G810" s="1" t="inlineStr">
         <is>
-          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
         </is>
       </c>
       <c r="H810" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I810" s="1" t="inlineStr">
@@ -62414,26 +62425,34 @@
         </is>
       </c>
       <c r="J810" s="2" t="n">
-        <v>46279.39292399306</v>
+        <v>46265.45567503473</v>
       </c>
       <c r="K810" s="2" t="n">
-        <v>46281</v>
+        <v>46293</v>
       </c>
       <c r="L810" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M810" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N810" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N810" s="2" t="n">
+        <v>46266.72388877315</v>
+      </c>
       <c r="O810" s="1" t="n"/>
       <c r="P810" s="1" t="n"/>
       <c r="Q810" s="1" t="inlineStr"/>
-      <c r="R810" s="1" t="inlineStr"/>
+      <c r="R810" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde.
+Preparando a minuta.
+Atenciosamente,</t>
+        </is>
+      </c>
       <c r="S810" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -62444,34 +62463,34 @@
     </row>
     <row r="811">
       <c r="A811" s="1" t="n">
-        <v>83907</v>
+        <v>84107</v>
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C811" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D811" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E811" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t xml:space="preserve">boa tarde!!Por gentileza, fazer ALVARÁ de funcionamento da loja. </t>
         </is>
       </c>
       <c r="F811" s="1" t="n">
-        <v>7041</v>
+        <v>7051</v>
       </c>
       <c r="G811" s="1" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN SERVICOS PROMOCIONAIS LTDA</t>
+          <t>TODOS ADMINISTRADORA DE CARTAO DE DESCONTOS BOTUCATU LTDA</t>
         </is>
       </c>
       <c r="H811" s="1" t="inlineStr">
@@ -62485,10 +62504,10 @@
         </is>
       </c>
       <c r="J811" s="2" t="n">
-        <v>46279.39348993055</v>
+        <v>46282.58430902778</v>
       </c>
       <c r="K811" s="2" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="L811" s="1" t="inlineStr">
         <is>
@@ -62497,7 +62516,7 @@
       </c>
       <c r="M811" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="N811" s="1" t="n"/>
@@ -62515,39 +62534,39 @@
     </row>
     <row r="812">
       <c r="A812" s="1" t="n">
-        <v>83261</v>
+        <v>83908</v>
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C812" s="1" t="inlineStr">
         <is>
-          <t>Sócios</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D812" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E812" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual do QSA da empresa: 7046-RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDAGrupo: RamiroProposta já negociada no valor de R$1.800,00Retirar os dois sócios (João e Lucas) e deixar 100% do QSA com o Ramiro. Colocar atividade no Simples impeditiva, para que no mês de outubro essa empresa entre no Lucro Real</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F812" s="1" t="n">
-        <v>7046</v>
+        <v>7052</v>
       </c>
       <c r="G812" s="1" t="inlineStr">
         <is>
-          <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
+          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
         </is>
       </c>
       <c r="H812" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I812" s="1" t="inlineStr">
@@ -62556,34 +62575,26 @@
         </is>
       </c>
       <c r="J812" s="2" t="n">
-        <v>46265.45567503473</v>
+        <v>46279.3937971875</v>
       </c>
       <c r="K812" s="2" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="L812" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M812" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N812" s="2" t="n">
-        <v>46266.72388877315</v>
-      </c>
+          <t>Ney Barbosa</t>
+        </is>
+      </c>
+      <c r="N812" s="1" t="n"/>
       <c r="O812" s="1" t="n"/>
       <c r="P812" s="1" t="n"/>
       <c r="Q812" s="1" t="inlineStr"/>
-      <c r="R812" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde.
-Preparando a minuta.
-Atenciosamente,</t>
-        </is>
-      </c>
+      <c r="R812" s="1" t="inlineStr"/>
       <c r="S812" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -62594,39 +62605,39 @@
     </row>
     <row r="813">
       <c r="A813" s="1" t="n">
-        <v>84107</v>
+        <v>83909</v>
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C813" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D813" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E813" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">boa tarde!!Por gentileza, fazer ALVARÁ de funcionamento da loja. </t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F813" s="1" t="n">
-        <v>7051</v>
+        <v>7053</v>
       </c>
       <c r="G813" s="1" t="inlineStr">
         <is>
-          <t>TODOS ADMINISTRADORA DE CARTAO DE DESCONTOS BOTUCATU LTDA</t>
+          <t>BIANCA EMBREAGENS LTDA</t>
         </is>
       </c>
       <c r="H813" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I813" s="1" t="inlineStr">
@@ -62635,10 +62646,10 @@
         </is>
       </c>
       <c r="J813" s="2" t="n">
-        <v>46282.58430902778</v>
+        <v>46279.39412114584</v>
       </c>
       <c r="K813" s="2" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="L813" s="1" t="inlineStr">
         <is>
@@ -62647,7 +62658,7 @@
       </c>
       <c r="M813" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Ney Barbosa</t>
         </is>
       </c>
       <c r="N813" s="1" t="n"/>
@@ -62665,7 +62676,7 @@
     </row>
     <row r="814">
       <c r="A814" s="1" t="n">
-        <v>83908</v>
+        <v>83910</v>
       </c>
       <c r="B814" s="1" t="inlineStr">
         <is>
@@ -62688,11 +62699,11 @@
         </is>
       </c>
       <c r="F814" s="1" t="n">
-        <v>7052</v>
+        <v>7054</v>
       </c>
       <c r="G814" s="1" t="inlineStr">
         <is>
-          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
+          <t>KADOSH DISTRIBUIDOR COMERCIO E SERVICO DIGITAL LTDA</t>
         </is>
       </c>
       <c r="H814" s="1" t="inlineStr">
@@ -62706,7 +62717,7 @@
         </is>
       </c>
       <c r="J814" s="2" t="n">
-        <v>46279.3937971875</v>
+        <v>46279.39450123843</v>
       </c>
       <c r="K814" s="2" t="n">
         <v>46281</v>
@@ -62736,7 +62747,7 @@
     </row>
     <row r="815">
       <c r="A815" s="1" t="n">
-        <v>83909</v>
+        <v>83911</v>
       </c>
       <c r="B815" s="1" t="inlineStr">
         <is>
@@ -62759,11 +62770,11 @@
         </is>
       </c>
       <c r="F815" s="1" t="n">
-        <v>7053</v>
+        <v>7055</v>
       </c>
       <c r="G815" s="1" t="inlineStr">
         <is>
-          <t>BIANCA EMBREAGENS LTDA</t>
+          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
         </is>
       </c>
       <c r="H815" s="1" t="inlineStr">
@@ -62777,7 +62788,7 @@
         </is>
       </c>
       <c r="J815" s="2" t="n">
-        <v>46279.39412114584</v>
+        <v>46279.39479143519</v>
       </c>
       <c r="K815" s="2" t="n">
         <v>46281</v>
@@ -62807,7 +62818,7 @@
     </row>
     <row r="816">
       <c r="A816" s="1" t="n">
-        <v>83910</v>
+        <v>83912</v>
       </c>
       <c r="B816" s="1" t="inlineStr">
         <is>
@@ -62830,11 +62841,11 @@
         </is>
       </c>
       <c r="F816" s="1" t="n">
-        <v>7054</v>
+        <v>7056</v>
       </c>
       <c r="G816" s="1" t="inlineStr">
         <is>
-          <t>KADOSH DISTRIBUIDOR COMERCIO E SERVICO DIGITAL LTDA</t>
+          <t>AUTO CENTER EMBRASIL LTDA</t>
         </is>
       </c>
       <c r="H816" s="1" t="inlineStr">
@@ -62848,7 +62859,7 @@
         </is>
       </c>
       <c r="J816" s="2" t="n">
-        <v>46279.39450123843</v>
+        <v>46279.39518283565</v>
       </c>
       <c r="K816" s="2" t="n">
         <v>46281</v>
@@ -62878,7 +62889,7 @@
     </row>
     <row r="817">
       <c r="A817" s="1" t="n">
-        <v>83911</v>
+        <v>83913</v>
       </c>
       <c r="B817" s="1" t="inlineStr">
         <is>
@@ -62901,11 +62912,11 @@
         </is>
       </c>
       <c r="F817" s="1" t="n">
-        <v>7055</v>
+        <v>7057</v>
       </c>
       <c r="G817" s="1" t="inlineStr">
         <is>
-          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H817" s="1" t="inlineStr">
@@ -62919,7 +62930,7 @@
         </is>
       </c>
       <c r="J817" s="2" t="n">
-        <v>46279.39479143519</v>
+        <v>46279.39551385416</v>
       </c>
       <c r="K817" s="2" t="n">
         <v>46281</v>
@@ -62949,7 +62960,7 @@
     </row>
     <row r="818">
       <c r="A818" s="1" t="n">
-        <v>83912</v>
+        <v>83916</v>
       </c>
       <c r="B818" s="1" t="inlineStr">
         <is>
@@ -62972,11 +62983,11 @@
         </is>
       </c>
       <c r="F818" s="1" t="n">
-        <v>7056</v>
+        <v>7060</v>
       </c>
       <c r="G818" s="1" t="inlineStr">
         <is>
-          <t>AUTO CENTER EMBRASIL LTDA</t>
+          <t>GAPEMA LOCACAO DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H818" s="1" t="inlineStr">
@@ -62990,7 +63001,7 @@
         </is>
       </c>
       <c r="J818" s="2" t="n">
-        <v>46279.39518283565</v>
+        <v>46279.39634756945</v>
       </c>
       <c r="K818" s="2" t="n">
         <v>46281</v>
@@ -63020,7 +63031,7 @@
     </row>
     <row r="819">
       <c r="A819" s="1" t="n">
-        <v>83913</v>
+        <v>83917</v>
       </c>
       <c r="B819" s="1" t="inlineStr">
         <is>
@@ -63043,11 +63054,11 @@
         </is>
       </c>
       <c r="F819" s="1" t="n">
-        <v>7057</v>
+        <v>7061</v>
       </c>
       <c r="G819" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
+          <t>BF CORTES E FUROS TECNICOS E LOCACAO LTDA</t>
         </is>
       </c>
       <c r="H819" s="1" t="inlineStr">
@@ -63061,7 +63072,7 @@
         </is>
       </c>
       <c r="J819" s="2" t="n">
-        <v>46279.39551385416</v>
+        <v>46279.39663144676</v>
       </c>
       <c r="K819" s="2" t="n">
         <v>46281</v>
@@ -63091,7 +63102,7 @@
     </row>
     <row r="820">
       <c r="A820" s="1" t="n">
-        <v>83916</v>
+        <v>83918</v>
       </c>
       <c r="B820" s="1" t="inlineStr">
         <is>
@@ -63114,11 +63125,11 @@
         </is>
       </c>
       <c r="F820" s="1" t="n">
-        <v>7060</v>
+        <v>7062</v>
       </c>
       <c r="G820" s="1" t="inlineStr">
         <is>
-          <t>GAPEMA LOCACAO DE EQUIPAMENTOS LTDA</t>
+          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="H820" s="1" t="inlineStr">
@@ -63132,7 +63143,7 @@
         </is>
       </c>
       <c r="J820" s="2" t="n">
-        <v>46279.39634756945</v>
+        <v>46279.39692175926</v>
       </c>
       <c r="K820" s="2" t="n">
         <v>46281</v>
@@ -63162,7 +63173,7 @@
     </row>
     <row r="821">
       <c r="A821" s="1" t="n">
-        <v>83917</v>
+        <v>83919</v>
       </c>
       <c r="B821" s="1" t="inlineStr">
         <is>
@@ -63185,11 +63196,11 @@
         </is>
       </c>
       <c r="F821" s="1" t="n">
-        <v>7061</v>
+        <v>7063</v>
       </c>
       <c r="G821" s="1" t="inlineStr">
         <is>
-          <t>BF CORTES E FUROS TECNICOS E LOCACAO LTDA</t>
+          <t>CR LOCACAO E VENDAS DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H821" s="1" t="inlineStr">
@@ -63203,7 +63214,7 @@
         </is>
       </c>
       <c r="J821" s="2" t="n">
-        <v>46279.39663144676</v>
+        <v>46279.39713047454</v>
       </c>
       <c r="K821" s="2" t="n">
         <v>46281</v>
@@ -63233,39 +63244,39 @@
     </row>
     <row r="822">
       <c r="A822" s="1" t="n">
-        <v>83918</v>
+        <v>83982</v>
       </c>
       <c r="B822" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C822" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D822" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E822" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Abertura de nova empresa do grupo: 7064-BC SUPERMERCADOTributação: Simples NacionalTipo de Atividade: ComércioFinalidade: OperacionalForma Juridica: LtdaProposta: já negociada no valor de R$1.800,00</t>
         </is>
       </c>
       <c r="F822" s="1" t="n">
-        <v>7062</v>
+        <v>7064</v>
       </c>
       <c r="G822" s="1" t="inlineStr">
         <is>
-          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
+          <t>BISPO E CARVALHO SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="H822" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I822" s="1" t="inlineStr">
@@ -63274,10 +63285,10 @@
         </is>
       </c>
       <c r="J822" s="2" t="n">
-        <v>46279.39692175926</v>
+        <v>46280.39557824074</v>
       </c>
       <c r="K822" s="2" t="n">
-        <v>46281</v>
+        <v>46308</v>
       </c>
       <c r="L822" s="1" t="inlineStr">
         <is>
@@ -63286,7 +63297,7 @@
       </c>
       <c r="M822" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N822" s="1" t="n"/>
@@ -63304,7 +63315,7 @@
     </row>
     <row r="823">
       <c r="A823" s="1" t="n">
-        <v>83919</v>
+        <v>83922</v>
       </c>
       <c r="B823" s="1" t="inlineStr">
         <is>
@@ -63327,16 +63338,16 @@
         </is>
       </c>
       <c r="F823" s="1" t="n">
-        <v>7063</v>
+        <v>7065</v>
       </c>
       <c r="G823" s="1" t="inlineStr">
         <is>
-          <t>CR LOCACAO E VENDAS DE EQUIPAMENTOS LTDA</t>
+          <t>GRANUA AGROINDUSTRIA E COMERCIO DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H823" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I823" s="1" t="inlineStr">
@@ -63345,7 +63356,7 @@
         </is>
       </c>
       <c r="J823" s="2" t="n">
-        <v>46279.39713047454</v>
+        <v>46279.39797662037</v>
       </c>
       <c r="K823" s="2" t="n">
         <v>46281</v>
@@ -63375,67 +63386,75 @@
     </row>
     <row r="824">
       <c r="A824" s="1" t="n">
-        <v>83982</v>
+        <v>83218</v>
       </c>
       <c r="B824" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C824" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Comércio</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D824" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E824" s="1" t="inlineStr">
         <is>
-          <t>Abertura de nova empresa do grupo: 7064-BC SUPERMERCADOTributação: Simples NacionalTipo de Atividade: ComércioFinalidade: OperacionalForma Juridica: LtdaProposta: já negociada no valor de R$1.800,00</t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F824" s="1" t="n">
-        <v>7064</v>
+        <v>7063</v>
       </c>
       <c r="G824" s="1" t="inlineStr">
         <is>
-          <t>BISPO E CARVALHO SUPERMERCADO LTDA</t>
+          <t>CR LOCACAO E VENDAS DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H824" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I824" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J824" s="2" t="n">
-        <v>46280.39557824074</v>
+        <v>46262.49630575231</v>
       </c>
       <c r="K824" s="2" t="n">
-        <v>46308</v>
+        <v>46265</v>
       </c>
       <c r="L824" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M824" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N824" s="1" t="n"/>
-      <c r="O824" s="1" t="n"/>
+          <t>Santos Karina</t>
+        </is>
+      </c>
+      <c r="N824" s="2" t="n">
+        <v>46267.54627245371</v>
+      </c>
+      <c r="O824" s="2" t="n">
+        <v>46283</v>
+      </c>
       <c r="P824" s="1" t="n"/>
       <c r="Q824" s="1" t="inlineStr"/>
-      <c r="R824" s="1" t="inlineStr"/>
+      <c r="R824" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando o SAC liberar para cobrar os documentos .</t>
+        </is>
+      </c>
       <c r="S824" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -63446,67 +63465,75 @@
     </row>
     <row r="825">
       <c r="A825" s="1" t="n">
-        <v>83922</v>
+        <v>83216</v>
       </c>
       <c r="B825" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C825" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D825" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E825" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F825" s="1" t="n">
-        <v>7065</v>
+        <v>7061</v>
       </c>
       <c r="G825" s="1" t="inlineStr">
         <is>
-          <t>GRANUA AGROINDUSTRIA E COMERCIO DE ALIMENTOS LTDA</t>
+          <t>BF CORTES E FUROS TECNICOS E LOCACAO LTDA</t>
         </is>
       </c>
       <c r="H825" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I825" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J825" s="2" t="n">
-        <v>46279.39797662037</v>
+        <v>46262.49574116898</v>
       </c>
       <c r="K825" s="2" t="n">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="L825" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M825" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N825" s="1" t="n"/>
-      <c r="O825" s="1" t="n"/>
+          <t>Santos Karina</t>
+        </is>
+      </c>
+      <c r="N825" s="2" t="n">
+        <v>46267.54612248843</v>
+      </c>
+      <c r="O825" s="2" t="n">
+        <v>46283</v>
+      </c>
       <c r="P825" s="1" t="n"/>
       <c r="Q825" s="1" t="inlineStr"/>
-      <c r="R825" s="1" t="inlineStr"/>
+      <c r="R825" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando o SAC liberar para cobrar os documentos .</t>
+        </is>
+      </c>
       <c r="S825" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -63517,7 +63544,7 @@
     </row>
     <row r="826">
       <c r="A826" s="1" t="n">
-        <v>83218</v>
+        <v>83217</v>
       </c>
       <c r="B826" s="1" t="inlineStr">
         <is>
@@ -63540,11 +63567,11 @@
         </is>
       </c>
       <c r="F826" s="1" t="n">
-        <v>7063</v>
+        <v>7062</v>
       </c>
       <c r="G826" s="1" t="inlineStr">
         <is>
-          <t>CR LOCACAO E VENDAS DE EQUIPAMENTOS LTDA</t>
+          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="H826" s="1" t="inlineStr">
@@ -63554,18 +63581,18 @@
       </c>
       <c r="I826" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J826" s="2" t="n">
-        <v>46262.49630575231</v>
+        <v>46262.49604351852</v>
       </c>
       <c r="K826" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="L826" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M826" s="1" t="inlineStr">
@@ -63573,9 +63600,7 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N826" s="2" t="n">
-        <v>46267.54627245371</v>
-      </c>
+      <c r="N826" s="1" t="n"/>
       <c r="O826" s="2" t="n">
         <v>46283</v>
       </c>
@@ -63591,12 +63616,16 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T826" s="1" t="n"/>
+      <c r="T826" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
       <c r="U826" s="1" t="inlineStr"/>
     </row>
     <row r="827">
       <c r="A827" s="1" t="n">
-        <v>83216</v>
+        <v>83213</v>
       </c>
       <c r="B827" s="1" t="inlineStr">
         <is>
@@ -63619,11 +63648,11 @@
         </is>
       </c>
       <c r="F827" s="1" t="n">
-        <v>7061</v>
+        <v>7058</v>
       </c>
       <c r="G827" s="1" t="inlineStr">
         <is>
-          <t>BF CORTES E FUROS TECNICOS E LOCACAO LTDA</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H827" s="1" t="inlineStr">
@@ -63633,18 +63662,18 @@
       </c>
       <c r="I827" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J827" s="2" t="n">
-        <v>46262.49574116898</v>
+        <v>46262.49500332176</v>
       </c>
       <c r="K827" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="L827" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M827" s="1" t="inlineStr">
@@ -63652,9 +63681,7 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N827" s="2" t="n">
-        <v>46267.54612248843</v>
-      </c>
+      <c r="N827" s="1" t="n"/>
       <c r="O827" s="2" t="n">
         <v>46283</v>
       </c>
@@ -63670,12 +63697,16 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T827" s="1" t="n"/>
+      <c r="T827" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
       <c r="U827" s="1" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" s="1" t="n">
-        <v>83217</v>
+        <v>83214</v>
       </c>
       <c r="B828" s="1" t="inlineStr">
         <is>
@@ -63698,11 +63729,11 @@
         </is>
       </c>
       <c r="F828" s="1" t="n">
-        <v>7062</v>
+        <v>7059</v>
       </c>
       <c r="G828" s="1" t="inlineStr">
         <is>
-          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 2)</t>
         </is>
       </c>
       <c r="H828" s="1" t="inlineStr">
@@ -63716,7 +63747,7 @@
         </is>
       </c>
       <c r="J828" s="2" t="n">
-        <v>46262.49604351852</v>
+        <v>46262.49526809028</v>
       </c>
       <c r="K828" s="2" t="n">
         <v>46265</v>
@@ -63756,7 +63787,7 @@
     </row>
     <row r="829">
       <c r="A829" s="1" t="n">
-        <v>83213</v>
+        <v>83215</v>
       </c>
       <c r="B829" s="1" t="inlineStr">
         <is>
@@ -63779,11 +63810,11 @@
         </is>
       </c>
       <c r="F829" s="1" t="n">
-        <v>7058</v>
+        <v>7060</v>
       </c>
       <c r="G829" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 1)</t>
+          <t>GAPEMA LOCACAO DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H829" s="1" t="inlineStr">
@@ -63793,18 +63824,18 @@
       </c>
       <c r="I829" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J829" s="2" t="n">
-        <v>46262.49500332176</v>
+        <v>46262.49551331018</v>
       </c>
       <c r="K829" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="L829" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M829" s="1" t="inlineStr">
@@ -63812,7 +63843,9 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N829" s="1" t="n"/>
+      <c r="N829" s="2" t="n">
+        <v>46267.54604818287</v>
+      </c>
       <c r="O829" s="2" t="n">
         <v>46283</v>
       </c>
@@ -63828,16 +63861,12 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T829" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
+      <c r="T829" s="1" t="n"/>
       <c r="U829" s="1" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" s="1" t="n">
-        <v>83214</v>
+        <v>83117</v>
       </c>
       <c r="B830" s="1" t="inlineStr">
         <is>
@@ -63856,15 +63885,15 @@
       </c>
       <c r="E830" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
         </is>
       </c>
       <c r="F830" s="1" t="n">
-        <v>7059</v>
+        <v>7056</v>
       </c>
       <c r="G830" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 2)</t>
+          <t>AUTO CENTER EMBRASIL LTDA</t>
         </is>
       </c>
       <c r="H830" s="1" t="inlineStr">
@@ -63874,18 +63903,18 @@
       </c>
       <c r="I830" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J830" s="2" t="n">
-        <v>46262.49526809028</v>
+        <v>46261.47502040509</v>
       </c>
       <c r="K830" s="2" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="L830" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M830" s="1" t="inlineStr">
@@ -63893,7 +63922,9 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N830" s="1" t="n"/>
+      <c r="N830" s="2" t="n">
+        <v>46261.69782774305</v>
+      </c>
       <c r="O830" s="2" t="n">
         <v>46283</v>
       </c>
@@ -63901,7 +63932,7 @@
       <c r="Q830" s="1" t="inlineStr"/>
       <c r="R830" s="1" t="inlineStr">
         <is>
-          <t>Aguardando o SAC liberar para cobrar os documentos .</t>
+          <t>Cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S830" s="1" t="inlineStr">
@@ -63909,16 +63940,12 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T830" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
+      <c r="T830" s="1" t="n"/>
       <c r="U830" s="1" t="inlineStr"/>
     </row>
     <row r="831">
       <c r="A831" s="1" t="n">
-        <v>83215</v>
+        <v>83212</v>
       </c>
       <c r="B831" s="1" t="inlineStr">
         <is>
@@ -63941,11 +63968,11 @@
         </is>
       </c>
       <c r="F831" s="1" t="n">
-        <v>7060</v>
+        <v>7057</v>
       </c>
       <c r="G831" s="1" t="inlineStr">
         <is>
-          <t>GAPEMA LOCACAO DE EQUIPAMENTOS LTDA</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H831" s="1" t="inlineStr">
@@ -63955,18 +63982,18 @@
       </c>
       <c r="I831" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J831" s="2" t="n">
-        <v>46262.49551331018</v>
+        <v>46262.49474181713</v>
       </c>
       <c r="K831" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="L831" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M831" s="1" t="inlineStr">
@@ -63974,9 +64001,7 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N831" s="2" t="n">
-        <v>46267.54604818287</v>
-      </c>
+      <c r="N831" s="1" t="n"/>
       <c r="O831" s="2" t="n">
         <v>46283</v>
       </c>
@@ -63992,12 +64017,16 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T831" s="1" t="n"/>
+      <c r="T831" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
       <c r="U831" s="1" t="inlineStr"/>
     </row>
     <row r="832">
       <c r="A832" s="1" t="n">
-        <v>83117</v>
+        <v>83115</v>
       </c>
       <c r="B832" s="1" t="inlineStr">
         <is>
@@ -64020,11 +64049,11 @@
         </is>
       </c>
       <c r="F832" s="1" t="n">
-        <v>7056</v>
+        <v>7054</v>
       </c>
       <c r="G832" s="1" t="inlineStr">
         <is>
-          <t>AUTO CENTER EMBRASIL LTDA</t>
+          <t>KADOSH DISTRIBUIDOR COMERCIO E SERVICO DIGITAL LTDA</t>
         </is>
       </c>
       <c r="H832" s="1" t="inlineStr">
@@ -64038,7 +64067,7 @@
         </is>
       </c>
       <c r="J832" s="2" t="n">
-        <v>46261.47502040509</v>
+        <v>46261.47454267361</v>
       </c>
       <c r="K832" s="2" t="n">
         <v>46262</v>
@@ -64054,7 +64083,7 @@
         </is>
       </c>
       <c r="N832" s="2" t="n">
-        <v>46261.69782774305</v>
+        <v>46261.6975778125</v>
       </c>
       <c r="O832" s="2" t="n">
         <v>46283</v>
@@ -64076,7 +64105,7 @@
     </row>
     <row r="833">
       <c r="A833" s="1" t="n">
-        <v>83212</v>
+        <v>83116</v>
       </c>
       <c r="B833" s="1" t="inlineStr">
         <is>
@@ -64095,15 +64124,15 @@
       </c>
       <c r="E833" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
         </is>
       </c>
       <c r="F833" s="1" t="n">
-        <v>7057</v>
+        <v>7055</v>
       </c>
       <c r="G833" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
+          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
         </is>
       </c>
       <c r="H833" s="1" t="inlineStr">
@@ -64113,18 +64142,18 @@
       </c>
       <c r="I833" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J833" s="2" t="n">
-        <v>46262.49474181713</v>
+        <v>46261.47479783565</v>
       </c>
       <c r="K833" s="2" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="L833" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M833" s="1" t="inlineStr">
@@ -64132,7 +64161,9 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N833" s="1" t="n"/>
+      <c r="N833" s="2" t="n">
+        <v>46261.69765454861</v>
+      </c>
       <c r="O833" s="2" t="n">
         <v>46283</v>
       </c>
@@ -64140,7 +64171,7 @@
       <c r="Q833" s="1" t="inlineStr"/>
       <c r="R833" s="1" t="inlineStr">
         <is>
-          <t>Aguardando o SAC liberar para cobrar os documentos .</t>
+          <t>Cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S833" s="1" t="inlineStr">
@@ -64148,16 +64179,12 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T833" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
+      <c r="T833" s="1" t="n"/>
       <c r="U833" s="1" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" s="1" t="n">
-        <v>83115</v>
+        <v>83112</v>
       </c>
       <c r="B834" s="1" t="inlineStr">
         <is>
@@ -64180,11 +64207,11 @@
         </is>
       </c>
       <c r="F834" s="1" t="n">
-        <v>7054</v>
+        <v>7052</v>
       </c>
       <c r="G834" s="1" t="inlineStr">
         <is>
-          <t>KADOSH DISTRIBUIDOR COMERCIO E SERVICO DIGITAL LTDA</t>
+          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
         </is>
       </c>
       <c r="H834" s="1" t="inlineStr">
@@ -64198,7 +64225,7 @@
         </is>
       </c>
       <c r="J834" s="2" t="n">
-        <v>46261.47454267361</v>
+        <v>46261.47219082176</v>
       </c>
       <c r="K834" s="2" t="n">
         <v>46262</v>
@@ -64214,7 +64241,7 @@
         </is>
       </c>
       <c r="N834" s="2" t="n">
-        <v>46261.6975778125</v>
+        <v>46261.69723422454</v>
       </c>
       <c r="O834" s="2" t="n">
         <v>46283</v>
@@ -64236,7 +64263,7 @@
     </row>
     <row r="835">
       <c r="A835" s="1" t="n">
-        <v>83116</v>
+        <v>82905</v>
       </c>
       <c r="B835" s="1" t="inlineStr">
         <is>
@@ -64255,15 +64282,15 @@
       </c>
       <c r="E835" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
+          <t xml:space="preserve">Boa tarde, por gentileza, solicitar os documentos para a implantação da empresa. </t>
         </is>
       </c>
       <c r="F835" s="1" t="n">
-        <v>7055</v>
+        <v>7046</v>
       </c>
       <c r="G835" s="1" t="inlineStr">
         <is>
-          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
+          <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
         </is>
       </c>
       <c r="H835" s="1" t="inlineStr">
@@ -64277,10 +64304,10 @@
         </is>
       </c>
       <c r="J835" s="2" t="n">
-        <v>46261.47479783565</v>
+        <v>46258.65608700232</v>
       </c>
       <c r="K835" s="2" t="n">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="L835" s="1" t="inlineStr">
         <is>
@@ -64293,7 +64320,7 @@
         </is>
       </c>
       <c r="N835" s="2" t="n">
-        <v>46261.69765454861</v>
+        <v>46259.7507258449</v>
       </c>
       <c r="O835" s="2" t="n">
         <v>46283</v>
@@ -64302,7 +64329,7 @@
       <c r="Q835" s="1" t="inlineStr"/>
       <c r="R835" s="1" t="inlineStr">
         <is>
-          <t>Cobramos os documentos do antigo contador.</t>
+          <t xml:space="preserve">Cobramos os documentos </t>
         </is>
       </c>
       <c r="S835" s="1" t="inlineStr">
@@ -64315,7 +64342,7 @@
     </row>
     <row r="836">
       <c r="A836" s="1" t="n">
-        <v>83112</v>
+        <v>82755</v>
       </c>
       <c r="B836" s="1" t="inlineStr">
         <is>
@@ -64334,15 +64361,15 @@
       </c>
       <c r="E836" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
+          <t>Boa tarde, por gentileza, providenciar documentos para implantação.</t>
         </is>
       </c>
       <c r="F836" s="1" t="n">
-        <v>7052</v>
+        <v>7005</v>
       </c>
       <c r="G836" s="1" t="inlineStr">
         <is>
-          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
+          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H836" s="1" t="inlineStr">
@@ -64356,10 +64383,10 @@
         </is>
       </c>
       <c r="J836" s="2" t="n">
-        <v>46261.47219082176</v>
+        <v>46254.65957604167</v>
       </c>
       <c r="K836" s="2" t="n">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="L836" s="1" t="inlineStr">
         <is>
@@ -64372,7 +64399,7 @@
         </is>
       </c>
       <c r="N836" s="2" t="n">
-        <v>46261.69723422454</v>
+        <v>46255.48691519676</v>
       </c>
       <c r="O836" s="2" t="n">
         <v>46283</v>
@@ -64381,7 +64408,7 @@
       <c r="Q836" s="1" t="inlineStr"/>
       <c r="R836" s="1" t="inlineStr">
         <is>
-          <t>Cobramos os documentos do antigo contador.</t>
+          <t>cobramos novamente o retorno dos documentos</t>
         </is>
       </c>
       <c r="S836" s="1" t="inlineStr">
@@ -64394,7 +64421,7 @@
     </row>
     <row r="837">
       <c r="A837" s="1" t="n">
-        <v>82905</v>
+        <v>82756</v>
       </c>
       <c r="B837" s="1" t="inlineStr">
         <is>
@@ -64413,15 +64440,15 @@
       </c>
       <c r="E837" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tarde, por gentileza, solicitar os documentos para a implantação da empresa. </t>
+          <t>Boa tarde, por gentileza, providenciar documentos para implantação.</t>
         </is>
       </c>
       <c r="F837" s="1" t="n">
-        <v>7046</v>
+        <v>7006</v>
       </c>
       <c r="G837" s="1" t="inlineStr">
         <is>
-          <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
+          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H837" s="1" t="inlineStr">
@@ -64435,10 +64462,10 @@
         </is>
       </c>
       <c r="J837" s="2" t="n">
-        <v>46258.65608700232</v>
+        <v>46254.65986380787</v>
       </c>
       <c r="K837" s="2" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="L837" s="1" t="inlineStr">
         <is>
@@ -64451,7 +64478,7 @@
         </is>
       </c>
       <c r="N837" s="2" t="n">
-        <v>46259.7507258449</v>
+        <v>46255.48792758102</v>
       </c>
       <c r="O837" s="2" t="n">
         <v>46283</v>
@@ -64460,7 +64487,7 @@
       <c r="Q837" s="1" t="inlineStr"/>
       <c r="R837" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cobramos os documentos </t>
+          <t>cobramos novamente os documentos</t>
         </is>
       </c>
       <c r="S837" s="1" t="inlineStr">
@@ -64473,7 +64500,7 @@
     </row>
     <row r="838">
       <c r="A838" s="1" t="n">
-        <v>82755</v>
+        <v>79867</v>
       </c>
       <c r="B838" s="1" t="inlineStr">
         <is>
@@ -64482,30 +64509,30 @@
       </c>
       <c r="C838" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D838" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E838" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza, providenciar documentos para implantação.</t>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
         </is>
       </c>
       <c r="F838" s="1" t="n">
-        <v>7005</v>
+        <v>6704</v>
       </c>
       <c r="G838" s="1" t="inlineStr">
         <is>
-          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="H838" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I838" s="1" t="inlineStr">
@@ -64514,10 +64541,10 @@
         </is>
       </c>
       <c r="J838" s="2" t="n">
-        <v>46254.65957604167</v>
+        <v>46183.62582114583</v>
       </c>
       <c r="K838" s="2" t="n">
-        <v>46255</v>
+        <v>46185</v>
       </c>
       <c r="L838" s="1" t="inlineStr">
         <is>
@@ -64526,20 +64553,19 @@
       </c>
       <c r="M838" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N838" s="2" t="n">
-        <v>46255.48691519676</v>
-      </c>
-      <c r="O838" s="2" t="n">
-        <v>46283</v>
-      </c>
+        <v>46237.4174340625</v>
+      </c>
+      <c r="O838" s="1" t="n"/>
       <c r="P838" s="1" t="n"/>
       <c r="Q838" s="1" t="inlineStr"/>
       <c r="R838" s="1" t="inlineStr">
         <is>
-          <t>cobramos novamente o retorno dos documentos</t>
+          <t>Bom dia!
+Cobramos a antiga contabilidade.</t>
         </is>
       </c>
       <c r="S838" s="1" t="inlineStr">
@@ -64552,7 +64578,7 @@
     </row>
     <row r="839">
       <c r="A839" s="1" t="n">
-        <v>82756</v>
+        <v>82310</v>
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
@@ -64561,25 +64587,25 @@
       </c>
       <c r="C839" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D839" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E839" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza, providenciar documentos para implantação.</t>
+          <t>Bom dia!Por favor, solicitar ao antigo contador o balanço de abertura.</t>
         </is>
       </c>
       <c r="F839" s="1" t="n">
-        <v>7006</v>
+        <v>6974</v>
       </c>
       <c r="G839" s="1" t="inlineStr">
         <is>
-          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>FRANCINALDO FERREIRA DE ANDRADE LTDA</t>
         </is>
       </c>
       <c r="H839" s="1" t="inlineStr">
@@ -64593,10 +64619,10 @@
         </is>
       </c>
       <c r="J839" s="2" t="n">
-        <v>46254.65986380787</v>
+        <v>46247.3783179051</v>
       </c>
       <c r="K839" s="2" t="n">
-        <v>46255</v>
+        <v>46248</v>
       </c>
       <c r="L839" s="1" t="inlineStr">
         <is>
@@ -64605,20 +64631,20 @@
       </c>
       <c r="M839" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N839" s="2" t="n">
-        <v>46255.48792758102</v>
+        <v>46253.39089305556</v>
       </c>
       <c r="O839" s="2" t="n">
-        <v>46283</v>
+        <v>46297</v>
       </c>
       <c r="P839" s="1" t="n"/>
       <c r="Q839" s="1" t="inlineStr"/>
       <c r="R839" s="1" t="inlineStr">
         <is>
-          <t>cobramos novamente os documentos</t>
+          <t>cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S839" s="1" t="inlineStr">
@@ -64631,16 +64657,16 @@
     </row>
     <row r="840">
       <c r="A840" s="1" t="n">
-        <v>79867</v>
+        <v>79865</v>
       </c>
       <c r="B840" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C840" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D840" s="1" t="inlineStr">
@@ -64650,20 +64676,20 @@
       </c>
       <c r="E840" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F840" s="1" t="n">
-        <v>6704</v>
+        <v>6278</v>
       </c>
       <c r="G840" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="H840" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I840" s="1" t="inlineStr">
@@ -64672,7 +64698,7 @@
         </is>
       </c>
       <c r="J840" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K840" s="2" t="n">
         <v>46185</v>
@@ -64688,7 +64714,7 @@
         </is>
       </c>
       <c r="N840" s="2" t="n">
-        <v>46237.4174340625</v>
+        <v>46246.6616841088</v>
       </c>
       <c r="O840" s="1" t="n"/>
       <c r="P840" s="1" t="n"/>
@@ -64696,7 +64722,7 @@
       <c r="R840" s="1" t="inlineStr">
         <is>
           <t>Bom dia!
-Cobramos a antiga contabilidade.</t>
+Já foi atendido?</t>
         </is>
       </c>
       <c r="S840" s="1" t="inlineStr">
@@ -64709,7 +64735,7 @@
     </row>
     <row r="841">
       <c r="A841" s="1" t="n">
-        <v>82310</v>
+        <v>82701</v>
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
@@ -64718,27 +64744,23 @@
       </c>
       <c r="C841" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D841" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E841" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Por favor, solicitar ao antigo contador o balanço de abertura.</t>
+          <t>Boa tarde, por gentileza, providencias documentos de implantação da empresa: 7037 - EXPANDItens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F841" s="1" t="n">
-        <v>6974</v>
-      </c>
-      <c r="G841" s="1" t="inlineStr">
-        <is>
-          <t>FRANCINALDO FERREIRA DE ANDRADE LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G841" s="1" t="n"/>
       <c r="H841" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -64750,10 +64772,10 @@
         </is>
       </c>
       <c r="J841" s="2" t="n">
-        <v>46247.3783179051</v>
+        <v>46253.71124814815</v>
       </c>
       <c r="K841" s="2" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="L841" s="1" t="inlineStr">
         <is>
@@ -64762,20 +64784,20 @@
       </c>
       <c r="M841" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="N841" s="2" t="n">
-        <v>46253.39089305556</v>
+        <v>46255.46909065972</v>
       </c>
       <c r="O841" s="2" t="n">
-        <v>46297</v>
+        <v>46283</v>
       </c>
       <c r="P841" s="1" t="n"/>
       <c r="Q841" s="1" t="inlineStr"/>
       <c r="R841" s="1" t="inlineStr">
         <is>
-          <t>cobramos os documentos do antigo contador.</t>
+          <t xml:space="preserve">CObramos os documentos </t>
         </is>
       </c>
       <c r="S841" s="1" t="inlineStr">
@@ -64788,36 +64810,32 @@
     </row>
     <row r="842">
       <c r="A842" s="1" t="n">
-        <v>79865</v>
+        <v>82706</v>
       </c>
       <c r="B842" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C842" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D842" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E842" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde, por gentileza, providenciar documentos de implantação da empresa: 6978 - HEPA FILTROS.Itens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F842" s="1" t="n">
-        <v>6278</v>
-      </c>
-      <c r="G842" s="1" t="inlineStr">
-        <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G842" s="1" t="n"/>
       <c r="H842" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -64829,10 +64847,10 @@
         </is>
       </c>
       <c r="J842" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46253.72086076389</v>
       </c>
       <c r="K842" s="2" t="n">
-        <v>46185</v>
+        <v>46255</v>
       </c>
       <c r="L842" s="1" t="inlineStr">
         <is>
@@ -64841,19 +64859,18 @@
       </c>
       <c r="M842" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="N842" s="2" t="n">
-        <v>46246.6616841088</v>
+        <v>46255.48540517361</v>
       </c>
       <c r="O842" s="1" t="n"/>
       <c r="P842" s="1" t="n"/>
       <c r="Q842" s="1" t="inlineStr"/>
       <c r="R842" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!
-Já foi atendido?</t>
+          <t>cobramos os documentos.</t>
         </is>
       </c>
       <c r="S842" s="1" t="inlineStr">
@@ -64863,227 +64880,6 @@
       </c>
       <c r="T842" s="1" t="n"/>
       <c r="U842" s="1" t="inlineStr"/>
-    </row>
-    <row r="843">
-      <c r="A843" s="1" t="n">
-        <v>82701</v>
-      </c>
-      <c r="B843" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C843" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D843" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E843" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde, por gentileza, providencias documentos de implantação da empresa: 7037 - EXPANDItens dispensáveis, por gentileza, sinalizar.</t>
-        </is>
-      </c>
-      <c r="F843" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G843" s="1" t="n"/>
-      <c r="H843" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="I843" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="J843" s="2" t="n">
-        <v>46253.71124814815</v>
-      </c>
-      <c r="K843" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="L843" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M843" s="1" t="inlineStr">
-        <is>
-          <t>Santos Karina</t>
-        </is>
-      </c>
-      <c r="N843" s="2" t="n">
-        <v>46255.46909065972</v>
-      </c>
-      <c r="O843" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="P843" s="1" t="n"/>
-      <c r="Q843" s="1" t="inlineStr"/>
-      <c r="R843" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CObramos os documentos </t>
-        </is>
-      </c>
-      <c r="S843" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T843" s="1" t="n"/>
-      <c r="U843" s="1" t="inlineStr"/>
-    </row>
-    <row r="844">
-      <c r="A844" s="1" t="n">
-        <v>82706</v>
-      </c>
-      <c r="B844" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C844" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D844" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E844" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde, por gentileza, providenciar documentos de implantação da empresa: 6978 - HEPA FILTROS.Itens dispensáveis, por gentileza, sinalizar.</t>
-        </is>
-      </c>
-      <c r="F844" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G844" s="1" t="n"/>
-      <c r="H844" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="I844" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="J844" s="2" t="n">
-        <v>46253.72086076389</v>
-      </c>
-      <c r="K844" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="L844" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M844" s="1" t="inlineStr">
-        <is>
-          <t>Santos Karina</t>
-        </is>
-      </c>
-      <c r="N844" s="2" t="n">
-        <v>46255.48540517361</v>
-      </c>
-      <c r="O844" s="1" t="n"/>
-      <c r="P844" s="1" t="n"/>
-      <c r="Q844" s="1" t="inlineStr"/>
-      <c r="R844" s="1" t="inlineStr">
-        <is>
-          <t>cobramos os documentos.</t>
-        </is>
-      </c>
-      <c r="S844" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T844" s="1" t="n"/>
-      <c r="U844" s="1" t="inlineStr"/>
-    </row>
-    <row r="845">
-      <c r="A845" s="1" t="n">
-        <v>81055</v>
-      </c>
-      <c r="B845" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C845" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D845" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E845" s="1" t="inlineStr">
-        <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
-        </is>
-      </c>
-      <c r="F845" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G845" s="1" t="n"/>
-      <c r="H845" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="I845" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="J845" s="2" t="n">
-        <v>46218.40379614583</v>
-      </c>
-      <c r="K845" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="L845" s="1" t="inlineStr">
-        <is>
-          <t>Devolvido</t>
-        </is>
-      </c>
-      <c r="M845" s="1" t="inlineStr">
-        <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
-      <c r="N845" s="1" t="n"/>
-      <c r="O845" s="2" t="n">
-        <v>46295</v>
-      </c>
-      <c r="P845" s="1" t="n"/>
-      <c r="Q845" s="1" t="inlineStr"/>
-      <c r="R845" s="1" t="inlineStr">
-        <is>
-          <t>Aguardando retorno dos dados do contador</t>
-        </is>
-      </c>
-      <c r="S845" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T845" s="1" t="n"/>
-      <c r="U845" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U851" headerRowCount="1">
-  <autoFilter ref="A1:U851"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U850" headerRowCount="1">
+  <autoFilter ref="A1:U850"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U851"/>
+  <dimension ref="A1:U850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -56481,39 +56481,39 @@
     </row>
     <row r="738">
       <c r="A738" s="1" t="n">
-        <v>84161</v>
+        <v>82810</v>
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Processo de VISA</t>
         </is>
       </c>
       <c r="C738" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Renovação</t>
         </is>
       </c>
       <c r="D738" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E738" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por gentileza, preciso do login e senha da prefeitura de Paulinia.</t>
+          <t>Cliente solicita renovação de alvará de funcionamento.</t>
         </is>
       </c>
       <c r="F738" s="1" t="n">
-        <v>3691</v>
+        <v>3759</v>
       </c>
       <c r="G738" s="1" t="inlineStr">
         <is>
-          <t>CUCINARE PRO ALIMENTAÇÃO LTDA (FILIAL 24)</t>
+          <t xml:space="preserve">MEDIC NET LTDA </t>
         </is>
       </c>
       <c r="H738" s="1" t="inlineStr">
         <is>
-          <t>Talita Silva</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I738" s="1" t="inlineStr">
@@ -56522,26 +56522,34 @@
         </is>
       </c>
       <c r="J738" s="2" t="n">
-        <v>46283.63162295139</v>
+        <v>46255.63596686342</v>
       </c>
       <c r="K738" s="2" t="n">
-        <v>46286</v>
+        <v>46258</v>
       </c>
       <c r="L738" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M738" s="1" t="inlineStr">
         <is>
-          <t>Stephanny Silva</t>
-        </is>
-      </c>
-      <c r="N738" s="1" t="n"/>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N738" s="2" t="n">
+        <v>46273.36963711806</v>
+      </c>
       <c r="O738" s="1" t="n"/>
       <c r="P738" s="1" t="n"/>
       <c r="Q738" s="1" t="inlineStr"/>
-      <c r="R738" s="1" t="inlineStr"/>
+      <c r="R738" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prezados(as), bom dia!
+Solicitação em andamento. 
+Atenciosamente, </t>
+        </is>
+      </c>
       <c r="S738" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -56552,7 +56560,7 @@
     </row>
     <row r="739">
       <c r="A739" s="1" t="n">
-        <v>82810</v>
+        <v>82809</v>
       </c>
       <c r="B739" s="1" t="inlineStr">
         <is>
@@ -56575,11 +56583,11 @@
         </is>
       </c>
       <c r="F739" s="1" t="n">
-        <v>3759</v>
+        <v>3760</v>
       </c>
       <c r="G739" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDIC NET LTDA </t>
+          <t xml:space="preserve">MED ALPHA DISTRIBUIDORA DE PRODUTOS MÉDICOS E HOSPITALARES EM GERAL LTDA </t>
         </is>
       </c>
       <c r="H739" s="1" t="inlineStr">
@@ -56593,7 +56601,7 @@
         </is>
       </c>
       <c r="J739" s="2" t="n">
-        <v>46255.63596686342</v>
+        <v>46255.63541871528</v>
       </c>
       <c r="K739" s="2" t="n">
         <v>46258</v>
@@ -56609,7 +56617,7 @@
         </is>
       </c>
       <c r="N739" s="2" t="n">
-        <v>46273.36963711806</v>
+        <v>46273.36949383102</v>
       </c>
       <c r="O739" s="1" t="n"/>
       <c r="P739" s="1" t="n"/>
@@ -56631,39 +56639,39 @@
     </row>
     <row r="740">
       <c r="A740" s="1" t="n">
-        <v>82809</v>
+        <v>84048</v>
       </c>
       <c r="B740" s="1" t="inlineStr">
         <is>
-          <t>Processo de VISA</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C740" s="1" t="inlineStr">
         <is>
-          <t>Renovação</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D740" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E740" s="1" t="inlineStr">
         <is>
-          <t>Cliente solicita renovação de alvará de funcionamento.</t>
+          <t>Boa tarde!Por gentileza providenciar a CND da Prefeitura.Obrigada.</t>
         </is>
       </c>
       <c r="F740" s="1" t="n">
-        <v>3760</v>
+        <v>3859</v>
       </c>
       <c r="G740" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED ALPHA DISTRIBUIDORA DE PRODUTOS MÉDICOS E HOSPITALARES EM GERAL LTDA </t>
+          <t>Montezanno Administração de Bens S.A.</t>
         </is>
       </c>
       <c r="H740" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I740" s="1" t="inlineStr">
@@ -56672,37 +56680,40 @@
         </is>
       </c>
       <c r="J740" s="2" t="n">
-        <v>46255.63541871528</v>
+        <v>46280.75768283565</v>
       </c>
       <c r="K740" s="2" t="n">
-        <v>46258</v>
+        <v>46281</v>
       </c>
       <c r="L740" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M740" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N740" s="2" t="n">
-        <v>46273.36949383102</v>
-      </c>
+          <t>Karine Gusmão</t>
+        </is>
+      </c>
+      <c r="N740" s="1" t="n"/>
       <c r="O740" s="1" t="n"/>
-      <c r="P740" s="1" t="n"/>
-      <c r="Q740" s="1" t="inlineStr"/>
+      <c r="P740" s="2" t="n">
+        <v>46286.39383434028</v>
+      </c>
+      <c r="Q740" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
       <c r="R740" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados(as), bom dia!
-Solicitação em andamento. 
-Atenciosamente, </t>
+          <t xml:space="preserve">Bom dia!
+A empresa não possui inscrição municipal. </t>
         </is>
       </c>
       <c r="S740" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T740" s="1" t="n"/>
@@ -56710,7 +56721,7 @@
     </row>
     <row r="741">
       <c r="A741" s="1" t="n">
-        <v>84048</v>
+        <v>81560</v>
       </c>
       <c r="B741" s="1" t="inlineStr">
         <is>
@@ -56719,7 +56730,7 @@
       </c>
       <c r="C741" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Divida Ativa ICMS</t>
         </is>
       </c>
       <c r="D741" s="1" t="inlineStr">
@@ -56729,20 +56740,20 @@
       </c>
       <c r="E741" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por gentileza providenciar a CND da Prefeitura.Obrigada.</t>
+          <t xml:space="preserve">Certidão de Débitos Estaduais (ICMS) </t>
         </is>
       </c>
       <c r="F741" s="1" t="n">
-        <v>3859</v>
+        <v>4091</v>
       </c>
       <c r="G741" s="1" t="inlineStr">
         <is>
-          <t>Montezanno Administração de Bens S.A.</t>
+          <t>NOBRES DOCES DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="H741" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I741" s="1" t="inlineStr">
@@ -56751,10 +56762,10 @@
         </is>
       </c>
       <c r="J741" s="2" t="n">
-        <v>46280.75768283565</v>
+        <v>46232.47750069445</v>
       </c>
       <c r="K741" s="2" t="n">
-        <v>46281</v>
+        <v>46234</v>
       </c>
       <c r="L741" s="1" t="inlineStr">
         <is>
@@ -56763,23 +56774,22 @@
       </c>
       <c r="M741" s="1" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N741" s="1" t="n"/>
       <c r="O741" s="1" t="n"/>
       <c r="P741" s="2" t="n">
-        <v>46286.39383434028</v>
+        <v>46233.73991982639</v>
       </c>
       <c r="Q741" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="R741" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia!
-A empresa não possui inscrição municipal. </t>
+          <t>Conforme e-mail do GM Fernando Sensulini, solicitação deve ser desconsiderada.</t>
         </is>
       </c>
       <c r="S741" s="1" t="inlineStr">
@@ -56792,7 +56802,7 @@
     </row>
     <row r="742">
       <c r="A742" s="1" t="n">
-        <v>81560</v>
+        <v>81561</v>
       </c>
       <c r="B742" s="1" t="inlineStr">
         <is>
@@ -56801,7 +56811,7 @@
       </c>
       <c r="C742" s="1" t="inlineStr">
         <is>
-          <t>Divida Ativa ICMS</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="D742" s="1" t="inlineStr">
@@ -56811,7 +56821,7 @@
       </c>
       <c r="E742" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Certidão de Débitos Estaduais (ICMS) </t>
+          <t>Certidão de Débitos Municipais (ISS)</t>
         </is>
       </c>
       <c r="F742" s="1" t="n">
@@ -56833,7 +56843,7 @@
         </is>
       </c>
       <c r="J742" s="2" t="n">
-        <v>46232.47750069445</v>
+        <v>46232.47807924769</v>
       </c>
       <c r="K742" s="2" t="n">
         <v>46234</v>
@@ -56851,7 +56861,7 @@
       <c r="N742" s="1" t="n"/>
       <c r="O742" s="1" t="n"/>
       <c r="P742" s="2" t="n">
-        <v>46233.73991982639</v>
+        <v>46233.74022094908</v>
       </c>
       <c r="Q742" s="1" t="inlineStr">
         <is>
@@ -56873,7 +56883,7 @@
     </row>
     <row r="743">
       <c r="A743" s="1" t="n">
-        <v>81561</v>
+        <v>81562</v>
       </c>
       <c r="B743" s="1" t="inlineStr">
         <is>
@@ -56892,7 +56902,7 @@
       </c>
       <c r="E743" s="1" t="inlineStr">
         <is>
-          <t>Certidão de Débitos Municipais (ISS)</t>
+          <t>Certidão Negativa de Débitos Federais (CND), abrangendo a Receita Federal e a Dívida Ativa da União.</t>
         </is>
       </c>
       <c r="F743" s="1" t="n">
@@ -56914,7 +56924,7 @@
         </is>
       </c>
       <c r="J743" s="2" t="n">
-        <v>46232.47807924769</v>
+        <v>46232.47872149305</v>
       </c>
       <c r="K743" s="2" t="n">
         <v>46234</v>
@@ -56932,7 +56942,7 @@
       <c r="N743" s="1" t="n"/>
       <c r="O743" s="1" t="n"/>
       <c r="P743" s="2" t="n">
-        <v>46233.74022094908</v>
+        <v>46233.74015570602</v>
       </c>
       <c r="Q743" s="1" t="inlineStr">
         <is>
@@ -56954,16 +56964,16 @@
     </row>
     <row r="744">
       <c r="A744" s="1" t="n">
-        <v>81562</v>
+        <v>84014</v>
       </c>
       <c r="B744" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C744" s="1" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D744" s="1" t="inlineStr">
@@ -56973,20 +56983,20 @@
       </c>
       <c r="E744" s="1" t="inlineStr">
         <is>
-          <t>Certidão Negativa de Débitos Federais (CND), abrangendo a Receita Federal e a Dívida Ativa da União.</t>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
         </is>
       </c>
       <c r="F744" s="1" t="n">
-        <v>4091</v>
+        <v>4178</v>
       </c>
       <c r="G744" s="1" t="inlineStr">
         <is>
-          <t>NOBRES DOCES DISTRIBUIDORA LTDA</t>
+          <t>SERFARMA DROGARIA LTDA</t>
         </is>
       </c>
       <c r="H744" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I744" s="1" t="inlineStr">
@@ -56995,10 +57005,10 @@
         </is>
       </c>
       <c r="J744" s="2" t="n">
-        <v>46232.47872149305</v>
+        <v>46280.47752337963</v>
       </c>
       <c r="K744" s="2" t="n">
-        <v>46234</v>
+        <v>46281</v>
       </c>
       <c r="L744" s="1" t="inlineStr">
         <is>
@@ -57007,22 +57017,22 @@
       </c>
       <c r="M744" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N744" s="1" t="n"/>
       <c r="O744" s="1" t="n"/>
       <c r="P744" s="2" t="n">
-        <v>46233.74015570602</v>
+        <v>46281.42727723379</v>
       </c>
       <c r="Q744" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="R744" s="1" t="inlineStr">
         <is>
-          <t>Conforme e-mail do GM Fernando Sensulini, solicitação deve ser desconsiderada.</t>
+          <t>Yasmin, segue levantamento de débitos na Prefeitura de Itapecerica da Serfarma, consta um ISS de 2023, segue guia atualizada com vencimento para hoje, 16/09/2026.</t>
         </is>
       </c>
       <c r="S744" s="1" t="inlineStr">
@@ -57035,39 +57045,39 @@
     </row>
     <row r="745">
       <c r="A745" s="1" t="n">
-        <v>84014</v>
+        <v>81601</v>
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Processo de VISA</t>
         </is>
       </c>
       <c r="C745" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Renovação</t>
         </is>
       </c>
       <c r="D745" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E745" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa BEST SALAD conforme solicitação do cliente.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F745" s="1" t="n">
-        <v>4178</v>
+        <v>4194</v>
       </c>
       <c r="G745" s="1" t="inlineStr">
         <is>
-          <t>SERFARMA DROGARIA LTDA</t>
+          <t>BEST SALAD HORTI FRUTI LTDA</t>
         </is>
       </c>
       <c r="H745" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I745" s="1" t="inlineStr">
@@ -57076,10 +57086,10 @@
         </is>
       </c>
       <c r="J745" s="2" t="n">
-        <v>46280.47752337963</v>
+        <v>46233.40595859953</v>
       </c>
       <c r="K745" s="2" t="n">
-        <v>46281</v>
+        <v>46237</v>
       </c>
       <c r="L745" s="1" t="inlineStr">
         <is>
@@ -57088,22 +57098,25 @@
       </c>
       <c r="M745" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N745" s="1" t="n"/>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N745" s="2" t="n">
+        <v>46234.48805347223</v>
+      </c>
       <c r="O745" s="1" t="n"/>
       <c r="P745" s="2" t="n">
-        <v>46281.42727723379</v>
+        <v>46237.37169996528</v>
       </c>
       <c r="Q745" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="R745" s="1" t="inlineStr">
         <is>
-          <t>Yasmin, segue levantamento de débitos na Prefeitura de Itapecerica da Serfarma, consta um ISS de 2023, segue guia atualizada com vencimento para hoje, 16/09/2026.</t>
+          <t>O sistema do VRE está com problemas, assim que disponível, concluímos o CLI.
+Atenciosamente,</t>
         </is>
       </c>
       <c r="S745" s="1" t="inlineStr">
@@ -57116,7 +57129,7 @@
     </row>
     <row r="746">
       <c r="A746" s="1" t="n">
-        <v>81601</v>
+        <v>81603</v>
       </c>
       <c r="B746" s="1" t="inlineStr">
         <is>
@@ -57135,15 +57148,15 @@
       </c>
       <c r="E746" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa BEST SALAD conforme solicitação do cliente.Grato,Bruno.</t>
+          <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa Terra Brasil conforme solicitação do cliente.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F746" s="1" t="n">
-        <v>4194</v>
+        <v>4195</v>
       </c>
       <c r="G746" s="1" t="inlineStr">
         <is>
-          <t>BEST SALAD HORTI FRUTI LTDA</t>
+          <t>TERRA BRASIL HORTI FRUTI LTDA</t>
         </is>
       </c>
       <c r="H746" s="1" t="inlineStr">
@@ -57157,7 +57170,7 @@
         </is>
       </c>
       <c r="J746" s="2" t="n">
-        <v>46233.40595859953</v>
+        <v>46233.40691574074</v>
       </c>
       <c r="K746" s="2" t="n">
         <v>46237</v>
@@ -57173,11 +57186,11 @@
         </is>
       </c>
       <c r="N746" s="2" t="n">
-        <v>46234.48805347223</v>
+        <v>46234.48788619213</v>
       </c>
       <c r="O746" s="1" t="n"/>
       <c r="P746" s="2" t="n">
-        <v>46237.37169996528</v>
+        <v>46240.39679517361</v>
       </c>
       <c r="Q746" s="1" t="inlineStr">
         <is>
@@ -57200,7 +57213,7 @@
     </row>
     <row r="747">
       <c r="A747" s="1" t="n">
-        <v>81603</v>
+        <v>83684</v>
       </c>
       <c r="B747" s="1" t="inlineStr">
         <is>
@@ -57214,12 +57227,12 @@
       </c>
       <c r="D747" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E747" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa Terra Brasil conforme solicitação do cliente.Grato,Bruno.</t>
+          <t xml:space="preserve">Por gentileza, providenciar renovação de alvará de funcionamento. </t>
         </is>
       </c>
       <c r="F747" s="1" t="n">
@@ -57241,10 +57254,10 @@
         </is>
       </c>
       <c r="J747" s="2" t="n">
-        <v>46233.40691574074</v>
+        <v>46273.73010833334</v>
       </c>
       <c r="K747" s="2" t="n">
-        <v>46237</v>
+        <v>46275</v>
       </c>
       <c r="L747" s="1" t="inlineStr">
         <is>
@@ -57256,12 +57269,10 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N747" s="2" t="n">
-        <v>46234.48788619213</v>
-      </c>
+      <c r="N747" s="1" t="n"/>
       <c r="O747" s="1" t="n"/>
       <c r="P747" s="2" t="n">
-        <v>46240.39679517361</v>
+        <v>46274.48608564815</v>
       </c>
       <c r="Q747" s="1" t="inlineStr">
         <is>
@@ -57269,97 +57280,92 @@
         </is>
       </c>
       <c r="R747" s="1" t="inlineStr">
-        <is>
-          <t>O sistema do VRE está com problemas, assim que disponível, concluímos o CLI.
-Atenciosamente,</t>
-        </is>
-      </c>
-      <c r="S747" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T747" s="1" t="n"/>
-      <c r="U747" s="1" t="inlineStr"/>
-    </row>
-    <row r="748">
-      <c r="A748" s="1" t="n">
-        <v>83684</v>
-      </c>
-      <c r="B748" s="1" t="inlineStr">
-        <is>
-          <t>Processo de VISA</t>
-        </is>
-      </c>
-      <c r="C748" s="1" t="inlineStr">
-        <is>
-          <t>Renovação</t>
-        </is>
-      </c>
-      <c r="D748" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E748" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por gentileza, providenciar renovação de alvará de funcionamento. </t>
-        </is>
-      </c>
-      <c r="F748" s="1" t="n">
-        <v>4195</v>
-      </c>
-      <c r="G748" s="1" t="inlineStr">
-        <is>
-          <t>TERRA BRASIL HORTI FRUTI LTDA</t>
-        </is>
-      </c>
-      <c r="H748" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
-      <c r="I748" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J748" s="2" t="n">
-        <v>46273.73010833334</v>
-      </c>
-      <c r="K748" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="L748" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M748" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N748" s="1" t="n"/>
-      <c r="O748" s="1" t="n"/>
-      <c r="P748" s="2" t="n">
-        <v>46274.48608564815</v>
-      </c>
-      <c r="Q748" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
-      <c r="R748" s="1" t="inlineStr">
         <is>
           <t>Bom dia.
 Email respondido hoje para a Patricia com Gerente Bruno em cópia.
 Atenciosamente,</t>
         </is>
       </c>
+      <c r="S747" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T747" s="1" t="n"/>
+      <c r="U747" s="1" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="n">
+        <v>84011</v>
+      </c>
+      <c r="B748" s="1" t="inlineStr">
+        <is>
+          <t>Levantamento de Débitos</t>
+        </is>
+      </c>
+      <c r="C748" s="1" t="inlineStr">
+        <is>
+          <t>Prefeitura</t>
+        </is>
+      </c>
+      <c r="D748" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E748" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+        </is>
+      </c>
+      <c r="F748" s="1" t="n">
+        <v>5398</v>
+      </c>
+      <c r="G748" s="1" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 07)</t>
+        </is>
+      </c>
+      <c r="H748" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I748" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J748" s="2" t="n">
+        <v>46280.47591111111</v>
+      </c>
+      <c r="K748" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="L748" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M748" s="1" t="inlineStr">
+        <is>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N748" s="2" t="n">
+        <v>46281.50318923611</v>
+      </c>
+      <c r="O748" s="1" t="n"/>
+      <c r="P748" s="1" t="n"/>
+      <c r="Q748" s="1" t="inlineStr"/>
+      <c r="R748" s="1" t="inlineStr">
+        <is>
+          <t>Certidão será solicitada presencialmente.</t>
+        </is>
+      </c>
       <c r="S748" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T748" s="1" t="n"/>
@@ -57367,16 +57373,16 @@
     </row>
     <row r="749">
       <c r="A749" s="1" t="n">
-        <v>84011</v>
+        <v>81565</v>
       </c>
       <c r="B749" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C749" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D749" s="1" t="inlineStr">
@@ -57386,20 +57392,20 @@
       </c>
       <c r="E749" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Certidão de Débitos Municipais (ISS)</t>
         </is>
       </c>
       <c r="F749" s="1" t="n">
-        <v>5398</v>
+        <v>5488</v>
       </c>
       <c r="G749" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 07)</t>
+          <t>GMP DISTRIBUIDORA DE DOCES LTDA</t>
         </is>
       </c>
       <c r="H749" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I749" s="1" t="inlineStr">
@@ -57408,35 +57414,39 @@
         </is>
       </c>
       <c r="J749" s="2" t="n">
-        <v>46280.47591111111</v>
+        <v>46232.47982982639</v>
       </c>
       <c r="K749" s="2" t="n">
-        <v>46281</v>
+        <v>46234</v>
       </c>
       <c r="L749" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M749" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N749" s="2" t="n">
-        <v>46281.50318923611</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N749" s="1" t="n"/>
       <c r="O749" s="1" t="n"/>
-      <c r="P749" s="1" t="n"/>
-      <c r="Q749" s="1" t="inlineStr"/>
+      <c r="P749" s="2" t="n">
+        <v>46233.74043113426</v>
+      </c>
+      <c r="Q749" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="R749" s="1" t="inlineStr">
         <is>
-          <t>Certidão será solicitada presencialmente.</t>
+          <t>Conforme e-mail do GM Fernando Sensulini, solicitação deve ser desconsiderada.</t>
         </is>
       </c>
       <c r="S749" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T749" s="1" t="n"/>
@@ -57444,7 +57454,7 @@
     </row>
     <row r="750">
       <c r="A750" s="1" t="n">
-        <v>81565</v>
+        <v>81566</v>
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
@@ -57453,7 +57463,7 @@
       </c>
       <c r="C750" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="D750" s="1" t="inlineStr">
@@ -57463,7 +57473,7 @@
       </c>
       <c r="E750" s="1" t="inlineStr">
         <is>
-          <t>Certidão de Débitos Municipais (ISS)</t>
+          <t>Certidão Negativa de Débitos Federais (CND), abrangendo a Receita Federal e a Dívida Ativa da União.</t>
         </is>
       </c>
       <c r="F750" s="1" t="n">
@@ -57485,7 +57495,7 @@
         </is>
       </c>
       <c r="J750" s="2" t="n">
-        <v>46232.47982982639</v>
+        <v>46232.48020107639</v>
       </c>
       <c r="K750" s="2" t="n">
         <v>46234</v>
@@ -57503,7 +57513,7 @@
       <c r="N750" s="1" t="n"/>
       <c r="O750" s="1" t="n"/>
       <c r="P750" s="2" t="n">
-        <v>46233.74043113426</v>
+        <v>46233.74078938657</v>
       </c>
       <c r="Q750" s="1" t="inlineStr">
         <is>
@@ -57525,7 +57535,7 @@
     </row>
     <row r="751">
       <c r="A751" s="1" t="n">
-        <v>81566</v>
+        <v>84133</v>
       </c>
       <c r="B751" s="1" t="inlineStr">
         <is>
@@ -57534,7 +57544,7 @@
       </c>
       <c r="C751" s="1" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D751" s="1" t="inlineStr">
@@ -57544,20 +57554,20 @@
       </c>
       <c r="E751" s="1" t="inlineStr">
         <is>
-          <t>Certidão Negativa de Débitos Federais (CND), abrangendo a Receita Federal e a Dívida Ativa da União.</t>
+          <t>Bom dia!Por gentileza disponibilizar a certidão municipal da empresa 5512.Obrigada.</t>
         </is>
       </c>
       <c r="F751" s="1" t="n">
-        <v>5488</v>
+        <v>5512</v>
       </c>
       <c r="G751" s="1" t="inlineStr">
         <is>
-          <t>GMP DISTRIBUIDORA DE DOCES LTDA</t>
+          <t>PROGRESSO ADMINISTRADORA DE BENS PROPRIOS LTDA</t>
         </is>
       </c>
       <c r="H751" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I751" s="1" t="inlineStr">
@@ -57566,39 +57576,29 @@
         </is>
       </c>
       <c r="J751" s="2" t="n">
-        <v>46232.48020107639</v>
+        <v>46283.37417395833</v>
       </c>
       <c r="K751" s="2" t="n">
-        <v>46234</v>
+        <v>46286</v>
       </c>
       <c r="L751" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M751" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="N751" s="1" t="n"/>
       <c r="O751" s="1" t="n"/>
-      <c r="P751" s="2" t="n">
-        <v>46233.74078938657</v>
-      </c>
-      <c r="Q751" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
-      <c r="R751" s="1" t="inlineStr">
-        <is>
-          <t>Conforme e-mail do GM Fernando Sensulini, solicitação deve ser desconsiderada.</t>
-        </is>
-      </c>
+      <c r="P751" s="1" t="n"/>
+      <c r="Q751" s="1" t="inlineStr"/>
+      <c r="R751" s="1" t="inlineStr"/>
       <c r="S751" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T751" s="1" t="n"/>
@@ -57606,39 +57606,39 @@
     </row>
     <row r="752">
       <c r="A752" s="1" t="n">
-        <v>84133</v>
+        <v>83339</v>
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C752" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D752" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E752" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Por gentileza disponibilizar a certidão municipal da empresa 5512.Obrigada.</t>
+          <t>Alteração contratual do QSA da empresa: 5589-ACS COMERCIO E SERVIÇOS DE MANUTENÇÃO LTDAGrupo: AntoconProposta já negociada no valor de R$1.800,00Substituição do atual sócio Sra LEANDRO SEBASTIÃO SIQUEIRA, faz-se necessária substituição do QSA para LUCIANA MARIA SIQUEIRA.</t>
         </is>
       </c>
       <c r="F752" s="1" t="n">
-        <v>5512</v>
+        <v>5589</v>
       </c>
       <c r="G752" s="1" t="inlineStr">
         <is>
-          <t>PROGRESSO ADMINISTRADORA DE BENS PROPRIOS LTDA</t>
+          <t>ACS COMÉRCIO E SERVIÇOS DE MANUTENÇÃO LTDA</t>
         </is>
       </c>
       <c r="H752" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I752" s="1" t="inlineStr">
@@ -57647,108 +57647,118 @@
         </is>
       </c>
       <c r="J752" s="2" t="n">
-        <v>46283.37417395833</v>
+        <v>46266.5560746875</v>
       </c>
       <c r="K752" s="2" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="L752" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M752" s="1" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
-        </is>
-      </c>
-      <c r="N752" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N752" s="2" t="n">
+        <v>46274.56034679398</v>
+      </c>
       <c r="O752" s="1" t="n"/>
       <c r="P752" s="1" t="n"/>
       <c r="Q752" s="1" t="inlineStr"/>
-      <c r="R752" s="1" t="inlineStr"/>
-      <c r="S752" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T752" s="1" t="n"/>
-      <c r="U752" s="1" t="inlineStr"/>
-    </row>
-    <row r="753">
-      <c r="A753" s="1" t="n">
-        <v>83339</v>
-      </c>
-      <c r="B753" s="1" t="inlineStr">
-        <is>
-          <t>Alteração Contratual</t>
-        </is>
-      </c>
-      <c r="C753" s="1" t="inlineStr">
-        <is>
-          <t>Sócios</t>
-        </is>
-      </c>
-      <c r="D753" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E753" s="1" t="inlineStr">
-        <is>
-          <t>Alteração contratual do QSA da empresa: 5589-ACS COMERCIO E SERVIÇOS DE MANUTENÇÃO LTDAGrupo: AntoconProposta já negociada no valor de R$1.800,00Substituição do atual sócio Sra LEANDRO SEBASTIÃO SIQUEIRA, faz-se necessária substituição do QSA para LUCIANA MARIA SIQUEIRA.</t>
-        </is>
-      </c>
-      <c r="F753" s="1" t="n">
-        <v>5589</v>
-      </c>
-      <c r="G753" s="1" t="inlineStr">
-        <is>
-          <t>ACS COMÉRCIO E SERVIÇOS DE MANUTENÇÃO LTDA</t>
-        </is>
-      </c>
-      <c r="H753" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
-      <c r="I753" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J753" s="2" t="n">
-        <v>46266.5560746875</v>
-      </c>
-      <c r="K753" s="2" t="n">
-        <v>46294</v>
-      </c>
-      <c r="L753" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M753" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N753" s="2" t="n">
-        <v>46274.56034679398</v>
-      </c>
-      <c r="O753" s="1" t="n"/>
-      <c r="P753" s="1" t="n"/>
-      <c r="Q753" s="1" t="inlineStr"/>
-      <c r="R753" s="1" t="inlineStr">
+      <c r="R752" s="1" t="inlineStr">
         <is>
           <t>Prezados(as), boa tarde!
 Alteração contratual em andamento, conforme solicitado.
 Atenciosamente,</t>
         </is>
       </c>
+      <c r="S752" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T752" s="1" t="n"/>
+      <c r="U752" s="1" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="n">
+        <v>82763</v>
+      </c>
+      <c r="B753" s="1" t="inlineStr">
+        <is>
+          <t>Certidão</t>
+        </is>
+      </c>
+      <c r="C753" s="1" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="D753" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E753" s="1" t="inlineStr">
+        <is>
+          <t>Prezados,Boa tarde!Por gentileza, providenciar CND Federal, Estadual e Municipal da empresa 5640-Comercial Prado.Grato,Bruno.</t>
+        </is>
+      </c>
+      <c r="F753" s="1" t="n">
+        <v>5640</v>
+      </c>
+      <c r="G753" s="1" t="inlineStr">
+        <is>
+          <t>COMERCIAL PRADO - MATERIAL DE CONSTRUCAO LTDA</t>
+        </is>
+      </c>
+      <c r="H753" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I753" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J753" s="2" t="n">
+        <v>46254.72416542824</v>
+      </c>
+      <c r="K753" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="L753" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M753" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N753" s="1" t="n"/>
+      <c r="O753" s="1" t="n"/>
+      <c r="P753" s="2" t="n">
+        <v>46255.48925019676</v>
+      </c>
+      <c r="Q753" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R753" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seguem certidões referente ao cliente 5640 - COMERCIAL PRADO, conforme solicitado. </t>
+        </is>
+      </c>
       <c r="S753" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T753" s="1" t="n"/>
@@ -57756,39 +57766,39 @@
     </row>
     <row r="754">
       <c r="A754" s="1" t="n">
-        <v>82763</v>
+        <v>83611</v>
       </c>
       <c r="B754" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C754" s="1" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D754" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E754" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Boa tarde!Por gentileza, providenciar CND Federal, Estadual e Municipal da empresa 5640-Comercial Prado.Grato,Bruno.</t>
+          <t>Boa tarde!!Por gentileza, realizar levantamento de débitos federais. E gerar guia de pagamento para o dia 09/09.</t>
         </is>
       </c>
       <c r="F754" s="1" t="n">
-        <v>5640</v>
+        <v>5661</v>
       </c>
       <c r="G754" s="1" t="inlineStr">
         <is>
-          <t>COMERCIAL PRADO - MATERIAL DE CONSTRUCAO LTDA</t>
+          <t>ELETRICA IPOJUCA LTDA</t>
         </is>
       </c>
       <c r="H754" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I754" s="1" t="inlineStr">
@@ -57797,10 +57807,10 @@
         </is>
       </c>
       <c r="J754" s="2" t="n">
-        <v>46254.72416542824</v>
+        <v>46269.51044244213</v>
       </c>
       <c r="K754" s="2" t="n">
-        <v>46255</v>
+        <v>46274</v>
       </c>
       <c r="L754" s="1" t="inlineStr">
         <is>
@@ -57809,22 +57819,24 @@
       </c>
       <c r="M754" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N754" s="1" t="n"/>
       <c r="O754" s="1" t="n"/>
       <c r="P754" s="2" t="n">
-        <v>46255.48925019676</v>
+        <v>46274.49946655093</v>
       </c>
       <c r="Q754" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="R754" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguem certidões referente ao cliente 5640 - COMERCIAL PRADO, conforme solicitado. </t>
+          <t>Yasmin, bom dia!
+Segue, em anexo, a situação fiscal. Há impostos em aberto; solicitar aos departamentos responsáveis o recálculo.
+Referente aos parcelamentos em aberto, nosso sistema irá iniciar o envio amanhã</t>
         </is>
       </c>
       <c r="S754" s="1" t="inlineStr">
@@ -57837,7 +57849,7 @@
     </row>
     <row r="755">
       <c r="A755" s="1" t="n">
-        <v>83611</v>
+        <v>83613</v>
       </c>
       <c r="B755" s="1" t="inlineStr">
         <is>
@@ -57856,20 +57868,20 @@
       </c>
       <c r="E755" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!!Por gentileza, realizar levantamento de débitos federais. E gerar guia de pagamento para o dia 09/09.</t>
+          <t>Boa tarde!!Por gentileza, realizar levantamento de débitos federais. E gerar guia de pagamento para o dia 09/09</t>
         </is>
       </c>
       <c r="F755" s="1" t="n">
-        <v>5661</v>
+        <v>5662</v>
       </c>
       <c r="G755" s="1" t="inlineStr">
         <is>
-          <t>ELETRICA IPOJUCA LTDA</t>
+          <t>COMERCIAL DE MATERIAIS ELETRICOS MM LTDA</t>
         </is>
       </c>
       <c r="H755" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I755" s="1" t="inlineStr">
@@ -57878,7 +57890,7 @@
         </is>
       </c>
       <c r="J755" s="2" t="n">
-        <v>46269.51044244213</v>
+        <v>46269.51153171296</v>
       </c>
       <c r="K755" s="2" t="n">
         <v>46274</v>
@@ -57896,18 +57908,17 @@
       <c r="N755" s="1" t="n"/>
       <c r="O755" s="1" t="n"/>
       <c r="P755" s="2" t="n">
-        <v>46274.49946655093</v>
+        <v>46269.70410119213</v>
       </c>
       <c r="Q755" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="R755" s="1" t="inlineStr">
         <is>
-          <t>Yasmin, bom dia!
-Segue, em anexo, a situação fiscal. Há impostos em aberto; solicitar aos departamentos responsáveis o recálculo.
-Referente aos parcelamentos em aberto, nosso sistema irá iniciar o envio amanhã</t>
+          <t>Por gentileza enviar a cópia do documento sócio responsável abaixo, para cadastro no regularize, para emissão dos débitos inscritos em dívida ativa.
+JOSE UMBERTO BORGES DA SILVA</t>
         </is>
       </c>
       <c r="S755" s="1" t="inlineStr">
@@ -57920,39 +57931,39 @@
     </row>
     <row r="756">
       <c r="A756" s="1" t="n">
-        <v>83613</v>
+        <v>83307</v>
       </c>
       <c r="B756" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C756" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Objeto Social</t>
         </is>
       </c>
       <c r="D756" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E756" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!!Por gentileza, realizar levantamento de débitos federais. E gerar guia de pagamento para o dia 09/09</t>
+          <t>Inclusão dos CNAEs 5911-1-99, 7319-0-99 e 7312-2-00.</t>
         </is>
       </c>
       <c r="F756" s="1" t="n">
-        <v>5662</v>
+        <v>5680</v>
       </c>
       <c r="G756" s="1" t="inlineStr">
         <is>
-          <t>COMERCIAL DE MATERIAIS ELETRICOS MM LTDA</t>
+          <t>UNIVERSO DAS COISINHAS E-COMMERCE LTDA</t>
         </is>
       </c>
       <c r="H756" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I756" s="1" t="inlineStr">
@@ -57961,40 +57972,35 @@
         </is>
       </c>
       <c r="J756" s="2" t="n">
-        <v>46269.51153171296</v>
+        <v>46266.37445135417</v>
       </c>
       <c r="K756" s="2" t="n">
-        <v>46274</v>
+        <v>46269</v>
       </c>
       <c r="L756" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M756" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N756" s="1" t="n"/>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N756" s="2" t="n">
+        <v>46273.6798315162</v>
+      </c>
       <c r="O756" s="1" t="n"/>
-      <c r="P756" s="2" t="n">
-        <v>46269.70410119213</v>
-      </c>
-      <c r="Q756" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P756" s="1" t="n"/>
+      <c r="Q756" s="1" t="inlineStr"/>
       <c r="R756" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza enviar a cópia do documento sócio responsável abaixo, para cadastro no regularize, para emissão dos débitos inscritos em dívida ativa.
-JOSE UMBERTO BORGES DA SILVA</t>
+          <t>Processo em elaboração</t>
         </is>
       </c>
       <c r="S756" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T756" s="1" t="n"/>
@@ -58002,39 +58008,39 @@
     </row>
     <row r="757">
       <c r="A757" s="1" t="n">
-        <v>83307</v>
+        <v>82780</v>
       </c>
       <c r="B757" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C757" s="1" t="inlineStr">
         <is>
-          <t>Objeto Social</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D757" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E757" s="1" t="inlineStr">
         <is>
-          <t>Inclusão dos CNAEs 5911-1-99, 7319-0-99 e 7312-2-00.</t>
+          <t>Olá, Boa tarde!!!A empresa 5880, não possui senhas salvas para consulta de NFSE ou encerramento, poderiam verificar?</t>
         </is>
       </c>
       <c r="F757" s="1" t="n">
-        <v>5680</v>
+        <v>5880</v>
       </c>
       <c r="G757" s="1" t="inlineStr">
         <is>
-          <t>UNIVERSO DAS COISINHAS E-COMMERCE LTDA</t>
+          <t>Cucinare Pro Alimentacao LTDA (Filial 86)</t>
         </is>
       </c>
       <c r="H757" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Talita Silva</t>
         </is>
       </c>
       <c r="I757" s="1" t="inlineStr">
@@ -58043,30 +58049,29 @@
         </is>
       </c>
       <c r="J757" s="2" t="n">
-        <v>46266.37445135417</v>
+        <v>46255.43914973379</v>
       </c>
       <c r="K757" s="2" t="n">
-        <v>46269</v>
+        <v>46262</v>
       </c>
       <c r="L757" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M757" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N757" s="2" t="n">
-        <v>46273.6798315162</v>
-      </c>
+          <t>Eduardo Lopes</t>
+        </is>
+      </c>
+      <c r="N757" s="1" t="n"/>
       <c r="O757" s="1" t="n"/>
       <c r="P757" s="1" t="n"/>
       <c r="Q757" s="1" t="inlineStr"/>
       <c r="R757" s="1" t="inlineStr">
         <is>
-          <t>Processo em elaboração</t>
+          <t>Boa tarde!
+Estou verificando o acesso junto a prefeitura.</t>
         </is>
       </c>
       <c r="S757" s="1" t="inlineStr">
@@ -58079,39 +58084,39 @@
     </row>
     <row r="758">
       <c r="A758" s="1" t="n">
-        <v>82780</v>
+        <v>82000</v>
       </c>
       <c r="B758" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Restituição</t>
         </is>
       </c>
       <c r="C758" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D758" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E758" s="1" t="inlineStr">
         <is>
-          <t>Olá, Boa tarde!!!A empresa 5880, não possui senhas salvas para consulta de NFSE ou encerramento, poderiam verificar?</t>
+          <t>Prezados, boa tarde!O gerente Eduardo Aparicio está me perguntando se foi solicitado a reembolso referente a ICMS Difal que a empresa ITA pagou para o Estado do Ceará referente a NF 13436, que o posto fiscal deixou a mercadoria presa, pois alegam que eles deveriam pagar por essa mercadoria, e para o cliente deles não cancelar a compra, porém a mercadoria enviada é isenta de ICMS em ambito nacional e por esse motivo estão solicitando que abra um processo para reembolso do pagamento indevido dessa GNRE.</t>
         </is>
       </c>
       <c r="F758" s="1" t="n">
-        <v>5880</v>
+        <v>5885</v>
       </c>
       <c r="G758" s="1" t="inlineStr">
         <is>
-          <t>Cucinare Pro Alimentacao LTDA (Filial 86)</t>
+          <t>INSTITUTO DE TECNOLOGIA ASSISTIVA LTDA</t>
         </is>
       </c>
       <c r="H758" s="1" t="inlineStr">
         <is>
-          <t>Talita Silva</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I758" s="1" t="inlineStr">
@@ -58120,113 +58125,118 @@
         </is>
       </c>
       <c r="J758" s="2" t="n">
-        <v>46255.43914973379</v>
+        <v>46240.64507523148</v>
       </c>
       <c r="K758" s="2" t="n">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="L758" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M758" s="1" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
-        </is>
-      </c>
-      <c r="N758" s="1" t="n"/>
+          <t>Rodrigo Rego</t>
+        </is>
+      </c>
+      <c r="N758" s="2" t="n">
+        <v>46269.68263113426</v>
+      </c>
       <c r="O758" s="1" t="n"/>
       <c r="P758" s="1" t="n"/>
       <c r="Q758" s="1" t="inlineStr"/>
       <c r="R758" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!
-Estou verificando o acesso junto a prefeitura.</t>
-        </is>
-      </c>
-      <c r="S758" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T758" s="1" t="n"/>
-      <c r="U758" s="1" t="inlineStr"/>
-    </row>
-    <row r="759">
-      <c r="A759" s="1" t="n">
-        <v>82000</v>
-      </c>
-      <c r="B759" s="1" t="inlineStr">
-        <is>
-          <t>Restituição</t>
-        </is>
-      </c>
-      <c r="C759" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="D759" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E759" s="1" t="inlineStr">
-        <is>
-          <t>Prezados, boa tarde!O gerente Eduardo Aparicio está me perguntando se foi solicitado a reembolso referente a ICMS Difal que a empresa ITA pagou para o Estado do Ceará referente a NF 13436, que o posto fiscal deixou a mercadoria presa, pois alegam que eles deveriam pagar por essa mercadoria, e para o cliente deles não cancelar a compra, porém a mercadoria enviada é isenta de ICMS em ambito nacional e por esse motivo estão solicitando que abra um processo para reembolso do pagamento indevido dessa GNRE.</t>
-        </is>
-      </c>
-      <c r="F759" s="1" t="n">
-        <v>5885</v>
-      </c>
-      <c r="G759" s="1" t="inlineStr">
-        <is>
-          <t>INSTITUTO DE TECNOLOGIA ASSISTIVA LTDA</t>
-        </is>
-      </c>
-      <c r="H759" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="I759" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J759" s="2" t="n">
-        <v>46240.64507523148</v>
-      </c>
-      <c r="K759" s="2" t="n">
-        <v>46244</v>
-      </c>
-      <c r="L759" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M759" s="1" t="inlineStr">
-        <is>
-          <t>Rodrigo Rego</t>
-        </is>
-      </c>
-      <c r="N759" s="2" t="n">
-        <v>46269.68263113426</v>
-      </c>
-      <c r="O759" s="1" t="n"/>
-      <c r="P759" s="1" t="n"/>
-      <c r="Q759" s="1" t="inlineStr"/>
-      <c r="R759" s="1" t="inlineStr">
-        <is>
           <t>Rodrigo, 
 Segue proposta para protocolo do pedido de restituição.
 Obs. Não recebemos solicitação anteriormente sobre essa questão. GM solicitou para quem?</t>
         </is>
       </c>
+      <c r="S758" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T758" s="1" t="n"/>
+      <c r="U758" s="1" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="n">
+        <v>81845</v>
+      </c>
+      <c r="B759" s="1" t="inlineStr">
+        <is>
+          <t>Parcelamento PGFN</t>
+        </is>
+      </c>
+      <c r="C759" s="1" t="inlineStr">
+        <is>
+          <t>Simples Nacional</t>
+        </is>
+      </c>
+      <c r="D759" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E759" s="1" t="inlineStr">
+        <is>
+          <t>Prezados,Boa tarde! Por gentileza, providenciar simulação de parcelamento dos débitos federais da empresa 5908-Merch Link em 36 e 60 parcelas para análise e aceite do cliente.Desde já agradeço o apoio.</t>
+        </is>
+      </c>
+      <c r="F759" s="1" t="n">
+        <v>5908</v>
+      </c>
+      <c r="G759" s="1" t="inlineStr">
+        <is>
+          <t>MERCH LINK LTDA</t>
+        </is>
+      </c>
+      <c r="H759" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I759" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J759" s="2" t="n">
+        <v>46238.57314429398</v>
+      </c>
+      <c r="K759" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="L759" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M759" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N759" s="1" t="n"/>
+      <c r="O759" s="1" t="n"/>
+      <c r="P759" s="2" t="n">
+        <v>46238.62655219907</v>
+      </c>
+      <c r="Q759" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R759" s="1" t="inlineStr">
+        <is>
+          <t>Simulado e proposta enviados por email ao GC Bruno.</t>
+        </is>
+      </c>
       <c r="S759" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T759" s="1" t="n"/>
@@ -58234,39 +58244,39 @@
     </row>
     <row r="760">
       <c r="A760" s="1" t="n">
-        <v>81845</v>
+        <v>82811</v>
       </c>
       <c r="B760" s="1" t="inlineStr">
         <is>
-          <t>Parcelamento PGFN</t>
+          <t>Processo de VISA</t>
         </is>
       </c>
       <c r="C760" s="1" t="inlineStr">
         <is>
-          <t>Simples Nacional</t>
+          <t>Renovação</t>
         </is>
       </c>
       <c r="D760" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E760" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Boa tarde! Por gentileza, providenciar simulação de parcelamento dos débitos federais da empresa 5908-Merch Link em 36 e 60 parcelas para análise e aceite do cliente.Desde já agradeço o apoio.</t>
+          <t>Cliente solicita renovação de alvará de funcionamento.</t>
         </is>
       </c>
       <c r="F760" s="1" t="n">
-        <v>5908</v>
+        <v>5923</v>
       </c>
       <c r="G760" s="1" t="inlineStr">
         <is>
-          <t>MERCH LINK LTDA</t>
+          <t>ALUSMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
         </is>
       </c>
       <c r="H760" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I760" s="1" t="inlineStr">
@@ -58275,39 +58285,37 @@
         </is>
       </c>
       <c r="J760" s="2" t="n">
-        <v>46238.57314429398</v>
+        <v>46255.63641273148</v>
       </c>
       <c r="K760" s="2" t="n">
-        <v>46240</v>
+        <v>46258</v>
       </c>
       <c r="L760" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M760" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N760" s="1" t="n"/>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N760" s="2" t="n">
+        <v>46273.36977268518</v>
+      </c>
       <c r="O760" s="1" t="n"/>
-      <c r="P760" s="2" t="n">
-        <v>46238.62655219907</v>
-      </c>
-      <c r="Q760" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P760" s="1" t="n"/>
+      <c r="Q760" s="1" t="inlineStr"/>
       <c r="R760" s="1" t="inlineStr">
         <is>
-          <t>Simulado e proposta enviados por email ao GC Bruno.</t>
+          <t xml:space="preserve">Prezados(as), bom dia!
+Solicitação em andamento. 
+Atenciosamente, </t>
         </is>
       </c>
       <c r="S760" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T760" s="1" t="n"/>
@@ -58315,7 +58323,7 @@
     </row>
     <row r="761">
       <c r="A761" s="1" t="n">
-        <v>82811</v>
+        <v>82812</v>
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
@@ -58338,11 +58346,11 @@
         </is>
       </c>
       <c r="F761" s="1" t="n">
-        <v>5923</v>
+        <v>5924</v>
       </c>
       <c r="G761" s="1" t="inlineStr">
         <is>
-          <t>ALUSMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
+          <t>LUSMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
         </is>
       </c>
       <c r="H761" s="1" t="inlineStr">
@@ -58356,7 +58364,7 @@
         </is>
       </c>
       <c r="J761" s="2" t="n">
-        <v>46255.63641273148</v>
+        <v>46255.63676828704</v>
       </c>
       <c r="K761" s="2" t="n">
         <v>46258</v>
@@ -58372,7 +58380,7 @@
         </is>
       </c>
       <c r="N761" s="2" t="n">
-        <v>46273.36977268518</v>
+        <v>46273.37007592592</v>
       </c>
       <c r="O761" s="1" t="n"/>
       <c r="P761" s="1" t="n"/>
@@ -58394,7 +58402,7 @@
     </row>
     <row r="762">
       <c r="A762" s="1" t="n">
-        <v>82812</v>
+        <v>82813</v>
       </c>
       <c r="B762" s="1" t="inlineStr">
         <is>
@@ -58417,11 +58425,11 @@
         </is>
       </c>
       <c r="F762" s="1" t="n">
-        <v>5924</v>
+        <v>5925</v>
       </c>
       <c r="G762" s="1" t="inlineStr">
         <is>
-          <t>LUSMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
+          <t>LIVMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
         </is>
       </c>
       <c r="H762" s="1" t="inlineStr">
@@ -58435,7 +58443,7 @@
         </is>
       </c>
       <c r="J762" s="2" t="n">
-        <v>46255.63676828704</v>
+        <v>46255.63725177084</v>
       </c>
       <c r="K762" s="2" t="n">
         <v>46258</v>
@@ -58451,7 +58459,7 @@
         </is>
       </c>
       <c r="N762" s="2" t="n">
-        <v>46273.37007592592</v>
+        <v>46273.37023221065</v>
       </c>
       <c r="O762" s="1" t="n"/>
       <c r="P762" s="1" t="n"/>
@@ -58473,7 +58481,7 @@
     </row>
     <row r="763">
       <c r="A763" s="1" t="n">
-        <v>82813</v>
+        <v>82814</v>
       </c>
       <c r="B763" s="1" t="inlineStr">
         <is>
@@ -58496,11 +58504,11 @@
         </is>
       </c>
       <c r="F763" s="1" t="n">
-        <v>5925</v>
+        <v>5926</v>
       </c>
       <c r="G763" s="1" t="inlineStr">
         <is>
-          <t>LIVMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
+          <t>HHMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
         </is>
       </c>
       <c r="H763" s="1" t="inlineStr">
@@ -58514,7 +58522,7 @@
         </is>
       </c>
       <c r="J763" s="2" t="n">
-        <v>46255.63725177084</v>
+        <v>46255.63768873842</v>
       </c>
       <c r="K763" s="2" t="n">
         <v>46258</v>
@@ -58530,7 +58538,7 @@
         </is>
       </c>
       <c r="N763" s="2" t="n">
-        <v>46273.37023221065</v>
+        <v>46273.37038981482</v>
       </c>
       <c r="O763" s="1" t="n"/>
       <c r="P763" s="1" t="n"/>
@@ -58552,39 +58560,39 @@
     </row>
     <row r="764">
       <c r="A764" s="1" t="n">
-        <v>82814</v>
+        <v>83752</v>
       </c>
       <c r="B764" s="1" t="inlineStr">
         <is>
-          <t>Processo de VISA</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C764" s="1" t="inlineStr">
         <is>
-          <t>Renovação</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D764" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E764" s="1" t="inlineStr">
         <is>
-          <t>Cliente solicita renovação de alvará de funcionamento.</t>
+          <t>Prezados, Boa tarde! Por gentileza, elaborar proposta para abertura de uma nova empresa do grupo Seu Góis.No aguardo.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F764" s="1" t="n">
-        <v>5926</v>
+        <v>5929</v>
       </c>
       <c r="G764" s="1" t="inlineStr">
         <is>
-          <t>HHMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
+          <t>BAR E RESTAURANTE 1566 LTDA</t>
         </is>
       </c>
       <c r="H764" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I764" s="1" t="inlineStr">
@@ -58593,37 +58601,39 @@
         </is>
       </c>
       <c r="J764" s="2" t="n">
-        <v>46255.63768873842</v>
+        <v>46274.70572450232</v>
       </c>
       <c r="K764" s="2" t="n">
-        <v>46258</v>
+        <v>46276</v>
       </c>
       <c r="L764" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M764" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N764" s="2" t="n">
-        <v>46273.37038981482</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N764" s="1" t="n"/>
       <c r="O764" s="1" t="n"/>
-      <c r="P764" s="1" t="n"/>
-      <c r="Q764" s="1" t="inlineStr"/>
+      <c r="P764" s="2" t="n">
+        <v>46276.61454390046</v>
+      </c>
+      <c r="Q764" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="R764" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados(as), bom dia!
-Solicitação em andamento. 
-Atenciosamente, </t>
+          <t>Segue proposta.</t>
         </is>
       </c>
       <c r="S764" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T764" s="1" t="n"/>
@@ -58631,16 +58641,16 @@
     </row>
     <row r="765">
       <c r="A765" s="1" t="n">
-        <v>83752</v>
+        <v>83765</v>
       </c>
       <c r="B765" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C765" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Comércio</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D765" s="1" t="inlineStr">
@@ -58650,20 +58660,20 @@
       </c>
       <c r="E765" s="1" t="inlineStr">
         <is>
-          <t>Prezados, Boa tarde! Por gentileza, elaborar proposta para abertura de uma nova empresa do grupo Seu Góis.No aguardo.Grato,Bruno.</t>
+          <t xml:space="preserve">Bom dia, por gentileza encaminhar TFE </t>
         </is>
       </c>
       <c r="F765" s="1" t="n">
-        <v>5929</v>
+        <v>6065</v>
       </c>
       <c r="G765" s="1" t="inlineStr">
         <is>
-          <t>BAR E RESTAURANTE 1566 LTDA</t>
+          <t xml:space="preserve">PS3 INSTALACOES E MONTAGENS LTDA </t>
         </is>
       </c>
       <c r="H765" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I765" s="1" t="inlineStr">
@@ -58672,7 +58682,7 @@
         </is>
       </c>
       <c r="J765" s="2" t="n">
-        <v>46274.70572450232</v>
+        <v>46275.36535266204</v>
       </c>
       <c r="K765" s="2" t="n">
         <v>46276</v>
@@ -58684,22 +58694,22 @@
       </c>
       <c r="M765" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N765" s="1" t="n"/>
       <c r="O765" s="1" t="n"/>
       <c r="P765" s="2" t="n">
-        <v>46276.61454390046</v>
+        <v>46280.78301616898</v>
       </c>
       <c r="Q765" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="R765" s="1" t="inlineStr">
         <is>
-          <t>Segue proposta.</t>
+          <t>Boa noite! Segue em anexo.</t>
         </is>
       </c>
       <c r="S765" s="1" t="inlineStr">
@@ -58712,7 +58722,7 @@
     </row>
     <row r="766">
       <c r="A766" s="1" t="n">
-        <v>83765</v>
+        <v>82751</v>
       </c>
       <c r="B766" s="1" t="inlineStr">
         <is>
@@ -58721,7 +58731,7 @@
       </c>
       <c r="C766" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Protestos</t>
         </is>
       </c>
       <c r="D766" s="1" t="inlineStr">
@@ -58731,20 +58741,20 @@
       </c>
       <c r="E766" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, por gentileza encaminhar TFE </t>
+          <t xml:space="preserve">O cliente informou que recebeu o protesto referente a Taxa de fiscalização. Por gentileza verificar se há pendência em aberto e se é possível emitir a guia para pagamento. </t>
         </is>
       </c>
       <c r="F766" s="1" t="n">
-        <v>6065</v>
+        <v>6077</v>
       </c>
       <c r="G766" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS3 INSTALACOES E MONTAGENS LTDA </t>
+          <t xml:space="preserve">DELLON DIOVANI SOARES </t>
         </is>
       </c>
       <c r="H766" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I766" s="1" t="inlineStr">
@@ -58753,10 +58763,10 @@
         </is>
       </c>
       <c r="J766" s="2" t="n">
-        <v>46275.36535266204</v>
+        <v>46254.65013561342</v>
       </c>
       <c r="K766" s="2" t="n">
-        <v>46276</v>
+        <v>46255</v>
       </c>
       <c r="L766" s="1" t="inlineStr">
         <is>
@@ -58768,19 +58778,21 @@
           <t>Beatriz Rangel</t>
         </is>
       </c>
-      <c r="N766" s="1" t="n"/>
+      <c r="N766" s="2" t="n">
+        <v>46255.48898734953</v>
+      </c>
       <c r="O766" s="1" t="n"/>
       <c r="P766" s="2" t="n">
-        <v>46280.78301616898</v>
+        <v>46283.44702604166</v>
       </c>
       <c r="Q766" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="R766" s="1" t="inlineStr">
         <is>
-          <t>Boa noite! Segue em anexo.</t>
+          <t>Aguardando liberação do cartório para emissão da guia na PM de Itaquaquecetuba</t>
         </is>
       </c>
       <c r="S766" s="1" t="inlineStr">
@@ -58793,34 +58805,34 @@
     </row>
     <row r="767">
       <c r="A767" s="1" t="n">
-        <v>82751</v>
+        <v>81209</v>
       </c>
       <c r="B767" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Processo de Prefeitura</t>
         </is>
       </c>
       <c r="C767" s="1" t="inlineStr">
         <is>
-          <t>Protestos</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="D767" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E767" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">O cliente informou que recebeu o protesto referente a Taxa de fiscalização. Por gentileza verificar se há pendência em aberto e se é possível emitir a guia para pagamento. </t>
+          <t>Cliente cancelou NFS-e posterior a emissão da guia de ISS no mês de junho e emitiu notas fiscais em junho com competência em maio, informado ao GC do ocorrido, o qual solicitou que o cliente cancelasse as notas emitidas na competência errada e que já esta encerrada e emitisse corretamente na competência de junho, contudo esta prefeitura (Itapetininga) não é possível cancelar as guias geradas de forma remota sendo necessário protocolar pessoalmente no balcão do setor de protocolos.</t>
         </is>
       </c>
       <c r="F767" s="1" t="n">
-        <v>6077</v>
+        <v>6094</v>
       </c>
       <c r="G767" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">DELLON DIOVANI SOARES </t>
+          <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
         </is>
       </c>
       <c r="H767" s="1" t="inlineStr">
@@ -58834,41 +58846,31 @@
         </is>
       </c>
       <c r="J767" s="2" t="n">
-        <v>46254.65013561342</v>
+        <v>46223.52088677084</v>
       </c>
       <c r="K767" s="2" t="n">
-        <v>46255</v>
+        <v>46224</v>
       </c>
       <c r="L767" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M767" s="1" t="inlineStr">
-        <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M767" s="1" t="n"/>
       <c r="N767" s="2" t="n">
-        <v>46255.48898734953</v>
+        <v>46232.72821697917</v>
       </c>
       <c r="O767" s="1" t="n"/>
-      <c r="P767" s="2" t="n">
-        <v>46283.44702604166</v>
-      </c>
-      <c r="Q767" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P767" s="1" t="n"/>
+      <c r="Q767" s="1" t="inlineStr"/>
       <c r="R767" s="1" t="inlineStr">
         <is>
-          <t>Aguardando liberação do cartório para emissão da guia na PM de Itaquaquecetuba</t>
+          <t>Enviado ao cliente procuração para assinatura.</t>
         </is>
       </c>
       <c r="S767" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T767" s="1" t="n"/>
@@ -58876,34 +58878,34 @@
     </row>
     <row r="768">
       <c r="A768" s="1" t="n">
-        <v>81209</v>
+        <v>83775</v>
       </c>
       <c r="B768" s="1" t="inlineStr">
         <is>
-          <t>Processo de Prefeitura</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C768" s="1" t="inlineStr">
         <is>
-          <t>Geral</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D768" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E768" s="1" t="inlineStr">
         <is>
-          <t>Cliente cancelou NFS-e posterior a emissão da guia de ISS no mês de junho e emitiu notas fiscais em junho com competência em maio, informado ao GC do ocorrido, o qual solicitou que o cliente cancelasse as notas emitidas na competência errada e que já esta encerrada e emitisse corretamente na competência de junho, contudo esta prefeitura (Itapetininga) não é possível cancelar as guias geradas de forma remota sendo necessário protocolar pessoalmente no balcão do setor de protocolos.</t>
+          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos Federais. </t>
         </is>
       </c>
       <c r="F768" s="1" t="n">
-        <v>6094</v>
+        <v>5020</v>
       </c>
       <c r="G768" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
+          <t>M GOMES CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="H768" s="1" t="inlineStr">
@@ -58917,31 +58919,39 @@
         </is>
       </c>
       <c r="J768" s="2" t="n">
-        <v>46223.52088677084</v>
+        <v>46275.43249725694</v>
       </c>
       <c r="K768" s="2" t="n">
-        <v>46224</v>
+        <v>46276</v>
       </c>
       <c r="L768" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M768" s="1" t="n"/>
-      <c r="N768" s="2" t="n">
-        <v>46232.72821697917</v>
-      </c>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M768" s="1" t="inlineStr">
+        <is>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N768" s="1" t="n"/>
       <c r="O768" s="1" t="n"/>
-      <c r="P768" s="1" t="n"/>
-      <c r="Q768" s="1" t="inlineStr"/>
+      <c r="P768" s="2" t="n">
+        <v>46275.80605767361</v>
+      </c>
+      <c r="Q768" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="R768" s="1" t="inlineStr">
         <is>
-          <t>Enviado ao cliente procuração para assinatura.</t>
+          <t>Não há débitos federais em aberto, segue certidão negativa.</t>
         </is>
       </c>
       <c r="S768" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T768" s="1" t="n"/>
@@ -58949,7 +58959,7 @@
     </row>
     <row r="769">
       <c r="A769" s="1" t="n">
-        <v>83775</v>
+        <v>83776</v>
       </c>
       <c r="B769" s="1" t="inlineStr">
         <is>
@@ -58958,7 +58968,7 @@
       </c>
       <c r="C769" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D769" s="1" t="inlineStr">
@@ -58968,7 +58978,7 @@
       </c>
       <c r="E769" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos Federais. </t>
+          <t>Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos Estaduais.</t>
         </is>
       </c>
       <c r="F769" s="1" t="n">
@@ -58990,7 +59000,7 @@
         </is>
       </c>
       <c r="J769" s="2" t="n">
-        <v>46275.43249725694</v>
+        <v>46275.43319429398</v>
       </c>
       <c r="K769" s="2" t="n">
         <v>46276</v>
@@ -59008,7 +59018,7 @@
       <c r="N769" s="1" t="n"/>
       <c r="O769" s="1" t="n"/>
       <c r="P769" s="2" t="n">
-        <v>46275.80605767361</v>
+        <v>46275.80373197917</v>
       </c>
       <c r="Q769" s="1" t="inlineStr">
         <is>
@@ -59017,7 +59027,7 @@
       </c>
       <c r="R769" s="1" t="inlineStr">
         <is>
-          <t>Não há débitos federais em aberto, segue certidão negativa.</t>
+          <t>Não há débitos estaduais em aberto, seguem certidões negativas.</t>
         </is>
       </c>
       <c r="S769" s="1" t="inlineStr">
@@ -59030,7 +59040,7 @@
     </row>
     <row r="770">
       <c r="A770" s="1" t="n">
-        <v>83776</v>
+        <v>83777</v>
       </c>
       <c r="B770" s="1" t="inlineStr">
         <is>
@@ -59039,7 +59049,7 @@
       </c>
       <c r="C770" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D770" s="1" t="inlineStr">
@@ -59049,7 +59059,7 @@
       </c>
       <c r="E770" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos Estaduais.</t>
+          <t>Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos da Prefeitura.</t>
         </is>
       </c>
       <c r="F770" s="1" t="n">
@@ -59071,7 +59081,7 @@
         </is>
       </c>
       <c r="J770" s="2" t="n">
-        <v>46275.43319429398</v>
+        <v>46275.43366273148</v>
       </c>
       <c r="K770" s="2" t="n">
         <v>46276</v>
@@ -59089,7 +59099,7 @@
       <c r="N770" s="1" t="n"/>
       <c r="O770" s="1" t="n"/>
       <c r="P770" s="2" t="n">
-        <v>46275.80373197917</v>
+        <v>46275.80130501158</v>
       </c>
       <c r="Q770" s="1" t="inlineStr">
         <is>
@@ -59098,7 +59108,7 @@
       </c>
       <c r="R770" s="1" t="inlineStr">
         <is>
-          <t>Não há débitos estaduais em aberto, seguem certidões negativas.</t>
+          <t>Não há débitos, segue certidão negativa.</t>
         </is>
       </c>
       <c r="S770" s="1" t="inlineStr">
@@ -59111,39 +59121,39 @@
     </row>
     <row r="771">
       <c r="A771" s="1" t="n">
-        <v>83777</v>
+        <v>82909</v>
       </c>
       <c r="B771" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C771" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D771" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="E771" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos da Prefeitura.</t>
+          <t>ALTERAÇÃO DO ENDEREÇO E OBJETO SOCIAL CONFORME VIABILIDADE.</t>
         </is>
       </c>
       <c r="F771" s="1" t="n">
-        <v>5020</v>
+        <v>5048</v>
       </c>
       <c r="G771" s="1" t="inlineStr">
         <is>
-          <t>M GOMES CONSULTORIA LTDA</t>
+          <t>UNIFORTE DO BRASIL COMÉRCIO ATACADISTA DE EMBALAGENS LTDA</t>
         </is>
       </c>
       <c r="H771" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I771" s="1" t="inlineStr">
@@ -59152,39 +59162,37 @@
         </is>
       </c>
       <c r="J771" s="2" t="n">
-        <v>46275.43366273148</v>
+        <v>46258.68138819445</v>
       </c>
       <c r="K771" s="2" t="n">
-        <v>46276</v>
+        <v>46259</v>
       </c>
       <c r="L771" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M771" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N771" s="1" t="n"/>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
+      <c r="N771" s="2" t="n">
+        <v>46261.36105216435</v>
+      </c>
       <c r="O771" s="1" t="n"/>
-      <c r="P771" s="2" t="n">
-        <v>46275.80130501158</v>
-      </c>
-      <c r="Q771" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P771" s="1" t="n"/>
+      <c r="Q771" s="1" t="inlineStr"/>
       <c r="R771" s="1" t="inlineStr">
         <is>
-          <t>Não há débitos, segue certidão negativa.</t>
+          <t>Bom dia 
+Preparando a minuta.
+Atenciosamente,</t>
         </is>
       </c>
       <c r="S771" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T771" s="1" t="n"/>
@@ -59192,51 +59200,51 @@
     </row>
     <row r="772">
       <c r="A772" s="1" t="n">
-        <v>82909</v>
+        <v>83650</v>
       </c>
       <c r="B772" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C772" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D772" s="1" t="inlineStr">
         <is>
+          <t>GERENCIA MASTER</t>
+        </is>
+      </c>
+      <c r="E772" s="1" t="inlineStr">
+        <is>
+          <t>Abertura de nova empresa do grupo 5050-MARECHAL Tributação: Lucro Presumido Proposta já negociada no valor de: R$ 2.500,00Razão Social: Opção 1: RESTAURANTE E LANCHONETE MARECHAL LTDAObjeto Social: FORNECIMENTO DE REFEIÇÕES - RESTAURANTE, ORGANIZAÇÃO DE EVENTOSCapital social de R$ 50.000,00</t>
+        </is>
+      </c>
+      <c r="F772" s="1" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G772" s="1" t="inlineStr">
+        <is>
+          <t>HIPERMERCADO MARECHAL LTDA</t>
+        </is>
+      </c>
+      <c r="H772" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
+      <c r="I772" s="1" t="inlineStr">
+        <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="E772" s="1" t="inlineStr">
-        <is>
-          <t>ALTERAÇÃO DO ENDEREÇO E OBJETO SOCIAL CONFORME VIABILIDADE.</t>
-        </is>
-      </c>
-      <c r="F772" s="1" t="n">
-        <v>5048</v>
-      </c>
-      <c r="G772" s="1" t="inlineStr">
-        <is>
-          <t>UNIFORTE DO BRASIL COMÉRCIO ATACADISTA DE EMBALAGENS LTDA</t>
-        </is>
-      </c>
-      <c r="H772" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
-      <c r="I772" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
       <c r="J772" s="2" t="n">
-        <v>46258.68138819445</v>
+        <v>46273.5154474537</v>
       </c>
       <c r="K772" s="2" t="n">
-        <v>46259</v>
+        <v>46301</v>
       </c>
       <c r="L772" s="1" t="inlineStr">
         <is>
@@ -59245,104 +59253,108 @@
       </c>
       <c r="M772" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N772" s="2" t="n">
-        <v>46261.36105216435</v>
+        <v>46275.42730894676</v>
       </c>
       <c r="O772" s="1" t="n"/>
       <c r="P772" s="1" t="n"/>
       <c r="Q772" s="1" t="inlineStr"/>
       <c r="R772" s="1" t="inlineStr">
         <is>
-          <t>Bom dia 
-Preparando a minuta.
-Atenciosamente,</t>
-        </is>
-      </c>
-      <c r="S772" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T772" s="1" t="n"/>
-      <c r="U772" s="1" t="inlineStr"/>
-    </row>
-    <row r="773">
-      <c r="A773" s="1" t="n">
-        <v>83650</v>
-      </c>
-      <c r="B773" s="1" t="inlineStr">
-        <is>
-          <t>Abertura de Empresa</t>
-        </is>
-      </c>
-      <c r="C773" s="1" t="inlineStr">
-        <is>
-          <t>Sociedade - Comércio</t>
-        </is>
-      </c>
-      <c r="D773" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E773" s="1" t="inlineStr">
-        <is>
-          <t>Abertura de nova empresa do grupo 5050-MARECHAL Tributação: Lucro Presumido Proposta já negociada no valor de: R$ 2.500,00Razão Social: Opção 1: RESTAURANTE E LANCHONETE MARECHAL LTDAObjeto Social: FORNECIMENTO DE REFEIÇÕES - RESTAURANTE, ORGANIZAÇÃO DE EVENTOSCapital social de R$ 50.000,00</t>
-        </is>
-      </c>
-      <c r="F773" s="1" t="n">
-        <v>5050</v>
-      </c>
-      <c r="G773" s="1" t="inlineStr">
-        <is>
-          <t>HIPERMERCADO MARECHAL LTDA</t>
-        </is>
-      </c>
-      <c r="H773" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
-      <c r="I773" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J773" s="2" t="n">
-        <v>46273.5154474537</v>
-      </c>
-      <c r="K773" s="2" t="n">
-        <v>46301</v>
-      </c>
-      <c r="L773" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M773" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N773" s="2" t="n">
-        <v>46275.42730894676</v>
-      </c>
-      <c r="O773" s="1" t="n"/>
-      <c r="P773" s="1" t="n"/>
-      <c r="Q773" s="1" t="inlineStr"/>
-      <c r="R773" s="1" t="inlineStr">
-        <is>
           <t>Bom dia,
 minuta em andamento
 Atenciosamente,</t>
         </is>
       </c>
+      <c r="S772" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T772" s="1" t="n"/>
+      <c r="U772" s="1" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="1" t="n">
+        <v>83714</v>
+      </c>
+      <c r="B773" s="1" t="inlineStr">
+        <is>
+          <t>Certidão</t>
+        </is>
+      </c>
+      <c r="C773" s="1" t="inlineStr">
+        <is>
+          <t>Trabalhista</t>
+        </is>
+      </c>
+      <c r="D773" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E773" s="1" t="inlineStr">
+        <is>
+          <t>Por gentileza, providenciar CLI, certidões federais, municipais, estaduais e trabalhistas da empresa 5100</t>
+        </is>
+      </c>
+      <c r="F773" s="1" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G773" s="1" t="inlineStr">
+        <is>
+          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
+        </is>
+      </c>
+      <c r="H773" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="I773" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J773" s="2" t="n">
+        <v>46274.44445876157</v>
+      </c>
+      <c r="K773" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="L773" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M773" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N773" s="1" t="n"/>
+      <c r="O773" s="1" t="n"/>
+      <c r="P773" s="2" t="n">
+        <v>46281.63185188657</v>
+      </c>
+      <c r="Q773" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R773" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde!
+CLI não se enquadra para esta empresa. Segue pesquisas federal, estadual e certidão trabalhista.
+A certidão municipal, fiz a solicitação e estou aguardando</t>
+        </is>
+      </c>
       <c r="S773" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T773" s="1" t="n"/>
@@ -59350,16 +59362,16 @@
     </row>
     <row r="774">
       <c r="A774" s="1" t="n">
-        <v>83714</v>
+        <v>84010</v>
       </c>
       <c r="B774" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C774" s="1" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D774" s="1" t="inlineStr">
@@ -59369,20 +59381,20 @@
       </c>
       <c r="E774" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar CLI, certidões federais, municipais, estaduais e trabalhistas da empresa 5100</t>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
         </is>
       </c>
       <c r="F774" s="1" t="n">
-        <v>5100</v>
+        <v>5118</v>
       </c>
       <c r="G774" s="1" t="inlineStr">
         <is>
-          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 06)</t>
         </is>
       </c>
       <c r="H774" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I774" s="1" t="inlineStr">
@@ -59391,10 +59403,10 @@
         </is>
       </c>
       <c r="J774" s="2" t="n">
-        <v>46274.44445876157</v>
+        <v>46280.47515841435</v>
       </c>
       <c r="K774" s="2" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="L774" s="1" t="inlineStr">
         <is>
@@ -59403,24 +59415,22 @@
       </c>
       <c r="M774" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N774" s="1" t="n"/>
       <c r="O774" s="1" t="n"/>
       <c r="P774" s="2" t="n">
-        <v>46281.63185188657</v>
+        <v>46283.43439984954</v>
       </c>
       <c r="Q774" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="R774" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!
-CLI não se enquadra para esta empresa. Segue pesquisas federal, estadual e certidão trabalhista.
-A certidão municipal, fiz a solicitação e estou aguardando</t>
+          <t>Situação regular das filiais do município de São Paulo, segue certidão negativa.</t>
         </is>
       </c>
       <c r="S774" s="1" t="inlineStr">
@@ -59433,11 +59443,11 @@
     </row>
     <row r="775">
       <c r="A775" s="1" t="n">
-        <v>84010</v>
+        <v>84205</v>
       </c>
       <c r="B775" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C775" s="1" t="inlineStr">
@@ -59447,66 +59457,52 @@
       </c>
       <c r="D775" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E775" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Cliente necessita de regularização de cadastro municipal pois não foi realizado em sua ultima alteração de contrato social.</t>
         </is>
       </c>
       <c r="F775" s="1" t="n">
-        <v>5118</v>
+        <v>5144</v>
       </c>
       <c r="G775" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 06)</t>
-        </is>
-      </c>
-      <c r="H775" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+          <t>CASA DE ESFIHA E SALGADOS AKIEBON LTDA</t>
+        </is>
+      </c>
+      <c r="H775" s="1" t="n"/>
       <c r="I775" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J775" s="2" t="n">
-        <v>46280.47515841435</v>
+        <v>46286.47680138889</v>
       </c>
       <c r="K775" s="2" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="L775" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M775" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Romero Borges</t>
         </is>
       </c>
       <c r="N775" s="1" t="n"/>
       <c r="O775" s="1" t="n"/>
-      <c r="P775" s="2" t="n">
-        <v>46283.43439984954</v>
-      </c>
-      <c r="Q775" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="R775" s="1" t="inlineStr">
-        <is>
-          <t>Situação regular das filiais do município de São Paulo, segue certidão negativa.</t>
-        </is>
-      </c>
+      <c r="P775" s="1" t="n"/>
+      <c r="Q775" s="1" t="inlineStr"/>
+      <c r="R775" s="1" t="n"/>
       <c r="S775" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T775" s="1" t="n"/>
@@ -59514,11 +59510,11 @@
     </row>
     <row r="776">
       <c r="A776" s="1" t="n">
-        <v>84205</v>
+        <v>84240</v>
       </c>
       <c r="B776" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C776" s="1" t="inlineStr">
@@ -59528,20 +59524,20 @@
       </c>
       <c r="D776" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E776" s="1" t="inlineStr">
         <is>
-          <t>Cliente necessita de regularização de cadastro municipal pois não foi realizado em sua ultima alteração de contrato social.</t>
+          <t>Boa tarde,Preciso do login e senha da prefeitura de Valinhos, não consigo acessar com o que já existe nos dados da loja.</t>
         </is>
       </c>
       <c r="F776" s="1" t="n">
-        <v>5144</v>
+        <v>4287</v>
       </c>
       <c r="G776" s="1" t="inlineStr">
         <is>
-          <t>CASA DE ESFIHA E SALGADOS AKIEBON LTDA</t>
+          <t>CUCINARE PRO ALIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="H776" s="1" t="n"/>
@@ -59551,10 +59547,10 @@
         </is>
       </c>
       <c r="J776" s="2" t="n">
-        <v>46286.47680138889</v>
+        <v>46286.77992762731</v>
       </c>
       <c r="K776" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="L776" s="1" t="inlineStr">
         <is>
@@ -59563,7 +59559,7 @@
       </c>
       <c r="M776" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
+          <t>Stephanny Silva</t>
         </is>
       </c>
       <c r="N776" s="1" t="n"/>
@@ -59581,145 +59577,161 @@
     </row>
     <row r="777">
       <c r="A777" s="1" t="n">
-        <v>84240</v>
+        <v>83703</v>
       </c>
       <c r="B777" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C777" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Razão Social</t>
         </is>
       </c>
       <c r="D777" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="E777" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde,Preciso do login e senha da prefeitura de Valinhos, não consigo acessar com o que já existe nos dados da loja.</t>
+          <t>SVG GROUP EMPREENDIMENTOS E PARTICIPAÇÕES S.ACNPJ: 38.042.809/0001-59 Alteração:JSVG COMPANY EMPREENDIMENTOS E PARTICIPAÇÕES S.A</t>
         </is>
       </c>
       <c r="F777" s="1" t="n">
-        <v>4287</v>
+        <v>4295</v>
       </c>
       <c r="G777" s="1" t="inlineStr">
         <is>
-          <t>CUCINARE PRO ALIMENTACAO LTDA</t>
-        </is>
-      </c>
-      <c r="H777" s="1" t="n"/>
+          <t>SVG GROUP EMPREENDIMENTOS E PARTICIPAÇÕES S.A</t>
+        </is>
+      </c>
+      <c r="H777" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Ribeiro</t>
+        </is>
+      </c>
       <c r="I777" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J777" s="2" t="n">
-        <v>46286.77992762731</v>
+        <v>46274.42515038195</v>
       </c>
       <c r="K777" s="2" t="n">
-        <v>46289</v>
+        <v>46275</v>
       </c>
       <c r="L777" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M777" s="1" t="inlineStr">
         <is>
-          <t>Stephanny Silva</t>
-        </is>
-      </c>
-      <c r="N777" s="1" t="n"/>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
+      <c r="N777" s="2" t="n">
+        <v>46274.79132711806</v>
+      </c>
       <c r="O777" s="1" t="n"/>
       <c r="P777" s="1" t="n"/>
       <c r="Q777" s="1" t="inlineStr"/>
-      <c r="R777" s="1" t="n"/>
-      <c r="S777" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T777" s="1" t="n"/>
-      <c r="U777" s="1" t="inlineStr"/>
-    </row>
-    <row r="778">
-      <c r="A778" s="1" t="n">
-        <v>83703</v>
-      </c>
-      <c r="B778" s="1" t="inlineStr">
-        <is>
-          <t>Alteração Contratual</t>
-        </is>
-      </c>
-      <c r="C778" s="1" t="inlineStr">
-        <is>
-          <t>Razão Social</t>
-        </is>
-      </c>
-      <c r="D778" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="E778" s="1" t="inlineStr">
-        <is>
-          <t>SVG GROUP EMPREENDIMENTOS E PARTICIPAÇÕES S.ACNPJ: 38.042.809/0001-59 Alteração:JSVG COMPANY EMPREENDIMENTOS E PARTICIPAÇÕES S.A</t>
-        </is>
-      </c>
-      <c r="F778" s="1" t="n">
-        <v>4295</v>
-      </c>
-      <c r="G778" s="1" t="inlineStr">
-        <is>
-          <t>SVG GROUP EMPREENDIMENTOS E PARTICIPAÇÕES S.A</t>
-        </is>
-      </c>
-      <c r="H778" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
-      <c r="I778" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J778" s="2" t="n">
-        <v>46274.42515038195</v>
-      </c>
-      <c r="K778" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="L778" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M778" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
-      <c r="N778" s="2" t="n">
-        <v>46274.79132711806</v>
-      </c>
-      <c r="O778" s="1" t="n"/>
-      <c r="P778" s="1" t="n"/>
-      <c r="Q778" s="1" t="inlineStr"/>
-      <c r="R778" s="1" t="inlineStr">
+      <c r="R777" s="1" t="inlineStr">
         <is>
           <t>Prezados(as), boa tarde!
 Alteração contratual em andamento, conforme solicitado.
 Atenciosamente,</t>
         </is>
       </c>
+      <c r="S777" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T777" s="1" t="n"/>
+      <c r="U777" s="1" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="1" t="n">
+        <v>84004</v>
+      </c>
+      <c r="B778" s="1" t="inlineStr">
+        <is>
+          <t>Levantamento de Débitos</t>
+        </is>
+      </c>
+      <c r="C778" s="1" t="inlineStr">
+        <is>
+          <t>Prefeitura</t>
+        </is>
+      </c>
+      <c r="D778" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E778" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+        </is>
+      </c>
+      <c r="F778" s="1" t="n">
+        <v>4357</v>
+      </c>
+      <c r="G778" s="1" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 04)</t>
+        </is>
+      </c>
+      <c r="H778" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I778" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J778" s="2" t="n">
+        <v>46280.47172650463</v>
+      </c>
+      <c r="K778" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="L778" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M778" s="1" t="inlineStr">
+        <is>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N778" s="2" t="n">
+        <v>46280.72251597222</v>
+      </c>
+      <c r="O778" s="1" t="n"/>
+      <c r="P778" s="2" t="n">
+        <v>46283.44246041666</v>
+      </c>
+      <c r="Q778" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R778" s="1" t="inlineStr">
+        <is>
+          <t>Solicitado à Prefeitura levantamento de débitos atualizado, aguardando.</t>
+        </is>
+      </c>
       <c r="S778" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T778" s="1" t="n"/>
@@ -59727,11 +59739,11 @@
     </row>
     <row r="779">
       <c r="A779" s="1" t="n">
-        <v>84004</v>
+        <v>81970</v>
       </c>
       <c r="B779" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C779" s="1" t="inlineStr">
@@ -59741,25 +59753,25 @@
       </c>
       <c r="D779" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E779" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Efetuar a atualização do cadastro da prefeitura para o novo modelo do Gissonline</t>
         </is>
       </c>
       <c r="F779" s="1" t="n">
-        <v>4357</v>
+        <v>4414</v>
       </c>
       <c r="G779" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 04)</t>
+          <t>HN LEONE ADMINISTRAÇÃO DE BENS LTDA</t>
         </is>
       </c>
       <c r="H779" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I779" s="1" t="inlineStr">
@@ -59768,41 +59780,37 @@
         </is>
       </c>
       <c r="J779" s="2" t="n">
-        <v>46280.47172650463</v>
+        <v>46240.4986315162</v>
       </c>
       <c r="K779" s="2" t="n">
-        <v>46281</v>
+        <v>46244</v>
       </c>
       <c r="L779" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M779" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="N779" s="2" t="n">
-        <v>46280.72251597222</v>
+        <v>46244.66312627315</v>
       </c>
       <c r="O779" s="1" t="n"/>
-      <c r="P779" s="2" t="n">
-        <v>46283.44246041666</v>
-      </c>
-      <c r="Q779" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P779" s="1" t="n"/>
+      <c r="Q779" s="1" t="inlineStr"/>
       <c r="R779" s="1" t="inlineStr">
         <is>
-          <t>Solicitado à Prefeitura levantamento de débitos atualizado, aguardando.</t>
+          <t xml:space="preserve">Prezados(as), boa tarde!
+Para ciência, empresa já possui os dados para cesso, entretanto, não possuímos. Neste caso, estamos em contato com cliente, favor aguardar retorno. 
+Atenciosamente, </t>
         </is>
       </c>
       <c r="S779" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T779" s="1" t="n"/>
@@ -59810,75 +59818,63 @@
     </row>
     <row r="780">
       <c r="A780" s="1" t="n">
-        <v>81970</v>
+        <v>84290</v>
       </c>
       <c r="B780" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Notificação</t>
         </is>
       </c>
       <c r="C780" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D780" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E780" s="1" t="inlineStr">
         <is>
-          <t>Efetuar a atualização do cadastro da prefeitura para o novo modelo do Gissonline</t>
+          <t>por gentileza, providenciar contrato social da empresa 6179 - ITALO BRASILEIRA</t>
         </is>
       </c>
       <c r="F780" s="1" t="n">
-        <v>4414</v>
+        <v>6179</v>
       </c>
       <c r="G780" s="1" t="inlineStr">
         <is>
-          <t>HN LEONE ADMINISTRAÇÃO DE BENS LTDA</t>
-        </is>
-      </c>
-      <c r="H780" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
+          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="H780" s="1" t="n"/>
       <c r="I780" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J780" s="2" t="n">
-        <v>46240.4986315162</v>
+        <v>46287.49436180555</v>
       </c>
       <c r="K780" s="2" t="n">
-        <v>46244</v>
+        <v>46288</v>
       </c>
       <c r="L780" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M780" s="1" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
-        </is>
-      </c>
-      <c r="N780" s="2" t="n">
-        <v>46244.66312627315</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N780" s="1" t="n"/>
       <c r="O780" s="1" t="n"/>
       <c r="P780" s="1" t="n"/>
       <c r="Q780" s="1" t="inlineStr"/>
-      <c r="R780" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prezados(as), boa tarde!
-Para ciência, empresa já possui os dados para cesso, entretanto, não possuímos. Neste caso, estamos em contato com cliente, favor aguardar retorno. 
-Atenciosamente, </t>
-        </is>
-      </c>
+      <c r="R780" s="1" t="n"/>
       <c r="S780" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -59889,26 +59885,26 @@
     </row>
     <row r="781">
       <c r="A781" s="1" t="n">
-        <v>84290</v>
+        <v>82236</v>
       </c>
       <c r="B781" s="1" t="inlineStr">
         <is>
-          <t>Notificação</t>
+          <t>Inuitilização de Nota Fiscais</t>
         </is>
       </c>
       <c r="C781" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="D781" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E781" s="1" t="inlineStr">
         <is>
-          <t>por gentileza, providenciar contrato social da empresa 6179 - ITALO BRASILEIRA</t>
+          <t>Informado pelo cliente sequencia de Cupons que foram indevidamente emitidos. Confirmado com equipe fiscal que todos os cupons estão ativos e foram escriturados no mês 06. Se faz necessário processo de cancelamento extemporâneo tendo em vista o prazo limite ser 30 minutos.Processo conversado com o Gerente Master Reynaldo segundo ele cliente está ciente que este processo gera proposta de serviços extraordinários.Favor manter o contato com o cliente Guilherme (11) 99991-9311 ou Gabriela (11) 99797-6771Relação dos cupons informados pelo cliente estão no anexo.</t>
         </is>
       </c>
       <c r="F781" s="1" t="n">
@@ -59919,33 +59915,37 @@
           <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
         </is>
       </c>
-      <c r="H781" s="1" t="n"/>
+      <c r="H781" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I781" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J781" s="2" t="n">
-        <v>46287.49436180555</v>
+        <v>46245.58840929398</v>
       </c>
       <c r="K781" s="2" t="n">
-        <v>46288</v>
+        <v>46248</v>
       </c>
       <c r="L781" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M781" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N781" s="1" t="n"/>
       <c r="O781" s="1" t="n"/>
       <c r="P781" s="1" t="n"/>
       <c r="Q781" s="1" t="inlineStr"/>
-      <c r="R781" s="1" t="n"/>
+      <c r="R781" s="1" t="inlineStr"/>
       <c r="S781" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -59956,16 +59956,16 @@
     </row>
     <row r="782">
       <c r="A782" s="1" t="n">
-        <v>82236</v>
+        <v>84108</v>
       </c>
       <c r="B782" s="1" t="inlineStr">
         <is>
-          <t>Inuitilização de Nota Fiscais</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C782" s="1" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D782" s="1" t="inlineStr">
@@ -59975,20 +59975,20 @@
       </c>
       <c r="E782" s="1" t="inlineStr">
         <is>
-          <t>Informado pelo cliente sequencia de Cupons que foram indevidamente emitidos. Confirmado com equipe fiscal que todos os cupons estão ativos e foram escriturados no mês 06. Se faz necessário processo de cancelamento extemporâneo tendo em vista o prazo limite ser 30 minutos.Processo conversado com o Gerente Master Reynaldo segundo ele cliente está ciente que este processo gera proposta de serviços extraordinários.Favor manter o contato com o cliente Guilherme (11) 99991-9311 ou Gabriela (11) 99797-6771Relação dos cupons informados pelo cliente estão no anexo.</t>
+          <t>Prezados,Boa tarde!Conforme solicitação do cliente, por gentileza, realizar levantamento de débitos federais, estaduais, municipais, trabalhistas.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F782" s="1" t="n">
-        <v>6179</v>
+        <v>6276</v>
       </c>
       <c r="G782" s="1" t="inlineStr">
         <is>
-          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
+          <t>LP GESTAO EMPRESARIAL LTDA</t>
         </is>
       </c>
       <c r="H782" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I782" s="1" t="inlineStr">
@@ -59997,29 +59997,40 @@
         </is>
       </c>
       <c r="J782" s="2" t="n">
-        <v>46245.58840929398</v>
+        <v>46282.58642442129</v>
       </c>
       <c r="K782" s="2" t="n">
-        <v>46248</v>
+        <v>46283</v>
       </c>
       <c r="L782" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M782" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N782" s="1" t="n"/>
       <c r="O782" s="1" t="n"/>
-      <c r="P782" s="1" t="n"/>
-      <c r="Q782" s="1" t="inlineStr"/>
-      <c r="R782" s="1" t="inlineStr"/>
+      <c r="P782" s="2" t="n">
+        <v>46286.3909099537</v>
+      </c>
+      <c r="Q782" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R782" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bom dia!
+Segue levantamento. </t>
+        </is>
+      </c>
       <c r="S782" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T782" s="1" t="n"/>
@@ -60027,39 +60038,39 @@
     </row>
     <row r="783">
       <c r="A783" s="1" t="n">
-        <v>84108</v>
+        <v>84121</v>
       </c>
       <c r="B783" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C783" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D783" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E783" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Boa tarde!Conforme solicitação do cliente, por gentileza, realizar levantamento de débitos federais, estaduais, municipais, trabalhistas.Grato,Bruno.</t>
+          <t>Por gentileza poderia me informar o login e a senha da prefeitura.</t>
         </is>
       </c>
       <c r="F783" s="1" t="n">
-        <v>6276</v>
+        <v>6368</v>
       </c>
       <c r="G783" s="1" t="inlineStr">
         <is>
-          <t>LP GESTAO EMPRESARIAL LTDA</t>
+          <t>CUCINARE PRO ALIMENTACAO LTDA (FILIAL 102)</t>
         </is>
       </c>
       <c r="H783" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Talita Silva</t>
         </is>
       </c>
       <c r="I783" s="1" t="inlineStr">
@@ -60068,40 +60079,29 @@
         </is>
       </c>
       <c r="J783" s="2" t="n">
-        <v>46282.58642442129</v>
+        <v>46282.72291574074</v>
       </c>
       <c r="K783" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="L783" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M783" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Rafaella Macedo</t>
         </is>
       </c>
       <c r="N783" s="1" t="n"/>
       <c r="O783" s="1" t="n"/>
-      <c r="P783" s="2" t="n">
-        <v>46286.3909099537</v>
-      </c>
-      <c r="Q783" s="1" t="inlineStr">
-        <is>
-          <t>Karina Dantas</t>
-        </is>
-      </c>
-      <c r="R783" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bom dia!
-Segue levantamento. </t>
-        </is>
-      </c>
+      <c r="P783" s="1" t="n"/>
+      <c r="Q783" s="1" t="inlineStr"/>
+      <c r="R783" s="1" t="inlineStr"/>
       <c r="S783" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T783" s="1" t="n"/>
@@ -60109,7 +60109,7 @@
     </row>
     <row r="784">
       <c r="A784" s="1" t="n">
-        <v>84121</v>
+        <v>84122</v>
       </c>
       <c r="B784" s="1" t="inlineStr">
         <is>
@@ -60132,11 +60132,11 @@
         </is>
       </c>
       <c r="F784" s="1" t="n">
-        <v>6368</v>
+        <v>6388</v>
       </c>
       <c r="G784" s="1" t="inlineStr">
         <is>
-          <t>CUCINARE PRO ALIMENTACAO LTDA (FILIAL 102)</t>
+          <t>CUCINARE PRO ALIMENTAÇÃO LTDA  (FILIAL 103)</t>
         </is>
       </c>
       <c r="H784" s="1" t="inlineStr">
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="J784" s="2" t="n">
-        <v>46282.72291574074</v>
+        <v>46282.72886608796</v>
       </c>
       <c r="K784" s="2" t="n">
         <v>46286</v>
@@ -60180,39 +60180,39 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>84122</v>
+        <v>82771</v>
       </c>
       <c r="B785" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C785" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras Cláusulas</t>
         </is>
       </c>
       <c r="D785" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E785" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza poderia me informar o login e a senha da prefeitura.</t>
+          <t>Alteração contratual da empresa: 6404-Solar Investimentos LtdaGrupo: Solar InvestimentosProposta ainda não foi negociada, o Master solicitou que fosse enviado a proposta com o valor padrãoInclusão de CNAE's abaixo:INCLUIR: (OK)•	7490-1/04 Atividades de intermediação e agenciamento de serviços e negócios em geral, exceto imobiliários•	4618-4/99 Outros representantes comerciais e agentes do comércio especializado em produtos não especificados anteriormenteEstes CNAE's estão sendo incluídos para a pratica dos serviços que seguem abaixo, "Paralegal", por favor validar se faz sentido e se atende os serviços abaixo relacionados:•10.02 – Agenciamento, corretagem ou intermediação de títulos em geral, valores mobiliários e contratos quaisquer.•10.05 – Agenciamento, corretagem ou intermediação de bens móveis ou imóveis, não abrangidos em outros itens ou subitens, inclusive aqueles realizados no âmbito de Bolsas de Mercadorias e Futuros, por quaisquer meios•10.09 – Representação de qualquer natureza, inclusive comercial</t>
         </is>
       </c>
       <c r="F785" s="1" t="n">
-        <v>6388</v>
+        <v>6404</v>
       </c>
       <c r="G785" s="1" t="inlineStr">
         <is>
-          <t>CUCINARE PRO ALIMENTAÇÃO LTDA  (FILIAL 103)</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H785" s="1" t="inlineStr">
         <is>
-          <t>Talita Silva</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I785" s="1" t="inlineStr">
@@ -60221,108 +60221,120 @@
         </is>
       </c>
       <c r="J785" s="2" t="n">
-        <v>46282.72886608796</v>
+        <v>46255.3884375</v>
       </c>
       <c r="K785" s="2" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="L785" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M785" s="1" t="inlineStr">
         <is>
-          <t>Rafaella Macedo</t>
-        </is>
-      </c>
-      <c r="N785" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N785" s="2" t="n">
+        <v>46261.63239140046</v>
+      </c>
       <c r="O785" s="1" t="n"/>
       <c r="P785" s="1" t="n"/>
       <c r="Q785" s="1" t="inlineStr"/>
-      <c r="R785" s="1" t="inlineStr"/>
-      <c r="S785" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T785" s="1" t="n"/>
-      <c r="U785" s="1" t="inlineStr"/>
-    </row>
-    <row r="786">
-      <c r="A786" s="1" t="n">
-        <v>82771</v>
-      </c>
-      <c r="B786" s="1" t="inlineStr">
-        <is>
-          <t>Alteração Contratual</t>
-        </is>
-      </c>
-      <c r="C786" s="1" t="inlineStr">
-        <is>
-          <t>Outras Cláusulas</t>
-        </is>
-      </c>
-      <c r="D786" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E786" s="1" t="inlineStr">
-        <is>
-          <t>Alteração contratual da empresa: 6404-Solar Investimentos LtdaGrupo: Solar InvestimentosProposta ainda não foi negociada, o Master solicitou que fosse enviado a proposta com o valor padrãoInclusão de CNAE's abaixo:INCLUIR: (OK)•	7490-1/04 Atividades de intermediação e agenciamento de serviços e negócios em geral, exceto imobiliários•	4618-4/99 Outros representantes comerciais e agentes do comércio especializado em produtos não especificados anteriormenteEstes CNAE's estão sendo incluídos para a pratica dos serviços que seguem abaixo, "Paralegal", por favor validar se faz sentido e se atende os serviços abaixo relacionados:•10.02 – Agenciamento, corretagem ou intermediação de títulos em geral, valores mobiliários e contratos quaisquer.•10.05 – Agenciamento, corretagem ou intermediação de bens móveis ou imóveis, não abrangidos em outros itens ou subitens, inclusive aqueles realizados no âmbito de Bolsas de Mercadorias e Futuros, por quaisquer meios•10.09 – Representação de qualquer natureza, inclusive comercial</t>
-        </is>
-      </c>
-      <c r="F786" s="1" t="n">
-        <v>6404</v>
-      </c>
-      <c r="G786" s="1" t="inlineStr">
-        <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
-        </is>
-      </c>
-      <c r="H786" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
-      <c r="I786" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J786" s="2" t="n">
-        <v>46255.3884375</v>
-      </c>
-      <c r="K786" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="L786" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M786" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N786" s="2" t="n">
-        <v>46261.63239140046</v>
-      </c>
-      <c r="O786" s="1" t="n"/>
-      <c r="P786" s="1" t="n"/>
-      <c r="Q786" s="1" t="inlineStr"/>
-      <c r="R786" s="1" t="inlineStr">
+      <c r="R785" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Prezados(as), boa tarde!
 Conforme solicitado, alteração contratual em andamento. 
 Atenciosamente, </t>
         </is>
       </c>
+      <c r="S785" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T785" s="1" t="n"/>
+      <c r="U785" s="1" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="1" t="n">
+        <v>83854</v>
+      </c>
+      <c r="B786" s="1" t="inlineStr">
+        <is>
+          <t>Levantamento de Débitos</t>
+        </is>
+      </c>
+      <c r="C786" s="1" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="D786" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E786" s="1" t="inlineStr">
+        <is>
+          <t>Prezados,Bom dia!Conforme solicitação do cliente, por gentileza, realizar levantamento de débitos federais, estaduais, municipais, trabalhistas das empresas do grupo Casa Glória (6125-CORA SERVIÇOS e 6276-LP GESTÃO EMPRESARIAL LTDA).Atenciosamente,Bruno.</t>
+        </is>
+      </c>
+      <c r="F786" s="1" t="n">
+        <v>6125</v>
+      </c>
+      <c r="G786" s="1" t="inlineStr">
+        <is>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+        </is>
+      </c>
+      <c r="H786" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="I786" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J786" s="2" t="n">
+        <v>46276.4970653588</v>
+      </c>
+      <c r="K786" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="L786" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M786" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N786" s="2" t="n">
+        <v>46283.43609560185</v>
+      </c>
+      <c r="O786" s="1" t="n"/>
+      <c r="P786" s="2" t="n">
+        <v>46286.3846287037</v>
+      </c>
+      <c r="Q786" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R786" s="1" t="inlineStr">
+        <is>
+          <t>Bruno, por gentileza abrir um chamado por empresa</t>
+        </is>
+      </c>
       <c r="S786" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T786" s="1" t="n"/>
@@ -60330,7 +60342,7 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>83854</v>
+        <v>83800</v>
       </c>
       <c r="B787" s="1" t="inlineStr">
         <is>
@@ -60344,20 +60356,20 @@
       </c>
       <c r="D787" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E787" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Bom dia!Conforme solicitação do cliente, por gentileza, realizar levantamento de débitos federais, estaduais, municipais, trabalhistas das empresas do grupo Casa Glória (6125-CORA SERVIÇOS e 6276-LP GESTÃO EMPRESARIAL LTDA).Atenciosamente,Bruno.</t>
+          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos Federais. </t>
         </is>
       </c>
       <c r="F787" s="1" t="n">
-        <v>6125</v>
+        <v>6454</v>
       </c>
       <c r="G787" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+          <t>MPJ - PRODUTOS, EQUIPAMENTOS E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="H787" s="1" t="inlineStr">
@@ -60371,10 +60383,10 @@
         </is>
       </c>
       <c r="J787" s="2" t="n">
-        <v>46276.4970653588</v>
+        <v>46275.48413533565</v>
       </c>
       <c r="K787" s="2" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="L787" s="1" t="inlineStr">
         <is>
@@ -60383,24 +60395,23 @@
       </c>
       <c r="M787" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N787" s="2" t="n">
-        <v>46283.43609560185</v>
-      </c>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N787" s="1" t="n"/>
       <c r="O787" s="1" t="n"/>
       <c r="P787" s="2" t="n">
-        <v>46286.3846287037</v>
+        <v>46280.78507179398</v>
       </c>
       <c r="Q787" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="R787" s="1" t="inlineStr">
         <is>
-          <t>Bruno, por gentileza abrir um chamado por empresa</t>
+          <t>Yasmin, boa noite!
+Não ha débitos em aberto, segue pesquisa e certidão.</t>
         </is>
       </c>
       <c r="S787" s="1" t="inlineStr">
@@ -60413,7 +60424,7 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>83800</v>
+        <v>83801</v>
       </c>
       <c r="B788" s="1" t="inlineStr">
         <is>
@@ -60422,7 +60433,7 @@
       </c>
       <c r="C788" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D788" s="1" t="inlineStr">
@@ -60432,7 +60443,7 @@
       </c>
       <c r="E788" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos Federais. </t>
+          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos Estaduais. </t>
         </is>
       </c>
       <c r="F788" s="1" t="n">
@@ -60454,7 +60465,7 @@
         </is>
       </c>
       <c r="J788" s="2" t="n">
-        <v>46275.48413533565</v>
+        <v>46275.48453171297</v>
       </c>
       <c r="K788" s="2" t="n">
         <v>46276</v>
@@ -60472,7 +60483,7 @@
       <c r="N788" s="1" t="n"/>
       <c r="O788" s="1" t="n"/>
       <c r="P788" s="2" t="n">
-        <v>46280.78507179398</v>
+        <v>46280.79029938657</v>
       </c>
       <c r="Q788" s="1" t="inlineStr">
         <is>
@@ -60481,8 +60492,8 @@
       </c>
       <c r="R788" s="1" t="inlineStr">
         <is>
-          <t>Yasmin, boa noite!
-Não ha débitos em aberto, segue pesquisa e certidão.</t>
+          <t>Boa noite!
+Segue.</t>
         </is>
       </c>
       <c r="S788" s="1" t="inlineStr">
@@ -60495,7 +60506,7 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>83801</v>
+        <v>83802</v>
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
@@ -60504,7 +60515,7 @@
       </c>
       <c r="C789" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D789" s="1" t="inlineStr">
@@ -60514,7 +60525,7 @@
       </c>
       <c r="E789" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos Estaduais. </t>
+          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos da Prefeitura. </t>
         </is>
       </c>
       <c r="F789" s="1" t="n">
@@ -60536,7 +60547,7 @@
         </is>
       </c>
       <c r="J789" s="2" t="n">
-        <v>46275.48453171297</v>
+        <v>46275.48498935185</v>
       </c>
       <c r="K789" s="2" t="n">
         <v>46276</v>
@@ -60554,7 +60565,7 @@
       <c r="N789" s="1" t="n"/>
       <c r="O789" s="1" t="n"/>
       <c r="P789" s="2" t="n">
-        <v>46280.79029938657</v>
+        <v>46280.7878784375</v>
       </c>
       <c r="Q789" s="1" t="inlineStr">
         <is>
@@ -60563,8 +60574,8 @@
       </c>
       <c r="R789" s="1" t="inlineStr">
         <is>
-          <t>Boa noite!
-Segue.</t>
+          <t xml:space="preserve">Boa noite!
+Segue taxas em aberto. </t>
         </is>
       </c>
       <c r="S789" s="1" t="inlineStr">
@@ -60577,39 +60588,39 @@
     </row>
     <row r="790">
       <c r="A790" s="1" t="n">
-        <v>83802</v>
+        <v>82787</v>
       </c>
       <c r="B790" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Declaração</t>
         </is>
       </c>
       <c r="C790" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Decore</t>
         </is>
       </c>
       <c r="D790" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E790" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos da Prefeitura. </t>
+          <t>Por gentileza, providenciar Decore para Sócio Roberto Toledo, referente aos pagamentos realizados entre 05/2026 e 07/2026 que somam R$ 133.560,00 , finalidade da decore Visto AmericanoROBERTO TOLEDO FERREIRA DE MORAES – CPF. 332.558.388-19 RG. 32.608.800-SSP-SO</t>
         </is>
       </c>
       <c r="F790" s="1" t="n">
-        <v>6454</v>
+        <v>6460</v>
       </c>
       <c r="G790" s="1" t="inlineStr">
         <is>
-          <t>MPJ - PRODUTOS, EQUIPAMENTOS E SERVICOS LTDA</t>
+          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H790" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I790" s="1" t="inlineStr">
@@ -60618,10 +60629,10 @@
         </is>
       </c>
       <c r="J790" s="2" t="n">
-        <v>46275.48498935185</v>
+        <v>46255.54234074074</v>
       </c>
       <c r="K790" s="2" t="n">
-        <v>46276</v>
+        <v>46258</v>
       </c>
       <c r="L790" s="1" t="inlineStr">
         <is>
@@ -60630,23 +60641,24 @@
       </c>
       <c r="M790" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N790" s="1" t="n"/>
+          <t>Simone Marques</t>
+        </is>
+      </c>
+      <c r="N790" s="2" t="n">
+        <v>46259.42845466435</v>
+      </c>
       <c r="O790" s="1" t="n"/>
       <c r="P790" s="2" t="n">
-        <v>46280.7878784375</v>
+        <v>46259.4294483449</v>
       </c>
       <c r="Q790" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="R790" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa noite!
-Segue taxas em aberto. </t>
+          <t xml:space="preserve">Providenciando </t>
         </is>
       </c>
       <c r="S790" s="1" t="inlineStr">
@@ -60659,16 +60671,16 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>82787</v>
+        <v>84074</v>
       </c>
       <c r="B791" s="1" t="inlineStr">
         <is>
-          <t>Declaração</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C791" s="1" t="inlineStr">
         <is>
-          <t>Decore</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D791" s="1" t="inlineStr">
@@ -60678,20 +60690,20 @@
       </c>
       <c r="E791" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar Decore para Sócio Roberto Toledo, referente aos pagamentos realizados entre 05/2026 e 07/2026 que somam R$ 133.560,00 , finalidade da decore Visto AmericanoROBERTO TOLEDO FERREIRA DE MORAES – CPF. 332.558.388-19 RG. 32.608.800-SSP-SO</t>
+          <t>Por gentileza solicitar abaixa do débitos junto a Sefaz de Minas, comprovantes anexos :                                                                                                                       Destas pendências só não localizamos 4 indicações conforme segue:31/07/22 R$ 13,1831/10/22 R$ 13,1830/11/22 R$   1,6830/11/22 R$ 31,19Total de R$ 59,23</t>
         </is>
       </c>
       <c r="F791" s="1" t="n">
-        <v>6460</v>
+        <v>6462</v>
       </c>
       <c r="G791" s="1" t="inlineStr">
         <is>
-          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
+          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (FILIAL 2)</t>
         </is>
       </c>
       <c r="H791" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I791" s="1" t="inlineStr">
@@ -60700,14 +60712,14 @@
         </is>
       </c>
       <c r="J791" s="2" t="n">
-        <v>46255.54234074074</v>
+        <v>46281.48259829861</v>
       </c>
       <c r="K791" s="2" t="n">
-        <v>46258</v>
+        <v>46286</v>
       </c>
       <c r="L791" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M791" s="1" t="inlineStr">
@@ -60716,25 +60728,20 @@
         </is>
       </c>
       <c r="N791" s="2" t="n">
-        <v>46259.42845466435</v>
+        <v>46283.43791516204</v>
       </c>
       <c r="O791" s="1" t="n"/>
-      <c r="P791" s="2" t="n">
-        <v>46259.4294483449</v>
-      </c>
-      <c r="Q791" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+      <c r="P791" s="1" t="n"/>
+      <c r="Q791" s="1" t="inlineStr"/>
       <c r="R791" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Providenciando </t>
+          <t xml:space="preserve">Bom dia!
+Processo protocolado. iremos acompanhar o deferimento. </t>
         </is>
       </c>
       <c r="S791" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T791" s="1" t="n"/>
@@ -60742,16 +60749,16 @@
     </row>
     <row r="792">
       <c r="A792" s="1" t="n">
-        <v>84074</v>
+        <v>83246</v>
       </c>
       <c r="B792" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Notificação</t>
         </is>
       </c>
       <c r="C792" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D792" s="1" t="inlineStr">
@@ -60761,20 +60768,20 @@
       </c>
       <c r="E792" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza solicitar abaixa do débitos junto a Sefaz de Minas, comprovantes anexos :                                                                                                                       Destas pendências só não localizamos 4 indicações conforme segue:31/07/22 R$ 13,1831/10/22 R$ 13,1830/11/22 R$   1,6830/11/22 R$ 31,19Total de R$ 59,23</t>
+          <t xml:space="preserve">Atender a notificação da Prefeitura  - regularizar Cnae da atividade econômica. </t>
         </is>
       </c>
       <c r="F792" s="1" t="n">
-        <v>6462</v>
+        <v>6507</v>
       </c>
       <c r="G792" s="1" t="inlineStr">
         <is>
-          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (FILIAL 2)</t>
+          <t xml:space="preserve">ERS PRINT SOLUÇÕES GRAFICAS E VISUAIS LTDA </t>
         </is>
       </c>
       <c r="H792" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I792" s="1" t="inlineStr">
@@ -60783,14 +60790,14 @@
         </is>
       </c>
       <c r="J792" s="2" t="n">
-        <v>46281.48259829861</v>
+        <v>46262.73318298611</v>
       </c>
       <c r="K792" s="2" t="n">
-        <v>46286</v>
+        <v>46269</v>
       </c>
       <c r="L792" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M792" s="1" t="inlineStr">
@@ -60798,18 +60805,11 @@
           <t>Simone Marques</t>
         </is>
       </c>
-      <c r="N792" s="2" t="n">
-        <v>46283.43791516204</v>
-      </c>
+      <c r="N792" s="1" t="n"/>
       <c r="O792" s="1" t="n"/>
       <c r="P792" s="1" t="n"/>
       <c r="Q792" s="1" t="inlineStr"/>
-      <c r="R792" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bom dia!
-Processo protocolado. iremos acompanhar o deferimento. </t>
-        </is>
-      </c>
+      <c r="R792" s="1" t="inlineStr"/>
       <c r="S792" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -60820,16 +60820,16 @@
     </row>
     <row r="793">
       <c r="A793" s="1" t="n">
-        <v>83246</v>
+        <v>82207</v>
       </c>
       <c r="B793" s="1" t="inlineStr">
         <is>
-          <t>Notificação</t>
+          <t>Restituição</t>
         </is>
       </c>
       <c r="C793" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D793" s="1" t="inlineStr">
@@ -60839,20 +60839,20 @@
       </c>
       <c r="E793" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atender a notificação da Prefeitura  - regularizar Cnae da atividade econômica. </t>
+          <t>6538 - SALDÃO CASA &amp; LARPreciso que inicie o processo de devolução do valor pago a maior.Houve dois pagamento de 803,78  marquei de laranja no PDF. Este processo preciso estar constantemente atualizado do status, pois após a conclusão o cliente devolverá o valor para MG, que pagou a segunda guia.Att.Vander</t>
         </is>
       </c>
       <c r="F793" s="1" t="n">
-        <v>6507</v>
+        <v>6538</v>
       </c>
       <c r="G793" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERS PRINT SOLUÇÕES GRAFICAS E VISUAIS LTDA </t>
+          <t>SALDAO CASA &amp; LAR MOVEIS E ELETRODOMESTICOS LTDA</t>
         </is>
       </c>
       <c r="H793" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I793" s="1" t="inlineStr">
@@ -60861,26 +60861,32 @@
         </is>
       </c>
       <c r="J793" s="2" t="n">
-        <v>46262.73318298611</v>
+        <v>46245.45257068287</v>
       </c>
       <c r="K793" s="2" t="n">
-        <v>46269</v>
+        <v>46247</v>
       </c>
       <c r="L793" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M793" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
-        </is>
-      </c>
-      <c r="N793" s="1" t="n"/>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="N793" s="2" t="n">
+        <v>46255.48998958334</v>
+      </c>
       <c r="O793" s="1" t="n"/>
       <c r="P793" s="1" t="n"/>
       <c r="Q793" s="1" t="inlineStr"/>
-      <c r="R793" s="1" t="inlineStr"/>
+      <c r="R793" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando dados bancários para solicitar a restituição.</t>
+        </is>
+      </c>
       <c r="S793" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -60891,39 +60897,39 @@
     </row>
     <row r="794">
       <c r="A794" s="1" t="n">
-        <v>82207</v>
+        <v>83642</v>
       </c>
       <c r="B794" s="1" t="inlineStr">
         <is>
-          <t>Restituição</t>
+          <t>Notificação</t>
         </is>
       </c>
       <c r="C794" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D794" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E794" s="1" t="inlineStr">
         <is>
-          <t>6538 - SALDÃO CASA &amp; LARPreciso que inicie o processo de devolução do valor pago a maior.Houve dois pagamento de 803,78  marquei de laranja no PDF. Este processo preciso estar constantemente atualizado do status, pois após a conclusão o cliente devolverá o valor para MG, que pagou a segunda guia.Att.Vander</t>
+          <t>Cliente recebeu notificação CRC, prazo de 15 dias de retorno.</t>
         </is>
       </c>
       <c r="F794" s="1" t="n">
-        <v>6538</v>
+        <v>6588</v>
       </c>
       <c r="G794" s="1" t="inlineStr">
         <is>
-          <t>SALDAO CASA &amp; LAR MOVEIS E ELETRODOMESTICOS LTDA</t>
+          <t>ALM GESTAO TECH RETAIL LTDA</t>
         </is>
       </c>
       <c r="H794" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I794" s="1" t="inlineStr">
@@ -60932,32 +60938,26 @@
         </is>
       </c>
       <c r="J794" s="2" t="n">
-        <v>46245.45257068287</v>
+        <v>46273.44699390046</v>
       </c>
       <c r="K794" s="2" t="n">
-        <v>46247</v>
+        <v>46276</v>
       </c>
       <c r="L794" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M794" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
-        </is>
-      </c>
-      <c r="N794" s="2" t="n">
-        <v>46255.48998958334</v>
-      </c>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N794" s="1" t="n"/>
       <c r="O794" s="1" t="n"/>
       <c r="P794" s="1" t="n"/>
       <c r="Q794" s="1" t="inlineStr"/>
-      <c r="R794" s="1" t="inlineStr">
-        <is>
-          <t>Aguardando dados bancários para solicitar a restituição.</t>
-        </is>
-      </c>
+      <c r="R794" s="1" t="inlineStr"/>
       <c r="S794" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -60968,39 +60968,39 @@
     </row>
     <row r="795">
       <c r="A795" s="1" t="n">
-        <v>83642</v>
+        <v>84129</v>
       </c>
       <c r="B795" s="1" t="inlineStr">
         <is>
-          <t>Notificação</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C795" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D795" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E795" s="1" t="inlineStr">
         <is>
-          <t>Cliente recebeu notificação CRC, prazo de 15 dias de retorno.</t>
+          <t>Por gentileza poderia me informar o login e a senha da prefeitura.</t>
         </is>
       </c>
       <c r="F795" s="1" t="n">
-        <v>6588</v>
+        <v>6608</v>
       </c>
       <c r="G795" s="1" t="inlineStr">
         <is>
-          <t>ALM GESTAO TECH RETAIL LTDA</t>
+          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 4)</t>
         </is>
       </c>
       <c r="H795" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Talita Silva</t>
         </is>
       </c>
       <c r="I795" s="1" t="inlineStr">
@@ -61009,10 +61009,10 @@
         </is>
       </c>
       <c r="J795" s="2" t="n">
-        <v>46273.44699390046</v>
+        <v>46282.74585570602</v>
       </c>
       <c r="K795" s="2" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="L795" s="1" t="inlineStr">
         <is>
@@ -61021,7 +61021,7 @@
       </c>
       <c r="M795" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
+          <t>Rafaella Macedo</t>
         </is>
       </c>
       <c r="N795" s="1" t="n"/>
@@ -61039,11 +61039,11 @@
     </row>
     <row r="796">
       <c r="A796" s="1" t="n">
-        <v>84129</v>
+        <v>82264</v>
       </c>
       <c r="B796" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C796" s="1" t="inlineStr">
@@ -61053,25 +61053,25 @@
       </c>
       <c r="D796" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E796" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza poderia me informar o login e a senha da prefeitura.</t>
+          <t>Por gentileza enviar a guia atualizada da TFEdas duas empresas do grupo BOMBEIROS 6621 E 6622</t>
         </is>
       </c>
       <c r="F796" s="1" t="n">
-        <v>6608</v>
+        <v>6621</v>
       </c>
       <c r="G796" s="1" t="inlineStr">
         <is>
-          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 4)</t>
+          <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
         </is>
       </c>
       <c r="H796" s="1" t="inlineStr">
         <is>
-          <t>Talita Silva</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I796" s="1" t="inlineStr">
@@ -61080,29 +61080,40 @@
         </is>
       </c>
       <c r="J796" s="2" t="n">
-        <v>46282.74585570602</v>
+        <v>46246.3872690162</v>
       </c>
       <c r="K796" s="2" t="n">
-        <v>46286</v>
+        <v>46248</v>
       </c>
       <c r="L796" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M796" s="1" t="inlineStr">
         <is>
-          <t>Rafaella Macedo</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N796" s="1" t="n"/>
       <c r="O796" s="1" t="n"/>
-      <c r="P796" s="1" t="n"/>
-      <c r="Q796" s="1" t="inlineStr"/>
-      <c r="R796" s="1" t="inlineStr"/>
+      <c r="P796" s="2" t="n">
+        <v>46246.66841165509</v>
+      </c>
+      <c r="Q796" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R796" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boa tarde!
+Não há débitos em aberto, seguem certidões. </t>
+        </is>
+      </c>
       <c r="S796" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T796" s="1" t="n"/>
@@ -61110,39 +61121,39 @@
     </row>
     <row r="797">
       <c r="A797" s="1" t="n">
-        <v>82264</v>
+        <v>82915</v>
       </c>
       <c r="B797" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C797" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D797" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E797" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza enviar a guia atualizada da TFEdas duas empresas do grupo BOMBEIROS 6621 E 6622</t>
+          <t>Alteração contratual do CAPITAL SOCIAL, QSA, ADMINISTRADOR e ATIVIDADE/CNAE da empresa 6628-TSN TECHNICAL SERVICE NETWORK LTDAGrupo: GTG1- Alteração de Sócio:Saida da Sra. MARIA BARBOSA DOS SANTOS CLEMENTE, que sede e tranfere o total das cotas para o Sr. ALISSON BARBOSA DE SOUSA 2- Aumento do capital:será aumentado de 150.000, para 300.000, sendo a integralização de 50.000, através do registro de um carro, e o restante (100.000), a integralizar em 12 parcelas.3- Alteração de CNAEs, seram removidos  4 e temos e incluir 6, conforme abaixo:CNAEs RETIRAR: (OK)•	23.41-9-00 - Fabricação de produtos cerâmicos refratários •	61.10-8-01 - Serviços de telefonia fixa comutada - STFC •	61.10-8-03 - Serviços de comunicação multimídia - SCM•	62.02-3-00 - Desenvolvimento e licenciamento de programas de computador customizáveisINCLUIR: (OK)•	4686-9/02 — Comércio atacadista de embalagens;•	4789-0/99 — Comércio varejista de outros produtos não especificados anteriormente;•	4744-0/03 — Comércio varejista de materiais hidráulicos;•	4679-6/04 — Comércio atacadista especializado de materiais de construção não especificados anteriormente;•	4673-7/00 — Comércio atacadista de material elétrico.•	86.60-7-00 - Atividades de apoio à gestão de saúde</t>
         </is>
       </c>
       <c r="F797" s="1" t="n">
-        <v>6621</v>
+        <v>6628</v>
       </c>
       <c r="G797" s="1" t="inlineStr">
         <is>
-          <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="H797" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I797" s="1" t="inlineStr">
@@ -61151,119 +61162,120 @@
         </is>
       </c>
       <c r="J797" s="2" t="n">
-        <v>46246.3872690162</v>
+        <v>46258.70282021991</v>
       </c>
       <c r="K797" s="2" t="n">
-        <v>46248</v>
+        <v>46286</v>
       </c>
       <c r="L797" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M797" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N797" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N797" s="2" t="n">
+        <v>46261.63173943287</v>
+      </c>
       <c r="O797" s="1" t="n"/>
-      <c r="P797" s="2" t="n">
-        <v>46246.66841165509</v>
-      </c>
-      <c r="Q797" s="1" t="inlineStr">
-        <is>
-          <t>Karina Dantas</t>
-        </is>
-      </c>
+      <c r="P797" s="1" t="n"/>
+      <c r="Q797" s="1" t="inlineStr"/>
       <c r="R797" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Boa tarde!
-Não há débitos em aberto, seguem certidões. </t>
-        </is>
-      </c>
-      <c r="S797" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T797" s="1" t="n"/>
-      <c r="U797" s="1" t="inlineStr"/>
-    </row>
-    <row r="798">
-      <c r="A798" s="1" t="n">
-        <v>82915</v>
-      </c>
-      <c r="B798" s="1" t="inlineStr">
-        <is>
-          <t>Alteração Contratual</t>
-        </is>
-      </c>
-      <c r="C798" s="1" t="inlineStr">
-        <is>
-          <t>Sócios</t>
-        </is>
-      </c>
-      <c r="D798" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E798" s="1" t="inlineStr">
-        <is>
-          <t>Alteração contratual do CAPITAL SOCIAL, QSA, ADMINISTRADOR e ATIVIDADE/CNAE da empresa 6628-TSN TECHNICAL SERVICE NETWORK LTDAGrupo: GTG1- Alteração de Sócio:Saida da Sra. MARIA BARBOSA DOS SANTOS CLEMENTE, que sede e tranfere o total das cotas para o Sr. ALISSON BARBOSA DE SOUSA 2- Aumento do capital:será aumentado de 150.000, para 300.000, sendo a integralização de 50.000, através do registro de um carro, e o restante (100.000), a integralizar em 12 parcelas.3- Alteração de CNAEs, seram removidos  4 e temos e incluir 6, conforme abaixo:CNAEs RETIRAR: (OK)•	23.41-9-00 - Fabricação de produtos cerâmicos refratários •	61.10-8-01 - Serviços de telefonia fixa comutada - STFC •	61.10-8-03 - Serviços de comunicação multimídia - SCM•	62.02-3-00 - Desenvolvimento e licenciamento de programas de computador customizáveisINCLUIR: (OK)•	4686-9/02 — Comércio atacadista de embalagens;•	4789-0/99 — Comércio varejista de outros produtos não especificados anteriormente;•	4744-0/03 — Comércio varejista de materiais hidráulicos;•	4679-6/04 — Comércio atacadista especializado de materiais de construção não especificados anteriormente;•	4673-7/00 — Comércio atacadista de material elétrico.•	86.60-7-00 - Atividades de apoio à gestão de saúde</t>
-        </is>
-      </c>
-      <c r="F798" s="1" t="n">
-        <v>6628</v>
-      </c>
-      <c r="G798" s="1" t="inlineStr">
-        <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
-        </is>
-      </c>
-      <c r="H798" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
-      <c r="I798" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J798" s="2" t="n">
-        <v>46258.70282021991</v>
-      </c>
-      <c r="K798" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="L798" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M798" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N798" s="2" t="n">
-        <v>46261.63173943287</v>
-      </c>
-      <c r="O798" s="1" t="n"/>
-      <c r="P798" s="1" t="n"/>
-      <c r="Q798" s="1" t="inlineStr"/>
-      <c r="R798" s="1" t="inlineStr">
         <is>
           <t>Prezados(as), boa tarde!
 Conforme solicitado, alteração contratual em andamento. 
 Atenciosamente,</t>
         </is>
       </c>
+      <c r="S797" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T797" s="1" t="n"/>
+      <c r="U797" s="1" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>84101</v>
+      </c>
+      <c r="B798" s="1" t="inlineStr">
+        <is>
+          <t>Parcelamento PGFN</t>
+        </is>
+      </c>
+      <c r="C798" s="1" t="inlineStr">
+        <is>
+          <t>Simples Nacional</t>
+        </is>
+      </c>
+      <c r="D798" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E798" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia! Por gentileza, poderiam emitir uma guia atualizada</t>
+        </is>
+      </c>
+      <c r="F798" s="1" t="n">
+        <v>6650</v>
+      </c>
+      <c r="G798" s="1" t="inlineStr">
+        <is>
+          <t>ACJ COMERCIO DE EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="H798" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="I798" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J798" s="2" t="n">
+        <v>46282.47985864583</v>
+      </c>
+      <c r="K798" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="L798" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M798" s="1" t="inlineStr">
+        <is>
+          <t>Sofia Souza</t>
+        </is>
+      </c>
+      <c r="N798" s="1" t="n"/>
+      <c r="O798" s="1" t="n"/>
+      <c r="P798" s="2" t="n">
+        <v>46283.70308052083</v>
+      </c>
+      <c r="Q798" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R798" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde!
+Qual parcela que voce deseja que seja emitida?
+Simples Nacional ou PGFN Simples Nacional?</t>
+        </is>
+      </c>
       <c r="S798" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T798" s="1" t="n"/>
@@ -61271,16 +61283,16 @@
     </row>
     <row r="799">
       <c r="A799" s="1" t="n">
-        <v>84101</v>
+        <v>81317</v>
       </c>
       <c r="B799" s="1" t="inlineStr">
         <is>
-          <t>Parcelamento PGFN</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C799" s="1" t="inlineStr">
         <is>
-          <t>Simples Nacional</t>
+          <t xml:space="preserve">Inclusão de Ata </t>
         </is>
       </c>
       <c r="D799" s="1" t="inlineStr">
@@ -61290,20 +61302,20 @@
       </c>
       <c r="E799" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, poderiam emitir uma guia atualizada</t>
+          <t>6673 – CHER SOLUÇÕESAlteração contratual na empresa CHER tirando a Juliana“Necessário realizar a alteração contratual tirando a JULIANA do quadro societário e a sócia remanescente ficará com 100% das cotas da empresa. Enviar a relação de documentos necessários.”</t>
         </is>
       </c>
       <c r="F799" s="1" t="n">
-        <v>6650</v>
+        <v>6673</v>
       </c>
       <c r="G799" s="1" t="inlineStr">
         <is>
-          <t>ACJ COMERCIO DE EMBALAGENS LTDA</t>
+          <t>CHER SOLUÇÕES COMERCIAIS LTDA</t>
         </is>
       </c>
       <c r="H799" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I799" s="1" t="inlineStr">
@@ -61312,10 +61324,10 @@
         </is>
       </c>
       <c r="J799" s="2" t="n">
-        <v>46282.47985864583</v>
+        <v>46225.61752997685</v>
       </c>
       <c r="K799" s="2" t="n">
-        <v>46286</v>
+        <v>46231</v>
       </c>
       <c r="L799" s="1" t="inlineStr">
         <is>
@@ -61324,24 +61336,22 @@
       </c>
       <c r="M799" s="1" t="inlineStr">
         <is>
-          <t>Sofia Souza</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="N799" s="1" t="n"/>
       <c r="O799" s="1" t="n"/>
       <c r="P799" s="2" t="n">
-        <v>46283.70308052083</v>
+        <v>46230.66237318287</v>
       </c>
       <c r="Q799" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="R799" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!
-Qual parcela que voce deseja que seja emitida?
-Simples Nacional ou PGFN Simples Nacional?</t>
+          <t>Enviar a planilha devidamente preechida (com todas as informações).</t>
         </is>
       </c>
       <c r="S799" s="1" t="inlineStr">
@@ -61354,7 +61364,7 @@
     </row>
     <row r="800">
       <c r="A800" s="1" t="n">
-        <v>81317</v>
+        <v>81316</v>
       </c>
       <c r="B800" s="1" t="inlineStr">
         <is>
@@ -61373,15 +61383,15 @@
       </c>
       <c r="E800" s="1" t="inlineStr">
         <is>
-          <t>6673 – CHER SOLUÇÕESAlteração contratual na empresa CHER tirando a Juliana“Necessário realizar a alteração contratual tirando a JULIANA do quadro societário e a sócia remanescente ficará com 100% das cotas da empresa. Enviar a relação de documentos necessários.”</t>
+          <t>6674 – HORTIFRUTI CENTRALAlteração contratual incluindo o CPF dos sócios da Nippo com o Fernando“No Hortifruti vai receber os sócios da Nippo. Fazer essa alteração contratual. Vamos aguardar o cliente definir as participações societárias na empresa. Enviar relação de documentos.”</t>
         </is>
       </c>
       <c r="F800" s="1" t="n">
-        <v>6673</v>
+        <v>6674</v>
       </c>
       <c r="G800" s="1" t="inlineStr">
         <is>
-          <t>CHER SOLUÇÕES COMERCIAIS LTDA</t>
+          <t>HORTIFRUTI CENTRAL DO COIMBRA LTDA</t>
         </is>
       </c>
       <c r="H800" s="1" t="inlineStr">
@@ -61395,7 +61405,7 @@
         </is>
       </c>
       <c r="J800" s="2" t="n">
-        <v>46225.61752997685</v>
+        <v>46225.61705821759</v>
       </c>
       <c r="K800" s="2" t="n">
         <v>46231</v>
@@ -61413,7 +61423,7 @@
       <c r="N800" s="1" t="n"/>
       <c r="O800" s="1" t="n"/>
       <c r="P800" s="2" t="n">
-        <v>46230.66237318287</v>
+        <v>46230.66303518519</v>
       </c>
       <c r="Q800" s="1" t="inlineStr">
         <is>
@@ -61422,7 +61432,7 @@
       </c>
       <c r="R800" s="1" t="inlineStr">
         <is>
-          <t>Enviar a planilha devidamente preechida (com todas as informações).</t>
+          <t>Enviar a planilha devidamente preenchida e completa.</t>
         </is>
       </c>
       <c r="S800" s="1" t="inlineStr">
@@ -61435,39 +61445,39 @@
     </row>
     <row r="801">
       <c r="A801" s="1" t="n">
-        <v>81316</v>
+        <v>83168</v>
       </c>
       <c r="B801" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C801" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inclusão de Ata </t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D801" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E801" s="1" t="inlineStr">
         <is>
-          <t>6674 – HORTIFRUTI CENTRALAlteração contratual incluindo o CPF dos sócios da Nippo com o Fernando“No Hortifruti vai receber os sócios da Nippo. Fazer essa alteração contratual. Vamos aguardar o cliente definir as participações societárias na empresa. Enviar relação de documentos.”</t>
+          <t xml:space="preserve">Alteração de endereço da empresa 6704-TECNO COM INFORMATICA LTDAGrupo: Tecno ComE alteração do endereço do e-mail no cartão CNPJ para contato@tecnocombrasil.com.br </t>
         </is>
       </c>
       <c r="F801" s="1" t="n">
-        <v>6674</v>
+        <v>6704</v>
       </c>
       <c r="G801" s="1" t="inlineStr">
         <is>
-          <t>HORTIFRUTI CENTRAL DO COIMBRA LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="H801" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I801" s="1" t="inlineStr">
@@ -61476,39 +61486,37 @@
         </is>
       </c>
       <c r="J801" s="2" t="n">
-        <v>46225.61705821759</v>
+        <v>46262.37490482639</v>
       </c>
       <c r="K801" s="2" t="n">
-        <v>46231</v>
+        <v>46290</v>
       </c>
       <c r="L801" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M801" s="1" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
-        </is>
-      </c>
-      <c r="N801" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N801" s="2" t="n">
+        <v>46266.48691802083</v>
+      </c>
       <c r="O801" s="1" t="n"/>
-      <c r="P801" s="2" t="n">
-        <v>46230.66303518519</v>
-      </c>
-      <c r="Q801" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="P801" s="1" t="n"/>
+      <c r="Q801" s="1" t="inlineStr"/>
       <c r="R801" s="1" t="inlineStr">
         <is>
-          <t>Enviar a planilha devidamente preenchida e completa.</t>
+          <t xml:space="preserve">Prezados(as), bom dia!
+Para ciência, alteração contratual em andamento conforme solicitado.
+Atenciosamente, </t>
         </is>
       </c>
       <c r="S801" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T801" s="1" t="n"/>
@@ -61516,7 +61524,7 @@
     </row>
     <row r="802">
       <c r="A802" s="1" t="n">
-        <v>83168</v>
+        <v>82821</v>
       </c>
       <c r="B802" s="1" t="inlineStr">
         <is>
@@ -61525,7 +61533,7 @@
       </c>
       <c r="C802" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Outras Cláusulas</t>
         </is>
       </c>
       <c r="D802" s="1" t="inlineStr">
@@ -61535,20 +61543,20 @@
       </c>
       <c r="E802" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração de endereço da empresa 6704-TECNO COM INFORMATICA LTDAGrupo: Tecno ComE alteração do endereço do e-mail no cartão CNPJ para contato@tecnocombrasil.com.br </t>
+          <t>Alteração contratual do CNAE da empresa: 6767-ALCANTARA LOGÍSTICA E TRANSPORTE LTDAGrupo: TW ALCANTARAProposta já negociada no valor de: R$ 2.500,00Incluir CNAE - 4712-1/00 COMO PRINCIPAL e o atual como secundário</t>
         </is>
       </c>
       <c r="F802" s="1" t="n">
-        <v>6704</v>
+        <v>6767</v>
       </c>
       <c r="G802" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>ALCANTARA LOGÍSTICA E TRANSPORTE LTDA</t>
         </is>
       </c>
       <c r="H802" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I802" s="1" t="inlineStr">
@@ -61557,10 +61565,10 @@
         </is>
       </c>
       <c r="J802" s="2" t="n">
-        <v>46262.37490482639</v>
+        <v>46255.68806971065</v>
       </c>
       <c r="K802" s="2" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="L802" s="1" t="inlineStr">
         <is>
@@ -61573,16 +61581,14 @@
         </is>
       </c>
       <c r="N802" s="2" t="n">
-        <v>46266.48691802083</v>
+        <v>46260.66751527778</v>
       </c>
       <c r="O802" s="1" t="n"/>
       <c r="P802" s="1" t="n"/>
       <c r="Q802" s="1" t="inlineStr"/>
       <c r="R802" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados(as), bom dia!
-Para ciência, alteração contratual em andamento conforme solicitado.
-Atenciosamente, </t>
+          <t xml:space="preserve">Processo em elaboração </t>
         </is>
       </c>
       <c r="S802" s="1" t="inlineStr">
@@ -61595,39 +61601,39 @@
     </row>
     <row r="803">
       <c r="A803" s="1" t="n">
-        <v>82821</v>
+        <v>83419</v>
       </c>
       <c r="B803" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Parcelamento PGFN</t>
         </is>
       </c>
       <c r="C803" s="1" t="inlineStr">
         <is>
-          <t>Outras Cláusulas</t>
+          <t>Ordinário</t>
         </is>
       </c>
       <c r="D803" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E803" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual do CNAE da empresa: 6767-ALCANTARA LOGÍSTICA E TRANSPORTE LTDAGrupo: TW ALCANTARAProposta já negociada no valor de: R$ 2.500,00Incluir CNAE - 4712-1/00 COMO PRINCIPAL e o atual como secundário</t>
+          <t>Por gentileza, efetur a simulação do parcelamento dos debitos apresentados da loja 6776</t>
         </is>
       </c>
       <c r="F803" s="1" t="n">
-        <v>6767</v>
+        <v>6776</v>
       </c>
       <c r="G803" s="1" t="inlineStr">
         <is>
-          <t>ALCANTARA LOGÍSTICA E TRANSPORTE LTDA</t>
+          <t>AR BRASIL COMERCIO DE PEÇAS DE REFRIGERAÇÃO LTDA</t>
         </is>
       </c>
       <c r="H803" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I803" s="1" t="inlineStr">
@@ -61636,35 +61642,39 @@
         </is>
       </c>
       <c r="J803" s="2" t="n">
-        <v>46255.68806971065</v>
+        <v>46266.72804910879</v>
       </c>
       <c r="K803" s="2" t="n">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="L803" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M803" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N803" s="2" t="n">
-        <v>46260.66751527778</v>
-      </c>
+          <t>Rogerio Egidio</t>
+        </is>
+      </c>
+      <c r="N803" s="1" t="n"/>
       <c r="O803" s="1" t="n"/>
-      <c r="P803" s="1" t="n"/>
-      <c r="Q803" s="1" t="inlineStr"/>
+      <c r="P803" s="2" t="n">
+        <v>46273.72911628473</v>
+      </c>
+      <c r="Q803" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="R803" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo em elaboração </t>
+          <t>Segue simulado referente aos debitos em aberto, entretanto, não há débitos em divida ativa.</t>
         </is>
       </c>
       <c r="S803" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T803" s="1" t="n"/>
@@ -61672,16 +61682,16 @@
     </row>
     <row r="804">
       <c r="A804" s="1" t="n">
-        <v>83419</v>
+        <v>84054</v>
       </c>
       <c r="B804" s="1" t="inlineStr">
         <is>
-          <t>Parcelamento PGFN</t>
+          <t>Parcelamento Estadual</t>
         </is>
       </c>
       <c r="C804" s="1" t="inlineStr">
         <is>
-          <t>Ordinário</t>
+          <t>ICMS</t>
         </is>
       </c>
       <c r="D804" s="1" t="inlineStr">
@@ -61691,7 +61701,7 @@
       </c>
       <c r="E804" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, efetur a simulação do parcelamento dos debitos apresentados da loja 6776</t>
+          <t>Por favor gerar o simulado do parcelamento dos debitos anexo</t>
         </is>
       </c>
       <c r="F804" s="1" t="n">
@@ -61704,7 +61714,7 @@
       </c>
       <c r="H804" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I804" s="1" t="inlineStr">
@@ -61713,10 +61723,10 @@
         </is>
       </c>
       <c r="J804" s="2" t="n">
-        <v>46266.72804910879</v>
+        <v>46280.80415454861</v>
       </c>
       <c r="K804" s="2" t="n">
-        <v>46268</v>
+        <v>46283</v>
       </c>
       <c r="L804" s="1" t="inlineStr">
         <is>
@@ -61731,16 +61741,17 @@
       <c r="N804" s="1" t="n"/>
       <c r="O804" s="1" t="n"/>
       <c r="P804" s="2" t="n">
-        <v>46273.72911628473</v>
+        <v>46287.39302276621</v>
       </c>
       <c r="Q804" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="R804" s="1" t="inlineStr">
         <is>
-          <t>Segue simulado referente aos debitos em aberto, entretanto, não há débitos em divida ativa.</t>
+          <t xml:space="preserve">Bom dia!
+Segue simulado e proposta. </t>
         </is>
       </c>
       <c r="S804" s="1" t="inlineStr">
@@ -61753,16 +61764,16 @@
     </row>
     <row r="805">
       <c r="A805" s="1" t="n">
-        <v>84054</v>
+        <v>84293</v>
       </c>
       <c r="B805" s="1" t="inlineStr">
         <is>
-          <t>Parcelamento Estadual</t>
+          <t>Restituição</t>
         </is>
       </c>
       <c r="C805" s="1" t="inlineStr">
         <is>
-          <t>ICMS</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D805" s="1" t="inlineStr">
@@ -61772,62 +61783,47 @@
       </c>
       <c r="E805" s="1" t="inlineStr">
         <is>
-          <t>Por favor gerar o simulado do parcelamento dos debitos anexo</t>
+          <t>DM COMERCIO - PROCESSO DE RESTÍTUIÇÃO DO ICMS - COMPROVAÇÃOPrezados preciso de um documento confirmando o estado do pedido de restituição do ICMS.Att.Vander</t>
         </is>
       </c>
       <c r="F805" s="1" t="n">
-        <v>6776</v>
+        <v>6816</v>
       </c>
       <c r="G805" s="1" t="inlineStr">
         <is>
-          <t>AR BRASIL COMERCIO DE PEÇAS DE REFRIGERAÇÃO LTDA</t>
-        </is>
-      </c>
-      <c r="H805" s="1" t="inlineStr">
-        <is>
-          <t>Karina Dantas</t>
-        </is>
-      </c>
+          <t>DM COMERCIO ALIMENTICIO LTDA</t>
+        </is>
+      </c>
+      <c r="H805" s="1" t="n"/>
       <c r="I805" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J805" s="2" t="n">
-        <v>46280.80415454861</v>
+        <v>46287.51194953704</v>
       </c>
       <c r="K805" s="2" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="L805" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M805" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="N805" s="1" t="n"/>
       <c r="O805" s="1" t="n"/>
-      <c r="P805" s="2" t="n">
-        <v>46287.39302276621</v>
-      </c>
-      <c r="Q805" s="1" t="inlineStr">
-        <is>
-          <t>Karina Dantas</t>
-        </is>
-      </c>
-      <c r="R805" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bom dia!
-Segue simulado e proposta. </t>
-        </is>
-      </c>
+      <c r="P805" s="1" t="n"/>
+      <c r="Q805" s="1" t="inlineStr"/>
+      <c r="R805" s="1" t="n"/>
       <c r="S805" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T805" s="1" t="n"/>
@@ -61835,63 +61831,67 @@
     </row>
     <row r="806">
       <c r="A806" s="1" t="n">
-        <v>84293</v>
+        <v>83885</v>
       </c>
       <c r="B806" s="1" t="inlineStr">
         <is>
-          <t>Restituição</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C806" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D806" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E806" s="1" t="inlineStr">
         <is>
-          <t>DM COMERCIO - PROCESSO DE RESTÍTUIÇÃO DO ICMS - COMPROVAÇÃOPrezados preciso de um documento confirmando o estado do pedido de restituição do ICMS.Att.Vander</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F806" s="1" t="n">
-        <v>6816</v>
+        <v>6907</v>
       </c>
       <c r="G806" s="1" t="inlineStr">
         <is>
-          <t>DM COMERCIO ALIMENTICIO LTDA</t>
-        </is>
-      </c>
-      <c r="H806" s="1" t="n"/>
+          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
+        </is>
+      </c>
+      <c r="H806" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
       <c r="I806" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J806" s="2" t="n">
-        <v>46287.51194953704</v>
+        <v>46279.38710362268</v>
       </c>
       <c r="K806" s="2" t="n">
-        <v>46289</v>
+        <v>46281</v>
       </c>
       <c r="L806" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M806" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ney Barbosa</t>
         </is>
       </c>
       <c r="N806" s="1" t="n"/>
       <c r="O806" s="1" t="n"/>
       <c r="P806" s="1" t="n"/>
       <c r="Q806" s="1" t="inlineStr"/>
-      <c r="R806" s="1" t="n"/>
+      <c r="R806" s="1" t="inlineStr"/>
       <c r="S806" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -61902,39 +61902,39 @@
     </row>
     <row r="807">
       <c r="A807" s="1" t="n">
-        <v>83885</v>
+        <v>83805</v>
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C807" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D807" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E807" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Prezados,Por gentileza, providenciar CND Municipal das empresas 6915/6916-Taiti - matriz e filial.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F807" s="1" t="n">
-        <v>6907</v>
+        <v>6915</v>
       </c>
       <c r="G807" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
+          <t>TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="H807" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I807" s="1" t="inlineStr">
@@ -61943,29 +61943,39 @@
         </is>
       </c>
       <c r="J807" s="2" t="n">
-        <v>46279.38710362268</v>
+        <v>46275.50182450232</v>
       </c>
       <c r="K807" s="2" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="L807" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M807" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N807" s="1" t="n"/>
       <c r="O807" s="1" t="n"/>
-      <c r="P807" s="1" t="n"/>
-      <c r="Q807" s="1" t="inlineStr"/>
-      <c r="R807" s="1" t="inlineStr"/>
+      <c r="P807" s="2" t="n">
+        <v>46275.79579456019</v>
+      </c>
+      <c r="Q807" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R807" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Segue certidão municipal da matriz, estou verificando referente a filial (município de Embu das Artes), peço que devolvam o chamado para que eu anexe assim que conseguir emitir. </t>
+        </is>
+      </c>
       <c r="S807" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T807" s="1" t="n"/>
@@ -61973,26 +61983,26 @@
     </row>
     <row r="808">
       <c r="A808" s="1" t="n">
-        <v>83805</v>
+        <v>83520</v>
       </c>
       <c r="B808" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C808" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Outras Cláusulas</t>
         </is>
       </c>
       <c r="D808" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E808" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Por gentileza, providenciar CND Municipal das empresas 6915/6916-Taiti - matriz e filial.Grato,Bruno.</t>
+          <t xml:space="preserve">Abertura de filial da Empresa: 6915-TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDAGrupo:TaitiProposta já negociada no Valor de R$ 1.700,00Abertura da filal 0003 que será no lugar da empresa 6917, que mudará de endereço. </t>
         </is>
       </c>
       <c r="F808" s="1" t="n">
@@ -62005,7 +62015,7 @@
       </c>
       <c r="H808" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I808" s="1" t="inlineStr">
@@ -62014,39 +62024,37 @@
         </is>
       </c>
       <c r="J808" s="2" t="n">
-        <v>46275.50182450232</v>
+        <v>46267.69369174769</v>
       </c>
       <c r="K808" s="2" t="n">
-        <v>46276</v>
+        <v>46295</v>
       </c>
       <c r="L808" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M808" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N808" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N808" s="2" t="n">
+        <v>46269.61665887731</v>
+      </c>
       <c r="O808" s="1" t="n"/>
-      <c r="P808" s="2" t="n">
-        <v>46275.79579456019</v>
-      </c>
-      <c r="Q808" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P808" s="1" t="n"/>
+      <c r="Q808" s="1" t="inlineStr"/>
       <c r="R808" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segue certidão municipal da matriz, estou verificando referente a filial (município de Embu das Artes), peço que devolvam o chamado para que eu anexe assim que conseguir emitir. </t>
+          <t>Boa tarde.
+Preparando a minuta.
+Atenciosamente,</t>
         </is>
       </c>
       <c r="S808" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T808" s="1" t="n"/>
@@ -62054,7 +62062,7 @@
     </row>
     <row r="809">
       <c r="A809" s="1" t="n">
-        <v>83520</v>
+        <v>83521</v>
       </c>
       <c r="B809" s="1" t="inlineStr">
         <is>
@@ -62063,7 +62071,7 @@
       </c>
       <c r="C809" s="1" t="inlineStr">
         <is>
-          <t>Outras Cláusulas</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D809" s="1" t="inlineStr">
@@ -62073,15 +62081,15 @@
       </c>
       <c r="E809" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abertura de filial da Empresa: 6915-TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDAGrupo:TaitiProposta já negociada no Valor de R$ 1.700,00Abertura da filal 0003 que será no lugar da empresa 6917, que mudará de endereço. </t>
+          <t>Alteração de endereço da empresa: 6917-LOJA DE FABRICA PISOS E REVESTIMENTOS LTDAGrupo: TaitiProposta já negociada no valor de R$1.700,00Alteração de endereço para sobreloja na empresa 6915, adicionar CNAE de Serviços de apoio Administrativos</t>
         </is>
       </c>
       <c r="F809" s="1" t="n">
-        <v>6915</v>
+        <v>6917</v>
       </c>
       <c r="G809" s="1" t="inlineStr">
         <is>
-          <t>TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDA</t>
+          <t>LOJA DE FABRICA PISOS E REVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H809" s="1" t="inlineStr">
@@ -62095,7 +62103,7 @@
         </is>
       </c>
       <c r="J809" s="2" t="n">
-        <v>46267.69369174769</v>
+        <v>46267.69573402778</v>
       </c>
       <c r="K809" s="2" t="n">
         <v>46295</v>
@@ -62111,16 +62119,16 @@
         </is>
       </c>
       <c r="N809" s="2" t="n">
-        <v>46269.61665887731</v>
+        <v>46269.46270142361</v>
       </c>
       <c r="O809" s="1" t="n"/>
       <c r="P809" s="1" t="n"/>
       <c r="Q809" s="1" t="inlineStr"/>
       <c r="R809" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.
-Preparando a minuta.
-Atenciosamente,</t>
+          <t>Bom dia.
+Minuta em preparação.
+Atenciosamente</t>
         </is>
       </c>
       <c r="S809" s="1" t="inlineStr">
@@ -62133,39 +62141,39 @@
     </row>
     <row r="810">
       <c r="A810" s="1" t="n">
-        <v>83521</v>
+        <v>83886</v>
       </c>
       <c r="B810" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C810" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D810" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E810" s="1" t="inlineStr">
         <is>
-          <t>Alteração de endereço da empresa: 6917-LOJA DE FABRICA PISOS E REVESTIMENTOS LTDAGrupo: TaitiProposta já negociada no valor de R$1.700,00Alteração de endereço para sobreloja na empresa 6915, adicionar CNAE de Serviços de apoio Administrativos</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F810" s="1" t="n">
-        <v>6917</v>
+        <v>6921</v>
       </c>
       <c r="G810" s="1" t="inlineStr">
         <is>
-          <t>LOJA DE FABRICA PISOS E REVESTIMENTOS LTDA</t>
+          <t>METALURGICA G3 LTDA</t>
         </is>
       </c>
       <c r="H810" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I810" s="1" t="inlineStr">
@@ -62174,34 +62182,26 @@
         </is>
       </c>
       <c r="J810" s="2" t="n">
-        <v>46267.69573402778</v>
+        <v>46279.38743356481</v>
       </c>
       <c r="K810" s="2" t="n">
-        <v>46295</v>
+        <v>46281</v>
       </c>
       <c r="L810" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M810" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N810" s="2" t="n">
-        <v>46269.46270142361</v>
-      </c>
+          <t>Ney Barbosa</t>
+        </is>
+      </c>
+      <c r="N810" s="1" t="n"/>
       <c r="O810" s="1" t="n"/>
       <c r="P810" s="1" t="n"/>
       <c r="Q810" s="1" t="inlineStr"/>
-      <c r="R810" s="1" t="inlineStr">
-        <is>
-          <t>Bom dia.
-Minuta em preparação.
-Atenciosamente</t>
-        </is>
-      </c>
+      <c r="R810" s="1" t="inlineStr"/>
       <c r="S810" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -62212,39 +62212,39 @@
     </row>
     <row r="811">
       <c r="A811" s="1" t="n">
-        <v>83886</v>
+        <v>83375</v>
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C811" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D811" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E811" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Abertura de empresa (Matriz e Filiais) do Grupo: Hugo DeleonTributação: Lucro RealTipo de Atividade: ComercioFinalidade: OperacionalForma Juridica: Eireli/SLUProposta:Cliente fez um pacote de alterações e aberturas, pois haverá essa abertura e uma alteração em cada CNPJ já existente:R$14.000,00 (quatorze mil) em 3 vezes.Obs: Planilha enviada com as informações da abertura da Matriz e das filiais (uma em cada aba)</t>
         </is>
       </c>
       <c r="F811" s="1" t="n">
-        <v>6921</v>
+        <v>6926</v>
       </c>
       <c r="G811" s="1" t="inlineStr">
         <is>
-          <t>METALURGICA G3 LTDA</t>
+          <t>HUGO DELEON CONFECCOES LTDA</t>
         </is>
       </c>
       <c r="H811" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I811" s="1" t="inlineStr">
@@ -62253,26 +62253,32 @@
         </is>
       </c>
       <c r="J811" s="2" t="n">
-        <v>46279.38743356481</v>
+        <v>46266.67255648148</v>
       </c>
       <c r="K811" s="2" t="n">
-        <v>46281</v>
+        <v>46294</v>
       </c>
       <c r="L811" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M811" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N811" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N811" s="2" t="n">
+        <v>46274.4455877662</v>
+      </c>
       <c r="O811" s="1" t="n"/>
       <c r="P811" s="1" t="n"/>
       <c r="Q811" s="1" t="inlineStr"/>
-      <c r="R811" s="1" t="inlineStr"/>
+      <c r="R811" s="1" t="inlineStr">
+        <is>
+          <t>Processo em elaboração</t>
+        </is>
+      </c>
       <c r="S811" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -62283,16 +62289,16 @@
     </row>
     <row r="812">
       <c r="A812" s="1" t="n">
-        <v>83375</v>
+        <v>84210</v>
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C812" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Comércio</t>
+          <t>Objeto Social</t>
         </is>
       </c>
       <c r="D812" s="1" t="inlineStr">
@@ -62302,36 +62308,32 @@
       </c>
       <c r="E812" s="1" t="inlineStr">
         <is>
-          <t>Abertura de empresa (Matriz e Filiais) do Grupo: Hugo DeleonTributação: Lucro RealTipo de Atividade: ComercioFinalidade: OperacionalForma Juridica: Eireli/SLUProposta:Cliente fez um pacote de alterações e aberturas, pois haverá essa abertura e uma alteração em cada CNPJ já existente:R$14.000,00 (quatorze mil) em 3 vezes.Obs: Planilha enviada com as informações da abertura da Matriz e das filiais (uma em cada aba)</t>
+          <t>Alteração contratual do objeto social, endereço e atividade/CNAE da empresa: 6944-MERCADO VIOLETA LTDA (FILIAL 11)Grupo: VioletaCobrar mesmo valor da ultima alteração.</t>
         </is>
       </c>
       <c r="F812" s="1" t="n">
-        <v>6926</v>
+        <v>6944</v>
       </c>
       <c r="G812" s="1" t="inlineStr">
         <is>
-          <t>HUGO DELEON CONFECCOES LTDA</t>
-        </is>
-      </c>
-      <c r="H812" s="1" t="inlineStr">
-        <is>
-          <t>Thifany Leite</t>
-        </is>
-      </c>
+          <t>MERCADO VIOLETA LTDA (FILIAL 11)</t>
+        </is>
+      </c>
+      <c r="H812" s="1" t="n"/>
       <c r="I812" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J812" s="2" t="n">
-        <v>46266.67255648148</v>
+        <v>46286.53263483796</v>
       </c>
       <c r="K812" s="2" t="n">
-        <v>46294</v>
+        <v>46314</v>
       </c>
       <c r="L812" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M812" s="1" t="inlineStr">
@@ -62339,17 +62341,11 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N812" s="2" t="n">
-        <v>46274.4455877662</v>
-      </c>
+      <c r="N812" s="1" t="n"/>
       <c r="O812" s="1" t="n"/>
       <c r="P812" s="1" t="n"/>
       <c r="Q812" s="1" t="inlineStr"/>
-      <c r="R812" s="1" t="inlineStr">
-        <is>
-          <t>Processo em elaboração</t>
-        </is>
-      </c>
+      <c r="R812" s="1" t="n"/>
       <c r="S812" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -62360,140 +62356,73 @@
     </row>
     <row r="813">
       <c r="A813" s="1" t="n">
-        <v>84210</v>
+        <v>83739</v>
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Levantamento de Débitos Anual</t>
         </is>
       </c>
       <c r="C813" s="1" t="inlineStr">
         <is>
-          <t>Objeto Social</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D813" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E813" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual do objeto social, endereço e atividade/CNAE da empresa: 6944-MERCADO VIOLETA LTDA (FILIAL 11)Grupo: VioletaCobrar mesmo valor da ultima alteração.</t>
+          <t>Prezados, o cliente solicita revisão dos seus debitos para negociações mais vantajosas (Banner anexo), sendo o caso providenciar simulados de parcelamentos.</t>
         </is>
       </c>
       <c r="F813" s="1" t="n">
-        <v>6944</v>
+        <v>6949</v>
       </c>
       <c r="G813" s="1" t="inlineStr">
         <is>
-          <t>MERCADO VIOLETA LTDA (FILIAL 11)</t>
-        </is>
-      </c>
-      <c r="H813" s="1" t="n"/>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+        </is>
+      </c>
+      <c r="H813" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="I813" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J813" s="2" t="n">
-        <v>46286.53263483796</v>
+        <v>46274.63486909722</v>
       </c>
       <c r="K813" s="2" t="n">
-        <v>46314</v>
+        <v>46275</v>
       </c>
       <c r="L813" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M813" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N813" s="1" t="n"/>
       <c r="O813" s="1" t="n"/>
-      <c r="P813" s="1" t="n"/>
-      <c r="Q813" s="1" t="inlineStr"/>
-      <c r="R813" s="1" t="n"/>
-      <c r="S813" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T813" s="1" t="n"/>
-      <c r="U813" s="1" t="inlineStr"/>
-    </row>
-    <row r="814">
-      <c r="A814" s="1" t="n">
-        <v>83739</v>
-      </c>
-      <c r="B814" s="1" t="inlineStr">
-        <is>
-          <t>Levantamento de Débitos Anual</t>
-        </is>
-      </c>
-      <c r="C814" s="1" t="inlineStr">
-        <is>
-          <t>RFB</t>
-        </is>
-      </c>
-      <c r="D814" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E814" s="1" t="inlineStr">
-        <is>
-          <t>Prezados, o cliente solicita revisão dos seus debitos para negociações mais vantajosas (Banner anexo), sendo o caso providenciar simulados de parcelamentos.</t>
-        </is>
-      </c>
-      <c r="F814" s="1" t="n">
-        <v>6949</v>
-      </c>
-      <c r="G814" s="1" t="inlineStr">
-        <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
-        </is>
-      </c>
-      <c r="H814" s="1" t="inlineStr">
+      <c r="P813" s="2" t="n">
+        <v>46281.75655381945</v>
+      </c>
+      <c r="Q813" s="1" t="inlineStr">
         <is>
           <t>Ellen Leite</t>
         </is>
       </c>
-      <c r="I814" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J814" s="2" t="n">
-        <v>46274.63486909722</v>
-      </c>
-      <c r="K814" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="L814" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M814" s="1" t="inlineStr">
-        <is>
-          <t>Ricardo Ferreira</t>
-        </is>
-      </c>
-      <c r="N814" s="1" t="n"/>
-      <c r="O814" s="1" t="n"/>
-      <c r="P814" s="2" t="n">
-        <v>46281.75655381945</v>
-      </c>
-      <c r="Q814" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="R814" s="1" t="inlineStr">
+      <c r="R813" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Ricardo, boa tarde!
 Realizei as simulações considerando as opções atualmente disponíveis para adesão. Como a PGFN estabeleceu limites para os valores que podem ser incluídos em cada modalidade de transação, foi necessário realizar as simulações separadamente, de acordo com cada opção disponível.
@@ -62503,9 +62432,87 @@
 </t>
         </is>
       </c>
+      <c r="S813" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T813" s="1" t="n"/>
+      <c r="U813" s="1" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>82258</v>
+      </c>
+      <c r="B814" s="1" t="inlineStr">
+        <is>
+          <t>Levantamento de Débitos</t>
+        </is>
+      </c>
+      <c r="C814" s="1" t="inlineStr">
+        <is>
+          <t>Prefeitura</t>
+        </is>
+      </c>
+      <c r="D814" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E814" s="1" t="inlineStr">
+        <is>
+          <t>prezados, favor providenciar levantamento de débitos junto a prefeitura e providenciar simulado de parcelamento. empresas: 6963 e 6962.</t>
+        </is>
+      </c>
+      <c r="F814" s="1" t="n">
+        <v>6963</v>
+      </c>
+      <c r="G814" s="1" t="inlineStr">
+        <is>
+          <t>PROMOTORAS GYN LTDA</t>
+        </is>
+      </c>
+      <c r="H814" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I814" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J814" s="2" t="n">
+        <v>46245.76093032408</v>
+      </c>
+      <c r="K814" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="L814" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M814" s="1" t="inlineStr">
+        <is>
+          <t>Ricardo Ferreira</t>
+        </is>
+      </c>
+      <c r="N814" s="2" t="n">
+        <v>46254.40280482639</v>
+      </c>
+      <c r="O814" s="1" t="n"/>
+      <c r="P814" s="1" t="n"/>
+      <c r="Q814" s="1" t="inlineStr"/>
+      <c r="R814" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando, 
+Parcelamento é solicitado somente presencialmente.</t>
+        </is>
+      </c>
       <c r="S814" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T814" s="1" t="n"/>
@@ -62513,39 +62520,39 @@
     </row>
     <row r="815">
       <c r="A815" s="1" t="n">
-        <v>82258</v>
+        <v>82091</v>
       </c>
       <c r="B815" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C815" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D815" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E815" s="1" t="inlineStr">
         <is>
-          <t>prezados, favor providenciar levantamento de débitos junto a prefeitura e providenciar simulado de parcelamento. empresas: 6963 e 6962.</t>
+          <t>ALTERAÇÃO CONTRATUAL NA EMPRESA 6977-PROTECTION SHIELD LTDAGRUPO: FILM FACILALTERAÇÃO DE ATIVIDADE E QSAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$1.500,00EMPRESA DE ESTRATEGIA PARA FUNCIONARIOS, APÓS A TRANSFERRENCIA DOS FUNCIONÁRIOS, VOLTAR QUADRO SOCIETARIO ANTIGO</t>
         </is>
       </c>
       <c r="F815" s="1" t="n">
-        <v>6963</v>
+        <v>6977</v>
       </c>
       <c r="G815" s="1" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>PROTECTION SHIELD LTDA</t>
         </is>
       </c>
       <c r="H815" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I815" s="1" t="inlineStr">
@@ -62554,10 +62561,10 @@
         </is>
       </c>
       <c r="J815" s="2" t="n">
-        <v>46245.76093032408</v>
+        <v>46241.64981377315</v>
       </c>
       <c r="K815" s="2" t="n">
-        <v>46246</v>
+        <v>46269</v>
       </c>
       <c r="L815" s="1" t="inlineStr">
         <is>
@@ -62566,19 +62573,18 @@
       </c>
       <c r="M815" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N815" s="2" t="n">
-        <v>46254.40280482639</v>
+        <v>46268.68579398148</v>
       </c>
       <c r="O815" s="1" t="n"/>
       <c r="P815" s="1" t="n"/>
       <c r="Q815" s="1" t="inlineStr"/>
       <c r="R815" s="1" t="inlineStr">
         <is>
-          <t>Aguardando, 
-Parcelamento é solicitado somente presencialmente.</t>
+          <t>Raisa, a empresa  6977 já possui o quadro de sócios exatamente como consta na planilha, não tem o que ser alterado.</t>
         </is>
       </c>
       <c r="S815" s="1" t="inlineStr">
@@ -62591,7 +62597,7 @@
     </row>
     <row r="816">
       <c r="A816" s="1" t="n">
-        <v>82091</v>
+        <v>81987</v>
       </c>
       <c r="B816" s="1" t="inlineStr">
         <is>
@@ -62600,17 +62606,17 @@
       </c>
       <c r="C816" s="1" t="inlineStr">
         <is>
-          <t>Sócios</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="D816" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E816" s="1" t="inlineStr">
         <is>
-          <t>ALTERAÇÃO CONTRATUAL NA EMPRESA 6977-PROTECTION SHIELD LTDAGRUPO: FILM FACILALTERAÇÃO DE ATIVIDADE E QSAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$1.500,00EMPRESA DE ESTRATEGIA PARA FUNCIONARIOS, APÓS A TRANSFERRENCIA DOS FUNCIONÁRIOS, VOLTAR QUADRO SOCIETARIO ANTIGO</t>
+          <t>6977 - PROTECTION SHIELD - MUDANÇAS NO CONTRATO SOCIALO Cliente precisa mudar o CNAI e incluir um sócio, poderia nos informar qual o honorário e quais documento você precisa?Desejo do cliente é fazer a transferência dos funcionário que estão hoje na 6976, para 6977, para isto é necessário haver a equiparação de atividades para não ter problemas Sindicais, então será necessita mudanças no CNAE, e para haver formação de grupo econômico a sócia deseja ter 1% de participação na 6977, hoje ela  da sociedade apenas como tutora do socio de menor, e como administradora.  Mais informações com o REYNALDO.Att.Vander</t>
         </is>
       </c>
       <c r="F816" s="1" t="n">
@@ -62632,10 +62638,10 @@
         </is>
       </c>
       <c r="J816" s="2" t="n">
-        <v>46241.64981377315</v>
+        <v>46240.55237392361</v>
       </c>
       <c r="K816" s="2" t="n">
-        <v>46269</v>
+        <v>46241</v>
       </c>
       <c r="L816" s="1" t="inlineStr">
         <is>
@@ -62644,18 +62650,18 @@
       </c>
       <c r="M816" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="N816" s="2" t="n">
-        <v>46268.68579398148</v>
+        <v>46268.68733116899</v>
       </c>
       <c r="O816" s="1" t="n"/>
       <c r="P816" s="1" t="n"/>
       <c r="Q816" s="1" t="inlineStr"/>
       <c r="R816" s="1" t="inlineStr">
         <is>
-          <t>Raisa, a empresa  6977 já possui o quadro de sócios exatamente como consta na planilha, não tem o que ser alterado.</t>
+          <t>Favor, informar o que vai ser alterado de fato.</t>
         </is>
       </c>
       <c r="S816" s="1" t="inlineStr">
@@ -62668,26 +62674,26 @@
     </row>
     <row r="817">
       <c r="A817" s="1" t="n">
-        <v>81987</v>
+        <v>83899</v>
       </c>
       <c r="B817" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C817" s="1" t="inlineStr">
         <is>
-          <t>Geral</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D817" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E817" s="1" t="inlineStr">
         <is>
-          <t>6977 - PROTECTION SHIELD - MUDANÇAS NO CONTRATO SOCIALO Cliente precisa mudar o CNAI e incluir um sócio, poderia nos informar qual o honorário e quais documento você precisa?Desejo do cliente é fazer a transferência dos funcionário que estão hoje na 6976, para 6977, para isto é necessário haver a equiparação de atividades para não ter problemas Sindicais, então será necessita mudanças no CNAE, e para haver formação de grupo econômico a sócia deseja ter 1% de participação na 6977, hoje ela  da sociedade apenas como tutora do socio de menor, e como administradora.  Mais informações com o REYNALDO.Att.Vander</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F817" s="1" t="n">
@@ -62700,7 +62706,7 @@
       </c>
       <c r="H817" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I817" s="1" t="inlineStr">
@@ -62709,32 +62715,26 @@
         </is>
       </c>
       <c r="J817" s="2" t="n">
-        <v>46240.55237392361</v>
+        <v>46279.39114621528</v>
       </c>
       <c r="K817" s="2" t="n">
-        <v>46241</v>
+        <v>46281</v>
       </c>
       <c r="L817" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M817" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
-        </is>
-      </c>
-      <c r="N817" s="2" t="n">
-        <v>46268.68733116899</v>
-      </c>
+          <t>Ney Barbosa</t>
+        </is>
+      </c>
+      <c r="N817" s="1" t="n"/>
       <c r="O817" s="1" t="n"/>
       <c r="P817" s="1" t="n"/>
       <c r="Q817" s="1" t="inlineStr"/>
-      <c r="R817" s="1" t="inlineStr">
-        <is>
-          <t>Favor, informar o que vai ser alterado de fato.</t>
-        </is>
-      </c>
+      <c r="R817" s="1" t="inlineStr"/>
       <c r="S817" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -62745,39 +62745,39 @@
     </row>
     <row r="818">
       <c r="A818" s="1" t="n">
-        <v>83899</v>
+        <v>81753</v>
       </c>
       <c r="B818" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C818" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D818" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E818" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>ABERTURA DE EMPRESA - 6981-LUIZ GOMES DA SILVA - O GOIANOGRUPO: SUPERMERCADO AVENIDATRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIO FINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.500,00EMPRESA DE ESTRATÉGIA, APÓS CONSTITUIDA MIGRAR OS FUNCIONARIOS. APÓS TERMINO DA MIGRAÇÃO ALTERAR ATIVIDADE E QUADRO SOCIETÁRIO.</t>
         </is>
       </c>
       <c r="F818" s="1" t="n">
-        <v>6977</v>
+        <v>6981</v>
       </c>
       <c r="G818" s="1" t="inlineStr">
         <is>
-          <t>PROTECTION SHIELD LTDA</t>
+          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
         </is>
       </c>
       <c r="H818" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I818" s="1" t="inlineStr">
@@ -62786,26 +62786,34 @@
         </is>
       </c>
       <c r="J818" s="2" t="n">
-        <v>46279.39114621528</v>
+        <v>46237.51070853009</v>
       </c>
       <c r="K818" s="2" t="n">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="L818" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M818" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N818" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N818" s="2" t="n">
+        <v>46246.66714818287</v>
+      </c>
       <c r="O818" s="1" t="n"/>
       <c r="P818" s="1" t="n"/>
       <c r="Q818" s="1" t="inlineStr"/>
-      <c r="R818" s="1" t="inlineStr"/>
+      <c r="R818" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prezados(as), boa tarde!
+Processo de abertura em andamento. 
+Atenciosamente, </t>
+        </is>
+      </c>
       <c r="S818" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -62816,39 +62824,39 @@
     </row>
     <row r="819">
       <c r="A819" s="1" t="n">
-        <v>81753</v>
+        <v>83634</v>
       </c>
       <c r="B819" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C819" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Comércio</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D819" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E819" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA - 6981-LUIZ GOMES DA SILVA - O GOIANOGRUPO: SUPERMERCADO AVENIDATRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIO FINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.500,00EMPRESA DE ESTRATÉGIA, APÓS CONSTITUIDA MIGRAR OS FUNCIONARIOS. APÓS TERMINO DA MIGRAÇÃO ALTERAR ATIVIDADE E QUADRO SOCIETÁRIO.</t>
+          <t>6984 – SUPERMERCADOS BANDEIRA LTDA - senha DA PREFEITURA DE ITAPECERICA DA SERRA - PARA DECLARAR ISS NA PREFEITURA</t>
         </is>
       </c>
       <c r="F819" s="1" t="n">
-        <v>6981</v>
+        <v>6984</v>
       </c>
       <c r="G819" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
+          <t xml:space="preserve"> SUPERMERCADOS BANDEIRA LTDA.</t>
         </is>
       </c>
       <c r="H819" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I819" s="1" t="inlineStr">
@@ -62857,10 +62865,10 @@
         </is>
       </c>
       <c r="J819" s="2" t="n">
-        <v>46237.51070853009</v>
+        <v>46273.39513472222</v>
       </c>
       <c r="K819" s="2" t="n">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="L819" s="1" t="inlineStr">
         <is>
@@ -62869,20 +62877,18 @@
       </c>
       <c r="M819" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="N819" s="2" t="n">
-        <v>46246.66714818287</v>
+        <v>46274.49502619213</v>
       </c>
       <c r="O819" s="1" t="n"/>
       <c r="P819" s="1" t="n"/>
       <c r="Q819" s="1" t="inlineStr"/>
       <c r="R819" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados(as), boa tarde!
-Processo de abertura em andamento. 
-Atenciosamente, </t>
+          <t>Cobramos novamente o antigo contador</t>
         </is>
       </c>
       <c r="S819" s="1" t="inlineStr">
@@ -62895,39 +62901,39 @@
     </row>
     <row r="820">
       <c r="A820" s="1" t="n">
-        <v>83634</v>
+        <v>81933</v>
       </c>
       <c r="B820" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C820" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D820" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E820" s="1" t="inlineStr">
         <is>
-          <t>6984 – SUPERMERCADOS BANDEIRA LTDA - senha DA PREFEITURA DE ITAPECERICA DA SERRA - PARA DECLARAR ISS NA PREFEITURA</t>
+          <t>Por gentileza, providenciar:6990 - RC MATERIAIS ELETRICOS E HIDRAULICOS (MATRIZ) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL6991 - RC MATERIAIS ELETRICOS E HIDRAULICOS (FILIAL 1) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL</t>
         </is>
       </c>
       <c r="F820" s="1" t="n">
-        <v>6984</v>
+        <v>6990</v>
       </c>
       <c r="G820" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SUPERMERCADOS BANDEIRA LTDA.</t>
+          <t>AMANCIO S ELETRICA, HIDRAULICA E CONSTRUCAO EM GERAL LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H820" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I820" s="1" t="inlineStr">
@@ -62936,35 +62942,39 @@
         </is>
       </c>
       <c r="J820" s="2" t="n">
-        <v>46273.39513472222</v>
+        <v>46239.72520292824</v>
       </c>
       <c r="K820" s="2" t="n">
-        <v>46275</v>
+        <v>46241</v>
       </c>
       <c r="L820" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M820" s="1" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
-        </is>
-      </c>
-      <c r="N820" s="2" t="n">
-        <v>46274.49502619213</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N820" s="1" t="n"/>
       <c r="O820" s="1" t="n"/>
-      <c r="P820" s="1" t="n"/>
-      <c r="Q820" s="1" t="inlineStr"/>
+      <c r="P820" s="2" t="n">
+        <v>46241.65195802083</v>
+      </c>
+      <c r="Q820" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="R820" s="1" t="inlineStr">
         <is>
-          <t>Cobramos novamente o antigo contador</t>
+          <t>Abrir um chamado por empresa, por gentileza.</t>
         </is>
       </c>
       <c r="S820" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T820" s="1" t="n"/>
@@ -62972,39 +62982,39 @@
     </row>
     <row r="821">
       <c r="A821" s="1" t="n">
-        <v>81933</v>
+        <v>81780</v>
       </c>
       <c r="B821" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C821" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Objeto Social</t>
         </is>
       </c>
       <c r="D821" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E821" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar:6990 - RC MATERIAIS ELETRICOS E HIDRAULICOS (MATRIZ) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL6991 - RC MATERIAIS ELETRICOS E HIDRAULICOS (FILIAL 1) - CERTIDÃO ESTADUAL FEDERAL, ESTADUAL E MUNICIPAL</t>
+          <t>ALTERAÇÃO CONTRATUAL DA EMPRESA: 6993-GOMES SERVIÇOS - LTDAGRUPO: CRISTO REIALTERAÇÃO DE QSA E OBJETO SOCIALPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.500,00MESMA ATIVIDADE E SÓCIOS DO SUP. AVENIDA, APÓS ALTERAÇÃO MIGRAR FUNCIONÁRIOS PARA NOVA EMPRESA ALTERAR QSA E OBJETO SOCIAL.</t>
         </is>
       </c>
       <c r="F821" s="1" t="n">
-        <v>6990</v>
+        <v>6993</v>
       </c>
       <c r="G821" s="1" t="inlineStr">
         <is>
-          <t>AMANCIO S ELETRICA, HIDRAULICA E CONSTRUCAO EM GERAL LTDA (MATRIZ)</t>
+          <t>GOMES SERVIÇOS - LTDA</t>
         </is>
       </c>
       <c r="H821" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I821" s="1" t="inlineStr">
@@ -63013,39 +63023,37 @@
         </is>
       </c>
       <c r="J821" s="2" t="n">
-        <v>46239.72520292824</v>
+        <v>46237.62372283565</v>
       </c>
       <c r="K821" s="2" t="n">
-        <v>46241</v>
+        <v>46265</v>
       </c>
       <c r="L821" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M821" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N821" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N821" s="2" t="n">
+        <v>46246.66900671296</v>
+      </c>
       <c r="O821" s="1" t="n"/>
-      <c r="P821" s="2" t="n">
-        <v>46241.65195802083</v>
-      </c>
-      <c r="Q821" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P821" s="1" t="n"/>
+      <c r="Q821" s="1" t="inlineStr"/>
       <c r="R821" s="1" t="inlineStr">
         <is>
-          <t>Abrir um chamado por empresa, por gentileza.</t>
+          <t xml:space="preserve">Prezados(as), boa tarde!
+Alteração contratual em andamento. 
+Atenciosamente, </t>
         </is>
       </c>
       <c r="S821" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T821" s="1" t="n"/>
@@ -63053,39 +63061,39 @@
     </row>
     <row r="822">
       <c r="A822" s="1" t="n">
-        <v>81780</v>
+        <v>83904</v>
       </c>
       <c r="B822" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C822" s="1" t="inlineStr">
         <is>
-          <t>Objeto Social</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D822" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E822" s="1" t="inlineStr">
         <is>
-          <t>ALTERAÇÃO CONTRATUAL DA EMPRESA: 6993-GOMES SERVIÇOS - LTDAGRUPO: CRISTO REIALTERAÇÃO DE QSA E OBJETO SOCIALPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.500,00MESMA ATIVIDADE E SÓCIOS DO SUP. AVENIDA, APÓS ALTERAÇÃO MIGRAR FUNCIONÁRIOS PARA NOVA EMPRESA ALTERAR QSA E OBJETO SOCIAL.</t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F822" s="1" t="n">
-        <v>6993</v>
+        <v>7005</v>
       </c>
       <c r="G822" s="1" t="inlineStr">
         <is>
-          <t>GOMES SERVIÇOS - LTDA</t>
+          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H822" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I822" s="1" t="inlineStr">
@@ -63094,34 +63102,26 @@
         </is>
       </c>
       <c r="J822" s="2" t="n">
-        <v>46237.62372283565</v>
+        <v>46279.39261207176</v>
       </c>
       <c r="K822" s="2" t="n">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="L822" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M822" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N822" s="2" t="n">
-        <v>46246.66900671296</v>
-      </c>
+          <t>Ney Barbosa</t>
+        </is>
+      </c>
+      <c r="N822" s="1" t="n"/>
       <c r="O822" s="1" t="n"/>
       <c r="P822" s="1" t="n"/>
       <c r="Q822" s="1" t="inlineStr"/>
-      <c r="R822" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prezados(as), boa tarde!
-Alteração contratual em andamento. 
-Atenciosamente, </t>
-        </is>
-      </c>
+      <c r="R822" s="1" t="inlineStr"/>
       <c r="S822" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -63132,7 +63132,7 @@
     </row>
     <row r="823">
       <c r="A823" s="1" t="n">
-        <v>83904</v>
+        <v>83905</v>
       </c>
       <c r="B823" s="1" t="inlineStr">
         <is>
@@ -63155,11 +63155,11 @@
         </is>
       </c>
       <c r="F823" s="1" t="n">
-        <v>7005</v>
+        <v>7006</v>
       </c>
       <c r="G823" s="1" t="inlineStr">
         <is>
-          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H823" s="1" t="inlineStr">
@@ -63173,7 +63173,7 @@
         </is>
       </c>
       <c r="J823" s="2" t="n">
-        <v>46279.39261207176</v>
+        <v>46279.39292399306</v>
       </c>
       <c r="K823" s="2" t="n">
         <v>46281</v>
@@ -63203,39 +63203,39 @@
     </row>
     <row r="824">
       <c r="A824" s="1" t="n">
-        <v>83905</v>
+        <v>84107</v>
       </c>
       <c r="B824" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C824" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D824" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E824" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t xml:space="preserve">boa tarde!!Por gentileza, fazer ALVARÁ de funcionamento da loja. </t>
         </is>
       </c>
       <c r="F824" s="1" t="n">
-        <v>7006</v>
+        <v>7051</v>
       </c>
       <c r="G824" s="1" t="inlineStr">
         <is>
-          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>TODOS ADMINISTRADORA DE CARTAO DE DESCONTOS BOTUCATU LTDA</t>
         </is>
       </c>
       <c r="H824" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I824" s="1" t="inlineStr">
@@ -63244,26 +63244,34 @@
         </is>
       </c>
       <c r="J824" s="2" t="n">
-        <v>46279.39292399306</v>
+        <v>46282.58430902778</v>
       </c>
       <c r="K824" s="2" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="L824" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M824" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N824" s="1" t="n"/>
+          <t>Rogerio Egidio</t>
+        </is>
+      </c>
+      <c r="N824" s="2" t="n">
+        <v>46287.41361241898</v>
+      </c>
       <c r="O824" s="1" t="n"/>
       <c r="P824" s="1" t="n"/>
       <c r="Q824" s="1" t="inlineStr"/>
-      <c r="R824" s="1" t="inlineStr"/>
+      <c r="R824" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prezados(as), bom dia!
+Solicitação em andamento, conforme solicitado. 
+Atenciosamente, </t>
+        </is>
+      </c>
       <c r="S824" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -63274,39 +63282,39 @@
     </row>
     <row r="825">
       <c r="A825" s="1" t="n">
-        <v>84107</v>
+        <v>83908</v>
       </c>
       <c r="B825" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C825" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D825" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E825" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">boa tarde!!Por gentileza, fazer ALVARÁ de funcionamento da loja. </t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F825" s="1" t="n">
-        <v>7051</v>
+        <v>7052</v>
       </c>
       <c r="G825" s="1" t="inlineStr">
         <is>
-          <t>TODOS ADMINISTRADORA DE CARTAO DE DESCONTOS BOTUCATU LTDA</t>
+          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
         </is>
       </c>
       <c r="H825" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I825" s="1" t="inlineStr">
@@ -63315,34 +63323,26 @@
         </is>
       </c>
       <c r="J825" s="2" t="n">
-        <v>46282.58430902778</v>
+        <v>46279.3937971875</v>
       </c>
       <c r="K825" s="2" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="L825" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M825" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
-        </is>
-      </c>
-      <c r="N825" s="2" t="n">
-        <v>46287.41361241898</v>
-      </c>
+          <t>Ney Barbosa</t>
+        </is>
+      </c>
+      <c r="N825" s="1" t="n"/>
       <c r="O825" s="1" t="n"/>
       <c r="P825" s="1" t="n"/>
       <c r="Q825" s="1" t="inlineStr"/>
-      <c r="R825" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prezados(as), bom dia!
-Solicitação em andamento, conforme solicitado. 
-Atenciosamente, </t>
-        </is>
-      </c>
+      <c r="R825" s="1" t="inlineStr"/>
       <c r="S825" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -63353,7 +63353,7 @@
     </row>
     <row r="826">
       <c r="A826" s="1" t="n">
-        <v>83908</v>
+        <v>83909</v>
       </c>
       <c r="B826" s="1" t="inlineStr">
         <is>
@@ -63376,11 +63376,11 @@
         </is>
       </c>
       <c r="F826" s="1" t="n">
-        <v>7052</v>
+        <v>7053</v>
       </c>
       <c r="G826" s="1" t="inlineStr">
         <is>
-          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
+          <t>BIANCA EMBREAGENS LTDA</t>
         </is>
       </c>
       <c r="H826" s="1" t="inlineStr">
@@ -63394,7 +63394,7 @@
         </is>
       </c>
       <c r="J826" s="2" t="n">
-        <v>46279.3937971875</v>
+        <v>46279.39412114584</v>
       </c>
       <c r="K826" s="2" t="n">
         <v>46281</v>
@@ -63424,7 +63424,7 @@
     </row>
     <row r="827">
       <c r="A827" s="1" t="n">
-        <v>83909</v>
+        <v>83910</v>
       </c>
       <c r="B827" s="1" t="inlineStr">
         <is>
@@ -63447,11 +63447,11 @@
         </is>
       </c>
       <c r="F827" s="1" t="n">
-        <v>7053</v>
+        <v>7054</v>
       </c>
       <c r="G827" s="1" t="inlineStr">
         <is>
-          <t>BIANCA EMBREAGENS LTDA</t>
+          <t>KADOSH DISTRIBUIDOR COMERCIO E SERVICO DIGITAL LTDA</t>
         </is>
       </c>
       <c r="H827" s="1" t="inlineStr">
@@ -63465,7 +63465,7 @@
         </is>
       </c>
       <c r="J827" s="2" t="n">
-        <v>46279.39412114584</v>
+        <v>46279.39450123843</v>
       </c>
       <c r="K827" s="2" t="n">
         <v>46281</v>
@@ -63495,7 +63495,7 @@
     </row>
     <row r="828">
       <c r="A828" s="1" t="n">
-        <v>83910</v>
+        <v>83911</v>
       </c>
       <c r="B828" s="1" t="inlineStr">
         <is>
@@ -63518,11 +63518,11 @@
         </is>
       </c>
       <c r="F828" s="1" t="n">
-        <v>7054</v>
+        <v>7055</v>
       </c>
       <c r="G828" s="1" t="inlineStr">
         <is>
-          <t>KADOSH DISTRIBUIDOR COMERCIO E SERVICO DIGITAL LTDA</t>
+          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
         </is>
       </c>
       <c r="H828" s="1" t="inlineStr">
@@ -63536,7 +63536,7 @@
         </is>
       </c>
       <c r="J828" s="2" t="n">
-        <v>46279.39450123843</v>
+        <v>46279.39479143519</v>
       </c>
       <c r="K828" s="2" t="n">
         <v>46281</v>
@@ -63566,7 +63566,7 @@
     </row>
     <row r="829">
       <c r="A829" s="1" t="n">
-        <v>83911</v>
+        <v>83912</v>
       </c>
       <c r="B829" s="1" t="inlineStr">
         <is>
@@ -63589,11 +63589,11 @@
         </is>
       </c>
       <c r="F829" s="1" t="n">
-        <v>7055</v>
+        <v>7056</v>
       </c>
       <c r="G829" s="1" t="inlineStr">
         <is>
-          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
+          <t>AUTO CENTER EMBRASIL LTDA</t>
         </is>
       </c>
       <c r="H829" s="1" t="inlineStr">
@@ -63607,7 +63607,7 @@
         </is>
       </c>
       <c r="J829" s="2" t="n">
-        <v>46279.39479143519</v>
+        <v>46279.39518283565</v>
       </c>
       <c r="K829" s="2" t="n">
         <v>46281</v>
@@ -63637,7 +63637,7 @@
     </row>
     <row r="830">
       <c r="A830" s="1" t="n">
-        <v>83912</v>
+        <v>83913</v>
       </c>
       <c r="B830" s="1" t="inlineStr">
         <is>
@@ -63660,11 +63660,11 @@
         </is>
       </c>
       <c r="F830" s="1" t="n">
-        <v>7056</v>
+        <v>7057</v>
       </c>
       <c r="G830" s="1" t="inlineStr">
         <is>
-          <t>AUTO CENTER EMBRASIL LTDA</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H830" s="1" t="inlineStr">
@@ -63678,7 +63678,7 @@
         </is>
       </c>
       <c r="J830" s="2" t="n">
-        <v>46279.39518283565</v>
+        <v>46279.39551385416</v>
       </c>
       <c r="K830" s="2" t="n">
         <v>46281</v>
@@ -63708,7 +63708,7 @@
     </row>
     <row r="831">
       <c r="A831" s="1" t="n">
-        <v>83913</v>
+        <v>83916</v>
       </c>
       <c r="B831" s="1" t="inlineStr">
         <is>
@@ -63731,11 +63731,11 @@
         </is>
       </c>
       <c r="F831" s="1" t="n">
-        <v>7057</v>
+        <v>7060</v>
       </c>
       <c r="G831" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
+          <t>GAPEMA LOCACAO DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H831" s="1" t="inlineStr">
@@ -63749,7 +63749,7 @@
         </is>
       </c>
       <c r="J831" s="2" t="n">
-        <v>46279.39551385416</v>
+        <v>46279.39634756945</v>
       </c>
       <c r="K831" s="2" t="n">
         <v>46281</v>
@@ -63779,7 +63779,7 @@
     </row>
     <row r="832">
       <c r="A832" s="1" t="n">
-        <v>83916</v>
+        <v>83917</v>
       </c>
       <c r="B832" s="1" t="inlineStr">
         <is>
@@ -63802,11 +63802,11 @@
         </is>
       </c>
       <c r="F832" s="1" t="n">
-        <v>7060</v>
+        <v>7061</v>
       </c>
       <c r="G832" s="1" t="inlineStr">
         <is>
-          <t>GAPEMA LOCACAO DE EQUIPAMENTOS LTDA</t>
+          <t>BF CORTES E FUROS TECNICOS E LOCACAO LTDA</t>
         </is>
       </c>
       <c r="H832" s="1" t="inlineStr">
@@ -63820,7 +63820,7 @@
         </is>
       </c>
       <c r="J832" s="2" t="n">
-        <v>46279.39634756945</v>
+        <v>46279.39663144676</v>
       </c>
       <c r="K832" s="2" t="n">
         <v>46281</v>
@@ -63850,7 +63850,7 @@
     </row>
     <row r="833">
       <c r="A833" s="1" t="n">
-        <v>83917</v>
+        <v>83918</v>
       </c>
       <c r="B833" s="1" t="inlineStr">
         <is>
@@ -63873,11 +63873,11 @@
         </is>
       </c>
       <c r="F833" s="1" t="n">
-        <v>7061</v>
+        <v>7062</v>
       </c>
       <c r="G833" s="1" t="inlineStr">
         <is>
-          <t>BF CORTES E FUROS TECNICOS E LOCACAO LTDA</t>
+          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="H833" s="1" t="inlineStr">
@@ -63891,7 +63891,7 @@
         </is>
       </c>
       <c r="J833" s="2" t="n">
-        <v>46279.39663144676</v>
+        <v>46279.39692175926</v>
       </c>
       <c r="K833" s="2" t="n">
         <v>46281</v>
@@ -63921,7 +63921,7 @@
     </row>
     <row r="834">
       <c r="A834" s="1" t="n">
-        <v>83918</v>
+        <v>83919</v>
       </c>
       <c r="B834" s="1" t="inlineStr">
         <is>
@@ -63944,11 +63944,11 @@
         </is>
       </c>
       <c r="F834" s="1" t="n">
-        <v>7062</v>
+        <v>7063</v>
       </c>
       <c r="G834" s="1" t="inlineStr">
         <is>
-          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
+          <t>CR LOCACAO E VENDAS DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H834" s="1" t="inlineStr">
@@ -63962,7 +63962,7 @@
         </is>
       </c>
       <c r="J834" s="2" t="n">
-        <v>46279.39692175926</v>
+        <v>46279.39713047454</v>
       </c>
       <c r="K834" s="2" t="n">
         <v>46281</v>
@@ -63992,39 +63992,39 @@
     </row>
     <row r="835">
       <c r="A835" s="1" t="n">
-        <v>83919</v>
+        <v>83261</v>
       </c>
       <c r="B835" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C835" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D835" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E835" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>Alteração contratual do QSA da empresa: 7046-RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDAGrupo: RamiroProposta já negociada no valor de R$1.800,00Retirar os dois sócios (João e Lucas) e deixar 100% do QSA com o Ramiro. Colocar atividade no Simples impeditiva, para que no mês de outubro essa empresa entre no Lucro Real</t>
         </is>
       </c>
       <c r="F835" s="1" t="n">
-        <v>7063</v>
+        <v>7046</v>
       </c>
       <c r="G835" s="1" t="inlineStr">
         <is>
-          <t>CR LOCACAO E VENDAS DE EQUIPAMENTOS LTDA</t>
+          <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
         </is>
       </c>
       <c r="H835" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I835" s="1" t="inlineStr">
@@ -64033,26 +64033,34 @@
         </is>
       </c>
       <c r="J835" s="2" t="n">
-        <v>46279.39713047454</v>
+        <v>46265.45567503473</v>
       </c>
       <c r="K835" s="2" t="n">
-        <v>46281</v>
+        <v>46293</v>
       </c>
       <c r="L835" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M835" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N835" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N835" s="2" t="n">
+        <v>46266.72388877315</v>
+      </c>
       <c r="O835" s="1" t="n"/>
       <c r="P835" s="1" t="n"/>
       <c r="Q835" s="1" t="inlineStr"/>
-      <c r="R835" s="1" t="inlineStr"/>
+      <c r="R835" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde.
+Preparando a minuta.
+Atenciosamente,</t>
+        </is>
+      </c>
       <c r="S835" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -64063,16 +64071,16 @@
     </row>
     <row r="836">
       <c r="A836" s="1" t="n">
-        <v>83261</v>
+        <v>83982</v>
       </c>
       <c r="B836" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C836" s="1" t="inlineStr">
         <is>
-          <t>Sócios</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D836" s="1" t="inlineStr">
@@ -64082,20 +64090,20 @@
       </c>
       <c r="E836" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual do QSA da empresa: 7046-RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDAGrupo: RamiroProposta já negociada no valor de R$1.800,00Retirar os dois sócios (João e Lucas) e deixar 100% do QSA com o Ramiro. Colocar atividade no Simples impeditiva, para que no mês de outubro essa empresa entre no Lucro Real</t>
+          <t>Abertura de nova empresa do grupo: 7064-BC SUPERMERCADOTributação: Simples NacionalTipo de Atividade: ComércioFinalidade: OperacionalForma Juridica: LtdaProposta: já negociada no valor de R$1.800,00</t>
         </is>
       </c>
       <c r="F836" s="1" t="n">
-        <v>7046</v>
+        <v>7064</v>
       </c>
       <c r="G836" s="1" t="inlineStr">
         <is>
-          <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
+          <t>BISPO E CARVALHO SUPERMERCADO LTDA</t>
         </is>
       </c>
       <c r="H836" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I836" s="1" t="inlineStr">
@@ -64104,10 +64112,10 @@
         </is>
       </c>
       <c r="J836" s="2" t="n">
-        <v>46265.45567503473</v>
+        <v>46280.39557824074</v>
       </c>
       <c r="K836" s="2" t="n">
-        <v>46293</v>
+        <v>46308</v>
       </c>
       <c r="L836" s="1" t="inlineStr">
         <is>
@@ -64120,109 +64128,111 @@
         </is>
       </c>
       <c r="N836" s="2" t="n">
-        <v>46266.72388877315</v>
+        <v>46287.41896099537</v>
       </c>
       <c r="O836" s="1" t="n"/>
       <c r="P836" s="1" t="n"/>
       <c r="Q836" s="1" t="inlineStr"/>
       <c r="R836" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.
-Preparando a minuta.
-Atenciosamente,</t>
-        </is>
-      </c>
-      <c r="S836" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T836" s="1" t="n"/>
-      <c r="U836" s="1" t="inlineStr"/>
-    </row>
-    <row r="837">
-      <c r="A837" s="1" t="n">
-        <v>83982</v>
-      </c>
-      <c r="B837" s="1" t="inlineStr">
-        <is>
-          <t>Abertura de Empresa</t>
-        </is>
-      </c>
-      <c r="C837" s="1" t="inlineStr">
-        <is>
-          <t>Sociedade - Comércio</t>
-        </is>
-      </c>
-      <c r="D837" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E837" s="1" t="inlineStr">
-        <is>
-          <t>Abertura de nova empresa do grupo: 7064-BC SUPERMERCADOTributação: Simples NacionalTipo de Atividade: ComércioFinalidade: OperacionalForma Juridica: LtdaProposta: já negociada no valor de R$1.800,00</t>
-        </is>
-      </c>
-      <c r="F837" s="1" t="n">
-        <v>7064</v>
-      </c>
-      <c r="G837" s="1" t="inlineStr">
-        <is>
-          <t>BISPO E CARVALHO SUPERMERCADO LTDA</t>
-        </is>
-      </c>
-      <c r="H837" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
-      <c r="I837" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J837" s="2" t="n">
-        <v>46280.39557824074</v>
-      </c>
-      <c r="K837" s="2" t="n">
-        <v>46308</v>
-      </c>
-      <c r="L837" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M837" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N837" s="2" t="n">
-        <v>46287.41896099537</v>
-      </c>
-      <c r="O837" s="1" t="n"/>
-      <c r="P837" s="1" t="n"/>
-      <c r="Q837" s="1" t="inlineStr"/>
-      <c r="R837" s="1" t="inlineStr">
-        <is>
           <t xml:space="preserve">Prezados(as), bom dia! 
 Solicitação em andamento, conforme solicitado. 
 Atenciosamente,
 </t>
         </is>
       </c>
+      <c r="S836" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T836" s="1" t="n"/>
+      <c r="U836" s="1" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="1" t="n">
+        <v>83217</v>
+      </c>
+      <c r="B837" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C837" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D837" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E837" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
+        </is>
+      </c>
+      <c r="F837" s="1" t="n">
+        <v>7062</v>
+      </c>
+      <c r="G837" s="1" t="inlineStr">
+        <is>
+          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
+        </is>
+      </c>
+      <c r="H837" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I837" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="J837" s="2" t="n">
+        <v>46262.49604351852</v>
+      </c>
+      <c r="K837" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L837" s="1" t="inlineStr">
+        <is>
+          <t>Devolvido para Solicitante</t>
+        </is>
+      </c>
+      <c r="M837" s="1" t="inlineStr">
+        <is>
+          <t>Santos Karina</t>
+        </is>
+      </c>
+      <c r="N837" s="1" t="n"/>
+      <c r="O837" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="P837" s="1" t="n"/>
+      <c r="Q837" s="1" t="inlineStr"/>
+      <c r="R837" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando o SAC liberar para cobrar os documentos .</t>
+        </is>
+      </c>
       <c r="S837" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T837" s="1" t="n"/>
+      <c r="T837" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
       <c r="U837" s="1" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" s="1" t="n">
-        <v>83217</v>
+        <v>83213</v>
       </c>
       <c r="B838" s="1" t="inlineStr">
         <is>
@@ -64245,11 +64255,11 @@
         </is>
       </c>
       <c r="F838" s="1" t="n">
-        <v>7062</v>
+        <v>7058</v>
       </c>
       <c r="G838" s="1" t="inlineStr">
         <is>
-          <t>ALFA MAQUINAS LOCACAO E SERVICOS LTDA</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H838" s="1" t="inlineStr">
@@ -64263,7 +64273,7 @@
         </is>
       </c>
       <c r="J838" s="2" t="n">
-        <v>46262.49604351852</v>
+        <v>46262.49500332176</v>
       </c>
       <c r="K838" s="2" t="n">
         <v>46265</v>
@@ -64303,7 +64313,7 @@
     </row>
     <row r="839">
       <c r="A839" s="1" t="n">
-        <v>83213</v>
+        <v>83214</v>
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
@@ -64326,11 +64336,11 @@
         </is>
       </c>
       <c r="F839" s="1" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="G839" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 1)</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 2)</t>
         </is>
       </c>
       <c r="H839" s="1" t="inlineStr">
@@ -64344,7 +64354,7 @@
         </is>
       </c>
       <c r="J839" s="2" t="n">
-        <v>46262.49500332176</v>
+        <v>46262.49526809028</v>
       </c>
       <c r="K839" s="2" t="n">
         <v>46265</v>
@@ -64384,7 +64394,7 @@
     </row>
     <row r="840">
       <c r="A840" s="1" t="n">
-        <v>83214</v>
+        <v>83117</v>
       </c>
       <c r="B840" s="1" t="inlineStr">
         <is>
@@ -64403,15 +64413,15 @@
       </c>
       <c r="E840" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
         </is>
       </c>
       <c r="F840" s="1" t="n">
-        <v>7059</v>
+        <v>7056</v>
       </c>
       <c r="G840" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (FILIAL 2)</t>
+          <t>AUTO CENTER EMBRASIL LTDA</t>
         </is>
       </c>
       <c r="H840" s="1" t="inlineStr">
@@ -64421,18 +64431,18 @@
       </c>
       <c r="I840" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J840" s="2" t="n">
-        <v>46262.49526809028</v>
+        <v>46261.47502040509</v>
       </c>
       <c r="K840" s="2" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="L840" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M840" s="1" t="inlineStr">
@@ -64440,7 +64450,9 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N840" s="1" t="n"/>
+      <c r="N840" s="2" t="n">
+        <v>46261.69782774305</v>
+      </c>
       <c r="O840" s="2" t="n">
         <v>46283</v>
       </c>
@@ -64448,7 +64460,7 @@
       <c r="Q840" s="1" t="inlineStr"/>
       <c r="R840" s="1" t="inlineStr">
         <is>
-          <t>Aguardando o SAC liberar para cobrar os documentos .</t>
+          <t>Cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S840" s="1" t="inlineStr">
@@ -64456,16 +64468,12 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T840" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
+      <c r="T840" s="1" t="n"/>
       <c r="U840" s="1" t="inlineStr"/>
     </row>
     <row r="841">
       <c r="A841" s="1" t="n">
-        <v>83117</v>
+        <v>83212</v>
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
@@ -64484,15 +64492,15 @@
       </c>
       <c r="E841" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F841" s="1" t="n">
-        <v>7056</v>
+        <v>7057</v>
       </c>
       <c r="G841" s="1" t="inlineStr">
         <is>
-          <t>AUTO CENTER EMBRASIL LTDA</t>
+          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H841" s="1" t="inlineStr">
@@ -64502,18 +64510,18 @@
       </c>
       <c r="I841" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J841" s="2" t="n">
-        <v>46261.47502040509</v>
+        <v>46262.49474181713</v>
       </c>
       <c r="K841" s="2" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="L841" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M841" s="1" t="inlineStr">
@@ -64521,9 +64529,7 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N841" s="2" t="n">
-        <v>46261.69782774305</v>
-      </c>
+      <c r="N841" s="1" t="n"/>
       <c r="O841" s="2" t="n">
         <v>46283</v>
       </c>
@@ -64531,7 +64537,7 @@
       <c r="Q841" s="1" t="inlineStr"/>
       <c r="R841" s="1" t="inlineStr">
         <is>
-          <t>Cobramos os documentos do antigo contador.</t>
+          <t>Aguardando o SAC liberar para cobrar os documentos .</t>
         </is>
       </c>
       <c r="S841" s="1" t="inlineStr">
@@ -64539,12 +64545,16 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T841" s="1" t="n"/>
+      <c r="T841" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
       <c r="U841" s="1" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" s="1" t="n">
-        <v>83212</v>
+        <v>83116</v>
       </c>
       <c r="B842" s="1" t="inlineStr">
         <is>
@@ -64563,15 +64573,15 @@
       </c>
       <c r="E842" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa;Itens dispensáveis, por gentileza, sinalizar.</t>
+          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
         </is>
       </c>
       <c r="F842" s="1" t="n">
-        <v>7057</v>
+        <v>7055</v>
       </c>
       <c r="G842" s="1" t="inlineStr">
         <is>
-          <t>JP LOCACAO COMERCIO DE EQUIPAMENTOS LTDA (MATRIZ)</t>
+          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
         </is>
       </c>
       <c r="H842" s="1" t="inlineStr">
@@ -64581,18 +64591,18 @@
       </c>
       <c r="I842" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J842" s="2" t="n">
-        <v>46262.49474181713</v>
+        <v>46261.47479783565</v>
       </c>
       <c r="K842" s="2" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="L842" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M842" s="1" t="inlineStr">
@@ -64600,7 +64610,9 @@
           <t>Santos Karina</t>
         </is>
       </c>
-      <c r="N842" s="1" t="n"/>
+      <c r="N842" s="2" t="n">
+        <v>46261.69765454861</v>
+      </c>
       <c r="O842" s="2" t="n">
         <v>46283</v>
       </c>
@@ -64608,7 +64620,7 @@
       <c r="Q842" s="1" t="inlineStr"/>
       <c r="R842" s="1" t="inlineStr">
         <is>
-          <t>Aguardando o SAC liberar para cobrar os documentos .</t>
+          <t>Cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S842" s="1" t="inlineStr">
@@ -64616,16 +64628,12 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T842" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
+      <c r="T842" s="1" t="n"/>
       <c r="U842" s="1" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" s="1" t="n">
-        <v>83116</v>
+        <v>83112</v>
       </c>
       <c r="B843" s="1" t="inlineStr">
         <is>
@@ -64648,11 +64656,11 @@
         </is>
       </c>
       <c r="F843" s="1" t="n">
-        <v>7055</v>
+        <v>7052</v>
       </c>
       <c r="G843" s="1" t="inlineStr">
         <is>
-          <t>YURI CESTARI DA SILVA EMBREAGENS OSASCO</t>
+          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
         </is>
       </c>
       <c r="H843" s="1" t="inlineStr">
@@ -64666,7 +64674,7 @@
         </is>
       </c>
       <c r="J843" s="2" t="n">
-        <v>46261.47479783565</v>
+        <v>46261.47219082176</v>
       </c>
       <c r="K843" s="2" t="n">
         <v>46262</v>
@@ -64682,7 +64690,7 @@
         </is>
       </c>
       <c r="N843" s="2" t="n">
-        <v>46261.69765454861</v>
+        <v>46261.69723422454</v>
       </c>
       <c r="O843" s="2" t="n">
         <v>46283</v>
@@ -64704,7 +64712,7 @@
     </row>
     <row r="844">
       <c r="A844" s="1" t="n">
-        <v>83112</v>
+        <v>82755</v>
       </c>
       <c r="B844" s="1" t="inlineStr">
         <is>
@@ -64723,15 +64731,15 @@
       </c>
       <c r="E844" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza, providenciar os documentos para implantação da empresa.</t>
+          <t>Boa tarde, por gentileza, providenciar documentos para implantação.</t>
         </is>
       </c>
       <c r="F844" s="1" t="n">
-        <v>7052</v>
+        <v>7005</v>
       </c>
       <c r="G844" s="1" t="inlineStr">
         <is>
-          <t>EMBRASIL COMERCIO DE AUTO PECAS LTDA</t>
+          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H844" s="1" t="inlineStr">
@@ -64745,10 +64753,10 @@
         </is>
       </c>
       <c r="J844" s="2" t="n">
-        <v>46261.47219082176</v>
+        <v>46254.65957604167</v>
       </c>
       <c r="K844" s="2" t="n">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="L844" s="1" t="inlineStr">
         <is>
@@ -64761,7 +64769,7 @@
         </is>
       </c>
       <c r="N844" s="2" t="n">
-        <v>46261.69723422454</v>
+        <v>46255.48691519676</v>
       </c>
       <c r="O844" s="2" t="n">
         <v>46283</v>
@@ -64770,7 +64778,7 @@
       <c r="Q844" s="1" t="inlineStr"/>
       <c r="R844" s="1" t="inlineStr">
         <is>
-          <t>Cobramos os documentos do antigo contador.</t>
+          <t>cobramos novamente o retorno dos documentos</t>
         </is>
       </c>
       <c r="S844" s="1" t="inlineStr">
@@ -64783,7 +64791,7 @@
     </row>
     <row r="845">
       <c r="A845" s="1" t="n">
-        <v>82755</v>
+        <v>82756</v>
       </c>
       <c r="B845" s="1" t="inlineStr">
         <is>
@@ -64806,11 +64814,11 @@
         </is>
       </c>
       <c r="F845" s="1" t="n">
-        <v>7005</v>
+        <v>7006</v>
       </c>
       <c r="G845" s="1" t="inlineStr">
         <is>
-          <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
         </is>
       </c>
       <c r="H845" s="1" t="inlineStr">
@@ -64824,7 +64832,7 @@
         </is>
       </c>
       <c r="J845" s="2" t="n">
-        <v>46254.65957604167</v>
+        <v>46254.65986380787</v>
       </c>
       <c r="K845" s="2" t="n">
         <v>46255</v>
@@ -64840,7 +64848,7 @@
         </is>
       </c>
       <c r="N845" s="2" t="n">
-        <v>46255.48691519676</v>
+        <v>46255.48792758102</v>
       </c>
       <c r="O845" s="2" t="n">
         <v>46283</v>
@@ -64849,7 +64857,7 @@
       <c r="Q845" s="1" t="inlineStr"/>
       <c r="R845" s="1" t="inlineStr">
         <is>
-          <t>cobramos novamente o retorno dos documentos</t>
+          <t>cobramos novamente os documentos</t>
         </is>
       </c>
       <c r="S845" s="1" t="inlineStr">
@@ -64862,7 +64870,7 @@
     </row>
     <row r="846">
       <c r="A846" s="1" t="n">
-        <v>82756</v>
+        <v>82310</v>
       </c>
       <c r="B846" s="1" t="inlineStr">
         <is>
@@ -64871,25 +64879,25 @@
       </c>
       <c r="C846" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D846" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E846" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza, providenciar documentos para implantação.</t>
+          <t>Bom dia!Por favor, solicitar ao antigo contador o balanço de abertura.</t>
         </is>
       </c>
       <c r="F846" s="1" t="n">
-        <v>7006</v>
+        <v>6974</v>
       </c>
       <c r="G846" s="1" t="inlineStr">
         <is>
-          <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+          <t>FRANCINALDO FERREIRA DE ANDRADE LTDA</t>
         </is>
       </c>
       <c r="H846" s="1" t="inlineStr">
@@ -64903,10 +64911,10 @@
         </is>
       </c>
       <c r="J846" s="2" t="n">
-        <v>46254.65986380787</v>
+        <v>46247.3783179051</v>
       </c>
       <c r="K846" s="2" t="n">
-        <v>46255</v>
+        <v>46248</v>
       </c>
       <c r="L846" s="1" t="inlineStr">
         <is>
@@ -64915,20 +64923,20 @@
       </c>
       <c r="M846" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N846" s="2" t="n">
-        <v>46255.48792758102</v>
+        <v>46253.39089305556</v>
       </c>
       <c r="O846" s="2" t="n">
-        <v>46283</v>
+        <v>46297</v>
       </c>
       <c r="P846" s="1" t="n"/>
       <c r="Q846" s="1" t="inlineStr"/>
       <c r="R846" s="1" t="inlineStr">
         <is>
-          <t>cobramos novamente os documentos</t>
+          <t>cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S846" s="1" t="inlineStr">
@@ -64941,7 +64949,7 @@
     </row>
     <row r="847">
       <c r="A847" s="1" t="n">
-        <v>82310</v>
+        <v>79867</v>
       </c>
       <c r="B847" s="1" t="inlineStr">
         <is>
@@ -64960,20 +64968,20 @@
       </c>
       <c r="E847" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Por favor, solicitar ao antigo contador o balanço de abertura.</t>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
         </is>
       </c>
       <c r="F847" s="1" t="n">
-        <v>6974</v>
+        <v>6704</v>
       </c>
       <c r="G847" s="1" t="inlineStr">
         <is>
-          <t>FRANCINALDO FERREIRA DE ANDRADE LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="H847" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I847" s="1" t="inlineStr">
@@ -64982,10 +64990,10 @@
         </is>
       </c>
       <c r="J847" s="2" t="n">
-        <v>46247.3783179051</v>
+        <v>46183.62582114583</v>
       </c>
       <c r="K847" s="2" t="n">
-        <v>46248</v>
+        <v>46185</v>
       </c>
       <c r="L847" s="1" t="inlineStr">
         <is>
@@ -64998,16 +65006,15 @@
         </is>
       </c>
       <c r="N847" s="2" t="n">
-        <v>46253.39089305556</v>
-      </c>
-      <c r="O847" s="2" t="n">
-        <v>46297</v>
-      </c>
+        <v>46237.4174340625</v>
+      </c>
+      <c r="O847" s="1" t="n"/>
       <c r="P847" s="1" t="n"/>
       <c r="Q847" s="1" t="inlineStr"/>
       <c r="R847" s="1" t="inlineStr">
         <is>
-          <t>cobramos os documentos do antigo contador.</t>
+          <t>Bom dia!
+Cobramos a antiga contabilidade.</t>
         </is>
       </c>
       <c r="S847" s="1" t="inlineStr">
@@ -65020,16 +65027,16 @@
     </row>
     <row r="848">
       <c r="A848" s="1" t="n">
-        <v>79867</v>
+        <v>79865</v>
       </c>
       <c r="B848" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C848" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D848" s="1" t="inlineStr">
@@ -65039,20 +65046,20 @@
       </c>
       <c r="E848" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F848" s="1" t="n">
-        <v>6704</v>
+        <v>6278</v>
       </c>
       <c r="G848" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="H848" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I848" s="1" t="inlineStr">
@@ -65061,7 +65068,7 @@
         </is>
       </c>
       <c r="J848" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K848" s="2" t="n">
         <v>46185</v>
@@ -65077,7 +65084,7 @@
         </is>
       </c>
       <c r="N848" s="2" t="n">
-        <v>46237.4174340625</v>
+        <v>46246.6616841088</v>
       </c>
       <c r="O848" s="1" t="n"/>
       <c r="P848" s="1" t="n"/>
@@ -65085,7 +65092,7 @@
       <c r="R848" s="1" t="inlineStr">
         <is>
           <t>Bom dia!
-Cobramos a antiga contabilidade.</t>
+Já foi atendido?</t>
         </is>
       </c>
       <c r="S848" s="1" t="inlineStr">
@@ -65098,36 +65105,32 @@
     </row>
     <row r="849">
       <c r="A849" s="1" t="n">
-        <v>79865</v>
+        <v>82701</v>
       </c>
       <c r="B849" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C849" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D849" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E849" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde, por gentileza, providencias documentos de implantação da empresa: 7037 - EXPANDItens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F849" s="1" t="n">
-        <v>6278</v>
-      </c>
-      <c r="G849" s="1" t="inlineStr">
-        <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G849" s="1" t="n"/>
       <c r="H849" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -65139,10 +65142,10 @@
         </is>
       </c>
       <c r="J849" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46253.71124814815</v>
       </c>
       <c r="K849" s="2" t="n">
-        <v>46185</v>
+        <v>46255</v>
       </c>
       <c r="L849" s="1" t="inlineStr">
         <is>
@@ -65151,19 +65154,20 @@
       </c>
       <c r="M849" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="N849" s="2" t="n">
-        <v>46246.6616841088</v>
-      </c>
-      <c r="O849" s="1" t="n"/>
+        <v>46255.46909065972</v>
+      </c>
+      <c r="O849" s="2" t="n">
+        <v>46283</v>
+      </c>
       <c r="P849" s="1" t="n"/>
       <c r="Q849" s="1" t="inlineStr"/>
       <c r="R849" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!
-Já foi atendido?</t>
+          <t xml:space="preserve">CObramos os documentos </t>
         </is>
       </c>
       <c r="S849" s="1" t="inlineStr">
@@ -65176,7 +65180,7 @@
     </row>
     <row r="850">
       <c r="A850" s="1" t="n">
-        <v>82701</v>
+        <v>82706</v>
       </c>
       <c r="B850" s="1" t="inlineStr">
         <is>
@@ -65195,7 +65199,7 @@
       </c>
       <c r="E850" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza, providencias documentos de implantação da empresa: 7037 - EXPANDItens dispensáveis, por gentileza, sinalizar.</t>
+          <t>Boa tarde, por gentileza, providenciar documentos de implantação da empresa: 6978 - HEPA FILTROS.Itens dispensáveis, por gentileza, sinalizar.</t>
         </is>
       </c>
       <c r="F850" s="1" t="n">
@@ -65213,7 +65217,7 @@
         </is>
       </c>
       <c r="J850" s="2" t="n">
-        <v>46253.71124814815</v>
+        <v>46253.72086076389</v>
       </c>
       <c r="K850" s="2" t="n">
         <v>46255</v>
@@ -65229,16 +65233,14 @@
         </is>
       </c>
       <c r="N850" s="2" t="n">
-        <v>46255.46909065972</v>
-      </c>
-      <c r="O850" s="2" t="n">
-        <v>46283</v>
-      </c>
+        <v>46255.48540517361</v>
+      </c>
+      <c r="O850" s="1" t="n"/>
       <c r="P850" s="1" t="n"/>
       <c r="Q850" s="1" t="inlineStr"/>
       <c r="R850" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CObramos os documentos </t>
+          <t>cobramos os documentos.</t>
         </is>
       </c>
       <c r="S850" s="1" t="inlineStr">
@@ -65248,79 +65250,6 @@
       </c>
       <c r="T850" s="1" t="n"/>
       <c r="U850" s="1" t="inlineStr"/>
-    </row>
-    <row r="851">
-      <c r="A851" s="1" t="n">
-        <v>82706</v>
-      </c>
-      <c r="B851" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C851" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D851" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E851" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde, por gentileza, providenciar documentos de implantação da empresa: 6978 - HEPA FILTROS.Itens dispensáveis, por gentileza, sinalizar.</t>
-        </is>
-      </c>
-      <c r="F851" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G851" s="1" t="n"/>
-      <c r="H851" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="I851" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="J851" s="2" t="n">
-        <v>46253.72086076389</v>
-      </c>
-      <c r="K851" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="L851" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M851" s="1" t="inlineStr">
-        <is>
-          <t>Santos Karina</t>
-        </is>
-      </c>
-      <c r="N851" s="2" t="n">
-        <v>46255.48540517361</v>
-      </c>
-      <c r="O851" s="1" t="n"/>
-      <c r="P851" s="1" t="n"/>
-      <c r="Q851" s="1" t="inlineStr"/>
-      <c r="R851" s="1" t="inlineStr">
-        <is>
-          <t>cobramos os documentos.</t>
-        </is>
-      </c>
-      <c r="S851" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T851" s="1" t="n"/>
-      <c r="U851" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -1097,7 +1097,7 @@
       <c r="G8" s="1" t="n"/>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M8" s="1" t="inlineStr">
@@ -1121,28 +1121,18 @@
           <t>Mauricio Lermen</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
-        <v>46288.63074707176</v>
-      </c>
+      <c r="N8" s="1" t="n"/>
       <c r="O8" s="1" t="n"/>
       <c r="P8" s="1" t="n"/>
       <c r="Q8" s="1" t="inlineStr"/>
-      <c r="R8" s="1" t="inlineStr">
-        <is>
-          <t>Cadastros revisados e atualizações realizadas, nas empresas de prola-bore, pendente as empresas de domésticas. Em andamento.</t>
-        </is>
-      </c>
+      <c r="R8" s="1" t="inlineStr"/>
       <c r="S8" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T8" s="1" t="n"/>
-      <c r="U8" s="1" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+      <c r="U8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -15662,7 +15652,11 @@
           <t>NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
-      <c r="H183" s="1" t="n"/>
+      <c r="H183" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I183" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -15676,7 +15670,7 @@
       </c>
       <c r="L183" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M183" s="1" t="inlineStr">
@@ -15688,14 +15682,18 @@
       <c r="O183" s="1" t="n"/>
       <c r="P183" s="1" t="n"/>
       <c r="Q183" s="1" t="inlineStr"/>
-      <c r="R183" s="1" t="n"/>
+      <c r="R183" s="1" t="inlineStr"/>
       <c r="S183" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T183" s="1" t="n"/>
-      <c r="U183" s="1" t="inlineStr"/>
+      <c r="U183" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -16164,7 +16162,11 @@
           <t>POWER FINANCIAL DO BRASIL S.A. (FILIAL 1)</t>
         </is>
       </c>
-      <c r="H189" s="1" t="n"/>
+      <c r="H189" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I189" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -16178,7 +16180,7 @@
       </c>
       <c r="L189" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M189" s="1" t="inlineStr">
@@ -16190,14 +16192,18 @@
       <c r="O189" s="1" t="n"/>
       <c r="P189" s="1" t="n"/>
       <c r="Q189" s="1" t="inlineStr"/>
-      <c r="R189" s="1" t="n"/>
+      <c r="R189" s="1" t="inlineStr"/>
       <c r="S189" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T189" s="1" t="n"/>
-      <c r="U189" s="1" t="inlineStr"/>
+      <c r="U189" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -51859,7 +51865,7 @@
       </c>
       <c r="L677" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M677" s="1" t="inlineStr">
@@ -51867,7 +51873,9 @@
           <t>Ricardo Fischer</t>
         </is>
       </c>
-      <c r="N677" s="1" t="n"/>
+      <c r="N677" s="2" t="n">
+        <v>46288.64739603009</v>
+      </c>
       <c r="O677" s="1" t="n"/>
       <c r="P677" s="1" t="n"/>
       <c r="Q677" s="1" t="inlineStr"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -1097,7 +1097,7 @@
       <c r="G8" s="1" t="n"/>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
@@ -1132,7 +1132,11 @@
         </is>
       </c>
       <c r="T8" s="1" t="n"/>
-      <c r="U8" s="1" t="inlineStr"/>
+      <c r="U8" s="1" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -2154,7 +2158,7 @@
         <v>46281.64028348379</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="P21" s="1" t="n"/>
       <c r="Q21" s="1" t="inlineStr"/>
@@ -3990,7 +3994,7 @@
       </c>
       <c r="N43" s="1" t="n"/>
       <c r="O43" s="2" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="P43" s="1" t="n"/>
       <c r="Q43" s="1" t="inlineStr"/>
@@ -4963,7 +4967,11 @@
           <t>P.E Latina Maquinas para Rotulagem Ltda.</t>
         </is>
       </c>
-      <c r="H55" s="1" t="n"/>
+      <c r="H55" s="1" t="inlineStr">
+        <is>
+          <t>Andrea Medeiros</t>
+        </is>
+      </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -4977,7 +4985,7 @@
       </c>
       <c r="L55" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M55" s="1" t="inlineStr">
@@ -4986,17 +4994,23 @@
         </is>
       </c>
       <c r="N55" s="1" t="n"/>
-      <c r="O55" s="1" t="n"/>
+      <c r="O55" s="2" t="n">
+        <v>46290</v>
+      </c>
       <c r="P55" s="1" t="n"/>
       <c r="Q55" s="1" t="inlineStr"/>
-      <c r="R55" s="1" t="n"/>
+      <c r="R55" s="1" t="inlineStr"/>
       <c r="S55" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T55" s="1" t="n"/>
-      <c r="U55" s="1" t="inlineStr"/>
+      <c r="U55" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -5400,7 +5414,7 @@
         <v>46281.55894710648</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="P60" s="1" t="n"/>
       <c r="Q60" s="1" t="inlineStr"/>
@@ -8140,7 +8154,7 @@
         <v>46273.64280181713</v>
       </c>
       <c r="O92" s="2" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="P92" s="1" t="n"/>
       <c r="Q92" s="1" t="inlineStr"/>
@@ -8555,7 +8569,7 @@
       </c>
       <c r="L97" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M97" s="1" t="inlineStr">
@@ -8567,12 +8581,22 @@
       <c r="O97" s="2" t="n">
         <v>46289</v>
       </c>
-      <c r="P97" s="1" t="n"/>
-      <c r="Q97" s="1" t="inlineStr"/>
-      <c r="R97" s="1" t="inlineStr"/>
+      <c r="P97" s="2" t="n">
+        <v>46288.68792091435</v>
+      </c>
+      <c r="Q97" s="1" t="inlineStr">
+        <is>
+          <t>Ana Flavia Silva</t>
+        </is>
+      </c>
+      <c r="R97" s="1" t="inlineStr">
+        <is>
+          <t>Seguem arquivos solicitados.</t>
+        </is>
+      </c>
       <c r="S97" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T97" s="1" t="n"/>
@@ -13380,7 +13404,7 @@
       </c>
       <c r="N155" s="1" t="n"/>
       <c r="O155" s="2" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="P155" s="1" t="n"/>
       <c r="Q155" s="1" t="inlineStr"/>
@@ -13854,7 +13878,11 @@
           <t>G13 IMPORTAÇÃO E EXPORTAÇÃO LTDA (FILIAL 3)</t>
         </is>
       </c>
-      <c r="H161" s="1" t="n"/>
+      <c r="H161" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I161" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -13868,7 +13896,7 @@
       </c>
       <c r="L161" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M161" s="1" t="inlineStr">
@@ -13877,17 +13905,23 @@
         </is>
       </c>
       <c r="N161" s="1" t="n"/>
-      <c r="O161" s="1" t="n"/>
+      <c r="O161" s="2" t="n">
+        <v>46290</v>
+      </c>
       <c r="P161" s="1" t="n"/>
       <c r="Q161" s="1" t="inlineStr"/>
-      <c r="R161" s="1" t="n"/>
+      <c r="R161" s="1" t="inlineStr"/>
       <c r="S161" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T161" s="1" t="n"/>
-      <c r="U161" s="1" t="inlineStr"/>
+      <c r="U161" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -13921,7 +13955,11 @@
           <t>G13 IMPORTAÇÃO E EXPORTAÇÃO LTDA (FILIAL 3)</t>
         </is>
       </c>
-      <c r="H162" s="1" t="n"/>
+      <c r="H162" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I162" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -13935,7 +13973,7 @@
       </c>
       <c r="L162" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M162" s="1" t="inlineStr">
@@ -13944,17 +13982,23 @@
         </is>
       </c>
       <c r="N162" s="1" t="n"/>
-      <c r="O162" s="1" t="n"/>
+      <c r="O162" s="2" t="n">
+        <v>46290</v>
+      </c>
       <c r="P162" s="1" t="n"/>
       <c r="Q162" s="1" t="inlineStr"/>
-      <c r="R162" s="1" t="n"/>
+      <c r="R162" s="1" t="inlineStr"/>
       <c r="S162" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T162" s="1" t="n"/>
-      <c r="U162" s="1" t="inlineStr"/>
+      <c r="U162" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -13988,7 +14032,11 @@
           <t>G13 IMPORTAÇÃO E EXPORTAÇÃO LTDA (FILIAL 3)</t>
         </is>
       </c>
-      <c r="H163" s="1" t="n"/>
+      <c r="H163" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I163" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -14002,7 +14050,7 @@
       </c>
       <c r="L163" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M163" s="1" t="inlineStr">
@@ -14011,17 +14059,23 @@
         </is>
       </c>
       <c r="N163" s="1" t="n"/>
-      <c r="O163" s="1" t="n"/>
+      <c r="O163" s="2" t="n">
+        <v>46290</v>
+      </c>
       <c r="P163" s="1" t="n"/>
       <c r="Q163" s="1" t="inlineStr"/>
-      <c r="R163" s="1" t="n"/>
+      <c r="R163" s="1" t="inlineStr"/>
       <c r="S163" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T163" s="1" t="n"/>
-      <c r="U163" s="1" t="inlineStr"/>
+      <c r="U163" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -14511,7 +14565,7 @@
       </c>
       <c r="N169" s="1" t="n"/>
       <c r="O169" s="2" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="P169" s="1" t="n"/>
       <c r="Q169" s="1" t="inlineStr"/>
@@ -15679,7 +15733,9 @@
         </is>
       </c>
       <c r="N183" s="1" t="n"/>
-      <c r="O183" s="1" t="n"/>
+      <c r="O183" s="2" t="n">
+        <v>46290</v>
+      </c>
       <c r="P183" s="1" t="n"/>
       <c r="Q183" s="1" t="inlineStr"/>
       <c r="R183" s="1" t="inlineStr"/>
@@ -16189,7 +16245,9 @@
         </is>
       </c>
       <c r="N189" s="1" t="n"/>
-      <c r="O189" s="1" t="n"/>
+      <c r="O189" s="2" t="n">
+        <v>46290</v>
+      </c>
       <c r="P189" s="1" t="n"/>
       <c r="Q189" s="1" t="inlineStr"/>
       <c r="R189" s="1" t="inlineStr"/>
@@ -16255,7 +16313,7 @@
       </c>
       <c r="L190" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M190" s="1" t="inlineStr">
@@ -16265,10 +16323,16 @@
       </c>
       <c r="N190" s="1" t="n"/>
       <c r="O190" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="P190" s="1" t="n"/>
-      <c r="Q190" s="1" t="inlineStr"/>
+        <v>46290</v>
+      </c>
+      <c r="P190" s="2" t="n">
+        <v>46288.68280138889</v>
+      </c>
+      <c r="Q190" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="R190" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Pagamento da taxa feito hoje dia 21/09, aguardar para a SEFAZ aprovar o SPED </t>
@@ -16276,7 +16340,7 @@
       </c>
       <c r="S190" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T190" s="1" t="n"/>
@@ -16673,7 +16737,7 @@
       </c>
       <c r="L195" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M195" s="1" t="inlineStr">
@@ -16681,8 +16745,12 @@
           <t>Clara Maria</t>
         </is>
       </c>
-      <c r="N195" s="1" t="n"/>
-      <c r="O195" s="1" t="n"/>
+      <c r="N195" s="2" t="n">
+        <v>46281.64077820602</v>
+      </c>
+      <c r="O195" s="2" t="n">
+        <v>46290</v>
+      </c>
       <c r="P195" s="1" t="n"/>
       <c r="Q195" s="1" t="inlineStr"/>
       <c r="R195" s="1" t="inlineStr">
@@ -17651,7 +17719,7 @@
       </c>
       <c r="I207" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J207" s="2" t="n">
@@ -17662,7 +17730,7 @@
       </c>
       <c r="L207" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M207" s="1" t="inlineStr">
@@ -17670,9 +17738,7 @@
           <t>Daniel Oliveira</t>
         </is>
       </c>
-      <c r="N207" s="2" t="n">
-        <v>46275.47392515047</v>
-      </c>
+      <c r="N207" s="1" t="n"/>
       <c r="O207" s="1" t="n"/>
       <c r="P207" s="1" t="n"/>
       <c r="Q207" s="1" t="inlineStr"/>
@@ -17686,7 +17752,11 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T207" s="1" t="n"/>
+      <c r="T207" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
       <c r="U207" s="1" t="inlineStr">
         <is>
           <t>David Bragança</t>
@@ -18253,7 +18323,7 @@
         <v>46286</v>
       </c>
       <c r="P214" s="2" t="n">
-        <v>46286.68722434028</v>
+        <v>46288.68383885417</v>
       </c>
       <c r="Q214" s="1" t="inlineStr">
         <is>
@@ -18582,7 +18652,7 @@
       </c>
       <c r="L218" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M218" s="1" t="inlineStr">
@@ -18594,12 +18664,22 @@
       <c r="O218" s="2" t="n">
         <v>46287</v>
       </c>
-      <c r="P218" s="1" t="n"/>
-      <c r="Q218" s="1" t="inlineStr"/>
-      <c r="R218" s="1" t="inlineStr"/>
+      <c r="P218" s="2" t="n">
+        <v>46288.66689505787</v>
+      </c>
+      <c r="Q218" s="1" t="inlineStr">
+        <is>
+          <t>Diogo Calazans</t>
+        </is>
+      </c>
+      <c r="R218" s="1" t="inlineStr">
+        <is>
+          <t>A situação fiscal é referente a falta de pagamento da guia do simples nacional , e esta situação é com o departamento fiscal.</t>
+        </is>
+      </c>
       <c r="S218" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T218" s="1" t="n"/>
@@ -52537,7 +52617,7 @@
     </row>
     <row r="687">
       <c r="A687" s="1" t="n">
-        <v>84311</v>
+        <v>84348</v>
       </c>
       <c r="B687" s="1" t="inlineStr">
         <is>
@@ -52556,44 +52636,40 @@
       </c>
       <c r="E687" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza disponibilizar nova senha GissOnline referente a empresa 6366 - CucinareObrigada!</t>
+          <t>6985 - LOJA NOVA NA MG - LIBERA A SENHA DA LOJA NO APP - PREFEITURA DE ITAPECERICA DA SERRA</t>
         </is>
       </c>
       <c r="F687" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G687" s="1" t="n"/>
-      <c r="H687" s="1" t="inlineStr">
-        <is>
-          <t>Sarah Amaro</t>
-        </is>
-      </c>
+      <c r="H687" s="1" t="n"/>
       <c r="I687" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J687" s="2" t="n">
-        <v>46287.65949065972</v>
+        <v>46288.37956327546</v>
       </c>
       <c r="K687" s="2" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="L687" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M687" s="1" t="inlineStr">
         <is>
-          <t>Julia Medeiros</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="N687" s="1" t="n"/>
       <c r="O687" s="1" t="n"/>
       <c r="P687" s="1" t="n"/>
       <c r="Q687" s="1" t="inlineStr"/>
-      <c r="R687" s="1" t="inlineStr"/>
+      <c r="R687" s="1" t="n"/>
       <c r="S687" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -52604,7 +52680,7 @@
     </row>
     <row r="688">
       <c r="A688" s="1" t="n">
-        <v>84348</v>
+        <v>84349</v>
       </c>
       <c r="B688" s="1" t="inlineStr">
         <is>
@@ -52613,7 +52689,7 @@
       </c>
       <c r="C688" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outra</t>
         </is>
       </c>
       <c r="D688" s="1" t="inlineStr">
@@ -52623,7 +52699,7 @@
       </c>
       <c r="E688" s="1" t="inlineStr">
         <is>
-          <t>6985 - LOJA NOVA NA MG - LIBERA A SENHA DA LOJA NO APP - PREFEITURA DE ITAPECERICA DA SERRA</t>
+          <t>Boa tarde.Por favor criar acesso para entrega da DIPAM https://www.savam.com.br/</t>
         </is>
       </c>
       <c r="F688" s="1" t="n">
@@ -52637,7 +52713,7 @@
         </is>
       </c>
       <c r="J688" s="2" t="n">
-        <v>46288.37956327546</v>
+        <v>46288.38786315973</v>
       </c>
       <c r="K688" s="2" t="n">
         <v>46290</v>
@@ -52649,7 +52725,7 @@
       </c>
       <c r="M688" s="1" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="N688" s="1" t="n"/>
@@ -52667,26 +52743,26 @@
     </row>
     <row r="689">
       <c r="A689" s="1" t="n">
-        <v>84349</v>
+        <v>84359</v>
       </c>
       <c r="B689" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C689" s="1" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D689" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E689" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por favor criar acesso para entrega da DIPAM https://www.savam.com.br/</t>
+          <t>Bom dia! Por gentileza, poderia realizar o levamento de TFA e TFE de todas as empresas do grupo Alfa Maquinas.</t>
         </is>
       </c>
       <c r="F689" s="1" t="n">
@@ -52700,10 +52776,10 @@
         </is>
       </c>
       <c r="J689" s="2" t="n">
-        <v>46288.38786315973</v>
+        <v>46288.40677905093</v>
       </c>
       <c r="K689" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="L689" s="1" t="inlineStr">
         <is>
@@ -52712,7 +52788,7 @@
       </c>
       <c r="M689" s="1" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N689" s="1" t="n"/>
@@ -52730,26 +52806,26 @@
     </row>
     <row r="690">
       <c r="A690" s="1" t="n">
-        <v>84359</v>
+        <v>84369</v>
       </c>
       <c r="B690" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C690" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outra</t>
         </is>
       </c>
       <c r="D690" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E690" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, poderia realizar o levamento de TFA e TFE de todas as empresas do grupo Alfa Maquinas.</t>
+          <t>Bom dia, Favor disponibilizar a senha SAVAM das empresas em anexo. Ambas tem acesso, pois eu acessava, porem mudou minha maquina e perdi as senhas salvas. Ambas tinham senha no MG Controle, por algum motivo não tem mais.</t>
         </is>
       </c>
       <c r="F690" s="1" t="n">
@@ -52763,10 +52839,10 @@
         </is>
       </c>
       <c r="J690" s="2" t="n">
-        <v>46288.40677905093</v>
+        <v>46288.4677772338</v>
       </c>
       <c r="K690" s="2" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="L690" s="1" t="inlineStr">
         <is>
@@ -52775,7 +52851,7 @@
       </c>
       <c r="M690" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Andre Silva</t>
         </is>
       </c>
       <c r="N690" s="1" t="n"/>
@@ -52793,26 +52869,26 @@
     </row>
     <row r="691">
       <c r="A691" s="1" t="n">
-        <v>84369</v>
+        <v>84372</v>
       </c>
       <c r="B691" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C691" s="1" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D691" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E691" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, Favor disponibilizar a senha SAVAM das empresas em anexo. Ambas tem acesso, pois eu acessava, porem mudou minha maquina e perdi as senhas salvas. Ambas tinham senha no MG Controle, por algum motivo não tem mais.</t>
+          <t>Bom dia!!Recebemos a informação de alteração cadastral da empresa 5048 - Uniforte. No entanto, esta alteração está pendente no sistema Único. Favor atualizar. Anexo o CNPJ, e tela do Único</t>
         </is>
       </c>
       <c r="F691" s="1" t="n">
@@ -52826,10 +52902,10 @@
         </is>
       </c>
       <c r="J691" s="2" t="n">
-        <v>46288.4677772338</v>
+        <v>46288.47592491898</v>
       </c>
       <c r="K691" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="L691" s="1" t="inlineStr">
         <is>
@@ -52838,7 +52914,7 @@
       </c>
       <c r="M691" s="1" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="N691" s="1" t="n"/>
@@ -52856,7 +52932,7 @@
     </row>
     <row r="692">
       <c r="A692" s="1" t="n">
-        <v>84372</v>
+        <v>84373</v>
       </c>
       <c r="B692" s="1" t="inlineStr">
         <is>
@@ -52889,7 +52965,7 @@
         </is>
       </c>
       <c r="J692" s="2" t="n">
-        <v>46288.47592491898</v>
+        <v>46288.47944568287</v>
       </c>
       <c r="K692" s="2" t="n">
         <v>46289</v>
@@ -52919,26 +52995,26 @@
     </row>
     <row r="693">
       <c r="A693" s="1" t="n">
-        <v>84373</v>
+        <v>84381</v>
       </c>
       <c r="B693" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Encerramento de Empresa</t>
         </is>
       </c>
       <c r="C693" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D693" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E693" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Recebemos a informação de alteração cadastral da empresa 5048 - Uniforte. No entanto, esta alteração está pendente no sistema Único. Favor atualizar. Anexo o CNPJ, e tela do Único</t>
+          <t>Precisamos da baixa da empresa filial referente CNPJ 01.6776944/0004-03 (ESMI ESTACIONAMENTO LTDA  -  FILIAL).Baixa de CNPJ e inscrição municipal.</t>
         </is>
       </c>
       <c r="F693" s="1" t="n">
@@ -52952,10 +53028,10 @@
         </is>
       </c>
       <c r="J693" s="2" t="n">
-        <v>46288.47944568287</v>
+        <v>46288.53023684028</v>
       </c>
       <c r="K693" s="2" t="n">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="L693" s="1" t="inlineStr">
         <is>
@@ -52964,7 +53040,7 @@
       </c>
       <c r="M693" s="1" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Romero Borges</t>
         </is>
       </c>
       <c r="N693" s="1" t="n"/>
@@ -52982,16 +53058,16 @@
     </row>
     <row r="694">
       <c r="A694" s="1" t="n">
-        <v>84381</v>
+        <v>84392</v>
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>Encerramento de Empresa</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C694" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Outro</t>
         </is>
       </c>
       <c r="D694" s="1" t="inlineStr">
@@ -53001,7 +53077,7 @@
       </c>
       <c r="E694" s="1" t="inlineStr">
         <is>
-          <t>Precisamos da baixa da empresa filial referente CNPJ 01.6776944/0004-03 (ESMI ESTACIONAMENTO LTDA  -  FILIAL).Baixa de CNPJ e inscrição municipal.</t>
+          <t>Boa Tarde !Por Gentileza realizar levantamento de Débitos e também condições de Parcelamento e negociação desses débitos pendentes para o cliente 511- NEI CABELEIREIRO LTDA .Qualquer dúvida estou a disposiçãoDesde já Agradeço</t>
         </is>
       </c>
       <c r="F694" s="1" t="n">
@@ -53015,10 +53091,10 @@
         </is>
       </c>
       <c r="J694" s="2" t="n">
-        <v>46288.53023684028</v>
+        <v>46288.66219552083</v>
       </c>
       <c r="K694" s="2" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="L694" s="1" t="inlineStr">
         <is>
@@ -53027,7 +53103,7 @@
       </c>
       <c r="M694" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
+          <t>Helmer Dantas</t>
         </is>
       </c>
       <c r="N694" s="1" t="n"/>
@@ -54174,16 +54250,16 @@
     </row>
     <row r="709">
       <c r="A709" s="1" t="n">
-        <v>84387</v>
+        <v>83960</v>
       </c>
       <c r="B709" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião de Sócios</t>
+          <t>Restituição</t>
         </is>
       </c>
       <c r="C709" s="1" t="inlineStr">
         <is>
-          <t>Sociedade Limitada Jucesp</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D709" s="1" t="inlineStr">
@@ -54193,44 +54269,48 @@
       </c>
       <c r="E709" s="1" t="inlineStr">
         <is>
-          <t>Não encontrei na pasta de Contratos Digitalizados a pasta da empresa 2497 - VYTADM do Grupo Xeryus.A Jesica está solicitando as ATAS devido a um processo jurídico; informa que tem urgência em receber. Poderiam por gentileza verificar?Obrigada.</t>
+          <t>Prezados, Houve um erro na informação de quotas do IRPJ e CSLL 3º trimestre de 2025.anexo comprovantes de pagamento do protesto.</t>
         </is>
       </c>
       <c r="F709" s="1" t="n">
-        <v>2497</v>
+        <v>2575</v>
       </c>
       <c r="G709" s="1" t="inlineStr">
         <is>
-          <t>VYTADM Administração e Participação Ltda.</t>
-        </is>
-      </c>
-      <c r="H709" s="1" t="n"/>
+          <t>VITTA SALAD - PRODUTOS NATURAIS COMÉRCIO DE HORTI FRUTI LTDA</t>
+        </is>
+      </c>
+      <c r="H709" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="I709" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J709" s="2" t="n">
-        <v>46288.61576003472</v>
+        <v>46279.67358012732</v>
       </c>
       <c r="K709" s="2" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="L709" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M709" s="1" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N709" s="1" t="n"/>
       <c r="O709" s="1" t="n"/>
       <c r="P709" s="1" t="n"/>
       <c r="Q709" s="1" t="inlineStr"/>
-      <c r="R709" s="1" t="n"/>
+      <c r="R709" s="1" t="inlineStr"/>
       <c r="S709" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -54241,16 +54321,16 @@
     </row>
     <row r="710">
       <c r="A710" s="1" t="n">
-        <v>83960</v>
+        <v>83708</v>
       </c>
       <c r="B710" s="1" t="inlineStr">
         <is>
-          <t>Restituição</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C710" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D710" s="1" t="inlineStr">
@@ -54260,20 +54340,20 @@
       </c>
       <c r="E710" s="1" t="inlineStr">
         <is>
-          <t>Prezados, Houve um erro na informação de quotas do IRPJ e CSLL 3º trimestre de 2025.anexo comprovantes de pagamento do protesto.</t>
+          <t xml:space="preserve">Por gentileza, providenciar a CND Municipal e enviar para Sr. Aurelio </t>
         </is>
       </c>
       <c r="F710" s="1" t="n">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="G710" s="1" t="inlineStr">
         <is>
-          <t>VITTA SALAD - PRODUTOS NATURAIS COMÉRCIO DE HORTI FRUTI LTDA</t>
+          <t>P.E Latina Maquinas para Rotulagem Ltda.</t>
         </is>
       </c>
       <c r="H710" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I710" s="1" t="inlineStr">
@@ -54282,29 +54362,40 @@
         </is>
       </c>
       <c r="J710" s="2" t="n">
-        <v>46279.67358012732</v>
+        <v>46274.43152577546</v>
       </c>
       <c r="K710" s="2" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="L710" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M710" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N710" s="1" t="n"/>
       <c r="O710" s="1" t="n"/>
-      <c r="P710" s="1" t="n"/>
-      <c r="Q710" s="1" t="inlineStr"/>
-      <c r="R710" s="1" t="inlineStr"/>
+      <c r="P710" s="2" t="n">
+        <v>46280.78062473379</v>
+      </c>
+      <c r="Q710" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R710" s="1" t="inlineStr">
+        <is>
+          <t>Boa noite!
+Não foi possivel emitir, há débitos em aberto.</t>
+        </is>
+      </c>
       <c r="S710" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T710" s="1" t="n"/>
@@ -54312,39 +54403,39 @@
     </row>
     <row r="711">
       <c r="A711" s="1" t="n">
-        <v>83708</v>
+        <v>83030</v>
       </c>
       <c r="B711" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C711" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D711" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E711" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, providenciar a CND Municipal e enviar para Sr. Aurelio </t>
+          <t>Abertura de holding da empresa 2681- Mercadinho Alves e Farias.Grupo: Paraná GuarulhosTributação: Lucro PresumidoFinalidade: Holding/EstratégiaForma Juridica: LTDAProposta já negociada no valor de: R$9.800,00 em 5x</t>
         </is>
       </c>
       <c r="F711" s="1" t="n">
-        <v>2576</v>
+        <v>2681</v>
       </c>
       <c r="G711" s="1" t="inlineStr">
         <is>
-          <t>P.E Latina Maquinas para Rotulagem Ltda.</t>
+          <t>COMÉRCIO DE ALIMENTOS ALVES E FARIAS LTDA</t>
         </is>
       </c>
       <c r="H711" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I711" s="1" t="inlineStr">
@@ -54353,40 +54444,35 @@
         </is>
       </c>
       <c r="J711" s="2" t="n">
-        <v>46274.43152577546</v>
+        <v>46260.44763082176</v>
       </c>
       <c r="K711" s="2" t="n">
-        <v>46275</v>
+        <v>46287</v>
       </c>
       <c r="L711" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M711" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
-        </is>
-      </c>
-      <c r="N711" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N711" s="2" t="n">
+        <v>46267.34800902778</v>
+      </c>
       <c r="O711" s="1" t="n"/>
-      <c r="P711" s="2" t="n">
-        <v>46280.78062473379</v>
-      </c>
-      <c r="Q711" s="1" t="inlineStr">
-        <is>
-          <t>Karina Dantas</t>
-        </is>
-      </c>
+      <c r="P711" s="1" t="n"/>
+      <c r="Q711" s="1" t="inlineStr"/>
       <c r="R711" s="1" t="inlineStr">
         <is>
-          <t>Boa noite!
-Não foi possivel emitir, há débitos em aberto.</t>
+          <t>Processo em elaboração</t>
         </is>
       </c>
       <c r="S711" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T711" s="1" t="n"/>
@@ -54394,16 +54480,16 @@
     </row>
     <row r="712">
       <c r="A712" s="1" t="n">
-        <v>83030</v>
+        <v>83004</v>
       </c>
       <c r="B712" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C712" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D712" s="1" t="inlineStr">
@@ -54413,20 +54499,20 @@
       </c>
       <c r="E712" s="1" t="inlineStr">
         <is>
-          <t>Abertura de holding da empresa 2681- Mercadinho Alves e Farias.Grupo: Paraná GuarulhosTributação: Lucro PresumidoFinalidade: Holding/EstratégiaForma Juridica: LTDAProposta já negociada no valor de: R$9.800,00 em 5x</t>
+          <t>Alteração contratual na empresa 2710-HORTIFRUTI BOM DO CAMPOGrupo: AlvoradaRETIRAR A LETICIA TORQUATO SILVEIRA DO QUADRO SOCIETÁRIO</t>
         </is>
       </c>
       <c r="F712" s="1" t="n">
-        <v>2681</v>
+        <v>2710</v>
       </c>
       <c r="G712" s="1" t="inlineStr">
         <is>
-          <t>COMÉRCIO DE ALIMENTOS ALVES E FARIAS LTDA</t>
+          <t>HORTIFRUTI BOM DO CAMPO LTDA</t>
         </is>
       </c>
       <c r="H712" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I712" s="1" t="inlineStr">
@@ -54435,7 +54521,7 @@
         </is>
       </c>
       <c r="J712" s="2" t="n">
-        <v>46260.44763082176</v>
+        <v>46259.70523434028</v>
       </c>
       <c r="K712" s="2" t="n">
         <v>46287</v>
@@ -54451,14 +54537,16 @@
         </is>
       </c>
       <c r="N712" s="2" t="n">
-        <v>46267.34800902778</v>
+        <v>46266.72352233796</v>
       </c>
       <c r="O712" s="1" t="n"/>
       <c r="P712" s="1" t="n"/>
       <c r="Q712" s="1" t="inlineStr"/>
       <c r="R712" s="1" t="inlineStr">
         <is>
-          <t>Processo em elaboração</t>
+          <t>Boa tarde.
+Preparando a minuta.
+Atenciosamente,</t>
         </is>
       </c>
       <c r="S712" s="1" t="inlineStr">
@@ -54471,39 +54559,39 @@
     </row>
     <row r="713">
       <c r="A713" s="1" t="n">
-        <v>83004</v>
+        <v>83570</v>
       </c>
       <c r="B713" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Inuitilização de Nota Fiscais</t>
         </is>
       </c>
       <c r="C713" s="1" t="inlineStr">
         <is>
-          <t>Sócios</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D713" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E713" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual na empresa 2710-HORTIFRUTI BOM DO CAMPOGrupo: AlvoradaRETIRAR A LETICIA TORQUATO SILVEIRA DO QUADRO SOCIETÁRIO</t>
+          <t>Bom dia. Nosso cliente 2789 está com um valor de ISS em aberto. Este valor é referente a uma NF que foi emitida incorretamente pela MG e não foi cancelada.Precisamos fazer um processo de cancelamento desta nota e cancelamento do valor que está sendo cobrado de ISS.NF Anexa</t>
         </is>
       </c>
       <c r="F713" s="1" t="n">
-        <v>2710</v>
+        <v>2789</v>
       </c>
       <c r="G713" s="1" t="inlineStr">
         <is>
-          <t>HORTIFRUTI BOM DO CAMPO LTDA</t>
+          <t>MARINGÁ MANUTENÇÃO DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H713" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I713" s="1" t="inlineStr">
@@ -54512,10 +54600,10 @@
         </is>
       </c>
       <c r="J713" s="2" t="n">
-        <v>46259.70523434028</v>
+        <v>46268.57512141204</v>
       </c>
       <c r="K713" s="2" t="n">
-        <v>46287</v>
+        <v>46272</v>
       </c>
       <c r="L713" s="1" t="inlineStr">
         <is>
@@ -54524,104 +54612,107 @@
       </c>
       <c r="M713" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N713" s="2" t="n">
-        <v>46266.72352233796</v>
+        <v>46273.66325274306</v>
       </c>
       <c r="O713" s="1" t="n"/>
       <c r="P713" s="1" t="n"/>
       <c r="Q713" s="1" t="inlineStr"/>
       <c r="R713" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.
-Preparando a minuta.
-Atenciosamente,</t>
-        </is>
-      </c>
-      <c r="S713" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T713" s="1" t="n"/>
-      <c r="U713" s="1" t="inlineStr"/>
-    </row>
-    <row r="714">
-      <c r="A714" s="1" t="n">
-        <v>83570</v>
-      </c>
-      <c r="B714" s="1" t="inlineStr">
-        <is>
-          <t>Inuitilização de Nota Fiscais</t>
-        </is>
-      </c>
-      <c r="C714" s="1" t="inlineStr">
-        <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="D714" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E714" s="1" t="inlineStr">
-        <is>
-          <t>Bom dia. Nosso cliente 2789 está com um valor de ISS em aberto. Este valor é referente a uma NF que foi emitida incorretamente pela MG e não foi cancelada.Precisamos fazer um processo de cancelamento desta nota e cancelamento do valor que está sendo cobrado de ISS.NF Anexa</t>
-        </is>
-      </c>
-      <c r="F714" s="1" t="n">
-        <v>2789</v>
-      </c>
-      <c r="G714" s="1" t="inlineStr">
-        <is>
-          <t>MARINGÁ MANUTENÇÃO DE EQUIPAMENTOS LTDA</t>
-        </is>
-      </c>
-      <c r="H714" s="1" t="inlineStr">
-        <is>
-          <t>Karina Dantas</t>
-        </is>
-      </c>
-      <c r="I714" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J714" s="2" t="n">
-        <v>46268.57512141204</v>
-      </c>
-      <c r="K714" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="L714" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M714" s="1" t="inlineStr">
-        <is>
-          <t>Daniel Oliveira</t>
-        </is>
-      </c>
-      <c r="N714" s="2" t="n">
-        <v>46273.66325274306</v>
-      </c>
-      <c r="O714" s="1" t="n"/>
-      <c r="P714" s="1" t="n"/>
-      <c r="Q714" s="1" t="inlineStr"/>
-      <c r="R714" s="1" t="inlineStr">
-        <is>
           <t xml:space="preserve">Boa tarde!
 A Prefeitura solicita que seja informado o motivo do cancelamento. Qual o motivo?
 Iremos precisar enviar ao cliente a carta de anuência e procuração para assinatura. </t>
         </is>
       </c>
+      <c r="S713" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T713" s="1" t="n"/>
+      <c r="U713" s="1" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="n">
+        <v>83990</v>
+      </c>
+      <c r="B714" s="1" t="inlineStr">
+        <is>
+          <t>Levantamento de Débitos</t>
+        </is>
+      </c>
+      <c r="C714" s="1" t="inlineStr">
+        <is>
+          <t>Prefeitura</t>
+        </is>
+      </c>
+      <c r="D714" s="1" t="inlineStr">
+        <is>
+          <t>SANTOS - ADM</t>
+        </is>
+      </c>
+      <c r="E714" s="1" t="inlineStr">
+        <is>
+          <t>A empresa 2823 está sem Inscrição Municipal disponível, impossibilitando o levantamento de débitos.Foi localizado um e-mail de 08/05/2025 informando que a inscrição estava em processo de abertura.Podem verificar a situação atual e nos auxiliar com o levantamento?</t>
+        </is>
+      </c>
+      <c r="F714" s="1" t="n">
+        <v>2823</v>
+      </c>
+      <c r="G714" s="1" t="inlineStr">
+        <is>
+          <t>GT OSHIRO DISTRIBUIDORA DE HORTIFRUTIGRANJEIROS LTDA</t>
+        </is>
+      </c>
+      <c r="H714" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
+      <c r="I714" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J714" s="2" t="n">
+        <v>46280.43936226852</v>
+      </c>
+      <c r="K714" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="L714" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M714" s="1" t="inlineStr">
+        <is>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="N714" s="1" t="n"/>
+      <c r="O714" s="1" t="n"/>
+      <c r="P714" s="2" t="n">
+        <v>46282.42984756944</v>
+      </c>
+      <c r="Q714" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
+      <c r="R714" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde levantamento de débitos não é comigo direciona esse chamado para o Ronaldo e ele irá te orientar melhor.
+Atenciosamente</t>
+        </is>
+      </c>
       <c r="S714" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T714" s="1" t="n"/>
@@ -54629,34 +54720,34 @@
     </row>
     <row r="715">
       <c r="A715" s="1" t="n">
-        <v>83990</v>
+        <v>83967</v>
       </c>
       <c r="B715" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C715" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D715" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E715" s="1" t="inlineStr">
         <is>
-          <t>A empresa 2823 está sem Inscrição Municipal disponível, impossibilitando o levantamento de débitos.Foi localizado um e-mail de 08/05/2025 informando que a inscrição estava em processo de abertura.Podem verificar a situação atual e nos auxiliar com o levantamento?</t>
+          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A3</t>
         </is>
       </c>
       <c r="F715" s="1" t="n">
-        <v>2823</v>
+        <v>2853</v>
       </c>
       <c r="G715" s="1" t="inlineStr">
         <is>
-          <t>GT OSHIRO DISTRIBUIDORA DE HORTIFRUTIGRANJEIROS LTDA</t>
+          <t>BERTON SUPERMERCADOS COMERCIO DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H715" s="1" t="inlineStr">
@@ -54670,40 +54761,37 @@
         </is>
       </c>
       <c r="J715" s="2" t="n">
-        <v>46280.43936226852</v>
+        <v>46279.73161238426</v>
       </c>
       <c r="K715" s="2" t="n">
-        <v>46281</v>
+        <v>46307</v>
       </c>
       <c r="L715" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M715" s="1" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
-        </is>
-      </c>
-      <c r="N715" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N715" s="2" t="n">
+        <v>46286.69842271991</v>
+      </c>
       <c r="O715" s="1" t="n"/>
-      <c r="P715" s="2" t="n">
-        <v>46282.42984756944</v>
-      </c>
-      <c r="Q715" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
+      <c r="P715" s="1" t="n"/>
+      <c r="Q715" s="1" t="inlineStr"/>
       <c r="R715" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde levantamento de débitos não é comigo direciona esse chamado para o Ronaldo e ele irá te orientar melhor.
-Atenciosamente</t>
+          <t>Boa tarde.
+Minuta em andamento.
+Atenciosamente,</t>
         </is>
       </c>
       <c r="S715" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T715" s="1" t="n"/>
@@ -54711,7 +54799,7 @@
     </row>
     <row r="716">
       <c r="A716" s="1" t="n">
-        <v>83967</v>
+        <v>83969</v>
       </c>
       <c r="B716" s="1" t="inlineStr">
         <is>
@@ -54730,7 +54818,7 @@
       </c>
       <c r="E716" s="1" t="inlineStr">
         <is>
-          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A3</t>
+          <t>Abertura de nova empresa vinculada ao grupo: Berton Tributação: Simples NacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A2</t>
         </is>
       </c>
       <c r="F716" s="1" t="n">
@@ -54752,7 +54840,7 @@
         </is>
       </c>
       <c r="J716" s="2" t="n">
-        <v>46279.73161238426</v>
+        <v>46279.73473055555</v>
       </c>
       <c r="K716" s="2" t="n">
         <v>46307</v>
@@ -54768,7 +54856,7 @@
         </is>
       </c>
       <c r="N716" s="2" t="n">
-        <v>46286.69842271991</v>
+        <v>46286.69851774305</v>
       </c>
       <c r="O716" s="1" t="n"/>
       <c r="P716" s="1" t="n"/>
@@ -54790,7 +54878,7 @@
     </row>
     <row r="717">
       <c r="A717" s="1" t="n">
-        <v>83969</v>
+        <v>83970</v>
       </c>
       <c r="B717" s="1" t="inlineStr">
         <is>
@@ -54809,7 +54897,7 @@
       </c>
       <c r="E717" s="1" t="inlineStr">
         <is>
-          <t>Abertura de nova empresa vinculada ao grupo: Berton Tributação: Simples NacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A2</t>
+          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A1</t>
         </is>
       </c>
       <c r="F717" s="1" t="n">
@@ -54831,7 +54919,7 @@
         </is>
       </c>
       <c r="J717" s="2" t="n">
-        <v>46279.73473055555</v>
+        <v>46279.73921559028</v>
       </c>
       <c r="K717" s="2" t="n">
         <v>46307</v>
@@ -54847,7 +54935,7 @@
         </is>
       </c>
       <c r="N717" s="2" t="n">
-        <v>46286.69851774305</v>
+        <v>46286.69860459491</v>
       </c>
       <c r="O717" s="1" t="n"/>
       <c r="P717" s="1" t="n"/>
@@ -54869,7 +54957,7 @@
     </row>
     <row r="718">
       <c r="A718" s="1" t="n">
-        <v>83970</v>
+        <v>83972</v>
       </c>
       <c r="B718" s="1" t="inlineStr">
         <is>
@@ -54888,7 +54976,7 @@
       </c>
       <c r="E718" s="1" t="inlineStr">
         <is>
-          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala A1</t>
+          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples NacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala B-1</t>
         </is>
       </c>
       <c r="F718" s="1" t="n">
@@ -54910,7 +54998,7 @@
         </is>
       </c>
       <c r="J718" s="2" t="n">
-        <v>46279.73921559028</v>
+        <v>46279.74341068287</v>
       </c>
       <c r="K718" s="2" t="n">
         <v>46307</v>
@@ -54926,7 +55014,7 @@
         </is>
       </c>
       <c r="N718" s="2" t="n">
-        <v>46286.69860459491</v>
+        <v>46286.69870274306</v>
       </c>
       <c r="O718" s="1" t="n"/>
       <c r="P718" s="1" t="n"/>
@@ -54948,7 +55036,7 @@
     </row>
     <row r="719">
       <c r="A719" s="1" t="n">
-        <v>83972</v>
+        <v>83974</v>
       </c>
       <c r="B719" s="1" t="inlineStr">
         <is>
@@ -54967,7 +55055,7 @@
       </c>
       <c r="E719" s="1" t="inlineStr">
         <is>
-          <t>Abertura de nova empresa vinculada ao grupo: BertonTributação: Simples NacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala B-1</t>
+          <t>Abertura de empresa vinculada ao grupo: Berton Tributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala B-2</t>
         </is>
       </c>
       <c r="F719" s="1" t="n">
@@ -54989,7 +55077,7 @@
         </is>
       </c>
       <c r="J719" s="2" t="n">
-        <v>46279.74341068287</v>
+        <v>46279.74682947917</v>
       </c>
       <c r="K719" s="2" t="n">
         <v>46307</v>
@@ -55005,7 +55093,7 @@
         </is>
       </c>
       <c r="N719" s="2" t="n">
-        <v>46286.69870274306</v>
+        <v>46286.69879675926</v>
       </c>
       <c r="O719" s="1" t="n"/>
       <c r="P719" s="1" t="n"/>
@@ -55027,39 +55115,39 @@
     </row>
     <row r="720">
       <c r="A720" s="1" t="n">
-        <v>83974</v>
+        <v>83702</v>
       </c>
       <c r="B720" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C720" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Razão Social</t>
         </is>
       </c>
       <c r="D720" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="E720" s="1" t="inlineStr">
         <is>
-          <t>Abertura de empresa vinculada ao grupo: Berton Tributação: Simples nacionalProposta já negociada no valor de R$1.400,00Obs.: complemento do endereço: sala B-2</t>
+          <t>AGGYO ADMINISTRAÇÃO DE BENS E PATICIPAÇÕES S.ACNPJ: 21.940.311/0001-00 Alteração: JSVE RENTAL ADMINISTRAÇÃO DE BENS E PATICIPAÇÕES S.A</t>
         </is>
       </c>
       <c r="F720" s="1" t="n">
-        <v>2853</v>
+        <v>2956</v>
       </c>
       <c r="G720" s="1" t="inlineStr">
         <is>
-          <t>BERTON SUPERMERCADOS COMERCIO DE ALIMENTOS LTDA</t>
+          <t>AGGYO ADMINISTRAÇÃO DE BENS E PARTICIPAÇÕES S.A.</t>
         </is>
       </c>
       <c r="H720" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I720" s="1" t="inlineStr">
@@ -55068,10 +55156,10 @@
         </is>
       </c>
       <c r="J720" s="2" t="n">
-        <v>46279.74682947917</v>
+        <v>46274.42399050926</v>
       </c>
       <c r="K720" s="2" t="n">
-        <v>46307</v>
+        <v>46275</v>
       </c>
       <c r="L720" s="1" t="inlineStr">
         <is>
@@ -55080,104 +55168,107 @@
       </c>
       <c r="M720" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="N720" s="2" t="n">
-        <v>46286.69879675926</v>
+        <v>46274.79115416667</v>
       </c>
       <c r="O720" s="1" t="n"/>
       <c r="P720" s="1" t="n"/>
       <c r="Q720" s="1" t="inlineStr"/>
       <c r="R720" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.
-Minuta em andamento.
-Atenciosamente,</t>
-        </is>
-      </c>
-      <c r="S720" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T720" s="1" t="n"/>
-      <c r="U720" s="1" t="inlineStr"/>
-    </row>
-    <row r="721">
-      <c r="A721" s="1" t="n">
-        <v>83702</v>
-      </c>
-      <c r="B721" s="1" t="inlineStr">
-        <is>
-          <t>Alteração Contratual</t>
-        </is>
-      </c>
-      <c r="C721" s="1" t="inlineStr">
-        <is>
-          <t>Razão Social</t>
-        </is>
-      </c>
-      <c r="D721" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="E721" s="1" t="inlineStr">
-        <is>
-          <t>AGGYO ADMINISTRAÇÃO DE BENS E PATICIPAÇÕES S.ACNPJ: 21.940.311/0001-00 Alteração: JSVE RENTAL ADMINISTRAÇÃO DE BENS E PATICIPAÇÕES S.A</t>
-        </is>
-      </c>
-      <c r="F721" s="1" t="n">
-        <v>2956</v>
-      </c>
-      <c r="G721" s="1" t="inlineStr">
-        <is>
-          <t>AGGYO ADMINISTRAÇÃO DE BENS E PARTICIPAÇÕES S.A.</t>
-        </is>
-      </c>
-      <c r="H721" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
-      <c r="I721" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J721" s="2" t="n">
-        <v>46274.42399050926</v>
-      </c>
-      <c r="K721" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="L721" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M721" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
-      <c r="N721" s="2" t="n">
-        <v>46274.79115416667</v>
-      </c>
-      <c r="O721" s="1" t="n"/>
-      <c r="P721" s="1" t="n"/>
-      <c r="Q721" s="1" t="inlineStr"/>
-      <c r="R721" s="1" t="inlineStr">
-        <is>
           <t>Prezados(as), boa tarde!
 Alteração contratual em andamento, conforme solicitado.
 Atenciosamente,</t>
         </is>
       </c>
+      <c r="S720" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T720" s="1" t="n"/>
+      <c r="U720" s="1" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="n">
+        <v>83075</v>
+      </c>
+      <c r="B721" s="1" t="inlineStr">
+        <is>
+          <t>Parcelamento Estadual</t>
+        </is>
+      </c>
+      <c r="C721" s="1" t="inlineStr">
+        <is>
+          <t>Divida Ativa</t>
+        </is>
+      </c>
+      <c r="D721" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E721" s="1" t="inlineStr">
+        <is>
+          <t>Prezados, o cliente está solicitando a simulação de parcelamento dos débitos, que estão no CADIN.</t>
+        </is>
+      </c>
+      <c r="F721" s="1" t="n">
+        <v>3153</v>
+      </c>
+      <c r="G721" s="1" t="inlineStr">
+        <is>
+          <t>Zibetto Pizzaria Eireli</t>
+        </is>
+      </c>
+      <c r="H721" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="I721" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J721" s="2" t="n">
+        <v>46260.70641142361</v>
+      </c>
+      <c r="K721" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L721" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M721" s="1" t="inlineStr">
+        <is>
+          <t>Rodrigo Rego</t>
+        </is>
+      </c>
+      <c r="N721" s="1" t="n"/>
+      <c r="O721" s="1" t="n"/>
+      <c r="P721" s="2" t="n">
+        <v>46262.43234614583</v>
+      </c>
+      <c r="Q721" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R721" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bom dia!
+Segue simulados e proposta. </t>
+        </is>
+      </c>
       <c r="S721" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T721" s="1" t="n"/>
@@ -55185,39 +55276,39 @@
     </row>
     <row r="722">
       <c r="A722" s="1" t="n">
-        <v>83075</v>
+        <v>84015</v>
       </c>
       <c r="B722" s="1" t="inlineStr">
         <is>
-          <t>Parcelamento Estadual</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C722" s="1" t="inlineStr">
         <is>
-          <t>Divida Ativa</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D722" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E722" s="1" t="inlineStr">
         <is>
-          <t>Prezados, o cliente está solicitando a simulação de parcelamento dos débitos, que estão no CADIN.</t>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
         </is>
       </c>
       <c r="F722" s="1" t="n">
-        <v>3153</v>
+        <v>3482</v>
       </c>
       <c r="G722" s="1" t="inlineStr">
         <is>
-          <t>Zibetto Pizzaria Eireli</t>
+          <t>L. A. TAHA - ESTACIONAMENTO</t>
         </is>
       </c>
       <c r="H722" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I722" s="1" t="inlineStr">
@@ -55226,10 +55317,10 @@
         </is>
       </c>
       <c r="J722" s="2" t="n">
-        <v>46260.70641142361</v>
+        <v>46280.47807916666</v>
       </c>
       <c r="K722" s="2" t="n">
-        <v>46262</v>
+        <v>46281</v>
       </c>
       <c r="L722" s="1" t="inlineStr">
         <is>
@@ -55238,23 +55329,24 @@
       </c>
       <c r="M722" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
-        </is>
-      </c>
-      <c r="N722" s="1" t="n"/>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N722" s="2" t="n">
+        <v>46281.75651021991</v>
+      </c>
       <c r="O722" s="1" t="n"/>
       <c r="P722" s="2" t="n">
-        <v>46262.43234614583</v>
+        <v>46283.4427380787</v>
       </c>
       <c r="Q722" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="R722" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia!
-Segue simulados e proposta. </t>
+          <t>Certidão/Levantamento solicitado, aguardando retorno.</t>
         </is>
       </c>
       <c r="S722" s="1" t="inlineStr">
@@ -55267,39 +55359,39 @@
     </row>
     <row r="723">
       <c r="A723" s="1" t="n">
-        <v>84015</v>
+        <v>82810</v>
       </c>
       <c r="B723" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Processo de VISA</t>
         </is>
       </c>
       <c r="C723" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Renovação</t>
         </is>
       </c>
       <c r="D723" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E723" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Cliente solicita renovação de alvará de funcionamento.</t>
         </is>
       </c>
       <c r="F723" s="1" t="n">
-        <v>3482</v>
+        <v>3759</v>
       </c>
       <c r="G723" s="1" t="inlineStr">
         <is>
-          <t>L. A. TAHA - ESTACIONAMENTO</t>
+          <t xml:space="preserve">MEDIC NET LTDA </t>
         </is>
       </c>
       <c r="H723" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I723" s="1" t="inlineStr">
@@ -55308,41 +55400,37 @@
         </is>
       </c>
       <c r="J723" s="2" t="n">
-        <v>46280.47807916666</v>
+        <v>46255.63596686342</v>
       </c>
       <c r="K723" s="2" t="n">
-        <v>46281</v>
+        <v>46258</v>
       </c>
       <c r="L723" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M723" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Romero Borges</t>
         </is>
       </c>
       <c r="N723" s="2" t="n">
-        <v>46281.75651021991</v>
+        <v>46273.36963711806</v>
       </c>
       <c r="O723" s="1" t="n"/>
-      <c r="P723" s="2" t="n">
-        <v>46283.4427380787</v>
-      </c>
-      <c r="Q723" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P723" s="1" t="n"/>
+      <c r="Q723" s="1" t="inlineStr"/>
       <c r="R723" s="1" t="inlineStr">
         <is>
-          <t>Certidão/Levantamento solicitado, aguardando retorno.</t>
+          <t xml:space="preserve">Prezados(as), bom dia!
+Solicitação em andamento. 
+Atenciosamente, </t>
         </is>
       </c>
       <c r="S723" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T723" s="1" t="n"/>
@@ -55350,7 +55438,7 @@
     </row>
     <row r="724">
       <c r="A724" s="1" t="n">
-        <v>82810</v>
+        <v>82809</v>
       </c>
       <c r="B724" s="1" t="inlineStr">
         <is>
@@ -55373,11 +55461,11 @@
         </is>
       </c>
       <c r="F724" s="1" t="n">
-        <v>3759</v>
+        <v>3760</v>
       </c>
       <c r="G724" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDIC NET LTDA </t>
+          <t xml:space="preserve">MED ALPHA DISTRIBUIDORA DE PRODUTOS MÉDICOS E HOSPITALARES EM GERAL LTDA </t>
         </is>
       </c>
       <c r="H724" s="1" t="inlineStr">
@@ -55391,7 +55479,7 @@
         </is>
       </c>
       <c r="J724" s="2" t="n">
-        <v>46255.63596686342</v>
+        <v>46255.63541871528</v>
       </c>
       <c r="K724" s="2" t="n">
         <v>46258</v>
@@ -55407,7 +55495,7 @@
         </is>
       </c>
       <c r="N724" s="2" t="n">
-        <v>46273.36963711806</v>
+        <v>46273.36949383102</v>
       </c>
       <c r="O724" s="1" t="n"/>
       <c r="P724" s="1" t="n"/>
@@ -55429,39 +55517,39 @@
     </row>
     <row r="725">
       <c r="A725" s="1" t="n">
-        <v>82809</v>
+        <v>84014</v>
       </c>
       <c r="B725" s="1" t="inlineStr">
         <is>
-          <t>Processo de VISA</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C725" s="1" t="inlineStr">
         <is>
-          <t>Renovação</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D725" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E725" s="1" t="inlineStr">
         <is>
-          <t>Cliente solicita renovação de alvará de funcionamento.</t>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
         </is>
       </c>
       <c r="F725" s="1" t="n">
-        <v>3760</v>
+        <v>4178</v>
       </c>
       <c r="G725" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED ALPHA DISTRIBUIDORA DE PRODUTOS MÉDICOS E HOSPITALARES EM GERAL LTDA </t>
+          <t>SERFARMA DROGARIA LTDA</t>
         </is>
       </c>
       <c r="H725" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I725" s="1" t="inlineStr">
@@ -55470,37 +55558,39 @@
         </is>
       </c>
       <c r="J725" s="2" t="n">
-        <v>46255.63541871528</v>
+        <v>46280.47752337963</v>
       </c>
       <c r="K725" s="2" t="n">
-        <v>46258</v>
+        <v>46281</v>
       </c>
       <c r="L725" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M725" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N725" s="2" t="n">
-        <v>46273.36949383102</v>
-      </c>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N725" s="1" t="n"/>
       <c r="O725" s="1" t="n"/>
-      <c r="P725" s="1" t="n"/>
-      <c r="Q725" s="1" t="inlineStr"/>
+      <c r="P725" s="2" t="n">
+        <v>46281.42727723379</v>
+      </c>
+      <c r="Q725" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="R725" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados(as), bom dia!
-Solicitação em andamento. 
-Atenciosamente, </t>
+          <t>Yasmin, segue levantamento de débitos na Prefeitura de Itapecerica da Serfarma, consta um ISS de 2023, segue guia atualizada com vencimento para hoje, 16/09/2026.</t>
         </is>
       </c>
       <c r="S725" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T725" s="1" t="n"/>
@@ -55508,39 +55598,39 @@
     </row>
     <row r="726">
       <c r="A726" s="1" t="n">
-        <v>84014</v>
+        <v>81601</v>
       </c>
       <c r="B726" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Processo de VISA</t>
         </is>
       </c>
       <c r="C726" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Renovação</t>
         </is>
       </c>
       <c r="D726" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E726" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa BEST SALAD conforme solicitação do cliente.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F726" s="1" t="n">
-        <v>4178</v>
+        <v>4194</v>
       </c>
       <c r="G726" s="1" t="inlineStr">
         <is>
-          <t>SERFARMA DROGARIA LTDA</t>
+          <t>BEST SALAD HORTI FRUTI LTDA</t>
         </is>
       </c>
       <c r="H726" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I726" s="1" t="inlineStr">
@@ -55549,10 +55639,10 @@
         </is>
       </c>
       <c r="J726" s="2" t="n">
-        <v>46280.47752337963</v>
+        <v>46233.40595859953</v>
       </c>
       <c r="K726" s="2" t="n">
-        <v>46281</v>
+        <v>46237</v>
       </c>
       <c r="L726" s="1" t="inlineStr">
         <is>
@@ -55561,22 +55651,25 @@
       </c>
       <c r="M726" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N726" s="1" t="n"/>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N726" s="2" t="n">
+        <v>46234.48805347223</v>
+      </c>
       <c r="O726" s="1" t="n"/>
       <c r="P726" s="2" t="n">
-        <v>46281.42727723379</v>
+        <v>46237.37169996528</v>
       </c>
       <c r="Q726" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="R726" s="1" t="inlineStr">
         <is>
-          <t>Yasmin, segue levantamento de débitos na Prefeitura de Itapecerica da Serfarma, consta um ISS de 2023, segue guia atualizada com vencimento para hoje, 16/09/2026.</t>
+          <t>O sistema do VRE está com problemas, assim que disponível, concluímos o CLI.
+Atenciosamente,</t>
         </is>
       </c>
       <c r="S726" s="1" t="inlineStr">
@@ -55589,7 +55682,7 @@
     </row>
     <row r="727">
       <c r="A727" s="1" t="n">
-        <v>81601</v>
+        <v>81603</v>
       </c>
       <c r="B727" s="1" t="inlineStr">
         <is>
@@ -55608,15 +55701,15 @@
       </c>
       <c r="E727" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa BEST SALAD conforme solicitação do cliente.Grato,Bruno.</t>
+          <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa Terra Brasil conforme solicitação do cliente.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F727" s="1" t="n">
-        <v>4194</v>
+        <v>4195</v>
       </c>
       <c r="G727" s="1" t="inlineStr">
         <is>
-          <t>BEST SALAD HORTI FRUTI LTDA</t>
+          <t>TERRA BRASIL HORTI FRUTI LTDA</t>
         </is>
       </c>
       <c r="H727" s="1" t="inlineStr">
@@ -55630,7 +55723,7 @@
         </is>
       </c>
       <c r="J727" s="2" t="n">
-        <v>46233.40595859953</v>
+        <v>46233.40691574074</v>
       </c>
       <c r="K727" s="2" t="n">
         <v>46237</v>
@@ -55646,11 +55739,11 @@
         </is>
       </c>
       <c r="N727" s="2" t="n">
-        <v>46234.48805347223</v>
+        <v>46234.48788619213</v>
       </c>
       <c r="O727" s="1" t="n"/>
       <c r="P727" s="2" t="n">
-        <v>46237.37169996528</v>
+        <v>46240.39679517361</v>
       </c>
       <c r="Q727" s="1" t="inlineStr">
         <is>
@@ -55673,7 +55766,7 @@
     </row>
     <row r="728">
       <c r="A728" s="1" t="n">
-        <v>81603</v>
+        <v>83684</v>
       </c>
       <c r="B728" s="1" t="inlineStr">
         <is>
@@ -55687,12 +55780,12 @@
       </c>
       <c r="D728" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E728" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Bom dia!Por gentileza, providenciar VRE da empresa Terra Brasil conforme solicitação do cliente.Grato,Bruno.</t>
+          <t xml:space="preserve">Por gentileza, providenciar renovação de alvará de funcionamento. </t>
         </is>
       </c>
       <c r="F728" s="1" t="n">
@@ -55714,10 +55807,10 @@
         </is>
       </c>
       <c r="J728" s="2" t="n">
-        <v>46233.40691574074</v>
+        <v>46273.73010833334</v>
       </c>
       <c r="K728" s="2" t="n">
-        <v>46237</v>
+        <v>46275</v>
       </c>
       <c r="L728" s="1" t="inlineStr">
         <is>
@@ -55729,12 +55822,10 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N728" s="2" t="n">
-        <v>46234.48788619213</v>
-      </c>
+      <c r="N728" s="1" t="n"/>
       <c r="O728" s="1" t="n"/>
       <c r="P728" s="2" t="n">
-        <v>46240.39679517361</v>
+        <v>46274.48608564815</v>
       </c>
       <c r="Q728" s="1" t="inlineStr">
         <is>
@@ -55742,176 +55833,177 @@
         </is>
       </c>
       <c r="R728" s="1" t="inlineStr">
-        <is>
-          <t>O sistema do VRE está com problemas, assim que disponível, concluímos o CLI.
-Atenciosamente,</t>
-        </is>
-      </c>
-      <c r="S728" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T728" s="1" t="n"/>
-      <c r="U728" s="1" t="inlineStr"/>
-    </row>
-    <row r="729">
-      <c r="A729" s="1" t="n">
-        <v>83684</v>
-      </c>
-      <c r="B729" s="1" t="inlineStr">
-        <is>
-          <t>Processo de VISA</t>
-        </is>
-      </c>
-      <c r="C729" s="1" t="inlineStr">
-        <is>
-          <t>Renovação</t>
-        </is>
-      </c>
-      <c r="D729" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E729" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por gentileza, providenciar renovação de alvará de funcionamento. </t>
-        </is>
-      </c>
-      <c r="F729" s="1" t="n">
-        <v>4195</v>
-      </c>
-      <c r="G729" s="1" t="inlineStr">
-        <is>
-          <t>TERRA BRASIL HORTI FRUTI LTDA</t>
-        </is>
-      </c>
-      <c r="H729" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
-      <c r="I729" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J729" s="2" t="n">
-        <v>46273.73010833334</v>
-      </c>
-      <c r="K729" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="L729" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M729" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N729" s="1" t="n"/>
-      <c r="O729" s="1" t="n"/>
-      <c r="P729" s="2" t="n">
-        <v>46274.48608564815</v>
-      </c>
-      <c r="Q729" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
-      <c r="R729" s="1" t="inlineStr">
         <is>
           <t>Bom dia.
 Email respondido hoje para a Patricia com Gerente Bruno em cópia.
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S729" s="1" t="inlineStr">
+      <c r="S728" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T729" s="1" t="n"/>
-      <c r="U729" s="1" t="inlineStr"/>
-    </row>
-    <row r="730">
-      <c r="A730" s="1" t="n">
+      <c r="T728" s="1" t="n"/>
+      <c r="U728" s="1" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="n">
         <v>83703</v>
       </c>
-      <c r="B730" s="1" t="inlineStr">
+      <c r="B729" s="1" t="inlineStr">
         <is>
           <t>Alteração Contratual</t>
         </is>
       </c>
-      <c r="C730" s="1" t="inlineStr">
+      <c r="C729" s="1" t="inlineStr">
         <is>
           <t>Razão Social</t>
         </is>
       </c>
-      <c r="D730" s="1" t="inlineStr">
+      <c r="D729" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="E730" s="1" t="inlineStr">
+      <c r="E729" s="1" t="inlineStr">
         <is>
           <t>SVG GROUP EMPREENDIMENTOS E PARTICIPAÇÕES S.ACNPJ: 38.042.809/0001-59 Alteração:JSVG COMPANY EMPREENDIMENTOS E PARTICIPAÇÕES S.A</t>
         </is>
       </c>
-      <c r="F730" s="1" t="n">
+      <c r="F729" s="1" t="n">
         <v>4295</v>
       </c>
-      <c r="G730" s="1" t="inlineStr">
+      <c r="G729" s="1" t="inlineStr">
         <is>
           <t>SVG GROUP EMPREENDIMENTOS E PARTICIPAÇÕES S.A</t>
         </is>
       </c>
-      <c r="H730" s="1" t="inlineStr">
+      <c r="H729" s="1" t="inlineStr">
         <is>
           <t>Bianca Ribeiro</t>
         </is>
       </c>
-      <c r="I730" s="1" t="inlineStr">
+      <c r="I729" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J730" s="2" t="n">
+      <c r="J729" s="2" t="n">
         <v>46274.42515038195</v>
       </c>
-      <c r="K730" s="2" t="n">
+      <c r="K729" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="L730" s="1" t="inlineStr">
+      <c r="L729" s="1" t="inlineStr">
         <is>
           <t>Em Atendimento</t>
         </is>
       </c>
-      <c r="M730" s="1" t="inlineStr">
+      <c r="M729" s="1" t="inlineStr">
         <is>
           <t>Ronaldo Dias</t>
         </is>
       </c>
-      <c r="N730" s="2" t="n">
+      <c r="N729" s="2" t="n">
         <v>46274.79132711806</v>
       </c>
-      <c r="O730" s="1" t="n"/>
-      <c r="P730" s="1" t="n"/>
-      <c r="Q730" s="1" t="inlineStr"/>
-      <c r="R730" s="1" t="inlineStr">
+      <c r="O729" s="1" t="n"/>
+      <c r="P729" s="1" t="n"/>
+      <c r="Q729" s="1" t="inlineStr"/>
+      <c r="R729" s="1" t="inlineStr">
         <is>
           <t>Prezados(as), boa tarde!
 Alteração contratual em andamento, conforme solicitado.
 Atenciosamente,</t>
         </is>
       </c>
+      <c r="S729" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T729" s="1" t="n"/>
+      <c r="U729" s="1" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="n">
+        <v>84004</v>
+      </c>
+      <c r="B730" s="1" t="inlineStr">
+        <is>
+          <t>Levantamento de Débitos</t>
+        </is>
+      </c>
+      <c r="C730" s="1" t="inlineStr">
+        <is>
+          <t>Prefeitura</t>
+        </is>
+      </c>
+      <c r="D730" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E730" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+        </is>
+      </c>
+      <c r="F730" s="1" t="n">
+        <v>4357</v>
+      </c>
+      <c r="G730" s="1" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 04)</t>
+        </is>
+      </c>
+      <c r="H730" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I730" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J730" s="2" t="n">
+        <v>46280.47172650463</v>
+      </c>
+      <c r="K730" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="L730" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M730" s="1" t="inlineStr">
+        <is>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N730" s="2" t="n">
+        <v>46280.72251597222</v>
+      </c>
+      <c r="O730" s="1" t="n"/>
+      <c r="P730" s="2" t="n">
+        <v>46283.44246041666</v>
+      </c>
+      <c r="Q730" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R730" s="1" t="inlineStr">
+        <is>
+          <t>Solicitado à Prefeitura levantamento de débitos atualizado, aguardando.</t>
+        </is>
+      </c>
       <c r="S730" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T730" s="1" t="n"/>
@@ -55919,16 +56011,16 @@
     </row>
     <row r="731">
       <c r="A731" s="1" t="n">
-        <v>84004</v>
+        <v>84385</v>
       </c>
       <c r="B731" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Processo de Prefeitura</t>
         </is>
       </c>
       <c r="C731" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D731" s="1" t="inlineStr">
@@ -55938,63 +56030,47 @@
       </c>
       <c r="E731" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Boa tarde! Por gentileza, poderia encaminhar uma proposta para alteração de endereço, conforme a alteração contratual.</t>
         </is>
       </c>
       <c r="F731" s="1" t="n">
-        <v>4357</v>
+        <v>4359</v>
       </c>
       <c r="G731" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 04)</t>
-        </is>
-      </c>
-      <c r="H731" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+          <t>ROBSON DE SOUSA LIMA COMERCIO DE ABRASIVOS</t>
+        </is>
+      </c>
+      <c r="H731" s="1" t="n"/>
       <c r="I731" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J731" s="2" t="n">
-        <v>46280.47172650463</v>
+        <v>46288.57906299768</v>
       </c>
       <c r="K731" s="2" t="n">
-        <v>46281</v>
+        <v>46289</v>
       </c>
       <c r="L731" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M731" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N731" s="2" t="n">
-        <v>46280.72251597222</v>
-      </c>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N731" s="1" t="n"/>
       <c r="O731" s="1" t="n"/>
-      <c r="P731" s="2" t="n">
-        <v>46283.44246041666</v>
-      </c>
-      <c r="Q731" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="R731" s="1" t="inlineStr">
-        <is>
-          <t>Solicitado à Prefeitura levantamento de débitos atualizado, aguardando.</t>
-        </is>
-      </c>
+      <c r="P731" s="1" t="n"/>
+      <c r="Q731" s="1" t="inlineStr"/>
+      <c r="R731" s="1" t="n"/>
       <c r="S731" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T731" s="1" t="n"/>
@@ -56002,63 +56078,75 @@
     </row>
     <row r="732">
       <c r="A732" s="1" t="n">
-        <v>84385</v>
+        <v>81970</v>
       </c>
       <c r="B732" s="1" t="inlineStr">
         <is>
-          <t>Processo de Prefeitura</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C732" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D732" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E732" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, poderia encaminhar uma proposta para alteração de endereço, conforme a alteração contratual.</t>
+          <t>Efetuar a atualização do cadastro da prefeitura para o novo modelo do Gissonline</t>
         </is>
       </c>
       <c r="F732" s="1" t="n">
-        <v>4359</v>
+        <v>4414</v>
       </c>
       <c r="G732" s="1" t="inlineStr">
         <is>
-          <t>ROBSON DE SOUSA LIMA COMERCIO DE ABRASIVOS</t>
-        </is>
-      </c>
-      <c r="H732" s="1" t="n"/>
+          <t>HN LEONE ADMINISTRAÇÃO DE BENS LTDA</t>
+        </is>
+      </c>
+      <c r="H732" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Ribeiro</t>
+        </is>
+      </c>
       <c r="I732" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J732" s="2" t="n">
-        <v>46288.57906299768</v>
+        <v>46240.4986315162</v>
       </c>
       <c r="K732" s="2" t="n">
-        <v>46289</v>
+        <v>46244</v>
       </c>
       <c r="L732" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M732" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
-      <c r="N732" s="1" t="n"/>
+          <t>Jonatan Hayashibara</t>
+        </is>
+      </c>
+      <c r="N732" s="2" t="n">
+        <v>46244.66312627315</v>
+      </c>
       <c r="O732" s="1" t="n"/>
       <c r="P732" s="1" t="n"/>
       <c r="Q732" s="1" t="inlineStr"/>
-      <c r="R732" s="1" t="n"/>
+      <c r="R732" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prezados(as), boa tarde!
+Para ciência, empresa já possui os dados para cesso, entretanto, não possuímos. Neste caso, estamos em contato com cliente, favor aguardar retorno. 
+Atenciosamente, </t>
+        </is>
+      </c>
       <c r="S732" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -56069,75 +56157,63 @@
     </row>
     <row r="733">
       <c r="A733" s="1" t="n">
-        <v>81970</v>
+        <v>84342</v>
       </c>
       <c r="B733" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C733" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D733" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E733" s="1" t="inlineStr">
         <is>
-          <t>Efetuar a atualização do cadastro da prefeitura para o novo modelo do Gissonline</t>
+          <t>Por gentileza, emitir a CND municipal. Caso não seja possivel por favor verificar as pendencias</t>
         </is>
       </c>
       <c r="F733" s="1" t="n">
-        <v>4414</v>
+        <v>4527</v>
       </c>
       <c r="G733" s="1" t="inlineStr">
         <is>
-          <t>HN LEONE ADMINISTRAÇÃO DE BENS LTDA</t>
-        </is>
-      </c>
-      <c r="H733" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
+          <t>SMART BREAK COMERCIO LANCHES S.A.</t>
+        </is>
+      </c>
+      <c r="H733" s="1" t="n"/>
       <c r="I733" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J733" s="2" t="n">
-        <v>46240.4986315162</v>
+        <v>46287.78913105324</v>
       </c>
       <c r="K733" s="2" t="n">
-        <v>46244</v>
+        <v>46289</v>
       </c>
       <c r="L733" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M733" s="1" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
-        </is>
-      </c>
-      <c r="N733" s="2" t="n">
-        <v>46244.66312627315</v>
-      </c>
+          <t>Rogerio Egidio</t>
+        </is>
+      </c>
+      <c r="N733" s="1" t="n"/>
       <c r="O733" s="1" t="n"/>
       <c r="P733" s="1" t="n"/>
       <c r="Q733" s="1" t="inlineStr"/>
-      <c r="R733" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prezados(as), boa tarde!
-Para ciência, empresa já possui os dados para cesso, entretanto, não possuímos. Neste caso, estamos em contato com cliente, favor aguardar retorno. 
-Atenciosamente, </t>
-        </is>
-      </c>
+      <c r="R733" s="1" t="n"/>
       <c r="S733" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -56148,66 +56224,80 @@
     </row>
     <row r="734">
       <c r="A734" s="1" t="n">
-        <v>84342</v>
+        <v>83775</v>
       </c>
       <c r="B734" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C734" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D734" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E734" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, emitir a CND municipal. Caso não seja possivel por favor verificar as pendencias</t>
+          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos Federais. </t>
         </is>
       </c>
       <c r="F734" s="1" t="n">
-        <v>4527</v>
+        <v>5020</v>
       </c>
       <c r="G734" s="1" t="inlineStr">
         <is>
-          <t>SMART BREAK COMERCIO LANCHES S.A.</t>
-        </is>
-      </c>
-      <c r="H734" s="1" t="n"/>
+          <t>M GOMES CONSULTORIA LTDA</t>
+        </is>
+      </c>
+      <c r="H734" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="I734" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J734" s="2" t="n">
-        <v>46287.78913105324</v>
+        <v>46275.43249725694</v>
       </c>
       <c r="K734" s="2" t="n">
-        <v>46289</v>
+        <v>46276</v>
       </c>
       <c r="L734" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M734" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N734" s="1" t="n"/>
       <c r="O734" s="1" t="n"/>
-      <c r="P734" s="1" t="n"/>
-      <c r="Q734" s="1" t="inlineStr"/>
-      <c r="R734" s="1" t="n"/>
+      <c r="P734" s="2" t="n">
+        <v>46275.80605767361</v>
+      </c>
+      <c r="Q734" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R734" s="1" t="inlineStr">
+        <is>
+          <t>Não há débitos federais em aberto, segue certidão negativa.</t>
+        </is>
+      </c>
       <c r="S734" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T734" s="1" t="n"/>
@@ -56215,7 +56305,7 @@
     </row>
     <row r="735">
       <c r="A735" s="1" t="n">
-        <v>83775</v>
+        <v>83776</v>
       </c>
       <c r="B735" s="1" t="inlineStr">
         <is>
@@ -56224,7 +56314,7 @@
       </c>
       <c r="C735" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D735" s="1" t="inlineStr">
@@ -56234,7 +56324,7 @@
       </c>
       <c r="E735" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos Federais. </t>
+          <t>Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos Estaduais.</t>
         </is>
       </c>
       <c r="F735" s="1" t="n">
@@ -56256,7 +56346,7 @@
         </is>
       </c>
       <c r="J735" s="2" t="n">
-        <v>46275.43249725694</v>
+        <v>46275.43319429398</v>
       </c>
       <c r="K735" s="2" t="n">
         <v>46276</v>
@@ -56274,7 +56364,7 @@
       <c r="N735" s="1" t="n"/>
       <c r="O735" s="1" t="n"/>
       <c r="P735" s="2" t="n">
-        <v>46275.80605767361</v>
+        <v>46275.80373197917</v>
       </c>
       <c r="Q735" s="1" t="inlineStr">
         <is>
@@ -56283,7 +56373,7 @@
       </c>
       <c r="R735" s="1" t="inlineStr">
         <is>
-          <t>Não há débitos federais em aberto, segue certidão negativa.</t>
+          <t>Não há débitos estaduais em aberto, seguem certidões negativas.</t>
         </is>
       </c>
       <c r="S735" s="1" t="inlineStr">
@@ -56296,7 +56386,7 @@
     </row>
     <row r="736">
       <c r="A736" s="1" t="n">
-        <v>83776</v>
+        <v>83777</v>
       </c>
       <c r="B736" s="1" t="inlineStr">
         <is>
@@ -56305,7 +56395,7 @@
       </c>
       <c r="C736" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D736" s="1" t="inlineStr">
@@ -56315,7 +56405,7 @@
       </c>
       <c r="E736" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos Estaduais.</t>
+          <t>Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos da Prefeitura.</t>
         </is>
       </c>
       <c r="F736" s="1" t="n">
@@ -56337,7 +56427,7 @@
         </is>
       </c>
       <c r="J736" s="2" t="n">
-        <v>46275.43319429398</v>
+        <v>46275.43366273148</v>
       </c>
       <c r="K736" s="2" t="n">
         <v>46276</v>
@@ -56355,7 +56445,7 @@
       <c r="N736" s="1" t="n"/>
       <c r="O736" s="1" t="n"/>
       <c r="P736" s="2" t="n">
-        <v>46275.80373197917</v>
+        <v>46275.80130501158</v>
       </c>
       <c r="Q736" s="1" t="inlineStr">
         <is>
@@ -56364,7 +56454,7 @@
       </c>
       <c r="R736" s="1" t="inlineStr">
         <is>
-          <t>Não há débitos estaduais em aberto, seguem certidões negativas.</t>
+          <t>Não há débitos, segue certidão negativa.</t>
         </is>
       </c>
       <c r="S736" s="1" t="inlineStr">
@@ -56377,39 +56467,39 @@
     </row>
     <row r="737">
       <c r="A737" s="1" t="n">
-        <v>83777</v>
+        <v>82909</v>
       </c>
       <c r="B737" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C737" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D737" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="E737" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, prezados!!Por gentileza, realizar o levantamento de débitos da Prefeitura.</t>
+          <t>ALTERAÇÃO DO ENDEREÇO E OBJETO SOCIAL CONFORME VIABILIDADE.</t>
         </is>
       </c>
       <c r="F737" s="1" t="n">
-        <v>5020</v>
+        <v>5048</v>
       </c>
       <c r="G737" s="1" t="inlineStr">
         <is>
-          <t>M GOMES CONSULTORIA LTDA</t>
+          <t>UNIFORTE DO BRASIL COMÉRCIO ATACADISTA DE EMBALAGENS LTDA</t>
         </is>
       </c>
       <c r="H737" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I737" s="1" t="inlineStr">
@@ -56418,39 +56508,37 @@
         </is>
       </c>
       <c r="J737" s="2" t="n">
-        <v>46275.43366273148</v>
+        <v>46258.68138819445</v>
       </c>
       <c r="K737" s="2" t="n">
-        <v>46276</v>
+        <v>46259</v>
       </c>
       <c r="L737" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M737" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N737" s="1" t="n"/>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
+      <c r="N737" s="2" t="n">
+        <v>46261.36105216435</v>
+      </c>
       <c r="O737" s="1" t="n"/>
-      <c r="P737" s="2" t="n">
-        <v>46275.80130501158</v>
-      </c>
-      <c r="Q737" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P737" s="1" t="n"/>
+      <c r="Q737" s="1" t="inlineStr"/>
       <c r="R737" s="1" t="inlineStr">
         <is>
-          <t>Não há débitos, segue certidão negativa.</t>
+          <t>Bom dia 
+Preparando a minuta.
+Atenciosamente,</t>
         </is>
       </c>
       <c r="S737" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T737" s="1" t="n"/>
@@ -56458,51 +56546,51 @@
     </row>
     <row r="738">
       <c r="A738" s="1" t="n">
-        <v>82909</v>
+        <v>83650</v>
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C738" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D738" s="1" t="inlineStr">
         <is>
+          <t>GERENCIA MASTER</t>
+        </is>
+      </c>
+      <c r="E738" s="1" t="inlineStr">
+        <is>
+          <t>Abertura de nova empresa do grupo 5050-MARECHAL Tributação: Lucro Presumido Proposta já negociada no valor de: R$ 2.500,00Razão Social: Opção 1: RESTAURANTE E LANCHONETE MARECHAL LTDAObjeto Social: FORNECIMENTO DE REFEIÇÕES - RESTAURANTE, ORGANIZAÇÃO DE EVENTOSCapital social de R$ 50.000,00</t>
+        </is>
+      </c>
+      <c r="F738" s="1" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G738" s="1" t="inlineStr">
+        <is>
+          <t>HIPERMERCADO MARECHAL LTDA</t>
+        </is>
+      </c>
+      <c r="H738" s="1" t="inlineStr">
+        <is>
+          <t>Edson Silva</t>
+        </is>
+      </c>
+      <c r="I738" s="1" t="inlineStr">
+        <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="E738" s="1" t="inlineStr">
-        <is>
-          <t>ALTERAÇÃO DO ENDEREÇO E OBJETO SOCIAL CONFORME VIABILIDADE.</t>
-        </is>
-      </c>
-      <c r="F738" s="1" t="n">
-        <v>5048</v>
-      </c>
-      <c r="G738" s="1" t="inlineStr">
-        <is>
-          <t>UNIFORTE DO BRASIL COMÉRCIO ATACADISTA DE EMBALAGENS LTDA</t>
-        </is>
-      </c>
-      <c r="H738" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
-      <c r="I738" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
       <c r="J738" s="2" t="n">
-        <v>46258.68138819445</v>
+        <v>46273.5154474537</v>
       </c>
       <c r="K738" s="2" t="n">
-        <v>46259</v>
+        <v>46301</v>
       </c>
       <c r="L738" s="1" t="inlineStr">
         <is>
@@ -56511,104 +56599,108 @@
       </c>
       <c r="M738" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N738" s="2" t="n">
-        <v>46261.36105216435</v>
+        <v>46275.42730894676</v>
       </c>
       <c r="O738" s="1" t="n"/>
       <c r="P738" s="1" t="n"/>
       <c r="Q738" s="1" t="inlineStr"/>
       <c r="R738" s="1" t="inlineStr">
         <is>
-          <t>Bom dia 
-Preparando a minuta.
-Atenciosamente,</t>
-        </is>
-      </c>
-      <c r="S738" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T738" s="1" t="n"/>
-      <c r="U738" s="1" t="inlineStr"/>
-    </row>
-    <row r="739">
-      <c r="A739" s="1" t="n">
-        <v>83650</v>
-      </c>
-      <c r="B739" s="1" t="inlineStr">
-        <is>
-          <t>Abertura de Empresa</t>
-        </is>
-      </c>
-      <c r="C739" s="1" t="inlineStr">
-        <is>
-          <t>Sociedade - Comércio</t>
-        </is>
-      </c>
-      <c r="D739" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E739" s="1" t="inlineStr">
-        <is>
-          <t>Abertura de nova empresa do grupo 5050-MARECHAL Tributação: Lucro Presumido Proposta já negociada no valor de: R$ 2.500,00Razão Social: Opção 1: RESTAURANTE E LANCHONETE MARECHAL LTDAObjeto Social: FORNECIMENTO DE REFEIÇÕES - RESTAURANTE, ORGANIZAÇÃO DE EVENTOSCapital social de R$ 50.000,00</t>
-        </is>
-      </c>
-      <c r="F739" s="1" t="n">
-        <v>5050</v>
-      </c>
-      <c r="G739" s="1" t="inlineStr">
-        <is>
-          <t>HIPERMERCADO MARECHAL LTDA</t>
-        </is>
-      </c>
-      <c r="H739" s="1" t="inlineStr">
-        <is>
-          <t>Edson Silva</t>
-        </is>
-      </c>
-      <c r="I739" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J739" s="2" t="n">
-        <v>46273.5154474537</v>
-      </c>
-      <c r="K739" s="2" t="n">
-        <v>46301</v>
-      </c>
-      <c r="L739" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M739" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N739" s="2" t="n">
-        <v>46275.42730894676</v>
-      </c>
-      <c r="O739" s="1" t="n"/>
-      <c r="P739" s="1" t="n"/>
-      <c r="Q739" s="1" t="inlineStr"/>
-      <c r="R739" s="1" t="inlineStr">
-        <is>
           <t>Bom dia,
 minuta em andamento
 Atenciosamente,</t>
         </is>
       </c>
+      <c r="S738" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T738" s="1" t="n"/>
+      <c r="U738" s="1" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="n">
+        <v>83714</v>
+      </c>
+      <c r="B739" s="1" t="inlineStr">
+        <is>
+          <t>Certidão</t>
+        </is>
+      </c>
+      <c r="C739" s="1" t="inlineStr">
+        <is>
+          <t>Trabalhista</t>
+        </is>
+      </c>
+      <c r="D739" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E739" s="1" t="inlineStr">
+        <is>
+          <t>Por gentileza, providenciar CLI, certidões federais, municipais, estaduais e trabalhistas da empresa 5100</t>
+        </is>
+      </c>
+      <c r="F739" s="1" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G739" s="1" t="inlineStr">
+        <is>
+          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
+        </is>
+      </c>
+      <c r="H739" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="I739" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J739" s="2" t="n">
+        <v>46274.44445876157</v>
+      </c>
+      <c r="K739" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="L739" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M739" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N739" s="1" t="n"/>
+      <c r="O739" s="1" t="n"/>
+      <c r="P739" s="2" t="n">
+        <v>46281.63185188657</v>
+      </c>
+      <c r="Q739" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R739" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde!
+CLI não se enquadra para esta empresa. Segue pesquisas federal, estadual e certidão trabalhista.
+A certidão municipal, fiz a solicitação e estou aguardando</t>
+        </is>
+      </c>
       <c r="S739" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T739" s="1" t="n"/>
@@ -56616,16 +56708,16 @@
     </row>
     <row r="740">
       <c r="A740" s="1" t="n">
-        <v>83714</v>
+        <v>84010</v>
       </c>
       <c r="B740" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C740" s="1" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D740" s="1" t="inlineStr">
@@ -56635,20 +56727,20 @@
       </c>
       <c r="E740" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar CLI, certidões federais, municipais, estaduais e trabalhistas da empresa 5100</t>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
         </is>
       </c>
       <c r="F740" s="1" t="n">
-        <v>5100</v>
+        <v>5118</v>
       </c>
       <c r="G740" s="1" t="inlineStr">
         <is>
-          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 06)</t>
         </is>
       </c>
       <c r="H740" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I740" s="1" t="inlineStr">
@@ -56657,10 +56749,10 @@
         </is>
       </c>
       <c r="J740" s="2" t="n">
-        <v>46274.44445876157</v>
+        <v>46280.47515841435</v>
       </c>
       <c r="K740" s="2" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="L740" s="1" t="inlineStr">
         <is>
@@ -56669,24 +56761,22 @@
       </c>
       <c r="M740" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N740" s="1" t="n"/>
       <c r="O740" s="1" t="n"/>
       <c r="P740" s="2" t="n">
-        <v>46281.63185188657</v>
+        <v>46283.43439984954</v>
       </c>
       <c r="Q740" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="R740" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!
-CLI não se enquadra para esta empresa. Segue pesquisas federal, estadual e certidão trabalhista.
-A certidão municipal, fiz a solicitação e estou aguardando</t>
+          <t>Situação regular das filiais do município de São Paulo, segue certidão negativa.</t>
         </is>
       </c>
       <c r="S740" s="1" t="inlineStr">
@@ -56699,39 +56789,39 @@
     </row>
     <row r="741">
       <c r="A741" s="1" t="n">
-        <v>84010</v>
+        <v>84296</v>
       </c>
       <c r="B741" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Levantamento de Débitos Trimestral</t>
         </is>
       </c>
       <c r="C741" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D741" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E741" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Boa tarde,Segue solicitação vinda através de ATA de reunião do GM Eduardo. Poderiam por gentileza verificar se há possibilidade?5122 - 5123	TRYNOVA - Parcelamento	Por favor, cliente gostaria de saber se tem desconto no parcelamento da Receita Federal para quitar, já que esta classificado com A - bom pagador!Obrigada.</t>
         </is>
       </c>
       <c r="F741" s="1" t="n">
-        <v>5118</v>
+        <v>5122</v>
       </c>
       <c r="G741" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 06)</t>
+          <t>TRYNOVA CONSULTORIA IMOBILIARIA LTDA</t>
         </is>
       </c>
       <c r="H741" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I741" s="1" t="inlineStr">
@@ -56740,39 +56830,29 @@
         </is>
       </c>
       <c r="J741" s="2" t="n">
-        <v>46280.47515841435</v>
+        <v>46287.57421716435</v>
       </c>
       <c r="K741" s="2" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="L741" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M741" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="N741" s="1" t="n"/>
       <c r="O741" s="1" t="n"/>
-      <c r="P741" s="2" t="n">
-        <v>46283.43439984954</v>
-      </c>
-      <c r="Q741" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="R741" s="1" t="inlineStr">
-        <is>
-          <t>Situação regular das filiais do município de São Paulo, segue certidão negativa.</t>
-        </is>
-      </c>
+      <c r="P741" s="1" t="n"/>
+      <c r="Q741" s="1" t="inlineStr"/>
+      <c r="R741" s="1" t="inlineStr"/>
       <c r="S741" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T741" s="1" t="n"/>
@@ -56780,67 +56860,63 @@
     </row>
     <row r="742">
       <c r="A742" s="1" t="n">
-        <v>84296</v>
+        <v>84205</v>
       </c>
       <c r="B742" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos Trimestral</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C742" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D742" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E742" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde,Segue solicitação vinda através de ATA de reunião do GM Eduardo. Poderiam por gentileza verificar se há possibilidade?5122 - 5123	TRYNOVA - Parcelamento	Por favor, cliente gostaria de saber se tem desconto no parcelamento da Receita Federal para quitar, já que esta classificado com A - bom pagador!Obrigada.</t>
+          <t>Cliente necessita de regularização de cadastro municipal pois não foi realizado em sua ultima alteração de contrato social.</t>
         </is>
       </c>
       <c r="F742" s="1" t="n">
-        <v>5122</v>
+        <v>5144</v>
       </c>
       <c r="G742" s="1" t="inlineStr">
         <is>
-          <t>TRYNOVA CONSULTORIA IMOBILIARIA LTDA</t>
-        </is>
-      </c>
-      <c r="H742" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+          <t>CASA DE ESFIHA E SALGADOS AKIEBON LTDA</t>
+        </is>
+      </c>
+      <c r="H742" s="1" t="n"/>
       <c r="I742" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J742" s="2" t="n">
-        <v>46287.57421716435</v>
+        <v>46286.47680138889</v>
       </c>
       <c r="K742" s="2" t="n">
         <v>46288</v>
       </c>
       <c r="L742" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M742" s="1" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Romero Borges</t>
         </is>
       </c>
       <c r="N742" s="1" t="n"/>
       <c r="O742" s="1" t="n"/>
       <c r="P742" s="1" t="n"/>
       <c r="Q742" s="1" t="inlineStr"/>
-      <c r="R742" s="1" t="inlineStr"/>
+      <c r="R742" s="1" t="n"/>
       <c r="S742" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -56851,11 +56927,11 @@
     </row>
     <row r="743">
       <c r="A743" s="1" t="n">
-        <v>84205</v>
+        <v>84011</v>
       </c>
       <c r="B743" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C743" s="1" t="inlineStr">
@@ -56865,49 +56941,59 @@
       </c>
       <c r="D743" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E743" s="1" t="inlineStr">
         <is>
-          <t>Cliente necessita de regularização de cadastro municipal pois não foi realizado em sua ultima alteração de contrato social.</t>
+          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
         </is>
       </c>
       <c r="F743" s="1" t="n">
-        <v>5144</v>
+        <v>5398</v>
       </c>
       <c r="G743" s="1" t="inlineStr">
         <is>
-          <t>CASA DE ESFIHA E SALGADOS AKIEBON LTDA</t>
-        </is>
-      </c>
-      <c r="H743" s="1" t="n"/>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 07)</t>
+        </is>
+      </c>
+      <c r="H743" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="I743" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J743" s="2" t="n">
-        <v>46286.47680138889</v>
+        <v>46280.47591111111</v>
       </c>
       <c r="K743" s="2" t="n">
-        <v>46288</v>
+        <v>46281</v>
       </c>
       <c r="L743" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M743" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N743" s="1" t="n"/>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N743" s="2" t="n">
+        <v>46281.50318923611</v>
+      </c>
       <c r="O743" s="1" t="n"/>
       <c r="P743" s="1" t="n"/>
       <c r="Q743" s="1" t="inlineStr"/>
-      <c r="R743" s="1" t="n"/>
+      <c r="R743" s="1" t="inlineStr">
+        <is>
+          <t>Certidão será solicitada presencialmente.</t>
+        </is>
+      </c>
       <c r="S743" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -56918,39 +57004,39 @@
     </row>
     <row r="744">
       <c r="A744" s="1" t="n">
-        <v>84011</v>
+        <v>83339</v>
       </c>
       <c r="B744" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C744" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D744" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E744" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, levantar toda e qualquer TAXA/TARIFA pendente junto a prefeitura.Por favor encaminhar guia para pagamento, caso tenha, Obrigada</t>
+          <t>Alteração contratual do QSA da empresa: 5589-ACS COMERCIO E SERVIÇOS DE MANUTENÇÃO LTDAGrupo: AntoconProposta já negociada no valor de R$1.800,00Substituição do atual sócio Sra LEANDRO SEBASTIÃO SIQUEIRA, faz-se necessária substituição do QSA para LUCIANA MARIA SIQUEIRA.</t>
         </is>
       </c>
       <c r="F744" s="1" t="n">
-        <v>5398</v>
+        <v>5589</v>
       </c>
       <c r="G744" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO CASTELO DA SERRA LTDA (FILIAL 07)</t>
+          <t>ACS COMÉRCIO E SERVIÇOS DE MANUTENÇÃO LTDA</t>
         </is>
       </c>
       <c r="H744" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I744" s="1" t="inlineStr">
@@ -56959,10 +57045,10 @@
         </is>
       </c>
       <c r="J744" s="2" t="n">
-        <v>46280.47591111111</v>
+        <v>46266.5560746875</v>
       </c>
       <c r="K744" s="2" t="n">
-        <v>46281</v>
+        <v>46294</v>
       </c>
       <c r="L744" s="1" t="inlineStr">
         <is>
@@ -56971,18 +57057,20 @@
       </c>
       <c r="M744" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N744" s="2" t="n">
-        <v>46281.50318923611</v>
+        <v>46274.56034679398</v>
       </c>
       <c r="O744" s="1" t="n"/>
       <c r="P744" s="1" t="n"/>
       <c r="Q744" s="1" t="inlineStr"/>
       <c r="R744" s="1" t="inlineStr">
         <is>
-          <t>Certidão será solicitada presencialmente.</t>
+          <t>Prezados(as), boa tarde!
+Alteração contratual em andamento, conforme solicitado.
+Atenciosamente,</t>
         </is>
       </c>
       <c r="S744" s="1" t="inlineStr">
@@ -56995,75 +57083,63 @@
     </row>
     <row r="745">
       <c r="A745" s="1" t="n">
-        <v>83339</v>
+        <v>84347</v>
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C745" s="1" t="inlineStr">
         <is>
-          <t>Sócios</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D745" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E745" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual do QSA da empresa: 5589-ACS COMERCIO E SERVIÇOS DE MANUTENÇÃO LTDAGrupo: AntoconProposta já negociada no valor de R$1.800,00Substituição do atual sócio Sra LEANDRO SEBASTIÃO SIQUEIRA, faz-se necessária substituição do QSA para LUCIANA MARIA SIQUEIRA.</t>
+          <t>Bom dia! Por gentileza, poderia encaminhar a segunda via da taxa do carne que venceu dia 20/09. A CND não foi possivel emitir, pois conta um débito na divida ativa, por favor, encaminhar o débito.</t>
         </is>
       </c>
       <c r="F745" s="1" t="n">
-        <v>5589</v>
+        <v>5604</v>
       </c>
       <c r="G745" s="1" t="inlineStr">
         <is>
-          <t>ACS COMÉRCIO E SERVIÇOS DE MANUTENÇÃO LTDA</t>
-        </is>
-      </c>
-      <c r="H745" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
+          <t>GRAFICA TABOAO LTDA</t>
+        </is>
+      </c>
+      <c r="H745" s="1" t="n"/>
       <c r="I745" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J745" s="2" t="n">
-        <v>46266.5560746875</v>
+        <v>46288.37931114584</v>
       </c>
       <c r="K745" s="2" t="n">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="L745" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M745" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N745" s="2" t="n">
-        <v>46274.56034679398</v>
-      </c>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N745" s="1" t="n"/>
       <c r="O745" s="1" t="n"/>
       <c r="P745" s="1" t="n"/>
       <c r="Q745" s="1" t="inlineStr"/>
-      <c r="R745" s="1" t="inlineStr">
-        <is>
-          <t>Prezados(as), boa tarde!
-Alteração contratual em andamento, conforme solicitado.
-Atenciosamente,</t>
-        </is>
-      </c>
+      <c r="R745" s="1" t="n"/>
       <c r="S745" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -57074,66 +57150,80 @@
     </row>
     <row r="746">
       <c r="A746" s="1" t="n">
-        <v>84347</v>
+        <v>82763</v>
       </c>
       <c r="B746" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C746" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="D746" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E746" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, poderia encaminhar a segunda via da taxa do carne que venceu dia 20/09. A CND não foi possivel emitir, pois conta um débito na divida ativa, por favor, encaminhar o débito.</t>
+          <t>Prezados,Boa tarde!Por gentileza, providenciar CND Federal, Estadual e Municipal da empresa 5640-Comercial Prado.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F746" s="1" t="n">
-        <v>5604</v>
+        <v>5640</v>
       </c>
       <c r="G746" s="1" t="inlineStr">
         <is>
-          <t>GRAFICA TABOAO LTDA</t>
-        </is>
-      </c>
-      <c r="H746" s="1" t="n"/>
+          <t>COMERCIAL PRADO - MATERIAL DE CONSTRUCAO LTDA</t>
+        </is>
+      </c>
+      <c r="H746" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="I746" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J746" s="2" t="n">
-        <v>46288.37931114584</v>
+        <v>46254.72416542824</v>
       </c>
       <c r="K746" s="2" t="n">
-        <v>46289</v>
+        <v>46255</v>
       </c>
       <c r="L746" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M746" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N746" s="1" t="n"/>
       <c r="O746" s="1" t="n"/>
-      <c r="P746" s="1" t="n"/>
-      <c r="Q746" s="1" t="inlineStr"/>
-      <c r="R746" s="1" t="n"/>
+      <c r="P746" s="2" t="n">
+        <v>46255.48925019676</v>
+      </c>
+      <c r="Q746" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R746" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seguem certidões referente ao cliente 5640 - COMERCIAL PRADO, conforme solicitado. </t>
+        </is>
+      </c>
       <c r="S746" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T746" s="1" t="n"/>
@@ -57141,39 +57231,39 @@
     </row>
     <row r="747">
       <c r="A747" s="1" t="n">
-        <v>82763</v>
+        <v>83611</v>
       </c>
       <c r="B747" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C747" s="1" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D747" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E747" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Boa tarde!Por gentileza, providenciar CND Federal, Estadual e Municipal da empresa 5640-Comercial Prado.Grato,Bruno.</t>
+          <t>Boa tarde!!Por gentileza, realizar levantamento de débitos federais. E gerar guia de pagamento para o dia 09/09.</t>
         </is>
       </c>
       <c r="F747" s="1" t="n">
-        <v>5640</v>
+        <v>5661</v>
       </c>
       <c r="G747" s="1" t="inlineStr">
         <is>
-          <t>COMERCIAL PRADO - MATERIAL DE CONSTRUCAO LTDA</t>
+          <t>ELETRICA IPOJUCA LTDA</t>
         </is>
       </c>
       <c r="H747" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I747" s="1" t="inlineStr">
@@ -57182,10 +57272,10 @@
         </is>
       </c>
       <c r="J747" s="2" t="n">
-        <v>46254.72416542824</v>
+        <v>46269.51044244213</v>
       </c>
       <c r="K747" s="2" t="n">
-        <v>46255</v>
+        <v>46274</v>
       </c>
       <c r="L747" s="1" t="inlineStr">
         <is>
@@ -57194,22 +57284,24 @@
       </c>
       <c r="M747" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N747" s="1" t="n"/>
       <c r="O747" s="1" t="n"/>
       <c r="P747" s="2" t="n">
-        <v>46255.48925019676</v>
+        <v>46274.49946655093</v>
       </c>
       <c r="Q747" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="R747" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguem certidões referente ao cliente 5640 - COMERCIAL PRADO, conforme solicitado. </t>
+          <t>Yasmin, bom dia!
+Segue, em anexo, a situação fiscal. Há impostos em aberto; solicitar aos departamentos responsáveis o recálculo.
+Referente aos parcelamentos em aberto, nosso sistema irá iniciar o envio amanhã</t>
         </is>
       </c>
       <c r="S747" s="1" t="inlineStr">
@@ -57222,7 +57314,7 @@
     </row>
     <row r="748">
       <c r="A748" s="1" t="n">
-        <v>83611</v>
+        <v>83613</v>
       </c>
       <c r="B748" s="1" t="inlineStr">
         <is>
@@ -57241,20 +57333,20 @@
       </c>
       <c r="E748" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!!Por gentileza, realizar levantamento de débitos federais. E gerar guia de pagamento para o dia 09/09.</t>
+          <t>Boa tarde!!Por gentileza, realizar levantamento de débitos federais. E gerar guia de pagamento para o dia 09/09</t>
         </is>
       </c>
       <c r="F748" s="1" t="n">
-        <v>5661</v>
+        <v>5662</v>
       </c>
       <c r="G748" s="1" t="inlineStr">
         <is>
-          <t>ELETRICA IPOJUCA LTDA</t>
+          <t>COMERCIAL DE MATERIAIS ELETRICOS MM LTDA</t>
         </is>
       </c>
       <c r="H748" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I748" s="1" t="inlineStr">
@@ -57263,7 +57355,7 @@
         </is>
       </c>
       <c r="J748" s="2" t="n">
-        <v>46269.51044244213</v>
+        <v>46269.51153171296</v>
       </c>
       <c r="K748" s="2" t="n">
         <v>46274</v>
@@ -57281,18 +57373,17 @@
       <c r="N748" s="1" t="n"/>
       <c r="O748" s="1" t="n"/>
       <c r="P748" s="2" t="n">
-        <v>46274.49946655093</v>
+        <v>46269.70410119213</v>
       </c>
       <c r="Q748" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="R748" s="1" t="inlineStr">
         <is>
-          <t>Yasmin, bom dia!
-Segue, em anexo, a situação fiscal. Há impostos em aberto; solicitar aos departamentos responsáveis o recálculo.
-Referente aos parcelamentos em aberto, nosso sistema irá iniciar o envio amanhã</t>
+          <t>Por gentileza enviar a cópia do documento sócio responsável abaixo, para cadastro no regularize, para emissão dos débitos inscritos em dívida ativa.
+JOSE UMBERTO BORGES DA SILVA</t>
         </is>
       </c>
       <c r="S748" s="1" t="inlineStr">
@@ -57305,39 +57396,39 @@
     </row>
     <row r="749">
       <c r="A749" s="1" t="n">
-        <v>83613</v>
+        <v>83307</v>
       </c>
       <c r="B749" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C749" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Objeto Social</t>
         </is>
       </c>
       <c r="D749" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E749" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!!Por gentileza, realizar levantamento de débitos federais. E gerar guia de pagamento para o dia 09/09</t>
+          <t>Inclusão dos CNAEs 5911-1-99, 7319-0-99 e 7312-2-00.</t>
         </is>
       </c>
       <c r="F749" s="1" t="n">
-        <v>5662</v>
+        <v>5680</v>
       </c>
       <c r="G749" s="1" t="inlineStr">
         <is>
-          <t>COMERCIAL DE MATERIAIS ELETRICOS MM LTDA</t>
+          <t>UNIVERSO DAS COISINHAS E-COMMERCE LTDA</t>
         </is>
       </c>
       <c r="H749" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I749" s="1" t="inlineStr">
@@ -57346,40 +57437,35 @@
         </is>
       </c>
       <c r="J749" s="2" t="n">
-        <v>46269.51153171296</v>
+        <v>46266.37445135417</v>
       </c>
       <c r="K749" s="2" t="n">
-        <v>46274</v>
+        <v>46269</v>
       </c>
       <c r="L749" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M749" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N749" s="1" t="n"/>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N749" s="2" t="n">
+        <v>46273.6798315162</v>
+      </c>
       <c r="O749" s="1" t="n"/>
-      <c r="P749" s="2" t="n">
-        <v>46269.70410119213</v>
-      </c>
-      <c r="Q749" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P749" s="1" t="n"/>
+      <c r="Q749" s="1" t="inlineStr"/>
       <c r="R749" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza enviar a cópia do documento sócio responsável abaixo, para cadastro no regularize, para emissão dos débitos inscritos em dívida ativa.
-JOSE UMBERTO BORGES DA SILVA</t>
+          <t>Processo em elaboração</t>
         </is>
       </c>
       <c r="S749" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T749" s="1" t="n"/>
@@ -57387,7 +57473,7 @@
     </row>
     <row r="750">
       <c r="A750" s="1" t="n">
-        <v>83307</v>
+        <v>84335</v>
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
@@ -57401,59 +57487,49 @@
       </c>
       <c r="D750" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E750" s="1" t="inlineStr">
         <is>
-          <t>Inclusão dos CNAEs 5911-1-99, 7319-0-99 e 7312-2-00.</t>
+          <t>Alteração contratual da empresa: 5685- CORONEL PIGGrupo: CampsuiProposta já negociada no valor de R$2.500,00INCLUIR AS ATIVIDADES DE comércio varejista e atacadista de carnes bovinas, suínas e derivados</t>
         </is>
       </c>
       <c r="F750" s="1" t="n">
-        <v>5680</v>
+        <v>5685</v>
       </c>
       <c r="G750" s="1" t="inlineStr">
         <is>
-          <t>UNIVERSO DAS COISINHAS E-COMMERCE LTDA</t>
-        </is>
-      </c>
-      <c r="H750" s="1" t="inlineStr">
-        <is>
-          <t>Thifany Leite</t>
-        </is>
-      </c>
+          <t>CORONEL PIG COMERCIO DE PRODUTOS ALIMENTICIOS LTDA</t>
+        </is>
+      </c>
+      <c r="H750" s="1" t="n"/>
       <c r="I750" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J750" s="2" t="n">
-        <v>46266.37445135417</v>
+        <v>46287.73699806713</v>
       </c>
       <c r="K750" s="2" t="n">
-        <v>46269</v>
+        <v>46315</v>
       </c>
       <c r="L750" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M750" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N750" s="2" t="n">
-        <v>46273.6798315162</v>
-      </c>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N750" s="1" t="n"/>
       <c r="O750" s="1" t="n"/>
       <c r="P750" s="1" t="n"/>
       <c r="Q750" s="1" t="inlineStr"/>
-      <c r="R750" s="1" t="inlineStr">
-        <is>
-          <t>Processo em elaboração</t>
-        </is>
-      </c>
+      <c r="R750" s="1" t="n"/>
       <c r="S750" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -57464,63 +57540,72 @@
     </row>
     <row r="751">
       <c r="A751" s="1" t="n">
-        <v>84335</v>
+        <v>82780</v>
       </c>
       <c r="B751" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C751" s="1" t="inlineStr">
         <is>
-          <t>Objeto Social</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D751" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E751" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual da empresa: 5685- CORONEL PIGGrupo: CampsuiProposta já negociada no valor de R$2.500,00INCLUIR AS ATIVIDADES DE comércio varejista e atacadista de carnes bovinas, suínas e derivados</t>
+          <t>Olá, Boa tarde!!!A empresa 5880, não possui senhas salvas para consulta de NFSE ou encerramento, poderiam verificar?</t>
         </is>
       </c>
       <c r="F751" s="1" t="n">
-        <v>5685</v>
+        <v>5880</v>
       </c>
       <c r="G751" s="1" t="inlineStr">
         <is>
-          <t>CORONEL PIG COMERCIO DE PRODUTOS ALIMENTICIOS LTDA</t>
-        </is>
-      </c>
-      <c r="H751" s="1" t="n"/>
+          <t>Cucinare Pro Alimentacao LTDA (Filial 86)</t>
+        </is>
+      </c>
+      <c r="H751" s="1" t="inlineStr">
+        <is>
+          <t>Talita Silva</t>
+        </is>
+      </c>
       <c r="I751" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J751" s="2" t="n">
-        <v>46287.73699806713</v>
+        <v>46255.43914973379</v>
       </c>
       <c r="K751" s="2" t="n">
-        <v>46315</v>
+        <v>46262</v>
       </c>
       <c r="L751" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M751" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="N751" s="1" t="n"/>
       <c r="O751" s="1" t="n"/>
       <c r="P751" s="1" t="n"/>
       <c r="Q751" s="1" t="inlineStr"/>
-      <c r="R751" s="1" t="n"/>
+      <c r="R751" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde!
+Estou verificando o acesso junto a prefeitura.</t>
+        </is>
+      </c>
       <c r="S751" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -57531,39 +57616,39 @@
     </row>
     <row r="752">
       <c r="A752" s="1" t="n">
-        <v>82780</v>
+        <v>82000</v>
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Restituição</t>
         </is>
       </c>
       <c r="C752" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D752" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E752" s="1" t="inlineStr">
         <is>
-          <t>Olá, Boa tarde!!!A empresa 5880, não possui senhas salvas para consulta de NFSE ou encerramento, poderiam verificar?</t>
+          <t>Prezados, boa tarde!O gerente Eduardo Aparicio está me perguntando se foi solicitado a reembolso referente a ICMS Difal que a empresa ITA pagou para o Estado do Ceará referente a NF 13436, que o posto fiscal deixou a mercadoria presa, pois alegam que eles deveriam pagar por essa mercadoria, e para o cliente deles não cancelar a compra, porém a mercadoria enviada é isenta de ICMS em ambito nacional e por esse motivo estão solicitando que abra um processo para reembolso do pagamento indevido dessa GNRE.</t>
         </is>
       </c>
       <c r="F752" s="1" t="n">
-        <v>5880</v>
+        <v>5885</v>
       </c>
       <c r="G752" s="1" t="inlineStr">
         <is>
-          <t>Cucinare Pro Alimentacao LTDA (Filial 86)</t>
+          <t>INSTITUTO DE TECNOLOGIA ASSISTIVA LTDA</t>
         </is>
       </c>
       <c r="H752" s="1" t="inlineStr">
         <is>
-          <t>Talita Silva</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I752" s="1" t="inlineStr">
@@ -57572,113 +57657,118 @@
         </is>
       </c>
       <c r="J752" s="2" t="n">
-        <v>46255.43914973379</v>
+        <v>46240.64507523148</v>
       </c>
       <c r="K752" s="2" t="n">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="L752" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M752" s="1" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
-        </is>
-      </c>
-      <c r="N752" s="1" t="n"/>
+          <t>Rodrigo Rego</t>
+        </is>
+      </c>
+      <c r="N752" s="2" t="n">
+        <v>46269.68263113426</v>
+      </c>
       <c r="O752" s="1" t="n"/>
       <c r="P752" s="1" t="n"/>
       <c r="Q752" s="1" t="inlineStr"/>
       <c r="R752" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!
-Estou verificando o acesso junto a prefeitura.</t>
-        </is>
-      </c>
-      <c r="S752" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T752" s="1" t="n"/>
-      <c r="U752" s="1" t="inlineStr"/>
-    </row>
-    <row r="753">
-      <c r="A753" s="1" t="n">
-        <v>82000</v>
-      </c>
-      <c r="B753" s="1" t="inlineStr">
-        <is>
-          <t>Restituição</t>
-        </is>
-      </c>
-      <c r="C753" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="D753" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E753" s="1" t="inlineStr">
-        <is>
-          <t>Prezados, boa tarde!O gerente Eduardo Aparicio está me perguntando se foi solicitado a reembolso referente a ICMS Difal que a empresa ITA pagou para o Estado do Ceará referente a NF 13436, que o posto fiscal deixou a mercadoria presa, pois alegam que eles deveriam pagar por essa mercadoria, e para o cliente deles não cancelar a compra, porém a mercadoria enviada é isenta de ICMS em ambito nacional e por esse motivo estão solicitando que abra um processo para reembolso do pagamento indevido dessa GNRE.</t>
-        </is>
-      </c>
-      <c r="F753" s="1" t="n">
-        <v>5885</v>
-      </c>
-      <c r="G753" s="1" t="inlineStr">
-        <is>
-          <t>INSTITUTO DE TECNOLOGIA ASSISTIVA LTDA</t>
-        </is>
-      </c>
-      <c r="H753" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="I753" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J753" s="2" t="n">
-        <v>46240.64507523148</v>
-      </c>
-      <c r="K753" s="2" t="n">
-        <v>46244</v>
-      </c>
-      <c r="L753" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M753" s="1" t="inlineStr">
-        <is>
-          <t>Rodrigo Rego</t>
-        </is>
-      </c>
-      <c r="N753" s="2" t="n">
-        <v>46269.68263113426</v>
-      </c>
-      <c r="O753" s="1" t="n"/>
-      <c r="P753" s="1" t="n"/>
-      <c r="Q753" s="1" t="inlineStr"/>
-      <c r="R753" s="1" t="inlineStr">
-        <is>
           <t>Rodrigo, 
 Segue proposta para protocolo do pedido de restituição.
 Obs. Não recebemos solicitação anteriormente sobre essa questão. GM solicitou para quem?</t>
         </is>
       </c>
+      <c r="S752" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T752" s="1" t="n"/>
+      <c r="U752" s="1" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="n">
+        <v>81845</v>
+      </c>
+      <c r="B753" s="1" t="inlineStr">
+        <is>
+          <t>Parcelamento PGFN</t>
+        </is>
+      </c>
+      <c r="C753" s="1" t="inlineStr">
+        <is>
+          <t>Simples Nacional</t>
+        </is>
+      </c>
+      <c r="D753" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E753" s="1" t="inlineStr">
+        <is>
+          <t>Prezados,Boa tarde! Por gentileza, providenciar simulação de parcelamento dos débitos federais da empresa 5908-Merch Link em 36 e 60 parcelas para análise e aceite do cliente.Desde já agradeço o apoio.</t>
+        </is>
+      </c>
+      <c r="F753" s="1" t="n">
+        <v>5908</v>
+      </c>
+      <c r="G753" s="1" t="inlineStr">
+        <is>
+          <t>MERCH LINK LTDA</t>
+        </is>
+      </c>
+      <c r="H753" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I753" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J753" s="2" t="n">
+        <v>46238.57314429398</v>
+      </c>
+      <c r="K753" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="L753" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M753" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N753" s="1" t="n"/>
+      <c r="O753" s="1" t="n"/>
+      <c r="P753" s="2" t="n">
+        <v>46238.62655219907</v>
+      </c>
+      <c r="Q753" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R753" s="1" t="inlineStr">
+        <is>
+          <t>Simulado e proposta enviados por email ao GC Bruno.</t>
+        </is>
+      </c>
       <c r="S753" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T753" s="1" t="n"/>
@@ -57686,39 +57776,39 @@
     </row>
     <row r="754">
       <c r="A754" s="1" t="n">
-        <v>81845</v>
+        <v>82811</v>
       </c>
       <c r="B754" s="1" t="inlineStr">
         <is>
-          <t>Parcelamento PGFN</t>
+          <t>Processo de VISA</t>
         </is>
       </c>
       <c r="C754" s="1" t="inlineStr">
         <is>
-          <t>Simples Nacional</t>
+          <t>Renovação</t>
         </is>
       </c>
       <c r="D754" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E754" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Boa tarde! Por gentileza, providenciar simulação de parcelamento dos débitos federais da empresa 5908-Merch Link em 36 e 60 parcelas para análise e aceite do cliente.Desde já agradeço o apoio.</t>
+          <t>Cliente solicita renovação de alvará de funcionamento.</t>
         </is>
       </c>
       <c r="F754" s="1" t="n">
-        <v>5908</v>
+        <v>5923</v>
       </c>
       <c r="G754" s="1" t="inlineStr">
         <is>
-          <t>MERCH LINK LTDA</t>
+          <t>ALUSMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
         </is>
       </c>
       <c r="H754" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I754" s="1" t="inlineStr">
@@ -57727,39 +57817,37 @@
         </is>
       </c>
       <c r="J754" s="2" t="n">
-        <v>46238.57314429398</v>
+        <v>46255.63641273148</v>
       </c>
       <c r="K754" s="2" t="n">
-        <v>46240</v>
+        <v>46258</v>
       </c>
       <c r="L754" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M754" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N754" s="1" t="n"/>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N754" s="2" t="n">
+        <v>46273.36977268518</v>
+      </c>
       <c r="O754" s="1" t="n"/>
-      <c r="P754" s="2" t="n">
-        <v>46238.62655219907</v>
-      </c>
-      <c r="Q754" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P754" s="1" t="n"/>
+      <c r="Q754" s="1" t="inlineStr"/>
       <c r="R754" s="1" t="inlineStr">
         <is>
-          <t>Simulado e proposta enviados por email ao GC Bruno.</t>
+          <t xml:space="preserve">Prezados(as), bom dia!
+Solicitação em andamento. 
+Atenciosamente, </t>
         </is>
       </c>
       <c r="S754" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T754" s="1" t="n"/>
@@ -57767,7 +57855,7 @@
     </row>
     <row r="755">
       <c r="A755" s="1" t="n">
-        <v>82811</v>
+        <v>82812</v>
       </c>
       <c r="B755" s="1" t="inlineStr">
         <is>
@@ -57790,11 +57878,11 @@
         </is>
       </c>
       <c r="F755" s="1" t="n">
-        <v>5923</v>
+        <v>5924</v>
       </c>
       <c r="G755" s="1" t="inlineStr">
         <is>
-          <t>ALUSMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
+          <t>LUSMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
         </is>
       </c>
       <c r="H755" s="1" t="inlineStr">
@@ -57808,7 +57896,7 @@
         </is>
       </c>
       <c r="J755" s="2" t="n">
-        <v>46255.63641273148</v>
+        <v>46255.63676828704</v>
       </c>
       <c r="K755" s="2" t="n">
         <v>46258</v>
@@ -57824,7 +57912,7 @@
         </is>
       </c>
       <c r="N755" s="2" t="n">
-        <v>46273.36977268518</v>
+        <v>46273.37007592592</v>
       </c>
       <c r="O755" s="1" t="n"/>
       <c r="P755" s="1" t="n"/>
@@ -57846,7 +57934,7 @@
     </row>
     <row r="756">
       <c r="A756" s="1" t="n">
-        <v>82812</v>
+        <v>82813</v>
       </c>
       <c r="B756" s="1" t="inlineStr">
         <is>
@@ -57869,11 +57957,11 @@
         </is>
       </c>
       <c r="F756" s="1" t="n">
-        <v>5924</v>
+        <v>5925</v>
       </c>
       <c r="G756" s="1" t="inlineStr">
         <is>
-          <t>LUSMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
+          <t>LIVMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
         </is>
       </c>
       <c r="H756" s="1" t="inlineStr">
@@ -57887,7 +57975,7 @@
         </is>
       </c>
       <c r="J756" s="2" t="n">
-        <v>46255.63676828704</v>
+        <v>46255.63725177084</v>
       </c>
       <c r="K756" s="2" t="n">
         <v>46258</v>
@@ -57903,7 +57991,7 @@
         </is>
       </c>
       <c r="N756" s="2" t="n">
-        <v>46273.37007592592</v>
+        <v>46273.37023221065</v>
       </c>
       <c r="O756" s="1" t="n"/>
       <c r="P756" s="1" t="n"/>
@@ -57925,7 +58013,7 @@
     </row>
     <row r="757">
       <c r="A757" s="1" t="n">
-        <v>82813</v>
+        <v>82814</v>
       </c>
       <c r="B757" s="1" t="inlineStr">
         <is>
@@ -57948,11 +58036,11 @@
         </is>
       </c>
       <c r="F757" s="1" t="n">
-        <v>5925</v>
+        <v>5926</v>
       </c>
       <c r="G757" s="1" t="inlineStr">
         <is>
-          <t>LIVMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
+          <t>HHMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
         </is>
       </c>
       <c r="H757" s="1" t="inlineStr">
@@ -57966,7 +58054,7 @@
         </is>
       </c>
       <c r="J757" s="2" t="n">
-        <v>46255.63725177084</v>
+        <v>46255.63768873842</v>
       </c>
       <c r="K757" s="2" t="n">
         <v>46258</v>
@@ -57982,7 +58070,7 @@
         </is>
       </c>
       <c r="N757" s="2" t="n">
-        <v>46273.37023221065</v>
+        <v>46273.37038981482</v>
       </c>
       <c r="O757" s="1" t="n"/>
       <c r="P757" s="1" t="n"/>
@@ -58004,39 +58092,39 @@
     </row>
     <row r="758">
       <c r="A758" s="1" t="n">
-        <v>82814</v>
+        <v>83752</v>
       </c>
       <c r="B758" s="1" t="inlineStr">
         <is>
-          <t>Processo de VISA</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C758" s="1" t="inlineStr">
         <is>
-          <t>Renovação</t>
+          <t>Sociedade - Comércio</t>
         </is>
       </c>
       <c r="D758" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E758" s="1" t="inlineStr">
         <is>
-          <t>Cliente solicita renovação de alvará de funcionamento.</t>
+          <t>Prezados, Boa tarde! Por gentileza, elaborar proposta para abertura de uma nova empresa do grupo Seu Góis.No aguardo.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F758" s="1" t="n">
-        <v>5926</v>
+        <v>5929</v>
       </c>
       <c r="G758" s="1" t="inlineStr">
         <is>
-          <t>HHMEDESTHETK DISTRIBUIDORA E COMERCIO DE PRODUTOS LTDA</t>
+          <t>BAR E RESTAURANTE 1566 LTDA</t>
         </is>
       </c>
       <c r="H758" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I758" s="1" t="inlineStr">
@@ -58045,37 +58133,39 @@
         </is>
       </c>
       <c r="J758" s="2" t="n">
-        <v>46255.63768873842</v>
+        <v>46274.70572450232</v>
       </c>
       <c r="K758" s="2" t="n">
-        <v>46258</v>
+        <v>46276</v>
       </c>
       <c r="L758" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M758" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N758" s="2" t="n">
-        <v>46273.37038981482</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N758" s="1" t="n"/>
       <c r="O758" s="1" t="n"/>
-      <c r="P758" s="1" t="n"/>
-      <c r="Q758" s="1" t="inlineStr"/>
+      <c r="P758" s="2" t="n">
+        <v>46276.61454390046</v>
+      </c>
+      <c r="Q758" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="R758" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados(as), bom dia!
-Solicitação em andamento. 
-Atenciosamente, </t>
+          <t>Segue proposta.</t>
         </is>
       </c>
       <c r="S758" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T758" s="1" t="n"/>
@@ -58083,16 +58173,16 @@
     </row>
     <row r="759">
       <c r="A759" s="1" t="n">
-        <v>83752</v>
+        <v>83765</v>
       </c>
       <c r="B759" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C759" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Comércio</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="D759" s="1" t="inlineStr">
@@ -58102,20 +58192,20 @@
       </c>
       <c r="E759" s="1" t="inlineStr">
         <is>
-          <t>Prezados, Boa tarde! Por gentileza, elaborar proposta para abertura de uma nova empresa do grupo Seu Góis.No aguardo.Grato,Bruno.</t>
+          <t xml:space="preserve">Bom dia, por gentileza encaminhar TFE </t>
         </is>
       </c>
       <c r="F759" s="1" t="n">
-        <v>5929</v>
+        <v>6065</v>
       </c>
       <c r="G759" s="1" t="inlineStr">
         <is>
-          <t>BAR E RESTAURANTE 1566 LTDA</t>
+          <t xml:space="preserve">PS3 INSTALACOES E MONTAGENS LTDA </t>
         </is>
       </c>
       <c r="H759" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I759" s="1" t="inlineStr">
@@ -58124,7 +58214,7 @@
         </is>
       </c>
       <c r="J759" s="2" t="n">
-        <v>46274.70572450232</v>
+        <v>46275.36535266204</v>
       </c>
       <c r="K759" s="2" t="n">
         <v>46276</v>
@@ -58136,22 +58226,22 @@
       </c>
       <c r="M759" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N759" s="1" t="n"/>
       <c r="O759" s="1" t="n"/>
       <c r="P759" s="2" t="n">
-        <v>46276.61454390046</v>
+        <v>46280.78301616898</v>
       </c>
       <c r="Q759" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="R759" s="1" t="inlineStr">
         <is>
-          <t>Segue proposta.</t>
+          <t>Boa noite! Segue em anexo.</t>
         </is>
       </c>
       <c r="S759" s="1" t="inlineStr">
@@ -58164,7 +58254,7 @@
     </row>
     <row r="760">
       <c r="A760" s="1" t="n">
-        <v>83765</v>
+        <v>82751</v>
       </c>
       <c r="B760" s="1" t="inlineStr">
         <is>
@@ -58173,7 +58263,7 @@
       </c>
       <c r="C760" s="1" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Protestos</t>
         </is>
       </c>
       <c r="D760" s="1" t="inlineStr">
@@ -58183,20 +58273,20 @@
       </c>
       <c r="E760" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, por gentileza encaminhar TFE </t>
+          <t xml:space="preserve">O cliente informou que recebeu o protesto referente a Taxa de fiscalização. Por gentileza verificar se há pendência em aberto e se é possível emitir a guia para pagamento. </t>
         </is>
       </c>
       <c r="F760" s="1" t="n">
-        <v>6065</v>
+        <v>6077</v>
       </c>
       <c r="G760" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PS3 INSTALACOES E MONTAGENS LTDA </t>
+          <t xml:space="preserve">DELLON DIOVANI SOARES </t>
         </is>
       </c>
       <c r="H760" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I760" s="1" t="inlineStr">
@@ -58205,10 +58295,10 @@
         </is>
       </c>
       <c r="J760" s="2" t="n">
-        <v>46275.36535266204</v>
+        <v>46254.65013561342</v>
       </c>
       <c r="K760" s="2" t="n">
-        <v>46276</v>
+        <v>46255</v>
       </c>
       <c r="L760" s="1" t="inlineStr">
         <is>
@@ -58220,19 +58310,21 @@
           <t>Beatriz Rangel</t>
         </is>
       </c>
-      <c r="N760" s="1" t="n"/>
+      <c r="N760" s="2" t="n">
+        <v>46255.48898734953</v>
+      </c>
       <c r="O760" s="1" t="n"/>
       <c r="P760" s="2" t="n">
-        <v>46280.78301616898</v>
+        <v>46283.44702604166</v>
       </c>
       <c r="Q760" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="R760" s="1" t="inlineStr">
         <is>
-          <t>Boa noite! Segue em anexo.</t>
+          <t>Aguardando liberação do cartório para emissão da guia na PM de Itaquaquecetuba</t>
         </is>
       </c>
       <c r="S760" s="1" t="inlineStr">
@@ -58245,34 +58337,34 @@
     </row>
     <row r="761">
       <c r="A761" s="1" t="n">
-        <v>82751</v>
+        <v>81209</v>
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Processo de Prefeitura</t>
         </is>
       </c>
       <c r="C761" s="1" t="inlineStr">
         <is>
-          <t>Protestos</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="D761" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E761" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">O cliente informou que recebeu o protesto referente a Taxa de fiscalização. Por gentileza verificar se há pendência em aberto e se é possível emitir a guia para pagamento. </t>
+          <t>Cliente cancelou NFS-e posterior a emissão da guia de ISS no mês de junho e emitiu notas fiscais em junho com competência em maio, informado ao GC do ocorrido, o qual solicitou que o cliente cancelasse as notas emitidas na competência errada e que já esta encerrada e emitisse corretamente na competência de junho, contudo esta prefeitura (Itapetininga) não é possível cancelar as guias geradas de forma remota sendo necessário protocolar pessoalmente no balcão do setor de protocolos.</t>
         </is>
       </c>
       <c r="F761" s="1" t="n">
-        <v>6077</v>
+        <v>6094</v>
       </c>
       <c r="G761" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">DELLON DIOVANI SOARES </t>
+          <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
         </is>
       </c>
       <c r="H761" s="1" t="inlineStr">
@@ -58286,41 +58378,31 @@
         </is>
       </c>
       <c r="J761" s="2" t="n">
-        <v>46254.65013561342</v>
+        <v>46223.52088677084</v>
       </c>
       <c r="K761" s="2" t="n">
-        <v>46255</v>
+        <v>46224</v>
       </c>
       <c r="L761" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M761" s="1" t="inlineStr">
-        <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M761" s="1" t="n"/>
       <c r="N761" s="2" t="n">
-        <v>46255.48898734953</v>
+        <v>46232.72821697917</v>
       </c>
       <c r="O761" s="1" t="n"/>
-      <c r="P761" s="2" t="n">
-        <v>46283.44702604166</v>
-      </c>
-      <c r="Q761" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="P761" s="1" t="n"/>
+      <c r="Q761" s="1" t="inlineStr"/>
       <c r="R761" s="1" t="inlineStr">
         <is>
-          <t>Aguardando liberação do cartório para emissão da guia na PM de Itaquaquecetuba</t>
+          <t>Enviado ao cliente procuração para assinatura.</t>
         </is>
       </c>
       <c r="S761" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T761" s="1" t="n"/>
@@ -58328,7 +58410,7 @@
     </row>
     <row r="762">
       <c r="A762" s="1" t="n">
-        <v>81209</v>
+        <v>81267</v>
       </c>
       <c r="B762" s="1" t="inlineStr">
         <is>
@@ -58347,17 +58429,13 @@
       </c>
       <c r="E762" s="1" t="inlineStr">
         <is>
-          <t>Cliente cancelou NFS-e posterior a emissão da guia de ISS no mês de junho e emitiu notas fiscais em junho com competência em maio, informado ao GC do ocorrido, o qual solicitou que o cliente cancelasse as notas emitidas na competência errada e que já esta encerrada e emitisse corretamente na competência de junho, contudo esta prefeitura (Itapetininga) não é possível cancelar as guias geradas de forma remota sendo necessário protocolar pessoalmente no balcão do setor de protocolos.</t>
+          <t>Boa tarde, poderia cancelar a nota na prefeitura do cliente 4422 - ALL Service , numero da nota 841</t>
         </is>
       </c>
       <c r="F762" s="1" t="n">
-        <v>6094</v>
-      </c>
-      <c r="G762" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G762" s="1" t="n"/>
       <c r="H762" s="1" t="inlineStr">
         <is>
           <t>Ellen Leite</t>
@@ -58369,26 +58447,30 @@
         </is>
       </c>
       <c r="J762" s="2" t="n">
-        <v>46223.52088677084</v>
+        <v>46224.66958634259</v>
       </c>
       <c r="K762" s="2" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="L762" s="1" t="inlineStr">
         <is>
           <t>Em Atendimento</t>
         </is>
       </c>
-      <c r="M762" s="1" t="n"/>
+      <c r="M762" s="1" t="inlineStr">
+        <is>
+          <t>Romario Silva</t>
+        </is>
+      </c>
       <c r="N762" s="2" t="n">
-        <v>46232.72821697917</v>
+        <v>46231.70811304398</v>
       </c>
       <c r="O762" s="1" t="n"/>
       <c r="P762" s="1" t="n"/>
       <c r="Q762" s="1" t="inlineStr"/>
       <c r="R762" s="1" t="inlineStr">
         <is>
-          <t>Enviado ao cliente procuração para assinatura.</t>
+          <t>Enviada proposta ao cliente, aguardando aceite para providenciar a documentação.</t>
         </is>
       </c>
       <c r="S762" s="1" t="inlineStr">
@@ -58401,26 +58483,26 @@
     </row>
     <row r="763">
       <c r="A763" s="1" t="n">
-        <v>81267</v>
+        <v>81296</v>
       </c>
       <c r="B763" s="1" t="inlineStr">
         <is>
-          <t>Processo de Prefeitura</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C763" s="1" t="inlineStr">
         <is>
-          <t>Geral</t>
+          <t>Outras Cláusulas</t>
         </is>
       </c>
       <c r="D763" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E763" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, poderia cancelar a nota na prefeitura do cliente 4422 - ALL Service , numero da nota 841</t>
+          <t>Providenciar a inclusão do CNAE descrito abaixo na empresa.8630-5/03 - ATIVIDADE MÉDICA AMBULATORIAL RESTRITA A CONSULTAS.Ela irá prestar serviços médicos como Pessoa Jurídica, para Hospitais, UBS, Clínicas e Eventos, conforme encaminhamento da resposta dela, pelo WhatsApp.Valor será o mesmo da última alteração do grupo.</t>
         </is>
       </c>
       <c r="F763" s="1" t="n">
@@ -58429,7 +58511,7 @@
       <c r="G763" s="1" t="n"/>
       <c r="H763" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Edson Silva</t>
         </is>
       </c>
       <c r="I763" s="1" t="inlineStr">
@@ -58438,10 +58520,10 @@
         </is>
       </c>
       <c r="J763" s="2" t="n">
-        <v>46224.66958634259</v>
+        <v>46225.4866127662</v>
       </c>
       <c r="K763" s="2" t="n">
-        <v>46225</v>
+        <v>46255</v>
       </c>
       <c r="L763" s="1" t="inlineStr">
         <is>
@@ -58450,18 +58532,18 @@
       </c>
       <c r="M763" s="1" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N763" s="2" t="n">
-        <v>46231.70811304398</v>
+        <v>46253.38738584491</v>
       </c>
       <c r="O763" s="1" t="n"/>
       <c r="P763" s="1" t="n"/>
       <c r="Q763" s="1" t="inlineStr"/>
       <c r="R763" s="1" t="inlineStr">
         <is>
-          <t>Enviada proposta ao cliente, aguardando aceite para providenciar a documentação.</t>
+          <t>Raisa, para esse processo, será necessário o envio do IPTU e também que seja informado quem será o responsável tecnico perante o CREMESP, enviando-nos inclusive a carteira do CREMESP do responsável.</t>
         </is>
       </c>
       <c r="S763" s="1" t="inlineStr">
@@ -58474,35 +58556,39 @@
     </row>
     <row r="764">
       <c r="A764" s="1" t="n">
-        <v>81296</v>
+        <v>84233</v>
       </c>
       <c r="B764" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C764" s="1" t="inlineStr">
         <is>
-          <t>Outras Cláusulas</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D764" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E764" s="1" t="inlineStr">
         <is>
-          <t>Providenciar a inclusão do CNAE descrito abaixo na empresa.8630-5/03 - ATIVIDADE MÉDICA AMBULATORIAL RESTRITA A CONSULTAS.Ela irá prestar serviços médicos como Pessoa Jurídica, para Hospitais, UBS, Clínicas e Eventos, conforme encaminhamento da resposta dela, pelo WhatsApp.Valor será o mesmo da última alteração do grupo.</t>
+          <t>Boa tarde.nosso cliente Paraná Guarulhos 2681- precisa realizar a consulta da nota fiscal paulista da filial 6180Precisa habilitar através do "empresas vinculadas" todas as filiais, para que o cliente consiga consultar com o certificado da MATRIZ.Desde já, agradeço.</t>
         </is>
       </c>
       <c r="F764" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G764" s="1" t="n"/>
+        <v>2190</v>
+      </c>
+      <c r="G764" s="1" t="inlineStr">
+        <is>
+          <t>Naoloc Participações  S.A</t>
+        </is>
+      </c>
       <c r="H764" s="1" t="inlineStr">
         <is>
-          <t>Edson Silva</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I764" s="1" t="inlineStr">
@@ -58511,32 +58597,26 @@
         </is>
       </c>
       <c r="J764" s="2" t="n">
-        <v>46225.4866127662</v>
+        <v>46286.7231099537</v>
       </c>
       <c r="K764" s="2" t="n">
-        <v>46255</v>
+        <v>46288</v>
       </c>
       <c r="L764" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M764" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N764" s="2" t="n">
-        <v>46253.38738584491</v>
-      </c>
+          <t>Clara Maria</t>
+        </is>
+      </c>
+      <c r="N764" s="1" t="n"/>
       <c r="O764" s="1" t="n"/>
       <c r="P764" s="1" t="n"/>
       <c r="Q764" s="1" t="inlineStr"/>
-      <c r="R764" s="1" t="inlineStr">
-        <is>
-          <t>Raisa, para esse processo, será necessário o envio do IPTU e também que seja informado quem será o responsável tecnico perante o CREMESP, enviando-nos inclusive a carteira do CREMESP do responsável.</t>
-        </is>
-      </c>
+      <c r="R764" s="1" t="inlineStr"/>
       <c r="S764" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -58547,16 +58627,16 @@
     </row>
     <row r="765">
       <c r="A765" s="1" t="n">
-        <v>84233</v>
+        <v>84106</v>
       </c>
       <c r="B765" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Cancelamento de Declarações</t>
         </is>
       </c>
       <c r="C765" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D765" s="1" t="inlineStr">
@@ -58566,15 +58646,15 @@
       </c>
       <c r="E765" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.nosso cliente Paraná Guarulhos 2681- precisa realizar a consulta da nota fiscal paulista da filial 6180Precisa habilitar através do "empresas vinculadas" todas as filiais, para que o cliente consiga consultar com o certificado da MATRIZ.Desde já, agradeço.</t>
+          <t>boa tarde!!Por gentileza, segue no anexo a nota que foi emitida dia 11/09/2026 com a quantidade errada e precisa de cancelamento extemporâneo.</t>
         </is>
       </c>
       <c r="F765" s="1" t="n">
-        <v>2190</v>
+        <v>2223</v>
       </c>
       <c r="G765" s="1" t="inlineStr">
         <is>
-          <t>Naoloc Participações  S.A</t>
+          <t>SUPERMERCADOS KAÇULA LTDA (FILIAL 02)</t>
         </is>
       </c>
       <c r="H765" s="1" t="inlineStr">
@@ -58588,182 +58668,111 @@
         </is>
       </c>
       <c r="J765" s="2" t="n">
-        <v>46286.7231099537</v>
+        <v>46282.57766640047</v>
       </c>
       <c r="K765" s="2" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="L765" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M765" s="1" t="inlineStr">
         <is>
-          <t>Clara Maria</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N765" s="1" t="n"/>
       <c r="O765" s="1" t="n"/>
-      <c r="P765" s="1" t="n"/>
-      <c r="Q765" s="1" t="inlineStr"/>
-      <c r="R765" s="1" t="inlineStr"/>
-      <c r="S765" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T765" s="1" t="n"/>
-      <c r="U765" s="1" t="inlineStr"/>
-    </row>
-    <row r="766">
-      <c r="A766" s="1" t="n">
-        <v>84106</v>
-      </c>
-      <c r="B766" s="1" t="inlineStr">
-        <is>
-          <t>Cancelamento de Declarações</t>
-        </is>
-      </c>
-      <c r="C766" s="1" t="inlineStr">
-        <is>
-          <t>Outras</t>
-        </is>
-      </c>
-      <c r="D766" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E766" s="1" t="inlineStr">
-        <is>
-          <t>boa tarde!!Por gentileza, segue no anexo a nota que foi emitida dia 11/09/2026 com a quantidade errada e precisa de cancelamento extemporâneo.</t>
-        </is>
-      </c>
-      <c r="F766" s="1" t="n">
-        <v>2223</v>
-      </c>
-      <c r="G766" s="1" t="inlineStr">
-        <is>
-          <t>SUPERMERCADOS KAÇULA LTDA (FILIAL 02)</t>
-        </is>
-      </c>
-      <c r="H766" s="1" t="inlineStr">
+      <c r="P765" s="2" t="n">
+        <v>46282.76913159722</v>
+      </c>
+      <c r="Q765" s="1" t="inlineStr">
         <is>
           <t>Ronaldo Dias</t>
         </is>
       </c>
-      <c r="I766" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J766" s="2" t="n">
-        <v>46282.57766640047</v>
-      </c>
-      <c r="K766" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="L766" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M766" s="1" t="inlineStr">
-        <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N766" s="1" t="n"/>
-      <c r="O766" s="1" t="n"/>
-      <c r="P766" s="2" t="n">
-        <v>46282.76913159722</v>
-      </c>
-      <c r="Q766" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
-      <c r="R766" s="1" t="inlineStr">
+      <c r="R765" s="1" t="inlineStr">
         <is>
           <t>Enviar xml da NF
 motivo do cancelamento
 erro de impedimento do cancelamento via sistema.</t>
         </is>
       </c>
-      <c r="S766" s="1" t="inlineStr">
+      <c r="S765" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T766" s="1" t="n"/>
-      <c r="U766" s="1" t="inlineStr"/>
-    </row>
-    <row r="767">
-      <c r="A767" s="1" t="n">
+      <c r="T765" s="1" t="n"/>
+      <c r="U765" s="1" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="1" t="n">
         <v>81967</v>
       </c>
-      <c r="B767" s="1" t="inlineStr">
+      <c r="B766" s="1" t="inlineStr">
         <is>
           <t>Senha</t>
         </is>
       </c>
-      <c r="C767" s="1" t="inlineStr">
+      <c r="C766" s="1" t="inlineStr">
         <is>
           <t>Prefeitura</t>
         </is>
       </c>
-      <c r="D767" s="1" t="inlineStr">
+      <c r="D766" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
         </is>
       </c>
-      <c r="E767" s="1" t="inlineStr">
+      <c r="E766" s="1" t="inlineStr">
         <is>
           <t>Efetuar a atualização do cadastro da prefeitura para o novo modelo do Gissonline</t>
         </is>
       </c>
-      <c r="F767" s="1" t="n">
+      <c r="F766" s="1" t="n">
         <v>2242</v>
       </c>
-      <c r="G767" s="1" t="inlineStr">
+      <c r="G766" s="1" t="inlineStr">
         <is>
           <t>Vilar VM Administração e Participação S.A</t>
         </is>
       </c>
-      <c r="H767" s="1" t="inlineStr">
+      <c r="H766" s="1" t="inlineStr">
         <is>
           <t>Talita Silva</t>
         </is>
       </c>
-      <c r="I767" s="1" t="inlineStr">
+      <c r="I766" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J767" s="2" t="n">
+      <c r="J766" s="2" t="n">
         <v>46240.49694957176</v>
       </c>
-      <c r="K767" s="2" t="n">
+      <c r="K766" s="2" t="n">
         <v>46244</v>
       </c>
-      <c r="L767" s="1" t="inlineStr">
+      <c r="L766" s="1" t="inlineStr">
         <is>
           <t>Em Atendimento</t>
         </is>
       </c>
-      <c r="M767" s="1" t="inlineStr">
+      <c r="M766" s="1" t="inlineStr">
         <is>
           <t>Jonatan Hayashibara</t>
         </is>
       </c>
-      <c r="N767" s="2" t="n">
+      <c r="N766" s="2" t="n">
         <v>46244.74218622685</v>
       </c>
-      <c r="O767" s="1" t="n"/>
-      <c r="P767" s="1" t="n"/>
-      <c r="Q767" s="1" t="inlineStr"/>
-      <c r="R767" s="1" t="inlineStr">
+      <c r="O766" s="1" t="n"/>
+      <c r="P766" s="1" t="n"/>
+      <c r="Q766" s="1" t="inlineStr"/>
+      <c r="R766" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Olá, boa tarde!
 Fizemos a senha de acesso do sócio no portal, porem não estamos conseguindo vincular a empresa pois a senha do antigo giss, esta dando invalida.
@@ -58771,6 +58780,77 @@
 </t>
         </is>
       </c>
+      <c r="S766" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T766" s="1" t="n"/>
+      <c r="U766" s="1" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="n">
+        <v>83956</v>
+      </c>
+      <c r="B767" s="1" t="inlineStr">
+        <is>
+          <t>Restituição</t>
+        </is>
+      </c>
+      <c r="C767" s="1" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="D767" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E767" s="1" t="inlineStr">
+        <is>
+          <t>Prezados, Houve um erro na informação de quotas no IRPJ e CSLL do 2º trimestre/2025 que originou protestos cujo os comprovantes estão em anexo, por favor... providenciar processo de restituição.  Anexo os protestos e comprovantes de pagamento.</t>
+        </is>
+      </c>
+      <c r="F767" s="1" t="n">
+        <v>2260</v>
+      </c>
+      <c r="G767" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIACHO VERDE DISTRIBUIDORA DE HORTTI FRUTTI LTDA </t>
+        </is>
+      </c>
+      <c r="H767" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I767" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J767" s="2" t="n">
+        <v>46279.65780119213</v>
+      </c>
+      <c r="K767" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="L767" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M767" s="1" t="inlineStr">
+        <is>
+          <t>Ricardo Ferreira</t>
+        </is>
+      </c>
+      <c r="N767" s="1" t="n"/>
+      <c r="O767" s="1" t="n"/>
+      <c r="P767" s="1" t="n"/>
+      <c r="Q767" s="1" t="inlineStr"/>
+      <c r="R767" s="1" t="inlineStr"/>
       <c r="S767" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -58781,16 +58861,16 @@
     </row>
     <row r="768">
       <c r="A768" s="1" t="n">
-        <v>83956</v>
+        <v>82721</v>
       </c>
       <c r="B768" s="1" t="inlineStr">
         <is>
-          <t>Restituição</t>
+          <t>Notificação</t>
         </is>
       </c>
       <c r="C768" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D768" s="1" t="inlineStr">
@@ -58800,20 +58880,20 @@
       </c>
       <c r="E768" s="1" t="inlineStr">
         <is>
-          <t>Prezados, Houve um erro na informação de quotas no IRPJ e CSLL do 2º trimestre/2025 que originou protestos cujo os comprovantes estão em anexo, por favor... providenciar processo de restituição.  Anexo os protestos e comprovantes de pagamento.</t>
+          <t xml:space="preserve">Prezados, CADAN - Notificação.cliente solicita nossa ajuda nesse atendimento, sendo o caso, se tivermos indicação de quem pode ajudar, agradeço. </t>
         </is>
       </c>
       <c r="F768" s="1" t="n">
-        <v>2260</v>
+        <v>2282</v>
       </c>
       <c r="G768" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIACHO VERDE DISTRIBUIDORA DE HORTTI FRUTTI LTDA </t>
+          <t>CASA SANTA GEMMA SUPERMERCADOS LTDA</t>
         </is>
       </c>
       <c r="H768" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I768" s="1" t="inlineStr">
@@ -58822,14 +58902,14 @@
         </is>
       </c>
       <c r="J768" s="2" t="n">
-        <v>46279.65780119213</v>
+        <v>46254.41795709491</v>
       </c>
       <c r="K768" s="2" t="n">
-        <v>46283</v>
+        <v>46255</v>
       </c>
       <c r="L768" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M768" s="1" t="inlineStr">
@@ -58839,12 +58919,22 @@
       </c>
       <c r="N768" s="1" t="n"/>
       <c r="O768" s="1" t="n"/>
-      <c r="P768" s="1" t="n"/>
-      <c r="Q768" s="1" t="inlineStr"/>
-      <c r="R768" s="1" t="inlineStr"/>
+      <c r="P768" s="2" t="n">
+        <v>46282.6795965625</v>
+      </c>
+      <c r="Q768" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
+      <c r="R768" s="1" t="inlineStr">
+        <is>
+          <t>Como explicado via Whatsapp, necessário o alvará de funcionamento para concluir o processo de legalização do anúncio, foi possivel verificar?</t>
+        </is>
+      </c>
       <c r="S768" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T768" s="1" t="n"/>
@@ -58852,7 +58942,7 @@
     </row>
     <row r="769">
       <c r="A769" s="1" t="n">
-        <v>82721</v>
+        <v>84290</v>
       </c>
       <c r="B769" s="1" t="inlineStr">
         <is>
@@ -58861,30 +58951,30 @@
       </c>
       <c r="C769" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D769" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E769" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados, CADAN - Notificação.cliente solicita nossa ajuda nesse atendimento, sendo o caso, se tivermos indicação de quem pode ajudar, agradeço. </t>
+          <t>por gentileza, providenciar contrato social da empresa 6179 - ITALO BRASILEIRA</t>
         </is>
       </c>
       <c r="F769" s="1" t="n">
-        <v>2282</v>
+        <v>6179</v>
       </c>
       <c r="G769" s="1" t="inlineStr">
         <is>
-          <t>CASA SANTA GEMMA SUPERMERCADOS LTDA</t>
+          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="H769" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I769" s="1" t="inlineStr">
@@ -58893,10 +58983,10 @@
         </is>
       </c>
       <c r="J769" s="2" t="n">
-        <v>46254.41795709491</v>
+        <v>46287.49436180555</v>
       </c>
       <c r="K769" s="2" t="n">
-        <v>46255</v>
+        <v>46288</v>
       </c>
       <c r="L769" s="1" t="inlineStr">
         <is>
@@ -58905,22 +58995,22 @@
       </c>
       <c r="M769" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N769" s="1" t="n"/>
       <c r="O769" s="1" t="n"/>
       <c r="P769" s="2" t="n">
-        <v>46282.6795965625</v>
+        <v>46287.70713295139</v>
       </c>
       <c r="Q769" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="R769" s="1" t="inlineStr">
         <is>
-          <t>Como explicado via Whatsapp, necessário o alvará de funcionamento para concluir o processo de legalização do anúncio, foi possivel verificar?</t>
+          <t xml:space="preserve">SEGUE, copia extraída da JUCESP. - Essa alteração nao foi feita pela MG, logo não temos a original. </t>
         </is>
       </c>
       <c r="S769" s="1" t="inlineStr">
@@ -58933,26 +59023,26 @@
     </row>
     <row r="770">
       <c r="A770" s="1" t="n">
-        <v>84290</v>
+        <v>82236</v>
       </c>
       <c r="B770" s="1" t="inlineStr">
         <is>
-          <t>Notificação</t>
+          <t>Inuitilização de Nota Fiscais</t>
         </is>
       </c>
       <c r="C770" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="D770" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E770" s="1" t="inlineStr">
         <is>
-          <t>por gentileza, providenciar contrato social da empresa 6179 - ITALO BRASILEIRA</t>
+          <t>Informado pelo cliente sequencia de Cupons que foram indevidamente emitidos. Confirmado com equipe fiscal que todos os cupons estão ativos e foram escriturados no mês 06. Se faz necessário processo de cancelamento extemporâneo tendo em vista o prazo limite ser 30 minutos.Processo conversado com o Gerente Master Reynaldo segundo ele cliente está ciente que este processo gera proposta de serviços extraordinários.Favor manter o contato com o cliente Guilherme (11) 99991-9311 ou Gabriela (11) 99797-6771Relação dos cupons informados pelo cliente estão no anexo.</t>
         </is>
       </c>
       <c r="F770" s="1" t="n">
@@ -58965,7 +59055,7 @@
       </c>
       <c r="H770" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I770" s="1" t="inlineStr">
@@ -58974,39 +59064,29 @@
         </is>
       </c>
       <c r="J770" s="2" t="n">
-        <v>46287.49436180555</v>
+        <v>46245.58840929398</v>
       </c>
       <c r="K770" s="2" t="n">
-        <v>46288</v>
+        <v>46248</v>
       </c>
       <c r="L770" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M770" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N770" s="1" t="n"/>
       <c r="O770" s="1" t="n"/>
-      <c r="P770" s="2" t="n">
-        <v>46287.70713295139</v>
-      </c>
-      <c r="Q770" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="R770" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEGUE, copia extraída da JUCESP. - Essa alteração nao foi feita pela MG, logo não temos a original. </t>
-        </is>
-      </c>
+      <c r="P770" s="1" t="n"/>
+      <c r="Q770" s="1" t="inlineStr"/>
+      <c r="R770" s="1" t="inlineStr"/>
       <c r="S770" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T770" s="1" t="n"/>
@@ -59014,16 +59094,16 @@
     </row>
     <row r="771">
       <c r="A771" s="1" t="n">
-        <v>82236</v>
+        <v>84108</v>
       </c>
       <c r="B771" s="1" t="inlineStr">
         <is>
-          <t>Inuitilização de Nota Fiscais</t>
+          <t>Levantamento de Débitos</t>
         </is>
       </c>
       <c r="C771" s="1" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D771" s="1" t="inlineStr">
@@ -59033,20 +59113,20 @@
       </c>
       <c r="E771" s="1" t="inlineStr">
         <is>
-          <t>Informado pelo cliente sequencia de Cupons que foram indevidamente emitidos. Confirmado com equipe fiscal que todos os cupons estão ativos e foram escriturados no mês 06. Se faz necessário processo de cancelamento extemporâneo tendo em vista o prazo limite ser 30 minutos.Processo conversado com o Gerente Master Reynaldo segundo ele cliente está ciente que este processo gera proposta de serviços extraordinários.Favor manter o contato com o cliente Guilherme (11) 99991-9311 ou Gabriela (11) 99797-6771Relação dos cupons informados pelo cliente estão no anexo.</t>
+          <t>Prezados,Boa tarde!Conforme solicitação do cliente, por gentileza, realizar levantamento de débitos federais, estaduais, municipais, trabalhistas.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F771" s="1" t="n">
-        <v>6179</v>
+        <v>6276</v>
       </c>
       <c r="G771" s="1" t="inlineStr">
         <is>
-          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
+          <t>LP GESTAO EMPRESARIAL LTDA</t>
         </is>
       </c>
       <c r="H771" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I771" s="1" t="inlineStr">
@@ -59055,29 +59135,40 @@
         </is>
       </c>
       <c r="J771" s="2" t="n">
-        <v>46245.58840929398</v>
+        <v>46282.58642442129</v>
       </c>
       <c r="K771" s="2" t="n">
-        <v>46248</v>
+        <v>46283</v>
       </c>
       <c r="L771" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M771" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N771" s="1" t="n"/>
       <c r="O771" s="1" t="n"/>
-      <c r="P771" s="1" t="n"/>
-      <c r="Q771" s="1" t="inlineStr"/>
-      <c r="R771" s="1" t="inlineStr"/>
+      <c r="P771" s="2" t="n">
+        <v>46286.3909099537</v>
+      </c>
+      <c r="Q771" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R771" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bom dia!
+Segue levantamento. </t>
+        </is>
+      </c>
       <c r="S771" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T771" s="1" t="n"/>
@@ -59085,39 +59176,39 @@
     </row>
     <row r="772">
       <c r="A772" s="1" t="n">
-        <v>84108</v>
+        <v>84121</v>
       </c>
       <c r="B772" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C772" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D772" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E772" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Boa tarde!Conforme solicitação do cliente, por gentileza, realizar levantamento de débitos federais, estaduais, municipais, trabalhistas.Grato,Bruno.</t>
+          <t>Por gentileza poderia me informar o login e a senha da prefeitura.</t>
         </is>
       </c>
       <c r="F772" s="1" t="n">
-        <v>6276</v>
+        <v>6368</v>
       </c>
       <c r="G772" s="1" t="inlineStr">
         <is>
-          <t>LP GESTAO EMPRESARIAL LTDA</t>
+          <t>CUCINARE PRO ALIMENTACAO LTDA (FILIAL 102)</t>
         </is>
       </c>
       <c r="H772" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Talita Silva</t>
         </is>
       </c>
       <c r="I772" s="1" t="inlineStr">
@@ -59126,40 +59217,29 @@
         </is>
       </c>
       <c r="J772" s="2" t="n">
-        <v>46282.58642442129</v>
+        <v>46282.72291574074</v>
       </c>
       <c r="K772" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="L772" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M772" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Rafaella Macedo</t>
         </is>
       </c>
       <c r="N772" s="1" t="n"/>
       <c r="O772" s="1" t="n"/>
-      <c r="P772" s="2" t="n">
-        <v>46286.3909099537</v>
-      </c>
-      <c r="Q772" s="1" t="inlineStr">
-        <is>
-          <t>Karina Dantas</t>
-        </is>
-      </c>
-      <c r="R772" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bom dia!
-Segue levantamento. </t>
-        </is>
-      </c>
+      <c r="P772" s="1" t="n"/>
+      <c r="Q772" s="1" t="inlineStr"/>
+      <c r="R772" s="1" t="inlineStr"/>
       <c r="S772" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T772" s="1" t="n"/>
@@ -59167,7 +59247,7 @@
     </row>
     <row r="773">
       <c r="A773" s="1" t="n">
-        <v>84121</v>
+        <v>84122</v>
       </c>
       <c r="B773" s="1" t="inlineStr">
         <is>
@@ -59190,11 +59270,11 @@
         </is>
       </c>
       <c r="F773" s="1" t="n">
-        <v>6368</v>
+        <v>6388</v>
       </c>
       <c r="G773" s="1" t="inlineStr">
         <is>
-          <t>CUCINARE PRO ALIMENTACAO LTDA (FILIAL 102)</t>
+          <t>CUCINARE PRO ALIMENTAÇÃO LTDA  (FILIAL 103)</t>
         </is>
       </c>
       <c r="H773" s="1" t="inlineStr">
@@ -59208,7 +59288,7 @@
         </is>
       </c>
       <c r="J773" s="2" t="n">
-        <v>46282.72291574074</v>
+        <v>46282.72886608796</v>
       </c>
       <c r="K773" s="2" t="n">
         <v>46286</v>
@@ -59238,39 +59318,39 @@
     </row>
     <row r="774">
       <c r="A774" s="1" t="n">
-        <v>84122</v>
+        <v>82771</v>
       </c>
       <c r="B774" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C774" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras Cláusulas</t>
         </is>
       </c>
       <c r="D774" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E774" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza poderia me informar o login e a senha da prefeitura.</t>
+          <t>Alteração contratual da empresa: 6404-Solar Investimentos LtdaGrupo: Solar InvestimentosProposta ainda não foi negociada, o Master solicitou que fosse enviado a proposta com o valor padrãoInclusão de CNAE's abaixo:INCLUIR: (OK)•	7490-1/04 Atividades de intermediação e agenciamento de serviços e negócios em geral, exceto imobiliários•	4618-4/99 Outros representantes comerciais e agentes do comércio especializado em produtos não especificados anteriormenteEstes CNAE's estão sendo incluídos para a pratica dos serviços que seguem abaixo, "Paralegal", por favor validar se faz sentido e se atende os serviços abaixo relacionados:•10.02 – Agenciamento, corretagem ou intermediação de títulos em geral, valores mobiliários e contratos quaisquer.•10.05 – Agenciamento, corretagem ou intermediação de bens móveis ou imóveis, não abrangidos em outros itens ou subitens, inclusive aqueles realizados no âmbito de Bolsas de Mercadorias e Futuros, por quaisquer meios•10.09 – Representação de qualquer natureza, inclusive comercial</t>
         </is>
       </c>
       <c r="F774" s="1" t="n">
-        <v>6388</v>
+        <v>6404</v>
       </c>
       <c r="G774" s="1" t="inlineStr">
         <is>
-          <t>CUCINARE PRO ALIMENTAÇÃO LTDA  (FILIAL 103)</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H774" s="1" t="inlineStr">
         <is>
-          <t>Talita Silva</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I774" s="1" t="inlineStr">
@@ -59279,108 +59359,120 @@
         </is>
       </c>
       <c r="J774" s="2" t="n">
-        <v>46282.72886608796</v>
+        <v>46255.3884375</v>
       </c>
       <c r="K774" s="2" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="L774" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M774" s="1" t="inlineStr">
         <is>
-          <t>Rafaella Macedo</t>
-        </is>
-      </c>
-      <c r="N774" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N774" s="2" t="n">
+        <v>46261.63239140046</v>
+      </c>
       <c r="O774" s="1" t="n"/>
       <c r="P774" s="1" t="n"/>
       <c r="Q774" s="1" t="inlineStr"/>
-      <c r="R774" s="1" t="inlineStr"/>
-      <c r="S774" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T774" s="1" t="n"/>
-      <c r="U774" s="1" t="inlineStr"/>
-    </row>
-    <row r="775">
-      <c r="A775" s="1" t="n">
-        <v>82771</v>
-      </c>
-      <c r="B775" s="1" t="inlineStr">
-        <is>
-          <t>Alteração Contratual</t>
-        </is>
-      </c>
-      <c r="C775" s="1" t="inlineStr">
-        <is>
-          <t>Outras Cláusulas</t>
-        </is>
-      </c>
-      <c r="D775" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E775" s="1" t="inlineStr">
-        <is>
-          <t>Alteração contratual da empresa: 6404-Solar Investimentos LtdaGrupo: Solar InvestimentosProposta ainda não foi negociada, o Master solicitou que fosse enviado a proposta com o valor padrãoInclusão de CNAE's abaixo:INCLUIR: (OK)•	7490-1/04 Atividades de intermediação e agenciamento de serviços e negócios em geral, exceto imobiliários•	4618-4/99 Outros representantes comerciais e agentes do comércio especializado em produtos não especificados anteriormenteEstes CNAE's estão sendo incluídos para a pratica dos serviços que seguem abaixo, "Paralegal", por favor validar se faz sentido e se atende os serviços abaixo relacionados:•10.02 – Agenciamento, corretagem ou intermediação de títulos em geral, valores mobiliários e contratos quaisquer.•10.05 – Agenciamento, corretagem ou intermediação de bens móveis ou imóveis, não abrangidos em outros itens ou subitens, inclusive aqueles realizados no âmbito de Bolsas de Mercadorias e Futuros, por quaisquer meios•10.09 – Representação de qualquer natureza, inclusive comercial</t>
-        </is>
-      </c>
-      <c r="F775" s="1" t="n">
-        <v>6404</v>
-      </c>
-      <c r="G775" s="1" t="inlineStr">
-        <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
-        </is>
-      </c>
-      <c r="H775" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
-      <c r="I775" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J775" s="2" t="n">
-        <v>46255.3884375</v>
-      </c>
-      <c r="K775" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="L775" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M775" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N775" s="2" t="n">
-        <v>46261.63239140046</v>
-      </c>
-      <c r="O775" s="1" t="n"/>
-      <c r="P775" s="1" t="n"/>
-      <c r="Q775" s="1" t="inlineStr"/>
-      <c r="R775" s="1" t="inlineStr">
+      <c r="R774" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Prezados(as), boa tarde!
 Conforme solicitado, alteração contratual em andamento. 
 Atenciosamente, </t>
         </is>
       </c>
+      <c r="S774" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T774" s="1" t="n"/>
+      <c r="U774" s="1" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="1" t="n">
+        <v>83854</v>
+      </c>
+      <c r="B775" s="1" t="inlineStr">
+        <is>
+          <t>Levantamento de Débitos</t>
+        </is>
+      </c>
+      <c r="C775" s="1" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="D775" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E775" s="1" t="inlineStr">
+        <is>
+          <t>Prezados,Bom dia!Conforme solicitação do cliente, por gentileza, realizar levantamento de débitos federais, estaduais, municipais, trabalhistas das empresas do grupo Casa Glória (6125-CORA SERVIÇOS e 6276-LP GESTÃO EMPRESARIAL LTDA).Atenciosamente,Bruno.</t>
+        </is>
+      </c>
+      <c r="F775" s="1" t="n">
+        <v>6125</v>
+      </c>
+      <c r="G775" s="1" t="inlineStr">
+        <is>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+        </is>
+      </c>
+      <c r="H775" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="I775" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J775" s="2" t="n">
+        <v>46276.4970653588</v>
+      </c>
+      <c r="K775" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="L775" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M775" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N775" s="2" t="n">
+        <v>46283.43609560185</v>
+      </c>
+      <c r="O775" s="1" t="n"/>
+      <c r="P775" s="2" t="n">
+        <v>46286.3846287037</v>
+      </c>
+      <c r="Q775" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="R775" s="1" t="inlineStr">
+        <is>
+          <t>Bruno, por gentileza abrir um chamado por empresa</t>
+        </is>
+      </c>
       <c r="S775" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T775" s="1" t="n"/>
@@ -59388,7 +59480,7 @@
     </row>
     <row r="776">
       <c r="A776" s="1" t="n">
-        <v>83854</v>
+        <v>83800</v>
       </c>
       <c r="B776" s="1" t="inlineStr">
         <is>
@@ -59402,20 +59494,20 @@
       </c>
       <c r="D776" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E776" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Bom dia!Conforme solicitação do cliente, por gentileza, realizar levantamento de débitos federais, estaduais, municipais, trabalhistas das empresas do grupo Casa Glória (6125-CORA SERVIÇOS e 6276-LP GESTÃO EMPRESARIAL LTDA).Atenciosamente,Bruno.</t>
+          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos Federais. </t>
         </is>
       </c>
       <c r="F776" s="1" t="n">
-        <v>6125</v>
+        <v>6454</v>
       </c>
       <c r="G776" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+          <t>MPJ - PRODUTOS, EQUIPAMENTOS E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="H776" s="1" t="inlineStr">
@@ -59429,10 +59521,10 @@
         </is>
       </c>
       <c r="J776" s="2" t="n">
-        <v>46276.4970653588</v>
+        <v>46275.48413533565</v>
       </c>
       <c r="K776" s="2" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="L776" s="1" t="inlineStr">
         <is>
@@ -59441,24 +59533,23 @@
       </c>
       <c r="M776" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N776" s="2" t="n">
-        <v>46283.43609560185</v>
-      </c>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
+      <c r="N776" s="1" t="n"/>
       <c r="O776" s="1" t="n"/>
       <c r="P776" s="2" t="n">
-        <v>46286.3846287037</v>
+        <v>46280.78507179398</v>
       </c>
       <c r="Q776" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="R776" s="1" t="inlineStr">
         <is>
-          <t>Bruno, por gentileza abrir um chamado por empresa</t>
+          <t>Yasmin, boa noite!
+Não ha débitos em aberto, segue pesquisa e certidão.</t>
         </is>
       </c>
       <c r="S776" s="1" t="inlineStr">
@@ -59471,7 +59562,7 @@
     </row>
     <row r="777">
       <c r="A777" s="1" t="n">
-        <v>83800</v>
+        <v>83801</v>
       </c>
       <c r="B777" s="1" t="inlineStr">
         <is>
@@ -59480,7 +59571,7 @@
       </c>
       <c r="C777" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D777" s="1" t="inlineStr">
@@ -59490,7 +59581,7 @@
       </c>
       <c r="E777" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos Federais. </t>
+          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos Estaduais. </t>
         </is>
       </c>
       <c r="F777" s="1" t="n">
@@ -59512,7 +59603,7 @@
         </is>
       </c>
       <c r="J777" s="2" t="n">
-        <v>46275.48413533565</v>
+        <v>46275.48453171297</v>
       </c>
       <c r="K777" s="2" t="n">
         <v>46276</v>
@@ -59530,7 +59621,7 @@
       <c r="N777" s="1" t="n"/>
       <c r="O777" s="1" t="n"/>
       <c r="P777" s="2" t="n">
-        <v>46280.78507179398</v>
+        <v>46280.79029938657</v>
       </c>
       <c r="Q777" s="1" t="inlineStr">
         <is>
@@ -59539,8 +59630,8 @@
       </c>
       <c r="R777" s="1" t="inlineStr">
         <is>
-          <t>Yasmin, boa noite!
-Não ha débitos em aberto, segue pesquisa e certidão.</t>
+          <t>Boa noite!
+Segue.</t>
         </is>
       </c>
       <c r="S777" s="1" t="inlineStr">
@@ -59553,7 +59644,7 @@
     </row>
     <row r="778">
       <c r="A778" s="1" t="n">
-        <v>83801</v>
+        <v>83802</v>
       </c>
       <c r="B778" s="1" t="inlineStr">
         <is>
@@ -59562,7 +59653,7 @@
       </c>
       <c r="C778" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D778" s="1" t="inlineStr">
@@ -59572,7 +59663,7 @@
       </c>
       <c r="E778" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos Estaduais. </t>
+          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos da Prefeitura. </t>
         </is>
       </c>
       <c r="F778" s="1" t="n">
@@ -59594,7 +59685,7 @@
         </is>
       </c>
       <c r="J778" s="2" t="n">
-        <v>46275.48453171297</v>
+        <v>46275.48498935185</v>
       </c>
       <c r="K778" s="2" t="n">
         <v>46276</v>
@@ -59612,7 +59703,7 @@
       <c r="N778" s="1" t="n"/>
       <c r="O778" s="1" t="n"/>
       <c r="P778" s="2" t="n">
-        <v>46280.79029938657</v>
+        <v>46280.7878784375</v>
       </c>
       <c r="Q778" s="1" t="inlineStr">
         <is>
@@ -59621,8 +59712,8 @@
       </c>
       <c r="R778" s="1" t="inlineStr">
         <is>
-          <t>Boa noite!
-Segue.</t>
+          <t xml:space="preserve">Boa noite!
+Segue taxas em aberto. </t>
         </is>
       </c>
       <c r="S778" s="1" t="inlineStr">
@@ -59635,39 +59726,39 @@
     </row>
     <row r="779">
       <c r="A779" s="1" t="n">
-        <v>83802</v>
+        <v>82787</v>
       </c>
       <c r="B779" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Declaração</t>
         </is>
       </c>
       <c r="C779" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Decore</t>
         </is>
       </c>
       <c r="D779" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E779" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, prezados!!Por gentileza, realizar levantamento de débitos da Prefeitura. </t>
+          <t>Por gentileza, providenciar Decore para Sócio Roberto Toledo, referente aos pagamentos realizados entre 05/2026 e 07/2026 que somam R$ 133.560,00 , finalidade da decore Visto AmericanoROBERTO TOLEDO FERREIRA DE MORAES – CPF. 332.558.388-19 RG. 32.608.800-SSP-SO</t>
         </is>
       </c>
       <c r="F779" s="1" t="n">
-        <v>6454</v>
+        <v>6460</v>
       </c>
       <c r="G779" s="1" t="inlineStr">
         <is>
-          <t>MPJ - PRODUTOS, EQUIPAMENTOS E SERVICOS LTDA</t>
+          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H779" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I779" s="1" t="inlineStr">
@@ -59676,10 +59767,10 @@
         </is>
       </c>
       <c r="J779" s="2" t="n">
-        <v>46275.48498935185</v>
+        <v>46255.54234074074</v>
       </c>
       <c r="K779" s="2" t="n">
-        <v>46276</v>
+        <v>46258</v>
       </c>
       <c r="L779" s="1" t="inlineStr">
         <is>
@@ -59688,23 +59779,24 @@
       </c>
       <c r="M779" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
-        </is>
-      </c>
-      <c r="N779" s="1" t="n"/>
+          <t>Simone Marques</t>
+        </is>
+      </c>
+      <c r="N779" s="2" t="n">
+        <v>46259.42845466435</v>
+      </c>
       <c r="O779" s="1" t="n"/>
       <c r="P779" s="2" t="n">
-        <v>46280.7878784375</v>
+        <v>46259.4294483449</v>
       </c>
       <c r="Q779" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="R779" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa noite!
-Segue taxas em aberto. </t>
+          <t xml:space="preserve">Providenciando </t>
         </is>
       </c>
       <c r="S779" s="1" t="inlineStr">
@@ -59717,16 +59809,16 @@
     </row>
     <row r="780">
       <c r="A780" s="1" t="n">
-        <v>82787</v>
+        <v>84074</v>
       </c>
       <c r="B780" s="1" t="inlineStr">
         <is>
-          <t>Declaração</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C780" s="1" t="inlineStr">
         <is>
-          <t>Decore</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D780" s="1" t="inlineStr">
@@ -59736,20 +59828,20 @@
       </c>
       <c r="E780" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar Decore para Sócio Roberto Toledo, referente aos pagamentos realizados entre 05/2026 e 07/2026 que somam R$ 133.560,00 , finalidade da decore Visto AmericanoROBERTO TOLEDO FERREIRA DE MORAES – CPF. 332.558.388-19 RG. 32.608.800-SSP-SO</t>
+          <t>Por gentileza solicitar abaixa do débitos junto a Sefaz de Minas, comprovantes anexos :                                                                                                                       Destas pendências só não localizamos 4 indicações conforme segue:31/07/22 R$ 13,1831/10/22 R$ 13,1830/11/22 R$   1,6830/11/22 R$ 31,19Total de R$ 59,23</t>
         </is>
       </c>
       <c r="F780" s="1" t="n">
-        <v>6460</v>
+        <v>6462</v>
       </c>
       <c r="G780" s="1" t="inlineStr">
         <is>
-          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
+          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (FILIAL 2)</t>
         </is>
       </c>
       <c r="H780" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I780" s="1" t="inlineStr">
@@ -59758,14 +59850,14 @@
         </is>
       </c>
       <c r="J780" s="2" t="n">
-        <v>46255.54234074074</v>
+        <v>46281.48259829861</v>
       </c>
       <c r="K780" s="2" t="n">
-        <v>46258</v>
+        <v>46286</v>
       </c>
       <c r="L780" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M780" s="1" t="inlineStr">
@@ -59774,25 +59866,20 @@
         </is>
       </c>
       <c r="N780" s="2" t="n">
-        <v>46259.42845466435</v>
+        <v>46283.43791516204</v>
       </c>
       <c r="O780" s="1" t="n"/>
-      <c r="P780" s="2" t="n">
-        <v>46259.4294483449</v>
-      </c>
-      <c r="Q780" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+      <c r="P780" s="1" t="n"/>
+      <c r="Q780" s="1" t="inlineStr"/>
       <c r="R780" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Providenciando </t>
+          <t xml:space="preserve">Bom dia!
+Processo protocolado. iremos acompanhar o deferimento. </t>
         </is>
       </c>
       <c r="S780" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T780" s="1" t="n"/>
@@ -59800,16 +59887,16 @@
     </row>
     <row r="781">
       <c r="A781" s="1" t="n">
-        <v>84074</v>
+        <v>83246</v>
       </c>
       <c r="B781" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Notificação</t>
         </is>
       </c>
       <c r="C781" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D781" s="1" t="inlineStr">
@@ -59819,20 +59906,20 @@
       </c>
       <c r="E781" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza solicitar abaixa do débitos junto a Sefaz de Minas, comprovantes anexos :                                                                                                                       Destas pendências só não localizamos 4 indicações conforme segue:31/07/22 R$ 13,1831/10/22 R$ 13,1830/11/22 R$   1,6830/11/22 R$ 31,19Total de R$ 59,23</t>
+          <t xml:space="preserve">Atender a notificação da Prefeitura  - regularizar Cnae da atividade econômica. </t>
         </is>
       </c>
       <c r="F781" s="1" t="n">
-        <v>6462</v>
+        <v>6507</v>
       </c>
       <c r="G781" s="1" t="inlineStr">
         <is>
-          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (FILIAL 2)</t>
+          <t xml:space="preserve">ERS PRINT SOLUÇÕES GRAFICAS E VISUAIS LTDA </t>
         </is>
       </c>
       <c r="H781" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I781" s="1" t="inlineStr">
@@ -59841,14 +59928,14 @@
         </is>
       </c>
       <c r="J781" s="2" t="n">
-        <v>46281.48259829861</v>
+        <v>46262.73318298611</v>
       </c>
       <c r="K781" s="2" t="n">
-        <v>46286</v>
+        <v>46269</v>
       </c>
       <c r="L781" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M781" s="1" t="inlineStr">
@@ -59856,18 +59943,11 @@
           <t>Simone Marques</t>
         </is>
       </c>
-      <c r="N781" s="2" t="n">
-        <v>46283.43791516204</v>
-      </c>
+      <c r="N781" s="1" t="n"/>
       <c r="O781" s="1" t="n"/>
       <c r="P781" s="1" t="n"/>
       <c r="Q781" s="1" t="inlineStr"/>
-      <c r="R781" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bom dia!
-Processo protocolado. iremos acompanhar o deferimento. </t>
-        </is>
-      </c>
+      <c r="R781" s="1" t="inlineStr"/>
       <c r="S781" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -59878,39 +59958,39 @@
     </row>
     <row r="782">
       <c r="A782" s="1" t="n">
-        <v>83246</v>
+        <v>83877</v>
       </c>
       <c r="B782" s="1" t="inlineStr">
         <is>
-          <t>Notificação</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C782" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D782" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E782" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atender a notificação da Prefeitura  - regularizar Cnae da atividade econômica. </t>
+          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
         </is>
       </c>
       <c r="F782" s="1" t="n">
-        <v>6507</v>
+        <v>6508</v>
       </c>
       <c r="G782" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERS PRINT SOLUÇÕES GRAFICAS E VISUAIS LTDA </t>
+          <t>MIRACOR GRAFICA LTDA</t>
         </is>
       </c>
       <c r="H782" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I782" s="1" t="inlineStr">
@@ -59919,26 +59999,30 @@
         </is>
       </c>
       <c r="J782" s="2" t="n">
-        <v>46262.73318298611</v>
+        <v>46276.71954690972</v>
       </c>
       <c r="K782" s="2" t="n">
-        <v>46269</v>
+        <v>46280</v>
       </c>
       <c r="L782" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M782" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Ney Barbosa</t>
         </is>
       </c>
       <c r="N782" s="1" t="n"/>
       <c r="O782" s="1" t="n"/>
       <c r="P782" s="1" t="n"/>
       <c r="Q782" s="1" t="inlineStr"/>
-      <c r="R782" s="1" t="inlineStr"/>
+      <c r="R782" s="1" t="inlineStr">
+        <is>
+          <t>A socia esta com problema no CPF juntamente como Titulo de Eleitor, Conforme informado pela o cliente a ELISA, a socia esta fora e nao consegue resolver essa pendencia. logo nao conseguimos criar o codigo de acesso.</t>
+        </is>
+      </c>
       <c r="S782" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -59949,39 +60033,39 @@
     </row>
     <row r="783">
       <c r="A783" s="1" t="n">
-        <v>83877</v>
+        <v>82207</v>
       </c>
       <c r="B783" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Restituição</t>
         </is>
       </c>
       <c r="C783" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D783" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E783" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderia providenciar o código de acesso do portal do Simples Nacional no MG controle.Desde já, agradeço.Atenciosamente.</t>
+          <t>6538 - SALDÃO CASA &amp; LARPreciso que inicie o processo de devolução do valor pago a maior.Houve dois pagamento de 803,78  marquei de laranja no PDF. Este processo preciso estar constantemente atualizado do status, pois após a conclusão o cliente devolverá o valor para MG, que pagou a segunda guia.Att.Vander</t>
         </is>
       </c>
       <c r="F783" s="1" t="n">
-        <v>6508</v>
+        <v>6538</v>
       </c>
       <c r="G783" s="1" t="inlineStr">
         <is>
-          <t>MIRACOR GRAFICA LTDA</t>
+          <t>SALDAO CASA &amp; LAR MOVEIS E ELETRODOMESTICOS LTDA</t>
         </is>
       </c>
       <c r="H783" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I783" s="1" t="inlineStr">
@@ -59990,28 +60074,30 @@
         </is>
       </c>
       <c r="J783" s="2" t="n">
-        <v>46276.71954690972</v>
+        <v>46245.45257068287</v>
       </c>
       <c r="K783" s="2" t="n">
-        <v>46280</v>
+        <v>46247</v>
       </c>
       <c r="L783" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M783" s="1" t="inlineStr">
         <is>
-          <t>Ney Barbosa</t>
-        </is>
-      </c>
-      <c r="N783" s="1" t="n"/>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="N783" s="2" t="n">
+        <v>46255.48998958334</v>
+      </c>
       <c r="O783" s="1" t="n"/>
       <c r="P783" s="1" t="n"/>
       <c r="Q783" s="1" t="inlineStr"/>
       <c r="R783" s="1" t="inlineStr">
         <is>
-          <t>A socia esta com problema no CPF juntamente como Titulo de Eleitor, Conforme informado pela o cliente a ELISA, a socia esta fora e nao consegue resolver essa pendencia. logo nao conseguimos criar o codigo de acesso.</t>
+          <t>Aguardando dados bancários para solicitar a restituição.</t>
         </is>
       </c>
       <c r="S783" s="1" t="inlineStr">
@@ -60024,16 +60110,16 @@
     </row>
     <row r="784">
       <c r="A784" s="1" t="n">
-        <v>82207</v>
+        <v>84386</v>
       </c>
       <c r="B784" s="1" t="inlineStr">
         <is>
-          <t>Restituição</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C784" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Vigilância Sanitária</t>
         </is>
       </c>
       <c r="D784" s="1" t="inlineStr">
@@ -60043,54 +60129,44 @@
       </c>
       <c r="E784" s="1" t="inlineStr">
         <is>
-          <t>6538 - SALDÃO CASA &amp; LARPreciso que inicie o processo de devolução do valor pago a maior.Houve dois pagamento de 803,78  marquei de laranja no PDF. Este processo preciso estar constantemente atualizado do status, pois após a conclusão o cliente devolverá o valor para MG, que pagou a segunda guia.Att.Vander</t>
+          <t>Por gentileza, dar entrada nas licenças solicitadas no email, se necessario proposto por gentileza encaminha, para que eu possa apresentar ao cliente. Qualquer duvida fico a disposição</t>
         </is>
       </c>
       <c r="F784" s="1" t="n">
-        <v>6538</v>
+        <v>6556</v>
       </c>
       <c r="G784" s="1" t="inlineStr">
         <is>
-          <t>SALDAO CASA &amp; LAR MOVEIS E ELETRODOMESTICOS LTDA</t>
-        </is>
-      </c>
-      <c r="H784" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+          <t>CLINICA MEDICA E ODONTOLOGICA AMOR SAUDE BOTUCATU LTDA</t>
+        </is>
+      </c>
+      <c r="H784" s="1" t="n"/>
       <c r="I784" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J784" s="2" t="n">
-        <v>46245.45257068287</v>
+        <v>46288.58970836805</v>
       </c>
       <c r="K784" s="2" t="n">
-        <v>46247</v>
+        <v>46290</v>
       </c>
       <c r="L784" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M784" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
-        </is>
-      </c>
-      <c r="N784" s="2" t="n">
-        <v>46255.48998958334</v>
-      </c>
+          <t>Rogerio Egidio</t>
+        </is>
+      </c>
+      <c r="N784" s="1" t="n"/>
       <c r="O784" s="1" t="n"/>
       <c r="P784" s="1" t="n"/>
       <c r="Q784" s="1" t="inlineStr"/>
-      <c r="R784" s="1" t="inlineStr">
-        <is>
-          <t>Aguardando dados bancários para solicitar a restituição.</t>
-        </is>
-      </c>
+      <c r="R784" s="1" t="n"/>
       <c r="S784" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -60101,63 +60177,73 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>84386</v>
+        <v>83642</v>
       </c>
       <c r="B785" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>Notificação</t>
         </is>
       </c>
       <c r="C785" s="1" t="inlineStr">
         <is>
-          <t>Vigilância Sanitária</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D785" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E785" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, dar entrada nas licenças solicitadas no email, se necessario proposto por gentileza encaminha, para que eu possa apresentar ao cliente. Qualquer duvida fico a disposição</t>
+          <t>Cliente recebeu notificação CRC, prazo de 15 dias de retorno.</t>
         </is>
       </c>
       <c r="F785" s="1" t="n">
-        <v>6556</v>
+        <v>6588</v>
       </c>
       <c r="G785" s="1" t="inlineStr">
         <is>
-          <t>CLINICA MEDICA E ODONTOLOGICA AMOR SAUDE BOTUCATU LTDA</t>
-        </is>
-      </c>
-      <c r="H785" s="1" t="n"/>
+          <t>ALM GESTAO TECH RETAIL LTDA</t>
+        </is>
+      </c>
+      <c r="H785" s="1" t="inlineStr">
+        <is>
+          <t>Thifany Leite</t>
+        </is>
+      </c>
       <c r="I785" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J785" s="2" t="n">
-        <v>46288.58970836805</v>
+        <v>46273.44699390046</v>
       </c>
       <c r="K785" s="2" t="n">
-        <v>46290</v>
+        <v>46276</v>
       </c>
       <c r="L785" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M785" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
-        </is>
-      </c>
-      <c r="N785" s="1" t="n"/>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N785" s="2" t="n">
+        <v>46283.63424204861</v>
+      </c>
       <c r="O785" s="1" t="n"/>
       <c r="P785" s="1" t="n"/>
       <c r="Q785" s="1" t="inlineStr"/>
-      <c r="R785" s="1" t="n"/>
+      <c r="R785" s="1" t="inlineStr">
+        <is>
+          <t>Romero, neste caso, ou fazemos a inscrição no CRC ou altera a atividade da empresa.</t>
+        </is>
+      </c>
       <c r="S785" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -60168,39 +60254,39 @@
     </row>
     <row r="786">
       <c r="A786" s="1" t="n">
-        <v>83642</v>
+        <v>84129</v>
       </c>
       <c r="B786" s="1" t="inlineStr">
         <is>
-          <t>Notificação</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C786" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D786" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E786" s="1" t="inlineStr">
         <is>
-          <t>Cliente recebeu notificação CRC, prazo de 15 dias de retorno.</t>
+          <t>Por gentileza poderia me informar o login e a senha da prefeitura.</t>
         </is>
       </c>
       <c r="F786" s="1" t="n">
-        <v>6588</v>
+        <v>6608</v>
       </c>
       <c r="G786" s="1" t="inlineStr">
         <is>
-          <t>ALM GESTAO TECH RETAIL LTDA</t>
+          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 4)</t>
         </is>
       </c>
       <c r="H786" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Talita Silva</t>
         </is>
       </c>
       <c r="I786" s="1" t="inlineStr">
@@ -60209,10 +60295,10 @@
         </is>
       </c>
       <c r="J786" s="2" t="n">
-        <v>46273.44699390046</v>
+        <v>46282.74585570602</v>
       </c>
       <c r="K786" s="2" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="L786" s="1" t="inlineStr">
         <is>
@@ -60221,7 +60307,7 @@
       </c>
       <c r="M786" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
+          <t>Rafaella Macedo</t>
         </is>
       </c>
       <c r="N786" s="1" t="n"/>
@@ -60239,11 +60325,11 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>84129</v>
+        <v>82264</v>
       </c>
       <c r="B787" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C787" s="1" t="inlineStr">
@@ -60253,25 +60339,25 @@
       </c>
       <c r="D787" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E787" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza poderia me informar o login e a senha da prefeitura.</t>
+          <t>Por gentileza enviar a guia atualizada da TFEdas duas empresas do grupo BOMBEIROS 6621 E 6622</t>
         </is>
       </c>
       <c r="F787" s="1" t="n">
-        <v>6608</v>
+        <v>6621</v>
       </c>
       <c r="G787" s="1" t="inlineStr">
         <is>
-          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 4)</t>
+          <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
         </is>
       </c>
       <c r="H787" s="1" t="inlineStr">
         <is>
-          <t>Talita Silva</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I787" s="1" t="inlineStr">
@@ -60280,29 +60366,40 @@
         </is>
       </c>
       <c r="J787" s="2" t="n">
-        <v>46282.74585570602</v>
+        <v>46246.3872690162</v>
       </c>
       <c r="K787" s="2" t="n">
-        <v>46286</v>
+        <v>46248</v>
       </c>
       <c r="L787" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M787" s="1" t="inlineStr">
         <is>
-          <t>Rafaella Macedo</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N787" s="1" t="n"/>
       <c r="O787" s="1" t="n"/>
-      <c r="P787" s="1" t="n"/>
-      <c r="Q787" s="1" t="inlineStr"/>
-      <c r="R787" s="1" t="inlineStr"/>
+      <c r="P787" s="2" t="n">
+        <v>46246.66841165509</v>
+      </c>
+      <c r="Q787" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R787" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boa tarde!
+Não há débitos em aberto, seguem certidões. </t>
+        </is>
+      </c>
       <c r="S787" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T787" s="1" t="n"/>
@@ -60310,39 +60407,39 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>82264</v>
+        <v>82915</v>
       </c>
       <c r="B788" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C788" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="D788" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E788" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza enviar a guia atualizada da TFEdas duas empresas do grupo BOMBEIROS 6621 E 6622</t>
+          <t>Alteração contratual do CAPITAL SOCIAL, QSA, ADMINISTRADOR e ATIVIDADE/CNAE da empresa 6628-TSN TECHNICAL SERVICE NETWORK LTDAGrupo: GTG1- Alteração de Sócio:Saida da Sra. MARIA BARBOSA DOS SANTOS CLEMENTE, que sede e tranfere o total das cotas para o Sr. ALISSON BARBOSA DE SOUSA 2- Aumento do capital:será aumentado de 150.000, para 300.000, sendo a integralização de 50.000, através do registro de um carro, e o restante (100.000), a integralizar em 12 parcelas.3- Alteração de CNAEs, seram removidos  4 e temos e incluir 6, conforme abaixo:CNAEs RETIRAR: (OK)•	23.41-9-00 - Fabricação de produtos cerâmicos refratários •	61.10-8-01 - Serviços de telefonia fixa comutada - STFC •	61.10-8-03 - Serviços de comunicação multimídia - SCM•	62.02-3-00 - Desenvolvimento e licenciamento de programas de computador customizáveisINCLUIR: (OK)•	4686-9/02 — Comércio atacadista de embalagens;•	4789-0/99 — Comércio varejista de outros produtos não especificados anteriormente;•	4744-0/03 — Comércio varejista de materiais hidráulicos;•	4679-6/04 — Comércio atacadista especializado de materiais de construção não especificados anteriormente;•	4673-7/00 — Comércio atacadista de material elétrico.•	86.60-7-00 - Atividades de apoio à gestão de saúde</t>
         </is>
       </c>
       <c r="F788" s="1" t="n">
-        <v>6621</v>
+        <v>6628</v>
       </c>
       <c r="G788" s="1" t="inlineStr">
         <is>
-          <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="H788" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I788" s="1" t="inlineStr">
@@ -60351,202 +60448,199 @@
         </is>
       </c>
       <c r="J788" s="2" t="n">
-        <v>46246.3872690162</v>
+        <v>46258.70282021991</v>
       </c>
       <c r="K788" s="2" t="n">
-        <v>46248</v>
+        <v>46286</v>
       </c>
       <c r="L788" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M788" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N788" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N788" s="2" t="n">
+        <v>46261.63173943287</v>
+      </c>
       <c r="O788" s="1" t="n"/>
-      <c r="P788" s="2" t="n">
-        <v>46246.66841165509</v>
-      </c>
-      <c r="Q788" s="1" t="inlineStr">
-        <is>
-          <t>Karina Dantas</t>
-        </is>
-      </c>
+      <c r="P788" s="1" t="n"/>
+      <c r="Q788" s="1" t="inlineStr"/>
       <c r="R788" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Boa tarde!
-Não há débitos em aberto, seguem certidões. </t>
-        </is>
-      </c>
-      <c r="S788" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T788" s="1" t="n"/>
-      <c r="U788" s="1" t="inlineStr"/>
-    </row>
-    <row r="789">
-      <c r="A789" s="1" t="n">
-        <v>82915</v>
-      </c>
-      <c r="B789" s="1" t="inlineStr">
-        <is>
-          <t>Alteração Contratual</t>
-        </is>
-      </c>
-      <c r="C789" s="1" t="inlineStr">
-        <is>
-          <t>Sócios</t>
-        </is>
-      </c>
-      <c r="D789" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA MASTER</t>
-        </is>
-      </c>
-      <c r="E789" s="1" t="inlineStr">
-        <is>
-          <t>Alteração contratual do CAPITAL SOCIAL, QSA, ADMINISTRADOR e ATIVIDADE/CNAE da empresa 6628-TSN TECHNICAL SERVICE NETWORK LTDAGrupo: GTG1- Alteração de Sócio:Saida da Sra. MARIA BARBOSA DOS SANTOS CLEMENTE, que sede e tranfere o total das cotas para o Sr. ALISSON BARBOSA DE SOUSA 2- Aumento do capital:será aumentado de 150.000, para 300.000, sendo a integralização de 50.000, através do registro de um carro, e o restante (100.000), a integralizar em 12 parcelas.3- Alteração de CNAEs, seram removidos  4 e temos e incluir 6, conforme abaixo:CNAEs RETIRAR: (OK)•	23.41-9-00 - Fabricação de produtos cerâmicos refratários •	61.10-8-01 - Serviços de telefonia fixa comutada - STFC •	61.10-8-03 - Serviços de comunicação multimídia - SCM•	62.02-3-00 - Desenvolvimento e licenciamento de programas de computador customizáveisINCLUIR: (OK)•	4686-9/02 — Comércio atacadista de embalagens;•	4789-0/99 — Comércio varejista de outros produtos não especificados anteriormente;•	4744-0/03 — Comércio varejista de materiais hidráulicos;•	4679-6/04 — Comércio atacadista especializado de materiais de construção não especificados anteriormente;•	4673-7/00 — Comércio atacadista de material elétrico.•	86.60-7-00 - Atividades de apoio à gestão de saúde</t>
-        </is>
-      </c>
-      <c r="F789" s="1" t="n">
-        <v>6628</v>
-      </c>
-      <c r="G789" s="1" t="inlineStr">
-        <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
-        </is>
-      </c>
-      <c r="H789" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
-      <c r="I789" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J789" s="2" t="n">
-        <v>46258.70282021991</v>
-      </c>
-      <c r="K789" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="L789" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M789" s="1" t="inlineStr">
-        <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N789" s="2" t="n">
-        <v>46261.63173943287</v>
-      </c>
-      <c r="O789" s="1" t="n"/>
-      <c r="P789" s="1" t="n"/>
-      <c r="Q789" s="1" t="inlineStr"/>
-      <c r="R789" s="1" t="inlineStr">
         <is>
           <t>Prezados(as), boa tarde!
 Conforme solicitado, alteração contratual em andamento. 
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S789" s="1" t="inlineStr">
+      <c r="S788" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T789" s="1" t="n"/>
-      <c r="U789" s="1" t="inlineStr"/>
-    </row>
-    <row r="790">
-      <c r="A790" s="1" t="n">
+      <c r="T788" s="1" t="n"/>
+      <c r="U788" s="1" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
         <v>84101</v>
       </c>
-      <c r="B790" s="1" t="inlineStr">
+      <c r="B789" s="1" t="inlineStr">
         <is>
           <t>Parcelamento PGFN</t>
         </is>
       </c>
-      <c r="C790" s="1" t="inlineStr">
+      <c r="C789" s="1" t="inlineStr">
         <is>
           <t>Simples Nacional</t>
         </is>
       </c>
-      <c r="D790" s="1" t="inlineStr">
+      <c r="D789" s="1" t="inlineStr">
         <is>
           <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="E790" s="1" t="inlineStr">
+      <c r="E789" s="1" t="inlineStr">
         <is>
           <t>Bom dia! Por gentileza, poderiam emitir uma guia atualizada</t>
         </is>
       </c>
-      <c r="F790" s="1" t="n">
+      <c r="F789" s="1" t="n">
         <v>6650</v>
       </c>
-      <c r="G790" s="1" t="inlineStr">
+      <c r="G789" s="1" t="inlineStr">
         <is>
           <t>ACJ COMERCIO DE EMBALAGENS LTDA</t>
         </is>
       </c>
-      <c r="H790" s="1" t="inlineStr">
+      <c r="H789" s="1" t="inlineStr">
         <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="I790" s="1" t="inlineStr">
+      <c r="I789" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J790" s="2" t="n">
+      <c r="J789" s="2" t="n">
         <v>46282.47985864583</v>
       </c>
-      <c r="K790" s="2" t="n">
+      <c r="K789" s="2" t="n">
         <v>46286</v>
       </c>
-      <c r="L790" s="1" t="inlineStr">
+      <c r="L789" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M790" s="1" t="inlineStr">
+      <c r="M789" s="1" t="inlineStr">
         <is>
           <t>Sofia Souza</t>
         </is>
       </c>
-      <c r="N790" s="1" t="n"/>
-      <c r="O790" s="1" t="n"/>
-      <c r="P790" s="2" t="n">
+      <c r="N789" s="1" t="n"/>
+      <c r="O789" s="1" t="n"/>
+      <c r="P789" s="2" t="n">
         <v>46288.46361616899</v>
       </c>
-      <c r="Q790" s="1" t="inlineStr">
+      <c r="Q789" s="1" t="inlineStr">
         <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="R790" s="1" t="inlineStr">
+      <c r="R789" s="1" t="inlineStr">
         <is>
           <t>Boa tarde!
 Qual parcela que voce deseja que seja emitida?
 Simples Nacional ou PGFN Simples Nacional?</t>
         </is>
       </c>
+      <c r="S789" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T789" s="1" t="n"/>
+      <c r="U789" s="1" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>83168</v>
+      </c>
+      <c r="B790" s="1" t="inlineStr">
+        <is>
+          <t>Alteração Contratual</t>
+        </is>
+      </c>
+      <c r="C790" s="1" t="inlineStr">
+        <is>
+          <t>Endereço</t>
+        </is>
+      </c>
+      <c r="D790" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA MASTER</t>
+        </is>
+      </c>
+      <c r="E790" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alteração de endereço da empresa 6704-TECNO COM INFORMATICA LTDAGrupo: Tecno ComE alteração do endereço do e-mail no cartão CNPJ para contato@tecnocombrasil.com.br </t>
+        </is>
+      </c>
+      <c r="F790" s="1" t="n">
+        <v>6704</v>
+      </c>
+      <c r="G790" s="1" t="inlineStr">
+        <is>
+          <t>TECNO COM INFORMATICA LTDA</t>
+        </is>
+      </c>
+      <c r="H790" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Ribeiro</t>
+        </is>
+      </c>
+      <c r="I790" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J790" s="2" t="n">
+        <v>46262.37490482639</v>
+      </c>
+      <c r="K790" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="L790" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M790" s="1" t="inlineStr">
+        <is>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N790" s="2" t="n">
+        <v>46266.48691802083</v>
+      </c>
+      <c r="O790" s="1" t="n"/>
+      <c r="P790" s="1" t="n"/>
+      <c r="Q790" s="1" t="inlineStr"/>
+      <c r="R790" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prezados(as), bom dia!
+Para ciência, alteração contratual em andamento conforme solicitado.
+Atenciosamente, </t>
+        </is>
+      </c>
       <c r="S790" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T790" s="1" t="n"/>
@@ -60554,7 +60648,7 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>83168</v>
+        <v>82821</v>
       </c>
       <c r="B791" s="1" t="inlineStr">
         <is>
@@ -60563,7 +60657,7 @@
       </c>
       <c r="C791" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Outras Cláusulas</t>
         </is>
       </c>
       <c r="D791" s="1" t="inlineStr">
@@ -60573,20 +60667,20 @@
       </c>
       <c r="E791" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração de endereço da empresa 6704-TECNO COM INFORMATICA LTDAGrupo: Tecno ComE alteração do endereço do e-mail no cartão CNPJ para contato@tecnocombrasil.com.br </t>
+          <t>Alteração contratual do CNAE da empresa: 6767-ALCANTARA LOGÍSTICA E TRANSPORTE LTDAGrupo: TW ALCANTARAProposta já negociada no valor de: R$ 2.500,00Incluir CNAE - 4712-1/00 COMO PRINCIPAL e o atual como secundário</t>
         </is>
       </c>
       <c r="F791" s="1" t="n">
-        <v>6704</v>
+        <v>6767</v>
       </c>
       <c r="G791" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>ALCANTARA LOGÍSTICA E TRANSPORTE LTDA</t>
         </is>
       </c>
       <c r="H791" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I791" s="1" t="inlineStr">
@@ -60595,10 +60689,10 @@
         </is>
       </c>
       <c r="J791" s="2" t="n">
-        <v>46262.37490482639</v>
+        <v>46255.68806971065</v>
       </c>
       <c r="K791" s="2" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="L791" s="1" t="inlineStr">
         <is>
@@ -60611,16 +60705,14 @@
         </is>
       </c>
       <c r="N791" s="2" t="n">
-        <v>46266.48691802083</v>
+        <v>46260.66751527778</v>
       </c>
       <c r="O791" s="1" t="n"/>
       <c r="P791" s="1" t="n"/>
       <c r="Q791" s="1" t="inlineStr"/>
       <c r="R791" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados(as), bom dia!
-Para ciência, alteração contratual em andamento conforme solicitado.
-Atenciosamente, </t>
+          <t xml:space="preserve">Processo em elaboração </t>
         </is>
       </c>
       <c r="S791" s="1" t="inlineStr">
@@ -60633,73 +60725,63 @@
     </row>
     <row r="792">
       <c r="A792" s="1" t="n">
-        <v>82821</v>
+        <v>84393</v>
       </c>
       <c r="B792" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Parcelamento RFB</t>
         </is>
       </c>
       <c r="C792" s="1" t="inlineStr">
         <is>
-          <t>Outras Cláusulas</t>
+          <t>Simples Nacional</t>
         </is>
       </c>
       <c r="D792" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E792" s="1" t="inlineStr">
         <is>
-          <t>Alteração contratual do CNAE da empresa: 6767-ALCANTARA LOGÍSTICA E TRANSPORTE LTDAGrupo: TW ALCANTARAProposta já negociada no valor de: R$ 2.500,00Incluir CNAE - 4712-1/00 COMO PRINCIPAL e o atual como secundário</t>
+          <t>Por gentileza, dar seguimento ao parcelamento da empresa Cabo Frio no simples nacional. Aprovação do parcelamento pelo cliente anexa</t>
         </is>
       </c>
       <c r="F792" s="1" t="n">
-        <v>6767</v>
+        <v>6774</v>
       </c>
       <c r="G792" s="1" t="inlineStr">
         <is>
-          <t>ALCANTARA LOGÍSTICA E TRANSPORTE LTDA</t>
-        </is>
-      </c>
-      <c r="H792" s="1" t="inlineStr">
-        <is>
-          <t>Thifany Leite</t>
-        </is>
-      </c>
+          <t>CABO FRIO PEÇAS LTDA</t>
+        </is>
+      </c>
+      <c r="H792" s="1" t="n"/>
       <c r="I792" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J792" s="2" t="n">
-        <v>46255.68806971065</v>
+        <v>46288.66527260416</v>
       </c>
       <c r="K792" s="2" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="L792" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M792" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N792" s="2" t="n">
-        <v>46260.66751527778</v>
-      </c>
+          <t>Rogerio Egidio</t>
+        </is>
+      </c>
+      <c r="N792" s="1" t="n"/>
       <c r="O792" s="1" t="n"/>
       <c r="P792" s="1" t="n"/>
       <c r="Q792" s="1" t="inlineStr"/>
-      <c r="R792" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Processo em elaboração </t>
-        </is>
-      </c>
+      <c r="R792" s="1" t="n"/>
       <c r="S792" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -10135,16 +10135,16 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>84337</v>
+        <v>83101</v>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza verificar resultado de 2025, DRE do período com resultado de R$ 58.181,84 e Balanço R$58.163,88</t>
+          <t xml:space="preserve">Bom dia, por gentileza verificar a pendência e encaminhar ao cliente. </t>
         </is>
       </c>
       <c r="F117" s="1" t="n">
@@ -10167,23 +10167,23 @@
       </c>
       <c r="H117" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>46287.7431491088</v>
+        <v>46261.41588966435</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>46288</v>
+        <v>46265</v>
       </c>
       <c r="L117" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M117" s="1" t="inlineStr">
@@ -10191,35 +10191,45 @@
           <t>Beatriz Rangel</t>
         </is>
       </c>
-      <c r="N117" s="1" t="n"/>
-      <c r="O117" s="1" t="n"/>
-      <c r="P117" s="1" t="n"/>
-      <c r="Q117" s="1" t="inlineStr"/>
-      <c r="R117" s="1" t="inlineStr"/>
+      <c r="N117" s="2" t="n">
+        <v>46261.6168647801</v>
+      </c>
+      <c r="O117" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="P117" s="2" t="n">
+        <v>46266.68528174768</v>
+      </c>
+      <c r="Q117" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
+      <c r="R117" s="1" t="inlineStr">
+        <is>
+          <t>em analise</t>
+        </is>
+      </c>
       <c r="S117" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T117" s="1" t="n"/>
-      <c r="U117" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+      <c r="U117" s="1" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>83101</v>
+        <v>83532</v>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
@@ -10229,7 +10239,7 @@
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, por gentileza verificar a pendência e encaminhar ao cliente. </t>
+          <t>Bom dia, por gentileza anexar balanço e dre 2025 e 2026 separados. das empresas 5053 RJR 5054 DINIZ5873 FRRD 6450 RDF</t>
         </is>
       </c>
       <c r="F118" s="1" t="n">
@@ -10242,19 +10252,19 @@
       </c>
       <c r="H118" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46261.41588966435</v>
+        <v>46268.36181149306</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="L118" s="1" t="inlineStr">
         <is>
@@ -10266,23 +10276,21 @@
           <t>Beatriz Rangel</t>
         </is>
       </c>
-      <c r="N118" s="2" t="n">
-        <v>46261.6168647801</v>
-      </c>
+      <c r="N118" s="1" t="n"/>
       <c r="O118" s="2" t="n">
-        <v>46266</v>
+        <v>46290</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>46266.68528174768</v>
+        <v>46287.75748996528</v>
       </c>
       <c r="Q118" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>em analise</t>
+          <t>em anexo</t>
         </is>
       </c>
       <c r="S118" s="1" t="inlineStr">
@@ -10291,20 +10299,24 @@
         </is>
       </c>
       <c r="T118" s="1" t="n"/>
-      <c r="U118" s="1" t="inlineStr"/>
+      <c r="U118" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>83532</v>
+        <v>81712</v>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
@@ -10314,32 +10326,32 @@
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza anexar balanço e dre 2025 e 2026 separados. das empresas 5053 RJR 5054 DINIZ5873 FRRD 6450 RDF</t>
+          <t>Prezados,Por gentileza, providenciar regularização do transporte de saldo credor incorreto ICMS período 08, 11 e 12/2025.Grato,Bruno.</t>
         </is>
       </c>
       <c r="F119" s="1" t="n">
-        <v>5053</v>
+        <v>5100</v>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>RJR INDUSTRIA DE ALIMENTOS LTDA</t>
+          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
         </is>
       </c>
       <c r="H119" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46268.36181149306</v>
+        <v>46234.60319799768</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>46269</v>
+        <v>46241</v>
       </c>
       <c r="L119" s="1" t="inlineStr">
         <is>
@@ -10348,115 +10360,115 @@
       </c>
       <c r="M119" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N119" s="1" t="n"/>
       <c r="O119" s="2" t="n">
-        <v>46290</v>
+        <v>46241</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>46287.75748996528</v>
+        <v>46241.67638564815</v>
       </c>
       <c r="Q119" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="R119" s="1" t="inlineStr">
-        <is>
-          <t>em anexo</t>
-        </is>
-      </c>
-      <c r="S119" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T119" s="1" t="n"/>
-      <c r="U119" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>81712</v>
-      </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>Saldo Credor Incorreto</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>Saldo Credor Incorreto</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>Prezados,Por gentileza, providenciar regularização do transporte de saldo credor incorreto ICMS período 08, 11 e 12/2025.Grato,Bruno.</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="n">
-        <v>5100</v>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>46234.60319799768</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>46241</v>
-      </c>
-      <c r="L120" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M120" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N120" s="1" t="n"/>
-      <c r="O120" s="2" t="n">
-        <v>46241</v>
-      </c>
-      <c r="P120" s="2" t="n">
-        <v>46241.67638564815</v>
-      </c>
-      <c r="Q120" s="1" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
-      <c r="R120" s="1" t="inlineStr">
         <is>
           <t>Boa tarde,
 O saldo credor deste período refere-se aos meses de 01 a 07/2025, nos quais o cliente não enviou os arquivos SPED ou os encaminhou com inconsistências.Não recebemos o retorno e a montagem não estava autorizada.
 Para regularizar essa pendência, solicitamos, por gentileza, que sejam solicitados ao cliente os arquivos SPED corrigidos referentes ao período de 01 a 07/2025.</t>
         </is>
       </c>
+      <c r="S119" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T119" s="1" t="n"/>
+      <c r="U119" s="1" t="inlineStr">
+        <is>
+          <t>Thaiza Oliveira</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>79665</v>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>Autorregularização</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>Autorregularização</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>Autoregularização - Simples Nacional - Janeiro a Dezembro 2024Cliente recebeu notificação de autoregularização do Simples Nacional referente período 2024. Por gentileza, providenciar retificação dentro do prazo estipulado pela Receita.</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>Thaiza Oliveira</t>
+        </is>
+      </c>
+      <c r="I120" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>46176.49184155092</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="L120" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M120" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>46183.62114679398</v>
+      </c>
+      <c r="O120" s="1" t="n"/>
+      <c r="P120" s="2" t="n">
+        <v>46211.66080744213</v>
+      </c>
+      <c r="Q120" s="1" t="inlineStr">
+        <is>
+          <t>Thaiza Oliveira</t>
+        </is>
+      </c>
+      <c r="R120" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando definição gerencia departamento e gerencia operacional</t>
+        </is>
+      </c>
       <c r="S120" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -10471,51 +10483,51 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>79665</v>
+        <v>79930</v>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>Autoregularização - Simples Nacional - Janeiro a Dezembro 2024Cliente recebeu notificação de autoregularização do Simples Nacional referente período 2024. Por gentileza, providenciar retificação dentro do prazo estipulado pela Receita.</t>
+          <t>Por gentileza, poderiam providenciar Última declaração do IRPJ entregue do cliente CEREALISTA</t>
         </is>
       </c>
       <c r="F121" s="1" t="n">
-        <v>5100</v>
+        <v>5101</v>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
+          <t>CEREALISTA IDEAL DE SÃO CAETANO LTDA</t>
         </is>
       </c>
       <c r="H121" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46176.49184155092</v>
+        <v>46184.70223510417</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>46199</v>
+        <v>46185</v>
       </c>
       <c r="L121" s="1" t="inlineStr">
         <is>
@@ -10524,24 +10536,22 @@
       </c>
       <c r="M121" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>46183.62114679398</v>
-      </c>
+          <t>Leticia Queiroz</t>
+        </is>
+      </c>
+      <c r="N121" s="1" t="n"/>
       <c r="O121" s="1" t="n"/>
       <c r="P121" s="2" t="n">
-        <v>46211.66080744213</v>
+        <v>46192.46905616898</v>
       </c>
       <c r="Q121" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>Aguardando definição gerencia departamento e gerencia operacional</t>
+          <t xml:space="preserve">Bom dia, não entendi, favor ser mais e especifica, seria memoria de cálculo ou alguma obrigação acessória como Sped????? </t>
         </is>
       </c>
       <c r="S121" s="1" t="inlineStr">
@@ -10552,57 +10562,57 @@
       <c r="T121" s="1" t="n"/>
       <c r="U121" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>79930</v>
+        <v>81857</v>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderiam providenciar Última declaração do IRPJ entregue do cliente CEREALISTA</t>
+          <t xml:space="preserve">Por gentileza, emitir a guia do DIFAL referente a  Notificação de Pendência Fiscal - ICMS DIFCON - Sefaz MS - CNPJ: 02.905.133/0001-32 -CABEXPRESS e enviar para cliente pagar copiando toda equipe da CABEX e o Sr. Reginaldo 'Reginaldo J Chagas' &lt;reginaldo@adviserempresarial.com.br&gt; </t>
         </is>
       </c>
       <c r="F122" s="1" t="n">
-        <v>5101</v>
+        <v>5132</v>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>CEREALISTA IDEAL DE SÃO CAETANO LTDA</t>
+          <t>CABEXPRESS INDUSTRIA E COMÉRCIO DE CABOS ELÉTRICOS LTDA</t>
         </is>
       </c>
       <c r="H122" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>46184.70223510417</v>
+        <v>46238.64146678241</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>46185</v>
+        <v>46240</v>
       </c>
       <c r="L122" s="1" t="inlineStr">
         <is>
@@ -10611,22 +10621,24 @@
       </c>
       <c r="M122" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N122" s="1" t="n"/>
-      <c r="O122" s="1" t="n"/>
+      <c r="O122" s="2" t="n">
+        <v>46241</v>
+      </c>
       <c r="P122" s="2" t="n">
-        <v>46192.46905616898</v>
+        <v>46238.74667160879</v>
       </c>
       <c r="Q122" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, não entendi, favor ser mais e especifica, seria memoria de cálculo ou alguma obrigação acessória como Sped????? </t>
+          <t>Recalculo DIFAL enviado ao cliente no e-mail na data de hoje</t>
         </is>
       </c>
       <c r="S122" s="1" t="inlineStr">
@@ -10637,100 +10649,96 @@
       <c r="T122" s="1" t="n"/>
       <c r="U122" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>81857</v>
+        <v>82046</v>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, emitir a guia do DIFAL referente a  Notificação de Pendência Fiscal - ICMS DIFCON - Sefaz MS - CNPJ: 02.905.133/0001-32 -CABEXPRESS e enviar para cliente pagar copiando toda equipe da CABEX e o Sr. Reginaldo 'Reginaldo J Chagas' &lt;reginaldo@adviserempresarial.com.br&gt; </t>
+          <t>Por favor verificar - Transporte de saldo credor incorreto EFD 05, 09, 10, 11 e 12/2024. Não veio no material de reunião, por favor verificar esta pendência!</t>
         </is>
       </c>
       <c r="F123" s="1" t="n">
-        <v>5132</v>
+        <v>5142</v>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>CABEXPRESS INDUSTRIA E COMÉRCIO DE CABOS ELÉTRICOS LTDA</t>
+          <t>MERCADO, PADARIA ACOUGUE E RESTAURANTE OLIMPIA LTDA</t>
         </is>
       </c>
       <c r="H123" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>46238.64146678241</v>
+        <v>46241.44565771991</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="L123" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M123" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
-        </is>
-      </c>
-      <c r="N123" s="1" t="n"/>
+          <t>Rodrigo Rego</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>46245.74680853009</v>
+      </c>
       <c r="O123" s="2" t="n">
-        <v>46241</v>
-      </c>
-      <c r="P123" s="2" t="n">
-        <v>46238.74667160879</v>
-      </c>
-      <c r="Q123" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+        <v>46288</v>
+      </c>
+      <c r="P123" s="1" t="n"/>
+      <c r="Q123" s="1" t="inlineStr"/>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>Recalculo DIFAL enviado ao cliente no e-mail na data de hoje</t>
+          <t xml:space="preserve">VERIFICANDO </t>
         </is>
       </c>
       <c r="S123" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T123" s="1" t="n"/>
       <c r="U123" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>82046</v>
+        <v>82044</v>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
@@ -10749,36 +10757,36 @@
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>Por favor verificar - Transporte de saldo credor incorreto EFD 05, 09, 10, 11 e 12/2024. Não veio no material de reunião, por favor verificar esta pendência!</t>
+          <t>"Empresa iniciou recebimentos de aluguel no mês 02/2026.Por gentileza, verificar nos extratos da empresa os recebimentos para fins de fechamento fiscal mensal (PIS/ COFINS) e fechamentos trimestrais (IRPJ/ CSLL).Por gentileza revisar os extratos da empresa para confirmação de não movimentação, visto que a empresa está realizando locações, como acima apontado. Por favor me retornar com a conclusão."</t>
         </is>
       </c>
       <c r="F124" s="1" t="n">
-        <v>5142</v>
+        <v>5145</v>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>MERCADO, PADARIA ACOUGUE E RESTAURANTE OLIMPIA LTDA</t>
+          <t>JK BURITI CAFETERIA E CONVENIENCIAS LTDA</t>
         </is>
       </c>
       <c r="H124" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>46241.44565771991</v>
+        <v>46241.43949221065</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="L124" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M124" s="1" t="inlineStr">
@@ -10786,43 +10794,48 @@
           <t>Rodrigo Rego</t>
         </is>
       </c>
-      <c r="N124" s="2" t="n">
-        <v>46245.74680853009</v>
-      </c>
+      <c r="N124" s="1" t="n"/>
       <c r="O124" s="2" t="n">
-        <v>46288</v>
-      </c>
-      <c r="P124" s="1" t="n"/>
-      <c r="Q124" s="1" t="inlineStr"/>
+        <v>46245</v>
+      </c>
+      <c r="P124" s="2" t="n">
+        <v>46244.5917212963</v>
+      </c>
+      <c r="Q124" s="1" t="inlineStr">
+        <is>
+          <t>Lucas Fischer</t>
+        </is>
+      </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFICANDO </t>
+          <t>Não identificamos recebimentos de aluguel nessa empresa.
+Precisamos de mais informações para procurar. Qual o nome do favorecido? quais são os valores? Foi recebido em qual banco?</t>
         </is>
       </c>
       <c r="S124" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T124" s="1" t="n"/>
       <c r="U124" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>82044</v>
+        <v>81298</v>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
@@ -10832,7 +10845,7 @@
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>"Empresa iniciou recebimentos de aluguel no mês 02/2026.Por gentileza, verificar nos extratos da empresa os recebimentos para fins de fechamento fiscal mensal (PIS/ COFINS) e fechamentos trimestrais (IRPJ/ CSLL).Por gentileza revisar os extratos da empresa para confirmação de não movimentação, visto que a empresa está realizando locações, como acima apontado. Por favor me retornar com a conclusão."</t>
+          <t>Por favor verificar com urgencia se na epoca foi enviado o debito que a receita esta notificando conforme anexo e enviar o DAS com o valor atualizado</t>
         </is>
       </c>
       <c r="F125" s="1" t="n">
@@ -10845,19 +10858,19 @@
       </c>
       <c r="H125" s="1" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46241.43949221065</v>
+        <v>46225.48881790509</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>46248</v>
+        <v>46227</v>
       </c>
       <c r="L125" s="1" t="inlineStr">
         <is>
@@ -10869,22 +10882,23 @@
           <t>Rodrigo Rego</t>
         </is>
       </c>
-      <c r="N125" s="1" t="n"/>
+      <c r="N125" s="2" t="n">
+        <v>46230.71356496528</v>
+      </c>
       <c r="O125" s="2" t="n">
-        <v>46245</v>
+        <v>46285</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>46244.5917212963</v>
+        <v>46287.75830049768</v>
       </c>
       <c r="Q125" s="1" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>Não identificamos recebimentos de aluguel nessa empresa.
-Precisamos de mais informações para procurar. Qual o nome do favorecido? quais são os valores? Foi recebido em qual banco?</t>
+          <t>verificando</t>
         </is>
       </c>
       <c r="S125" s="1" t="inlineStr">
@@ -10895,57 +10909,57 @@
       <c r="T125" s="1" t="n"/>
       <c r="U125" s="1" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>81298</v>
+        <v>79896</v>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>Por favor verificar com urgencia se na epoca foi enviado o debito que a receita esta notificando conforme anexo e enviar o DAS com o valor atualizado</t>
+          <t>Não estamos conseguindo dar continuidade ao assunto em cima do chamado 79551 -Favor emitir os DARFs de IRPJ e CSLL para atendimento ao Auto de Regularização da COXA -PRAZO PARA ATENDIMENTO 11.06.2026 (anexo). No e-mail (anexo) constam os valores originais dos débitos. O cliente está aguardando o os DARFs para efetuar o pagamento. Por gentileza, após a emissão, encaminhar os DARFs por e-mail  para gerencia de contas para que possamos enviá-los à Isadora, da COXA, visto que se trata de um ex-cliente e não será possível disponibilizar a documentação pelo SCI.  Solicitamos também que a ECF seja retificada ainda hoje,(11/06/2026), para que a Receita Federal tenha ciência de que o autorregularização foi atendido dentro do prazo estabelecido,(12/06/2026.)</t>
         </is>
       </c>
       <c r="F126" s="1" t="n">
-        <v>5145</v>
+        <v>5178</v>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>JK BURITI CAFETERIA E CONVENIENCIAS LTDA</t>
+          <t>COXA PARTICIPACOES S A</t>
         </is>
       </c>
       <c r="H126" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>46225.48881790509</v>
+        <v>46184.47763410879</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>46227</v>
+        <v>46188</v>
       </c>
       <c r="L126" s="1" t="inlineStr">
         <is>
@@ -10954,26 +10968,22 @@
       </c>
       <c r="M126" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
-        </is>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>46230.71356496528</v>
-      </c>
-      <c r="O126" s="2" t="n">
-        <v>46285</v>
-      </c>
+          <t>Simone Marques</t>
+        </is>
+      </c>
+      <c r="N126" s="1" t="n"/>
+      <c r="O126" s="1" t="n"/>
       <c r="P126" s="2" t="n">
-        <v>46287.75830049768</v>
+        <v>46240.68738668982</v>
       </c>
       <c r="Q126" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>verificando</t>
+          <t>DARFS e PERDCOMP CONCLUIDOS EM 15/06/2026 - ENVIADO POR E-MAIL</t>
         </is>
       </c>
       <c r="S126" s="1" t="inlineStr">
@@ -10984,22 +10994,22 @@
       <c r="T126" s="1" t="n"/>
       <c r="U126" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>79896</v>
+        <v>80417</v>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Reembolso</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Reembolso</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
@@ -11009,7 +11019,7 @@
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>Não estamos conseguindo dar continuidade ao assunto em cima do chamado 79551 -Favor emitir os DARFs de IRPJ e CSLL para atendimento ao Auto de Regularização da COXA -PRAZO PARA ATENDIMENTO 11.06.2026 (anexo). No e-mail (anexo) constam os valores originais dos débitos. O cliente está aguardando o os DARFs para efetuar o pagamento. Por gentileza, após a emissão, encaminhar os DARFs por e-mail  para gerencia de contas para que possamos enviá-los à Isadora, da COXA, visto que se trata de um ex-cliente e não será possível disponibilizar a documentação pelo SCI.  Solicitamos também que a ECF seja retificada ainda hoje,(11/06/2026), para que a Receita Federal tenha ciência de que o autorregularização foi atendido dentro do prazo estabelecido,(12/06/2026.)</t>
+          <t>O cliente está cobrando o reembolso no valor de R$ 15.748,98, referente aos juros e à multa dos DARFs pagos para atendimento da malha de débitos do 4º trimestre de 2023. Anexo comprovante de pagamento Dados bancários:Banco Itau (341)Ag: 8729CC: 99892-5CNPJ: 42.169.691/0001-00COXA PARTICIPAÇÕES S/A</t>
         </is>
       </c>
       <c r="F127" s="1" t="n">
@@ -11022,7 +11032,7 @@
       </c>
       <c r="H127" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I127" s="1" t="inlineStr">
@@ -11031,10 +11041,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>46184.47763410879</v>
+        <v>46195.6876917824</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>46188</v>
+        <v>46197</v>
       </c>
       <c r="L127" s="1" t="inlineStr">
         <is>
@@ -11049,16 +11059,17 @@
       <c r="N127" s="1" t="n"/>
       <c r="O127" s="1" t="n"/>
       <c r="P127" s="2" t="n">
-        <v>46240.68738668982</v>
+        <v>46204.40209097222</v>
       </c>
       <c r="Q127" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>DARFS e PERDCOMP CONCLUIDOS EM 15/06/2026 - ENVIADO POR E-MAIL</t>
+          <t>bom Dia, 
+Processo de reembolso realizado a entregue ao Andre Coelho no dia 01-07-2026</t>
         </is>
       </c>
       <c r="S127" s="1" t="inlineStr">
@@ -11067,24 +11078,20 @@
         </is>
       </c>
       <c r="T127" s="1" t="n"/>
-      <c r="U127" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="U127" s="1" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>80417</v>
+        <v>81016</v>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>Reembolso</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>Reembolso</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
@@ -11094,32 +11101,32 @@
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>O cliente está cobrando o reembolso no valor de R$ 15.748,98, referente aos juros e à multa dos DARFs pagos para atendimento da malha de débitos do 4º trimestre de 2023. Anexo comprovante de pagamento Dados bancários:Banco Itau (341)Ag: 8729CC: 99892-5CNPJ: 42.169.691/0001-00COXA PARTICIPAÇÕES S/A</t>
+          <t>Prezados, O cliente Marajoara disponibilizou novos arquivos no FTP correspondentes aos meses de abril, maio e junho 2026 para reapuração das entradas/ saídas do período.De acordo com o cliente, os arquivos speds enviados na época não estavam considerando todas as notas fiscais do período.</t>
         </is>
       </c>
       <c r="F128" s="1" t="n">
-        <v>5178</v>
+        <v>5253</v>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>COXA PARTICIPACOES S A</t>
+          <t>MARAJOARA II COMÉRCIO VAREJISTA DE CARNES, LANCHES E BEBIDAS LTDA</t>
         </is>
       </c>
       <c r="H128" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>46195.6876917824</v>
+        <v>46217.42263804398</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>46197</v>
+        <v>46224</v>
       </c>
       <c r="L128" s="1" t="inlineStr">
         <is>
@@ -11128,23 +11135,24 @@
       </c>
       <c r="M128" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N128" s="1" t="n"/>
-      <c r="O128" s="1" t="n"/>
+      <c r="O128" s="2" t="n">
+        <v>46233</v>
+      </c>
       <c r="P128" s="2" t="n">
-        <v>46204.40209097222</v>
+        <v>46234.38291929398</v>
       </c>
       <c r="Q128" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>bom Dia, 
-Processo de reembolso realizado a entregue ao Andre Coelho no dia 01-07-2026</t>
+          <t>Conforme conversamos precisamos de um novo SPED contendo as notas faltantes ou somente os XMLs faltantes.</t>
         </is>
       </c>
       <c r="S128" s="1" t="inlineStr">
@@ -11153,20 +11161,24 @@
         </is>
       </c>
       <c r="T128" s="1" t="n"/>
-      <c r="U128" s="1" t="inlineStr"/>
+      <c r="U128" s="1" t="inlineStr">
+        <is>
+          <t>Thaiza Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>81016</v>
+        <v>79674</v>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
@@ -11176,32 +11188,32 @@
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>Prezados, O cliente Marajoara disponibilizou novos arquivos no FTP correspondentes aos meses de abril, maio e junho 2026 para reapuração das entradas/ saídas do período.De acordo com o cliente, os arquivos speds enviados na época não estavam considerando todas as notas fiscais do período.</t>
+          <t>Favor retificar DCTF do período de MAIO/2025. Os valores de PIS e COFINS estão divergentes da apuração que consta no sistema de análise.</t>
         </is>
       </c>
       <c r="F129" s="1" t="n">
-        <v>5253</v>
+        <v>5331</v>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>MARAJOARA II COMÉRCIO VAREJISTA DE CARNES, LANCHES E BEBIDAS LTDA</t>
+          <t>PIRANA - AUTO SERVIÇO LTDA</t>
         </is>
       </c>
       <c r="H129" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>46217.42263804398</v>
+        <v>46176.62133761574</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>46224</v>
+        <v>46191</v>
       </c>
       <c r="L129" s="1" t="inlineStr">
         <is>
@@ -11214,20 +11226,18 @@
         </is>
       </c>
       <c r="N129" s="1" t="n"/>
-      <c r="O129" s="2" t="n">
-        <v>46233</v>
-      </c>
+      <c r="O129" s="1" t="n"/>
       <c r="P129" s="2" t="n">
-        <v>46234.38291929398</v>
+        <v>46181.60648179398</v>
       </c>
       <c r="Q129" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>Conforme conversamos precisamos de um novo SPED contendo as notas faltantes ou somente os XMLs faltantes.</t>
+          <t>Valores retificados na DCTFWEB em 08/06/2026.</t>
         </is>
       </c>
       <c r="S129" s="1" t="inlineStr">
@@ -11238,22 +11248,22 @@
       <c r="T129" s="1" t="n"/>
       <c r="U129" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Karina Fonseca</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>79674</v>
+        <v>79877</v>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
@@ -11263,7 +11273,7 @@
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>Favor retificar DCTF do período de MAIO/2025. Os valores de PIS e COFINS estão divergentes da apuração que consta no sistema de análise.</t>
+          <t>Por gentileza, providenciar regularização de transporte de saldo credor incorreto, conforme ocorrência no posto fiscal.</t>
         </is>
       </c>
       <c r="F130" s="1" t="n">
@@ -11276,23 +11286,23 @@
       </c>
       <c r="H130" s="1" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>46176.62133761574</v>
+        <v>46183.73675975695</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>46191</v>
+        <v>46199</v>
       </c>
       <c r="L130" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M130" s="1" t="inlineStr">
@@ -11300,45 +11310,43 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N130" s="1" t="n"/>
-      <c r="O130" s="1" t="n"/>
-      <c r="P130" s="2" t="n">
-        <v>46181.60648179398</v>
-      </c>
-      <c r="Q130" s="1" t="inlineStr">
-        <is>
-          <t>Danielle Silva</t>
-        </is>
-      </c>
+      <c r="N130" s="2" t="n">
+        <v>46189.6799341088</v>
+      </c>
+      <c r="O130" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="P130" s="1" t="n"/>
+      <c r="Q130" s="1" t="inlineStr"/>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>Valores retificados na DCTFWEB em 08/06/2026.</t>
+          <t>Verificando.</t>
         </is>
       </c>
       <c r="S130" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T130" s="1" t="n"/>
       <c r="U130" s="1" t="inlineStr">
         <is>
-          <t>Karina Fonseca</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>79877</v>
+        <v>82725</v>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>SPED</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>SPED</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
@@ -11348,7 +11356,7 @@
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar regularização de transporte de saldo credor incorreto, conforme ocorrência no posto fiscal.</t>
+          <t>Conforme autorização da diretoria, por gentileza, incluir crédito no valor de R$50.132,65 na apuração de julho 2026.Documento de aprovação anexo.</t>
         </is>
       </c>
       <c r="F131" s="1" t="n">
@@ -11370,14 +11378,14 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46183.73675975695</v>
+        <v>46254.44089421296</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>46199</v>
+        <v>46255</v>
       </c>
       <c r="L131" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M131" s="1" t="inlineStr">
@@ -11385,22 +11393,24 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N131" s="2" t="n">
-        <v>46189.6799341088</v>
-      </c>
-      <c r="O131" s="2" t="n">
-        <v>46287</v>
-      </c>
-      <c r="P131" s="1" t="n"/>
-      <c r="Q131" s="1" t="inlineStr"/>
+      <c r="N131" s="1" t="n"/>
+      <c r="O131" s="1" t="n"/>
+      <c r="P131" s="2" t="n">
+        <v>46254.68301747685</v>
+      </c>
+      <c r="Q131" s="1" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>Verificando.</t>
+          <t>Credito lançado,  novo imposto publicado!</t>
         </is>
       </c>
       <c r="S131" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T131" s="1" t="n"/>
@@ -11412,16 +11422,16 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>82725</v>
+        <v>80737</v>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>SPED</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>SPED</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
@@ -11431,20 +11441,20 @@
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>Conforme autorização da diretoria, por gentileza, incluir crédito no valor de R$50.132,65 na apuração de julho 2026.Documento de aprovação anexo.</t>
+          <t>Prezados,Cliente 5350-Akafer Materiais Elétricos recebeu Auto de regularização referente GIA/EFD dos períodos 07/2024 a 12/2024 totalizando R$126.900,69.Por gentileza, providenciar regularização dentro do prazo estipulado que encerra-se em 31/07/2026.</t>
         </is>
       </c>
       <c r="F132" s="1" t="n">
-        <v>5331</v>
+        <v>5350</v>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>PIRANA - AUTO SERVIÇO LTDA</t>
+          <t>AKAFER MATERIAIS ELETRICOS LTDA</t>
         </is>
       </c>
       <c r="H132" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I132" s="1" t="inlineStr">
@@ -11453,10 +11463,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>46254.44089421296</v>
+        <v>46206.7217474537</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>46255</v>
+        <v>46213</v>
       </c>
       <c r="L132" s="1" t="inlineStr">
         <is>
@@ -11471,16 +11481,17 @@
       <c r="N132" s="1" t="n"/>
       <c r="O132" s="1" t="n"/>
       <c r="P132" s="2" t="n">
-        <v>46254.68301747685</v>
+        <v>46209.50008553241</v>
       </c>
       <c r="Q132" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>Credito lançado,  novo imposto publicado!</t>
+          <t>Bom dia,
+Empresa pertence ao MG express, por gentileza direcionar ao Romero/ Helmer.</t>
         </is>
       </c>
       <c r="S132" s="1" t="inlineStr">
@@ -11489,24 +11500,20 @@
         </is>
       </c>
       <c r="T132" s="1" t="n"/>
-      <c r="U132" s="1" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
+      <c r="U132" s="1" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>80737</v>
+        <v>81703</v>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
@@ -11516,32 +11523,32 @@
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Cliente 5350-Akafer Materiais Elétricos recebeu Auto de regularização referente GIA/EFD dos períodos 07/2024 a 12/2024 totalizando R$126.900,69.Por gentileza, providenciar regularização dentro do prazo estipulado que encerra-se em 31/07/2026.</t>
+          <t>Bom dia, Por gentileza verificar mensagem recebida em nossa caixa referente a omissão, inconsistência ou omissão na Escritura fiscal Digital (EFD) ou em uma Dapi de período anterior.</t>
         </is>
       </c>
       <c r="F133" s="1" t="n">
-        <v>5350</v>
+        <v>5442</v>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>AKAFER MATERIAIS ELETRICOS LTDA</t>
+          <t>G13 IMPORTACAO E EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="H133" s="1" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46206.7217474537</v>
+        <v>46234.47681732639</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>46213</v>
+        <v>46237</v>
       </c>
       <c r="L133" s="1" t="inlineStr">
         <is>
@@ -11550,23 +11557,26 @@
       </c>
       <c r="M133" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N133" s="1" t="n"/>
-      <c r="O133" s="1" t="n"/>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>46238.74622743056</v>
+      </c>
+      <c r="O133" s="2" t="n">
+        <v>46255</v>
+      </c>
       <c r="P133" s="2" t="n">
-        <v>46209.50008553241</v>
+        <v>46286.59377850695</v>
       </c>
       <c r="Q133" s="1" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,
-Empresa pertence ao MG express, por gentileza direcionar ao Romero/ Helmer.</t>
+          <t>Analisando</t>
         </is>
       </c>
       <c r="S133" s="1" t="inlineStr">
@@ -11575,20 +11585,24 @@
         </is>
       </c>
       <c r="T133" s="1" t="n"/>
-      <c r="U133" s="1" t="inlineStr"/>
+      <c r="U133" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>81703</v>
+        <v>82955</v>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
@@ -11598,7 +11612,7 @@
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, Por gentileza verificar mensagem recebida em nossa caixa referente a omissão, inconsistência ou omissão na Escritura fiscal Digital (EFD) ou em uma Dapi de período anterior.</t>
+          <t>Bom dia, por gentileza verificar omissão de DAPI</t>
         </is>
       </c>
       <c r="F134" s="1" t="n">
@@ -11611,7 +11625,7 @@
       </c>
       <c r="H134" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I134" s="1" t="inlineStr">
@@ -11620,10 +11634,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46234.47681732639</v>
+        <v>46259.46279479167</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>46237</v>
+        <v>46261</v>
       </c>
       <c r="L134" s="1" t="inlineStr">
         <is>
@@ -11636,22 +11650,22 @@
         </is>
       </c>
       <c r="N134" s="2" t="n">
-        <v>46238.74622743056</v>
+        <v>46260.75763707176</v>
       </c>
       <c r="O134" s="2" t="n">
-        <v>46255</v>
+        <v>46269</v>
       </c>
       <c r="P134" s="2" t="n">
-        <v>46286.59377850695</v>
+        <v>46269.47718869213</v>
       </c>
       <c r="Q134" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>Analisando</t>
+          <t>operação realizando atendimento</t>
         </is>
       </c>
       <c r="S134" s="1" t="inlineStr">
@@ -11660,24 +11674,20 @@
         </is>
       </c>
       <c r="T134" s="1" t="n"/>
-      <c r="U134" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="U134" s="1" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>82955</v>
+        <v>84145</v>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
@@ -11687,32 +11697,32 @@
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza verificar omissão de DAPI</t>
+          <t>Bom dia, por gentileza encaminhar a documentação abaixo:  1. Balancetes mensais do ano corrente (janeiro até o último mês fechado);2. Relatório de receitas e despesas (DRE ou planilha equivalente) dos últimos 12</t>
         </is>
       </c>
       <c r="F135" s="1" t="n">
-        <v>5442</v>
+        <v>5472</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>G13 IMPORTACAO E EXPORTACAO LTDA</t>
+          <t>T C DE CASTRO EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46259.46279479167</v>
+        <v>46283.40513741898</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>46261</v>
+        <v>46286</v>
       </c>
       <c r="L135" s="1" t="inlineStr">
         <is>
@@ -11725,22 +11735,22 @@
         </is>
       </c>
       <c r="N135" s="2" t="n">
-        <v>46260.75763707176</v>
+        <v>46286.65661658565</v>
       </c>
       <c r="O135" s="2" t="n">
-        <v>46269</v>
+        <v>46287</v>
       </c>
       <c r="P135" s="2" t="n">
-        <v>46269.47718869213</v>
+        <v>46287.75436478009</v>
       </c>
       <c r="Q135" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>operação realizando atendimento</t>
+          <t>Boa tarde, Segue documentação solicitada.</t>
         </is>
       </c>
       <c r="S135" s="1" t="inlineStr">
@@ -11749,20 +11759,24 @@
         </is>
       </c>
       <c r="T135" s="1" t="n"/>
-      <c r="U135" s="1" t="inlineStr"/>
+      <c r="U135" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>84145</v>
+        <v>80685</v>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
@@ -11772,36 +11786,36 @@
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza encaminhar a documentação abaixo:  1. Balancetes mensais do ano corrente (janeiro até o último mês fechado);2. Relatório de receitas e despesas (DRE ou planilha equivalente) dos últimos 12</t>
+          <t>Boa tarde, por gentileza verificar mensagem recebida em nossa caixa referente o Sistema de conformidade. ATENÇÃO: A autorregularização deve ser feita até 14/08/2026. Após essa data, o contribuinte está sujeito à abertura de operação fiscal para apuração e constituição de eventuais créditos tributários relacionados.</t>
         </is>
       </c>
       <c r="F136" s="1" t="n">
-        <v>5472</v>
+        <v>5587</v>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>T C DE CASTRO EMPREENDIMENTOS LTDA</t>
+          <t>DALMEC SISTEMAS DE PONTO E ACESSO LTDA</t>
         </is>
       </c>
       <c r="H136" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46283.40513741898</v>
+        <v>46204.62099849537</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>46286</v>
+        <v>46206</v>
       </c>
       <c r="L136" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M136" s="1" t="inlineStr">
@@ -11809,40 +11823,33 @@
           <t>Beatriz Rangel</t>
         </is>
       </c>
-      <c r="N136" s="2" t="n">
-        <v>46286.65661658565</v>
-      </c>
+      <c r="N136" s="1" t="n"/>
       <c r="O136" s="2" t="n">
-        <v>46287</v>
-      </c>
-      <c r="P136" s="2" t="n">
-        <v>46287.75436478009</v>
-      </c>
-      <c r="Q136" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+        <v>46233</v>
+      </c>
+      <c r="P136" s="1" t="n"/>
+      <c r="Q136" s="1" t="inlineStr"/>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Segue documentação solicitada.</t>
+          <t>TAREFA SENDO EXECUTADA PELA OPERAÇÃO, 
+PRAZO 31/07</t>
         </is>
       </c>
       <c r="S136" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T136" s="1" t="n"/>
-      <c r="U136" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T136" s="1" t="inlineStr">
+        <is>
+          <t>EF - INDUSTRIA</t>
+        </is>
+      </c>
+      <c r="U136" s="1" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>80685</v>
+        <v>79664</v>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
@@ -11861,79 +11868,84 @@
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza verificar mensagem recebida em nossa caixa referente o Sistema de conformidade. ATENÇÃO: A autorregularização deve ser feita até 14/08/2026. Após essa data, o contribuinte está sujeito à abertura de operação fiscal para apuração e constituição de eventuais créditos tributários relacionados.</t>
+          <t>Autoregularização  Simples Nacional - Janeiro a Dezembro 2024.Cliente recebeu notificação de auto regularização referente período mencionado acima. Por gentileza, providenciar dentro do prazo estipulado pela Receita.</t>
         </is>
       </c>
       <c r="F137" s="1" t="n">
-        <v>5587</v>
+        <v>5595</v>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>DALMEC SISTEMAS DE PONTO E ACESSO LTDA</t>
+          <t>SUPERMERCADO QUEIROZ LTDA</t>
         </is>
       </c>
       <c r="H137" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46204.62099849537</v>
+        <v>46176.46938182871</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>46206</v>
+        <v>46199</v>
       </c>
       <c r="L137" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M137" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
-      <c r="N137" s="1" t="n"/>
-      <c r="O137" s="2" t="n">
-        <v>46233</v>
-      </c>
-      <c r="P137" s="1" t="n"/>
-      <c r="Q137" s="1" t="inlineStr"/>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>46183.62132037037</v>
+      </c>
+      <c r="O137" s="1" t="n"/>
+      <c r="P137" s="2" t="n">
+        <v>46210.54752037037</v>
+      </c>
+      <c r="Q137" s="1" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>TAREFA SENDO EXECUTADA PELA OPERAÇÃO, 
-PRAZO 31/07</t>
+          <t>Aguardando definição gerencia departamento e gerencia operacional</t>
         </is>
       </c>
       <c r="S137" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T137" s="1" t="inlineStr">
-        <is>
-          <t>EF - INDUSTRIA</t>
-        </is>
-      </c>
-      <c r="U137" s="1" t="inlineStr"/>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T137" s="1" t="n"/>
+      <c r="U137" s="1" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>79664</v>
+        <v>79916</v>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
@@ -11943,7 +11955,7 @@
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>Autoregularização  Simples Nacional - Janeiro a Dezembro 2024.Cliente recebeu notificação de auto regularização referente período mencionado acima. Por gentileza, providenciar dentro do prazo estipulado pela Receita.</t>
+          <t>Verificar Omissão de DCTF (Período de Apuração) 2024 - OUT NOV DEZ</t>
         </is>
       </c>
       <c r="F138" s="1" t="n">
@@ -11956,7 +11968,7 @@
       </c>
       <c r="H138" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I138" s="1" t="inlineStr">
@@ -11965,10 +11977,10 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46176.46938182871</v>
+        <v>46184.59114753472</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>46199</v>
+        <v>46192</v>
       </c>
       <c r="L138" s="1" t="inlineStr">
         <is>
@@ -11980,21 +11992,19 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N138" s="2" t="n">
-        <v>46183.62132037037</v>
-      </c>
+      <c r="N138" s="1" t="n"/>
       <c r="O138" s="1" t="n"/>
       <c r="P138" s="2" t="n">
-        <v>46210.54752037037</v>
+        <v>46191.43697144676</v>
       </c>
       <c r="Q138" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>Aguardando definição gerencia departamento e gerencia operacional</t>
+          <t>Por favor, verificar com o contabil.</t>
         </is>
       </c>
       <c r="S138" s="1" t="inlineStr">
@@ -12005,22 +12015,22 @@
       <c r="T138" s="1" t="n"/>
       <c r="U138" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>79916</v>
+        <v>83300</v>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
@@ -12030,7 +12040,7 @@
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>Verificar Omissão de DCTF (Período de Apuração) 2024 - OUT NOV DEZ</t>
+          <t>Por gentileza, providenciar regularização de transporte de saldo credor incorreto 08 e 09/2025 conforme situação do contribuinte anexo.</t>
         </is>
       </c>
       <c r="F139" s="1" t="n">
@@ -12043,7 +12053,7 @@
       </c>
       <c r="H139" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I139" s="1" t="inlineStr">
@@ -12052,10 +12062,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46184.59114753472</v>
+        <v>46265.73964244213</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>46192</v>
+        <v>46276</v>
       </c>
       <c r="L139" s="1" t="inlineStr">
         <is>
@@ -12070,99 +12080,14 @@
       <c r="N139" s="1" t="n"/>
       <c r="O139" s="1" t="n"/>
       <c r="P139" s="2" t="n">
-        <v>46191.43697144676</v>
+        <v>46280.4460440625</v>
       </c>
       <c r="Q139" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="R139" s="1" t="inlineStr">
-        <is>
-          <t>Por favor, verificar com o contabil.</t>
-        </is>
-      </c>
-      <c r="S139" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T139" s="1" t="n"/>
-      <c r="U139" s="1" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="n">
-        <v>83300</v>
-      </c>
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t>Saldo Credor Incorreto</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr">
-        <is>
-          <t>Saldo Credor Incorreto</t>
-        </is>
-      </c>
-      <c r="D140" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E140" s="1" t="inlineStr">
-        <is>
-          <t>Por gentileza, providenciar regularização de transporte de saldo credor incorreto 08 e 09/2025 conforme situação do contribuinte anexo.</t>
-        </is>
-      </c>
-      <c r="F140" s="1" t="n">
-        <v>5595</v>
-      </c>
-      <c r="G140" s="1" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO QUEIROZ LTDA</t>
-        </is>
-      </c>
-      <c r="H140" s="1" t="inlineStr">
-        <is>
-          <t>Idna Sousa</t>
-        </is>
-      </c>
-      <c r="I140" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>46265.73964244213</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="L140" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M140" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N140" s="1" t="n"/>
-      <c r="O140" s="1" t="n"/>
-      <c r="P140" s="2" t="n">
-        <v>46280.4460440625</v>
-      </c>
-      <c r="Q140" s="1" t="inlineStr">
-        <is>
-          <t>Idna Sousa</t>
-        </is>
-      </c>
-      <c r="R140" s="1" t="inlineStr">
         <is>
           <t>Bom dia,
 Mes 07/2025 não recebemos o sped icms para validação.
@@ -12170,26 +12095,111 @@
 Por gentileza providenciar os arquivos para que o EFV possa validar e fazer as devidas retificações.</t>
         </is>
       </c>
+      <c r="S139" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T139" s="1" t="n"/>
+      <c r="U139" s="1" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>79914</v>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t>Omissão de Obrigações Acessórias</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>Omissão de Obrigações Acessórias</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E140" s="1" t="inlineStr">
+        <is>
+          <t>Verificar Omissão de Omissão de DIRF (Ano de Retenção) 2023</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="n">
+        <v>5596</v>
+      </c>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t>SILVESTRE MERCADO E PADARIA LTDA</t>
+        </is>
+      </c>
+      <c r="H140" s="1" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
+      <c r="I140" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>46184.58962711805</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="L140" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M140" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N140" s="1" t="n"/>
+      <c r="O140" s="1" t="n"/>
+      <c r="P140" s="2" t="n">
+        <v>46188.70596524305</v>
+      </c>
+      <c r="Q140" s="1" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
+      <c r="R140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boa tarde. Por favor direcionar o chamado ao departamento contábil qual é o  responsavel pela entrega da DIRF, </t>
+        </is>
+      </c>
       <c r="S140" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
       <c r="T140" s="1" t="n"/>
-      <c r="U140" s="1" t="inlineStr"/>
+      <c r="U140" s="1" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>79914</v>
+        <v>79915</v>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
@@ -12199,7 +12209,7 @@
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>Verificar Omissão de Omissão de DIRF (Ano de Retenção) 2023</t>
+          <t>Verificar EFD Transporte de Saldo Credor Incorreto ref. 08/2025 e 09/2025</t>
         </is>
       </c>
       <c r="F141" s="1" t="n">
@@ -12221,10 +12231,10 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46184.58962711805</v>
+        <v>46184.59060590278</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="L141" s="1" t="inlineStr">
         <is>
@@ -12239,7 +12249,7 @@
       <c r="N141" s="1" t="n"/>
       <c r="O141" s="1" t="n"/>
       <c r="P141" s="2" t="n">
-        <v>46188.70596524305</v>
+        <v>46188.71399788195</v>
       </c>
       <c r="Q141" s="1" t="inlineStr">
         <is>
@@ -12248,7 +12258,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tarde. Por favor direcionar o chamado ao departamento contábil qual é o  responsavel pela entrega da DIRF, </t>
+          <t>Por gentileza, verificar solicitação. Loja 5596 optante pelo simples nacional.</t>
         </is>
       </c>
       <c r="S141" s="1" t="inlineStr">
@@ -12265,92 +12275,90 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>79915</v>
+        <v>83696</v>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Levantamento Divergências</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t xml:space="preserve">Levantar Divergencias </t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>Verificar EFD Transporte de Saldo Credor Incorreto ref. 08/2025 e 09/2025</t>
+          <t>Bom dia,  A empresa 5598 - Distribuidor de Morangos tem o pró-labore registrado em nome de Thais Kazi de Menezes, porém o sócio é Fabio Pereira da CostaPor favor, verificar.Agradeço</t>
         </is>
       </c>
       <c r="F142" s="1" t="n">
-        <v>5596</v>
+        <v>5598</v>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>SILVESTRE MERCADO E PADARIA LTDA</t>
+          <t>DISTRIBUIDOR DE MORANGOS LTDA</t>
         </is>
       </c>
       <c r="H142" s="1" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46184.59060590278</v>
+        <v>46274.38345836806</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>46192</v>
+        <v>46276</v>
       </c>
       <c r="L142" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M142" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N142" s="1" t="n"/>
-      <c r="O142" s="1" t="n"/>
-      <c r="P142" s="2" t="n">
-        <v>46188.71399788195</v>
-      </c>
-      <c r="Q142" s="1" t="inlineStr">
-        <is>
-          <t>Larice Souza</t>
-        </is>
-      </c>
+          <t>Fatima Rocha</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>46275.46922966436</v>
+      </c>
+      <c r="O142" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="P142" s="1" t="n"/>
+      <c r="Q142" s="1" t="inlineStr"/>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, verificar solicitação. Loja 5596 optante pelo simples nacional.</t>
+          <t>Realizando os ajustes.</t>
         </is>
       </c>
       <c r="S142" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T142" s="1" t="n"/>
       <c r="U142" s="1" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>83696</v>
+        <v>83697</v>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
@@ -12369,15 +12377,15 @@
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,  A empresa 5598 - Distribuidor de Morangos tem o pró-labore registrado em nome de Thais Kazi de Menezes, porém o sócio é Fabio Pereira da CostaPor favor, verificar.Agradeço</t>
+          <t>Bom dia,  A empresa 5599 - Sweet Berry tem o pró-labore registrado em nome de Fábio Pereira da Costa, porém a sócia é Thais Kazi de Menezes. Por favor, verificar.Agradeço</t>
         </is>
       </c>
       <c r="F143" s="1" t="n">
-        <v>5598</v>
+        <v>5599</v>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>DISTRIBUIDOR DE MORANGOS LTDA</t>
+          <t>SWEET BERRY COMERCIO DE FRUTAS LTDA</t>
         </is>
       </c>
       <c r="H143" s="1" t="inlineStr">
@@ -12391,7 +12399,7 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46274.38345836806</v>
+        <v>46274.38682858797</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>46276</v>
@@ -12407,7 +12415,7 @@
         </is>
       </c>
       <c r="N143" s="2" t="n">
-        <v>46275.46922966436</v>
+        <v>46275.46928533565</v>
       </c>
       <c r="O143" s="2" t="n">
         <v>46286</v>
@@ -12433,99 +12441,103 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>83697</v>
+        <v>83983</v>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>Levantamento Divergências</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Levantar Divergencias </t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,  A empresa 5599 - Sweet Berry tem o pró-labore registrado em nome de Fábio Pereira da Costa, porém a sócia é Thais Kazi de Menezes. Por favor, verificar.Agradeço</t>
+          <t xml:space="preserve">Prezados, boa tarde!Tudo bem?O cliente solicitou o Balanço Patrimonial, balancete e a DRE referentes ao exercício de 2026 até o mês 06/2026Fico no aguardo do envio dos documentos para que possamos encaminhá-los ao cliente.Desde já, agradeço pela atenção </t>
         </is>
       </c>
       <c r="F144" s="1" t="n">
-        <v>5599</v>
+        <v>5617</v>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>SWEET BERRY COMERCIO DE FRUTAS LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="H144" s="1" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46274.38682858797</v>
+        <v>46280.40219806713</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="L144" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M144" s="1" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
-        </is>
-      </c>
-      <c r="N144" s="2" t="n">
-        <v>46275.46928533565</v>
-      </c>
+          <t>Ricardo Ferreira</t>
+        </is>
+      </c>
+      <c r="N144" s="1" t="n"/>
       <c r="O144" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="P144" s="1" t="n"/>
-      <c r="Q144" s="1" t="inlineStr"/>
+        <v>46283</v>
+      </c>
+      <c r="P144" s="2" t="n">
+        <v>46283.45726087963</v>
+      </c>
+      <c r="Q144" s="1" t="inlineStr">
+        <is>
+          <t>Jackson Silva</t>
+        </is>
+      </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>Realizando os ajustes.</t>
+          <t>Segue relatórios como solicitados.</t>
         </is>
       </c>
       <c r="S144" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T144" s="1" t="n"/>
       <c r="U144" s="1" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>83983</v>
+        <v>83861</v>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
@@ -12535,32 +12547,32 @@
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados, boa tarde!Tudo bem?O cliente solicitou o Balanço Patrimonial, balancete e a DRE referentes ao exercício de 2026 até o mês 06/2026Fico no aguardo do envio dos documentos para que possamos encaminhá-los ao cliente.Desde já, agradeço pela atenção </t>
+          <t>Boa tarde!!Por gentileza, verificar o saldo credor incorreto.</t>
         </is>
       </c>
       <c r="F145" s="1" t="n">
-        <v>5617</v>
+        <v>5650</v>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>RICHETTI COMERCIO DE BEBIDAS E ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H145" s="1" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46280.40219806713</v>
+        <v>46276.62149768518</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="L145" s="1" t="inlineStr">
         <is>
@@ -12569,24 +12581,23 @@
       </c>
       <c r="M145" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N145" s="1" t="n"/>
-      <c r="O145" s="2" t="n">
-        <v>46283</v>
-      </c>
+      <c r="O145" s="1" t="n"/>
       <c r="P145" s="2" t="n">
-        <v>46283.45726087963</v>
+        <v>46280.51998788195</v>
       </c>
       <c r="Q145" s="1" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>Segue relatórios como solicitados.</t>
+          <t>Boa tarde,
+Para regularizar, precisamos retificar os períodos, entretanto, o cliente não paga taxa eletrônica. Por favor, verificar com o cliente sobre o pagamento da taxa.</t>
         </is>
       </c>
       <c r="S145" s="1" t="inlineStr">
@@ -12597,32 +12608,32 @@
       <c r="T145" s="1" t="n"/>
       <c r="U145" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>83861</v>
+        <v>83989</v>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!!Por gentileza, verificar o saldo credor incorreto.</t>
+          <t>Encaminho autorregularização da loja com prazo para conclusão 18/09/2026</t>
         </is>
       </c>
       <c r="F146" s="1" t="n">
@@ -12644,40 +12655,31 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46276.62149768518</v>
+        <v>46280.4334184375</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="L146" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M146" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="N146" s="1" t="n"/>
-      <c r="O146" s="1" t="n"/>
-      <c r="P146" s="2" t="n">
-        <v>46280.51998788195</v>
-      </c>
-      <c r="Q146" s="1" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
-      <c r="R146" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde,
-Para regularizar, precisamos retificar os períodos, entretanto, o cliente não paga taxa eletrônica. Por favor, verificar com o cliente sobre o pagamento da taxa.</t>
-        </is>
-      </c>
+      <c r="O146" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="P146" s="1" t="n"/>
+      <c r="Q146" s="1" t="inlineStr"/>
+      <c r="R146" s="1" t="inlineStr"/>
       <c r="S146" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T146" s="1" t="n"/>
@@ -12689,16 +12691,16 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>83989</v>
+        <v>80617</v>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
@@ -12708,74 +12710,84 @@
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>Encaminho autorregularização da loja com prazo para conclusão 18/09/2026</t>
+          <t>Consta saldo residual IRRF nos períodos de 05/2025 e 01/2026.Por gentileza, verificar se os débitos são devidos ou se a DCTF do período deve ser retificada.</t>
         </is>
       </c>
       <c r="F147" s="1" t="n">
-        <v>5650</v>
+        <v>5666</v>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>RICHETTI COMERCIO DE BEBIDAS E ALIMENTOS LTDA</t>
+          <t>S.K. UEHARA CIA LTDA</t>
         </is>
       </c>
       <c r="H147" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46280.4334184375</v>
+        <v>46203.44491331019</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>46283</v>
+        <v>46206</v>
       </c>
       <c r="L147" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M147" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N147" s="1" t="n"/>
       <c r="O147" s="2" t="n">
-        <v>46287</v>
-      </c>
-      <c r="P147" s="1" t="n"/>
-      <c r="Q147" s="1" t="inlineStr"/>
-      <c r="R147" s="1" t="inlineStr"/>
+        <v>46269</v>
+      </c>
+      <c r="P147" s="2" t="n">
+        <v>46269.68145385417</v>
+      </c>
+      <c r="Q147" s="1" t="inlineStr">
+        <is>
+          <t>Diogo Calazans</t>
+        </is>
+      </c>
+      <c r="R147" s="1" t="inlineStr">
+        <is>
+          <t>Não é devido, enviamos e-mail ao fiscal pedindo a retificação da Reinf para corrigir o valor.</t>
+        </is>
+      </c>
       <c r="S147" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T147" s="1" t="n"/>
       <c r="U147" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Karina Fonseca</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>80617</v>
+        <v>79827</v>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>DCTFWeb</t>
+          <t>Alteração de Regime Tributário</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>DCTFWeb</t>
+          <t>Alteração de Regime Tributário</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
@@ -12785,32 +12797,32 @@
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>Consta saldo residual IRRF nos períodos de 05/2025 e 01/2026.Por gentileza, verificar se os débitos são devidos ou se a DCTF do período deve ser retificada.</t>
+          <t xml:space="preserve">caros, O referido cliente deveria ter migrado para o lucro real no início de 2026.Em conversa com o Ronaldo, devemos retificar as obrigações acessórias e as guias de PIS e COFINS que outrora foram recolhidas como lucro presumido, quando concluido devemos comunicá-lo para que faça o pedido de alteração. </t>
         </is>
       </c>
       <c r="F148" s="1" t="n">
-        <v>5666</v>
+        <v>5726</v>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>S.K. UEHARA CIA LTDA</t>
+          <t>VIANA &amp; CIA LTDA</t>
         </is>
       </c>
       <c r="H148" s="1" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I148" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46203.44491331019</v>
+        <v>46183.43924510416</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>46206</v>
+        <v>46185</v>
       </c>
       <c r="L148" s="1" t="inlineStr">
         <is>
@@ -12819,24 +12831,24 @@
       </c>
       <c r="M148" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N148" s="1" t="n"/>
-      <c r="O148" s="2" t="n">
-        <v>46269</v>
-      </c>
+          <t>Ricardo Ferreira</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>46197.48391481482</v>
+      </c>
+      <c r="O148" s="1" t="n"/>
       <c r="P148" s="2" t="n">
-        <v>46269.68145385417</v>
+        <v>46204.7453832176</v>
       </c>
       <c r="Q148" s="1" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>Não é devido, enviamos e-mail ao fiscal pedindo a retificação da Reinf para corrigir o valor.</t>
+          <t xml:space="preserve">operação realizando o re-processo </t>
         </is>
       </c>
       <c r="S148" s="1" t="inlineStr">
@@ -12847,22 +12859,22 @@
       <c r="T148" s="1" t="n"/>
       <c r="U148" s="1" t="inlineStr">
         <is>
-          <t>Karina Fonseca</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>79827</v>
+        <v>82879</v>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>Alteração de Regime Tributário</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>Alteração de Regime Tributário</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
@@ -12872,84 +12884,80 @@
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">caros, O referido cliente deveria ter migrado para o lucro real no início de 2026.Em conversa com o Ronaldo, devemos retificar as obrigações acessórias e as guias de PIS e COFINS que outrora foram recolhidas como lucro presumido, quando concluido devemos comunicá-lo para que faça o pedido de alteração. </t>
+          <t>Conforme informado no chamado 78447 encerrado indevidamente, consta pendência de saldo credor incorreto do cliente 5740-Queiroz de Cotia no período de Abril 2026 e pendência de entrega de EFD/GIA do mês de Janeiro 2026.Por gentileza, providenciar correção.</t>
         </is>
       </c>
       <c r="F149" s="1" t="n">
-        <v>5726</v>
+        <v>5740</v>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>VIANA &amp; CIA LTDA</t>
+          <t>QUEIROZ SUPERMERCADOS MJRR LTDA</t>
         </is>
       </c>
       <c r="H149" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I149" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46183.43924510416</v>
+        <v>46258.42635717593</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>46185</v>
+        <v>46265</v>
       </c>
       <c r="L149" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M149" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
-        </is>
-      </c>
-      <c r="N149" s="2" t="n">
-        <v>46197.48391481482</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N149" s="1" t="n"/>
       <c r="O149" s="1" t="n"/>
-      <c r="P149" s="2" t="n">
-        <v>46204.7453832176</v>
-      </c>
-      <c r="Q149" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="P149" s="1" t="n"/>
+      <c r="Q149" s="1" t="inlineStr"/>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">operação realizando o re-processo </t>
+          <t>Situação em analise, o cliente foi desnquadrado do SN e não temos arquivo do periodo</t>
         </is>
       </c>
       <c r="S149" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T149" s="1" t="n"/>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T149" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
       <c r="U149" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>82879</v>
+        <v>83251</v>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
@@ -12959,71 +12967,71 @@
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>Conforme informado no chamado 78447 encerrado indevidamente, consta pendência de saldo credor incorreto do cliente 5740-Queiroz de Cotia no período de Abril 2026 e pendência de entrega de EFD/GIA do mês de Janeiro 2026.Por gentileza, providenciar correção.</t>
+          <t xml:space="preserve">Bom dia, por gentileza emitir as guias em aberto da prefeitura de Caieiras. </t>
         </is>
       </c>
       <c r="F150" s="1" t="n">
-        <v>5740</v>
+        <v>5801</v>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t>QUEIROZ SUPERMERCADOS MJRR LTDA</t>
+          <t xml:space="preserve">Nilcap Renovadora de Pneus LTDA </t>
         </is>
       </c>
       <c r="H150" s="1" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I150" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46258.42635717593</v>
+        <v>46265.39660358796</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="L150" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M150" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N150" s="1" t="n"/>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>46266.64227881945</v>
+      </c>
       <c r="O150" s="1" t="n"/>
-      <c r="P150" s="1" t="n"/>
-      <c r="Q150" s="1" t="inlineStr"/>
+      <c r="P150" s="2" t="n">
+        <v>46266.68481299769</v>
+      </c>
+      <c r="Q150" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>Situação em analise, o cliente foi desnquadrado do SN e não temos arquivo do periodo</t>
+          <t xml:space="preserve">operação realizando a demanda </t>
         </is>
       </c>
       <c r="S150" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T150" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
-      <c r="U150" s="1" t="inlineStr">
-        <is>
-          <t>Larice Souza</t>
-        </is>
-      </c>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T150" s="1" t="n"/>
+      <c r="U150" s="1" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>83251</v>
+        <v>84144</v>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
@@ -13042,7 +13050,7 @@
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, por gentileza emitir as guias em aberto da prefeitura de Caieiras. </t>
+          <t xml:space="preserve">Bom dia, por gentileza verificar a guia de ISS em aberto e encaminhar  recalculada </t>
         </is>
       </c>
       <c r="F151" s="1" t="n">
@@ -13055,7 +13063,7 @@
       </c>
       <c r="H151" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I151" s="1" t="inlineStr">
@@ -13064,10 +13072,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46265.39660358796</v>
+        <v>46283.40019563658</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>46266</v>
+        <v>46286</v>
       </c>
       <c r="L151" s="1" t="inlineStr">
         <is>
@@ -13079,21 +13087,20 @@
           <t>Beatriz Rangel</t>
         </is>
       </c>
-      <c r="N151" s="2" t="n">
-        <v>46266.64227881945</v>
-      </c>
+      <c r="N151" s="1" t="n"/>
       <c r="O151" s="1" t="n"/>
       <c r="P151" s="2" t="n">
-        <v>46266.68481299769</v>
+        <v>46286.61436994213</v>
       </c>
       <c r="Q151" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">operação realizando a demanda </t>
+          <t xml:space="preserve">Enviado por e-mail dia 18/09/2026
+</t>
         </is>
       </c>
       <c r="S151" s="1" t="inlineStr">
@@ -13102,162 +13109,157 @@
         </is>
       </c>
       <c r="T151" s="1" t="n"/>
-      <c r="U151" s="1" t="inlineStr"/>
+      <c r="U151" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>84144</v>
+        <v>83676</v>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Documentação</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Solicitação de Documentação</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, por gentileza verificar a guia de ISS em aberto e encaminhar  recalculada </t>
+          <t>Boa tarde!Por gentileza, disponibilizar a documentação para envio a nova contabilidade.</t>
         </is>
       </c>
       <c r="F152" s="1" t="n">
-        <v>5801</v>
+        <v>5822</v>
       </c>
       <c r="G152" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nilcap Renovadora de Pneus LTDA </t>
+          <t>RODRIGUES SERVICE SOLUTIONS LTDA</t>
         </is>
       </c>
       <c r="H152" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="I152" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46283.40019563658</v>
+        <v>46273.6644775463</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>46286</v>
+        <v>46274</v>
       </c>
       <c r="L152" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido para Responsável</t>
         </is>
       </c>
       <c r="M152" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="N152" s="1" t="n"/>
       <c r="O152" s="1" t="n"/>
-      <c r="P152" s="2" t="n">
-        <v>46286.61436994213</v>
-      </c>
-      <c r="Q152" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="P152" s="1" t="n"/>
+      <c r="Q152" s="1" t="inlineStr"/>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enviado por e-mail dia 18/09/2026
-</t>
+          <t>Boa tarde, Karina!
+Poderia me informar qual a relação de documentos que devo enviar?</t>
         </is>
       </c>
       <c r="S152" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T152" s="1" t="n"/>
       <c r="U152" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>83676</v>
+        <v>84252</v>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>Documentação</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentação</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por gentileza, disponibilizar a documentação para envio a nova contabilidade.</t>
+          <t>bom dia!!verificar balanço e dre 2025, porque o valor do resultado está divergente.verificar balanço e dre 01-06 2026, porque o valor do resultado está divergente.</t>
         </is>
       </c>
       <c r="F153" s="1" t="n">
-        <v>5822</v>
+        <v>5834</v>
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>RODRIGUES SERVICE SOLUTIONS LTDA</t>
+          <t>Caete Comunicacao Visual LTDA</t>
         </is>
       </c>
       <c r="H153" s="1" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I153" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46273.6644775463</v>
+        <v>46287.44208723379</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>46274</v>
+        <v>46288</v>
       </c>
       <c r="L153" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M153" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="N153" s="1" t="n"/>
-      <c r="O153" s="1" t="n"/>
+      <c r="O153" s="2" t="n">
+        <v>46289</v>
+      </c>
       <c r="P153" s="1" t="n"/>
       <c r="Q153" s="1" t="inlineStr"/>
-      <c r="R153" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde, Karina!
-Poderia me informar qual a relação de documentos que devo enviar?</t>
-        </is>
-      </c>
+      <c r="R153" s="1" t="inlineStr"/>
       <c r="S153" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -13266,22 +13268,22 @@
       <c r="T153" s="1" t="n"/>
       <c r="U153" s="1" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>84252</v>
+        <v>81709</v>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
@@ -13291,15 +13293,15 @@
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>bom dia!!verificar balanço e dre 2025, porque o valor do resultado está divergente.verificar balanço e dre 01-06 2026, porque o valor do resultado está divergente.</t>
+          <t>5885 - segue comunicado ecac referente a dctf omisso abril 2026</t>
         </is>
       </c>
       <c r="F154" s="1" t="n">
-        <v>5834</v>
+        <v>5885</v>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>Caete Comunicacao Visual LTDA</t>
+          <t>INSTITUTO DE TECNOLOGIA ASSISTIVA LTDA</t>
         </is>
       </c>
       <c r="H154" s="1" t="inlineStr">
@@ -13309,35 +13311,45 @@
       </c>
       <c r="I154" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46287.44208723379</v>
+        <v>46234.50876994213</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>46288</v>
+        <v>46237</v>
       </c>
       <c r="L154" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M154" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N154" s="1" t="n"/>
       <c r="O154" s="2" t="n">
-        <v>46289</v>
-      </c>
-      <c r="P154" s="1" t="n"/>
-      <c r="Q154" s="1" t="inlineStr"/>
-      <c r="R154" s="1" t="inlineStr"/>
+        <v>46237</v>
+      </c>
+      <c r="P154" s="2" t="n">
+        <v>46237.49066496528</v>
+      </c>
+      <c r="Q154" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
+      <c r="R154" s="1" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
+        </is>
+      </c>
       <c r="S154" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T154" s="1" t="n"/>
@@ -13349,16 +13361,16 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>81709</v>
+        <v>83938</v>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>DCTFWeb</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>DCTFWeb</t>
+          <t>Fiscalização Municipal</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
@@ -13368,102 +13380,92 @@
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>5885 - segue comunicado ecac referente a dctf omisso abril 2026</t>
+          <t>Bom dia!Segue mensagem recebida no DEC Municipal, por gentileza, verificar.Prazo: 09/10/2026</t>
         </is>
       </c>
       <c r="F155" s="1" t="n">
-        <v>5885</v>
+        <v>5901</v>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>INSTITUTO DE TECNOLOGIA ASSISTIVA LTDA</t>
+          <t>Local Serviços Especializados LTDA</t>
         </is>
       </c>
       <c r="H155" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I155" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46234.50876994213</v>
+        <v>46279.44351177083</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>46237</v>
+        <v>46286</v>
       </c>
       <c r="L155" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M155" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N155" s="1" t="n"/>
       <c r="O155" s="2" t="n">
-        <v>46237</v>
-      </c>
-      <c r="P155" s="2" t="n">
-        <v>46237.49066496528</v>
-      </c>
-      <c r="Q155" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+        <v>46290</v>
+      </c>
+      <c r="P155" s="1" t="n"/>
+      <c r="Q155" s="1" t="inlineStr"/>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>RESOLVIDO</t>
+          <t>e-mail sobre a fiscalização respondido. GC irá dar continuidade no processo</t>
         </is>
       </c>
       <c r="S155" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T155" s="1" t="n"/>
-      <c r="U155" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+      <c r="U155" s="1" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>83938</v>
+        <v>83137</v>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>Fiscalização Municipal</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Segue mensagem recebida no DEC Municipal, por gentileza, verificar.Prazo: 09/10/2026</t>
+          <t>Cliente está solicitando a certidão negativa de débitos da PIZZA CREK, estadual. Ao tentar gerar aparecendo a pendencia anexa. Por favor solucionar o mais breve possivel.</t>
         </is>
       </c>
       <c r="F156" s="1" t="n">
-        <v>5901</v>
+        <v>5902</v>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>Local Serviços Especializados LTDA</t>
+          <t>PIZZA CREK FAST FOOD LTDA (FILIAL 7)</t>
         </is>
       </c>
       <c r="H156" s="1" t="inlineStr">
@@ -13477,35 +13479,41 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46279.44351177083</v>
+        <v>46261.54069120371</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="L156" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M156" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="N156" s="1" t="n"/>
       <c r="O156" s="2" t="n">
-        <v>46290</v>
-      </c>
-      <c r="P156" s="1" t="n"/>
-      <c r="Q156" s="1" t="inlineStr"/>
+        <v>46280</v>
+      </c>
+      <c r="P156" s="2" t="n">
+        <v>46279.49325150463</v>
+      </c>
+      <c r="Q156" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>e-mail sobre a fiscalização respondido. GC irá dar continuidade no processo</t>
+          <t xml:space="preserve">sped já entregue </t>
         </is>
       </c>
       <c r="S156" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T156" s="1" t="n"/>
@@ -13513,16 +13521,16 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>83137</v>
+        <v>80527</v>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Documentação</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Ajuste de Documentação</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
@@ -13532,32 +13540,32 @@
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>Cliente está solicitando a certidão negativa de débitos da PIZZA CREK, estadual. Ao tentar gerar aparecendo a pendencia anexa. Por favor solucionar o mais breve possivel.</t>
+          <t>Prezados,Conforme solicitação do cliente favor providenciar o prólabore abaixo a partir do mês de julho 2026Merch Link LTDA: 49.797.761/0001-05- Ana Ligia Ribeiro Terensi Silva (proprietária)- ?Pró-labore: R$3.000,00</t>
         </is>
       </c>
       <c r="F157" s="1" t="n">
-        <v>5902</v>
+        <v>5908</v>
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>PIZZA CREK FAST FOOD LTDA (FILIAL 7)</t>
+          <t>MERCH LINK LTDA</t>
         </is>
       </c>
       <c r="H157" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I157" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46261.54069120371</v>
+        <v>46197.47626122685</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="L157" s="1" t="inlineStr">
         <is>
@@ -13566,24 +13574,24 @@
       </c>
       <c r="M157" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
-        </is>
-      </c>
-      <c r="N157" s="1" t="n"/>
-      <c r="O157" s="2" t="n">
-        <v>46280</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>46197.57248116898</v>
+      </c>
+      <c r="O157" s="1" t="n"/>
       <c r="P157" s="2" t="n">
-        <v>46279.49325150463</v>
+        <v>46203.72243090278</v>
       </c>
       <c r="Q157" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sped já entregue </t>
+          <t>Realizando cadastro para a folha de pro-labore.</t>
         </is>
       </c>
       <c r="S157" s="1" t="inlineStr">
@@ -13592,20 +13600,24 @@
         </is>
       </c>
       <c r="T157" s="1" t="n"/>
-      <c r="U157" s="1" t="inlineStr"/>
+      <c r="U157" s="1" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>80527</v>
+        <v>80203</v>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Documentação</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>Ajuste de Documentação</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
@@ -13615,7 +13627,7 @@
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Conforme solicitação do cliente favor providenciar o prólabore abaixo a partir do mês de julho 2026Merch Link LTDA: 49.797.761/0001-05- Ana Ligia Ribeiro Terensi Silva (proprietária)- ?Pró-labore: R$3.000,00</t>
+          <t>Prezados, Boa tarde!Clienrte notificado ref autoregularização ref divergências na comparação por referência entre os valores do PGDAS e da Declaração de Informações de Meios de Pagamentos (DIMP).Prazo para regularização até 12/07/26Documentos disponiveis na pasta abaixo:J:\Importação\AUTO REGULARIZAÇÃO - PGDAS\5908</t>
         </is>
       </c>
       <c r="F158" s="1" t="n">
@@ -13628,16 +13640,16 @@
       </c>
       <c r="H158" s="1" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I158" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46197.47626122685</v>
+        <v>46191.57591585648</v>
       </c>
       <c r="K158" s="2" t="n">
         <v>46203</v>
@@ -13653,20 +13665,20 @@
         </is>
       </c>
       <c r="N158" s="2" t="n">
-        <v>46197.57248116898</v>
+        <v>46192.52378078704</v>
       </c>
       <c r="O158" s="1" t="n"/>
       <c r="P158" s="2" t="n">
-        <v>46203.72243090278</v>
+        <v>46238.45672908565</v>
       </c>
       <c r="Q158" s="1" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>Realizando cadastro para a folha de pro-labore.</t>
+          <t xml:space="preserve">verificando </t>
         </is>
       </c>
       <c r="S158" s="1" t="inlineStr">
@@ -13677,22 +13689,22 @@
       <c r="T158" s="1" t="n"/>
       <c r="U158" s="1" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>80203</v>
+        <v>79868</v>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
@@ -13702,7 +13714,7 @@
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>Prezados, Boa tarde!Clienrte notificado ref autoregularização ref divergências na comparação por referência entre os valores do PGDAS e da Declaração de Informações de Meios de Pagamentos (DIMP).Prazo para regularização até 12/07/26Documentos disponiveis na pasta abaixo:J:\Importação\AUTO REGULARIZAÇÃO - PGDAS\5908</t>
+          <t>Prezados, boa tarde!Cliente comunicou que o valor apurado no período de março 2026 está incompleto. Segundo cliente os valores de NFCe não foram considerados.Por gentileza, avaliar se os arquivos disponibilizados na época, via FTP foram escriturados.</t>
         </is>
       </c>
       <c r="F159" s="1" t="n">
@@ -13720,48 +13732,45 @@
       </c>
       <c r="I159" s="1" t="inlineStr">
         <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>46183.63777893518</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="L159" s="1" t="inlineStr">
+        <is>
+          <t>Devolvido para Solicitante</t>
+        </is>
+      </c>
+      <c r="M159" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N159" s="1" t="n"/>
+      <c r="O159" s="1" t="n"/>
+      <c r="P159" s="1" t="n"/>
+      <c r="Q159" s="1" t="inlineStr"/>
+      <c r="R159" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Irei verificar. 
+foi enviado ao cliente a confirmação de faturamento, porém não tivemos retorno na época. </t>
+        </is>
+      </c>
+      <c r="S159" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T159" s="1" t="inlineStr">
+        <is>
           <t>EF - VAREJO</t>
         </is>
       </c>
-      <c r="J159" s="2" t="n">
-        <v>46191.57591585648</v>
-      </c>
-      <c r="K159" s="2" t="n">
-        <v>46203</v>
-      </c>
-      <c r="L159" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M159" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N159" s="2" t="n">
-        <v>46192.52378078704</v>
-      </c>
-      <c r="O159" s="1" t="n"/>
-      <c r="P159" s="2" t="n">
-        <v>46238.45672908565</v>
-      </c>
-      <c r="Q159" s="1" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
-      <c r="R159" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">verificando </t>
-        </is>
-      </c>
-      <c r="S159" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T159" s="1" t="n"/>
       <c r="U159" s="1" t="inlineStr">
         <is>
           <t>Lorrane Santos</t>
@@ -13770,16 +13779,16 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>79868</v>
+        <v>79820</v>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
@@ -13789,7 +13798,7 @@
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tarde!Cliente comunicou que o valor apurado no período de março 2026 está incompleto. Segundo cliente os valores de NFCe não foram considerados.Por gentileza, avaliar se os arquivos disponibilizados na época, via FTP foram escriturados.</t>
+          <t>Consta pendência parcial de INSS referente mês 03/2026. Favor verificar se a pendência é indevida para retificação da DCTF.</t>
         </is>
       </c>
       <c r="F160" s="1" t="n">
@@ -13802,23 +13811,23 @@
       </c>
       <c r="H160" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I160" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46183.63777893518</v>
+        <v>46182.79089837963</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="L160" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M160" s="1" t="inlineStr">
@@ -13828,99 +13837,15 @@
       </c>
       <c r="N160" s="1" t="n"/>
       <c r="O160" s="1" t="n"/>
-      <c r="P160" s="1" t="n"/>
-      <c r="Q160" s="1" t="inlineStr"/>
+      <c r="P160" s="2" t="n">
+        <v>46189.41413730324</v>
+      </c>
+      <c r="Q160" s="1" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
       <c r="R160" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Irei verificar. 
-foi enviado ao cliente a confirmação de faturamento, porém não tivemos retorno na época. </t>
-        </is>
-      </c>
-      <c r="S160" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T160" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
-      <c r="U160" s="1" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="n">
-        <v>79820</v>
-      </c>
-      <c r="B161" s="1" t="inlineStr">
-        <is>
-          <t>Pendência de Débito</t>
-        </is>
-      </c>
-      <c r="C161" s="1" t="inlineStr">
-        <is>
-          <t>Pendência de Débito</t>
-        </is>
-      </c>
-      <c r="D161" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E161" s="1" t="inlineStr">
-        <is>
-          <t>Consta pendência parcial de INSS referente mês 03/2026. Favor verificar se a pendência é indevida para retificação da DCTF.</t>
-        </is>
-      </c>
-      <c r="F161" s="1" t="n">
-        <v>5908</v>
-      </c>
-      <c r="G161" s="1" t="inlineStr">
-        <is>
-          <t>MERCH LINK LTDA</t>
-        </is>
-      </c>
-      <c r="H161" s="1" t="inlineStr">
-        <is>
-          <t>Mauricio Lermen</t>
-        </is>
-      </c>
-      <c r="I161" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>46182.79089837963</v>
-      </c>
-      <c r="K161" s="2" t="n">
-        <v>46189</v>
-      </c>
-      <c r="L161" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M161" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N161" s="1" t="n"/>
-      <c r="O161" s="1" t="n"/>
-      <c r="P161" s="2" t="n">
-        <v>46189.41413730324</v>
-      </c>
-      <c r="Q161" s="1" t="inlineStr">
-        <is>
-          <t>Mauricio Lermen</t>
-        </is>
-      </c>
-      <c r="R161" s="1" t="inlineStr">
         <is>
           <t>Bom dia!
 Os valores são devidos conforme resumo, estou levantando se houve alteração após liberação.
@@ -13928,26 +13853,103 @@
 devolve este chamado para continuidade.</t>
         </is>
       </c>
+      <c r="S160" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T160" s="1" t="n"/>
+      <c r="U160" s="1" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>84257</v>
+      </c>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t>Pendência de Débito</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>Pendência de Débito</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E161" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia!Por gentileza, verificar se é devido. Não localizamos a guia no SCI.</t>
+        </is>
+      </c>
+      <c r="F161" s="1" t="n">
+        <v>5920</v>
+      </c>
+      <c r="G161" s="1" t="inlineStr">
+        <is>
+          <t>G13 IMPORTAÇÃO E EXPORTAÇÃO LTDA (FILIAL 3)</t>
+        </is>
+      </c>
+      <c r="H161" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
+      <c r="I161" s="1" t="inlineStr">
+        <is>
+          <t>EF - INDUSTRIA</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>46287.4576400463</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="L161" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M161" s="1" t="inlineStr">
+        <is>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N161" s="1" t="n"/>
+      <c r="O161" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="P161" s="1" t="n"/>
+      <c r="Q161" s="1" t="inlineStr"/>
+      <c r="R161" s="1" t="inlineStr"/>
       <c r="S161" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T161" s="1" t="n"/>
-      <c r="U161" s="1" t="inlineStr"/>
+      <c r="U161" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>84257</v>
+        <v>83738</v>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
@@ -13957,133 +13959,56 @@
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Por gentileza, verificar se é devido. Não localizamos a guia no SCI.</t>
+          <t>por gentileza, providenciar regularização conforme anexo.Prazo para atendimento até 20/09/206periodo fora da gestão MG, cliente ciente que haverá custo para a realização do serviço.</t>
         </is>
       </c>
       <c r="F162" s="1" t="n">
-        <v>5920</v>
+        <v>5929</v>
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t>G13 IMPORTAÇÃO E EXPORTAÇÃO LTDA (FILIAL 3)</t>
+          <t>BAR E RESTAURANTE 1566 LTDA</t>
         </is>
       </c>
       <c r="H162" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I162" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46287.4576400463</v>
+        <v>46274.63414938658</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>46289</v>
+        <v>46280</v>
       </c>
       <c r="L162" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M162" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N162" s="1" t="n"/>
       <c r="O162" s="2" t="n">
-        <v>46290</v>
-      </c>
-      <c r="P162" s="1" t="n"/>
-      <c r="Q162" s="1" t="inlineStr"/>
-      <c r="R162" s="1" t="inlineStr"/>
-      <c r="S162" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T162" s="1" t="n"/>
-      <c r="U162" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="1" t="n">
-        <v>83738</v>
-      </c>
-      <c r="B163" s="1" t="inlineStr">
-        <is>
-          <t>Autorregularização</t>
-        </is>
-      </c>
-      <c r="C163" s="1" t="inlineStr">
-        <is>
-          <t>Autorregularização</t>
-        </is>
-      </c>
-      <c r="D163" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E163" s="1" t="inlineStr">
-        <is>
-          <t>por gentileza, providenciar regularização conforme anexo.Prazo para atendimento até 20/09/206periodo fora da gestão MG, cliente ciente que haverá custo para a realização do serviço.</t>
-        </is>
-      </c>
-      <c r="F163" s="1" t="n">
-        <v>5929</v>
-      </c>
-      <c r="G163" s="1" t="inlineStr">
-        <is>
-          <t>BAR E RESTAURANTE 1566 LTDA</t>
-        </is>
-      </c>
-      <c r="H163" s="1" t="inlineStr">
+        <v>46276</v>
+      </c>
+      <c r="P162" s="2" t="n">
+        <v>46280.45140825232</v>
+      </c>
+      <c r="Q162" s="1" t="inlineStr">
         <is>
           <t>Lucas Fischer</t>
         </is>
       </c>
-      <c r="I163" s="1" t="inlineStr">
-        <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>46274.63414938658</v>
-      </c>
-      <c r="K163" s="2" t="n">
-        <v>46280</v>
-      </c>
-      <c r="L163" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M163" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N163" s="1" t="n"/>
-      <c r="O163" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="P163" s="2" t="n">
-        <v>46280.45140825232</v>
-      </c>
-      <c r="Q163" s="1" t="inlineStr">
-        <is>
-          <t>Lucas Fischer</t>
-        </is>
-      </c>
-      <c r="R163" s="1" t="inlineStr">
+      <c r="R162" s="1" t="inlineStr">
         <is>
           <t>Bom dia, 
 Precisamos que voces providenciem as informações para realizarmos a regularização:
@@ -14092,17 +14017,84 @@
 Não temos essa informação e não conseguimos se o cliente ou ex contador não informar.</t>
         </is>
       </c>
+      <c r="S162" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T162" s="1" t="n"/>
+      <c r="U162" s="1" t="inlineStr">
+        <is>
+          <t>Lucas Fischer</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>84398</v>
+      </c>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t>Saldo Credor Incorreto</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>Saldo Credor Incorreto</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E163" s="1" t="inlineStr">
+        <is>
+          <t>Por gentileza, providencia regularização saldo credor incorreto, conforme situação do contribuinte anexa.</t>
+        </is>
+      </c>
+      <c r="F163" s="1" t="n">
+        <v>5930</v>
+      </c>
+      <c r="G163" s="1" t="inlineStr">
+        <is>
+          <t>ESPETINHO VILA MARIANA LTDA</t>
+        </is>
+      </c>
+      <c r="H163" s="1" t="n"/>
+      <c r="I163" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>46288.79362025463</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="L163" s="1" t="inlineStr">
+        <is>
+          <t>Sem Responsavel Atribuido</t>
+        </is>
+      </c>
+      <c r="M163" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N163" s="1" t="n"/>
+      <c r="O163" s="1" t="n"/>
+      <c r="P163" s="1" t="n"/>
+      <c r="Q163" s="1" t="inlineStr"/>
+      <c r="R163" s="1" t="n"/>
       <c r="S163" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T163" s="1" t="n"/>
-      <c r="U163" s="1" t="inlineStr">
-        <is>
-          <t>Lucas Fischer</t>
-        </is>
-      </c>
+      <c r="U163" s="1" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -54271,7 +54263,7 @@
       </c>
       <c r="H709" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I709" s="1" t="inlineStr">
@@ -54287,7 +54279,7 @@
       </c>
       <c r="L709" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M709" s="1" t="inlineStr">
@@ -54297,12 +54289,23 @@
       </c>
       <c r="N709" s="1" t="n"/>
       <c r="O709" s="1" t="n"/>
-      <c r="P709" s="1" t="n"/>
-      <c r="Q709" s="1" t="inlineStr"/>
-      <c r="R709" s="1" t="inlineStr"/>
+      <c r="P709" s="2" t="n">
+        <v>46288.7633241088</v>
+      </c>
+      <c r="Q709" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R709" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde!
+As declarações foram retificadas? Precisamos das copias das declarações originais e retificadoras.</t>
+        </is>
+      </c>
       <c r="S709" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T709" s="1" t="n"/>
@@ -58811,7 +58814,7 @@
       </c>
       <c r="H767" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Karina Dantas</t>
         </is>
       </c>
       <c r="I767" s="1" t="inlineStr">
@@ -58827,7 +58830,7 @@
       </c>
       <c r="L767" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M767" s="1" t="inlineStr">
@@ -58837,12 +58840,23 @@
       </c>
       <c r="N767" s="1" t="n"/>
       <c r="O767" s="1" t="n"/>
-      <c r="P767" s="1" t="n"/>
-      <c r="Q767" s="1" t="inlineStr"/>
-      <c r="R767" s="1" t="inlineStr"/>
+      <c r="P767" s="2" t="n">
+        <v>46288.76317905093</v>
+      </c>
+      <c r="Q767" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="R767" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde!
+As declarações foram retificadas? Precisamos das copias das declarações originais e retificadoras.</t>
+        </is>
+      </c>
       <c r="S767" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T767" s="1" t="n"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -51006,69 +51006,59 @@
     </row>
     <row r="666">
       <c r="A666" s="1" t="n">
-        <v>81777</v>
+        <v>84403</v>
       </c>
       <c r="B666" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C666" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D666" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>SANTOS - EF</t>
         </is>
       </c>
       <c r="E666" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tarde, poderia fazer o processo administrativo da empresa 3616 - CCV do ISS mes 04/2026, a guia foi cancelada para realizar emissão de notas da MG Negócios , que tinha nota emitidas contra a CCV, pós o financeiro realizou o pagamento da guia de ISS de serviços prestados </t>
+          <t>Bom dia,Solicito, por gentileza, a baixa das tarefas referentes à entrega da DIPAM das empresas 5945, 5986, 6114 e 6115.Ao realizar a transmissão dos arquivos, o sistema informa que o arquivo já se encontra na base de dados, indicando que a entrega foi realizada. Porém, ao tentar acessar a transmissão para consultar e obter o recibo, o sistema informa que não foi encontrado nenhum arquivo.Dessa forma, não estamos conseguindo acessar os recibos para anexá-los às respectivas tarefas.Informo também que já estou tomando as providências necessárias para obter os arquivos/recibos das transmissões.Empresas: 5945 – 5986 – 6114 – 6115</t>
         </is>
       </c>
       <c r="F666" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G666" s="1" t="n"/>
-      <c r="H666" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="H666" s="1" t="n"/>
       <c r="I666" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J666" s="2" t="n">
-        <v>46237.59220239583</v>
+        <v>46289.39711704861</v>
       </c>
       <c r="K666" s="2" t="n">
-        <v>46239</v>
+        <v>46290</v>
       </c>
       <c r="L666" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M666" s="1" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
-        </is>
-      </c>
-      <c r="N666" s="2" t="n">
-        <v>46241.63536697916</v>
-      </c>
+          <t>Jasmina Melo</t>
+        </is>
+      </c>
+      <c r="N666" s="1" t="n"/>
       <c r="O666" s="1" t="n"/>
       <c r="P666" s="1" t="n"/>
       <c r="Q666" s="1" t="inlineStr"/>
-      <c r="R666" s="1" t="inlineStr">
-        <is>
-          <t>Solicitei orientações à Prefeitura em como proceder para regularização, aguardando retorno.</t>
-        </is>
-      </c>
+      <c r="R666" s="1" t="n"/>
       <c r="S666" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -51079,26 +51069,26 @@
     </row>
     <row r="667">
       <c r="A667" s="1" t="n">
-        <v>82094</v>
+        <v>81777</v>
       </c>
       <c r="B667" s="1" t="inlineStr">
         <is>
-          <t>Processo de VISA</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C667" s="1" t="inlineStr">
         <is>
-          <t>Renovação</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D667" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - GC</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E667" s="1" t="inlineStr">
         <is>
-          <t>Favor providenciar a renovação da vigilância sanitária das empresas do grupo Atalaia - código - 1685/2616/4881/6175 - com urgência. Muito Obrigada!</t>
+          <t xml:space="preserve">Boa tarde, poderia fazer o processo administrativo da empresa 3616 - CCV do ISS mes 04/2026, a guia foi cancelada para realizar emissão de notas da MG Negócios , que tinha nota emitidas contra a CCV, pós o financeiro realizou o pagamento da guia de ISS de serviços prestados </t>
         </is>
       </c>
       <c r="F667" s="1" t="n">
@@ -51107,43 +51097,116 @@
       <c r="G667" s="1" t="n"/>
       <c r="H667" s="1" t="inlineStr">
         <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I667" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J667" s="2" t="n">
+        <v>46237.59220239583</v>
+      </c>
+      <c r="K667" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="L667" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M667" s="1" t="inlineStr">
+        <is>
+          <t>Romario Silva</t>
+        </is>
+      </c>
+      <c r="N667" s="2" t="n">
+        <v>46241.63536697916</v>
+      </c>
+      <c r="O667" s="1" t="n"/>
+      <c r="P667" s="1" t="n"/>
+      <c r="Q667" s="1" t="inlineStr"/>
+      <c r="R667" s="1" t="inlineStr">
+        <is>
+          <t>Solicitei orientações à Prefeitura em como proceder para regularização, aguardando retorno.</t>
+        </is>
+      </c>
+      <c r="S667" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T667" s="1" t="n"/>
+      <c r="U667" s="1" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>82094</v>
+      </c>
+      <c r="B668" s="1" t="inlineStr">
+        <is>
+          <t>Processo de VISA</t>
+        </is>
+      </c>
+      <c r="C668" s="1" t="inlineStr">
+        <is>
+          <t>Renovação</t>
+        </is>
+      </c>
+      <c r="D668" s="1" t="inlineStr">
+        <is>
+          <t>SANTOS - GC</t>
+        </is>
+      </c>
+      <c r="E668" s="1" t="inlineStr">
+        <is>
+          <t>Favor providenciar a renovação da vigilância sanitária das empresas do grupo Atalaia - código - 1685/2616/4881/6175 - com urgência. Muito Obrigada!</t>
+        </is>
+      </c>
+      <c r="F668" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G668" s="1" t="n"/>
+      <c r="H668" s="1" t="inlineStr">
+        <is>
           <t>Talita Silva</t>
         </is>
       </c>
-      <c r="I667" s="1" t="inlineStr">
+      <c r="I668" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J667" s="2" t="n">
+      <c r="J668" s="2" t="n">
         <v>46241.66958043981</v>
       </c>
-      <c r="K667" s="2" t="n">
+      <c r="K668" s="2" t="n">
         <v>46244</v>
       </c>
-      <c r="L667" s="1" t="inlineStr">
+      <c r="L668" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M667" s="1" t="inlineStr">
+      <c r="M668" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N667" s="2" t="n">
+      <c r="N668" s="2" t="n">
         <v>46252.70058159722</v>
       </c>
-      <c r="O667" s="1" t="n"/>
-      <c r="P667" s="2" t="n">
+      <c r="O668" s="1" t="n"/>
+      <c r="P668" s="2" t="n">
         <v>46280.42831450231</v>
       </c>
-      <c r="Q667" s="1" t="inlineStr">
+      <c r="Q668" s="1" t="inlineStr">
         <is>
           <t>Talita Silva</t>
         </is>
       </c>
-      <c r="R667" s="1" t="inlineStr">
+      <c r="R668" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Olá, boa tarde!
 Enviei por e-mail o Anexo III das empresas para assinatura.
@@ -51151,85 +51214,6 @@
 </t>
         </is>
       </c>
-      <c r="S667" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T667" s="1" t="n"/>
-      <c r="U667" s="1" t="inlineStr"/>
-    </row>
-    <row r="668">
-      <c r="A668" s="1" t="n">
-        <v>82296</v>
-      </c>
-      <c r="B668" s="1" t="inlineStr">
-        <is>
-          <t>Parcelamento Estadual</t>
-        </is>
-      </c>
-      <c r="C668" s="1" t="inlineStr">
-        <is>
-          <t>Divida Ativa</t>
-        </is>
-      </c>
-      <c r="D668" s="1" t="inlineStr">
-        <is>
-          <t>SANTOS - ADM</t>
-        </is>
-      </c>
-      <c r="E668" s="1" t="inlineStr">
-        <is>
-          <t>Cliente 5219 e 5551 solicitou parcelamento do ICMS , pode fazer a simulação</t>
-        </is>
-      </c>
-      <c r="F668" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G668" s="1" t="n"/>
-      <c r="H668" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="I668" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J668" s="2" t="n">
-        <v>46246.6211778588</v>
-      </c>
-      <c r="K668" s="2" t="n">
-        <v>46248</v>
-      </c>
-      <c r="L668" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M668" s="1" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
-      <c r="N668" s="2" t="n">
-        <v>46268.68634155093</v>
-      </c>
-      <c r="O668" s="1" t="n"/>
-      <c r="P668" s="2" t="n">
-        <v>46276.37282434028</v>
-      </c>
-      <c r="Q668" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="R668" s="1" t="inlineStr">
-        <is>
-          <t>Deve ser aberto um chamado para cada solicitação/cliente.</t>
-        </is>
-      </c>
       <c r="S668" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -51240,16 +51224,16 @@
     </row>
     <row r="669">
       <c r="A669" s="1" t="n">
-        <v>81227</v>
+        <v>82296</v>
       </c>
       <c r="B669" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Parcelamento Estadual</t>
         </is>
       </c>
       <c r="C669" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Divida Ativa</t>
         </is>
       </c>
       <c r="D669" s="1" t="inlineStr">
@@ -51259,7 +51243,7 @@
       </c>
       <c r="E669" s="1" t="inlineStr">
         <is>
-          <t>Empresa 5988 - Maurício Toniati - Cliente que haviamos feito a apuração incorreta de pis e cofins - Foi feito parcelamento , mais depois da retificação dos impostos não teria imposto a apagar. Gerei um relatório da situação fiscal e não consta nenhuma informação referente à Malha Fiscal, apenas a indicação de Parcelamento Suspenso.Poderia verificar, por gentileza, se há algum procedimento adicional que precise ser realizado ou alguma outra consulta que devemos efetuar?</t>
+          <t>Cliente 5219 e 5551 solicitou parcelamento do ICMS , pode fazer a simulação</t>
         </is>
       </c>
       <c r="F669" s="1" t="n">
@@ -51277,14 +51261,14 @@
         </is>
       </c>
       <c r="J669" s="2" t="n">
-        <v>46223.69836307871</v>
+        <v>46246.6211778588</v>
       </c>
       <c r="K669" s="2" t="n">
-        <v>46224</v>
+        <v>46248</v>
       </c>
       <c r="L669" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M669" s="1" t="inlineStr">
@@ -51293,19 +51277,25 @@
         </is>
       </c>
       <c r="N669" s="2" t="n">
-        <v>46232.73233688658</v>
+        <v>46268.68634155093</v>
       </c>
       <c r="O669" s="1" t="n"/>
-      <c r="P669" s="1" t="n"/>
-      <c r="Q669" s="1" t="inlineStr"/>
+      <c r="P669" s="2" t="n">
+        <v>46276.37282434028</v>
+      </c>
+      <c r="Q669" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="R669" s="1" t="inlineStr">
         <is>
-          <t>Verificando via chat.</t>
+          <t>Deve ser aberto um chamado para cada solicitação/cliente.</t>
         </is>
       </c>
       <c r="S669" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T669" s="1" t="n"/>
@@ -51313,26 +51303,26 @@
     </row>
     <row r="670">
       <c r="A670" s="1" t="n">
-        <v>83249</v>
+        <v>81227</v>
       </c>
       <c r="B670" s="1" t="inlineStr">
         <is>
-          <t>Regularização</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C670" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D670" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - GC</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="E670" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">6533 - OFICIALMED BOM JESUS PRODUTOS FARMACÊUTICOS E APOIO ADMINISTRATIVO LTDA - Renovação do Alvará </t>
+          <t>Empresa 5988 - Maurício Toniati - Cliente que haviamos feito a apuração incorreta de pis e cofins - Foi feito parcelamento , mais depois da retificação dos impostos não teria imposto a apagar. Gerei um relatório da situação fiscal e não consta nenhuma informação referente à Malha Fiscal, apenas a indicação de Parcelamento Suspenso.Poderia verificar, por gentileza, se há algum procedimento adicional que precise ser realizado ou alguma outra consulta que devemos efetuar?</t>
         </is>
       </c>
       <c r="F670" s="1" t="n">
@@ -51341,122 +51331,195 @@
       <c r="G670" s="1" t="n"/>
       <c r="H670" s="1" t="inlineStr">
         <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
+      <c r="I670" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J670" s="2" t="n">
+        <v>46223.69836307871</v>
+      </c>
+      <c r="K670" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="L670" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M670" s="1" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="N670" s="2" t="n">
+        <v>46232.73233688658</v>
+      </c>
+      <c r="O670" s="1" t="n"/>
+      <c r="P670" s="1" t="n"/>
+      <c r="Q670" s="1" t="inlineStr"/>
+      <c r="R670" s="1" t="inlineStr">
+        <is>
+          <t>Verificando via chat.</t>
+        </is>
+      </c>
+      <c r="S670" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T670" s="1" t="n"/>
+      <c r="U670" s="1" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>83249</v>
+      </c>
+      <c r="B671" s="1" t="inlineStr">
+        <is>
+          <t>Regularização</t>
+        </is>
+      </c>
+      <c r="C671" s="1" t="inlineStr">
+        <is>
+          <t>Prefeitura</t>
+        </is>
+      </c>
+      <c r="D671" s="1" t="inlineStr">
+        <is>
+          <t>SANTOS - GC</t>
+        </is>
+      </c>
+      <c r="E671" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6533 - OFICIALMED BOM JESUS PRODUTOS FARMACÊUTICOS E APOIO ADMINISTRATIVO LTDA - Renovação do Alvará </t>
+        </is>
+      </c>
+      <c r="F671" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G671" s="1" t="n"/>
+      <c r="H671" s="1" t="inlineStr">
+        <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="I670" s="1" t="inlineStr">
+      <c r="I671" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J670" s="2" t="n">
+      <c r="J671" s="2" t="n">
         <v>46265.38856802083</v>
       </c>
-      <c r="K670" s="2" t="n">
+      <c r="K671" s="2" t="n">
         <v>46267</v>
       </c>
-      <c r="L670" s="1" t="inlineStr">
+      <c r="L671" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M670" s="1" t="inlineStr">
+      <c r="M671" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N670" s="2" t="n">
+      <c r="N671" s="2" t="n">
         <v>46267.71143642361</v>
       </c>
-      <c r="O670" s="1" t="n"/>
-      <c r="P670" s="2" t="n">
+      <c r="O671" s="1" t="n"/>
+      <c r="P671" s="2" t="n">
         <v>46288.52680405093</v>
       </c>
-      <c r="Q670" s="1" t="inlineStr">
+      <c r="Q671" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R670" s="1" t="inlineStr">
+      <c r="R671" s="1" t="inlineStr">
         <is>
           <t>Boa tarde.
 Qual alvará?
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S670" s="1" t="inlineStr">
+      <c r="S671" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T670" s="1" t="n"/>
-      <c r="U670" s="1" t="inlineStr"/>
-    </row>
-    <row r="671">
-      <c r="A671" s="1" t="n">
+      <c r="T671" s="1" t="n"/>
+      <c r="U671" s="1" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
         <v>83452</v>
       </c>
-      <c r="B671" s="1" t="inlineStr">
+      <c r="B672" s="1" t="inlineStr">
         <is>
           <t>Encerramento de Empresa</t>
         </is>
       </c>
-      <c r="C671" s="1" t="inlineStr">
+      <c r="C672" s="1" t="inlineStr">
         <is>
           <t>Eireli - Comércio</t>
         </is>
       </c>
-      <c r="D671" s="1" t="inlineStr">
+      <c r="D672" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E671" s="1" t="inlineStr">
+      <c r="E672" s="1" t="inlineStr">
         <is>
           <t>Pós Ata de reunião - 2876 -  BAR E LANCHES JUVENTUDE DE PRAIA GRANDE- EIRELI  Juventude	Encerramento Empresa 	O cliente solicitou o encerramento da empresa Juventude, ficando registrada a pendência para avaliação e condução dos procedimentos fiscais, cadastrais e societários necessários. 31/08/2026</t>
         </is>
       </c>
-      <c r="F671" s="1" t="n">
+      <c r="F672" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G671" s="1" t="n"/>
-      <c r="H671" s="1" t="inlineStr">
+      <c r="G672" s="1" t="n"/>
+      <c r="H672" s="1" t="inlineStr">
         <is>
           <t>Ronaldo Dias</t>
         </is>
       </c>
-      <c r="I671" s="1" t="inlineStr">
+      <c r="I672" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J671" s="2" t="n">
+      <c r="J672" s="2" t="n">
         <v>46267.40487928241</v>
       </c>
-      <c r="K671" s="2" t="n">
+      <c r="K672" s="2" t="n">
         <v>46269</v>
       </c>
-      <c r="L671" s="1" t="inlineStr">
+      <c r="L672" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M671" s="1" t="inlineStr">
+      <c r="M672" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N671" s="1" t="n"/>
-      <c r="O671" s="1" t="n"/>
-      <c r="P671" s="2" t="n">
+      <c r="N672" s="1" t="n"/>
+      <c r="O672" s="1" t="n"/>
+      <c r="P672" s="2" t="n">
         <v>46268.72386732639</v>
       </c>
-      <c r="Q671" s="1" t="inlineStr">
+      <c r="Q672" s="1" t="inlineStr">
         <is>
           <t>Ronaldo Dias</t>
         </is>
       </c>
-      <c r="R671" s="1" t="inlineStr">
+      <c r="R672" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Anexo proposta e abaixo as condições para dar andamento.
 1.	Quadro de pessoal: não possuir funcionários ativos — todos os contratos de trabalho devem estar encerrados e as obrigações trabalhistas devidamente quitadas;
@@ -51467,320 +51530,320 @@
 </t>
         </is>
       </c>
-      <c r="S671" s="1" t="inlineStr">
+      <c r="S672" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T671" s="1" t="n"/>
-      <c r="U671" s="1" t="inlineStr"/>
-    </row>
-    <row r="672">
-      <c r="A672" s="1" t="n">
+      <c r="T672" s="1" t="n"/>
+      <c r="U672" s="1" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
         <v>83530</v>
       </c>
-      <c r="B672" s="1" t="inlineStr">
+      <c r="B673" s="1" t="inlineStr">
         <is>
           <t>Parcelamento RFB</t>
         </is>
       </c>
-      <c r="C672" s="1" t="inlineStr">
+      <c r="C673" s="1" t="inlineStr">
         <is>
           <t>Simplificado</t>
         </is>
       </c>
-      <c r="D672" s="1" t="inlineStr">
+      <c r="D673" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E672" s="1" t="inlineStr">
+      <c r="E673" s="1" t="inlineStr">
         <is>
           <t>6296 - GRAND DIVINO COMERCIO DE ALIMENTOS LTDA - Por gentileza simular em 12 vezes os debitos em aberto na RFB. obrigada.</t>
         </is>
       </c>
-      <c r="F672" s="1" t="n">
+      <c r="F673" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G672" s="1" t="n"/>
-      <c r="H672" s="1" t="inlineStr">
+      <c r="G673" s="1" t="n"/>
+      <c r="H673" s="1" t="inlineStr">
         <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="I672" s="1" t="inlineStr">
+      <c r="I673" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J672" s="2" t="n">
+      <c r="J673" s="2" t="n">
         <v>46267.7888037037</v>
       </c>
-      <c r="K672" s="2" t="n">
+      <c r="K673" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="L672" s="1" t="inlineStr">
+      <c r="L673" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M672" s="1" t="inlineStr">
+      <c r="M673" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N672" s="1" t="n"/>
-      <c r="O672" s="1" t="n"/>
-      <c r="P672" s="2" t="n">
+      <c r="N673" s="1" t="n"/>
+      <c r="O673" s="1" t="n"/>
+      <c r="P673" s="2" t="n">
         <v>46280.77879980324</v>
       </c>
-      <c r="Q672" s="1" t="inlineStr">
+      <c r="Q673" s="1" t="inlineStr">
         <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="R672" s="1" t="inlineStr">
+      <c r="R673" s="1" t="inlineStr">
         <is>
           <t>Rafa, boa tarde!
 Segue simulado e proposta em anexo.
 Por gentileza, verificar a omissão de DCTFWEB 12/2025.</t>
         </is>
       </c>
-      <c r="S672" s="1" t="inlineStr">
+      <c r="S673" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T672" s="1" t="n"/>
-      <c r="U672" s="1" t="inlineStr"/>
-    </row>
-    <row r="673">
-      <c r="A673" s="1" t="n">
+      <c r="T673" s="1" t="n"/>
+      <c r="U673" s="1" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="n">
         <v>83563</v>
       </c>
-      <c r="B673" s="1" t="inlineStr">
+      <c r="B674" s="1" t="inlineStr">
         <is>
           <t>Processo de Prefeitura</t>
         </is>
       </c>
-      <c r="C673" s="1" t="inlineStr">
+      <c r="C674" s="1" t="inlineStr">
         <is>
           <t>Geral</t>
         </is>
       </c>
-      <c r="D673" s="1" t="inlineStr">
+      <c r="D674" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E673" s="1" t="inlineStr">
+      <c r="E674" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">3173 - Providenciar o Alvará/CLI por favor </t>
         </is>
       </c>
-      <c r="F673" s="1" t="n">
+      <c r="F674" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G673" s="1" t="n"/>
-      <c r="H673" s="1" t="inlineStr">
+      <c r="G674" s="1" t="n"/>
+      <c r="H674" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="I673" s="1" t="inlineStr">
+      <c r="I674" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J673" s="2" t="n">
+      <c r="J674" s="2" t="n">
         <v>46268.54673834491</v>
       </c>
-      <c r="K673" s="2" t="n">
+      <c r="K674" s="2" t="n">
         <v>46273</v>
       </c>
-      <c r="L673" s="1" t="inlineStr">
+      <c r="L674" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M673" s="1" t="inlineStr">
+      <c r="M674" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N673" s="2" t="n">
+      <c r="N674" s="2" t="n">
         <v>46268.67929375</v>
       </c>
-      <c r="O673" s="1" t="n"/>
-      <c r="P673" s="2" t="n">
+      <c r="O674" s="1" t="n"/>
+      <c r="P674" s="2" t="n">
         <v>46275.64996585648</v>
       </c>
-      <c r="Q673" s="1" t="inlineStr">
+      <c r="Q674" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R673" s="1" t="inlineStr">
+      <c r="R674" s="1" t="inlineStr">
         <is>
           <t>Boa tarde.
 Providenciando a Viabilidade.
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S673" s="1" t="inlineStr">
+      <c r="S674" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T673" s="1" t="n"/>
-      <c r="U673" s="1" t="inlineStr"/>
-    </row>
-    <row r="674">
-      <c r="A674" s="1" t="n">
+      <c r="T674" s="1" t="n"/>
+      <c r="U674" s="1" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="n">
         <v>83564</v>
       </c>
-      <c r="B674" s="1" t="inlineStr">
+      <c r="B675" s="1" t="inlineStr">
         <is>
           <t>Processo de Prefeitura</t>
         </is>
       </c>
-      <c r="C674" s="1" t="inlineStr">
+      <c r="C675" s="1" t="inlineStr">
         <is>
           <t>Geral</t>
         </is>
       </c>
-      <c r="D674" s="1" t="inlineStr">
+      <c r="D675" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E674" s="1" t="inlineStr">
+      <c r="E675" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">3176 - renovar o Alvará/CLi por favor </t>
         </is>
       </c>
-      <c r="F674" s="1" t="n">
+      <c r="F675" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G674" s="1" t="n"/>
-      <c r="H674" s="1" t="inlineStr">
+      <c r="G675" s="1" t="n"/>
+      <c r="H675" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="I674" s="1" t="inlineStr">
+      <c r="I675" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J674" s="2" t="n">
+      <c r="J675" s="2" t="n">
         <v>46268.54783070602</v>
       </c>
-      <c r="K674" s="2" t="n">
+      <c r="K675" s="2" t="n">
         <v>46273</v>
       </c>
-      <c r="L674" s="1" t="inlineStr">
+      <c r="L675" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M674" s="1" t="inlineStr">
+      <c r="M675" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N674" s="2" t="n">
+      <c r="N675" s="2" t="n">
         <v>46268.67942207176</v>
       </c>
-      <c r="O674" s="1" t="n"/>
-      <c r="P674" s="2" t="n">
+      <c r="O675" s="1" t="n"/>
+      <c r="P675" s="2" t="n">
         <v>46275.65324540509</v>
       </c>
-      <c r="Q674" s="1" t="inlineStr">
+      <c r="Q675" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R674" s="1" t="inlineStr">
+      <c r="R675" s="1" t="inlineStr">
         <is>
           <t>Boa tarde.
 Providenciando a Viabilidade.
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S674" s="1" t="inlineStr">
+      <c r="S675" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T674" s="1" t="n"/>
-      <c r="U674" s="1" t="inlineStr"/>
-    </row>
-    <row r="675">
-      <c r="A675" s="1" t="n">
+      <c r="T675" s="1" t="n"/>
+      <c r="U675" s="1" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="n">
         <v>83565</v>
       </c>
-      <c r="B675" s="1" t="inlineStr">
+      <c r="B676" s="1" t="inlineStr">
         <is>
           <t>Processo de Prefeitura</t>
         </is>
       </c>
-      <c r="C675" s="1" t="inlineStr">
+      <c r="C676" s="1" t="inlineStr">
         <is>
           <t>Geral</t>
         </is>
       </c>
-      <c r="D675" s="1" t="inlineStr">
+      <c r="D676" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E675" s="1" t="inlineStr">
+      <c r="E676" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">3177 - Renovação de Alvará/cli por favor </t>
         </is>
       </c>
-      <c r="F675" s="1" t="n">
+      <c r="F676" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G675" s="1" t="n"/>
-      <c r="H675" s="1" t="inlineStr">
+      <c r="G676" s="1" t="n"/>
+      <c r="H676" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="I675" s="1" t="inlineStr">
+      <c r="I676" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J675" s="2" t="n">
+      <c r="J676" s="2" t="n">
         <v>46268.54870725694</v>
       </c>
-      <c r="K675" s="2" t="n">
+      <c r="K676" s="2" t="n">
         <v>46273</v>
       </c>
-      <c r="L675" s="1" t="inlineStr">
+      <c r="L676" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M675" s="1" t="inlineStr">
+      <c r="M676" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N675" s="1" t="n"/>
-      <c r="O675" s="1" t="n"/>
-      <c r="P675" s="2" t="n">
+      <c r="N676" s="1" t="n"/>
+      <c r="O676" s="1" t="n"/>
+      <c r="P676" s="2" t="n">
         <v>46268.56602326389</v>
       </c>
-      <c r="Q675" s="1" t="inlineStr">
+      <c r="Q676" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R675" s="1" t="inlineStr">
+      <c r="R676" s="1" t="inlineStr">
         <is>
           <t>Boa tarde.
 O endereço do AVCB ( AVENIDA CABUÇU Nº: 377) e o endereço da empresa (RUA JOAO MARIANO, 193).
@@ -51788,164 +51851,87 @@
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S675" s="1" t="inlineStr">
+      <c r="S676" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T675" s="1" t="n"/>
-      <c r="U675" s="1" t="inlineStr"/>
-    </row>
-    <row r="676">
-      <c r="A676" s="1" t="n">
+      <c r="T676" s="1" t="n"/>
+      <c r="U676" s="1" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="n">
         <v>83583</v>
       </c>
-      <c r="B676" s="1" t="inlineStr">
+      <c r="B677" s="1" t="inlineStr">
         <is>
           <t>Processo de Prefeitura</t>
         </is>
       </c>
-      <c r="C676" s="1" t="inlineStr">
+      <c r="C677" s="1" t="inlineStr">
         <is>
           <t>Geral</t>
         </is>
       </c>
-      <c r="D676" s="1" t="inlineStr">
+      <c r="D677" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E676" s="1" t="inlineStr">
+      <c r="E677" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">3174 - Ronovação do Alvará/Cli por favor </t>
         </is>
       </c>
-      <c r="F676" s="1" t="n">
+      <c r="F677" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G676" s="1" t="n"/>
-      <c r="H676" s="1" t="inlineStr">
+      <c r="G677" s="1" t="n"/>
+      <c r="H677" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="I676" s="1" t="inlineStr">
+      <c r="I677" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J676" s="2" t="n">
+      <c r="J677" s="2" t="n">
         <v>46268.69685413194</v>
       </c>
-      <c r="K676" s="2" t="n">
+      <c r="K677" s="2" t="n">
         <v>46273</v>
       </c>
-      <c r="L676" s="1" t="inlineStr">
+      <c r="L677" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M676" s="1" t="inlineStr">
+      <c r="M677" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N676" s="2" t="n">
+      <c r="N677" s="2" t="n">
         <v>46273.69585717592</v>
       </c>
-      <c r="O676" s="1" t="n"/>
-      <c r="P676" s="2" t="n">
+      <c r="O677" s="1" t="n"/>
+      <c r="P677" s="2" t="n">
         <v>46282.53441554398</v>
       </c>
-      <c r="Q676" s="1" t="inlineStr">
+      <c r="Q677" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="R676" s="1" t="inlineStr">
+      <c r="R677" s="1" t="inlineStr">
         <is>
           <t>Boa tarde,
 Aguardando a aprovação da viabilidade.
 Atenciosamente</t>
         </is>
       </c>
-      <c r="S676" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T676" s="1" t="n"/>
-      <c r="U676" s="1" t="inlineStr"/>
-    </row>
-    <row r="677">
-      <c r="A677" s="1" t="n">
-        <v>83704</v>
-      </c>
-      <c r="B677" s="1" t="inlineStr">
-        <is>
-          <t>Levantamento de Débitos Mensal</t>
-        </is>
-      </c>
-      <c r="C677" s="1" t="inlineStr">
-        <is>
-          <t>PGFN</t>
-        </is>
-      </c>
-      <c r="D677" s="1" t="inlineStr">
-        <is>
-          <t>SANTOS - GC</t>
-        </is>
-      </c>
-      <c r="E677" s="1" t="inlineStr">
-        <is>
-          <t>4200 - Henrique Leone- Por gentileza simular o parcelamento dos débitos que são mencionados na carta em anexo por favor.</t>
-        </is>
-      </c>
-      <c r="F677" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G677" s="1" t="n"/>
-      <c r="H677" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="I677" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J677" s="2" t="n">
-        <v>46274.42889741898</v>
-      </c>
-      <c r="K677" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="L677" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M677" s="1" t="inlineStr">
-        <is>
-          <t>Rafaella Massuia</t>
-        </is>
-      </c>
-      <c r="N677" s="1" t="n"/>
-      <c r="O677" s="1" t="n"/>
-      <c r="P677" s="2" t="n">
-        <v>46275.83228032407</v>
-      </c>
-      <c r="Q677" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="R677" s="1" t="inlineStr">
-        <is>
-          <t>Segue proposta e simulado para parcelamento das inscrições 80 6 26 082503-45, 80 2 26 064060-04 e 80 2 26 064396-03, referente a notificação recebida.</t>
-        </is>
-      </c>
       <c r="S677" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -51956,26 +51942,26 @@
     </row>
     <row r="678">
       <c r="A678" s="1" t="n">
-        <v>83052</v>
+        <v>83704</v>
       </c>
       <c r="B678" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Levantamento de Débitos Mensal</t>
         </is>
       </c>
       <c r="C678" s="1" t="inlineStr">
         <is>
-          <t>Divida Ativa ICMS</t>
+          <t>PGFN</t>
         </is>
       </c>
       <c r="D678" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>SANTOS - GC</t>
         </is>
       </c>
       <c r="E678" s="1" t="inlineStr">
         <is>
-          <t>Empresa 6070 - Megacar. Há um débito na competência 05/2026, referente a um erro na transmissão da DeSTDA, em que foi informado indevidamente o valor de R$ 25.769,04.A declaração foi retificada em 20/08/2026, sem esse valor, porém a informação ainda não foi atualizada na SEFAZ.Solicito por gentileza que verifiquem se há alguma forma de agilizar a regularização dessa pendência.Seguem anexos o comprovante da DeSTDA retificada em 20/08/2026 e os registros que comprovam que não houve compras de fora do estado no período.</t>
+          <t>4200 - Henrique Leone- Por gentileza simular o parcelamento dos débitos que são mencionados na carta em anexo por favor.</t>
         </is>
       </c>
       <c r="F678" s="1" t="n">
@@ -51984,7 +51970,7 @@
       <c r="G678" s="1" t="n"/>
       <c r="H678" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I678" s="1" t="inlineStr">
@@ -51993,35 +51979,39 @@
         </is>
       </c>
       <c r="J678" s="2" t="n">
-        <v>46260.53714988426</v>
+        <v>46274.42889741898</v>
       </c>
       <c r="K678" s="2" t="n">
-        <v>46261</v>
+        <v>46276</v>
       </c>
       <c r="L678" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M678" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
-      <c r="N678" s="2" t="n">
-        <v>46288.64739603009</v>
-      </c>
+          <t>Rafaella Massuia</t>
+        </is>
+      </c>
+      <c r="N678" s="1" t="n"/>
       <c r="O678" s="1" t="n"/>
-      <c r="P678" s="1" t="n"/>
-      <c r="Q678" s="1" t="inlineStr"/>
+      <c r="P678" s="2" t="n">
+        <v>46275.83228032407</v>
+      </c>
+      <c r="Q678" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="R678" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por favor, verificar se foi aprovada a retificação. </t>
+          <t>Segue proposta e simulado para parcelamento das inscrições 80 6 26 082503-45, 80 2 26 064060-04 e 80 2 26 064396-03, referente a notificação recebida.</t>
         </is>
       </c>
       <c r="S678" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T678" s="1" t="n"/>
@@ -52029,11 +52019,11 @@
     </row>
     <row r="679">
       <c r="A679" s="1" t="n">
-        <v>83130</v>
+        <v>83052</v>
       </c>
       <c r="B679" s="1" t="inlineStr">
         <is>
-          <t>Levantamento de Débitos</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C679" s="1" t="inlineStr">
@@ -52043,12 +52033,12 @@
       </c>
       <c r="D679" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E679" s="1" t="inlineStr">
         <is>
-          <t>Cliente solicitou o levantamento de débitos da empresa 5551 - L.B. Hortifruti</t>
+          <t>Empresa 6070 - Megacar. Há um débito na competência 05/2026, referente a um erro na transmissão da DeSTDA, em que foi informado indevidamente o valor de R$ 25.769,04.A declaração foi retificada em 20/08/2026, sem esse valor, porém a informação ainda não foi atualizada na SEFAZ.Solicito por gentileza que verifiquem se há alguma forma de agilizar a regularização dessa pendência.Seguem anexos o comprovante da DeSTDA retificada em 20/08/2026 e os registros que comprovam que não houve compras de fora do estado no período.</t>
         </is>
       </c>
       <c r="F679" s="1" t="n">
@@ -52057,189 +52047,195 @@
       <c r="G679" s="1" t="n"/>
       <c r="H679" s="1" t="inlineStr">
         <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
+      <c r="I679" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J679" s="2" t="n">
+        <v>46260.53714988426</v>
+      </c>
+      <c r="K679" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="L679" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M679" s="1" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
+      <c r="N679" s="2" t="n">
+        <v>46288.64739603009</v>
+      </c>
+      <c r="O679" s="1" t="n"/>
+      <c r="P679" s="1" t="n"/>
+      <c r="Q679" s="1" t="inlineStr"/>
+      <c r="R679" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por favor, verificar se foi aprovada a retificação. </t>
+        </is>
+      </c>
+      <c r="S679" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T679" s="1" t="n"/>
+      <c r="U679" s="1" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="n">
+        <v>83130</v>
+      </c>
+      <c r="B680" s="1" t="inlineStr">
+        <is>
+          <t>Levantamento de Débitos</t>
+        </is>
+      </c>
+      <c r="C680" s="1" t="inlineStr">
+        <is>
+          <t>Divida Ativa ICMS</t>
+        </is>
+      </c>
+      <c r="D680" s="1" t="inlineStr">
+        <is>
+          <t>SANTOS - ADM</t>
+        </is>
+      </c>
+      <c r="E680" s="1" t="inlineStr">
+        <is>
+          <t>Cliente solicitou o levantamento de débitos da empresa 5551 - L.B. Hortifruti</t>
+        </is>
+      </c>
+      <c r="F680" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G680" s="1" t="n"/>
+      <c r="H680" s="1" t="inlineStr">
+        <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="I679" s="1" t="inlineStr">
+      <c r="I680" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J679" s="2" t="n">
+      <c r="J680" s="2" t="n">
         <v>46261.51850563657</v>
       </c>
-      <c r="K679" s="2" t="n">
+      <c r="K680" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="L679" s="1" t="inlineStr">
+      <c r="L680" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M679" s="1" t="inlineStr">
+      <c r="M680" s="1" t="inlineStr">
         <is>
           <t>Lidia Tavares</t>
         </is>
       </c>
-      <c r="N679" s="1" t="n"/>
-      <c r="O679" s="1" t="n"/>
-      <c r="P679" s="2" t="n">
+      <c r="N680" s="1" t="n"/>
+      <c r="O680" s="1" t="n"/>
+      <c r="P680" s="2" t="n">
         <v>46280.77373244213</v>
       </c>
-      <c r="Q679" s="1" t="inlineStr">
+      <c r="Q680" s="1" t="inlineStr">
         <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="R679" s="1" t="inlineStr">
+      <c r="R680" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Lidia, bom dia!
 Essa empresa é filia, está correto a solicitação?
 Os débitos federais e estaduais são unificados com a matriz. </t>
         </is>
       </c>
-      <c r="S679" s="1" t="inlineStr">
+      <c r="S680" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="T679" s="1" t="n"/>
-      <c r="U679" s="1" t="inlineStr"/>
-    </row>
-    <row r="680">
-      <c r="A680" s="1" t="n">
+      <c r="T680" s="1" t="n"/>
+      <c r="U680" s="1" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n">
         <v>83924</v>
       </c>
-      <c r="B680" s="1" t="inlineStr">
+      <c r="B681" s="1" t="inlineStr">
         <is>
           <t>Regularização</t>
         </is>
       </c>
-      <c r="C680" s="1" t="inlineStr">
+      <c r="C681" s="1" t="inlineStr">
         <is>
           <t>Prefeitura</t>
         </is>
       </c>
-      <c r="D680" s="1" t="inlineStr">
+      <c r="D681" s="1" t="inlineStr">
         <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="E680" s="1" t="inlineStr">
+      <c r="E681" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">3828 - Supermercado Popular - Renovação do Cli </t>
         </is>
       </c>
-      <c r="F680" s="1" t="n">
+      <c r="F681" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G680" s="1" t="n"/>
-      <c r="H680" s="1" t="inlineStr">
+      <c r="G681" s="1" t="n"/>
+      <c r="H681" s="1" t="inlineStr">
         <is>
           <t>Edson Silva</t>
         </is>
       </c>
-      <c r="I680" s="1" t="inlineStr">
+      <c r="I681" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J680" s="2" t="n">
+      <c r="J681" s="2" t="n">
         <v>46279.40335633101</v>
       </c>
-      <c r="K680" s="2" t="n">
+      <c r="K681" s="2" t="n">
         <v>46281</v>
       </c>
-      <c r="L680" s="1" t="inlineStr">
+      <c r="L681" s="1" t="inlineStr">
         <is>
           <t>Em Atendimento</t>
         </is>
       </c>
-      <c r="M680" s="1" t="inlineStr">
+      <c r="M681" s="1" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="N680" s="2" t="n">
+      <c r="N681" s="2" t="n">
         <v>46281.55550413195</v>
       </c>
-      <c r="O680" s="1" t="n"/>
-      <c r="P680" s="1" t="n"/>
-      <c r="Q680" s="1" t="inlineStr"/>
-      <c r="R680" s="1" t="inlineStr">
+      <c r="O681" s="1" t="n"/>
+      <c r="P681" s="1" t="n"/>
+      <c r="Q681" s="1" t="inlineStr"/>
+      <c r="R681" s="1" t="inlineStr">
         <is>
           <t>Boa tarde.
 Aguardando o deferimento.
 Atenciosamente,</t>
         </is>
       </c>
-      <c r="S680" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T680" s="1" t="n"/>
-      <c r="U680" s="1" t="inlineStr"/>
-    </row>
-    <row r="681">
-      <c r="A681" s="1" t="n">
-        <v>83981</v>
-      </c>
-      <c r="B681" s="1" t="inlineStr">
-        <is>
-          <t>Regularização</t>
-        </is>
-      </c>
-      <c r="C681" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="D681" s="1" t="inlineStr">
-        <is>
-          <t>EF - INDUSTRIA</t>
-        </is>
-      </c>
-      <c r="E681" s="1" t="inlineStr">
-        <is>
-          <t>3262 - JCV - GNRE de ALPEC - AlagoasConforme solicitação no e-mail anexo, é necessário providenciar o preenchimento do REDAR, emissão da taxa e protocolar do processo junto à SEFAZ/AL.</t>
-        </is>
-      </c>
-      <c r="F681" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G681" s="1" t="n"/>
-      <c r="H681" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
-      <c r="I681" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J681" s="2" t="n">
-        <v>46280.38897322916</v>
-      </c>
-      <c r="K681" s="2" t="n">
-        <v>46282</v>
-      </c>
-      <c r="L681" s="1" t="inlineStr">
-        <is>
-          <t>Esperando Atendimento</t>
-        </is>
-      </c>
-      <c r="M681" s="1" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
-      <c r="N681" s="1" t="n"/>
-      <c r="O681" s="1" t="n"/>
-      <c r="P681" s="1" t="n"/>
-      <c r="Q681" s="1" t="inlineStr"/>
-      <c r="R681" s="1" t="inlineStr"/>
       <c r="S681" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -52250,7 +52246,7 @@
     </row>
     <row r="682">
       <c r="A682" s="1" t="n">
-        <v>84060</v>
+        <v>83981</v>
       </c>
       <c r="B682" s="1" t="inlineStr">
         <is>
@@ -52269,7 +52265,7 @@
       </c>
       <c r="E682" s="1" t="inlineStr">
         <is>
-          <t>5132 - CABEXPRESS - Notificação GNRE UF MT.Nosso cliente recebeu uma notificação da SEFAZ de MT sobre o não pagamento da GNRE de uma venda referente à NF-e 45.008 que já havia sido recolhido em 04/09/2026, 10 dias antes da emissão do TAD em 14/09/2026.O valor principal cobrado no TAD é exatamente o mesmo valor que consta na GNRE paga R$ 1.204,18. Porém, o TAD indica que a fiscalização não reconheceu/localizou esse recolhimento no momento da abordagem, e por isso constituiu o débito e acrescentou multa.O documento informa a possibilidade de provar a regularidade, mas não apresenta de forma clara, um canal eletrônico específico, e-mail ou botão/link para enviar os comprovantes.Segue anexo o e-mail do cliente com a GNRE e o comprovante bancário para que vejam a possibilidade de solicitar a baixa/cancelamento da exigência TAD.</t>
+          <t>3262 - JCV - GNRE de ALPEC - AlagoasConforme solicitação no e-mail anexo, é necessário providenciar o preenchimento do REDAR, emissão da taxa e protocolar do processo junto à SEFAZ/AL.</t>
         </is>
       </c>
       <c r="F682" s="1" t="n">
@@ -52287,14 +52283,14 @@
         </is>
       </c>
       <c r="J682" s="2" t="n">
-        <v>46281.40508255787</v>
+        <v>46280.38897322916</v>
       </c>
       <c r="K682" s="2" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="L682" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M682" s="1" t="inlineStr">
@@ -52302,17 +52298,11 @@
           <t>Ricardo Fischer</t>
         </is>
       </c>
-      <c r="N682" s="2" t="n">
-        <v>46287.76335497685</v>
-      </c>
+      <c r="N682" s="1" t="n"/>
       <c r="O682" s="1" t="n"/>
       <c r="P682" s="1" t="n"/>
       <c r="Q682" s="1" t="inlineStr"/>
-      <c r="R682" s="1" t="inlineStr">
-        <is>
-          <t>Protocolado processo de baixa do auto, acompanhando o processo.</t>
-        </is>
-      </c>
+      <c r="R682" s="1" t="inlineStr"/>
       <c r="S682" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -52323,26 +52313,26 @@
     </row>
     <row r="683">
       <c r="A683" s="1" t="n">
-        <v>84230</v>
+        <v>84060</v>
       </c>
       <c r="B683" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Guia</t>
+          <t>Regularização</t>
         </is>
       </c>
       <c r="C683" s="1" t="inlineStr">
         <is>
-          <t>DARF</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="D683" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E683" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde tudo bem?O cliente da empresa 1404 - ASMJ pagou um DARF referente ao mês 03/2026 no código incorreto, foi pago o DARF no valor de R$ 839,61 no código 2372 - CSLL, porem o correto seria o código 2089 - IRPJ Lucro presumido, se possível poderiam efetuar o REDARF por gentileza. Segue comprovante de arrecadação no código incorreto</t>
+          <t>5132 - CABEXPRESS - Notificação GNRE UF MT.Nosso cliente recebeu uma notificação da SEFAZ de MT sobre o não pagamento da GNRE de uma venda referente à NF-e 45.008 que já havia sido recolhido em 04/09/2026, 10 dias antes da emissão do TAD em 14/09/2026.O valor principal cobrado no TAD é exatamente o mesmo valor que consta na GNRE paga R$ 1.204,18. Porém, o TAD indica que a fiscalização não reconheceu/localizou esse recolhimento no momento da abordagem, e por isso constituiu o débito e acrescentou multa.O documento informa a possibilidade de provar a regularidade, mas não apresenta de forma clara, um canal eletrônico específico, e-mail ou botão/link para enviar os comprovantes.Segue anexo o e-mail do cliente com a GNRE e o comprovante bancário para que vejam a possibilidade de solicitar a baixa/cancelamento da exigência TAD.</t>
         </is>
       </c>
       <c r="F683" s="1" t="n">
@@ -52351,7 +52341,7 @@
       <c r="G683" s="1" t="n"/>
       <c r="H683" s="1" t="inlineStr">
         <is>
-          <t>Karina Dantas</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I683" s="1" t="inlineStr">
@@ -52360,10 +52350,10 @@
         </is>
       </c>
       <c r="J683" s="2" t="n">
-        <v>46286.69414984954</v>
+        <v>46281.40508255787</v>
       </c>
       <c r="K683" s="2" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="L683" s="1" t="inlineStr">
         <is>
@@ -52372,169 +52362,175 @@
       </c>
       <c r="M683" s="1" t="inlineStr">
         <is>
-          <t>Vitor de Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="N683" s="2" t="n">
-        <v>46287.59273383102</v>
+        <v>46287.76335497685</v>
       </c>
       <c r="O683" s="1" t="n"/>
       <c r="P683" s="1" t="n"/>
       <c r="Q683" s="1" t="inlineStr"/>
       <c r="R683" s="1" t="inlineStr">
         <is>
+          <t>Protocolado processo de baixa do auto, acompanhando o processo.</t>
+        </is>
+      </c>
+      <c r="S683" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T683" s="1" t="n"/>
+      <c r="U683" s="1" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>84230</v>
+      </c>
+      <c r="B684" s="1" t="inlineStr">
+        <is>
+          <t>Retificação de Guia</t>
+        </is>
+      </c>
+      <c r="C684" s="1" t="inlineStr">
+        <is>
+          <t>DARF</t>
+        </is>
+      </c>
+      <c r="D684" s="1" t="inlineStr">
+        <is>
+          <t>CTB - CONTÁBIL HOLDING</t>
+        </is>
+      </c>
+      <c r="E684" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde tudo bem?O cliente da empresa 1404 - ASMJ pagou um DARF referente ao mês 03/2026 no código incorreto, foi pago o DARF no valor de R$ 839,61 no código 2372 - CSLL, porem o correto seria o código 2089 - IRPJ Lucro presumido, se possível poderiam efetuar o REDARF por gentileza. Segue comprovante de arrecadação no código incorreto</t>
+        </is>
+      </c>
+      <c r="F684" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G684" s="1" t="n"/>
+      <c r="H684" s="1" t="inlineStr">
+        <is>
+          <t>Karina Dantas</t>
+        </is>
+      </c>
+      <c r="I684" s="1" t="inlineStr">
+        <is>
+          <t>PARALEGAL</t>
+        </is>
+      </c>
+      <c r="J684" s="2" t="n">
+        <v>46286.69414984954</v>
+      </c>
+      <c r="K684" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="L684" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M684" s="1" t="inlineStr">
+        <is>
+          <t>Vitor de Souza</t>
+        </is>
+      </c>
+      <c r="N684" s="2" t="n">
+        <v>46287.59273383102</v>
+      </c>
+      <c r="O684" s="1" t="n"/>
+      <c r="P684" s="1" t="n"/>
+      <c r="Q684" s="1" t="inlineStr"/>
+      <c r="R684" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Boa tarde!
 Redarf protocolado. </t>
         </is>
       </c>
-      <c r="S683" s="1" t="inlineStr">
+      <c r="S684" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T683" s="1" t="n"/>
-      <c r="U683" s="1" t="inlineStr"/>
-    </row>
-    <row r="684">
-      <c r="A684" s="1" t="n">
+      <c r="T684" s="1" t="n"/>
+      <c r="U684" s="1" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
         <v>84244</v>
       </c>
-      <c r="B684" s="1" t="inlineStr">
+      <c r="B685" s="1" t="inlineStr">
         <is>
           <t>Parcelamento RFB</t>
         </is>
       </c>
-      <c r="C684" s="1" t="inlineStr">
+      <c r="C685" s="1" t="inlineStr">
         <is>
           <t>Simplificado</t>
         </is>
       </c>
-      <c r="D684" s="1" t="inlineStr">
+      <c r="D685" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
-      <c r="E684" s="1" t="inlineStr">
+      <c r="E685" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bom dia, por gentileza encaminhar extrato dos parcelamentos do grupo Medical Discovery, cliente quer saber as parcelas que já foram pagas e o que ainda consta em aberto. </t>
         </is>
       </c>
-      <c r="F684" s="1" t="n">
+      <c r="F685" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G684" s="1" t="n"/>
-      <c r="H684" s="1" t="inlineStr">
+      <c r="G685" s="1" t="n"/>
+      <c r="H685" s="1" t="inlineStr">
         <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="I684" s="1" t="inlineStr">
+      <c r="I685" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="J684" s="2" t="n">
+      <c r="J685" s="2" t="n">
         <v>46287.38990729167</v>
       </c>
-      <c r="K684" s="2" t="n">
+      <c r="K685" s="2" t="n">
         <v>46289</v>
       </c>
-      <c r="L684" s="1" t="inlineStr">
+      <c r="L685" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M684" s="1" t="inlineStr">
+      <c r="M685" s="1" t="inlineStr">
         <is>
           <t>Beatriz Rangel</t>
         </is>
       </c>
-      <c r="N684" s="1" t="n"/>
-      <c r="O684" s="1" t="n"/>
-      <c r="P684" s="2" t="n">
+      <c r="N685" s="1" t="n"/>
+      <c r="O685" s="1" t="n"/>
+      <c r="P685" s="2" t="n">
         <v>46287.7625866551</v>
       </c>
-      <c r="Q684" s="1" t="inlineStr">
+      <c r="Q685" s="1" t="inlineStr">
         <is>
           <t>Karina Dantas</t>
         </is>
       </c>
-      <c r="R684" s="1" t="inlineStr">
+      <c r="R685" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Boa noite!
 Segue. </t>
         </is>
       </c>
-      <c r="S684" s="1" t="inlineStr">
+      <c r="S685" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
-        </is>
-      </c>
-      <c r="T684" s="1" t="n"/>
-      <c r="U684" s="1" t="inlineStr"/>
-    </row>
-    <row r="685">
-      <c r="A685" s="1" t="n">
-        <v>84305</v>
-      </c>
-      <c r="B685" s="1" t="inlineStr">
-        <is>
-          <t>Senha</t>
-        </is>
-      </c>
-      <c r="C685" s="1" t="inlineStr">
-        <is>
-          <t>Prefeitura</t>
-        </is>
-      </c>
-      <c r="D685" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
-      <c r="E685" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde, por gentileza disponibilizar login e senha da prefeitura referente a empresa 6204 - Cucinare FL91.Obrigada!</t>
-        </is>
-      </c>
-      <c r="F685" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G685" s="1" t="n"/>
-      <c r="H685" s="1" t="inlineStr">
-        <is>
-          <t>Sarah Amaro</t>
-        </is>
-      </c>
-      <c r="I685" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
-      <c r="J685" s="2" t="n">
-        <v>46287.64928989583</v>
-      </c>
-      <c r="K685" s="2" t="n">
-        <v>46289</v>
-      </c>
-      <c r="L685" s="1" t="inlineStr">
-        <is>
-          <t>Esperando Atendimento</t>
-        </is>
-      </c>
-      <c r="M685" s="1" t="inlineStr">
-        <is>
-          <t>Julia Medeiros</t>
-        </is>
-      </c>
-      <c r="N685" s="1" t="n"/>
-      <c r="O685" s="1" t="n"/>
-      <c r="P685" s="1" t="n"/>
-      <c r="Q685" s="1" t="inlineStr"/>
-      <c r="R685" s="1" t="inlineStr"/>
-      <c r="S685" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
         </is>
       </c>
       <c r="T685" s="1" t="n"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -1496,7 +1496,11 @@
           <t>Supermercado Kanashiro Ltda</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n"/>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -1510,7 +1514,7 @@
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M13" s="1" t="inlineStr">
@@ -1519,17 +1523,23 @@
         </is>
       </c>
       <c r="N13" s="1" t="n"/>
-      <c r="O13" s="1" t="n"/>
+      <c r="O13" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P13" s="1" t="n"/>
       <c r="Q13" s="1" t="inlineStr"/>
-      <c r="R13" s="1" t="n"/>
+      <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T13" s="1" t="n"/>
-      <c r="U13" s="1" t="inlineStr"/>
+      <c r="U13" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1677,7 +1687,9 @@
         </is>
       </c>
       <c r="N15" s="1" t="n"/>
-      <c r="O15" s="1" t="n"/>
+      <c r="O15" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P15" s="1" t="n"/>
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr"/>
@@ -1725,7 +1737,11 @@
           <t>BANDEIRANTES REFRIGERAÇÃO COMERCIAL LTDA</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n"/>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -1739,7 +1755,7 @@
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M16" s="1" t="inlineStr">
@@ -1749,16 +1765,30 @@
       </c>
       <c r="N16" s="1" t="n"/>
       <c r="O16" s="1" t="n"/>
-      <c r="P16" s="1" t="n"/>
-      <c r="Q16" s="1" t="inlineStr"/>
-      <c r="R16" s="1" t="n"/>
+      <c r="P16" s="2" t="n">
+        <v>46294.63901493056</v>
+      </c>
+      <c r="Q16" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
+      <c r="R16" s="1" t="inlineStr">
+        <is>
+          <t>Já foi ajustado e devolvido no analise.</t>
+        </is>
+      </c>
       <c r="S16" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T16" s="1" t="n"/>
-      <c r="U16" s="1" t="inlineStr"/>
+      <c r="U16" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2363,7 +2393,11 @@
           <t>XERYU'S IMPORTADORA E DISTRIBUIDORA DE ARTIGOS PARA VESTUARIO LTDA (MATRIZ)</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n"/>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -2377,7 +2411,7 @@
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M24" s="1" t="inlineStr">
@@ -2386,17 +2420,33 @@
         </is>
       </c>
       <c r="N24" s="1" t="n"/>
-      <c r="O24" s="1" t="n"/>
-      <c r="P24" s="1" t="n"/>
-      <c r="Q24" s="1" t="inlineStr"/>
-      <c r="R24" s="1" t="n"/>
+      <c r="O24" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>46294.65353996528</v>
+      </c>
+      <c r="Q24" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
+      <c r="R24" s="1" t="inlineStr">
+        <is>
+          <t>respondido via email desde 11:20 da manha</t>
+        </is>
+      </c>
       <c r="S24" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T24" s="1" t="n"/>
-      <c r="U24" s="1" t="inlineStr"/>
+      <c r="U24" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -3272,7 +3322,11 @@
           <t>NALLINI MANUTENÇÃO DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
-      <c r="H35" s="1" t="n"/>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -3286,7 +3340,7 @@
       </c>
       <c r="L35" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M35" s="1" t="inlineStr">
@@ -3295,17 +3349,23 @@
         </is>
       </c>
       <c r="N35" s="1" t="n"/>
-      <c r="O35" s="1" t="n"/>
+      <c r="O35" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P35" s="1" t="n"/>
       <c r="Q35" s="1" t="inlineStr"/>
-      <c r="R35" s="1" t="n"/>
+      <c r="R35" s="1" t="inlineStr"/>
       <c r="S35" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T35" s="1" t="n"/>
-      <c r="U35" s="1" t="inlineStr"/>
+      <c r="U35" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -4441,7 +4501,7 @@
       </c>
       <c r="L49" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M49" s="1" t="inlineStr">
@@ -4449,12 +4509,20 @@
           <t>Simone Marques</t>
         </is>
       </c>
-      <c r="N49" s="1" t="n"/>
+      <c r="N49" s="2" t="n">
+        <v>46190.46143564815</v>
+      </c>
       <c r="O49" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="P49" s="1" t="n"/>
-      <c r="Q49" s="1" t="inlineStr"/>
+      <c r="P49" s="2" t="n">
+        <v>46294.6576278588</v>
+      </c>
+      <c r="Q49" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="R49" s="1" t="inlineStr">
         <is>
           <t>Vai ser feito o levantamento</t>
@@ -4462,7 +4530,7 @@
       </c>
       <c r="S49" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T49" s="1" t="n"/>
@@ -6432,7 +6500,11 @@
           <t>V.B. MOREIRA LAVANDERIA</t>
         </is>
       </c>
-      <c r="H73" s="1" t="n"/>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -6446,7 +6518,7 @@
       </c>
       <c r="L73" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M73" s="1" t="inlineStr">
@@ -6455,17 +6527,23 @@
         </is>
       </c>
       <c r="N73" s="1" t="n"/>
-      <c r="O73" s="1" t="n"/>
+      <c r="O73" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P73" s="1" t="n"/>
       <c r="Q73" s="1" t="inlineStr"/>
-      <c r="R73" s="1" t="n"/>
+      <c r="R73" s="1" t="inlineStr"/>
       <c r="S73" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T73" s="1" t="n"/>
-      <c r="U73" s="1" t="inlineStr"/>
+      <c r="U73" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -9333,7 +9411,11 @@
           <t>YARA DESIGN E DECORAÇÃO LTDA</t>
         </is>
       </c>
-      <c r="H107" s="1" t="n"/>
+      <c r="H107" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
       <c r="I107" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -9347,7 +9429,7 @@
       </c>
       <c r="L107" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M107" s="1" t="inlineStr">
@@ -9356,17 +9438,23 @@
         </is>
       </c>
       <c r="N107" s="1" t="n"/>
-      <c r="O107" s="1" t="n"/>
+      <c r="O107" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P107" s="1" t="n"/>
       <c r="Q107" s="1" t="inlineStr"/>
-      <c r="R107" s="1" t="n"/>
+      <c r="R107" s="1" t="inlineStr"/>
       <c r="S107" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T107" s="1" t="n"/>
-      <c r="U107" s="1" t="inlineStr"/>
+      <c r="U107" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -12999,7 +13087,11 @@
           <t>GHOST KITCHENS ALIMENTOS LTDA</t>
         </is>
       </c>
-      <c r="H151" s="1" t="n"/>
+      <c r="H151" s="1" t="inlineStr">
+        <is>
+          <t>Edileide Dias</t>
+        </is>
+      </c>
       <c r="I151" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -13013,7 +13105,7 @@
       </c>
       <c r="L151" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M151" s="1" t="inlineStr">
@@ -13022,17 +13114,23 @@
         </is>
       </c>
       <c r="N151" s="1" t="n"/>
-      <c r="O151" s="1" t="n"/>
+      <c r="O151" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P151" s="1" t="n"/>
       <c r="Q151" s="1" t="inlineStr"/>
-      <c r="R151" s="1" t="n"/>
+      <c r="R151" s="1" t="inlineStr"/>
       <c r="S151" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T151" s="1" t="n"/>
-      <c r="U151" s="1" t="inlineStr"/>
+      <c r="U151" s="1" t="inlineStr">
+        <is>
+          <t>Edileide Dias</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -13066,7 +13164,11 @@
           <t>BLACK KITCHENS ALIMENTOS LTDA</t>
         </is>
       </c>
-      <c r="H152" s="1" t="n"/>
+      <c r="H152" s="1" t="inlineStr">
+        <is>
+          <t>Edileide Dias</t>
+        </is>
+      </c>
       <c r="I152" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -13080,7 +13182,7 @@
       </c>
       <c r="L152" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M152" s="1" t="inlineStr">
@@ -13089,17 +13191,23 @@
         </is>
       </c>
       <c r="N152" s="1" t="n"/>
-      <c r="O152" s="1" t="n"/>
+      <c r="O152" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P152" s="1" t="n"/>
       <c r="Q152" s="1" t="inlineStr"/>
-      <c r="R152" s="1" t="n"/>
+      <c r="R152" s="1" t="inlineStr"/>
       <c r="S152" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T152" s="1" t="n"/>
-      <c r="U152" s="1" t="inlineStr"/>
+      <c r="U152" s="1" t="inlineStr">
+        <is>
+          <t>Edileide Dias</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -15080,7 +15188,7 @@
       </c>
       <c r="L176" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M176" s="1" t="inlineStr">
@@ -15088,12 +15196,20 @@
           <t>Beatriz Rangel</t>
         </is>
       </c>
-      <c r="N176" s="1" t="n"/>
+      <c r="N176" s="2" t="n">
+        <v>46290.65051751157</v>
+      </c>
       <c r="O176" s="2" t="n">
         <v>46294</v>
       </c>
-      <c r="P176" s="1" t="n"/>
-      <c r="Q176" s="1" t="inlineStr"/>
+      <c r="P176" s="2" t="n">
+        <v>46294.64589545139</v>
+      </c>
+      <c r="Q176" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
           <t>Analisando</t>
@@ -15101,7 +15217,7 @@
       </c>
       <c r="S176" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T176" s="1" t="n"/>
@@ -15301,7 +15417,11 @@
           <t>ESPETINHO VILA MARIANA LTDA</t>
         </is>
       </c>
-      <c r="H179" s="1" t="n"/>
+      <c r="H179" s="1" t="inlineStr">
+        <is>
+          <t>Lucas Fischer</t>
+        </is>
+      </c>
       <c r="I179" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -15315,7 +15435,7 @@
       </c>
       <c r="L179" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M179" s="1" t="inlineStr">
@@ -15324,17 +15444,23 @@
         </is>
       </c>
       <c r="N179" s="1" t="n"/>
-      <c r="O179" s="1" t="n"/>
+      <c r="O179" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P179" s="1" t="n"/>
       <c r="Q179" s="1" t="inlineStr"/>
-      <c r="R179" s="1" t="n"/>
+      <c r="R179" s="1" t="inlineStr"/>
       <c r="S179" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T179" s="1" t="n"/>
-      <c r="U179" s="1" t="inlineStr"/>
+      <c r="U179" s="1" t="inlineStr">
+        <is>
+          <t>Lucas Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -15936,7 +16062,11 @@
           <t>OBA OBA MIX LTDA</t>
         </is>
       </c>
-      <c r="H187" s="1" t="n"/>
+      <c r="H187" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I187" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -15950,7 +16080,7 @@
       </c>
       <c r="L187" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M187" s="1" t="inlineStr">
@@ -15959,17 +16089,23 @@
         </is>
       </c>
       <c r="N187" s="1" t="n"/>
-      <c r="O187" s="1" t="n"/>
+      <c r="O187" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P187" s="1" t="n"/>
       <c r="Q187" s="1" t="inlineStr"/>
-      <c r="R187" s="1" t="n"/>
+      <c r="R187" s="1" t="inlineStr"/>
       <c r="S187" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T187" s="1" t="n"/>
-      <c r="U187" s="1" t="inlineStr"/>
+      <c r="U187" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -16488,7 +16624,11 @@
           <t xml:space="preserve">MEGACAR DISTRIBUIDORA AUTOMOTIVA LTDA </t>
         </is>
       </c>
-      <c r="H194" s="1" t="n"/>
+      <c r="H194" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I194" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -16502,7 +16642,7 @@
       </c>
       <c r="L194" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M194" s="1" t="inlineStr">
@@ -16511,17 +16651,33 @@
         </is>
       </c>
       <c r="N194" s="1" t="n"/>
-      <c r="O194" s="1" t="n"/>
-      <c r="P194" s="1" t="n"/>
-      <c r="Q194" s="1" t="inlineStr"/>
-      <c r="R194" s="1" t="n"/>
+      <c r="O194" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="P194" s="2" t="n">
+        <v>46294.65183695602</v>
+      </c>
+      <c r="Q194" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
+      <c r="R194" s="1" t="inlineStr">
+        <is>
+          <t>Foi enviado por email, cliente solicita guias recalculadas ref outros anos mensalmente. ja foi enviado.</t>
+        </is>
+      </c>
       <c r="S194" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T194" s="1" t="n"/>
-      <c r="U194" s="1" t="inlineStr"/>
+      <c r="U194" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -17412,7 +17568,7 @@
       </c>
       <c r="L205" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M205" s="1" t="inlineStr">
@@ -17420,12 +17576,20 @@
           <t>Beatriz Rangel</t>
         </is>
       </c>
-      <c r="N205" s="1" t="n"/>
+      <c r="N205" s="2" t="n">
+        <v>46290.6504658912</v>
+      </c>
       <c r="O205" s="2" t="n">
         <v>46295</v>
       </c>
-      <c r="P205" s="1" t="n"/>
-      <c r="Q205" s="1" t="inlineStr"/>
+      <c r="P205" s="2" t="n">
+        <v>46294.64073244213</v>
+      </c>
+      <c r="Q205" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
           <t>Analisando</t>
@@ -17433,7 +17597,7 @@
       </c>
       <c r="S205" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T205" s="1" t="n"/>
@@ -18750,7 +18914,11 @@
           <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
         </is>
       </c>
-      <c r="H221" s="1" t="n"/>
+      <c r="H221" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
       <c r="I221" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -18764,7 +18932,7 @@
       </c>
       <c r="L221" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M221" s="1" t="inlineStr">
@@ -18773,17 +18941,23 @@
         </is>
       </c>
       <c r="N221" s="1" t="n"/>
-      <c r="O221" s="1" t="n"/>
+      <c r="O221" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P221" s="1" t="n"/>
       <c r="Q221" s="1" t="inlineStr"/>
-      <c r="R221" s="1" t="n"/>
+      <c r="R221" s="1" t="inlineStr"/>
       <c r="S221" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T221" s="1" t="n"/>
-      <c r="U221" s="1" t="inlineStr"/>
+      <c r="U221" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -18817,7 +18991,11 @@
           <t>COMBATEAINCENDIOS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANCA LTDA</t>
         </is>
       </c>
-      <c r="H222" s="1" t="n"/>
+      <c r="H222" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
       <c r="I222" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -18831,7 +19009,7 @@
       </c>
       <c r="L222" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M222" s="1" t="inlineStr">
@@ -18840,17 +19018,23 @@
         </is>
       </c>
       <c r="N222" s="1" t="n"/>
-      <c r="O222" s="1" t="n"/>
+      <c r="O222" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P222" s="1" t="n"/>
       <c r="Q222" s="1" t="inlineStr"/>
-      <c r="R222" s="1" t="n"/>
+      <c r="R222" s="1" t="inlineStr"/>
       <c r="S222" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T222" s="1" t="n"/>
-      <c r="U222" s="1" t="inlineStr"/>
+      <c r="U222" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -20329,7 +20513,7 @@
       </c>
       <c r="L240" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M240" s="1" t="inlineStr">
@@ -20343,8 +20527,14 @@
       <c r="O240" s="2" t="n">
         <v>46295</v>
       </c>
-      <c r="P240" s="1" t="n"/>
-      <c r="Q240" s="1" t="inlineStr"/>
+      <c r="P240" s="2" t="n">
+        <v>46294.64758487268</v>
+      </c>
+      <c r="Q240" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="R240" s="1" t="inlineStr">
         <is>
           <t>Analisando</t>
@@ -20352,7 +20542,7 @@
       </c>
       <c r="S240" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T240" s="1" t="n"/>
@@ -20424,7 +20614,7 @@
         <v>46276.6543150463</v>
       </c>
       <c r="O241" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="P241" s="1" t="n"/>
       <c r="Q241" s="1" t="inlineStr"/>
@@ -64146,7 +64336,7 @@
       </c>
       <c r="L836" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M836" s="1" t="inlineStr">
@@ -64154,7 +64344,9 @@
           <t>Ney Barbosa</t>
         </is>
       </c>
-      <c r="N836" s="1" t="n"/>
+      <c r="N836" s="2" t="n">
+        <v>46294.64554829861</v>
+      </c>
       <c r="O836" s="1" t="n"/>
       <c r="P836" s="1" t="n"/>
       <c r="Q836" s="1" t="inlineStr"/>
@@ -67915,7 +68107,7 @@
       </c>
       <c r="L887" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M887" s="1" t="inlineStr">
@@ -67923,7 +68115,9 @@
           <t>Gabriela Peres</t>
         </is>
       </c>
-      <c r="N887" s="1" t="n"/>
+      <c r="N887" s="2" t="n">
+        <v>46261.69782774305</v>
+      </c>
       <c r="O887" s="2" t="n">
         <v>46297</v>
       </c>
@@ -68071,7 +68265,7 @@
       </c>
       <c r="L889" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M889" s="1" t="inlineStr">
@@ -68079,7 +68273,9 @@
           <t>Gabriela Peres</t>
         </is>
       </c>
-      <c r="N889" s="1" t="n"/>
+      <c r="N889" s="2" t="n">
+        <v>46261.69765454861</v>
+      </c>
       <c r="O889" s="2" t="n">
         <v>46283</v>
       </c>
@@ -68148,7 +68344,7 @@
       </c>
       <c r="L890" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M890" s="1" t="inlineStr">
@@ -68156,7 +68352,9 @@
           <t>Gabriela Peres</t>
         </is>
       </c>
-      <c r="N890" s="1" t="n"/>
+      <c r="N890" s="2" t="n">
+        <v>46261.69723422454</v>
+      </c>
       <c r="O890" s="2" t="n">
         <v>46283</v>
       </c>
@@ -68225,7 +68423,7 @@
       </c>
       <c r="L891" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M891" s="1" t="inlineStr">
@@ -68233,7 +68431,9 @@
           <t>Gabriela Peres</t>
         </is>
       </c>
-      <c r="N891" s="1" t="n"/>
+      <c r="N891" s="2" t="n">
+        <v>46259.7507258449</v>
+      </c>
       <c r="O891" s="2" t="n">
         <v>46297</v>
       </c>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -11250,7 +11250,11 @@
           <t>RJR INDUSTRIA DE ALIMENTOS LTDA</t>
         </is>
       </c>
-      <c r="H129" s="1" t="n"/>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -11264,7 +11268,7 @@
       </c>
       <c r="L129" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M129" s="1" t="inlineStr">
@@ -11273,17 +11277,23 @@
         </is>
       </c>
       <c r="N129" s="1" t="n"/>
-      <c r="O129" s="1" t="n"/>
+      <c r="O129" s="2" t="n">
+        <v>46295</v>
+      </c>
       <c r="P129" s="1" t="n"/>
       <c r="Q129" s="1" t="inlineStr"/>
-      <c r="R129" s="1" t="n"/>
+      <c r="R129" s="1" t="inlineStr"/>
       <c r="S129" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T129" s="1" t="n"/>
-      <c r="U129" s="1" t="inlineStr"/>
+      <c r="U129" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -16141,7 +16151,11 @@
           <t>OBA OBA MIX LTDA</t>
         </is>
       </c>
-      <c r="H188" s="1" t="n"/>
+      <c r="H188" s="1" t="inlineStr">
+        <is>
+          <t>Kaique Souza</t>
+        </is>
+      </c>
       <c r="I188" s="1" t="inlineStr">
         <is>
           <t>DP - DEPTO. PESSOAL</t>
@@ -16155,7 +16169,7 @@
       </c>
       <c r="L188" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M188" s="1" t="inlineStr">
@@ -16163,18 +16177,28 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N188" s="1" t="n"/>
+      <c r="N188" s="2" t="n">
+        <v>46294.75443252315</v>
+      </c>
       <c r="O188" s="1" t="n"/>
       <c r="P188" s="1" t="n"/>
       <c r="Q188" s="1" t="inlineStr"/>
-      <c r="R188" s="1" t="n"/>
+      <c r="R188" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento.</t>
+        </is>
+      </c>
       <c r="S188" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T188" s="1" t="n"/>
-      <c r="U188" s="1" t="inlineStr"/>
+      <c r="U188" s="1" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -18166,7 +18190,7 @@
       </c>
       <c r="I212" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J212" s="2" t="n">
@@ -18177,7 +18201,7 @@
       </c>
       <c r="L212" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M212" s="1" t="inlineStr">
@@ -18199,7 +18223,11 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T212" s="1" t="n"/>
+      <c r="T212" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
       <c r="U212" s="1" t="inlineStr">
         <is>
           <t>Sara Cavalheiro</t>
@@ -61287,7 +61315,7 @@
       </c>
       <c r="L796" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M796" s="1" t="inlineStr">
@@ -61299,7 +61327,12 @@
       <c r="O796" s="1" t="n"/>
       <c r="P796" s="1" t="n"/>
       <c r="Q796" s="1" t="inlineStr"/>
-      <c r="R796" s="1" t="inlineStr"/>
+      <c r="R796" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boa tarde!
+As guias são recalculadas para o dia, verifique com o cliente quando ele deseja efetuar o pagamento, que enviaremos as guias no primeiro horario. </t>
+        </is>
+      </c>
       <c r="S796" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -9843,7 +9843,11 @@
           <t>YARA DESIGN E DECORAÇÃO LTDA</t>
         </is>
       </c>
-      <c r="H112" s="1" t="n"/>
+      <c r="H112" s="1" t="inlineStr">
+        <is>
+          <t>Eveny Silva</t>
+        </is>
+      </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -9857,7 +9861,7 @@
       </c>
       <c r="L112" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M112" s="1" t="inlineStr">
@@ -9869,14 +9873,18 @@
       <c r="O112" s="1" t="n"/>
       <c r="P112" s="1" t="n"/>
       <c r="Q112" s="1" t="inlineStr"/>
-      <c r="R112" s="1" t="n"/>
+      <c r="R112" s="1" t="inlineStr"/>
       <c r="S112" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T112" s="1" t="n"/>
-      <c r="U112" s="1" t="inlineStr"/>
+      <c r="U112" s="1" t="inlineStr">
+        <is>
+          <t>Karina Fonseca</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -13768,7 +13776,7 @@
       </c>
       <c r="L159" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M159" s="1" t="inlineStr">
@@ -13778,12 +13786,22 @@
       </c>
       <c r="N159" s="1" t="n"/>
       <c r="O159" s="1" t="n"/>
-      <c r="P159" s="1" t="n"/>
-      <c r="Q159" s="1" t="inlineStr"/>
-      <c r="R159" s="1" t="inlineStr"/>
+      <c r="P159" s="2" t="n">
+        <v>46308.53981504629</v>
+      </c>
+      <c r="Q159" s="1" t="inlineStr">
+        <is>
+          <t>Eveny Silva</t>
+        </is>
+      </c>
+      <c r="R159" s="1" t="inlineStr">
+        <is>
+          <t>Despesas de agosto verificadas. Aguardando financeiro referente ao mês 09.</t>
+        </is>
+      </c>
       <c r="S159" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T159" s="1" t="n"/>
